--- a/RR_ISRU.xlsx
+++ b/RR_ISRU.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitHub\RationalResources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\GitHub\RationalResources\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="235">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="241">
   <si>
     <t>Resource</t>
   </si>
@@ -764,14 +764,32 @@
     <t>Cycle</t>
   </si>
   <si>
-    <t>Units</t>
+    <t>C60</t>
+  </si>
+  <si>
+    <t>Octaazacubane</t>
+  </si>
+  <si>
+    <t>N8+Ar6</t>
+  </si>
+  <si>
+    <t>LithiumSaltWater</t>
+  </si>
+  <si>
+    <t>LiD + 8(H2O)</t>
+  </si>
+  <si>
+    <t>Buckminsterfullerene</t>
+  </si>
+  <si>
+    <t>units</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <numFmts count="8">
+  <numFmts count="9">
     <numFmt numFmtId="164" formatCode="#,##0.00\ &quot;kg/mol&quot;"/>
     <numFmt numFmtId="165" formatCode="#,##0.000\ &quot;kg/unit&quot;"/>
     <numFmt numFmtId="166" formatCode="#,##0.00\ &quot;g/mol&quot;"/>
@@ -780,6 +798,7 @@
     <numFmt numFmtId="169" formatCode="0.0000000"/>
     <numFmt numFmtId="170" formatCode="0.00000"/>
     <numFmt numFmtId="171" formatCode="#,##0.0000&quot;:1&quot;"/>
+    <numFmt numFmtId="172" formatCode="0.000"/>
   </numFmts>
   <fonts count="16" x14ac:knownFonts="1">
     <font>
@@ -1006,7 +1025,7 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="47">
+  <cellXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1087,17 +1106,20 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="4" xfId="6"/>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="2" xfId="3" applyNumberFormat="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="3"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="3" applyAlignment="1"/>
+    <xf numFmtId="172" fontId="5" fillId="4" borderId="1" xfId="2" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="4" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="3" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="4" xfId="6"/>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="2" xfId="3" applyNumberFormat="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="3"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="3" applyAlignment="1"/>
+    <xf numFmtId="11" fontId="4" fillId="3" borderId="1" xfId="1" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="1" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="9">
     <cellStyle name="Calculation" xfId="2" builtinId="22"/>
@@ -1126,7 +1148,7 @@
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Green Yellow">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1134,34 +1156,34 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="44546A"/>
+        <a:srgbClr val="455F51"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="E7E6E6"/>
+        <a:srgbClr val="E2DFCC"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4472C4"/>
+        <a:srgbClr val="99CB38"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="ED7D31"/>
+        <a:srgbClr val="63A537"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="A5A5A5"/>
+        <a:srgbClr val="37A76F"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="FFC000"/>
+        <a:srgbClr val="44C1A3"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="5B9BD5"/>
+        <a:srgbClr val="4EB3CF"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="70AD47"/>
+        <a:srgbClr val="51C3F9"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0563C1"/>
+        <a:srgbClr val="EE7B08"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="954F72"/>
+        <a:srgbClr val="977B2D"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
@@ -1429,15 +1451,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="20.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="40" t="s">
+      <c r="A1" s="46" t="s">
         <v>92</v>
       </c>
-      <c r="B1" s="40"/>
-      <c r="C1" s="40"/>
-      <c r="D1" s="40"/>
-      <c r="E1" s="40"/>
-      <c r="F1" s="40"/>
-      <c r="G1" s="40"/>
+      <c r="B1" s="46"/>
+      <c r="C1" s="46"/>
+      <c r="D1" s="46"/>
+      <c r="E1" s="46"/>
+      <c r="F1" s="46"/>
+      <c r="G1" s="46"/>
     </row>
     <row r="2" spans="1:12" ht="16.5" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A2" s="27" t="s">
@@ -1455,27 +1477,27 @@
       </c>
     </row>
     <row r="5" spans="1:12" ht="18" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="44" t="s">
+      <c r="A5" s="42" t="s">
         <v>66</v>
       </c>
-      <c r="B5" s="44"/>
-      <c r="C5" s="44"/>
-      <c r="D5" s="44"/>
-      <c r="E5" s="44"/>
-      <c r="F5" s="44"/>
-      <c r="G5" s="44"/>
-      <c r="H5" s="45"/>
-      <c r="I5" s="45"/>
-      <c r="J5" s="45"/>
-      <c r="K5" s="45"/>
-      <c r="L5" s="45"/>
+      <c r="B5" s="42"/>
+      <c r="C5" s="42"/>
+      <c r="D5" s="42"/>
+      <c r="E5" s="42"/>
+      <c r="F5" s="42"/>
+      <c r="G5" s="42"/>
+      <c r="H5" s="43"/>
+      <c r="I5" s="43"/>
+      <c r="J5" s="43"/>
+      <c r="K5" s="43"/>
+      <c r="L5" s="43"/>
     </row>
     <row r="6" spans="1:12" ht="16.5" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A6" s="25" t="s">
         <v>90</v>
       </c>
-      <c r="B6" s="18">
-        <v>0.01</v>
+      <c r="B6" s="49">
+        <v>0</v>
       </c>
       <c r="C6" s="18">
         <v>0</v>
@@ -1510,9 +1532,7 @@
       <c r="A7" s="7" t="s">
         <v>96</v>
       </c>
-      <c r="B7" s="26" t="s">
-        <v>49</v>
-      </c>
+      <c r="B7" s="26"/>
       <c r="C7" s="26"/>
       <c r="D7" s="26"/>
       <c r="E7" s="26"/>
@@ -1525,7 +1545,7 @@
         <v>1</v>
       </c>
       <c r="K7" s="27" t="s">
-        <v>234</v>
+        <v>240</v>
       </c>
       <c r="L7" s="19">
         <f>IF(J8&gt;0,L6-(J8*3600),0)</f>
@@ -1536,34 +1556,34 @@
       <c r="A8" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="B8" s="21">
-        <f>IFERROR(VLOOKUP(B7,Database!$A$2:$E$135,5,FALSE),"-")</f>
-        <v>10</v>
+      <c r="B8" s="21" t="str">
+        <f>IFERROR(VLOOKUP(B7,Database!$A$3:$E$139,5,FALSE),"-")</f>
+        <v>-</v>
       </c>
       <c r="C8" s="21" t="str">
-        <f>IFERROR(VLOOKUP(C7,Database!$A$2:$E$135,5,FALSE),"-")</f>
+        <f>IFERROR(VLOOKUP(C7,Database!$A$3:$E$139,5,FALSE),"-")</f>
         <v>-</v>
       </c>
       <c r="D8" s="21" t="str">
-        <f>IFERROR(VLOOKUP(D7,Database!$A$2:$E$135,5,FALSE),"-")</f>
+        <f>IFERROR(VLOOKUP(D7,Database!$A$3:$E$139,5,FALSE),"-")</f>
         <v>-</v>
       </c>
       <c r="E8" s="21" t="str">
-        <f>IFERROR(VLOOKUP(E7,Database!$A$2:$E$135,5,FALSE),"-")</f>
+        <f>IFERROR(VLOOKUP(E7,Database!$A$3:$E$139,5,FALSE),"-")</f>
         <v>-</v>
       </c>
       <c r="F8" s="21" t="str">
-        <f>IFERROR(VLOOKUP(F7,Database!$A$2:$E$135,5,FALSE),"-")</f>
+        <f>IFERROR(VLOOKUP(F7,Database!$A$3:$E$139,5,FALSE),"-")</f>
         <v>-</v>
       </c>
       <c r="G8" s="21" t="str">
-        <f>IFERROR(VLOOKUP(G7,Database!$A$2:$E$135,5,FALSE),"-")</f>
-        <v>-</v>
-      </c>
-      <c r="I8" s="42" t="s">
+        <f>IFERROR(VLOOKUP(G7,Database!$A$3:$E$139,5,FALSE),"-")</f>
+        <v>-</v>
+      </c>
+      <c r="I8" s="40" t="s">
         <v>233</v>
       </c>
-      <c r="J8" s="43">
+      <c r="J8" s="41">
         <f>ROUNDDOWN(IF(L6&gt;3600,L6/3600,0),0)</f>
         <v>0</v>
       </c>
@@ -1579,9 +1599,9 @@
       <c r="A9" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="B9" s="24">
+      <c r="B9" s="24" t="str">
         <f t="shared" ref="B9:G9" si="0">IFERROR(B6*B8,"-")</f>
-        <v>0.1</v>
+        <v>-</v>
       </c>
       <c r="C9" s="24" t="str">
         <f t="shared" si="0"/>
@@ -1603,7 +1623,7 @@
         <f t="shared" si="0"/>
         <v>-</v>
       </c>
-      <c r="J9" s="43">
+      <c r="J9" s="41">
         <f>IF(L8&lt;60,L8,0)</f>
         <v>0</v>
       </c>
@@ -1621,14 +1641,14 @@
       </c>
       <c r="B10" s="32">
         <f>SUM(B9:G9)</f>
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="C10" s="28"/>
       <c r="D10" s="28"/>
       <c r="E10" s="28"/>
       <c r="F10" s="28"/>
       <c r="G10" s="28"/>
-      <c r="J10" s="43">
+      <c r="J10" s="41">
         <f>IF(L9&gt;0,L9,0)</f>
         <v>1</v>
       </c>
@@ -1637,31 +1657,30 @@
       </c>
     </row>
     <row r="13" spans="1:12" ht="18" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="44" t="s">
+      <c r="A13" s="42" t="s">
         <v>67</v>
       </c>
-      <c r="B13" s="44"/>
-      <c r="C13" s="44"/>
-      <c r="D13" s="44"/>
-      <c r="E13" s="44"/>
-      <c r="F13" s="44"/>
-      <c r="G13" s="44"/>
-      <c r="H13" s="45"/>
-      <c r="I13" s="45"/>
-      <c r="J13" s="45"/>
-      <c r="K13" s="45"/>
-      <c r="L13" s="45"/>
+      <c r="B13" s="42"/>
+      <c r="C13" s="42"/>
+      <c r="D13" s="42"/>
+      <c r="E13" s="42"/>
+      <c r="F13" s="42"/>
+      <c r="G13" s="42"/>
+      <c r="H13" s="43"/>
+      <c r="I13" s="43"/>
+      <c r="J13" s="43"/>
+      <c r="K13" s="43"/>
+      <c r="L13" s="43"/>
     </row>
     <row r="14" spans="1:12" ht="16.5" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A14" s="25" t="s">
         <v>90</v>
       </c>
-      <c r="B14" s="18">
-        <v>8.9999999999999993E-3</v>
+      <c r="B14" s="48">
+        <v>0</v>
       </c>
       <c r="C14" s="18">
-        <f>B14*1.222</f>
-        <v>1.0997999999999999E-2</v>
+        <v>0</v>
       </c>
       <c r="D14" s="18">
         <v>0</v>
@@ -1693,12 +1712,8 @@
       <c r="A15" s="7" t="s">
         <v>96</v>
       </c>
-      <c r="B15" s="26" t="s">
-        <v>5</v>
-      </c>
-      <c r="C15" s="26" t="s">
-        <v>7</v>
-      </c>
+      <c r="B15" s="26"/>
+      <c r="C15" s="26"/>
       <c r="D15" s="26"/>
       <c r="E15" s="26"/>
       <c r="F15" s="26"/>
@@ -1710,7 +1725,7 @@
         <v>1</v>
       </c>
       <c r="K15" s="27" t="s">
-        <v>234</v>
+        <v>240</v>
       </c>
       <c r="L15" s="19">
         <f>IF(J16&gt;0,L14-(J16*3600),0)</f>
@@ -1721,34 +1736,34 @@
       <c r="A16" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="B16" s="21">
-        <f>IFERROR(VLOOKUP(B15,Database!$A$2:$E$135,5,FALSE),"-")</f>
-        <v>5</v>
-      </c>
-      <c r="C16" s="21">
-        <f>IFERROR(VLOOKUP(C15,Database!$A$2:$E$135,5,FALSE),"-")</f>
-        <v>5</v>
+      <c r="B16" s="21" t="str">
+        <f>IFERROR(VLOOKUP(B15,Database!$A$3:$E$139,5,FALSE),"-")</f>
+        <v>-</v>
+      </c>
+      <c r="C16" s="21" t="str">
+        <f>IFERROR(VLOOKUP(C15,Database!$A$3:$E$139,5,FALSE),"-")</f>
+        <v>-</v>
       </c>
       <c r="D16" s="21" t="str">
-        <f>IFERROR(VLOOKUP(D15,Database!$A$2:$E$135,5,FALSE),"-")</f>
+        <f>IFERROR(VLOOKUP(D15,Database!$A$3:$E$139,5,FALSE),"-")</f>
         <v>-</v>
       </c>
       <c r="E16" s="21" t="str">
-        <f>IFERROR(VLOOKUP(E15,Database!$A$2:$E$135,5,FALSE),"-")</f>
+        <f>IFERROR(VLOOKUP(E15,Database!$A$3:$E$139,5,FALSE),"-")</f>
         <v>-</v>
       </c>
       <c r="F16" s="21" t="str">
-        <f>IFERROR(VLOOKUP(F15,Database!$A$2:$E$135,5,FALSE),"-")</f>
+        <f>IFERROR(VLOOKUP(F15,Database!$A$3:$E$139,5,FALSE),"-")</f>
         <v>-</v>
       </c>
       <c r="G16" s="21" t="str">
-        <f>IFERROR(VLOOKUP(G15,Database!$A$2:$E$135,5,FALSE),"-")</f>
-        <v>-</v>
-      </c>
-      <c r="I16" s="42" t="s">
+        <f>IFERROR(VLOOKUP(G15,Database!$A$3:$E$139,5,FALSE),"-")</f>
+        <v>-</v>
+      </c>
+      <c r="I16" s="40" t="s">
         <v>233</v>
       </c>
-      <c r="J16" s="43">
+      <c r="J16" s="41">
         <f>ROUNDDOWN(IF(L14&gt;3600,L14/3600,0),0)</f>
         <v>0</v>
       </c>
@@ -1764,13 +1779,13 @@
       <c r="A17" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="B17" s="31">
+      <c r="B17" s="31" t="str">
         <f t="shared" ref="B17:G17" si="1">IFERROR(B14*B16,"-")</f>
-        <v>4.4999999999999998E-2</v>
-      </c>
-      <c r="C17" s="24">
+        <v>-</v>
+      </c>
+      <c r="C17" s="24" t="str">
         <f t="shared" si="1"/>
-        <v>5.4989999999999997E-2</v>
+        <v>-</v>
       </c>
       <c r="D17" s="31" t="str">
         <f t="shared" si="1"/>
@@ -1788,7 +1803,7 @@
         <f t="shared" si="1"/>
         <v>-</v>
       </c>
-      <c r="J17" s="43">
+      <c r="J17" s="41">
         <f>IF(L16&lt;60,L16,0)</f>
         <v>0</v>
       </c>
@@ -1806,14 +1821,14 @@
       </c>
       <c r="B18" s="32">
         <f>SUM(B17:G17)</f>
-        <v>9.9989999999999996E-2</v>
+        <v>0</v>
       </c>
       <c r="C18" s="28"/>
       <c r="D18" s="28"/>
       <c r="E18" s="28"/>
       <c r="F18" s="28"/>
       <c r="G18" s="28"/>
-      <c r="J18" s="43">
+      <c r="J18" s="41">
         <f>IF(L17&gt;0,L17,0)</f>
         <v>1</v>
       </c>
@@ -1822,15 +1837,15 @@
       </c>
     </row>
     <row r="20" spans="1:12" ht="18" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="41" t="s">
+      <c r="A20" s="47" t="s">
         <v>71</v>
       </c>
-      <c r="B20" s="41"/>
-      <c r="C20" s="41"/>
-      <c r="D20" s="41"/>
-      <c r="E20" s="41"/>
-      <c r="F20" s="41"/>
-      <c r="G20" s="41"/>
+      <c r="B20" s="47"/>
+      <c r="C20" s="47"/>
+      <c r="D20" s="47"/>
+      <c r="E20" s="47"/>
+      <c r="F20" s="47"/>
+      <c r="G20" s="47"/>
     </row>
     <row r="21" spans="1:12" ht="16.5" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A21" s="7" t="s">
@@ -1838,11 +1853,11 @@
       </c>
       <c r="B21" s="20" t="str">
         <f>IF($B$10&gt;$B$18,"Input excesive",IF($B$10&lt;$B$18,"Output excessive","Equal"))</f>
-        <v>Input excesive</v>
+        <v>Equal</v>
       </c>
       <c r="C21" s="33">
         <f>IF($B$10&gt;$B$18,B10/B18,IF($B$10&lt;$B$18,B18/B10,1))</f>
-        <v>1.0001000100010002</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.25">
@@ -1856,10 +1871,10 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" disablePrompts="1" count="1">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
-            <xm:f>Database!$A$2:$A$135</xm:f>
+            <xm:f>Database!$A$3:$A$139</xm:f>
           </x14:formula1>
           <xm:sqref>B7:G7 B15:G15</xm:sqref>
         </x14:dataValidation>
@@ -1878,15 +1893,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="20.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="40" t="s">
+      <c r="A1" s="46" t="s">
         <v>91</v>
       </c>
-      <c r="B1" s="40"/>
-      <c r="C1" s="40"/>
-      <c r="D1" s="40"/>
-      <c r="E1" s="40"/>
-      <c r="F1" s="40"/>
-      <c r="G1" s="40"/>
+      <c r="B1" s="46"/>
+      <c r="C1" s="46"/>
+      <c r="D1" s="46"/>
+      <c r="E1" s="46"/>
+      <c r="F1" s="46"/>
+      <c r="G1" s="46"/>
     </row>
     <row r="2" spans="1:7" ht="16.5" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A2" s="27" t="s">
@@ -1904,15 +1919,15 @@
       </c>
     </row>
     <row r="5" spans="1:7" ht="18" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="44" t="s">
+      <c r="A5" s="42" t="s">
         <v>66</v>
       </c>
-      <c r="B5" s="44"/>
-      <c r="C5" s="44"/>
-      <c r="D5" s="44"/>
-      <c r="E5" s="44"/>
-      <c r="F5" s="44"/>
-      <c r="G5" s="44"/>
+      <c r="B5" s="42"/>
+      <c r="C5" s="42"/>
+      <c r="D5" s="42"/>
+      <c r="E5" s="42"/>
+      <c r="F5" s="42"/>
+      <c r="G5" s="42"/>
     </row>
     <row r="6" spans="1:7" ht="16.5" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
@@ -1953,27 +1968,27 @@
         <v>88</v>
       </c>
       <c r="B8" s="21" t="str">
-        <f>IFERROR(VLOOKUP(B7,Database!$A$2:$E$97,4,FALSE),"-")</f>
+        <f>IFERROR(VLOOKUP(B7,Database!$A$3:$E$101,4,FALSE),"-")</f>
         <v>-</v>
       </c>
       <c r="C8" s="21" t="str">
-        <f>IFERROR(VLOOKUP(C7,Database!$A$2:$E$97,4,FALSE),"-")</f>
+        <f>IFERROR(VLOOKUP(C7,Database!$A$3:$E$101,4,FALSE),"-")</f>
         <v>-</v>
       </c>
       <c r="D8" s="21" t="str">
-        <f>IFERROR(VLOOKUP(D7,Database!$A$2:$E$97,4,FALSE),"-")</f>
+        <f>IFERROR(VLOOKUP(D7,Database!$A$3:$E$101,4,FALSE),"-")</f>
         <v>-</v>
       </c>
       <c r="E8" s="21" t="str">
-        <f>IFERROR(VLOOKUP(E7,Database!$A$2:$E$97,4,FALSE),"-")</f>
+        <f>IFERROR(VLOOKUP(E7,Database!$A$3:$E$101,4,FALSE),"-")</f>
         <v>-</v>
       </c>
       <c r="F8" s="21" t="str">
-        <f>IFERROR(VLOOKUP(F7,Database!$A$2:$E$97,4,FALSE),"-")</f>
+        <f>IFERROR(VLOOKUP(F7,Database!$A$3:$E$101,4,FALSE),"-")</f>
         <v>-</v>
       </c>
       <c r="G8" s="21" t="str">
-        <f>IFERROR(VLOOKUP(G7,Database!$A$2:$E$97,4,FALSE),"-")</f>
+        <f>IFERROR(VLOOKUP(G7,Database!$A$3:$E$101,4,FALSE),"-")</f>
         <v>-</v>
       </c>
     </row>
@@ -1982,27 +1997,27 @@
         <v>93</v>
       </c>
       <c r="B9" s="21" t="str">
-        <f>IFERROR(VLOOKUP(B7,Database!$A$2:$E$97,5,FALSE),"-")</f>
+        <f>IFERROR(VLOOKUP(B7,Database!$A$3:$E$101,5,FALSE),"-")</f>
         <v>-</v>
       </c>
       <c r="C9" s="21" t="str">
-        <f>IFERROR(VLOOKUP(C7,Database!$A$2:$E$97,5,FALSE),"-")</f>
+        <f>IFERROR(VLOOKUP(C7,Database!$A$3:$E$101,5,FALSE),"-")</f>
         <v>-</v>
       </c>
       <c r="D9" s="21" t="str">
-        <f>IFERROR(VLOOKUP(D7,Database!$A$2:$E$97,5,FALSE),"-")</f>
+        <f>IFERROR(VLOOKUP(D7,Database!$A$3:$E$101,5,FALSE),"-")</f>
         <v>-</v>
       </c>
       <c r="E9" s="21" t="str">
-        <f>IFERROR(VLOOKUP(E7,Database!$A$2:$E$97,5,FALSE),"-")</f>
+        <f>IFERROR(VLOOKUP(E7,Database!$A$3:$E$101,5,FALSE),"-")</f>
         <v>-</v>
       </c>
       <c r="F9" s="21" t="str">
-        <f>IFERROR(VLOOKUP(F7,Database!$A$2:$E$97,5,FALSE),"-")</f>
+        <f>IFERROR(VLOOKUP(F7,Database!$A$3:$E$101,5,FALSE),"-")</f>
         <v>-</v>
       </c>
       <c r="G9" s="21" t="str">
-        <f>IFERROR(VLOOKUP(G7,Database!$A$2:$E$97,5,FALSE),"-")</f>
+        <f>IFERROR(VLOOKUP(G7,Database!$A$3:$E$101,5,FALSE),"-")</f>
         <v>-</v>
       </c>
     </row>
@@ -2010,11 +2025,11 @@
       <c r="A10" s="7" t="s">
         <v>89</v>
       </c>
-      <c r="B10" s="19">
+      <c r="B10" s="45">
         <f>IFERROR(B6*B8,0)</f>
         <v>0</v>
       </c>
-      <c r="C10" s="19" t="str">
+      <c r="C10" s="45" t="str">
         <f>IFERROR(C6*C8,"-")</f>
         <v>-</v>
       </c>
@@ -2074,15 +2089,15 @@
       </c>
     </row>
     <row r="14" spans="1:7" ht="18" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="44" t="s">
+      <c r="A14" s="42" t="s">
         <v>67</v>
       </c>
-      <c r="B14" s="44"/>
-      <c r="C14" s="44"/>
-      <c r="D14" s="44"/>
-      <c r="E14" s="44"/>
-      <c r="F14" s="44"/>
-      <c r="G14" s="44"/>
+      <c r="B14" s="42"/>
+      <c r="C14" s="42"/>
+      <c r="D14" s="42"/>
+      <c r="E14" s="42"/>
+      <c r="F14" s="42"/>
+      <c r="G14" s="42"/>
     </row>
     <row r="15" spans="1:7" ht="16.5" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
@@ -2123,27 +2138,27 @@
         <v>88</v>
       </c>
       <c r="B17" s="21" t="str">
-        <f>IFERROR(VLOOKUP(B16,Database!$A$2:$E$97,4,FALSE),"-")</f>
+        <f>IFERROR(VLOOKUP(B16,Database!$A$3:$E$101,4,FALSE),"-")</f>
         <v>-</v>
       </c>
       <c r="C17" s="21" t="str">
-        <f>IFERROR(VLOOKUP(C16,Database!$A$2:$E$97,4,FALSE),"-")</f>
+        <f>IFERROR(VLOOKUP(C16,Database!$A$3:$E$101,4,FALSE),"-")</f>
         <v>-</v>
       </c>
       <c r="D17" s="21" t="str">
-        <f>IFERROR(VLOOKUP(D16,Database!$A$2:$E$97,4,FALSE),"-")</f>
+        <f>IFERROR(VLOOKUP(D16,Database!$A$3:$E$101,4,FALSE),"-")</f>
         <v>-</v>
       </c>
       <c r="E17" s="21" t="str">
-        <f>IFERROR(VLOOKUP(E16,Database!$A$2:$E$97,4,FALSE),"-")</f>
+        <f>IFERROR(VLOOKUP(E16,Database!$A$3:$E$101,4,FALSE),"-")</f>
         <v>-</v>
       </c>
       <c r="F17" s="21" t="str">
-        <f>IFERROR(VLOOKUP(F16,Database!$A$2:$E$97,4,FALSE),"-")</f>
+        <f>IFERROR(VLOOKUP(F16,Database!$A$3:$E$101,4,FALSE),"-")</f>
         <v>-</v>
       </c>
       <c r="G17" s="21" t="str">
-        <f>IFERROR(VLOOKUP(G16,Database!$A$2:$E$97,4,FALSE),"-")</f>
+        <f>IFERROR(VLOOKUP(G16,Database!$A$3:$E$101,4,FALSE),"-")</f>
         <v>-</v>
       </c>
     </row>
@@ -2152,27 +2167,27 @@
         <v>93</v>
       </c>
       <c r="B18" s="21" t="str">
-        <f>IFERROR(VLOOKUP(B16,Database!$A$2:$E$97,5,FALSE),"-")</f>
+        <f>IFERROR(VLOOKUP(B16,Database!$A$3:$E$101,5,FALSE),"-")</f>
         <v>-</v>
       </c>
       <c r="C18" s="21" t="str">
-        <f>IFERROR(VLOOKUP(C16,Database!$A$2:$E$97,5,FALSE),"-")</f>
+        <f>IFERROR(VLOOKUP(C16,Database!$A$3:$E$101,5,FALSE),"-")</f>
         <v>-</v>
       </c>
       <c r="D18" s="21" t="str">
-        <f>IFERROR(VLOOKUP(D16,Database!$A$2:$E$97,5,FALSE),"-")</f>
+        <f>IFERROR(VLOOKUP(D16,Database!$A$3:$E$101,5,FALSE),"-")</f>
         <v>-</v>
       </c>
       <c r="E18" s="21" t="str">
-        <f>IFERROR(VLOOKUP(E16,Database!$A$2:$E$97,5,FALSE),"-")</f>
+        <f>IFERROR(VLOOKUP(E16,Database!$A$3:$E$101,5,FALSE),"-")</f>
         <v>-</v>
       </c>
       <c r="F18" s="21" t="str">
-        <f>IFERROR(VLOOKUP(F16,Database!$A$2:$E$97,5,FALSE),"-")</f>
+        <f>IFERROR(VLOOKUP(F16,Database!$A$3:$E$101,5,FALSE),"-")</f>
         <v>-</v>
       </c>
       <c r="G18" s="21" t="str">
-        <f>IFERROR(VLOOKUP(G16,Database!$A$2:$E$97,5,FALSE),"-")</f>
+        <f>IFERROR(VLOOKUP(G16,Database!$A$3:$E$101,5,FALSE),"-")</f>
         <v>-</v>
       </c>
     </row>
@@ -2247,15 +2262,15 @@
       <c r="A22" s="7"/>
     </row>
     <row r="23" spans="1:7" ht="18" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="46" t="s">
+      <c r="A23" s="44" t="s">
         <v>71</v>
       </c>
-      <c r="B23" s="46"/>
-      <c r="C23" s="46"/>
-      <c r="D23" s="46"/>
-      <c r="E23" s="46"/>
-      <c r="F23" s="46"/>
-      <c r="G23" s="46"/>
+      <c r="B23" s="44"/>
+      <c r="C23" s="44"/>
+      <c r="D23" s="44"/>
+      <c r="E23" s="44"/>
+      <c r="F23" s="44"/>
+      <c r="G23" s="44"/>
     </row>
     <row r="24" spans="1:7" ht="16.5" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A24" s="7" t="s">
@@ -2283,13 +2298,13 @@
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
-            <xm:f>Database!$A$2:$A$135</xm:f>
+            <xm:f>Database!$A$3:$A$139</xm:f>
           </x14:formula1>
           <xm:sqref>B16:G16</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
-            <xm:f>Database!$A$2:$A$135</xm:f>
+            <xm:f>Database!$A$3:$A$139</xm:f>
           </x14:formula1>
           <xm:sqref>B7:G7</xm:sqref>
         </x14:dataValidation>
@@ -2301,7 +2316,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L135"/>
+  <dimension ref="A1:L139"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.5" customWidth="1"/>
@@ -2311,6 +2326,7 @@
     <col min="5" max="5" width="18.125" customWidth="1"/>
     <col min="6" max="6" width="19" customWidth="1"/>
     <col min="7" max="7" width="11.625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="47.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -2333,2501 +2349,2590 @@
         <v>212</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
+    <row r="2" spans="1:12" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="1"/>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B3" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="C2" s="1">
-        <v>1</v>
-      </c>
-      <c r="D2" s="5">
+      <c r="C3" s="1">
+        <v>1</v>
+      </c>
+      <c r="D3" s="5">
         <v>207.2</v>
       </c>
-      <c r="E2" s="4">
+      <c r="E3" s="4">
         <f>0.01*1000</f>
         <v>10</v>
       </c>
-      <c r="F2" s="6">
-        <f>C2*D2/(E2 * 1000)</f>
+      <c r="F3" s="6">
+        <f>C3*D3/(E3 * 1000)</f>
         <v>2.0719999999999999E-2</v>
       </c>
-      <c r="G2" s="8"/>
-      <c r="I2" t="s">
+      <c r="G3" s="8"/>
+      <c r="I3" t="s">
         <v>0</v>
       </c>
-      <c r="J2" t="s">
+      <c r="J3" t="s">
         <v>83</v>
       </c>
-      <c r="K2" t="s">
+      <c r="K3" t="s">
         <v>84</v>
       </c>
-      <c r="L2" t="s">
+      <c r="L3" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B4" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="1">
-        <v>1</v>
-      </c>
-      <c r="D3" s="5">
+      <c r="C4" s="1">
+        <v>1</v>
+      </c>
+      <c r="D4" s="5">
         <v>170.34</v>
       </c>
-      <c r="E3" s="4">
+      <c r="E4" s="4">
         <f>0.005*1000</f>
         <v>5</v>
       </c>
-      <c r="F3" s="6">
-        <f>C3*D3/(E3 * 1000)</f>
+      <c r="F4" s="6">
+        <f>C4*D4/(E4 * 1000)</f>
         <v>3.4068000000000001E-2</v>
       </c>
-      <c r="I3" t="s">
+      <c r="I4" t="s">
         <v>77</v>
       </c>
-      <c r="J3" t="s">
+      <c r="J4" t="s">
         <v>78</v>
       </c>
-      <c r="K3">
+      <c r="K4">
         <v>117.49</v>
       </c>
-      <c r="L3" s="22">
+      <c r="L4" s="22">
         <v>0.69599999999999995</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A4" s="13" t="s">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A5" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="13" t="s">
+      <c r="B5" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="C4" s="13">
-        <v>1</v>
-      </c>
-      <c r="D4" s="14">
+      <c r="C5" s="13">
+        <v>1</v>
+      </c>
+      <c r="D5" s="14">
         <f>16*2</f>
         <v>32</v>
       </c>
-      <c r="E4" s="15">
+      <c r="E5" s="15">
         <f>0.005*1000</f>
         <v>5</v>
       </c>
-      <c r="F4" s="16">
-        <f>C4*D4/(E4 * 1000)</f>
+      <c r="F5" s="16">
+        <f>C5*D5/(E5 * 1000)</f>
         <v>6.4000000000000003E-3</v>
       </c>
-      <c r="I4" t="s">
+      <c r="I5" t="s">
         <v>79</v>
       </c>
-      <c r="J4" t="s">
+      <c r="J5" t="s">
         <v>45</v>
       </c>
-      <c r="K4">
+      <c r="K5">
         <v>26.98</v>
       </c>
-      <c r="L4" s="23">
+      <c r="L5" s="23">
         <v>0.16</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="B6" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C5" s="1">
-        <v>1</v>
-      </c>
-      <c r="D5" s="5">
+      <c r="C6" s="1">
+        <v>1</v>
+      </c>
+      <c r="D6" s="5">
         <f>(14.007*2)+(1.008*4)</f>
         <v>32.045999999999999</v>
       </c>
-      <c r="E5" s="4">
+      <c r="E6" s="4">
         <f>0.004*1000</f>
         <v>4</v>
       </c>
-      <c r="F5" s="6">
-        <f>C5*D5/(E5 * 1000)</f>
+      <c r="F6" s="6">
+        <f>C6*D6/(E6 * 1000)</f>
         <v>8.0114999999999995E-3</v>
       </c>
-      <c r="I5" t="s">
+      <c r="I6" t="s">
         <v>80</v>
       </c>
-      <c r="J5" t="s">
+      <c r="J6" t="s">
         <v>86</v>
       </c>
-      <c r="K5">
+      <c r="K6">
         <v>71.84</v>
       </c>
-      <c r="L5" s="22">
+      <c r="L6" s="22">
         <v>0.4</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="B7" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C6" s="1">
-        <v>1</v>
-      </c>
-      <c r="D6" s="5">
+      <c r="C7" s="1">
+        <v>1</v>
+      </c>
+      <c r="D7" s="5">
         <f>131.29</f>
         <v>131.29</v>
       </c>
-      <c r="E6" s="4">
+      <c r="E7" s="4">
         <f>0.0001*1000</f>
         <v>0.1</v>
       </c>
-      <c r="F6" s="6">
-        <f>C6*D6/(E6 * 1000)</f>
+      <c r="F7" s="6">
+        <f>C7*D7/(E7 * 1000)</f>
         <v>1.3129</v>
       </c>
-      <c r="L6" s="22"/>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
+      <c r="L7" s="22"/>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="B7" s="1"/>
-      <c r="C7" s="1">
-        <v>1</v>
-      </c>
-      <c r="D7" s="5"/>
-      <c r="E7" s="4">
+      <c r="B8" s="1"/>
+      <c r="C8" s="1">
+        <v>1</v>
+      </c>
+      <c r="D8" s="5"/>
+      <c r="E8" s="4">
         <f>0.0075*1000</f>
         <v>7.5</v>
       </c>
-      <c r="F7" s="6"/>
-      <c r="L7" s="22"/>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="I8" t="s">
+      <c r="F8" s="6"/>
+      <c r="L8" s="22"/>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="I9" t="s">
         <v>81</v>
       </c>
-      <c r="J8" t="s">
+      <c r="J9" t="s">
         <v>35</v>
       </c>
-      <c r="L8" s="23">
+      <c r="L9" s="23">
         <v>0.12</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="B10" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="C9" s="1">
-        <v>1</v>
-      </c>
-      <c r="D9" s="5">
-        <f>SUM(($D$45*0.5)+($D$93*0.5))</f>
+      <c r="C10" s="1">
+        <v>1</v>
+      </c>
+      <c r="D10" s="5">
+        <f>SUM(($D$47*0.5)+($D$97*0.5))</f>
         <v>46.073</v>
       </c>
-      <c r="E9" s="4">
+      <c r="E10" s="4">
         <f>0.0009*1000</f>
         <v>0.9</v>
       </c>
-      <c r="F9" s="6">
-        <f t="shared" ref="F9:F18" si="0">C9*D9/(E9 * 1000)</f>
+      <c r="F10" s="6">
+        <f t="shared" ref="F10:F20" si="0">C10*D10/(E10 * 1000)</f>
         <v>5.1192222222222222E-2</v>
       </c>
-      <c r="I9" t="s">
+      <c r="I10" t="s">
         <v>82</v>
       </c>
-      <c r="J9" t="s">
+      <c r="J10" t="s">
         <v>35</v>
       </c>
-      <c r="L9" s="22">
+      <c r="L10" s="22">
         <v>1.9599999999999999E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A10" s="1" t="s">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="B10" s="1" t="s">
+      <c r="B11" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C10" s="1">
-        <v>1</v>
-      </c>
-      <c r="D10" s="5">
+      <c r="C11" s="1">
+        <v>1</v>
+      </c>
+      <c r="D11" s="5">
         <v>101.96</v>
       </c>
-      <c r="E10" s="4">
+      <c r="E11" s="4">
         <f>0.00398*1000</f>
         <v>3.98</v>
       </c>
-      <c r="F10" s="6">
+      <c r="F11" s="6">
         <f t="shared" si="0"/>
         <v>2.5618090452261304E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A11" s="1" t="s">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="B11" s="1" t="s">
+      <c r="B12" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="C11" s="1">
-        <v>1</v>
-      </c>
-      <c r="D11" s="5">
+      <c r="C12" s="1">
+        <v>1</v>
+      </c>
+      <c r="D12" s="5">
         <v>26.98</v>
       </c>
-      <c r="E11" s="4">
+      <c r="E12" s="4">
         <f>0.00277*1000</f>
         <v>2.77</v>
       </c>
-      <c r="F11" s="6">
+      <c r="F12" s="6">
         <f t="shared" si="0"/>
         <v>9.7400722021660658E-3</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A12" s="1" t="s">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A13" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B12" s="1" t="s">
+      <c r="B13" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="C12" s="1">
-        <v>1</v>
-      </c>
-      <c r="D12" s="5">
+      <c r="C13" s="1">
+        <v>1</v>
+      </c>
+      <c r="D13" s="5">
         <v>17.03</v>
       </c>
-      <c r="E12" s="4">
+      <c r="E13" s="4">
         <f>0.000000769*1000</f>
         <v>7.6899999999999994E-4</v>
       </c>
-      <c r="F12" s="6">
+      <c r="F13" s="6">
         <f t="shared" si="0"/>
         <v>22.145643693107935</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A13" s="1" t="s">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A14" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B13" s="1" t="s">
+      <c r="B14" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C13" s="1">
-        <v>1</v>
-      </c>
-      <c r="D13" s="5">
+      <c r="C14" s="1">
+        <v>1</v>
+      </c>
+      <c r="D14" s="5">
         <v>39.950000000000003</v>
       </c>
-      <c r="E13" s="4">
+      <c r="E14" s="4">
         <f>0.000001784*1000</f>
         <v>1.784E-3</v>
       </c>
-      <c r="F13" s="6">
+      <c r="F14" s="6">
         <f t="shared" si="0"/>
         <v>22.393497757847534</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A14" s="35" t="s">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A15" s="35" t="s">
         <v>204</v>
       </c>
-      <c r="B14" s="35" t="s">
+      <c r="B15" s="35" t="s">
         <v>205</v>
       </c>
-      <c r="C14" s="35">
-        <v>1</v>
-      </c>
-      <c r="D14" s="36">
+      <c r="C15" s="35">
+        <v>1</v>
+      </c>
+      <c r="D15" s="36">
         <v>9.01</v>
       </c>
-      <c r="E14" s="37">
+      <c r="E15" s="37">
         <f>0.0007508*1000</f>
         <v>0.75080000000000002</v>
       </c>
-      <c r="F14" s="38">
+      <c r="F15" s="38">
         <f t="shared" si="0"/>
         <v>1.2000532765050611E-2</v>
       </c>
-      <c r="H14">
+      <c r="H15">
         <v>12</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A15" s="35" t="s">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A16" s="35" t="s">
         <v>206</v>
       </c>
-      <c r="B15" s="35" t="s">
+      <c r="B16" s="35" t="s">
         <v>207</v>
       </c>
-      <c r="C15" s="35">
-        <v>1</v>
-      </c>
-      <c r="D15" s="36">
+      <c r="C16" s="35">
+        <v>1</v>
+      </c>
+      <c r="D16" s="36">
         <v>66.02</v>
       </c>
-      <c r="E15" s="37">
+      <c r="E16" s="37">
         <f>0.00244518*1000</f>
         <v>2.4451800000000001</v>
       </c>
-      <c r="F15" s="38">
+      <c r="F16" s="38">
         <f t="shared" si="0"/>
         <v>2.7000057255498568E-2</v>
       </c>
-      <c r="H15">
+      <c r="H16">
         <v>27</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A16" s="9" t="s">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" s="35" t="s">
+        <v>239</v>
+      </c>
+      <c r="B17" s="35" t="s">
+        <v>234</v>
+      </c>
+      <c r="C17" s="35">
+        <v>1</v>
+      </c>
+      <c r="D17" s="36">
+        <v>720.6</v>
+      </c>
+      <c r="E17" s="37">
+        <f>0.126*1000</f>
+        <v>126</v>
+      </c>
+      <c r="F17" s="38">
+        <f t="shared" si="0"/>
+        <v>5.7190476190476193E-3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" s="9" t="s">
         <v>208</v>
       </c>
-      <c r="B16" s="9" t="s">
+      <c r="B18" s="9" t="s">
         <v>209</v>
       </c>
-      <c r="C16" s="9">
-        <v>1</v>
-      </c>
-      <c r="D16" s="10">
+      <c r="C18" s="9">
+        <v>1</v>
+      </c>
+      <c r="D18" s="10">
         <v>10.81</v>
       </c>
-      <c r="E16" s="11">
-        <f>D16/H16</f>
+      <c r="E18" s="11">
+        <f>D18/H18</f>
         <v>0.90083333333333337</v>
       </c>
-      <c r="F16" s="12">
+      <c r="F18" s="12">
         <f t="shared" si="0"/>
         <v>1.2E-2</v>
       </c>
-      <c r="H16">
+      <c r="H18">
         <v>12</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A17" s="9" t="s">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" s="9" t="s">
         <v>220</v>
       </c>
-      <c r="B17" s="9" t="s">
+      <c r="B19" s="9" t="s">
         <v>221</v>
       </c>
-      <c r="C17" s="9">
-        <v>1</v>
-      </c>
-      <c r="D17" s="10">
+      <c r="C19" s="9">
+        <v>1</v>
+      </c>
+      <c r="D19" s="10">
         <v>132.91</v>
       </c>
-      <c r="E17" s="11">
+      <c r="E19" s="11">
         <f>0.00193*1000</f>
         <v>1.9300000000000002</v>
       </c>
-      <c r="F17" s="12">
+      <c r="F19" s="12">
         <f t="shared" si="0"/>
         <v>6.8865284974093249E-2</v>
       </c>
-      <c r="G17" s="39"/>
-      <c r="H17" s="39"/>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A18" s="1" t="s">
+      <c r="G19" s="39"/>
+      <c r="H19" s="39"/>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="B18" s="1" t="s">
+      <c r="B20" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="C18" s="1">
-        <v>1</v>
-      </c>
-      <c r="D18" s="5">
+      <c r="C20" s="1">
+        <v>1</v>
+      </c>
+      <c r="D20" s="5">
         <v>12.01</v>
       </c>
-      <c r="E18" s="4">
+      <c r="E20" s="4">
         <f>0.0021*1000</f>
         <v>2.1</v>
       </c>
-      <c r="F18" s="6">
+      <c r="F20" s="6">
         <f t="shared" si="0"/>
         <v>5.7190476190476193E-3</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A19" s="1" t="s">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="B19" s="1" t="s">
+      <c r="B21" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C19" s="1">
-        <v>1</v>
-      </c>
-      <c r="D19" s="5">
+      <c r="C21" s="1">
+        <v>1</v>
+      </c>
+      <c r="D21" s="5">
         <v>44.01</v>
       </c>
-      <c r="E19" s="4">
+      <c r="E21" s="4">
         <f>0.000001951*1000</f>
         <v>1.951E-3</v>
       </c>
-      <c r="F19" s="6">
-        <f t="shared" ref="F19:F45" si="1">C19*D19/(E19 * 1000)</f>
+      <c r="F21" s="6">
+        <f t="shared" ref="F21:F47" si="1">C21*D21/(E21 * 1000)</f>
         <v>22.557662737057917</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A20" s="1" t="s">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" s="1" t="s">
         <v>181</v>
       </c>
-      <c r="B20" s="1" t="s">
+      <c r="B22" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="C20" s="1">
-        <v>1</v>
-      </c>
-      <c r="D20" s="5">
+      <c r="C22" s="1">
+        <v>1</v>
+      </c>
+      <c r="D22" s="5">
         <v>28.01</v>
       </c>
-      <c r="E20" s="4">
+      <c r="E22" s="4">
         <f>0.00000125*1000</f>
         <v>1.25E-3</v>
       </c>
-      <c r="F20" s="6">
+      <c r="F22" s="6">
         <f t="shared" si="1"/>
         <v>22.408000000000001</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A21" s="1" t="s">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="B21" s="1"/>
-      <c r="C21" s="1">
-        <v>1</v>
-      </c>
-      <c r="D21" s="5"/>
-      <c r="E21" s="4">
+      <c r="B23" s="1"/>
+      <c r="C23" s="1">
+        <v>1</v>
+      </c>
+      <c r="D23" s="5"/>
+      <c r="E23" s="4">
         <f>0.0025*1000</f>
         <v>2.5</v>
       </c>
-      <c r="F21" s="6"/>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A22" s="1" t="s">
+      <c r="F23" s="6"/>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="B22" s="1" t="s">
+      <c r="B24" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="C22" s="1">
-        <v>1</v>
-      </c>
-      <c r="D22" s="5">
+      <c r="C24" s="1">
+        <v>1</v>
+      </c>
+      <c r="D24" s="5">
         <v>35.450000000000003</v>
       </c>
-      <c r="E22" s="4">
+      <c r="E24" s="4">
         <f>0.0032*1000</f>
         <v>3.2</v>
       </c>
-      <c r="F22" s="6">
+      <c r="F24" s="6">
         <f t="shared" si="1"/>
         <v>1.1078125000000001E-2</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A23" s="1" t="s">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A25" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="B23" s="1"/>
-      <c r="C23" s="1">
-        <v>1</v>
-      </c>
-      <c r="D23" s="5"/>
-      <c r="E23" s="4">
+      <c r="B25" s="1"/>
+      <c r="C25" s="1">
+        <v>1</v>
+      </c>
+      <c r="D25" s="5"/>
+      <c r="E25" s="4">
         <f>0.001556*1000</f>
         <v>1.556</v>
       </c>
-      <c r="F23" s="6"/>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A24" s="1" t="s">
+      <c r="F25" s="6"/>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A26" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="B24" s="1" t="s">
+      <c r="B26" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="C24" s="1">
-        <v>1</v>
-      </c>
-      <c r="D24" s="5">
+      <c r="C26" s="1">
+        <v>1</v>
+      </c>
+      <c r="D26" s="5">
         <v>238.03</v>
       </c>
-      <c r="E24" s="4">
+      <c r="E26" s="4">
         <f>0.01097*1000</f>
         <v>10.97</v>
       </c>
-      <c r="F24" s="6">
+      <c r="F26" s="6">
         <f t="shared" si="1"/>
         <v>2.1698268003646309E-2</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A25" s="1" t="s">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A27" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="B25" s="1" t="s">
+      <c r="B27" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="C25" s="1">
-        <v>1</v>
-      </c>
-      <c r="D25" s="5">
+      <c r="C27" s="1">
+        <v>1</v>
+      </c>
+      <c r="D27" s="5">
         <v>2.0139999999999998</v>
       </c>
-      <c r="E25" s="4">
+      <c r="E27" s="4">
         <f>0.00000018*1000</f>
         <v>1.7999999999999998E-4</v>
       </c>
-      <c r="F25" s="6">
+      <c r="F27" s="6">
         <f t="shared" si="1"/>
         <v>11.188888888888888</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A26" s="1" t="s">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A28" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="B26" s="1" t="s">
+      <c r="B28" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="C26" s="1">
-        <v>1</v>
-      </c>
-      <c r="D26" s="5">
+      <c r="C28" s="1">
+        <v>1</v>
+      </c>
+      <c r="D28" s="5">
         <v>60.08</v>
       </c>
-      <c r="E26" s="4">
+      <c r="E28" s="4">
         <f>0.0016*1000</f>
         <v>1.6</v>
       </c>
-      <c r="F26" s="6">
+      <c r="F28" s="6">
         <f t="shared" si="1"/>
         <v>3.755E-2</v>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A27" s="1" t="s">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A29" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="B27" s="1" t="s">
+      <c r="B29" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="C27" s="1">
-        <v>1</v>
-      </c>
-      <c r="D27" s="5">
+      <c r="C29" s="1">
+        <v>1</v>
+      </c>
+      <c r="D29" s="5">
         <v>238.03</v>
       </c>
-      <c r="E27" s="4">
+      <c r="E29" s="4">
         <f>0.01097*1000</f>
         <v>10.97</v>
       </c>
-      <c r="F27" s="6">
+      <c r="F29" s="6">
         <f t="shared" si="1"/>
         <v>2.1698268003646309E-2</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A28" s="1" t="s">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A30" s="1" t="s">
         <v>179</v>
       </c>
-      <c r="B28" s="1" t="s">
+      <c r="B30" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="C28" s="1">
-        <v>1</v>
-      </c>
-      <c r="D28" s="5">
+      <c r="C30" s="1">
+        <v>1</v>
+      </c>
+      <c r="D30" s="5">
         <v>46.07</v>
       </c>
-      <c r="E28" s="4">
+      <c r="E30" s="4">
         <f>0.000789*1000</f>
         <v>0.78900000000000003</v>
       </c>
-      <c r="F28" s="6">
-        <f>C28*D28/(E28 * 1000)</f>
+      <c r="F30" s="6">
+        <f>C30*D30/(E30 * 1000)</f>
         <v>5.8390367553865653E-2</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A29" s="1" t="s">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A31" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="B29" s="1" t="s">
+      <c r="B31" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="C29" s="1">
-        <v>1</v>
-      </c>
-      <c r="D29" s="5">
+      <c r="C31" s="1">
+        <v>1</v>
+      </c>
+      <c r="D31" s="5">
         <v>61.206800000000001</v>
       </c>
-      <c r="E29" s="4">
+      <c r="E31" s="4">
         <f>0.00084175*1000</f>
         <v>0.84175</v>
       </c>
-      <c r="F29" s="6">
-        <f>C29*D29/(E29 * 1000)</f>
+      <c r="F31" s="6">
+        <f>C31*D31/(E31 * 1000)</f>
         <v>7.2713751113751113E-2</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A30" s="1" t="s">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A32" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="B30" s="1" t="s">
+      <c r="B32" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="C30" s="1">
-        <v>1</v>
-      </c>
-      <c r="D30" s="5">
+      <c r="C32" s="1">
+        <v>1</v>
+      </c>
+      <c r="D32" s="5">
         <v>668.34</v>
       </c>
-      <c r="E30" s="4">
+      <c r="E32" s="4">
         <f>0.0025*1000</f>
         <v>2.5</v>
       </c>
-      <c r="F30" s="6">
+      <c r="F32" s="6">
         <f t="shared" si="1"/>
         <v>0.26733600000000002</v>
       </c>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A31" s="1" t="s">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A33" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="B31" s="1"/>
-      <c r="C31" s="1">
-        <v>1</v>
-      </c>
-      <c r="D31" s="5"/>
-      <c r="E31" s="4">
+      <c r="B33" s="1"/>
+      <c r="C33" s="1">
+        <v>1</v>
+      </c>
+      <c r="D33" s="5"/>
+      <c r="E33" s="4">
         <f>0.001*1000</f>
         <v>1</v>
       </c>
-      <c r="F31" s="6">
+      <c r="F33" s="6">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A32" s="35" t="s">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A34" s="35" t="s">
         <v>213</v>
       </c>
-      <c r="B32" s="35" t="s">
+      <c r="B34" s="35" t="s">
         <v>215</v>
       </c>
-      <c r="C32" s="35">
-        <v>1</v>
-      </c>
-      <c r="D32" s="36">
+      <c r="C34" s="35">
+        <v>1</v>
+      </c>
+      <c r="D34" s="36">
         <v>412.91</v>
       </c>
-      <c r="E32" s="37">
+      <c r="E34" s="37">
         <f>0.001556*1000</f>
         <v>1.556</v>
       </c>
-      <c r="F32" s="6">
+      <c r="F34" s="38">
         <f t="shared" si="1"/>
         <v>0.26536632390745502</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A33" s="35" t="s">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A35" s="35" t="s">
         <v>214</v>
       </c>
-      <c r="B33" s="35" t="s">
+      <c r="B35" s="35" t="s">
         <v>216</v>
       </c>
-      <c r="C33" s="35">
-        <v>1</v>
-      </c>
-      <c r="D33" s="36">
+      <c r="C35" s="35">
+        <v>1</v>
+      </c>
+      <c r="D35" s="36">
         <v>278.13</v>
       </c>
-      <c r="E33" s="37">
+      <c r="E35" s="37">
         <f>0.00321*1000</f>
         <v>3.21</v>
       </c>
-      <c r="F33" s="6">
+      <c r="F35" s="38">
         <f t="shared" si="1"/>
         <v>8.6644859813084105E-2</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A34" s="1" t="s">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A36" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="B34" s="1"/>
-      <c r="C34" s="1">
-        <v>1</v>
-      </c>
-      <c r="D34" s="5"/>
-      <c r="E34" s="4">
+      <c r="B36" s="1"/>
+      <c r="C36" s="1">
+        <v>1</v>
+      </c>
+      <c r="D36" s="5"/>
+      <c r="E36" s="4">
         <f>0.001*1000</f>
         <v>1</v>
       </c>
-      <c r="F34" s="6"/>
-    </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A35" s="1" t="s">
+      <c r="F36" s="6"/>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A37" s="1" t="s">
         <v>225</v>
       </c>
-      <c r="B35" s="1" t="s">
+      <c r="B37" s="1" t="s">
         <v>226</v>
       </c>
-      <c r="C35" s="1">
-        <v>1</v>
-      </c>
-      <c r="D35" s="5">
+      <c r="C37" s="1">
+        <v>1</v>
+      </c>
+      <c r="D37" s="5">
         <v>741.30799999999999</v>
       </c>
-      <c r="E35" s="4">
+      <c r="E37" s="4">
         <f>0.05*1000</f>
         <v>50</v>
       </c>
-      <c r="F35" s="6">
+      <c r="F37" s="6">
         <f t="shared" si="1"/>
         <v>1.482616E-2</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A36" s="1" t="s">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A38" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="B36" s="1" t="s">
+      <c r="B38" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="C36" s="1">
-        <v>1</v>
-      </c>
-      <c r="D36" s="5">
+      <c r="C38" s="1">
+        <v>1</v>
+      </c>
+      <c r="D38" s="5">
         <v>19</v>
       </c>
-      <c r="E36" s="4">
+      <c r="E38" s="4">
         <f>0.0032*1000</f>
         <v>3.2</v>
       </c>
-      <c r="F36" s="6">
+      <c r="F38" s="6">
         <f t="shared" si="1"/>
         <v>5.9375000000000001E-3</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A37" s="1" t="s">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A39" s="1" t="s">
         <v>193</v>
       </c>
-      <c r="B37" s="1"/>
-      <c r="C37" s="1"/>
-      <c r="D37" s="5"/>
-      <c r="E37" s="4">
+      <c r="B39" s="1"/>
+      <c r="C39" s="1"/>
+      <c r="D39" s="5"/>
+      <c r="E39" s="4">
         <f xml:space="preserve"> 0.00028102905982906*1000</f>
         <v>0.28102905982906001</v>
       </c>
-      <c r="F37" s="6"/>
-    </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A38" s="1" t="s">
+      <c r="F39" s="6"/>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A40" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="B38" s="1" t="s">
+      <c r="B40" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="C38" s="1">
-        <v>1</v>
-      </c>
-      <c r="D38" s="5">
+      <c r="C40" s="1">
+        <v>1</v>
+      </c>
+      <c r="D40" s="5">
         <f>5.03</f>
         <v>5.03</v>
       </c>
-      <c r="E38" s="4">
+      <c r="E40" s="4">
         <f>0.000216*1000</f>
         <v>0.216</v>
       </c>
-      <c r="F38" s="6">
+      <c r="F40" s="6">
         <f t="shared" si="1"/>
         <v>2.3287037037037037E-2</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A39" s="1" t="s">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A41" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="B39" s="1" t="s">
+      <c r="B41" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="C39" s="1">
-        <v>1</v>
-      </c>
-      <c r="D39" s="5">
+      <c r="C41" s="1">
+        <v>1</v>
+      </c>
+      <c r="D41" s="5">
         <v>92.09</v>
       </c>
-      <c r="E39" s="4">
+      <c r="E41" s="4">
         <f>0.012*1000</f>
         <v>12</v>
       </c>
-      <c r="F39" s="6">
+      <c r="F41" s="6">
         <f t="shared" si="1"/>
         <v>7.6741666666666668E-3</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A40" s="1" t="s">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A42" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B40" s="1" t="s">
+      <c r="B42" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="C40" s="1">
-        <v>1</v>
-      </c>
-      <c r="D40" s="5">
+      <c r="C42" s="1">
+        <v>1</v>
+      </c>
+      <c r="D42" s="5">
         <v>172.14</v>
       </c>
-      <c r="E40" s="4">
+      <c r="E42" s="4">
         <f>0.0055*1000</f>
         <v>5.5</v>
       </c>
-      <c r="F40" s="6">
+      <c r="F42" s="6">
         <f t="shared" si="1"/>
         <v>3.1298181818181815E-2</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A41" s="1" t="s">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A43" s="1" t="s">
         <v>175</v>
       </c>
-      <c r="B41" s="1" t="s">
+      <c r="B43" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="C41" s="1">
-        <v>1</v>
-      </c>
-      <c r="D41" s="5">
+      <c r="C43" s="1">
+        <v>1</v>
+      </c>
+      <c r="D43" s="5">
         <v>3.016</v>
       </c>
-      <c r="E41" s="4">
+      <c r="E43" s="4">
         <f>0.000000125*1000</f>
         <v>1.25E-4</v>
       </c>
-      <c r="F41" s="6">
-        <f>C41*D41/(E41 * 1000)</f>
+      <c r="F43" s="6">
+        <f>C43*D43/(E43 * 1000)</f>
         <v>24.128</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A42" s="1" t="s">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A44" s="1" t="s">
         <v>176</v>
       </c>
-      <c r="B42" s="1" t="s">
+      <c r="B44" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="C42" s="1">
-        <v>1</v>
-      </c>
-      <c r="D42" s="5">
+      <c r="C44" s="1">
+        <v>1</v>
+      </c>
+      <c r="D44" s="5">
         <v>4.0019999999999998</v>
       </c>
-      <c r="E42" s="4">
+      <c r="E44" s="4">
         <f>0.0000001786*1000</f>
         <v>1.786E-4</v>
       </c>
-      <c r="F42" s="6">
-        <f>C42*D42/(E42 * 1000)</f>
+      <c r="F44" s="6">
+        <f>C44*D44/(E44 * 1000)</f>
         <v>22.407614781634937</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A43" s="1" t="s">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A45" s="1" t="s">
         <v>185</v>
       </c>
-      <c r="B43" s="1" t="s">
+      <c r="B45" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="C43" s="1">
-        <v>1</v>
-      </c>
-      <c r="D43" s="5">
+      <c r="C45" s="1">
+        <v>1</v>
+      </c>
+      <c r="D45" s="5">
         <v>34.01</v>
       </c>
-      <c r="E43" s="4">
+      <c r="E45" s="4">
         <f>0.001431*1000</f>
         <v>1.431</v>
       </c>
-      <c r="F43" s="6">
-        <f>C43*D43/(E43 * 1000)</f>
+      <c r="F45" s="6">
+        <f>C45*D45/(E45 * 1000)</f>
         <v>2.3766596785464708E-2</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A44" s="1" t="s">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A46" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B44" s="1" t="s">
+      <c r="B46" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="C44" s="1">
-        <v>1</v>
-      </c>
-      <c r="D44" s="5">
+      <c r="C46" s="1">
+        <v>1</v>
+      </c>
+      <c r="D46" s="5">
         <v>168.69</v>
       </c>
-      <c r="E44" s="4">
+      <c r="E46" s="4">
         <f>0.0015*1000</f>
         <v>1.5</v>
       </c>
-      <c r="F44" s="6">
+      <c r="F46" s="6">
         <f t="shared" si="1"/>
         <v>0.11246</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A45" s="1" t="s">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A47" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="B45" s="1" t="s">
+      <c r="B47" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="C45" s="1">
-        <v>1</v>
-      </c>
-      <c r="D45" s="5">
+      <c r="C47" s="1">
+        <v>1</v>
+      </c>
+      <c r="D47" s="5">
         <f>(14.007*2)+(1.008*4)</f>
         <v>32.045999999999999</v>
       </c>
-      <c r="E45" s="4">
+      <c r="E47" s="4">
         <f>0.001004*1000</f>
         <v>1.004</v>
       </c>
-      <c r="F45" s="6">
+      <c r="F47" s="6">
         <f t="shared" si="1"/>
         <v>3.1918326693227091E-2</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A46" s="1" t="s">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A48" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="B46" s="1" t="s">
+      <c r="B48" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C46" s="1">
-        <v>1</v>
-      </c>
-      <c r="D46" s="5">
+      <c r="C48" s="1">
+        <v>1</v>
+      </c>
+      <c r="D48" s="5">
         <v>2.02</v>
       </c>
-      <c r="E46" s="4">
+      <c r="E48" s="4">
         <f>0.0000000899*1000</f>
         <v>8.9900000000000003E-5</v>
       </c>
-      <c r="F46" s="6">
-        <f t="shared" ref="F46:F58" si="2">C46*D46/(E46 * 1000)</f>
+      <c r="F48" s="6">
+        <f t="shared" ref="F48:F61" si="2">C48*D48/(E48 * 1000)</f>
         <v>22.469410456062288</v>
       </c>
-      <c r="G46" s="8"/>
-    </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A47" s="1" t="s">
+      <c r="G48" s="8"/>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A49" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="B47" s="1" t="s">
+      <c r="B49" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C47" s="1">
-        <v>1</v>
-      </c>
-      <c r="D47" s="5">
+      <c r="C49" s="1">
+        <v>1</v>
+      </c>
+      <c r="D49" s="5">
         <v>170.34</v>
       </c>
-      <c r="E47" s="4">
+      <c r="E49" s="4">
         <f>0.00082*1000</f>
         <v>0.82</v>
       </c>
-      <c r="F47" s="6">
-        <f>C47*D47/(E47 * 1000)</f>
+      <c r="F49" s="6">
+        <f>C49*D49/(E49 * 1000)</f>
         <v>0.20773170731707319</v>
       </c>
-      <c r="G47" s="8"/>
-    </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A48" s="1" t="s">
+      <c r="G49" s="8"/>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A50" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="B48" s="1" t="s">
+      <c r="B50" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="C48" s="1">
-        <v>1</v>
-      </c>
-      <c r="D48" s="5">
+      <c r="C50" s="1">
+        <v>1</v>
+      </c>
+      <c r="D50" s="5">
         <v>6.94</v>
       </c>
-      <c r="E48" s="4">
-        <f xml:space="preserve"> 0.000534*1000</f>
+      <c r="E50" s="4">
+        <f>0.000534*1000</f>
         <v>0.53399999999999992</v>
       </c>
-      <c r="F48" s="6">
+      <c r="F50" s="6">
         <f t="shared" si="2"/>
         <v>1.2996254681647943E-2</v>
       </c>
-      <c r="G48" s="8"/>
-    </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A49" s="1" t="s">
+      <c r="G50" s="8"/>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A51" s="35" t="s">
+        <v>237</v>
+      </c>
+      <c r="B51" s="35" t="s">
+        <v>238</v>
+      </c>
+      <c r="C51" s="35">
+        <v>1</v>
+      </c>
+      <c r="D51" s="36">
+        <v>153.114</v>
+      </c>
+      <c r="E51" s="37">
+        <f>0.0086964*1000</f>
+        <v>8.6964000000000006</v>
+      </c>
+      <c r="F51" s="38">
+        <f t="shared" si="2"/>
+        <v>1.7606595832758379E-2</v>
+      </c>
+      <c r="G51" s="8"/>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A52" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="B49" s="1" t="s">
+      <c r="B52" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="C49" s="1">
-        <v>1</v>
-      </c>
-      <c r="D49" s="5">
+      <c r="C52" s="1">
+        <v>1</v>
+      </c>
+      <c r="D52" s="5">
         <v>17.03</v>
       </c>
-      <c r="E49" s="4">
+      <c r="E52" s="4">
         <f>0.0007021*1000</f>
         <v>0.70209999999999995</v>
       </c>
-      <c r="F49" s="6">
+      <c r="F52" s="6">
         <f t="shared" si="2"/>
         <v>2.4255804016521866E-2</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A50" s="1" t="s">
+    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A53" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="B50" s="1" t="s">
+      <c r="B53" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="C50" s="1">
-        <v>1</v>
-      </c>
-      <c r="D50" s="5">
+      <c r="C53" s="1">
+        <v>1</v>
+      </c>
+      <c r="D53" s="5">
         <v>28.01</v>
       </c>
-      <c r="E50" s="4">
+      <c r="E53" s="4">
         <f>0.00079*1000</f>
         <v>0.79</v>
       </c>
-      <c r="F50" s="6">
-        <f>C50*D50/(E50 * 1000)</f>
+      <c r="F53" s="6">
+        <f>C53*D53/(E53 * 1000)</f>
         <v>3.5455696202531646E-2</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A51" s="1" t="s">
+    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A54" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="B51" s="1" t="s">
+      <c r="B54" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C51" s="1">
-        <v>1</v>
-      </c>
-      <c r="D51" s="5">
+      <c r="C54" s="1">
+        <v>1</v>
+      </c>
+      <c r="D54" s="5">
         <v>44.01</v>
       </c>
-      <c r="E51" s="4">
+      <c r="E54" s="4">
         <f>0.00117325*1000</f>
         <v>1.1732500000000001</v>
       </c>
-      <c r="F51" s="6">
+      <c r="F54" s="6">
         <f t="shared" si="2"/>
         <v>3.7511186874067751E-2</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A52" s="1" t="s">
+    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A55" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="B52" s="1" t="s">
+      <c r="B55" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="C52" s="1">
-        <v>1</v>
-      </c>
-      <c r="D52" s="5">
+      <c r="C55" s="1">
+        <v>1</v>
+      </c>
+      <c r="D55" s="5">
         <v>2.0139999999999998</v>
       </c>
-      <c r="E52" s="4">
+      <c r="E55" s="4">
         <f>0.0001624*1000</f>
         <v>0.16239999999999999</v>
       </c>
-      <c r="F52" s="6">
+      <c r="F55" s="6">
         <f t="shared" si="2"/>
         <v>1.2401477832512315E-2</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A53" s="1" t="s">
+    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A56" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B53" s="1" t="s">
+      <c r="B56" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="C53" s="1">
-        <v>1</v>
-      </c>
-      <c r="D53" s="5">
+      <c r="C56" s="1">
+        <v>1</v>
+      </c>
+      <c r="D56" s="5">
         <v>3.016</v>
       </c>
-      <c r="E53" s="4">
+      <c r="E56" s="4">
         <f>0.000059*1000</f>
         <v>5.8999999999999997E-2</v>
       </c>
-      <c r="F53" s="6">
-        <f>C53*D53/(E53 * 1000)</f>
+      <c r="F56" s="6">
+        <f>C56*D56/(E56 * 1000)</f>
         <v>5.1118644067796613E-2</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A54" s="1" t="s">
+    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A57" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="B54" s="1" t="s">
+      <c r="B57" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="C54" s="1">
-        <v>1</v>
-      </c>
-      <c r="D54" s="5">
+      <c r="C57" s="1">
+        <v>1</v>
+      </c>
+      <c r="D57" s="5">
         <v>4.0019999999999998</v>
       </c>
-      <c r="E54" s="4">
+      <c r="E57" s="4">
         <f>0.0001786*1000</f>
         <v>0.17860000000000001</v>
       </c>
-      <c r="F54" s="6">
-        <f>C54*D54/(E54 * 1000)</f>
+      <c r="F57" s="6">
+        <f>C57*D57/(E57 * 1000)</f>
         <v>2.2407614781634933E-2</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A55" s="1" t="s">
+    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A58" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="B55" s="1" t="s">
+      <c r="B58" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C55" s="1">
-        <v>1</v>
-      </c>
-      <c r="D55" s="5">
+      <c r="C58" s="1">
+        <v>1</v>
+      </c>
+      <c r="D58" s="5">
         <v>2.02</v>
       </c>
-      <c r="E55" s="4">
+      <c r="E58" s="4">
         <f>0.00007085*1000</f>
         <v>7.0849999999999996E-2</v>
       </c>
-      <c r="F55" s="6">
-        <f>C55*D55/(E55 * 1000)</f>
+      <c r="F58" s="6">
+        <f>C58*D58/(E58 * 1000)</f>
         <v>2.8510938602681724E-2</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A56" s="1" t="s">
+    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A59" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B56" s="1" t="s">
+      <c r="B59" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C56" s="1">
-        <v>1</v>
-      </c>
-      <c r="D56" s="5">
+      <c r="C59" s="1">
+        <v>1</v>
+      </c>
+      <c r="D59" s="5">
         <v>16.05</v>
       </c>
-      <c r="E56" s="4">
+      <c r="E59" s="4">
         <f>0.00042561*1000</f>
         <v>0.42560999999999999</v>
       </c>
-      <c r="F56" s="6">
+      <c r="F59" s="6">
         <f t="shared" si="2"/>
         <v>3.7710580108550079E-2</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A57" s="1" t="s">
+    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A60" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="B57" s="9" t="s">
+      <c r="B60" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="C57" s="9">
-        <v>1</v>
-      </c>
-      <c r="D57" s="10">
+      <c r="C60" s="9">
+        <v>1</v>
+      </c>
+      <c r="D60" s="10">
         <v>32</v>
       </c>
-      <c r="E57" s="11">
+      <c r="E60" s="11">
         <f>0.001141*1000</f>
         <v>1.141</v>
       </c>
-      <c r="F57" s="12">
+      <c r="F60" s="12">
         <f t="shared" si="2"/>
         <v>2.8045574057843997E-2</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A58" s="1" t="s">
+    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A61" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="B58" s="1" t="s">
+      <c r="B61" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="C58" s="1">
-        <v>1</v>
-      </c>
-      <c r="D58" s="5">
+      <c r="C61" s="1">
+        <v>1</v>
+      </c>
+      <c r="D61" s="5">
         <v>28.01</v>
       </c>
-      <c r="E58" s="4">
+      <c r="E61" s="4">
         <f>0.000824907*1000</f>
         <v>0.82490700000000006</v>
       </c>
-      <c r="F58" s="6">
+      <c r="F61" s="6">
         <f t="shared" si="2"/>
         <v>3.3955342844708553E-2</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A59" s="1" t="s">
+    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A62" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="B59" s="1"/>
-      <c r="C59" s="1">
-        <v>1</v>
-      </c>
-      <c r="D59" s="5"/>
-      <c r="E59" s="4">
+      <c r="B62" s="1"/>
+      <c r="C62" s="1">
+        <v>1</v>
+      </c>
+      <c r="D62" s="5"/>
+      <c r="E62" s="4">
         <f>0.00378*1000</f>
         <v>3.78</v>
       </c>
-      <c r="F59" s="6"/>
-    </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A60" s="1" t="s">
+      <c r="F62" s="6"/>
+    </row>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A63" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="B60" s="1"/>
-      <c r="C60" s="1">
-        <v>1</v>
-      </c>
-      <c r="D60" s="5"/>
-      <c r="E60" s="4">
+      <c r="B63" s="1"/>
+      <c r="C63" s="1">
+        <v>1</v>
+      </c>
+      <c r="D63" s="5"/>
+      <c r="E63" s="4">
         <f>0.001*1000</f>
         <v>1</v>
       </c>
-      <c r="F60" s="6"/>
-    </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A61" s="1" t="s">
+      <c r="F63" s="6"/>
+    </row>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A64" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="B61" s="1" t="s">
+      <c r="B64" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C61" s="1">
-        <v>1</v>
-      </c>
-      <c r="D61" s="5">
-        <f>D55</f>
+      <c r="C64" s="1">
+        <v>1</v>
+      </c>
+      <c r="D64" s="5">
+        <f>D58</f>
         <v>2.02</v>
       </c>
-      <c r="E61" s="4">
+      <c r="E64" s="4">
         <f>0.007085*1000</f>
         <v>7.085</v>
       </c>
-      <c r="F61" s="6">
-        <f t="shared" ref="F61:F70" si="3">C61*D61/(E61 * 1000)</f>
+      <c r="F64" s="6">
+        <f t="shared" ref="F64:F73" si="3">C64*D64/(E64 * 1000)</f>
         <v>2.851093860268172E-4</v>
       </c>
-    </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A62" s="1" t="s">
+      <c r="H64">
+        <f>0.000824907*4</f>
+        <v>3.2996280000000002E-3</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A65" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="B62" s="1" t="s">
+      <c r="B65" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="C62" s="1">
-        <v>1</v>
-      </c>
-      <c r="D62" s="5">
+      <c r="C65" s="1">
+        <v>1</v>
+      </c>
+      <c r="D65" s="5">
         <v>159.69</v>
       </c>
-      <c r="E62" s="4">
+      <c r="E65" s="4">
         <f>0.0055*1000</f>
         <v>5.5</v>
       </c>
-      <c r="F62" s="6">
+      <c r="F65" s="6">
         <f t="shared" si="3"/>
         <v>2.9034545454545455E-2</v>
       </c>
-    </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A63" s="1" t="s">
+      <c r="H65">
+        <f>0.000001784*6</f>
+        <v>1.0703999999999999E-5</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A66" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="B63" s="1" t="s">
+      <c r="B66" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="C63" s="1">
-        <v>1</v>
-      </c>
-      <c r="D63" s="5">
+      <c r="C66" s="1">
+        <v>1</v>
+      </c>
+      <c r="D66" s="5">
         <v>159.69</v>
       </c>
-      <c r="E63" s="4">
+      <c r="E66" s="4">
         <f>0.026*1000</f>
         <v>26</v>
       </c>
-      <c r="F63" s="6">
+      <c r="F66" s="6">
         <f t="shared" si="3"/>
         <v>6.1419230769230769E-3</v>
       </c>
-    </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A64" s="1" t="s">
+      <c r="H66">
+        <f>H64+H65</f>
+        <v>3.310332E-3</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A67" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="B64" s="1" t="s">
+      <c r="B67" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="C64" s="1">
-        <v>1</v>
-      </c>
-      <c r="D64" s="5">
+      <c r="C67" s="1">
+        <v>1</v>
+      </c>
+      <c r="D67" s="5">
         <f>55.845*2</f>
         <v>111.69</v>
       </c>
-      <c r="E64" s="4">
+      <c r="E67" s="4">
         <f>0.039*1000</f>
         <v>39</v>
       </c>
-      <c r="F64" s="6">
+      <c r="F67" s="6">
         <f t="shared" si="3"/>
         <v>2.8638461538461539E-3</v>
       </c>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A65" s="1" t="s">
+    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A68" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="B65" s="1" t="s">
+      <c r="B68" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="C65" s="1">
-        <v>1</v>
-      </c>
-      <c r="D65" s="5">
+      <c r="C68" s="1">
+        <v>1</v>
+      </c>
+      <c r="D68" s="5">
         <f>55.845*2</f>
         <v>111.69</v>
       </c>
-      <c r="E65" s="4">
+      <c r="E68" s="4">
         <f>0.0078*1000</f>
         <v>7.8</v>
       </c>
-      <c r="F65" s="6">
+      <c r="F68" s="6">
         <f t="shared" si="3"/>
         <v>1.4319230769230768E-2</v>
       </c>
     </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A66" s="1" t="s">
+    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A69" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B66" s="1" t="s">
+      <c r="B69" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C66" s="1">
-        <v>1</v>
-      </c>
-      <c r="D66" s="5">
+      <c r="C69" s="1">
+        <v>1</v>
+      </c>
+      <c r="D69" s="5">
         <f>12.02+4*1.008</f>
         <v>16.052</v>
       </c>
-      <c r="E66" s="4">
+      <c r="E69" s="4">
         <f>0.000000717*1000</f>
         <v>7.1699999999999997E-4</v>
       </c>
-      <c r="F66" s="6">
+      <c r="F69" s="6">
         <f t="shared" si="3"/>
         <v>22.387726638772666</v>
       </c>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A67" s="1" t="s">
+    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A70" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="B67" s="1" t="s">
+      <c r="B70" s="1" t="s">
         <v>223</v>
       </c>
-      <c r="C67" s="1">
-        <v>1</v>
-      </c>
-      <c r="D67" s="5">
+      <c r="C70" s="1">
+        <v>1</v>
+      </c>
+      <c r="D70" s="5">
         <f>323.31+78.07</f>
         <v>401.38</v>
       </c>
-      <c r="E67" s="4">
+      <c r="E70" s="4">
         <f>0.0027*1000</f>
         <v>2.7</v>
       </c>
-      <c r="F67" s="6">
+      <c r="F70" s="6">
         <f t="shared" si="3"/>
         <v>0.14865925925925927</v>
       </c>
     </row>
-    <row r="68" spans="1:6" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A68" s="1" t="s">
+    <row r="71" spans="1:8" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="A71" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="B68" s="1" t="s">
+      <c r="B71" s="1" t="s">
         <v>173</v>
       </c>
-      <c r="C68" s="1">
-        <v>1</v>
-      </c>
-      <c r="D68" s="5">
+      <c r="C71" s="1">
+        <v>1</v>
+      </c>
+      <c r="D71" s="5">
         <v>46.07</v>
       </c>
-      <c r="E68" s="4">
+      <c r="E71" s="4">
         <f>0.00088*1000</f>
         <v>0.88</v>
       </c>
-      <c r="F68" s="6">
+      <c r="F71" s="6">
         <f t="shared" si="3"/>
         <v>5.2352272727272726E-2</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A69" s="35" t="s">
+    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A72" s="35" t="s">
         <v>202</v>
       </c>
-      <c r="B69" s="35" t="s">
+      <c r="B72" s="35" t="s">
         <v>203</v>
       </c>
-      <c r="C69" s="35">
-        <v>1</v>
-      </c>
-      <c r="D69" s="36">
+      <c r="C72" s="35">
+        <v>1</v>
+      </c>
+      <c r="D72" s="36">
         <v>60.08</v>
       </c>
-      <c r="E69" s="37">
+      <c r="E72" s="37">
         <f>0.00347*1000</f>
         <v>3.47</v>
       </c>
-      <c r="F69" s="38">
-        <f>C69*D69/(E69 * 1000)</f>
+      <c r="F72" s="38">
+        <f>C72*D72/(E72 * 1000)</f>
         <v>1.7314121037463978E-2</v>
       </c>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A70" s="1" t="s">
+    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A73" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="B70" s="1" t="s">
+      <c r="B73" s="1" t="s">
         <v>217</v>
       </c>
-      <c r="C70" s="1">
-        <v>1</v>
-      </c>
-      <c r="D70" s="5">
+      <c r="C73" s="1">
+        <v>1</v>
+      </c>
+      <c r="D73" s="5">
         <v>750.27</v>
       </c>
-      <c r="E70" s="4">
+      <c r="E73" s="4">
         <f>0.005*1000</f>
         <v>5</v>
       </c>
-      <c r="F70" s="6">
+      <c r="F73" s="6">
         <f t="shared" si="3"/>
         <v>0.15005399999999999</v>
       </c>
     </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A71" s="1" t="s">
+    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A74" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="B71" s="1"/>
-      <c r="C71" s="1">
-        <v>1</v>
-      </c>
-      <c r="D71" s="5"/>
-      <c r="E71" s="4">
+      <c r="B74" s="1"/>
+      <c r="C74" s="1">
+        <v>1</v>
+      </c>
+      <c r="D74" s="5"/>
+      <c r="E74" s="4">
         <f>0.001*1000</f>
         <v>1</v>
       </c>
-      <c r="F71" s="6"/>
-    </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A72" s="1" t="s">
+      <c r="F74" s="6"/>
+    </row>
+    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A75" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="B72" s="1" t="s">
+      <c r="B75" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="C72" s="1">
-        <v>1</v>
-      </c>
-      <c r="D72" s="5">
+      <c r="C75" s="1">
+        <v>1</v>
+      </c>
+      <c r="D75" s="5">
         <f>14.007*2</f>
         <v>28.013999999999999</v>
       </c>
-      <c r="E72" s="4">
+      <c r="E75" s="4">
         <f>0.000001251*1000</f>
         <v>1.2509999999999999E-3</v>
       </c>
-      <c r="F72" s="6">
-        <f>C72*D72/(E72 * 1000)</f>
+      <c r="F75" s="6">
+        <f>C75*D75/(E75 * 1000)</f>
         <v>22.393285371702639</v>
       </c>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A73" s="1" t="s">
+    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A76" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="B73" s="1" t="s">
+      <c r="B76" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="C73" s="1">
-        <v>1</v>
-      </c>
-      <c r="D73" s="5">
+      <c r="C76" s="1">
+        <v>1</v>
+      </c>
+      <c r="D76" s="5">
         <v>92.04</v>
       </c>
-      <c r="E73" s="4">
+      <c r="E76" s="4">
         <f>0.00145*1000</f>
         <v>1.45</v>
       </c>
-      <c r="F73" s="6">
-        <f>C73*D73/(E73 * 1000)</f>
+      <c r="F76" s="6">
+        <f>C76*D76/(E76 * 1000)</f>
         <v>6.3475862068965522E-2</v>
       </c>
     </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A74" s="1" t="s">
+    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A77" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="B74" s="1"/>
-      <c r="C74" s="1">
-        <v>1</v>
-      </c>
-      <c r="D74" s="5"/>
-      <c r="E74" s="4">
-        <v>1.0499999999999999E-3</v>
-      </c>
-      <c r="F74" s="6"/>
-    </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A75" s="1" t="s">
+      <c r="B77" s="1"/>
+      <c r="C77" s="1">
+        <v>1</v>
+      </c>
+      <c r="D77" s="5"/>
+      <c r="E77" s="4">
+        <f>0.00105*1000</f>
+        <v>1.05</v>
+      </c>
+      <c r="F77" s="6"/>
+    </row>
+    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A78" s="35" t="s">
+        <v>235</v>
+      </c>
+      <c r="B78" s="35" t="s">
+        <v>236</v>
+      </c>
+      <c r="C78" s="35">
+        <v>1</v>
+      </c>
+      <c r="D78" s="36">
+        <f>(14.005*8)+(39.95*6)</f>
+        <v>351.74</v>
+      </c>
+      <c r="E78" s="37">
+        <f>0.003310332*1000</f>
+        <v>3.3103319999999998</v>
+      </c>
+      <c r="F78" s="38">
+        <f>C78*D78/(E78 * 1000)</f>
+        <v>0.10625520340557987</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A79" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="B75" s="1"/>
-      <c r="C75" s="1">
-        <v>1</v>
-      </c>
-      <c r="D75" s="5"/>
-      <c r="E75" s="4">
+      <c r="B79" s="1"/>
+      <c r="C79" s="1">
+        <v>1</v>
+      </c>
+      <c r="D79" s="5"/>
+      <c r="E79" s="4">
         <f>0.001*1000</f>
         <v>1</v>
       </c>
-      <c r="F75" s="6"/>
-    </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A76" s="1" t="s">
+      <c r="F79" s="6"/>
+    </row>
+    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A80" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="B76" s="1" t="s">
+      <c r="B80" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C76" s="1">
-        <v>1</v>
-      </c>
-      <c r="D76" s="5">
+      <c r="C80" s="1">
+        <v>1</v>
+      </c>
+      <c r="D80" s="5">
         <v>32</v>
       </c>
-      <c r="E76" s="4">
+      <c r="E80" s="4">
         <f>0.00000141*1000</f>
         <v>1.41E-3</v>
       </c>
-      <c r="F76" s="6">
-        <f>C76*D76/(E76 * 1000)</f>
+      <c r="F80" s="6">
+        <f>C80*D80/(E80 * 1000)</f>
         <v>22.695035460992909</v>
       </c>
     </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A77" s="1" t="s">
+    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A81" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B77" s="1" t="s">
+      <c r="B81" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="C77" s="1">
-        <v>1</v>
-      </c>
-      <c r="D77" s="5">
+      <c r="C81" s="1">
+        <v>1</v>
+      </c>
+      <c r="D81" s="5">
         <v>30.97</v>
       </c>
-      <c r="E77" s="17">
-        <f>$E$3</f>
+      <c r="E81" s="17">
+        <f>$E$4</f>
         <v>5</v>
       </c>
-      <c r="F77" s="6">
-        <f>C77*D77/(E77 * 1000)</f>
+      <c r="F81" s="6">
+        <f>C81*D81/(E81 * 1000)</f>
         <v>6.1939999999999999E-3</v>
       </c>
     </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A78" s="1" t="s">
+    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A82" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="B78" s="1" t="s">
+      <c r="B82" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="C78" s="1">
-        <v>1</v>
-      </c>
-      <c r="D78" s="5">
+      <c r="C82" s="1">
+        <v>1</v>
+      </c>
+      <c r="D82" s="5">
         <v>244</v>
       </c>
-      <c r="E78" s="4">
+      <c r="E82" s="4">
         <f>0.019816*1000</f>
         <v>19.815999999999999</v>
       </c>
-      <c r="F78" s="6">
-        <f>C78*D78/(E78 * 1000)</f>
+      <c r="F82" s="6">
+        <f>C82*D82/(E82 * 1000)</f>
         <v>1.2313282196205087E-2</v>
       </c>
     </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A79" s="1" t="s">
+    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A83" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="B79" s="1"/>
-      <c r="C79" s="1">
-        <v>1</v>
-      </c>
-      <c r="D79" s="5"/>
-      <c r="E79" s="4">
+      <c r="B83" s="1"/>
+      <c r="C83" s="1">
+        <v>1</v>
+      </c>
+      <c r="D83" s="5"/>
+      <c r="E83" s="4">
         <f>0.00104*1000</f>
         <v>1.0399999999999998</v>
       </c>
-      <c r="F79" s="6"/>
-    </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A80" s="1" t="s">
+      <c r="F83" s="6"/>
+    </row>
+    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A84" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="B80" s="1" t="s">
+      <c r="B84" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="C80" s="1">
-        <v>1</v>
-      </c>
-      <c r="D80" s="5">
+      <c r="C84" s="1">
+        <v>1</v>
+      </c>
+      <c r="D84" s="5">
         <f>195.078</f>
         <v>195.078</v>
       </c>
-      <c r="E80" s="4">
+      <c r="E84" s="4">
         <f>0.0078*1000</f>
         <v>7.8</v>
       </c>
-      <c r="F80" s="6">
-        <f>C80*D80/(E80 * 1000)</f>
+      <c r="F84" s="6">
+        <f>C84*D84/(E84 * 1000)</f>
         <v>2.5010000000000001E-2</v>
       </c>
     </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A81" s="1" t="s">
+    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A85" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="B81" s="1"/>
-      <c r="C81" s="1">
-        <v>1</v>
-      </c>
-      <c r="D81" s="5"/>
-      <c r="E81" s="4">
+      <c r="B85" s="1"/>
+      <c r="C85" s="1">
+        <v>1</v>
+      </c>
+      <c r="D85" s="5"/>
+      <c r="E85" s="4">
         <f>0.00378*1000</f>
         <v>3.78</v>
       </c>
-      <c r="F81" s="6"/>
-    </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A82" s="1" t="s">
+      <c r="F85" s="6"/>
+    </row>
+    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A86" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="B82" s="1"/>
-      <c r="C82" s="1">
-        <v>1</v>
-      </c>
-      <c r="D82" s="5"/>
-      <c r="E82" s="4">
+      <c r="B86" s="1"/>
+      <c r="C86" s="1">
+        <v>1</v>
+      </c>
+      <c r="D86" s="5"/>
+      <c r="E86" s="4">
         <f>0.0052*1000</f>
         <v>5.2</v>
       </c>
-      <c r="F82" s="6"/>
-    </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A83" s="1" t="s">
+      <c r="F86" s="6"/>
+    </row>
+    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A87" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B83" s="1"/>
-      <c r="C83" s="1">
-        <v>1</v>
-      </c>
-      <c r="D83" s="5"/>
-      <c r="E83" s="4">
+      <c r="B87" s="1"/>
+      <c r="C87" s="1">
+        <v>1</v>
+      </c>
+      <c r="D87" s="5"/>
+      <c r="E87" s="4">
         <f>0.0025*1000</f>
         <v>2.5</v>
       </c>
-      <c r="F83" s="6"/>
-    </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A84" s="1" t="s">
+      <c r="F87" s="6"/>
+    </row>
+    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A88" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="B84" s="1"/>
-      <c r="C84" s="1">
-        <v>1</v>
-      </c>
-      <c r="D84" s="5"/>
-      <c r="E84" s="4">
+      <c r="B88" s="1"/>
+      <c r="C88" s="1">
+        <v>1</v>
+      </c>
+      <c r="D88" s="5"/>
+      <c r="E88" s="4">
         <f>0.004*1000</f>
         <v>4</v>
       </c>
-      <c r="F84" s="6"/>
-    </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A85" s="1" t="s">
+      <c r="F88" s="6"/>
+    </row>
+    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A89" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="B85" s="1" t="s">
+      <c r="B89" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="C85" s="1">
-        <v>1</v>
-      </c>
-      <c r="D85" s="5">
+      <c r="C89" s="1">
+        <v>1</v>
+      </c>
+      <c r="D89" s="5">
         <v>76.08</v>
       </c>
-      <c r="E85" s="4">
+      <c r="E89" s="4">
         <f>0.0025*1000</f>
         <v>2.5</v>
       </c>
-      <c r="F85" s="6">
-        <f>C85*D85/(E85 * 1000)</f>
+      <c r="F89" s="6">
+        <f>C89*D89/(E89 * 1000)</f>
         <v>3.0432000000000001E-2</v>
       </c>
     </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A86" s="1" t="s">
+    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A90" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="B86" s="1" t="s">
+      <c r="B90" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="C86" s="1">
-        <v>1</v>
-      </c>
-      <c r="D86" s="5">
+      <c r="C90" s="1">
+        <v>1</v>
+      </c>
+      <c r="D90" s="5">
         <v>28.09</v>
       </c>
-      <c r="E86" s="4">
+      <c r="E90" s="4">
         <f>0.002329*1000</f>
         <v>2.3289999999999997</v>
       </c>
-      <c r="F86" s="6">
-        <f>C86*D86/(E86 * 1000)</f>
+      <c r="F90" s="6">
+        <f>C90*D90/(E90 * 1000)</f>
         <v>1.2060970373550882E-2</v>
       </c>
     </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A87" s="1" t="s">
+    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A91" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="B87" s="1"/>
-      <c r="C87" s="1">
-        <v>1</v>
-      </c>
-      <c r="D87" s="5"/>
-      <c r="E87" s="4">
+      <c r="B91" s="1"/>
+      <c r="C91" s="1">
+        <v>1</v>
+      </c>
+      <c r="D91" s="5"/>
+      <c r="E91" s="4">
         <f>0.00378*1000</f>
         <v>3.78</v>
       </c>
-      <c r="F87" s="6"/>
-    </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A88" s="1" t="s">
+      <c r="F91" s="6"/>
+    </row>
+    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A92" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="B88" s="1" t="s">
+      <c r="B92" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="C88" s="1">
-        <v>1</v>
-      </c>
-      <c r="D88" s="5">
+      <c r="C92" s="1">
+        <v>1</v>
+      </c>
+      <c r="D92" s="5">
         <v>186.09</v>
       </c>
-      <c r="E88" s="4">
+      <c r="E92" s="4">
         <f>0.0031*1000</f>
         <v>3.1</v>
       </c>
-      <c r="F88" s="6">
-        <f>C88*D88/(E88 * 1000)</f>
+      <c r="F92" s="6">
+        <f>C92*D92/(E92 * 1000)</f>
         <v>6.0029032258064517E-2</v>
       </c>
     </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A89" s="1" t="s">
+    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A93" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="B89" s="1"/>
-      <c r="C89" s="1">
-        <v>1</v>
-      </c>
-      <c r="D89" s="5"/>
-      <c r="E89" s="4">
+      <c r="B93" s="1"/>
+      <c r="C93" s="1">
+        <v>1</v>
+      </c>
+      <c r="D93" s="5"/>
+      <c r="E93" s="4">
         <f>0.0016*1000</f>
         <v>1.6</v>
       </c>
-      <c r="F89" s="6"/>
-    </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A90" s="1" t="s">
+      <c r="F93" s="6"/>
+    </row>
+    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A94" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="B90" s="1"/>
-      <c r="C90" s="1">
-        <v>1</v>
-      </c>
-      <c r="D90" s="5"/>
-      <c r="E90" s="4">
+      <c r="B94" s="1"/>
+      <c r="C94" s="1">
+        <v>1</v>
+      </c>
+      <c r="D94" s="5"/>
+      <c r="E94" s="4">
         <f>0.001*1000</f>
         <v>1</v>
       </c>
-      <c r="F90" s="6"/>
-    </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A91" s="1" t="s">
+      <c r="F94" s="6"/>
+    </row>
+    <row r="95" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A95" s="1" t="s">
         <v>218</v>
       </c>
-      <c r="B91" s="1" t="s">
+      <c r="B95" s="1" t="s">
         <v>219</v>
       </c>
-      <c r="C91" s="1">
-        <v>1</v>
-      </c>
-      <c r="D91" s="5">
+      <c r="C95" s="1">
+        <v>1</v>
+      </c>
+      <c r="D95" s="5">
         <v>232.04</v>
       </c>
-      <c r="E91" s="4">
+      <c r="E95" s="4">
         <f>0.0117*1000</f>
         <v>11.700000000000001</v>
       </c>
-      <c r="F91" s="6">
-        <f>C91*D91/(E91 * 1000)</f>
+      <c r="F95" s="6">
+        <f>C95*D95/(E95 * 1000)</f>
         <v>1.9832478632478629E-2</v>
       </c>
     </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A92" s="1" t="s">
+    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A96" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="B92" s="1" t="s">
+      <c r="B96" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="C92" s="1">
-        <v>1</v>
-      </c>
-      <c r="D92" s="5">
+      <c r="C96" s="1">
+        <v>1</v>
+      </c>
+      <c r="D96" s="5">
         <v>270.02999999999997</v>
       </c>
-      <c r="E92" s="4">
+      <c r="E96" s="4">
         <f>0.0075*1000</f>
         <v>7.5</v>
       </c>
-      <c r="F92" s="6">
-        <f>C92*D92/(E92 * 1000)</f>
+      <c r="F96" s="6">
+        <f>C96*D96/(E96 * 1000)</f>
         <v>3.6003999999999994E-2</v>
       </c>
     </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A93" s="1" t="s">
+    <row r="97" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A97" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="B93" s="1" t="s">
+      <c r="B97" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="C93" s="1">
-        <v>1</v>
-      </c>
-      <c r="D93" s="5">
+      <c r="C97" s="1">
+        <v>1</v>
+      </c>
+      <c r="D97" s="5">
         <v>60.1</v>
       </c>
-      <c r="E93" s="4">
+      <c r="E97" s="4">
         <f>0.000791*1000</f>
         <v>0.79100000000000004</v>
       </c>
-      <c r="F93" s="6">
-        <f>C93*D93/(E93 * 1000)</f>
+      <c r="F97" s="6">
+        <f>C97*D97/(E97 * 1000)</f>
         <v>7.5979772439949439E-2</v>
       </c>
     </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A94" s="1" t="s">
+    <row r="98" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A98" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="B94" s="1" t="s">
+      <c r="B98" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="C94" s="1">
-        <v>1</v>
-      </c>
-      <c r="D94" s="5">
-        <f>SUM(($D$45*0.25)+($D$93*0.75))</f>
+      <c r="C98" s="1">
+        <v>1</v>
+      </c>
+      <c r="D98" s="5">
+        <f>SUM(($D$47*0.25)+($D$97*0.75))</f>
         <v>53.086500000000001</v>
       </c>
-      <c r="E94" s="4">
+      <c r="E98" s="4">
         <f>0.000829*1000</f>
         <v>0.82899999999999996</v>
       </c>
-      <c r="F94" s="6">
-        <f>C94*D94/(E94 * 1000)</f>
+      <c r="F98" s="6">
+        <f>C98*D98/(E98 * 1000)</f>
         <v>6.4036791314837152E-2</v>
       </c>
     </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A95" s="1" t="s">
+    <row r="99" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A99" s="1" t="s">
         <v>194</v>
       </c>
-      <c r="B95" s="1"/>
-      <c r="C95" s="1">
-        <v>1</v>
-      </c>
-      <c r="D95" s="5"/>
-      <c r="E95" s="4">
+      <c r="B99" s="1"/>
+      <c r="C99" s="1">
+        <v>1</v>
+      </c>
+      <c r="D99" s="5"/>
+      <c r="E99" s="4">
         <f>0.00075*1000</f>
         <v>0.75</v>
       </c>
-      <c r="F95" s="6"/>
-    </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A96" s="1" t="s">
+      <c r="F99" s="6"/>
+    </row>
+    <row r="100" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A100" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="B96" s="1"/>
-      <c r="C96" s="1">
-        <v>1</v>
-      </c>
-      <c r="D96" s="5"/>
-      <c r="E96" s="4">
+      <c r="B100" s="1"/>
+      <c r="C100" s="1">
+        <v>1</v>
+      </c>
+      <c r="D100" s="5"/>
+      <c r="E100" s="4">
         <f>0.001005*1000</f>
         <v>1.0050000000000001</v>
       </c>
-      <c r="F96" s="6"/>
-    </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A97" s="1" t="s">
+      <c r="F100" s="6"/>
+    </row>
+    <row r="101" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A101" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="B97" s="1" t="s">
+      <c r="B101" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="C97" s="1">
-        <v>1</v>
-      </c>
-      <c r="D97" s="5">
+      <c r="C101" s="1">
+        <v>1</v>
+      </c>
+      <c r="D101" s="5">
         <v>18.02</v>
       </c>
-      <c r="E97" s="4">
+      <c r="E101" s="4">
         <f>0.001*1000</f>
         <v>1</v>
       </c>
-      <c r="F97" s="6">
-        <f>C97*D97/(E97 * 1000)</f>
+      <c r="F101" s="6">
+        <f>C101*D101/(E101 * 1000)</f>
         <v>1.8020000000000001E-2</v>
       </c>
     </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A99" s="1" t="s">
+    <row r="103" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A103" s="1" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A100" s="29" t="s">
+    <row r="104" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A104" s="29" t="s">
         <v>98</v>
       </c>
-      <c r="D100" s="30"/>
-      <c r="E100" s="4">
-        <f t="shared" ref="E100:E135" si="4">F100*1000</f>
+      <c r="D104" s="30"/>
+      <c r="E104" s="4">
+        <f t="shared" ref="E104:E139" si="4">F104*1000</f>
         <v>5</v>
       </c>
-      <c r="F100" s="6">
+      <c r="F104" s="6">
         <v>5.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A101" s="29" t="s">
+    <row r="105" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A105" s="29" t="s">
         <v>106</v>
       </c>
-      <c r="E101" s="4">
+      <c r="E105" s="4">
         <f t="shared" si="4"/>
         <v>19.3</v>
       </c>
-      <c r="F101" s="6">
+      <c r="F105" s="6">
         <v>1.9300000000000001E-2</v>
       </c>
     </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A102" s="29" t="s">
+    <row r="106" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A106" s="29" t="s">
         <v>51</v>
       </c>
-      <c r="E102" s="4">
+      <c r="E106" s="4">
         <f t="shared" si="4"/>
         <v>54.4</v>
       </c>
-      <c r="F102" s="6">
+      <c r="F106" s="6">
         <v>5.4399999999999997E-2</v>
       </c>
     </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A103" s="29" t="s">
+    <row r="107" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A107" s="29" t="s">
         <v>99</v>
       </c>
-      <c r="E103" s="4">
+      <c r="E107" s="4">
         <f t="shared" si="4"/>
         <v>5</v>
       </c>
-      <c r="F103" s="6">
+      <c r="F107" s="6">
         <v>5.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A104" s="29" t="s">
+    <row r="108" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A108" s="29" t="s">
         <v>108</v>
       </c>
-      <c r="E104" s="4">
+      <c r="E108" s="4">
         <f t="shared" si="4"/>
         <v>7</v>
       </c>
-      <c r="F104" s="6">
+      <c r="F108" s="6">
         <v>7.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A105" s="29" t="s">
+    <row r="109" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A109" s="29" t="s">
         <v>142</v>
       </c>
-      <c r="E105" s="4">
+      <c r="E109" s="4">
         <f t="shared" si="4"/>
         <v>0.53399999999999992</v>
       </c>
-      <c r="F105" s="6">
+      <c r="F109" s="6">
         <v>5.3399999999999997E-4</v>
       </c>
     </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A106" s="29" t="s">
+    <row r="110" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A110" s="29" t="s">
         <v>100</v>
       </c>
-      <c r="E106" s="4">
+      <c r="E110" s="4">
         <f t="shared" si="4"/>
         <v>6.0000000000000005E-2</v>
       </c>
-      <c r="F106" s="6">
+      <c r="F110" s="6">
         <v>6.0000000000000002E-5</v>
       </c>
     </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A107" s="29" t="s">
+    <row r="111" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A111" s="29" t="s">
         <v>104</v>
       </c>
-      <c r="E107" s="4">
+      <c r="E111" s="4">
         <f t="shared" si="4"/>
         <v>2.5</v>
       </c>
-      <c r="F107" s="6">
+      <c r="F111" s="6">
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A108" s="29" t="s">
+    <row r="112" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A112" s="29" t="s">
         <v>61</v>
       </c>
-      <c r="E108" s="4">
+      <c r="E112" s="4">
         <f t="shared" si="4"/>
         <v>5.0108799999999993</v>
       </c>
-      <c r="F108" s="6">
+      <c r="F112" s="6">
         <v>5.0108799999999997E-3</v>
       </c>
     </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A109" s="29" t="s">
+    <row r="113" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A113" s="29" t="s">
         <v>109</v>
       </c>
-      <c r="E109" s="4">
+      <c r="E113" s="4">
         <f t="shared" si="4"/>
         <v>4.3499999999999996</v>
       </c>
-      <c r="F109" s="6">
+      <c r="F113" s="6">
         <v>4.3499999999999997E-3</v>
       </c>
     </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A110" s="29" t="s">
+    <row r="114" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A114" s="29" t="s">
         <v>103</v>
       </c>
-      <c r="E110" s="4">
+      <c r="E114" s="4">
         <f t="shared" si="4"/>
         <v>0.216</v>
       </c>
-      <c r="F110" s="6">
+      <c r="F114" s="6">
         <v>2.1599999999999999E-4</v>
       </c>
     </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A111" s="29" t="s">
+    <row r="115" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A115" s="29" t="s">
         <v>52</v>
       </c>
-      <c r="E111" s="4">
+      <c r="E115" s="4">
         <f t="shared" si="4"/>
         <v>23.125</v>
       </c>
-      <c r="F111" s="6">
+      <c r="F115" s="6">
         <v>2.3125E-2</v>
       </c>
     </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A112" s="29" t="s">
+    <row r="116" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A116" s="29" t="s">
         <v>53</v>
       </c>
-      <c r="E112" s="4">
+      <c r="E116" s="4">
         <f t="shared" si="4"/>
         <v>5.25</v>
       </c>
-      <c r="F112" s="6">
+      <c r="F116" s="6">
         <v>5.2500000000000003E-3</v>
       </c>
     </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A113" s="29" t="s">
+    <row r="117" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A117" s="29" t="s">
         <v>224</v>
       </c>
-      <c r="E113" s="4">
+      <c r="E117" s="4">
         <f t="shared" si="4"/>
         <v>6.24</v>
       </c>
-      <c r="F113" s="6">
+      <c r="F117" s="6">
         <v>6.2399999999999999E-3</v>
       </c>
     </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A114" s="29" t="s">
+    <row r="118" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A118" s="29" t="s">
         <v>54</v>
       </c>
-      <c r="E114" s="4">
+      <c r="E118" s="4">
         <f t="shared" si="4"/>
         <v>5</v>
       </c>
-      <c r="F114" s="6">
+      <c r="F118" s="6">
         <v>5.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="115" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A115" s="29" t="s">
+    <row r="119" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A119" s="29" t="s">
         <v>141</v>
       </c>
-      <c r="E115" s="4">
+      <c r="E119" s="4">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
-      <c r="F115" s="6">
+      <c r="F119" s="6">
         <v>1E-3</v>
       </c>
     </row>
-    <row r="116" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A116" s="29" t="s">
+    <row r="120" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A120" s="29" t="s">
         <v>55</v>
       </c>
-      <c r="E116" s="4">
+      <c r="E120" s="4">
         <f t="shared" si="4"/>
         <v>12.5</v>
       </c>
-      <c r="F116" s="6">
+      <c r="F120" s="6">
         <v>1.2500000000000001E-2</v>
       </c>
     </row>
-    <row r="117" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A117" s="29" t="s">
+    <row r="121" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A121" s="29" t="s">
         <v>105</v>
       </c>
-      <c r="E117" s="4">
+      <c r="E121" s="4">
         <f t="shared" si="4"/>
         <v>2.4</v>
       </c>
-      <c r="F117" s="6">
+      <c r="F121" s="6">
         <v>2.3999999999999998E-3</v>
       </c>
     </row>
-    <row r="118" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A118" s="29" t="s">
+    <row r="122" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A122" s="29" t="s">
         <v>56</v>
       </c>
-      <c r="E118" s="4">
+      <c r="E122" s="4">
         <f t="shared" si="4"/>
         <v>13.5</v>
       </c>
-      <c r="F118" s="6">
+      <c r="F122" s="6">
         <v>1.35E-2</v>
       </c>
     </row>
-    <row r="119" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A119" s="29" t="s">
+    <row r="123" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A123" s="29" t="s">
         <v>57</v>
       </c>
-      <c r="E119" s="4">
+      <c r="E123" s="4">
         <f t="shared" si="4"/>
         <v>8.6</v>
       </c>
-      <c r="F119" s="6">
+      <c r="F123" s="6">
         <v>8.6E-3</v>
       </c>
     </row>
-    <row r="120" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A120" s="29" t="s">
+    <row r="124" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A124" s="29" t="s">
         <v>164</v>
       </c>
-      <c r="E120" s="4">
+      <c r="E124" s="4">
         <f t="shared" si="4"/>
         <v>19.099999999999998</v>
       </c>
-      <c r="F120" s="6">
+      <c r="F124" s="6">
         <v>1.9099999999999999E-2</v>
       </c>
     </row>
-    <row r="121" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A121" s="29" t="s">
+    <row r="125" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A125" s="29" t="s">
         <v>165</v>
       </c>
-      <c r="E121" s="4">
+      <c r="E125" s="4">
         <f t="shared" si="4"/>
         <v>10.97</v>
       </c>
-      <c r="F121" s="6">
+      <c r="F125" s="6">
         <v>1.0970000000000001E-2</v>
-      </c>
-    </row>
-    <row r="122" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A122" s="29" t="s">
-        <v>58</v>
-      </c>
-      <c r="B122" s="1"/>
-      <c r="C122" s="1"/>
-      <c r="D122" s="3"/>
-      <c r="E122" s="4">
-        <f t="shared" si="4"/>
-        <v>5.7050000000000001</v>
-      </c>
-      <c r="F122" s="6">
-        <v>5.705E-3</v>
-      </c>
-    </row>
-    <row r="123" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A123" s="29" t="s">
-        <v>59</v>
-      </c>
-      <c r="B123" s="1"/>
-      <c r="C123" s="1"/>
-      <c r="D123" s="3"/>
-      <c r="E123" s="4">
-        <f t="shared" si="4"/>
-        <v>13.5</v>
-      </c>
-      <c r="F123" s="6">
-        <v>1.35E-2</v>
-      </c>
-    </row>
-    <row r="124" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A124" s="29" t="s">
-        <v>63</v>
-      </c>
-      <c r="B124" s="1"/>
-      <c r="C124" s="1"/>
-      <c r="D124" s="3"/>
-      <c r="E124" s="4">
-        <f t="shared" si="4"/>
-        <v>0.35399999999999998</v>
-      </c>
-      <c r="F124" s="6">
-        <v>3.5399999999999999E-4</v>
-      </c>
-    </row>
-    <row r="125" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A125" s="29" t="s">
-        <v>101</v>
-      </c>
-      <c r="B125" s="1"/>
-      <c r="C125" s="1"/>
-      <c r="D125" s="3"/>
-      <c r="E125" s="4">
-        <f t="shared" si="4"/>
-        <v>2.12805</v>
-      </c>
-      <c r="F125" s="6">
-        <v>2.1280499999999998E-3</v>
       </c>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A126" s="29" t="s">
-        <v>111</v>
+        <v>58</v>
       </c>
       <c r="B126" s="1"/>
       <c r="C126" s="1"/>
       <c r="D126" s="3"/>
       <c r="E126" s="4">
         <f t="shared" si="4"/>
-        <v>1.08</v>
+        <v>5.7050000000000001</v>
       </c>
       <c r="F126" s="6">
-        <v>1.08E-3</v>
+        <v>5.705E-3</v>
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A127" s="29" t="s">
-        <v>102</v>
+        <v>59</v>
       </c>
       <c r="B127" s="1"/>
       <c r="C127" s="1"/>
       <c r="D127" s="3"/>
       <c r="E127" s="4">
         <f t="shared" si="4"/>
-        <v>4.1000000000000005</v>
+        <v>13.5</v>
       </c>
       <c r="F127" s="6">
-        <v>4.1000000000000003E-3</v>
+        <v>1.35E-2</v>
       </c>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A128" s="29" t="s">
-        <v>46</v>
-      </c>
+        <v>63</v>
+      </c>
+      <c r="B128" s="1"/>
+      <c r="C128" s="1"/>
+      <c r="D128" s="3"/>
       <c r="E128" s="4">
         <f t="shared" si="4"/>
-        <v>12.5</v>
+        <v>0.35399999999999998</v>
       </c>
       <c r="F128" s="6">
-        <v>1.2500000000000001E-2</v>
+        <v>3.5399999999999999E-4</v>
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A129" s="29" t="s">
-        <v>65</v>
-      </c>
+        <v>101</v>
+      </c>
+      <c r="B129" s="1"/>
+      <c r="C129" s="1"/>
+      <c r="D129" s="3"/>
       <c r="E129" s="4">
         <f t="shared" si="4"/>
-        <v>4.5999999999999996</v>
+        <v>2.12805</v>
       </c>
       <c r="F129" s="6">
-        <v>4.5999999999999999E-3</v>
+        <v>2.1280499999999998E-3</v>
       </c>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A130" s="29" t="s">
-        <v>112</v>
-      </c>
+        <v>111</v>
+      </c>
+      <c r="B130" s="1"/>
+      <c r="C130" s="1"/>
+      <c r="D130" s="3"/>
       <c r="E130" s="4">
         <f t="shared" si="4"/>
-        <v>1</v>
+        <v>1.08</v>
       </c>
       <c r="F130" s="6">
-        <v>1E-3</v>
+        <v>1.08E-3</v>
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A131" s="29" t="s">
-        <v>113</v>
-      </c>
+        <v>102</v>
+      </c>
+      <c r="B131" s="1"/>
+      <c r="C131" s="1"/>
+      <c r="D131" s="3"/>
       <c r="E131" s="4">
         <f t="shared" si="4"/>
-        <v>1</v>
+        <v>4.1000000000000005</v>
       </c>
       <c r="F131" s="6">
-        <v>1E-3</v>
+        <v>4.1000000000000003E-3</v>
       </c>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A132" s="29" t="s">
-        <v>107</v>
+        <v>46</v>
       </c>
       <c r="E132" s="4">
         <f t="shared" si="4"/>
-        <v>7.5</v>
+        <v>12.5</v>
       </c>
       <c r="F132" s="6">
-        <v>7.4999999999999997E-3</v>
+        <v>1.2500000000000001E-2</v>
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A133" s="29" t="s">
-        <v>110</v>
+        <v>65</v>
       </c>
       <c r="E133" s="4">
         <f t="shared" si="4"/>
-        <v>4.3499999999999996</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="F133" s="6">
-        <v>4.3499999999999997E-3</v>
+        <v>4.5999999999999999E-3</v>
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A134" s="29" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="E134" s="4">
         <f t="shared" si="4"/>
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F134" s="6">
-        <v>5.0000000000000001E-3</v>
+        <v>1E-3</v>
       </c>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A135" s="29" t="s">
-        <v>60</v>
+        <v>113</v>
       </c>
       <c r="E135" s="4">
         <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="F135" s="6">
+        <v>1E-3</v>
+      </c>
+    </row>
+    <row r="136" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A136" s="29" t="s">
+        <v>107</v>
+      </c>
+      <c r="E136" s="4">
+        <f t="shared" si="4"/>
+        <v>7.5</v>
+      </c>
+      <c r="F136" s="6">
+        <v>7.4999999999999997E-3</v>
+      </c>
+    </row>
+    <row r="137" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A137" s="29" t="s">
+        <v>110</v>
+      </c>
+      <c r="E137" s="4">
+        <f t="shared" si="4"/>
+        <v>4.3499999999999996</v>
+      </c>
+      <c r="F137" s="6">
+        <v>4.3499999999999997E-3</v>
+      </c>
+    </row>
+    <row r="138" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A138" s="29" t="s">
+        <v>115</v>
+      </c>
+      <c r="E138" s="4">
+        <f t="shared" si="4"/>
         <v>5</v>
       </c>
-      <c r="F135" s="6">
+      <c r="F138" s="6">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="139" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A139" s="29" t="s">
+        <v>60</v>
+      </c>
+      <c r="E139" s="4">
+        <f t="shared" si="4"/>
+        <v>5</v>
+      </c>
+      <c r="F139" s="6">
         <v>5.0000000000000001E-3</v>
       </c>
     </row>

--- a/RR_ISRU.xlsx
+++ b/RR_ISRU.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="31620" yWindow="0" windowWidth="17700" windowHeight="10485"/>
+    <workbookView xWindow="31620" yWindow="0" windowWidth="17700" windowHeight="10485" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Calc (Kg)" sheetId="6" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="241">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="290" uniqueCount="242">
   <si>
     <t>Resource</t>
   </si>
@@ -783,6 +783,9 @@
   </si>
   <si>
     <t>units</t>
+  </si>
+  <si>
+    <t>LqdFluorine</t>
   </si>
 </sst>
 </file>
@@ -1112,14 +1115,14 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="3"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="3" applyAlignment="1"/>
     <xf numFmtId="172" fontId="5" fillId="4" borderId="1" xfId="2" applyNumberFormat="1"/>
+    <xf numFmtId="11" fontId="4" fillId="3" borderId="1" xfId="1" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="1" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="4" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="3" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="11" fontId="4" fillId="3" borderId="1" xfId="1" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="1" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="9">
     <cellStyle name="Calculation" xfId="2" builtinId="22"/>
@@ -1451,15 +1454,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="20.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="46" t="s">
+      <c r="A1" s="48" t="s">
         <v>92</v>
       </c>
-      <c r="B1" s="46"/>
-      <c r="C1" s="46"/>
-      <c r="D1" s="46"/>
-      <c r="E1" s="46"/>
-      <c r="F1" s="46"/>
-      <c r="G1" s="46"/>
+      <c r="B1" s="48"/>
+      <c r="C1" s="48"/>
+      <c r="D1" s="48"/>
+      <c r="E1" s="48"/>
+      <c r="F1" s="48"/>
+      <c r="G1" s="48"/>
     </row>
     <row r="2" spans="1:12" ht="16.5" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A2" s="27" t="s">
@@ -1496,7 +1499,7 @@
       <c r="A6" s="25" t="s">
         <v>90</v>
       </c>
-      <c r="B6" s="49">
+      <c r="B6" s="47">
         <v>0</v>
       </c>
       <c r="C6" s="18">
@@ -1557,27 +1560,27 @@
         <v>70</v>
       </c>
       <c r="B8" s="21" t="str">
-        <f>IFERROR(VLOOKUP(B7,Database!$A$3:$E$139,5,FALSE),"-")</f>
+        <f>IFERROR(VLOOKUP(B7,Database!$A$3:$E$140,5,FALSE),"-")</f>
         <v>-</v>
       </c>
       <c r="C8" s="21" t="str">
-        <f>IFERROR(VLOOKUP(C7,Database!$A$3:$E$139,5,FALSE),"-")</f>
+        <f>IFERROR(VLOOKUP(C7,Database!$A$3:$E$140,5,FALSE),"-")</f>
         <v>-</v>
       </c>
       <c r="D8" s="21" t="str">
-        <f>IFERROR(VLOOKUP(D7,Database!$A$3:$E$139,5,FALSE),"-")</f>
+        <f>IFERROR(VLOOKUP(D7,Database!$A$3:$E$140,5,FALSE),"-")</f>
         <v>-</v>
       </c>
       <c r="E8" s="21" t="str">
-        <f>IFERROR(VLOOKUP(E7,Database!$A$3:$E$139,5,FALSE),"-")</f>
+        <f>IFERROR(VLOOKUP(E7,Database!$A$3:$E$140,5,FALSE),"-")</f>
         <v>-</v>
       </c>
       <c r="F8" s="21" t="str">
-        <f>IFERROR(VLOOKUP(F7,Database!$A$3:$E$139,5,FALSE),"-")</f>
+        <f>IFERROR(VLOOKUP(F7,Database!$A$3:$E$140,5,FALSE),"-")</f>
         <v>-</v>
       </c>
       <c r="G8" s="21" t="str">
-        <f>IFERROR(VLOOKUP(G7,Database!$A$3:$E$139,5,FALSE),"-")</f>
+        <f>IFERROR(VLOOKUP(G7,Database!$A$3:$E$140,5,FALSE),"-")</f>
         <v>-</v>
       </c>
       <c r="I8" s="40" t="s">
@@ -1676,7 +1679,7 @@
       <c r="A14" s="25" t="s">
         <v>90</v>
       </c>
-      <c r="B14" s="48">
+      <c r="B14" s="46">
         <v>0</v>
       </c>
       <c r="C14" s="18">
@@ -1737,27 +1740,27 @@
         <v>70</v>
       </c>
       <c r="B16" s="21" t="str">
-        <f>IFERROR(VLOOKUP(B15,Database!$A$3:$E$139,5,FALSE),"-")</f>
+        <f>IFERROR(VLOOKUP(B15,Database!$A$3:$E$140,5,FALSE),"-")</f>
         <v>-</v>
       </c>
       <c r="C16" s="21" t="str">
-        <f>IFERROR(VLOOKUP(C15,Database!$A$3:$E$139,5,FALSE),"-")</f>
+        <f>IFERROR(VLOOKUP(C15,Database!$A$3:$E$140,5,FALSE),"-")</f>
         <v>-</v>
       </c>
       <c r="D16" s="21" t="str">
-        <f>IFERROR(VLOOKUP(D15,Database!$A$3:$E$139,5,FALSE),"-")</f>
+        <f>IFERROR(VLOOKUP(D15,Database!$A$3:$E$140,5,FALSE),"-")</f>
         <v>-</v>
       </c>
       <c r="E16" s="21" t="str">
-        <f>IFERROR(VLOOKUP(E15,Database!$A$3:$E$139,5,FALSE),"-")</f>
+        <f>IFERROR(VLOOKUP(E15,Database!$A$3:$E$140,5,FALSE),"-")</f>
         <v>-</v>
       </c>
       <c r="F16" s="21" t="str">
-        <f>IFERROR(VLOOKUP(F15,Database!$A$3:$E$139,5,FALSE),"-")</f>
+        <f>IFERROR(VLOOKUP(F15,Database!$A$3:$E$140,5,FALSE),"-")</f>
         <v>-</v>
       </c>
       <c r="G16" s="21" t="str">
-        <f>IFERROR(VLOOKUP(G15,Database!$A$3:$E$139,5,FALSE),"-")</f>
+        <f>IFERROR(VLOOKUP(G15,Database!$A$3:$E$140,5,FALSE),"-")</f>
         <v>-</v>
       </c>
       <c r="I16" s="40" t="s">
@@ -1837,15 +1840,15 @@
       </c>
     </row>
     <row r="20" spans="1:12" ht="18" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="47" t="s">
+      <c r="A20" s="49" t="s">
         <v>71</v>
       </c>
-      <c r="B20" s="47"/>
-      <c r="C20" s="47"/>
-      <c r="D20" s="47"/>
-      <c r="E20" s="47"/>
-      <c r="F20" s="47"/>
-      <c r="G20" s="47"/>
+      <c r="B20" s="49"/>
+      <c r="C20" s="49"/>
+      <c r="D20" s="49"/>
+      <c r="E20" s="49"/>
+      <c r="F20" s="49"/>
+      <c r="G20" s="49"/>
     </row>
     <row r="21" spans="1:12" ht="16.5" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A21" s="7" t="s">
@@ -1868,15 +1871,20 @@
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A20:G20"/>
   </mergeCells>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B15:G15">
+      <formula1>$A$3:$A$140</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
-            <xm:f>Database!$A$3:$A$139</xm:f>
+            <xm:f>Database!$A$3:$A$140</xm:f>
           </x14:formula1>
-          <xm:sqref>B7:G7 B15:G15</xm:sqref>
+          <xm:sqref>B7:G7</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -1893,15 +1901,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="20.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="46" t="s">
+      <c r="A1" s="48" t="s">
         <v>91</v>
       </c>
-      <c r="B1" s="46"/>
-      <c r="C1" s="46"/>
-      <c r="D1" s="46"/>
-      <c r="E1" s="46"/>
-      <c r="F1" s="46"/>
-      <c r="G1" s="46"/>
+      <c r="B1" s="48"/>
+      <c r="C1" s="48"/>
+      <c r="D1" s="48"/>
+      <c r="E1" s="48"/>
+      <c r="F1" s="48"/>
+      <c r="G1" s="48"/>
     </row>
     <row r="2" spans="1:7" ht="16.5" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A2" s="27" t="s">
@@ -1968,27 +1976,27 @@
         <v>88</v>
       </c>
       <c r="B8" s="21" t="str">
-        <f>IFERROR(VLOOKUP(B7,Database!$A$3:$E$101,4,FALSE),"-")</f>
+        <f>IFERROR(VLOOKUP(B7,Database!$A$3:$E$102,4,FALSE),"-")</f>
         <v>-</v>
       </c>
       <c r="C8" s="21" t="str">
-        <f>IFERROR(VLOOKUP(C7,Database!$A$3:$E$101,4,FALSE),"-")</f>
+        <f>IFERROR(VLOOKUP(C7,Database!$A$3:$E$102,4,FALSE),"-")</f>
         <v>-</v>
       </c>
       <c r="D8" s="21" t="str">
-        <f>IFERROR(VLOOKUP(D7,Database!$A$3:$E$101,4,FALSE),"-")</f>
+        <f>IFERROR(VLOOKUP(D7,Database!$A$3:$E$102,4,FALSE),"-")</f>
         <v>-</v>
       </c>
       <c r="E8" s="21" t="str">
-        <f>IFERROR(VLOOKUP(E7,Database!$A$3:$E$101,4,FALSE),"-")</f>
+        <f>IFERROR(VLOOKUP(E7,Database!$A$3:$E$102,4,FALSE),"-")</f>
         <v>-</v>
       </c>
       <c r="F8" s="21" t="str">
-        <f>IFERROR(VLOOKUP(F7,Database!$A$3:$E$101,4,FALSE),"-")</f>
+        <f>IFERROR(VLOOKUP(F7,Database!$A$3:$E$102,4,FALSE),"-")</f>
         <v>-</v>
       </c>
       <c r="G8" s="21" t="str">
-        <f>IFERROR(VLOOKUP(G7,Database!$A$3:$E$101,4,FALSE),"-")</f>
+        <f>IFERROR(VLOOKUP(G7,Database!$A$3:$E$102,4,FALSE),"-")</f>
         <v>-</v>
       </c>
     </row>
@@ -1997,27 +2005,27 @@
         <v>93</v>
       </c>
       <c r="B9" s="21" t="str">
-        <f>IFERROR(VLOOKUP(B7,Database!$A$3:$E$101,5,FALSE),"-")</f>
+        <f>IFERROR(VLOOKUP(B7,Database!$A$3:$E$102,5,FALSE),"-")</f>
         <v>-</v>
       </c>
       <c r="C9" s="21" t="str">
-        <f>IFERROR(VLOOKUP(C7,Database!$A$3:$E$101,5,FALSE),"-")</f>
+        <f>IFERROR(VLOOKUP(C7,Database!$A$3:$E$102,5,FALSE),"-")</f>
         <v>-</v>
       </c>
       <c r="D9" s="21" t="str">
-        <f>IFERROR(VLOOKUP(D7,Database!$A$3:$E$101,5,FALSE),"-")</f>
+        <f>IFERROR(VLOOKUP(D7,Database!$A$3:$E$102,5,FALSE),"-")</f>
         <v>-</v>
       </c>
       <c r="E9" s="21" t="str">
-        <f>IFERROR(VLOOKUP(E7,Database!$A$3:$E$101,5,FALSE),"-")</f>
+        <f>IFERROR(VLOOKUP(E7,Database!$A$3:$E$102,5,FALSE),"-")</f>
         <v>-</v>
       </c>
       <c r="F9" s="21" t="str">
-        <f>IFERROR(VLOOKUP(F7,Database!$A$3:$E$101,5,FALSE),"-")</f>
+        <f>IFERROR(VLOOKUP(F7,Database!$A$3:$E$102,5,FALSE),"-")</f>
         <v>-</v>
       </c>
       <c r="G9" s="21" t="str">
-        <f>IFERROR(VLOOKUP(G7,Database!$A$3:$E$101,5,FALSE),"-")</f>
+        <f>IFERROR(VLOOKUP(G7,Database!$A$3:$E$102,5,FALSE),"-")</f>
         <v>-</v>
       </c>
     </row>
@@ -2138,27 +2146,27 @@
         <v>88</v>
       </c>
       <c r="B17" s="21" t="str">
-        <f>IFERROR(VLOOKUP(B16,Database!$A$3:$E$101,4,FALSE),"-")</f>
+        <f>IFERROR(VLOOKUP(B16,Database!$A$3:$E$102,4,FALSE),"-")</f>
         <v>-</v>
       </c>
       <c r="C17" s="21" t="str">
-        <f>IFERROR(VLOOKUP(C16,Database!$A$3:$E$101,4,FALSE),"-")</f>
+        <f>IFERROR(VLOOKUP(C16,Database!$A$3:$E$102,4,FALSE),"-")</f>
         <v>-</v>
       </c>
       <c r="D17" s="21" t="str">
-        <f>IFERROR(VLOOKUP(D16,Database!$A$3:$E$101,4,FALSE),"-")</f>
+        <f>IFERROR(VLOOKUP(D16,Database!$A$3:$E$102,4,FALSE),"-")</f>
         <v>-</v>
       </c>
       <c r="E17" s="21" t="str">
-        <f>IFERROR(VLOOKUP(E16,Database!$A$3:$E$101,4,FALSE),"-")</f>
+        <f>IFERROR(VLOOKUP(E16,Database!$A$3:$E$102,4,FALSE),"-")</f>
         <v>-</v>
       </c>
       <c r="F17" s="21" t="str">
-        <f>IFERROR(VLOOKUP(F16,Database!$A$3:$E$101,4,FALSE),"-")</f>
+        <f>IFERROR(VLOOKUP(F16,Database!$A$3:$E$102,4,FALSE),"-")</f>
         <v>-</v>
       </c>
       <c r="G17" s="21" t="str">
-        <f>IFERROR(VLOOKUP(G16,Database!$A$3:$E$101,4,FALSE),"-")</f>
+        <f>IFERROR(VLOOKUP(G16,Database!$A$3:$E$102,4,FALSE),"-")</f>
         <v>-</v>
       </c>
     </row>
@@ -2167,27 +2175,27 @@
         <v>93</v>
       </c>
       <c r="B18" s="21" t="str">
-        <f>IFERROR(VLOOKUP(B16,Database!$A$3:$E$101,5,FALSE),"-")</f>
+        <f>IFERROR(VLOOKUP(B16,Database!$A$3:$E$102,5,FALSE),"-")</f>
         <v>-</v>
       </c>
       <c r="C18" s="21" t="str">
-        <f>IFERROR(VLOOKUP(C16,Database!$A$3:$E$101,5,FALSE),"-")</f>
+        <f>IFERROR(VLOOKUP(C16,Database!$A$3:$E$102,5,FALSE),"-")</f>
         <v>-</v>
       </c>
       <c r="D18" s="21" t="str">
-        <f>IFERROR(VLOOKUP(D16,Database!$A$3:$E$101,5,FALSE),"-")</f>
+        <f>IFERROR(VLOOKUP(D16,Database!$A$3:$E$102,5,FALSE),"-")</f>
         <v>-</v>
       </c>
       <c r="E18" s="21" t="str">
-        <f>IFERROR(VLOOKUP(E16,Database!$A$3:$E$101,5,FALSE),"-")</f>
+        <f>IFERROR(VLOOKUP(E16,Database!$A$3:$E$102,5,FALSE),"-")</f>
         <v>-</v>
       </c>
       <c r="F18" s="21" t="str">
-        <f>IFERROR(VLOOKUP(F16,Database!$A$3:$E$101,5,FALSE),"-")</f>
+        <f>IFERROR(VLOOKUP(F16,Database!$A$3:$E$102,5,FALSE),"-")</f>
         <v>-</v>
       </c>
       <c r="G18" s="21" t="str">
-        <f>IFERROR(VLOOKUP(G16,Database!$A$3:$E$101,5,FALSE),"-")</f>
+        <f>IFERROR(VLOOKUP(G16,Database!$A$3:$E$102,5,FALSE),"-")</f>
         <v>-</v>
       </c>
     </row>
@@ -2298,13 +2306,13 @@
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
-            <xm:f>Database!$A$3:$A$139</xm:f>
+            <xm:f>Database!$A$3:$A$140</xm:f>
           </x14:formula1>
           <xm:sqref>B16:G16</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
-            <xm:f>Database!$A$3:$A$139</xm:f>
+            <xm:f>Database!$A$3:$A$140</xm:f>
           </x14:formula1>
           <xm:sqref>B7:G7</xm:sqref>
         </x14:dataValidation>
@@ -2316,11 +2324,11 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L139"/>
+  <dimension ref="A1:L140"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.5" customWidth="1"/>
-    <col min="2" max="2" width="30.125" customWidth="1"/>
+    <col min="2" max="2" width="36.5" customWidth="1"/>
     <col min="3" max="3" width="13.625" customWidth="1"/>
     <col min="4" max="4" width="17" customWidth="1"/>
     <col min="5" max="5" width="18.125" customWidth="1"/>
@@ -2558,7 +2566,7 @@
         <v>1</v>
       </c>
       <c r="D10" s="5">
-        <f>SUM(($D$47*0.5)+($D$97*0.5))</f>
+        <f>SUM(($D$47*0.5)+($D$98*0.5))</f>
         <v>46.073</v>
       </c>
       <c r="E10" s="4">
@@ -3390,12 +3398,12 @@
         <v>8.9900000000000003E-5</v>
       </c>
       <c r="F48" s="6">
-        <f t="shared" ref="F48:F61" si="2">C48*D48/(E48 * 1000)</f>
+        <f t="shared" ref="F48:F62" si="2">C48*D48/(E48 * 1000)</f>
         <v>22.469410456062288</v>
       </c>
       <c r="G48" s="8"/>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
         <v>178</v>
       </c>
@@ -3418,7 +3426,7 @@
       </c>
       <c r="G49" s="8"/>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
         <v>136</v>
       </c>
@@ -3441,7 +3449,7 @@
       </c>
       <c r="G50" s="8"/>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A51" s="35" t="s">
         <v>237</v>
       </c>
@@ -3464,7 +3472,7 @@
       </c>
       <c r="G51" s="8"/>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
         <v>25</v>
       </c>
@@ -3486,7 +3494,7 @@
         <v>2.4255804016521866E-2</v>
       </c>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
         <v>182</v>
       </c>
@@ -3508,7 +3516,7 @@
         <v>3.5455696202531646E-2</v>
       </c>
     </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
         <v>23</v>
       </c>
@@ -3530,7 +3538,7 @@
         <v>3.7511186874067751E-2</v>
       </c>
     </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
         <v>143</v>
       </c>
@@ -3552,273 +3560,272 @@
         <v>1.2401477832512315E-2</v>
       </c>
     </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="C56" s="1">
+        <v>1</v>
+      </c>
+      <c r="D56" s="5">
+        <v>19</v>
+      </c>
+      <c r="E56" s="4">
+        <f>0.001505*1000</f>
+        <v>1.5050000000000001</v>
+      </c>
+      <c r="F56" s="6">
+        <f t="shared" si="2"/>
+        <v>1.2624584717607971E-2</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A57" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B56" s="1" t="s">
+      <c r="B57" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="C56" s="1">
-        <v>1</v>
-      </c>
-      <c r="D56" s="5">
+      <c r="C57" s="1">
+        <v>1</v>
+      </c>
+      <c r="D57" s="5">
         <v>3.016</v>
       </c>
-      <c r="E56" s="4">
+      <c r="E57" s="4">
         <f>0.000059*1000</f>
         <v>5.8999999999999997E-2</v>
       </c>
-      <c r="F56" s="6">
-        <f>C56*D56/(E56 * 1000)</f>
+      <c r="F57" s="6">
+        <f>C57*D57/(E57 * 1000)</f>
         <v>5.1118644067796613E-2</v>
       </c>
     </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A57" s="1" t="s">
+    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A58" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="B57" s="1" t="s">
+      <c r="B58" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="C57" s="1">
-        <v>1</v>
-      </c>
-      <c r="D57" s="5">
+      <c r="C58" s="1">
+        <v>1</v>
+      </c>
+      <c r="D58" s="5">
         <v>4.0019999999999998</v>
       </c>
-      <c r="E57" s="4">
+      <c r="E58" s="4">
         <f>0.0001786*1000</f>
         <v>0.17860000000000001</v>
       </c>
-      <c r="F57" s="6">
-        <f>C57*D57/(E57 * 1000)</f>
+      <c r="F58" s="6">
+        <f>C58*D58/(E58 * 1000)</f>
         <v>2.2407614781634933E-2</v>
       </c>
     </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A58" s="1" t="s">
+    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A59" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="B58" s="1" t="s">
+      <c r="B59" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C58" s="1">
-        <v>1</v>
-      </c>
-      <c r="D58" s="5">
+      <c r="C59" s="1">
+        <v>1</v>
+      </c>
+      <c r="D59" s="5">
         <v>2.02</v>
       </c>
-      <c r="E58" s="4">
+      <c r="E59" s="4">
         <f>0.00007085*1000</f>
         <v>7.0849999999999996E-2</v>
       </c>
-      <c r="F58" s="6">
-        <f>C58*D58/(E58 * 1000)</f>
+      <c r="F59" s="6">
+        <f>C59*D59/(E59 * 1000)</f>
         <v>2.8510938602681724E-2</v>
       </c>
     </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A59" s="1" t="s">
+    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A60" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B59" s="1" t="s">
+      <c r="B60" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C59" s="1">
-        <v>1</v>
-      </c>
-      <c r="D59" s="5">
+      <c r="C60" s="1">
+        <v>1</v>
+      </c>
+      <c r="D60" s="5">
         <v>16.05</v>
       </c>
-      <c r="E59" s="4">
+      <c r="E60" s="4">
         <f>0.00042561*1000</f>
         <v>0.42560999999999999</v>
       </c>
-      <c r="F59" s="6">
+      <c r="F60" s="6">
         <f t="shared" si="2"/>
         <v>3.7710580108550079E-2</v>
       </c>
     </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A60" s="1" t="s">
+    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A61" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="B60" s="9" t="s">
+      <c r="B61" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="C60" s="9">
-        <v>1</v>
-      </c>
-      <c r="D60" s="10">
+      <c r="C61" s="9">
+        <v>1</v>
+      </c>
+      <c r="D61" s="10">
         <v>32</v>
       </c>
-      <c r="E60" s="11">
+      <c r="E61" s="11">
         <f>0.001141*1000</f>
         <v>1.141</v>
       </c>
-      <c r="F60" s="12">
+      <c r="F61" s="12">
         <f t="shared" si="2"/>
         <v>2.8045574057843997E-2</v>
       </c>
     </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A61" s="1" t="s">
+    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A62" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="B61" s="1" t="s">
+      <c r="B62" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="C61" s="1">
-        <v>1</v>
-      </c>
-      <c r="D61" s="5">
+      <c r="C62" s="1">
+        <v>1</v>
+      </c>
+      <c r="D62" s="5">
         <v>28.01</v>
       </c>
-      <c r="E61" s="4">
+      <c r="E62" s="4">
         <f>0.000824907*1000</f>
         <v>0.82490700000000006</v>
       </c>
-      <c r="F61" s="6">
+      <c r="F62" s="6">
         <f t="shared" si="2"/>
         <v>3.3955342844708553E-2</v>
       </c>
     </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A62" s="1" t="s">
+    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A63" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="B62" s="1"/>
-      <c r="C62" s="1">
-        <v>1</v>
-      </c>
-      <c r="D62" s="5"/>
-      <c r="E62" s="4">
+      <c r="B63" s="1"/>
+      <c r="C63" s="1">
+        <v>1</v>
+      </c>
+      <c r="D63" s="5"/>
+      <c r="E63" s="4">
         <f>0.00378*1000</f>
         <v>3.78</v>
       </c>
-      <c r="F62" s="6"/>
-    </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A63" s="1" t="s">
+      <c r="F63" s="6"/>
+    </row>
+    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A64" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="B63" s="1"/>
-      <c r="C63" s="1">
-        <v>1</v>
-      </c>
-      <c r="D63" s="5"/>
-      <c r="E63" s="4">
+      <c r="B64" s="1"/>
+      <c r="C64" s="1">
+        <v>1</v>
+      </c>
+      <c r="D64" s="5"/>
+      <c r="E64" s="4">
         <f>0.001*1000</f>
         <v>1</v>
       </c>
-      <c r="F63" s="6"/>
-    </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A64" s="1" t="s">
+      <c r="F64" s="6"/>
+    </row>
+    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A65" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="B64" s="1" t="s">
+      <c r="B65" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C64" s="1">
-        <v>1</v>
-      </c>
-      <c r="D64" s="5">
-        <f>D58</f>
+      <c r="C65" s="1">
+        <v>1</v>
+      </c>
+      <c r="D65" s="5">
+        <f>D59</f>
         <v>2.02</v>
       </c>
-      <c r="E64" s="4">
+      <c r="E65" s="4">
         <f>0.007085*1000</f>
         <v>7.085</v>
       </c>
-      <c r="F64" s="6">
-        <f t="shared" ref="F64:F73" si="3">C64*D64/(E64 * 1000)</f>
+      <c r="F65" s="6">
+        <f t="shared" ref="F65:F74" si="3">C65*D65/(E65 * 1000)</f>
         <v>2.851093860268172E-4</v>
       </c>
-      <c r="H64">
+      <c r="H65">
         <f>0.000824907*4</f>
         <v>3.2996280000000002E-3</v>
       </c>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A65" s="1" t="s">
+    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A66" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="B65" s="1" t="s">
+      <c r="B66" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="C65" s="1">
-        <v>1</v>
-      </c>
-      <c r="D65" s="5">
+      <c r="C66" s="1">
+        <v>1</v>
+      </c>
+      <c r="D66" s="5">
         <v>159.69</v>
       </c>
-      <c r="E65" s="4">
+      <c r="E66" s="4">
         <f>0.0055*1000</f>
         <v>5.5</v>
       </c>
-      <c r="F65" s="6">
+      <c r="F66" s="6">
         <f t="shared" si="3"/>
         <v>2.9034545454545455E-2</v>
       </c>
-      <c r="H65">
+      <c r="H66">
         <f>0.000001784*6</f>
         <v>1.0703999999999999E-5</v>
       </c>
     </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A66" s="1" t="s">
+    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A67" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="B66" s="1" t="s">
+      <c r="B67" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="C66" s="1">
-        <v>1</v>
-      </c>
-      <c r="D66" s="5">
+      <c r="C67" s="1">
+        <v>1</v>
+      </c>
+      <c r="D67" s="5">
         <v>159.69</v>
       </c>
-      <c r="E66" s="4">
+      <c r="E67" s="4">
         <f>0.026*1000</f>
         <v>26</v>
       </c>
-      <c r="F66" s="6">
+      <c r="F67" s="6">
         <f t="shared" si="3"/>
         <v>6.1419230769230769E-3</v>
       </c>
-      <c r="H66">
-        <f>H64+H65</f>
+      <c r="H67">
+        <f>H65+H66</f>
         <v>3.310332E-3</v>
-      </c>
-    </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A67" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="B67" s="1" t="s">
-        <v>200</v>
-      </c>
-      <c r="C67" s="1">
-        <v>1</v>
-      </c>
-      <c r="D67" s="5">
-        <f>55.845*2</f>
-        <v>111.69</v>
-      </c>
-      <c r="E67" s="4">
-        <f>0.039*1000</f>
-        <v>39</v>
-      </c>
-      <c r="F67" s="6">
-        <f t="shared" si="3"/>
-        <v>2.8638461538461539E-3</v>
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B68" s="1" t="s">
         <v>200</v>
@@ -3831,1054 +3838,1065 @@
         <v>111.69</v>
       </c>
       <c r="E68" s="4">
+        <f>0.039*1000</f>
+        <v>39</v>
+      </c>
+      <c r="F68" s="6">
+        <f t="shared" si="3"/>
+        <v>2.8638461538461539E-3</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A69" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="B69" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="C69" s="1">
+        <v>1</v>
+      </c>
+      <c r="D69" s="5">
+        <f>55.845*2</f>
+        <v>111.69</v>
+      </c>
+      <c r="E69" s="4">
         <f>0.0078*1000</f>
         <v>7.8</v>
       </c>
-      <c r="F68" s="6">
+      <c r="F69" s="6">
         <f t="shared" si="3"/>
         <v>1.4319230769230768E-2</v>
       </c>
     </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A69" s="1" t="s">
+    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A70" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B69" s="1" t="s">
+      <c r="B70" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C69" s="1">
-        <v>1</v>
-      </c>
-      <c r="D69" s="5">
+      <c r="C70" s="1">
+        <v>1</v>
+      </c>
+      <c r="D70" s="5">
         <f>12.02+4*1.008</f>
         <v>16.052</v>
       </c>
-      <c r="E69" s="4">
+      <c r="E70" s="4">
         <f>0.000000717*1000</f>
         <v>7.1699999999999997E-4</v>
       </c>
-      <c r="F69" s="6">
+      <c r="F70" s="6">
         <f t="shared" si="3"/>
         <v>22.387726638772666</v>
       </c>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A70" s="1" t="s">
+    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A71" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="B70" s="1" t="s">
+      <c r="B71" s="1" t="s">
         <v>223</v>
       </c>
-      <c r="C70" s="1">
-        <v>1</v>
-      </c>
-      <c r="D70" s="5">
+      <c r="C71" s="1">
+        <v>1</v>
+      </c>
+      <c r="D71" s="5">
         <f>323.31+78.07</f>
         <v>401.38</v>
       </c>
-      <c r="E70" s="4">
+      <c r="E71" s="4">
         <f>0.0027*1000</f>
         <v>2.7</v>
       </c>
-      <c r="F70" s="6">
+      <c r="F71" s="6">
         <f t="shared" si="3"/>
         <v>0.14865925925925927</v>
       </c>
     </row>
-    <row r="71" spans="1:8" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A71" s="1" t="s">
+    <row r="72" spans="1:8" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="A72" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="B71" s="1" t="s">
+      <c r="B72" s="1" t="s">
         <v>173</v>
       </c>
-      <c r="C71" s="1">
-        <v>1</v>
-      </c>
-      <c r="D71" s="5">
+      <c r="C72" s="1">
+        <v>1</v>
+      </c>
+      <c r="D72" s="5">
         <v>46.07</v>
       </c>
-      <c r="E71" s="4">
+      <c r="E72" s="4">
         <f>0.00088*1000</f>
         <v>0.88</v>
       </c>
-      <c r="F71" s="6">
+      <c r="F72" s="6">
         <f t="shared" si="3"/>
         <v>5.2352272727272726E-2</v>
       </c>
     </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A72" s="35" t="s">
+    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A73" s="35" t="s">
         <v>202</v>
       </c>
-      <c r="B72" s="35" t="s">
+      <c r="B73" s="35" t="s">
         <v>203</v>
       </c>
-      <c r="C72" s="35">
-        <v>1</v>
-      </c>
-      <c r="D72" s="36">
+      <c r="C73" s="35">
+        <v>1</v>
+      </c>
+      <c r="D73" s="36">
         <v>60.08</v>
       </c>
-      <c r="E72" s="37">
+      <c r="E73" s="37">
         <f>0.00347*1000</f>
         <v>3.47</v>
       </c>
-      <c r="F72" s="38">
-        <f>C72*D72/(E72 * 1000)</f>
+      <c r="F73" s="38">
+        <f>C73*D73/(E73 * 1000)</f>
         <v>1.7314121037463978E-2</v>
       </c>
     </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A73" s="1" t="s">
+    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A74" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="B73" s="1" t="s">
+      <c r="B74" s="1" t="s">
         <v>217</v>
       </c>
-      <c r="C73" s="1">
-        <v>1</v>
-      </c>
-      <c r="D73" s="5">
+      <c r="C74" s="1">
+        <v>1</v>
+      </c>
+      <c r="D74" s="5">
         <v>750.27</v>
       </c>
-      <c r="E73" s="4">
+      <c r="E74" s="4">
         <f>0.005*1000</f>
         <v>5</v>
       </c>
-      <c r="F73" s="6">
+      <c r="F74" s="6">
         <f t="shared" si="3"/>
         <v>0.15005399999999999</v>
       </c>
     </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A74" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="B74" s="1"/>
-      <c r="C74" s="1">
-        <v>1</v>
-      </c>
-      <c r="D74" s="5"/>
-      <c r="E74" s="4">
-        <f>0.001*1000</f>
-        <v>1</v>
-      </c>
-      <c r="F74" s="6"/>
-    </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="B75" s="1"/>
+      <c r="C75" s="1">
+        <v>1</v>
+      </c>
+      <c r="D75" s="5"/>
+      <c r="E75" s="4">
+        <f>0.001*1000</f>
+        <v>1</v>
+      </c>
+      <c r="F75" s="6"/>
+    </row>
+    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A76" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="B75" s="1" t="s">
+      <c r="B76" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="C75" s="1">
-        <v>1</v>
-      </c>
-      <c r="D75" s="5">
+      <c r="C76" s="1">
+        <v>1</v>
+      </c>
+      <c r="D76" s="5">
         <f>14.007*2</f>
         <v>28.013999999999999</v>
       </c>
-      <c r="E75" s="4">
+      <c r="E76" s="4">
         <f>0.000001251*1000</f>
         <v>1.2509999999999999E-3</v>
       </c>
-      <c r="F75" s="6">
-        <f>C75*D75/(E75 * 1000)</f>
+      <c r="F76" s="6">
+        <f>C76*D76/(E76 * 1000)</f>
         <v>22.393285371702639</v>
       </c>
     </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A76" s="1" t="s">
+    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A77" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="B76" s="1" t="s">
+      <c r="B77" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="C76" s="1">
-        <v>1</v>
-      </c>
-      <c r="D76" s="5">
+      <c r="C77" s="1">
+        <v>1</v>
+      </c>
+      <c r="D77" s="5">
         <v>92.04</v>
       </c>
-      <c r="E76" s="4">
+      <c r="E77" s="4">
         <f>0.00145*1000</f>
         <v>1.45</v>
       </c>
-      <c r="F76" s="6">
-        <f>C76*D76/(E76 * 1000)</f>
+      <c r="F77" s="6">
+        <f>C77*D77/(E77 * 1000)</f>
         <v>6.3475862068965522E-2</v>
       </c>
     </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A77" s="1" t="s">
+    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A78" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="B77" s="1"/>
-      <c r="C77" s="1">
-        <v>1</v>
-      </c>
-      <c r="D77" s="5"/>
-      <c r="E77" s="4">
+      <c r="B78" s="1"/>
+      <c r="C78" s="1">
+        <v>1</v>
+      </c>
+      <c r="D78" s="5"/>
+      <c r="E78" s="4">
         <f>0.00105*1000</f>
         <v>1.05</v>
       </c>
-      <c r="F77" s="6"/>
-    </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A78" s="35" t="s">
+      <c r="F78" s="6"/>
+    </row>
+    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A79" s="35" t="s">
         <v>235</v>
       </c>
-      <c r="B78" s="35" t="s">
+      <c r="B79" s="35" t="s">
         <v>236</v>
       </c>
-      <c r="C78" s="35">
-        <v>1</v>
-      </c>
-      <c r="D78" s="36">
+      <c r="C79" s="35">
+        <v>1</v>
+      </c>
+      <c r="D79" s="36">
         <f>(14.005*8)+(39.95*6)</f>
         <v>351.74</v>
       </c>
-      <c r="E78" s="37">
+      <c r="E79" s="37">
         <f>0.003310332*1000</f>
         <v>3.3103319999999998</v>
       </c>
-      <c r="F78" s="38">
-        <f>C78*D78/(E78 * 1000)</f>
+      <c r="F79" s="38">
+        <f>C79*D79/(E79 * 1000)</f>
         <v>0.10625520340557987</v>
       </c>
-    </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A79" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="B79" s="1"/>
-      <c r="C79" s="1">
-        <v>1</v>
-      </c>
-      <c r="D79" s="5"/>
-      <c r="E79" s="4">
-        <f>0.001*1000</f>
-        <v>1</v>
-      </c>
-      <c r="F79" s="6"/>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="B80" s="1"/>
+      <c r="C80" s="1">
+        <v>1</v>
+      </c>
+      <c r="D80" s="5"/>
+      <c r="E80" s="4">
+        <f>0.001*1000</f>
+        <v>1</v>
+      </c>
+      <c r="F80" s="6"/>
+    </row>
+    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A81" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="B80" s="1" t="s">
+      <c r="B81" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C80" s="1">
-        <v>1</v>
-      </c>
-      <c r="D80" s="5">
+      <c r="C81" s="1">
+        <v>1</v>
+      </c>
+      <c r="D81" s="5">
         <v>32</v>
       </c>
-      <c r="E80" s="4">
+      <c r="E81" s="4">
         <f>0.00000141*1000</f>
         <v>1.41E-3</v>
       </c>
-      <c r="F80" s="6">
-        <f>C80*D80/(E80 * 1000)</f>
+      <c r="F81" s="6">
+        <f>C81*D81/(E81 * 1000)</f>
         <v>22.695035460992909</v>
       </c>
     </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A81" s="1" t="s">
+    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A82" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B81" s="1" t="s">
+      <c r="B82" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="C81" s="1">
-        <v>1</v>
-      </c>
-      <c r="D81" s="5">
+      <c r="C82" s="1">
+        <v>1</v>
+      </c>
+      <c r="D82" s="5">
         <v>30.97</v>
       </c>
-      <c r="E81" s="17">
+      <c r="E82" s="17">
         <f>$E$4</f>
         <v>5</v>
       </c>
-      <c r="F81" s="6">
-        <f>C81*D81/(E81 * 1000)</f>
+      <c r="F82" s="6">
+        <f>C82*D82/(E82 * 1000)</f>
         <v>6.1939999999999999E-3</v>
       </c>
     </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A82" s="1" t="s">
+    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A83" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="B82" s="1" t="s">
+      <c r="B83" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="C82" s="1">
-        <v>1</v>
-      </c>
-      <c r="D82" s="5">
+      <c r="C83" s="1">
+        <v>1</v>
+      </c>
+      <c r="D83" s="5">
         <v>244</v>
       </c>
-      <c r="E82" s="4">
+      <c r="E83" s="4">
         <f>0.019816*1000</f>
         <v>19.815999999999999</v>
       </c>
-      <c r="F82" s="6">
-        <f>C82*D82/(E82 * 1000)</f>
+      <c r="F83" s="6">
+        <f>C83*D83/(E83 * 1000)</f>
         <v>1.2313282196205087E-2</v>
       </c>
     </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A83" s="1" t="s">
+    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A84" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="B83" s="1"/>
-      <c r="C83" s="1">
-        <v>1</v>
-      </c>
-      <c r="D83" s="5"/>
-      <c r="E83" s="4">
+      <c r="B84" s="1"/>
+      <c r="C84" s="1">
+        <v>1</v>
+      </c>
+      <c r="D84" s="5"/>
+      <c r="E84" s="4">
         <f>0.00104*1000</f>
         <v>1.0399999999999998</v>
       </c>
-      <c r="F83" s="6"/>
-    </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A84" s="1" t="s">
+      <c r="F84" s="6"/>
+    </row>
+    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A85" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="B84" s="1" t="s">
+      <c r="B85" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="C84" s="1">
-        <v>1</v>
-      </c>
-      <c r="D84" s="5">
+      <c r="C85" s="1">
+        <v>1</v>
+      </c>
+      <c r="D85" s="5">
         <f>195.078</f>
         <v>195.078</v>
       </c>
-      <c r="E84" s="4">
+      <c r="E85" s="4">
         <f>0.0078*1000</f>
         <v>7.8</v>
       </c>
-      <c r="F84" s="6">
-        <f>C84*D84/(E84 * 1000)</f>
+      <c r="F85" s="6">
+        <f>C85*D85/(E85 * 1000)</f>
         <v>2.5010000000000001E-2</v>
       </c>
     </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A85" s="1" t="s">
+    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A86" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="B85" s="1"/>
-      <c r="C85" s="1">
-        <v>1</v>
-      </c>
-      <c r="D85" s="5"/>
-      <c r="E85" s="4">
+      <c r="B86" s="1"/>
+      <c r="C86" s="1">
+        <v>1</v>
+      </c>
+      <c r="D86" s="5"/>
+      <c r="E86" s="4">
         <f>0.00378*1000</f>
         <v>3.78</v>
       </c>
-      <c r="F85" s="6"/>
-    </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A86" s="1" t="s">
+      <c r="F86" s="6"/>
+    </row>
+    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A87" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="B86" s="1"/>
-      <c r="C86" s="1">
-        <v>1</v>
-      </c>
-      <c r="D86" s="5"/>
-      <c r="E86" s="4">
+      <c r="B87" s="1"/>
+      <c r="C87" s="1">
+        <v>1</v>
+      </c>
+      <c r="D87" s="5"/>
+      <c r="E87" s="4">
         <f>0.0052*1000</f>
         <v>5.2</v>
       </c>
-      <c r="F86" s="6"/>
-    </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A87" s="1" t="s">
+      <c r="F87" s="6"/>
+    </row>
+    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A88" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B87" s="1"/>
-      <c r="C87" s="1">
-        <v>1</v>
-      </c>
-      <c r="D87" s="5"/>
-      <c r="E87" s="4">
+      <c r="B88" s="1"/>
+      <c r="C88" s="1">
+        <v>1</v>
+      </c>
+      <c r="D88" s="5"/>
+      <c r="E88" s="4">
         <f>0.0025*1000</f>
         <v>2.5</v>
       </c>
-      <c r="F87" s="6"/>
-    </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A88" s="1" t="s">
+      <c r="F88" s="6"/>
+    </row>
+    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A89" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="B88" s="1"/>
-      <c r="C88" s="1">
-        <v>1</v>
-      </c>
-      <c r="D88" s="5"/>
-      <c r="E88" s="4">
+      <c r="B89" s="1"/>
+      <c r="C89" s="1">
+        <v>1</v>
+      </c>
+      <c r="D89" s="5"/>
+      <c r="E89" s="4">
         <f>0.004*1000</f>
         <v>4</v>
       </c>
-      <c r="F88" s="6"/>
-    </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A89" s="1" t="s">
+      <c r="F89" s="6"/>
+    </row>
+    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A90" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="B89" s="1" t="s">
+      <c r="B90" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="C89" s="1">
-        <v>1</v>
-      </c>
-      <c r="D89" s="5">
+      <c r="C90" s="1">
+        <v>1</v>
+      </c>
+      <c r="D90" s="5">
         <v>76.08</v>
       </c>
-      <c r="E89" s="4">
+      <c r="E90" s="4">
         <f>0.0025*1000</f>
         <v>2.5</v>
       </c>
-      <c r="F89" s="6">
-        <f>C89*D89/(E89 * 1000)</f>
+      <c r="F90" s="6">
+        <f>C90*D90/(E90 * 1000)</f>
         <v>3.0432000000000001E-2</v>
       </c>
     </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A90" s="1" t="s">
+    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A91" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="B90" s="1" t="s">
+      <c r="B91" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="C90" s="1">
-        <v>1</v>
-      </c>
-      <c r="D90" s="5">
+      <c r="C91" s="1">
+        <v>1</v>
+      </c>
+      <c r="D91" s="5">
         <v>28.09</v>
       </c>
-      <c r="E90" s="4">
+      <c r="E91" s="4">
         <f>0.002329*1000</f>
         <v>2.3289999999999997</v>
       </c>
-      <c r="F90" s="6">
-        <f>C90*D90/(E90 * 1000)</f>
+      <c r="F91" s="6">
+        <f>C91*D91/(E91 * 1000)</f>
         <v>1.2060970373550882E-2</v>
       </c>
     </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A91" s="1" t="s">
+    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A92" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="B91" s="1"/>
-      <c r="C91" s="1">
-        <v>1</v>
-      </c>
-      <c r="D91" s="5"/>
-      <c r="E91" s="4">
+      <c r="B92" s="1"/>
+      <c r="C92" s="1">
+        <v>1</v>
+      </c>
+      <c r="D92" s="5"/>
+      <c r="E92" s="4">
         <f>0.00378*1000</f>
         <v>3.78</v>
       </c>
-      <c r="F91" s="6"/>
-    </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A92" s="1" t="s">
+      <c r="F92" s="6"/>
+    </row>
+    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A93" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="B92" s="1" t="s">
+      <c r="B93" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="C92" s="1">
-        <v>1</v>
-      </c>
-      <c r="D92" s="5">
+      <c r="C93" s="1">
+        <v>1</v>
+      </c>
+      <c r="D93" s="5">
         <v>186.09</v>
       </c>
-      <c r="E92" s="4">
+      <c r="E93" s="4">
         <f>0.0031*1000</f>
         <v>3.1</v>
       </c>
-      <c r="F92" s="6">
-        <f>C92*D92/(E92 * 1000)</f>
+      <c r="F93" s="6">
+        <f>C93*D93/(E93 * 1000)</f>
         <v>6.0029032258064517E-2</v>
       </c>
     </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A93" s="1" t="s">
+    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A94" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="B93" s="1"/>
-      <c r="C93" s="1">
-        <v>1</v>
-      </c>
-      <c r="D93" s="5"/>
-      <c r="E93" s="4">
+      <c r="B94" s="1"/>
+      <c r="C94" s="1">
+        <v>1</v>
+      </c>
+      <c r="D94" s="5"/>
+      <c r="E94" s="4">
         <f>0.0016*1000</f>
         <v>1.6</v>
       </c>
-      <c r="F93" s="6"/>
-    </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A94" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="B94" s="1"/>
-      <c r="C94" s="1">
-        <v>1</v>
-      </c>
-      <c r="D94" s="5"/>
-      <c r="E94" s="4">
-        <f>0.001*1000</f>
-        <v>1</v>
-      </c>
       <c r="F94" s="6"/>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="B95" s="1"/>
+      <c r="C95" s="1">
+        <v>1</v>
+      </c>
+      <c r="D95" s="5"/>
+      <c r="E95" s="4">
+        <f>0.001*1000</f>
+        <v>1</v>
+      </c>
+      <c r="F95" s="6"/>
+    </row>
+    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A96" s="1" t="s">
         <v>218</v>
       </c>
-      <c r="B95" s="1" t="s">
+      <c r="B96" s="1" t="s">
         <v>219</v>
       </c>
-      <c r="C95" s="1">
-        <v>1</v>
-      </c>
-      <c r="D95" s="5">
+      <c r="C96" s="1">
+        <v>1</v>
+      </c>
+      <c r="D96" s="5">
         <v>232.04</v>
       </c>
-      <c r="E95" s="4">
+      <c r="E96" s="4">
         <f>0.0117*1000</f>
         <v>11.700000000000001</v>
       </c>
-      <c r="F95" s="6">
-        <f>C95*D95/(E95 * 1000)</f>
+      <c r="F96" s="6">
+        <f>C96*D96/(E96 * 1000)</f>
         <v>1.9832478632478629E-2</v>
       </c>
     </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A96" s="1" t="s">
+    <row r="97" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A97" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="B96" s="1" t="s">
+      <c r="B97" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="C96" s="1">
-        <v>1</v>
-      </c>
-      <c r="D96" s="5">
+      <c r="C97" s="1">
+        <v>1</v>
+      </c>
+      <c r="D97" s="5">
         <v>270.02999999999997</v>
       </c>
-      <c r="E96" s="4">
+      <c r="E97" s="4">
         <f>0.0075*1000</f>
         <v>7.5</v>
       </c>
-      <c r="F96" s="6">
-        <f>C96*D96/(E96 * 1000)</f>
+      <c r="F97" s="6">
+        <f>C97*D97/(E97 * 1000)</f>
         <v>3.6003999999999994E-2</v>
       </c>
     </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A97" s="1" t="s">
+    <row r="98" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A98" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="B97" s="1" t="s">
+      <c r="B98" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="C97" s="1">
-        <v>1</v>
-      </c>
-      <c r="D97" s="5">
+      <c r="C98" s="1">
+        <v>1</v>
+      </c>
+      <c r="D98" s="5">
         <v>60.1</v>
       </c>
-      <c r="E97" s="4">
+      <c r="E98" s="4">
         <f>0.000791*1000</f>
         <v>0.79100000000000004</v>
       </c>
-      <c r="F97" s="6">
-        <f>C97*D97/(E97 * 1000)</f>
+      <c r="F98" s="6">
+        <f>C98*D98/(E98 * 1000)</f>
         <v>7.5979772439949439E-2</v>
       </c>
     </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A98" s="1" t="s">
+    <row r="99" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A99" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="B98" s="1" t="s">
+      <c r="B99" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="C98" s="1">
-        <v>1</v>
-      </c>
-      <c r="D98" s="5">
-        <f>SUM(($D$47*0.25)+($D$97*0.75))</f>
+      <c r="C99" s="1">
+        <v>1</v>
+      </c>
+      <c r="D99" s="5">
+        <f>SUM(($D$47*0.25)+($D$98*0.75))</f>
         <v>53.086500000000001</v>
       </c>
-      <c r="E98" s="4">
+      <c r="E99" s="4">
         <f>0.000829*1000</f>
         <v>0.82899999999999996</v>
       </c>
-      <c r="F98" s="6">
-        <f>C98*D98/(E98 * 1000)</f>
+      <c r="F99" s="6">
+        <f>C99*D99/(E99 * 1000)</f>
         <v>6.4036791314837152E-2</v>
       </c>
     </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A99" s="1" t="s">
+    <row r="100" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A100" s="1" t="s">
         <v>194</v>
       </c>
-      <c r="B99" s="1"/>
-      <c r="C99" s="1">
-        <v>1</v>
-      </c>
-      <c r="D99" s="5"/>
-      <c r="E99" s="4">
+      <c r="B100" s="1"/>
+      <c r="C100" s="1">
+        <v>1</v>
+      </c>
+      <c r="D100" s="5"/>
+      <c r="E100" s="4">
         <f>0.00075*1000</f>
         <v>0.75</v>
       </c>
-      <c r="F99" s="6"/>
-    </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A100" s="1" t="s">
+      <c r="F100" s="6"/>
+    </row>
+    <row r="101" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A101" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="B100" s="1"/>
-      <c r="C100" s="1">
-        <v>1</v>
-      </c>
-      <c r="D100" s="5"/>
-      <c r="E100" s="4">
+      <c r="B101" s="1"/>
+      <c r="C101" s="1">
+        <v>1</v>
+      </c>
+      <c r="D101" s="5"/>
+      <c r="E101" s="4">
         <f>0.001005*1000</f>
         <v>1.0050000000000001</v>
       </c>
-      <c r="F100" s="6"/>
-    </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A101" s="1" t="s">
+      <c r="F101" s="6"/>
+    </row>
+    <row r="102" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A102" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="B101" s="1" t="s">
+      <c r="B102" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="C101" s="1">
-        <v>1</v>
-      </c>
-      <c r="D101" s="5">
+      <c r="C102" s="1">
+        <v>1</v>
+      </c>
+      <c r="D102" s="5">
         <v>18.02</v>
       </c>
-      <c r="E101" s="4">
+      <c r="E102" s="4">
         <f>0.001*1000</f>
         <v>1</v>
       </c>
-      <c r="F101" s="6">
-        <f>C101*D101/(E101 * 1000)</f>
+      <c r="F102" s="6">
+        <f>C102*D102/(E102 * 1000)</f>
         <v>1.8020000000000001E-2</v>
       </c>
     </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A103" s="1" t="s">
+    <row r="104" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A104" s="1" t="s">
         <v>97</v>
-      </c>
-    </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A104" s="29" t="s">
-        <v>98</v>
-      </c>
-      <c r="D104" s="30"/>
-      <c r="E104" s="4">
-        <f t="shared" ref="E104:E139" si="4">F104*1000</f>
-        <v>5</v>
-      </c>
-      <c r="F104" s="6">
-        <v>5.0000000000000001E-3</v>
       </c>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A105" s="29" t="s">
+        <v>98</v>
+      </c>
+      <c r="D105" s="30"/>
+      <c r="E105" s="4">
+        <f t="shared" ref="E105:E140" si="4">F105*1000</f>
+        <v>5</v>
+      </c>
+      <c r="F105" s="6">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="106" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A106" s="29" t="s">
         <v>106</v>
       </c>
-      <c r="E105" s="4">
+      <c r="E106" s="4">
         <f t="shared" si="4"/>
         <v>19.3</v>
       </c>
-      <c r="F105" s="6">
+      <c r="F106" s="6">
         <v>1.9300000000000001E-2</v>
       </c>
     </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A106" s="29" t="s">
+    <row r="107" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A107" s="29" t="s">
         <v>51</v>
       </c>
-      <c r="E106" s="4">
+      <c r="E107" s="4">
         <f t="shared" si="4"/>
         <v>54.4</v>
       </c>
-      <c r="F106" s="6">
+      <c r="F107" s="6">
         <v>5.4399999999999997E-2</v>
       </c>
     </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A107" s="29" t="s">
+    <row r="108" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A108" s="29" t="s">
         <v>99</v>
       </c>
-      <c r="E107" s="4">
+      <c r="E108" s="4">
         <f t="shared" si="4"/>
         <v>5</v>
       </c>
-      <c r="F107" s="6">
+      <c r="F108" s="6">
         <v>5.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A108" s="29" t="s">
+    <row r="109" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A109" s="29" t="s">
         <v>108</v>
       </c>
-      <c r="E108" s="4">
+      <c r="E109" s="4">
         <f t="shared" si="4"/>
         <v>7</v>
       </c>
-      <c r="F108" s="6">
+      <c r="F109" s="6">
         <v>7.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A109" s="29" t="s">
+    <row r="110" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A110" s="29" t="s">
         <v>142</v>
       </c>
-      <c r="E109" s="4">
+      <c r="E110" s="4">
         <f t="shared" si="4"/>
         <v>0.53399999999999992</v>
       </c>
-      <c r="F109" s="6">
+      <c r="F110" s="6">
         <v>5.3399999999999997E-4</v>
       </c>
     </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A110" s="29" t="s">
+    <row r="111" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A111" s="29" t="s">
         <v>100</v>
       </c>
-      <c r="E110" s="4">
+      <c r="E111" s="4">
         <f t="shared" si="4"/>
         <v>6.0000000000000005E-2</v>
       </c>
-      <c r="F110" s="6">
+      <c r="F111" s="6">
         <v>6.0000000000000002E-5</v>
       </c>
     </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A111" s="29" t="s">
+    <row r="112" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A112" s="29" t="s">
         <v>104</v>
       </c>
-      <c r="E111" s="4">
+      <c r="E112" s="4">
         <f t="shared" si="4"/>
         <v>2.5</v>
       </c>
-      <c r="F111" s="6">
+      <c r="F112" s="6">
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A112" s="29" t="s">
+    <row r="113" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A113" s="29" t="s">
         <v>61</v>
       </c>
-      <c r="E112" s="4">
+      <c r="E113" s="4">
         <f t="shared" si="4"/>
         <v>5.0108799999999993</v>
       </c>
-      <c r="F112" s="6">
+      <c r="F113" s="6">
         <v>5.0108799999999997E-3</v>
       </c>
     </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A113" s="29" t="s">
+    <row r="114" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A114" s="29" t="s">
         <v>109</v>
       </c>
-      <c r="E113" s="4">
+      <c r="E114" s="4">
         <f t="shared" si="4"/>
         <v>4.3499999999999996</v>
       </c>
-      <c r="F113" s="6">
+      <c r="F114" s="6">
         <v>4.3499999999999997E-3</v>
       </c>
     </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A114" s="29" t="s">
+    <row r="115" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A115" s="29" t="s">
         <v>103</v>
       </c>
-      <c r="E114" s="4">
+      <c r="E115" s="4">
         <f t="shared" si="4"/>
         <v>0.216</v>
       </c>
-      <c r="F114" s="6">
+      <c r="F115" s="6">
         <v>2.1599999999999999E-4</v>
       </c>
     </row>
-    <row r="115" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A115" s="29" t="s">
+    <row r="116" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A116" s="29" t="s">
         <v>52</v>
       </c>
-      <c r="E115" s="4">
+      <c r="E116" s="4">
         <f t="shared" si="4"/>
         <v>23.125</v>
       </c>
-      <c r="F115" s="6">
+      <c r="F116" s="6">
         <v>2.3125E-2</v>
       </c>
     </row>
-    <row r="116" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A116" s="29" t="s">
+    <row r="117" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A117" s="29" t="s">
         <v>53</v>
       </c>
-      <c r="E116" s="4">
+      <c r="E117" s="4">
         <f t="shared" si="4"/>
         <v>5.25</v>
       </c>
-      <c r="F116" s="6">
+      <c r="F117" s="6">
         <v>5.2500000000000003E-3</v>
       </c>
     </row>
-    <row r="117" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A117" s="29" t="s">
+    <row r="118" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A118" s="29" t="s">
         <v>224</v>
       </c>
-      <c r="E117" s="4">
+      <c r="E118" s="4">
         <f t="shared" si="4"/>
         <v>6.24</v>
       </c>
-      <c r="F117" s="6">
+      <c r="F118" s="6">
         <v>6.2399999999999999E-3</v>
       </c>
     </row>
-    <row r="118" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A118" s="29" t="s">
+    <row r="119" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A119" s="29" t="s">
         <v>54</v>
       </c>
-      <c r="E118" s="4">
+      <c r="E119" s="4">
         <f t="shared" si="4"/>
         <v>5</v>
       </c>
-      <c r="F118" s="6">
+      <c r="F119" s="6">
         <v>5.0000000000000001E-3</v>
-      </c>
-    </row>
-    <row r="119" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A119" s="29" t="s">
-        <v>141</v>
-      </c>
-      <c r="E119" s="4">
-        <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
-      <c r="F119" s="6">
-        <v>1E-3</v>
       </c>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A120" s="29" t="s">
-        <v>55</v>
+        <v>141</v>
       </c>
       <c r="E120" s="4">
         <f t="shared" si="4"/>
-        <v>12.5</v>
+        <v>1</v>
       </c>
       <c r="F120" s="6">
-        <v>1.2500000000000001E-2</v>
+        <v>1E-3</v>
       </c>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A121" s="29" t="s">
-        <v>105</v>
+        <v>55</v>
       </c>
       <c r="E121" s="4">
         <f t="shared" si="4"/>
-        <v>2.4</v>
+        <v>12.5</v>
       </c>
       <c r="F121" s="6">
-        <v>2.3999999999999998E-3</v>
+        <v>1.2500000000000001E-2</v>
       </c>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A122" s="29" t="s">
-        <v>56</v>
+        <v>105</v>
       </c>
       <c r="E122" s="4">
         <f t="shared" si="4"/>
-        <v>13.5</v>
+        <v>2.4</v>
       </c>
       <c r="F122" s="6">
-        <v>1.35E-2</v>
+        <v>2.3999999999999998E-3</v>
       </c>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A123" s="29" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E123" s="4">
         <f t="shared" si="4"/>
-        <v>8.6</v>
+        <v>13.5</v>
       </c>
       <c r="F123" s="6">
-        <v>8.6E-3</v>
+        <v>1.35E-2</v>
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A124" s="29" t="s">
-        <v>164</v>
+        <v>57</v>
       </c>
       <c r="E124" s="4">
         <f t="shared" si="4"/>
-        <v>19.099999999999998</v>
+        <v>8.6</v>
       </c>
       <c r="F124" s="6">
-        <v>1.9099999999999999E-2</v>
+        <v>8.6E-3</v>
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A125" s="29" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E125" s="4">
         <f t="shared" si="4"/>
-        <v>10.97</v>
+        <v>19.099999999999998</v>
       </c>
       <c r="F125" s="6">
-        <v>1.0970000000000001E-2</v>
+        <v>1.9099999999999999E-2</v>
       </c>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A126" s="29" t="s">
-        <v>58</v>
-      </c>
-      <c r="B126" s="1"/>
-      <c r="C126" s="1"/>
-      <c r="D126" s="3"/>
+        <v>165</v>
+      </c>
       <c r="E126" s="4">
         <f t="shared" si="4"/>
-        <v>5.7050000000000001</v>
+        <v>10.97</v>
       </c>
       <c r="F126" s="6">
-        <v>5.705E-3</v>
+        <v>1.0970000000000001E-2</v>
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A127" s="29" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B127" s="1"/>
       <c r="C127" s="1"/>
       <c r="D127" s="3"/>
       <c r="E127" s="4">
         <f t="shared" si="4"/>
-        <v>13.5</v>
+        <v>5.7050000000000001</v>
       </c>
       <c r="F127" s="6">
-        <v>1.35E-2</v>
+        <v>5.705E-3</v>
       </c>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A128" s="29" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="B128" s="1"/>
       <c r="C128" s="1"/>
       <c r="D128" s="3"/>
       <c r="E128" s="4">
         <f t="shared" si="4"/>
-        <v>0.35399999999999998</v>
+        <v>13.5</v>
       </c>
       <c r="F128" s="6">
-        <v>3.5399999999999999E-4</v>
+        <v>1.35E-2</v>
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A129" s="29" t="s">
-        <v>101</v>
+        <v>63</v>
       </c>
       <c r="B129" s="1"/>
       <c r="C129" s="1"/>
       <c r="D129" s="3"/>
       <c r="E129" s="4">
         <f t="shared" si="4"/>
-        <v>2.12805</v>
+        <v>0.35399999999999998</v>
       </c>
       <c r="F129" s="6">
-        <v>2.1280499999999998E-3</v>
+        <v>3.5399999999999999E-4</v>
       </c>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A130" s="29" t="s">
-        <v>111</v>
+        <v>101</v>
       </c>
       <c r="B130" s="1"/>
       <c r="C130" s="1"/>
       <c r="D130" s="3"/>
       <c r="E130" s="4">
         <f t="shared" si="4"/>
-        <v>1.08</v>
+        <v>2.12805</v>
       </c>
       <c r="F130" s="6">
-        <v>1.08E-3</v>
+        <v>2.1280499999999998E-3</v>
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A131" s="29" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="B131" s="1"/>
       <c r="C131" s="1"/>
       <c r="D131" s="3"/>
       <c r="E131" s="4">
         <f t="shared" si="4"/>
-        <v>4.1000000000000005</v>
+        <v>1.08</v>
       </c>
       <c r="F131" s="6">
-        <v>4.1000000000000003E-3</v>
+        <v>1.08E-3</v>
       </c>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A132" s="29" t="s">
-        <v>46</v>
-      </c>
+        <v>102</v>
+      </c>
+      <c r="B132" s="1"/>
+      <c r="C132" s="1"/>
+      <c r="D132" s="3"/>
       <c r="E132" s="4">
         <f t="shared" si="4"/>
-        <v>12.5</v>
+        <v>4.1000000000000005</v>
       </c>
       <c r="F132" s="6">
-        <v>1.2500000000000001E-2</v>
+        <v>4.1000000000000003E-3</v>
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A133" s="29" t="s">
-        <v>65</v>
+        <v>46</v>
       </c>
       <c r="E133" s="4">
         <f t="shared" si="4"/>
-        <v>4.5999999999999996</v>
+        <v>12.5</v>
       </c>
       <c r="F133" s="6">
-        <v>4.5999999999999999E-3</v>
+        <v>1.2500000000000001E-2</v>
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A134" s="29" t="s">
-        <v>112</v>
+        <v>65</v>
       </c>
       <c r="E134" s="4">
         <f t="shared" si="4"/>
-        <v>1</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="F134" s="6">
-        <v>1E-3</v>
+        <v>4.5999999999999999E-3</v>
       </c>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A135" s="29" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E135" s="4">
         <f t="shared" si="4"/>
@@ -4890,49 +4908,61 @@
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A136" s="29" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="E136" s="4">
         <f t="shared" si="4"/>
-        <v>7.5</v>
+        <v>1</v>
       </c>
       <c r="F136" s="6">
-        <v>7.4999999999999997E-3</v>
+        <v>1E-3</v>
       </c>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A137" s="29" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="E137" s="4">
         <f t="shared" si="4"/>
-        <v>4.3499999999999996</v>
+        <v>7.5</v>
       </c>
       <c r="F137" s="6">
-        <v>4.3499999999999997E-3</v>
+        <v>7.4999999999999997E-3</v>
       </c>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A138" s="29" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="E138" s="4">
         <f t="shared" si="4"/>
-        <v>5</v>
+        <v>4.3499999999999996</v>
       </c>
       <c r="F138" s="6">
-        <v>5.0000000000000001E-3</v>
+        <v>4.3499999999999997E-3</v>
       </c>
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A139" s="29" t="s">
-        <v>60</v>
+        <v>115</v>
       </c>
       <c r="E139" s="4">
         <f t="shared" si="4"/>
         <v>5</v>
       </c>
       <c r="F139" s="6">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="140" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A140" s="29" t="s">
+        <v>60</v>
+      </c>
+      <c r="E140" s="4">
+        <f t="shared" si="4"/>
+        <v>5</v>
+      </c>
+      <c r="F140" s="6">
         <v>5.0000000000000001E-3</v>
       </c>
     </row>

--- a/RR_ISRU.xlsx
+++ b/RR_ISRU.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="31620" yWindow="0" windowWidth="17700" windowHeight="10485" activeTab="1"/>
+    <workbookView xWindow="31620" yWindow="0" windowWidth="17700" windowHeight="10485"/>
   </bookViews>
   <sheets>
     <sheet name="Calc (Kg)" sheetId="6" r:id="rId1"/>
@@ -1028,7 +1028,7 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1115,7 +1115,6 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="3"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="3" applyAlignment="1"/>
     <xf numFmtId="172" fontId="5" fillId="4" borderId="1" xfId="2" applyNumberFormat="1"/>
-    <xf numFmtId="11" fontId="4" fillId="3" borderId="1" xfId="1" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="1" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="4" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1454,15 +1453,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="20.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="48" t="s">
+      <c r="A1" s="47" t="s">
         <v>92</v>
       </c>
-      <c r="B1" s="48"/>
-      <c r="C1" s="48"/>
-      <c r="D1" s="48"/>
-      <c r="E1" s="48"/>
-      <c r="F1" s="48"/>
-      <c r="G1" s="48"/>
+      <c r="B1" s="47"/>
+      <c r="C1" s="47"/>
+      <c r="D1" s="47"/>
+      <c r="E1" s="47"/>
+      <c r="F1" s="47"/>
+      <c r="G1" s="47"/>
     </row>
     <row r="2" spans="1:12" ht="16.5" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A2" s="27" t="s">
@@ -1499,7 +1498,7 @@
       <c r="A6" s="25" t="s">
         <v>90</v>
       </c>
-      <c r="B6" s="47">
+      <c r="B6" s="46">
         <v>0</v>
       </c>
       <c r="C6" s="18">
@@ -1840,15 +1839,15 @@
       </c>
     </row>
     <row r="20" spans="1:12" ht="18" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="49" t="s">
+      <c r="A20" s="48" t="s">
         <v>71</v>
       </c>
-      <c r="B20" s="49"/>
-      <c r="C20" s="49"/>
-      <c r="D20" s="49"/>
-      <c r="E20" s="49"/>
-      <c r="F20" s="49"/>
-      <c r="G20" s="49"/>
+      <c r="B20" s="48"/>
+      <c r="C20" s="48"/>
+      <c r="D20" s="48"/>
+      <c r="E20" s="48"/>
+      <c r="F20" s="48"/>
+      <c r="G20" s="48"/>
     </row>
     <row r="21" spans="1:12" ht="16.5" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A21" s="7" t="s">
@@ -1871,11 +1870,6 @@
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A20:G20"/>
   </mergeCells>
-  <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B15:G15">
-      <formula1>$A$3:$A$140</formula1>
-    </dataValidation>
-  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
@@ -1884,7 +1878,7 @@
           <x14:formula1>
             <xm:f>Database!$A$3:$A$140</xm:f>
           </x14:formula1>
-          <xm:sqref>B7:G7</xm:sqref>
+          <xm:sqref>B7:G7 B15:G15</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -1901,15 +1895,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="20.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="48" t="s">
+      <c r="A1" s="47" t="s">
         <v>91</v>
       </c>
-      <c r="B1" s="48"/>
-      <c r="C1" s="48"/>
-      <c r="D1" s="48"/>
-      <c r="E1" s="48"/>
-      <c r="F1" s="48"/>
-      <c r="G1" s="48"/>
+      <c r="B1" s="47"/>
+      <c r="C1" s="47"/>
+      <c r="D1" s="47"/>
+      <c r="E1" s="47"/>
+      <c r="F1" s="47"/>
+      <c r="G1" s="47"/>
     </row>
     <row r="2" spans="1:7" ht="16.5" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A2" s="27" t="s">

--- a/RR_ISRU.xlsx
+++ b/RR_ISRU.xlsx
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="290" uniqueCount="242">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="292" uniqueCount="242">
   <si>
     <t>Resource</t>
   </si>
@@ -1499,7 +1499,7 @@
         <v>90</v>
       </c>
       <c r="B6" s="46">
-        <v>0</v>
+        <v>0.18892</v>
       </c>
       <c r="C6" s="18">
         <v>0</v>
@@ -1534,7 +1534,9 @@
       <c r="A7" s="7" t="s">
         <v>96</v>
       </c>
-      <c r="B7" s="26"/>
+      <c r="B7" s="26" t="s">
+        <v>198</v>
+      </c>
       <c r="C7" s="26"/>
       <c r="D7" s="26"/>
       <c r="E7" s="26"/>
@@ -1558,9 +1560,9 @@
       <c r="A8" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="B8" s="21" t="str">
+      <c r="B8" s="21">
         <f>IFERROR(VLOOKUP(B7,Database!$A$3:$E$140,5,FALSE),"-")</f>
-        <v>-</v>
+        <v>39</v>
       </c>
       <c r="C8" s="21" t="str">
         <f>IFERROR(VLOOKUP(C7,Database!$A$3:$E$140,5,FALSE),"-")</f>
@@ -1601,9 +1603,9 @@
       <c r="A9" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="B9" s="24" t="str">
+      <c r="B9" s="24">
         <f t="shared" ref="B9:G9" si="0">IFERROR(B6*B8,"-")</f>
-        <v>-</v>
+        <v>7.3678800000000004</v>
       </c>
       <c r="C9" s="24" t="str">
         <f t="shared" si="0"/>
@@ -1643,7 +1645,7 @@
       </c>
       <c r="B10" s="32">
         <f>SUM(B9:G9)</f>
-        <v>0</v>
+        <v>7.3678800000000004</v>
       </c>
       <c r="C10" s="28"/>
       <c r="D10" s="28"/>
@@ -1679,7 +1681,7 @@
         <v>90</v>
       </c>
       <c r="B14" s="46">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="C14" s="18">
         <v>0</v>
@@ -1714,7 +1716,9 @@
       <c r="A15" s="7" t="s">
         <v>96</v>
       </c>
-      <c r="B15" s="26"/>
+      <c r="B15" s="26" t="s">
+        <v>139</v>
+      </c>
       <c r="C15" s="26"/>
       <c r="D15" s="26"/>
       <c r="E15" s="26"/>
@@ -1738,9 +1742,9 @@
       <c r="A16" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="B16" s="21" t="str">
+      <c r="B16" s="21">
         <f>IFERROR(VLOOKUP(B15,Database!$A$3:$E$140,5,FALSE),"-")</f>
-        <v>-</v>
+        <v>2.5</v>
       </c>
       <c r="C16" s="21" t="str">
         <f>IFERROR(VLOOKUP(C15,Database!$A$3:$E$140,5,FALSE),"-")</f>
@@ -1781,9 +1785,9 @@
       <c r="A17" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="B17" s="31" t="str">
+      <c r="B17" s="31">
         <f t="shared" ref="B17:G17" si="1">IFERROR(B14*B16,"-")</f>
-        <v>-</v>
+        <v>7</v>
       </c>
       <c r="C17" s="24" t="str">
         <f t="shared" si="1"/>
@@ -1823,7 +1827,7 @@
       </c>
       <c r="B18" s="32">
         <f>SUM(B17:G17)</f>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="C18" s="28"/>
       <c r="D18" s="28"/>
@@ -1855,11 +1859,11 @@
       </c>
       <c r="B21" s="20" t="str">
         <f>IF($B$10&gt;$B$18,"Input excesive",IF($B$10&lt;$B$18,"Output excessive","Equal"))</f>
-        <v>Equal</v>
+        <v>Input excesive</v>
       </c>
       <c r="C21" s="33">
         <f>IF($B$10&gt;$B$18,B10/B18,IF($B$10&lt;$B$18,B18/B10,1))</f>
-        <v>1</v>
+        <v>1.0525542857142858</v>
       </c>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.25">

--- a/RR_ISRU.xlsx
+++ b/RR_ISRU.xlsx
@@ -15,6 +15,7 @@
     <sheet name="Calc (Kg)" sheetId="6" r:id="rId1"/>
     <sheet name="Calc (Moles)" sheetId="7" r:id="rId2"/>
     <sheet name="Database" sheetId="1" r:id="rId3"/>
+    <sheet name="Ionization energy" sheetId="8" r:id="rId4"/>
   </sheets>
   <calcPr calcId="152511"/>
   <extLst>
@@ -26,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="292" uniqueCount="242">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="531" uniqueCount="432">
   <si>
     <t>Resource</t>
   </si>
@@ -52,9 +53,6 @@
     <t>Oxidizer</t>
   </si>
   <si>
-    <t>O2</t>
-  </si>
-  <si>
     <t>MonoPropellant</t>
   </si>
   <si>
@@ -73,9 +71,6 @@
     <t>Xe</t>
   </si>
   <si>
-    <t>H2</t>
-  </si>
-  <si>
     <t>CO2</t>
   </si>
   <si>
@@ -109,9 +104,6 @@
     <t>Gypsum</t>
   </si>
   <si>
-    <t>Gypsum (CaSO4+2H2O)</t>
-  </si>
-  <si>
     <t>Hydrates</t>
   </si>
   <si>
@@ -536,9 +528,6 @@
   </si>
   <si>
     <t>Fluorine</t>
-  </si>
-  <si>
-    <t>F2</t>
   </si>
   <si>
     <t>Cl2</t>
@@ -787,12 +776,594 @@
   <si>
     <t>LqdFluorine</t>
   </si>
+  <si>
+    <t>Biotite (Fe3+AlSi3O10+F2) + Calcite (CaCO3)</t>
+  </si>
+  <si>
+    <t>Fe</t>
+  </si>
+  <si>
+    <t>Ca</t>
+  </si>
+  <si>
+    <t>O</t>
+  </si>
+  <si>
+    <t>F</t>
+  </si>
+  <si>
+    <t>Neon</t>
+  </si>
+  <si>
+    <t>Sodium</t>
+  </si>
+  <si>
+    <t>Magnesium</t>
+  </si>
+  <si>
+    <t>Sulfur</t>
+  </si>
+  <si>
+    <t>Argon</t>
+  </si>
+  <si>
+    <t>Potassium</t>
+  </si>
+  <si>
+    <t>Iron</t>
+  </si>
+  <si>
+    <t>1st</t>
+  </si>
+  <si>
+    <t>Calcium</t>
+  </si>
+  <si>
+    <t>Titanium</t>
+  </si>
+  <si>
+    <t>Scandium</t>
+  </si>
+  <si>
+    <t>Vanadium</t>
+  </si>
+  <si>
+    <t>Chromium</t>
+  </si>
+  <si>
+    <t>Manganese</t>
+  </si>
+  <si>
+    <t>Cobalt</t>
+  </si>
+  <si>
+    <t>Copper</t>
+  </si>
+  <si>
+    <t>Zinc</t>
+  </si>
+  <si>
+    <t>Gallium</t>
+  </si>
+  <si>
+    <t>Germanium</t>
+  </si>
+  <si>
+    <t>Arsenic</t>
+  </si>
+  <si>
+    <t>Selenium</t>
+  </si>
+  <si>
+    <t>Bromine</t>
+  </si>
+  <si>
+    <t>Krypton</t>
+  </si>
+  <si>
+    <t>Rubidium</t>
+  </si>
+  <si>
+    <t>Strontium</t>
+  </si>
+  <si>
+    <t>Yttrium</t>
+  </si>
+  <si>
+    <t>Zirconium</t>
+  </si>
+  <si>
+    <t>Niobium</t>
+  </si>
+  <si>
+    <t>Molybdenum</t>
+  </si>
+  <si>
+    <t>Technetium</t>
+  </si>
+  <si>
+    <t>Ruthenium</t>
+  </si>
+  <si>
+    <t>Rhodium</t>
+  </si>
+  <si>
+    <t>Palladium</t>
+  </si>
+  <si>
+    <t>Silver</t>
+  </si>
+  <si>
+    <t>Cadmium</t>
+  </si>
+  <si>
+    <t>Indium</t>
+  </si>
+  <si>
+    <t>Tin</t>
+  </si>
+  <si>
+    <t>Antimony</t>
+  </si>
+  <si>
+    <t>Tellurium</t>
+  </si>
+  <si>
+    <t>Iodine</t>
+  </si>
+  <si>
+    <t>Xenon</t>
+  </si>
+  <si>
+    <t>Cesium</t>
+  </si>
+  <si>
+    <t>Barium</t>
+  </si>
+  <si>
+    <t>Lanthanum</t>
+  </si>
+  <si>
+    <t>Cerium</t>
+  </si>
+  <si>
+    <t>Praesodymium</t>
+  </si>
+  <si>
+    <t>Neodymium</t>
+  </si>
+  <si>
+    <t>Promethium</t>
+  </si>
+  <si>
+    <t>Samarium</t>
+  </si>
+  <si>
+    <t>Europium</t>
+  </si>
+  <si>
+    <t>Gadolinium</t>
+  </si>
+  <si>
+    <t>Terbium</t>
+  </si>
+  <si>
+    <t>Dysprosium</t>
+  </si>
+  <si>
+    <t>Holmium</t>
+  </si>
+  <si>
+    <t>Erbium</t>
+  </si>
+  <si>
+    <t>Thulium</t>
+  </si>
+  <si>
+    <t>Ytterbium</t>
+  </si>
+  <si>
+    <t>Lutetium</t>
+  </si>
+  <si>
+    <t>Hafnium</t>
+  </si>
+  <si>
+    <t>Tantalum</t>
+  </si>
+  <si>
+    <t>Tungsten</t>
+  </si>
+  <si>
+    <t>Rhenium</t>
+  </si>
+  <si>
+    <t>Osmium</t>
+  </si>
+  <si>
+    <t>Iridium</t>
+  </si>
+  <si>
+    <t>Platinum</t>
+  </si>
+  <si>
+    <t>Gold</t>
+  </si>
+  <si>
+    <t>Mercury</t>
+  </si>
+  <si>
+    <t>Thallium</t>
+  </si>
+  <si>
+    <t>Lead</t>
+  </si>
+  <si>
+    <t>Bismuth</t>
+  </si>
+  <si>
+    <t>Polonium</t>
+  </si>
+  <si>
+    <t>Astatine</t>
+  </si>
+  <si>
+    <t>Radon</t>
+  </si>
+  <si>
+    <t>Ra</t>
+  </si>
+  <si>
+    <t>At</t>
+  </si>
+  <si>
+    <t>Po</t>
+  </si>
+  <si>
+    <t>Bi</t>
+  </si>
+  <si>
+    <t>Tl</t>
+  </si>
+  <si>
+    <t>Hg</t>
+  </si>
+  <si>
+    <t>Au</t>
+  </si>
+  <si>
+    <t>Pt</t>
+  </si>
+  <si>
+    <t>Ir</t>
+  </si>
+  <si>
+    <t>Os</t>
+  </si>
+  <si>
+    <t>Re</t>
+  </si>
+  <si>
+    <t>W</t>
+  </si>
+  <si>
+    <t>Ta</t>
+  </si>
+  <si>
+    <t>Hf</t>
+  </si>
+  <si>
+    <t>Lu</t>
+  </si>
+  <si>
+    <t>Yb</t>
+  </si>
+  <si>
+    <t>Tm</t>
+  </si>
+  <si>
+    <t>Er</t>
+  </si>
+  <si>
+    <t>Ho</t>
+  </si>
+  <si>
+    <t>Dy</t>
+  </si>
+  <si>
+    <t>Tb</t>
+  </si>
+  <si>
+    <t>Gd</t>
+  </si>
+  <si>
+    <t>Eu</t>
+  </si>
+  <si>
+    <t>Sm</t>
+  </si>
+  <si>
+    <t>Pm</t>
+  </si>
+  <si>
+    <t>Nd</t>
+  </si>
+  <si>
+    <t>Pr</t>
+  </si>
+  <si>
+    <t>Ce</t>
+  </si>
+  <si>
+    <t>La</t>
+  </si>
+  <si>
+    <t>Ba</t>
+  </si>
+  <si>
+    <t>Te</t>
+  </si>
+  <si>
+    <t>Sb</t>
+  </si>
+  <si>
+    <t>Sn</t>
+  </si>
+  <si>
+    <t>In</t>
+  </si>
+  <si>
+    <t>Cd</t>
+  </si>
+  <si>
+    <t>Ag</t>
+  </si>
+  <si>
+    <t>Pd</t>
+  </si>
+  <si>
+    <t>Rh</t>
+  </si>
+  <si>
+    <t>Ru</t>
+  </si>
+  <si>
+    <t>Tc</t>
+  </si>
+  <si>
+    <t>Mo</t>
+  </si>
+  <si>
+    <t>Nb</t>
+  </si>
+  <si>
+    <t>Zr</t>
+  </si>
+  <si>
+    <t>Sr</t>
+  </si>
+  <si>
+    <t>Rb</t>
+  </si>
+  <si>
+    <t>Kr</t>
+  </si>
+  <si>
+    <t>Br</t>
+  </si>
+  <si>
+    <t>Se</t>
+  </si>
+  <si>
+    <t>As</t>
+  </si>
+  <si>
+    <t>Ge</t>
+  </si>
+  <si>
+    <t>Ga</t>
+  </si>
+  <si>
+    <t>Zn</t>
+  </si>
+  <si>
+    <t>Cu</t>
+  </si>
+  <si>
+    <t>Nickel</t>
+  </si>
+  <si>
+    <t>Ni</t>
+  </si>
+  <si>
+    <t>Co</t>
+  </si>
+  <si>
+    <t>Mn</t>
+  </si>
+  <si>
+    <t>Cr</t>
+  </si>
+  <si>
+    <t>V</t>
+  </si>
+  <si>
+    <t>Ti</t>
+  </si>
+  <si>
+    <t>Sc</t>
+  </si>
+  <si>
+    <t>Cl</t>
+  </si>
+  <si>
+    <t>S</t>
+  </si>
+  <si>
+    <t>Mg</t>
+  </si>
+  <si>
+    <t>Na</t>
+  </si>
+  <si>
+    <t>Ne</t>
+  </si>
+  <si>
+    <t>N</t>
+  </si>
+  <si>
+    <t>He</t>
+  </si>
+  <si>
+    <t>H</t>
+  </si>
+  <si>
+    <t>Symbol</t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>Qty</t>
+  </si>
+  <si>
+    <t>g/mol</t>
+  </si>
+  <si>
+    <t>Energy</t>
+  </si>
+  <si>
+    <t>Weight</t>
+  </si>
+  <si>
+    <t>kW</t>
+  </si>
+  <si>
+    <t>J</t>
+  </si>
+  <si>
+    <t>Pre-mult</t>
+  </si>
+  <si>
+    <t>LqdArgon</t>
+  </si>
+  <si>
+    <t>Rn</t>
+  </si>
+  <si>
+    <t>Fr</t>
+  </si>
+  <si>
+    <t>Ac</t>
+  </si>
+  <si>
+    <t>Pa</t>
+  </si>
+  <si>
+    <t>Np</t>
+  </si>
+  <si>
+    <t>Am</t>
+  </si>
+  <si>
+    <t>Cm</t>
+  </si>
+  <si>
+    <t>Bk</t>
+  </si>
+  <si>
+    <t>Cf</t>
+  </si>
+  <si>
+    <t>Es</t>
+  </si>
+  <si>
+    <t>Fm</t>
+  </si>
+  <si>
+    <t>Francium</t>
+  </si>
+  <si>
+    <t>Radium</t>
+  </si>
+  <si>
+    <t>Actinium</t>
+  </si>
+  <si>
+    <t>Protactinium</t>
+  </si>
+  <si>
+    <t>Uranium</t>
+  </si>
+  <si>
+    <t>Neptunium</t>
+  </si>
+  <si>
+    <t>Americium</t>
+  </si>
+  <si>
+    <t>Curium</t>
+  </si>
+  <si>
+    <t>Berkelium</t>
+  </si>
+  <si>
+    <t>Californium</t>
+  </si>
+  <si>
+    <t>Einsteinium</t>
+  </si>
+  <si>
+    <t>Fermium</t>
+  </si>
+  <si>
+    <t>Diatomic</t>
+  </si>
+  <si>
+    <t>Y</t>
+  </si>
+  <si>
+    <t>I</t>
+  </si>
+  <si>
+    <t>Resource DB</t>
+  </si>
+  <si>
+    <t>Urea (CO(NH2)2) + Water ((H2O)3)</t>
+  </si>
+  <si>
+    <t>Ionization energy (J)</t>
+  </si>
+  <si>
+    <t>Ionization energy</t>
+  </si>
+  <si>
+    <t>Composition</t>
+  </si>
+  <si>
+    <t>Element</t>
+  </si>
+  <si>
+    <t>Mass</t>
+  </si>
+  <si>
+    <t>Net (kW)</t>
+  </si>
+  <si>
+    <t>Gypsum (CaSO4+2(H2O))</t>
+  </si>
+  <si>
+    <t>Mass (mol)</t>
+  </si>
+  <si>
+    <t>Gross moles</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <numFmts count="9">
+  <numFmts count="10">
     <numFmt numFmtId="164" formatCode="#,##0.00\ &quot;kg/mol&quot;"/>
     <numFmt numFmtId="165" formatCode="#,##0.000\ &quot;kg/unit&quot;"/>
     <numFmt numFmtId="166" formatCode="#,##0.00\ &quot;g/mol&quot;"/>
@@ -802,8 +1373,9 @@
     <numFmt numFmtId="170" formatCode="0.00000"/>
     <numFmt numFmtId="171" formatCode="#,##0.0000&quot;:1&quot;"/>
     <numFmt numFmtId="172" formatCode="0.000"/>
+    <numFmt numFmtId="173" formatCode="0.0"/>
   </numFmts>
-  <fonts count="16" x14ac:knownFonts="1">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -813,13 +1385,6 @@
     </font>
     <font>
       <sz val="12"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color theme="0" tint="-0.249977111117893"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -1019,14 +1584,14 @@
   </borders>
   <cellStyleXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -1062,64 +1627,56 @@
     <xf numFmtId="167" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="2"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="2" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="7"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="168" fontId="4" fillId="4" borderId="1" xfId="2" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="7" fillId="5" borderId="0" xfId="5" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="8"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="169" fontId="4" fillId="4" borderId="1" xfId="2" applyNumberFormat="1"/>
+    <xf numFmtId="171" fontId="4" fillId="4" borderId="1" xfId="2" applyNumberFormat="1" applyAlignment="1"/>
+    <xf numFmtId="170" fontId="8" fillId="4" borderId="4" xfId="6" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="1"/>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="2"/>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="2" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="7"/>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="168" fontId="5" fillId="4" borderId="1" xfId="2" applyNumberFormat="1"/>
-    <xf numFmtId="165" fontId="8" fillId="5" borderId="0" xfId="5" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="8"/>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="169" fontId="5" fillId="4" borderId="1" xfId="2" applyNumberFormat="1"/>
-    <xf numFmtId="170" fontId="5" fillId="4" borderId="1" xfId="2" applyNumberFormat="1"/>
-    <xf numFmtId="171" fontId="5" fillId="4" borderId="1" xfId="2" applyNumberFormat="1" applyAlignment="1"/>
-    <xf numFmtId="170" fontId="9" fillId="4" borderId="4" xfId="6" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="4" xfId="6"/>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="2" xfId="3" applyNumberFormat="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="3"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="3" applyAlignment="1"/>
-    <xf numFmtId="172" fontId="5" fillId="4" borderId="1" xfId="2" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="1" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="4" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="4" xfId="6"/>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="2" xfId="3" applyNumberFormat="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="3"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="3" applyAlignment="1"/>
+    <xf numFmtId="172" fontId="4" fillId="4" borderId="1" xfId="2" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="4"/>
+    <xf numFmtId="2" fontId="8" fillId="4" borderId="4" xfId="6" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="173" fontId="4" fillId="4" borderId="1" xfId="2" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="173" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="4" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="3" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="3" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1444,17 +2001,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L22"/>
+  <dimension ref="A1:L27"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="7" width="18.625" customWidth="1"/>
-    <col min="9" max="9" width="13.875" customWidth="1"/>
+    <col min="9" max="9" width="9" customWidth="1"/>
     <col min="11" max="11" width="7.875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="20.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="47" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="B1" s="47"/>
       <c r="C1" s="47"/>
@@ -1464,415 +2021,517 @@
       <c r="G1" s="47"/>
     </row>
     <row r="2" spans="1:12" ht="16.5" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="27" t="s">
-        <v>95</v>
+      <c r="A2" s="23" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A3" s="27" t="s">
-        <v>190</v>
+      <c r="A3" s="23" t="s">
+        <v>186</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A4" s="27" t="s">
-        <v>191</v>
+      <c r="A4" s="23" t="s">
+        <v>187</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="18" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="42" t="s">
-        <v>66</v>
-      </c>
-      <c r="B5" s="42"/>
-      <c r="C5" s="42"/>
-      <c r="D5" s="42"/>
-      <c r="E5" s="42"/>
-      <c r="F5" s="42"/>
-      <c r="G5" s="42"/>
-      <c r="H5" s="43"/>
-      <c r="I5" s="43"/>
-      <c r="J5" s="43"/>
-      <c r="K5" s="43"/>
-      <c r="L5" s="43"/>
+      <c r="A5" s="36" t="s">
+        <v>63</v>
+      </c>
+      <c r="B5" s="36"/>
+      <c r="C5" s="36"/>
+      <c r="D5" s="36"/>
+      <c r="E5" s="36"/>
+      <c r="F5" s="36"/>
+      <c r="G5" s="36"/>
+      <c r="H5" s="37"/>
+      <c r="I5" s="37"/>
+      <c r="J5" s="37"/>
+      <c r="K5" s="37"/>
+      <c r="L5" s="37"/>
     </row>
     <row r="6" spans="1:12" ht="16.5" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="25" t="s">
-        <v>90</v>
-      </c>
-      <c r="B6" s="46">
-        <v>0.18892</v>
-      </c>
-      <c r="C6" s="18">
-        <v>0</v>
-      </c>
-      <c r="D6" s="18">
-        <v>0</v>
-      </c>
-      <c r="E6" s="18">
-        <v>0</v>
-      </c>
-      <c r="F6" s="18">
-        <v>0</v>
-      </c>
-      <c r="G6" s="18">
+      <c r="A6" s="21" t="s">
+        <v>87</v>
+      </c>
+      <c r="B6" s="14">
+        <v>0</v>
+      </c>
+      <c r="C6" s="14">
+        <v>0</v>
+      </c>
+      <c r="D6" s="14">
+        <v>0</v>
+      </c>
+      <c r="E6" s="14">
+        <v>0</v>
+      </c>
+      <c r="F6" s="14">
+        <v>0</v>
+      </c>
+      <c r="G6" s="14">
         <v>0</v>
       </c>
       <c r="I6" t="s">
-        <v>230</v>
-      </c>
-      <c r="J6" s="18">
-        <v>1</v>
-      </c>
-      <c r="K6" s="27" t="s">
-        <v>231</v>
-      </c>
-      <c r="L6" s="19">
+        <v>226</v>
+      </c>
+      <c r="J6" s="14">
+        <v>1</v>
+      </c>
+      <c r="K6" s="23" t="s">
+        <v>227</v>
+      </c>
+      <c r="L6" s="15">
         <f>J7/J6</f>
         <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
-        <v>96</v>
-      </c>
-      <c r="B7" s="26" t="s">
-        <v>198</v>
-      </c>
-      <c r="C7" s="26"/>
-      <c r="D7" s="26"/>
-      <c r="E7" s="26"/>
-      <c r="F7" s="26"/>
-      <c r="G7" s="26"/>
+        <v>93</v>
+      </c>
+      <c r="B7" s="22"/>
+      <c r="C7" s="22"/>
+      <c r="D7" s="22"/>
+      <c r="E7" s="22"/>
+      <c r="F7" s="22"/>
+      <c r="G7" s="22"/>
       <c r="I7" t="s">
-        <v>232</v>
-      </c>
-      <c r="J7" s="18">
-        <v>1</v>
-      </c>
-      <c r="K7" s="27" t="s">
-        <v>240</v>
-      </c>
-      <c r="L7" s="19">
+        <v>228</v>
+      </c>
+      <c r="J7" s="14">
+        <v>1</v>
+      </c>
+      <c r="K7" s="23" t="s">
+        <v>236</v>
+      </c>
+      <c r="L7" s="15">
         <f>IF(J8&gt;0,L6-(J8*3600),0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:12" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="7" t="s">
-        <v>70</v>
-      </c>
-      <c r="B8" s="21">
-        <f>IFERROR(VLOOKUP(B7,Database!$A$3:$E$140,5,FALSE),"-")</f>
-        <v>39</v>
-      </c>
-      <c r="C8" s="21" t="str">
-        <f>IFERROR(VLOOKUP(C7,Database!$A$3:$E$140,5,FALSE),"-")</f>
-        <v>-</v>
-      </c>
-      <c r="D8" s="21" t="str">
-        <f>IFERROR(VLOOKUP(D7,Database!$A$3:$E$140,5,FALSE),"-")</f>
-        <v>-</v>
-      </c>
-      <c r="E8" s="21" t="str">
-        <f>IFERROR(VLOOKUP(E7,Database!$A$3:$E$140,5,FALSE),"-")</f>
-        <v>-</v>
-      </c>
-      <c r="F8" s="21" t="str">
-        <f>IFERROR(VLOOKUP(F7,Database!$A$3:$E$140,5,FALSE),"-")</f>
-        <v>-</v>
-      </c>
-      <c r="G8" s="21" t="str">
-        <f>IFERROR(VLOOKUP(G7,Database!$A$3:$E$140,5,FALSE),"-")</f>
-        <v>-</v>
-      </c>
-      <c r="I8" s="40" t="s">
-        <v>233</v>
-      </c>
-      <c r="J8" s="41">
+        <v>67</v>
+      </c>
+      <c r="B8" s="17" t="str">
+        <f>IFERROR(VLOOKUP(B7,Database!$A$3:$E$141,5,FALSE),"-")</f>
+        <v>-</v>
+      </c>
+      <c r="C8" s="17" t="str">
+        <f>IFERROR(VLOOKUP(C7,Database!$A$3:$E$141,5,FALSE),"-")</f>
+        <v>-</v>
+      </c>
+      <c r="D8" s="17" t="str">
+        <f>IFERROR(VLOOKUP(D7,Database!$A$3:$E$141,5,FALSE),"-")</f>
+        <v>-</v>
+      </c>
+      <c r="E8" s="17" t="str">
+        <f>IFERROR(VLOOKUP(E7,Database!$A$3:$E$141,5,FALSE),"-")</f>
+        <v>-</v>
+      </c>
+      <c r="F8" s="17" t="str">
+        <f>IFERROR(VLOOKUP(F7,Database!$A$3:$E$141,5,FALSE),"-")</f>
+        <v>-</v>
+      </c>
+      <c r="G8" s="17" t="str">
+        <f>IFERROR(VLOOKUP(G7,Database!$A$3:$E$141,5,FALSE),"-")</f>
+        <v>-</v>
+      </c>
+      <c r="I8" s="34" t="s">
+        <v>229</v>
+      </c>
+      <c r="J8" s="35">
         <f>ROUNDDOWN(IF(L6&gt;3600,L6/3600,0),0)</f>
         <v>0</v>
       </c>
-      <c r="K8" s="27" t="s">
+      <c r="K8" s="23" t="s">
+        <v>223</v>
+      </c>
+      <c r="L8" s="15">
+        <f>ROUNDDOWN(IF(L7&gt;0,L7/60,L6/60),0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" ht="17.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="42" t="s">
+        <v>430</v>
+      </c>
+      <c r="B9" s="17" t="str">
+        <f>IFERROR(VLOOKUP(B7,Database!$A$3:$E$141,4,FALSE),"-")</f>
+        <v>-</v>
+      </c>
+      <c r="C9" s="17" t="str">
+        <f>IFERROR(VLOOKUP(C7,Database!$A$3:$E$141,4,FALSE),"-")</f>
+        <v>-</v>
+      </c>
+      <c r="D9" s="17" t="str">
+        <f>IFERROR(VLOOKUP(D7,Database!$A$3:$E$141,4,FALSE),"-")</f>
+        <v>-</v>
+      </c>
+      <c r="E9" s="17" t="str">
+        <f>IFERROR(VLOOKUP(E7,Database!$A$3:$E$141,4,FALSE),"-")</f>
+        <v>-</v>
+      </c>
+      <c r="F9" s="17" t="str">
+        <f>IFERROR(VLOOKUP(F7,Database!$A$3:$E$141,4,FALSE),"-")</f>
+        <v>-</v>
+      </c>
+      <c r="G9" s="17" t="str">
+        <f>IFERROR(VLOOKUP(G7,Database!$A$3:$E$141,4,FALSE),"-")</f>
+        <v>-</v>
+      </c>
+      <c r="J9" s="35">
+        <f>IF(L8&lt;60,L8,0)</f>
+        <v>0</v>
+      </c>
+      <c r="K9" s="23" t="s">
+        <v>224</v>
+      </c>
+      <c r="L9" s="15">
+        <f>IF(L6&gt;0,L6-((J8*3600)+(L8*60)),0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" ht="16.5" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="B10" s="20" t="str">
+        <f t="shared" ref="B10:G10" si="0">IFERROR(B6*B8,"-")</f>
+        <v>-</v>
+      </c>
+      <c r="C10" s="20" t="str">
+        <f t="shared" si="0"/>
+        <v>-</v>
+      </c>
+      <c r="D10" s="20" t="str">
+        <f t="shared" si="0"/>
+        <v>-</v>
+      </c>
+      <c r="E10" s="20" t="str">
+        <f t="shared" si="0"/>
+        <v>-</v>
+      </c>
+      <c r="F10" s="20" t="str">
+        <f t="shared" si="0"/>
+        <v>-</v>
+      </c>
+      <c r="G10" s="20" t="str">
+        <f t="shared" si="0"/>
+        <v>-</v>
+      </c>
+      <c r="J10" s="35">
+        <f>IF(L9&gt;0,L9,0)</f>
+        <v>1</v>
+      </c>
+      <c r="K10" s="23" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A11" s="42" t="s">
+        <v>431</v>
+      </c>
+      <c r="B11" s="20" t="str">
+        <f t="shared" ref="B11:C11" si="1">IFERROR((B6*(B8*1000))/B9,"-")</f>
+        <v>-</v>
+      </c>
+      <c r="C11" s="20" t="str">
+        <f t="shared" si="1"/>
+        <v>-</v>
+      </c>
+      <c r="D11" s="20" t="str">
+        <f>IFERROR((D6*(D8*1000))/D9,"-")</f>
+        <v>-</v>
+      </c>
+      <c r="E11" s="20" t="str">
+        <f t="shared" ref="E11:G11" si="2">IFERROR((E6*(E8*1000))/E9,"-")</f>
+        <v>-</v>
+      </c>
+      <c r="F11" s="20" t="str">
+        <f t="shared" si="2"/>
+        <v>-</v>
+      </c>
+      <c r="G11" s="20" t="str">
+        <f t="shared" si="2"/>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A12" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="B12" s="28">
+        <f>SUM(B10:G10)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" ht="18" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="36" t="s">
+        <v>64</v>
+      </c>
+      <c r="B15" s="36"/>
+      <c r="C15" s="36"/>
+      <c r="D15" s="36"/>
+      <c r="E15" s="36"/>
+      <c r="F15" s="36"/>
+      <c r="G15" s="36"/>
+      <c r="H15" s="37"/>
+      <c r="I15" s="37"/>
+      <c r="J15" s="37"/>
+      <c r="K15" s="37"/>
+      <c r="L15" s="37"/>
+    </row>
+    <row r="16" spans="1:12" ht="16.5" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="21" t="s">
+        <v>87</v>
+      </c>
+      <c r="B16" s="14">
+        <v>0</v>
+      </c>
+      <c r="C16" s="14">
+        <v>0</v>
+      </c>
+      <c r="D16" s="14">
+        <v>0</v>
+      </c>
+      <c r="E16" s="14">
+        <v>0</v>
+      </c>
+      <c r="F16" s="14">
+        <v>0</v>
+      </c>
+      <c r="G16" s="14">
+        <v>0</v>
+      </c>
+      <c r="I16" t="s">
+        <v>226</v>
+      </c>
+      <c r="J16" s="14">
+        <v>1</v>
+      </c>
+      <c r="K16" s="23" t="s">
         <v>227</v>
       </c>
-      <c r="L8" s="19">
-        <f>ROUNDDOWN(IF(L7&gt;0,L7/60,L6/60),0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" ht="16.5" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="7" t="s">
+      <c r="L16" s="15">
+        <f>J17/J16</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A17" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="B17" s="22"/>
+      <c r="C17" s="22"/>
+      <c r="D17" s="22"/>
+      <c r="E17" s="22"/>
+      <c r="F17" s="22"/>
+      <c r="G17" s="22"/>
+      <c r="I17" t="s">
+        <v>228</v>
+      </c>
+      <c r="J17" s="14">
+        <v>1</v>
+      </c>
+      <c r="K17" s="23" t="s">
+        <v>236</v>
+      </c>
+      <c r="L17" s="15">
+        <f>IF(J18&gt;0,L16-(J18*3600),0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="B18" s="17" t="str">
+        <f>IFERROR(VLOOKUP(B17,Database!$A$3:$E$141,5,FALSE),"-")</f>
+        <v>-</v>
+      </c>
+      <c r="C18" s="17" t="str">
+        <f>IFERROR(VLOOKUP(C17,Database!$A$3:$E$141,5,FALSE),"-")</f>
+        <v>-</v>
+      </c>
+      <c r="D18" s="17" t="str">
+        <f>IFERROR(VLOOKUP(D17,Database!$A$3:$E$141,5,FALSE),"-")</f>
+        <v>-</v>
+      </c>
+      <c r="E18" s="17" t="str">
+        <f>IFERROR(VLOOKUP(E17,Database!$A$3:$E$141,5,FALSE),"-")</f>
+        <v>-</v>
+      </c>
+      <c r="F18" s="17" t="str">
+        <f>IFERROR(VLOOKUP(F17,Database!$A$3:$E$141,5,FALSE),"-")</f>
+        <v>-</v>
+      </c>
+      <c r="G18" s="17" t="str">
+        <f>IFERROR(VLOOKUP(G17,Database!$A$3:$E$141,5,FALSE),"-")</f>
+        <v>-</v>
+      </c>
+      <c r="I18" s="34" t="s">
+        <v>229</v>
+      </c>
+      <c r="J18" s="35">
+        <f>ROUNDDOWN(IF(L16&gt;3600,L16/3600,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="K18" s="23" t="s">
+        <v>223</v>
+      </c>
+      <c r="L18" s="15">
+        <f>ROUNDDOWN(IF(L17&gt;0,L17/60,L16/60),0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" ht="17.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="42" t="s">
+        <v>430</v>
+      </c>
+      <c r="B19" s="17" t="str">
+        <f>IFERROR(VLOOKUP(B17,Database!$A$3:$E$141,4,FALSE),"-")</f>
+        <v>-</v>
+      </c>
+      <c r="C19" s="17" t="str">
+        <f>IFERROR(VLOOKUP(C17,Database!$A$3:$E$141,4,FALSE),"-")</f>
+        <v>-</v>
+      </c>
+      <c r="D19" s="17" t="str">
+        <f>IFERROR(VLOOKUP(D17,Database!$A$3:$E$141,4,FALSE),"-")</f>
+        <v>-</v>
+      </c>
+      <c r="E19" s="17" t="str">
+        <f>IFERROR(VLOOKUP(E17,Database!$A$3:$E$141,4,FALSE),"-")</f>
+        <v>-</v>
+      </c>
+      <c r="F19" s="17" t="str">
+        <f>IFERROR(VLOOKUP(F17,Database!$A$3:$E$141,4,FALSE),"-")</f>
+        <v>-</v>
+      </c>
+      <c r="G19" s="17" t="str">
+        <f>IFERROR(VLOOKUP(G17,Database!$A$3:$E$141,4,FALSE),"-")</f>
+        <v>-</v>
+      </c>
+      <c r="J19" s="35">
+        <f>IF(L18&lt;60,L18,0)</f>
+        <v>0</v>
+      </c>
+      <c r="K19" s="23" t="s">
+        <v>224</v>
+      </c>
+      <c r="L19" s="15">
+        <f>IF(L16&gt;0,L16-((J18*3600)+(L18*60)),0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" ht="16.5" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="B20" s="26" t="str">
+        <f t="shared" ref="B20:G20" si="3">IFERROR(B16*B18,"-")</f>
+        <v>-</v>
+      </c>
+      <c r="C20" s="20" t="str">
+        <f t="shared" si="3"/>
+        <v>-</v>
+      </c>
+      <c r="D20" s="26" t="str">
+        <f t="shared" si="3"/>
+        <v>-</v>
+      </c>
+      <c r="E20" s="20" t="str">
+        <f t="shared" si="3"/>
+        <v>-</v>
+      </c>
+      <c r="F20" s="20" t="str">
+        <f t="shared" si="3"/>
+        <v>-</v>
+      </c>
+      <c r="G20" s="20" t="str">
+        <f t="shared" si="3"/>
+        <v>-</v>
+      </c>
+      <c r="J20" s="35">
+        <f>IF(L19&gt;0,L19,0)</f>
+        <v>1</v>
+      </c>
+      <c r="K20" s="23" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A21" s="42" t="s">
+        <v>431</v>
+      </c>
+      <c r="B21" s="20" t="str">
+        <f t="shared" ref="B21:G21" si="4">IFERROR((B16*(B18*1000))/B19,"-")</f>
+        <v>-</v>
+      </c>
+      <c r="C21" s="20" t="str">
+        <f t="shared" si="4"/>
+        <v>-</v>
+      </c>
+      <c r="D21" s="20" t="str">
+        <f t="shared" si="4"/>
+        <v>-</v>
+      </c>
+      <c r="E21" s="20" t="str">
+        <f t="shared" si="4"/>
+        <v>-</v>
+      </c>
+      <c r="F21" s="20" t="str">
+        <f t="shared" si="4"/>
+        <v>-</v>
+      </c>
+      <c r="G21" s="20" t="str">
+        <f t="shared" si="4"/>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A22" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="B22" s="28">
+        <f>SUM(B20:G20)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" ht="18" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="48" t="s">
+        <v>68</v>
+      </c>
+      <c r="B25" s="48"/>
+      <c r="C25" s="48"/>
+      <c r="D25" s="48"/>
+      <c r="E25" s="48"/>
+      <c r="F25" s="48"/>
+      <c r="G25" s="48"/>
+    </row>
+    <row r="26" spans="1:12" ht="16.5" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="B9" s="24">
-        <f t="shared" ref="B9:G9" si="0">IFERROR(B6*B8,"-")</f>
-        <v>7.3678800000000004</v>
-      </c>
-      <c r="C9" s="24" t="str">
-        <f t="shared" si="0"/>
-        <v>-</v>
-      </c>
-      <c r="D9" s="24" t="str">
-        <f t="shared" si="0"/>
-        <v>-</v>
-      </c>
-      <c r="E9" s="24" t="str">
-        <f t="shared" si="0"/>
-        <v>-</v>
-      </c>
-      <c r="F9" s="24" t="str">
-        <f t="shared" si="0"/>
-        <v>-</v>
-      </c>
-      <c r="G9" s="24" t="str">
-        <f t="shared" si="0"/>
-        <v>-</v>
-      </c>
-      <c r="J9" s="41">
-        <f>IF(L8&lt;60,L8,0)</f>
-        <v>0</v>
-      </c>
-      <c r="K9" s="27" t="s">
-        <v>228</v>
-      </c>
-      <c r="L9" s="19">
-        <f>IF(L6&gt;0,L6-((J8*3600)+(L8*60)),0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A10" s="7" t="s">
-        <v>68</v>
-      </c>
-      <c r="B10" s="32">
-        <f>SUM(B9:G9)</f>
-        <v>7.3678800000000004</v>
-      </c>
-      <c r="C10" s="28"/>
-      <c r="D10" s="28"/>
-      <c r="E10" s="28"/>
-      <c r="F10" s="28"/>
-      <c r="G10" s="28"/>
-      <c r="J10" s="41">
-        <f>IF(L9&gt;0,L9,0)</f>
-        <v>1</v>
-      </c>
-      <c r="K10" s="27" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12" ht="18" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="42" t="s">
-        <v>67</v>
-      </c>
-      <c r="B13" s="42"/>
-      <c r="C13" s="42"/>
-      <c r="D13" s="42"/>
-      <c r="E13" s="42"/>
-      <c r="F13" s="42"/>
-      <c r="G13" s="42"/>
-      <c r="H13" s="43"/>
-      <c r="I13" s="43"/>
-      <c r="J13" s="43"/>
-      <c r="K13" s="43"/>
-      <c r="L13" s="43"/>
-    </row>
-    <row r="14" spans="1:12" ht="16.5" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="25" t="s">
-        <v>90</v>
-      </c>
-      <c r="B14" s="46">
-        <v>2.8</v>
-      </c>
-      <c r="C14" s="18">
-        <v>0</v>
-      </c>
-      <c r="D14" s="18">
-        <v>0</v>
-      </c>
-      <c r="E14" s="18">
-        <v>0</v>
-      </c>
-      <c r="F14" s="18">
-        <v>0</v>
-      </c>
-      <c r="G14" s="18">
-        <v>0</v>
-      </c>
-      <c r="I14" t="s">
-        <v>230</v>
-      </c>
-      <c r="J14" s="18">
-        <v>1</v>
-      </c>
-      <c r="K14" s="27" t="s">
-        <v>231</v>
-      </c>
-      <c r="L14" s="19">
-        <f>J15/J14</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A15" s="7" t="s">
-        <v>96</v>
-      </c>
-      <c r="B15" s="26" t="s">
-        <v>139</v>
-      </c>
-      <c r="C15" s="26"/>
-      <c r="D15" s="26"/>
-      <c r="E15" s="26"/>
-      <c r="F15" s="26"/>
-      <c r="G15" s="26"/>
-      <c r="I15" t="s">
-        <v>232</v>
-      </c>
-      <c r="J15" s="18">
-        <v>1</v>
-      </c>
-      <c r="K15" s="27" t="s">
-        <v>240</v>
-      </c>
-      <c r="L15" s="19">
-        <f>IF(J16&gt;0,L14-(J16*3600),0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="7" t="s">
-        <v>70</v>
-      </c>
-      <c r="B16" s="21">
-        <f>IFERROR(VLOOKUP(B15,Database!$A$3:$E$140,5,FALSE),"-")</f>
-        <v>2.5</v>
-      </c>
-      <c r="C16" s="21" t="str">
-        <f>IFERROR(VLOOKUP(C15,Database!$A$3:$E$140,5,FALSE),"-")</f>
-        <v>-</v>
-      </c>
-      <c r="D16" s="21" t="str">
-        <f>IFERROR(VLOOKUP(D15,Database!$A$3:$E$140,5,FALSE),"-")</f>
-        <v>-</v>
-      </c>
-      <c r="E16" s="21" t="str">
-        <f>IFERROR(VLOOKUP(E15,Database!$A$3:$E$140,5,FALSE),"-")</f>
-        <v>-</v>
-      </c>
-      <c r="F16" s="21" t="str">
-        <f>IFERROR(VLOOKUP(F15,Database!$A$3:$E$140,5,FALSE),"-")</f>
-        <v>-</v>
-      </c>
-      <c r="G16" s="21" t="str">
-        <f>IFERROR(VLOOKUP(G15,Database!$A$3:$E$140,5,FALSE),"-")</f>
-        <v>-</v>
-      </c>
-      <c r="I16" s="40" t="s">
-        <v>233</v>
-      </c>
-      <c r="J16" s="41">
-        <f>ROUNDDOWN(IF(L14&gt;3600,L14/3600,0),0)</f>
-        <v>0</v>
-      </c>
-      <c r="K16" s="27" t="s">
-        <v>227</v>
-      </c>
-      <c r="L16" s="19">
-        <f>ROUNDDOWN(IF(L15&gt;0,L15/60,L14/60),0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:12" ht="16.5" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="B17" s="31">
-        <f t="shared" ref="B17:G17" si="1">IFERROR(B14*B16,"-")</f>
-        <v>7</v>
-      </c>
-      <c r="C17" s="24" t="str">
-        <f t="shared" si="1"/>
-        <v>-</v>
-      </c>
-      <c r="D17" s="31" t="str">
-        <f t="shared" si="1"/>
-        <v>-</v>
-      </c>
-      <c r="E17" s="24" t="str">
-        <f t="shared" si="1"/>
-        <v>-</v>
-      </c>
-      <c r="F17" s="24" t="str">
-        <f t="shared" si="1"/>
-        <v>-</v>
-      </c>
-      <c r="G17" s="24" t="str">
-        <f t="shared" si="1"/>
-        <v>-</v>
-      </c>
-      <c r="J17" s="41">
-        <f>IF(L16&lt;60,L16,0)</f>
-        <v>0</v>
-      </c>
-      <c r="K17" s="27" t="s">
-        <v>228</v>
-      </c>
-      <c r="L17" s="19">
-        <f>IF(L14&gt;0,L14-((J16*3600)+(L16*60)),0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A18" s="7" t="s">
-        <v>68</v>
-      </c>
-      <c r="B18" s="32">
-        <f>SUM(B17:G17)</f>
-        <v>7</v>
-      </c>
-      <c r="C18" s="28"/>
-      <c r="D18" s="28"/>
-      <c r="E18" s="28"/>
-      <c r="F18" s="28"/>
-      <c r="G18" s="28"/>
-      <c r="J18" s="41">
-        <f>IF(L17&gt;0,L17,0)</f>
-        <v>1</v>
-      </c>
-      <c r="K18" s="27" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="20" spans="1:12" ht="18" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="48" t="s">
-        <v>71</v>
-      </c>
-      <c r="B20" s="48"/>
-      <c r="C20" s="48"/>
-      <c r="D20" s="48"/>
-      <c r="E20" s="48"/>
-      <c r="F20" s="48"/>
-      <c r="G20" s="48"/>
-    </row>
-    <row r="21" spans="1:12" ht="16.5" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="B21" s="20" t="str">
-        <f>IF($B$10&gt;$B$18,"Input excesive",IF($B$10&lt;$B$18,"Output excessive","Equal"))</f>
-        <v>Input excesive</v>
-      </c>
-      <c r="C21" s="33">
-        <f>IF($B$10&gt;$B$18,B10/B18,IF($B$10&lt;$B$18,B18/B10,1))</f>
-        <v>1.0525542857142858</v>
-      </c>
-    </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A22" s="7"/>
+      <c r="B26" s="16" t="str">
+        <f>IF($B$12&gt;$B$22,"Input excesive",IF($B$12&lt;$B$22,"Output excessive","Equal"))</f>
+        <v>Equal</v>
+      </c>
+      <c r="C26" s="27">
+        <f>IF($B$12&gt;$B$22,B12/B22,IF($B$12&lt;$B$22,B22/B12,1))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A27" s="7"/>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A20:G20"/>
+    <mergeCell ref="A25:G25"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <extLst>
@@ -1880,9 +2539,9 @@
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
-            <xm:f>Database!$A$3:$A$140</xm:f>
+            <xm:f>Database!$A$3:$A$141</xm:f>
           </x14:formula1>
-          <xm:sqref>B7:G7 B15:G15</xm:sqref>
+          <xm:sqref>B7:G7 B17:G17</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -1892,15 +2551,15 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G25"/>
+  <dimension ref="A1:J39"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="7" width="18.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="20.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:10" ht="20.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="47" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="B1" s="47"/>
       <c r="C1" s="47"/>
@@ -1909,410 +2568,541 @@
       <c r="F1" s="47"/>
       <c r="G1" s="47"/>
     </row>
-    <row r="2" spans="1:7" ht="16.5" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="27" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="27" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="27" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="18" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="42" t="s">
-        <v>66</v>
-      </c>
-      <c r="B5" s="42"/>
-      <c r="C5" s="42"/>
-      <c r="D5" s="42"/>
-      <c r="E5" s="42"/>
-      <c r="F5" s="42"/>
-      <c r="G5" s="42"/>
-    </row>
-    <row r="6" spans="1:7" ht="16.5" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" ht="16.5" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="23" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A3" s="23" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A4" s="23" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="18" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="36" t="s">
+        <v>63</v>
+      </c>
+      <c r="B5" s="36"/>
+      <c r="C5" s="36"/>
+      <c r="D5" s="36"/>
+      <c r="E5" s="36"/>
+      <c r="F5" s="36"/>
+      <c r="G5" s="36"/>
+      <c r="J5" s="1"/>
+    </row>
+    <row r="6" spans="1:10" ht="16.5" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="B6" s="14">
+        <v>0</v>
+      </c>
+      <c r="C6" s="14">
+        <v>0</v>
+      </c>
+      <c r="D6" s="14">
+        <v>0</v>
+      </c>
+      <c r="E6" s="14">
+        <v>0</v>
+      </c>
+      <c r="F6" s="14">
+        <v>0</v>
+      </c>
+      <c r="G6" s="14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A7" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="B7" s="22"/>
+      <c r="C7" s="22"/>
+      <c r="D7" s="22"/>
+      <c r="E7" s="22"/>
+      <c r="F7" s="22"/>
+      <c r="G7" s="22"/>
+    </row>
+    <row r="8" spans="1:10" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="B8" s="17" t="str">
+        <f>IFERROR(VLOOKUP(B7,Database!$A$3:$E$103,4,FALSE),"-")</f>
+        <v>-</v>
+      </c>
+      <c r="C8" s="17" t="str">
+        <f>IFERROR(VLOOKUP(C7,Database!$A$3:$E$103,4,FALSE),"-")</f>
+        <v>-</v>
+      </c>
+      <c r="D8" s="17" t="str">
+        <f>IFERROR(VLOOKUP(D7,Database!$A$3:$E$103,4,FALSE),"-")</f>
+        <v>-</v>
+      </c>
+      <c r="E8" s="17" t="str">
+        <f>IFERROR(VLOOKUP(E7,Database!$A$3:$E$103,4,FALSE),"-")</f>
+        <v>-</v>
+      </c>
+      <c r="F8" s="17" t="str">
+        <f>IFERROR(VLOOKUP(F7,Database!$A$3:$E$103,4,FALSE),"-")</f>
+        <v>-</v>
+      </c>
+      <c r="G8" s="17" t="str">
+        <f>IFERROR(VLOOKUP(G7,Database!$A$3:$E$103,4,FALSE),"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" ht="17.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="B9" s="17" t="str">
+        <f>IFERROR(VLOOKUP(B7,Database!$A$3:$E$103,5,FALSE),"-")</f>
+        <v>-</v>
+      </c>
+      <c r="C9" s="17" t="str">
+        <f>IFERROR(VLOOKUP(C7,Database!$A$3:$E$103,5,FALSE),"-")</f>
+        <v>-</v>
+      </c>
+      <c r="D9" s="17" t="str">
+        <f>IFERROR(VLOOKUP(D7,Database!$A$3:$E$103,5,FALSE),"-")</f>
+        <v>-</v>
+      </c>
+      <c r="E9" s="17" t="str">
+        <f>IFERROR(VLOOKUP(E7,Database!$A$3:$E$103,5,FALSE),"-")</f>
+        <v>-</v>
+      </c>
+      <c r="F9" s="17" t="str">
+        <f>IFERROR(VLOOKUP(F7,Database!$A$3:$E$103,5,FALSE),"-")</f>
+        <v>-</v>
+      </c>
+      <c r="G9" s="17" t="str">
+        <f>IFERROR(VLOOKUP(G7,Database!$A$3:$E$103,5,FALSE),"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" ht="16.5" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="B10" s="39">
+        <f>IFERROR(B6*B8,0)</f>
+        <v>0</v>
+      </c>
+      <c r="C10" s="39" t="str">
+        <f>IFERROR(C6*C8,"-")</f>
+        <v>-</v>
+      </c>
+      <c r="D10" s="15" t="str">
+        <f>IFERROR(D6*D8,"-")</f>
+        <v>-</v>
+      </c>
+      <c r="E10" s="15" t="str">
+        <f>IFERROR(E6*E8,"-")</f>
+        <v>-</v>
+      </c>
+      <c r="F10" s="15" t="str">
+        <f>IFERROR(F6*F8,"-")</f>
+        <v>-</v>
+      </c>
+      <c r="G10" s="15" t="str">
+        <f>IFERROR(G6*G8,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A11" s="21" t="s">
         <v>87</v>
       </c>
-      <c r="B6" s="18">
-        <v>0</v>
-      </c>
-      <c r="C6" s="18">
-        <v>0</v>
-      </c>
-      <c r="D6" s="18">
-        <v>0</v>
-      </c>
-      <c r="E6" s="18">
-        <v>0</v>
-      </c>
-      <c r="F6" s="18">
-        <v>0</v>
-      </c>
-      <c r="G6" s="18">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="7" t="s">
-        <v>96</v>
-      </c>
-      <c r="B7" s="26"/>
-      <c r="C7" s="26"/>
-      <c r="D7" s="26"/>
-      <c r="E7" s="26"/>
-      <c r="F7" s="26"/>
-      <c r="G7" s="26"/>
-    </row>
-    <row r="8" spans="1:7" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="B8" s="21" t="str">
-        <f>IFERROR(VLOOKUP(B7,Database!$A$3:$E$102,4,FALSE),"-")</f>
-        <v>-</v>
-      </c>
-      <c r="C8" s="21" t="str">
-        <f>IFERROR(VLOOKUP(C7,Database!$A$3:$E$102,4,FALSE),"-")</f>
-        <v>-</v>
-      </c>
-      <c r="D8" s="21" t="str">
-        <f>IFERROR(VLOOKUP(D7,Database!$A$3:$E$102,4,FALSE),"-")</f>
-        <v>-</v>
-      </c>
-      <c r="E8" s="21" t="str">
-        <f>IFERROR(VLOOKUP(E7,Database!$A$3:$E$102,4,FALSE),"-")</f>
-        <v>-</v>
-      </c>
-      <c r="F8" s="21" t="str">
-        <f>IFERROR(VLOOKUP(F7,Database!$A$3:$E$102,4,FALSE),"-")</f>
-        <v>-</v>
-      </c>
-      <c r="G8" s="21" t="str">
-        <f>IFERROR(VLOOKUP(G7,Database!$A$3:$E$102,4,FALSE),"-")</f>
-        <v>-</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" ht="17.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="7" t="s">
-        <v>93</v>
-      </c>
-      <c r="B9" s="21" t="str">
-        <f>IFERROR(VLOOKUP(B7,Database!$A$3:$E$102,5,FALSE),"-")</f>
-        <v>-</v>
-      </c>
-      <c r="C9" s="21" t="str">
-        <f>IFERROR(VLOOKUP(C7,Database!$A$3:$E$102,5,FALSE),"-")</f>
-        <v>-</v>
-      </c>
-      <c r="D9" s="21" t="str">
-        <f>IFERROR(VLOOKUP(D7,Database!$A$3:$E$102,5,FALSE),"-")</f>
-        <v>-</v>
-      </c>
-      <c r="E9" s="21" t="str">
-        <f>IFERROR(VLOOKUP(E7,Database!$A$3:$E$102,5,FALSE),"-")</f>
-        <v>-</v>
-      </c>
-      <c r="F9" s="21" t="str">
-        <f>IFERROR(VLOOKUP(F7,Database!$A$3:$E$102,5,FALSE),"-")</f>
-        <v>-</v>
-      </c>
-      <c r="G9" s="21" t="str">
-        <f>IFERROR(VLOOKUP(G7,Database!$A$3:$E$102,5,FALSE),"-")</f>
-        <v>-</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" ht="16.5" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="B10" s="45">
-        <f>IFERROR(B6*B8,0)</f>
-        <v>0</v>
-      </c>
-      <c r="C10" s="45" t="str">
-        <f>IFERROR(C6*C8,"-")</f>
-        <v>-</v>
-      </c>
-      <c r="D10" s="19" t="str">
-        <f>IFERROR(D6*D8,"-")</f>
-        <v>-</v>
-      </c>
-      <c r="E10" s="19" t="str">
-        <f>IFERROR(E6*E8,"-")</f>
-        <v>-</v>
-      </c>
-      <c r="F10" s="19" t="str">
-        <f>IFERROR(F6*F8,"-")</f>
-        <v>-</v>
-      </c>
-      <c r="G10" s="19" t="str">
-        <f>IFERROR(G6*G8,"-")</f>
-        <v>-</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="25" t="s">
-        <v>90</v>
-      </c>
-      <c r="B11" s="34" t="str">
+      <c r="B11" s="28" t="str">
         <f t="shared" ref="B11:G11" si="0">IFERROR(B10/(B9*1000),"-")</f>
         <v>-</v>
       </c>
-      <c r="C11" s="34" t="str">
+      <c r="C11" s="28" t="str">
         <f t="shared" si="0"/>
         <v>-</v>
       </c>
-      <c r="D11" s="34" t="str">
+      <c r="D11" s="28" t="str">
         <f t="shared" si="0"/>
         <v>-</v>
       </c>
-      <c r="E11" s="34" t="str">
+      <c r="E11" s="28" t="str">
         <f t="shared" si="0"/>
         <v>-</v>
       </c>
-      <c r="F11" s="34" t="str">
+      <c r="F11" s="28" t="str">
         <f t="shared" si="0"/>
         <v>-</v>
       </c>
-      <c r="G11" s="34" t="str">
+      <c r="G11" s="28" t="str">
         <f t="shared" si="0"/>
         <v>-</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="B12" s="24">
+        <v>91</v>
+      </c>
+      <c r="B12" s="20">
         <f>SUM(B10:G10)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="18" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:10" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="42" t="s">
-        <v>67</v>
-      </c>
-      <c r="B14" s="42"/>
-      <c r="C14" s="42"/>
-      <c r="D14" s="42"/>
-      <c r="E14" s="42"/>
-      <c r="F14" s="42"/>
-      <c r="G14" s="42"/>
-    </row>
-    <row r="15" spans="1:7" ht="16.5" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="7" t="s">
-        <v>87</v>
-      </c>
-      <c r="B15" s="18">
-        <v>0</v>
-      </c>
-      <c r="C15" s="18">
-        <v>0</v>
-      </c>
-      <c r="D15" s="18">
-        <v>0</v>
-      </c>
-      <c r="E15" s="18">
-        <v>0</v>
-      </c>
-      <c r="F15" s="18">
-        <v>0</v>
-      </c>
-      <c r="G15" s="18">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+        <v>424</v>
+      </c>
+      <c r="B14" s="17" t="str">
+        <f>IFERROR(VLOOKUP(B7,Database!$A$3:$G$103,7,FALSE),"-")</f>
+        <v>-</v>
+      </c>
+      <c r="C14" s="17" t="str">
+        <f>IFERROR(VLOOKUP(C7,Database!$A$3:$G$103,7,FALSE),"-")</f>
+        <v>-</v>
+      </c>
+      <c r="D14" s="17" t="str">
+        <f>IFERROR(VLOOKUP(D7,Database!$A$3:$G$103,7,FALSE),"-")</f>
+        <v>-</v>
+      </c>
+      <c r="E14" s="17" t="str">
+        <f>IFERROR(VLOOKUP(E7,Database!$A$3:$G$103,7,FALSE),"-")</f>
+        <v>-</v>
+      </c>
+      <c r="F14" s="17" t="str">
+        <f>IFERROR(VLOOKUP(F7,Database!$A$3:$G$103,7,FALSE),"-")</f>
+        <v>-</v>
+      </c>
+      <c r="G14" s="17" t="str">
+        <f>IFERROR(VLOOKUP(G7,Database!$A$3:$G$103,7,FALSE),"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" ht="16.5" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="B15" s="15">
+        <f>IFERROR(B6*B14,0)</f>
+        <v>0</v>
+      </c>
+      <c r="C15" s="15">
+        <f t="shared" ref="C15:G15" si="1">IFERROR(C6*C14,0)</f>
+        <v>0</v>
+      </c>
+      <c r="D15" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="E15" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F15" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="G15" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" s="7" t="s">
-        <v>96</v>
-      </c>
-      <c r="B16" s="26"/>
-      <c r="C16" s="26"/>
-      <c r="D16" s="26"/>
-      <c r="E16" s="26"/>
-      <c r="F16" s="26"/>
-      <c r="G16" s="26"/>
-    </row>
-    <row r="17" spans="1:7" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="B17" s="21" t="str">
-        <f>IFERROR(VLOOKUP(B16,Database!$A$3:$E$102,4,FALSE),"-")</f>
-        <v>-</v>
-      </c>
-      <c r="C17" s="21" t="str">
-        <f>IFERROR(VLOOKUP(C16,Database!$A$3:$E$102,4,FALSE),"-")</f>
-        <v>-</v>
-      </c>
-      <c r="D17" s="21" t="str">
-        <f>IFERROR(VLOOKUP(D16,Database!$A$3:$E$102,4,FALSE),"-")</f>
-        <v>-</v>
-      </c>
-      <c r="E17" s="21" t="str">
-        <f>IFERROR(VLOOKUP(E16,Database!$A$3:$E$102,4,FALSE),"-")</f>
-        <v>-</v>
-      </c>
-      <c r="F17" s="21" t="str">
-        <f>IFERROR(VLOOKUP(F16,Database!$A$3:$E$102,4,FALSE),"-")</f>
-        <v>-</v>
-      </c>
-      <c r="G17" s="21" t="str">
-        <f>IFERROR(VLOOKUP(G16,Database!$A$3:$E$102,4,FALSE),"-")</f>
-        <v>-</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" ht="17.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="7" t="s">
-        <v>93</v>
-      </c>
-      <c r="B18" s="21" t="str">
-        <f>IFERROR(VLOOKUP(B16,Database!$A$3:$E$102,5,FALSE),"-")</f>
-        <v>-</v>
-      </c>
-      <c r="C18" s="21" t="str">
-        <f>IFERROR(VLOOKUP(C16,Database!$A$3:$E$102,5,FALSE),"-")</f>
-        <v>-</v>
-      </c>
-      <c r="D18" s="21" t="str">
-        <f>IFERROR(VLOOKUP(D16,Database!$A$3:$E$102,5,FALSE),"-")</f>
-        <v>-</v>
-      </c>
-      <c r="E18" s="21" t="str">
-        <f>IFERROR(VLOOKUP(E16,Database!$A$3:$E$102,5,FALSE),"-")</f>
-        <v>-</v>
-      </c>
-      <c r="F18" s="21" t="str">
-        <f>IFERROR(VLOOKUP(F16,Database!$A$3:$E$102,5,FALSE),"-")</f>
-        <v>-</v>
-      </c>
-      <c r="G18" s="21" t="str">
-        <f>IFERROR(VLOOKUP(G16,Database!$A$3:$E$102,5,FALSE),"-")</f>
-        <v>-</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" ht="16.5" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="B19" s="19">
-        <f>IFERROR(B15*B17,0)</f>
-        <v>0</v>
-      </c>
-      <c r="C19" s="19" t="str">
-        <f>IFERROR(C15*C17,"-")</f>
-        <v>-</v>
-      </c>
-      <c r="D19" s="19" t="str">
-        <f>IFERROR(D15*D17,"-")</f>
-        <v>-</v>
-      </c>
-      <c r="E19" s="19" t="str">
-        <f>IFERROR(E15*E17,"-")</f>
-        <v>-</v>
-      </c>
-      <c r="F19" s="19" t="str">
-        <f>IFERROR(F15*F17,"-")</f>
-        <v>-</v>
-      </c>
-      <c r="G19" s="19" t="str">
-        <f>IFERROR(G15*G17,"-")</f>
-        <v>-</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20" s="25" t="s">
-        <v>90</v>
-      </c>
-      <c r="B20" s="34" t="str">
-        <f t="shared" ref="B20:G20" si="1">IFERROR(B19/(B18*1000),"-")</f>
-        <v>-</v>
-      </c>
-      <c r="C20" s="34" t="str">
-        <f t="shared" si="1"/>
-        <v>-</v>
-      </c>
-      <c r="D20" s="34" t="str">
-        <f t="shared" si="1"/>
-        <v>-</v>
-      </c>
-      <c r="E20" s="34" t="str">
-        <f t="shared" si="1"/>
-        <v>-</v>
-      </c>
-      <c r="F20" s="34" t="str">
-        <f t="shared" si="1"/>
-        <v>-</v>
-      </c>
-      <c r="G20" s="34" t="str">
-        <f t="shared" si="1"/>
-        <v>-</v>
+        <v>428</v>
+      </c>
+      <c r="B16" s="41">
+        <f>SUM(B15:G15)/20</f>
+        <v>0</v>
+      </c>
+      <c r="I16" s="1"/>
+    </row>
+    <row r="19" spans="1:7" ht="18" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="36" t="s">
+        <v>64</v>
+      </c>
+      <c r="B19" s="36"/>
+      <c r="C19" s="36"/>
+      <c r="D19" s="36"/>
+      <c r="E19" s="36"/>
+      <c r="F19" s="36"/>
+      <c r="G19" s="36"/>
+    </row>
+    <row r="20" spans="1:7" ht="16.5" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="B20" s="14">
+        <v>0</v>
+      </c>
+      <c r="C20" s="14">
+        <v>0</v>
+      </c>
+      <c r="D20" s="14">
+        <v>0</v>
+      </c>
+      <c r="E20" s="14">
+        <v>0</v>
+      </c>
+      <c r="F20" s="14">
+        <v>0</v>
+      </c>
+      <c r="G20" s="14">
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="B21" s="24">
-        <f>SUM(B19:G19)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A22" s="7"/>
-    </row>
-    <row r="23" spans="1:7" ht="18" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="44" t="s">
-        <v>71</v>
-      </c>
-      <c r="B23" s="44"/>
-      <c r="C23" s="44"/>
-      <c r="D23" s="44"/>
-      <c r="E23" s="44"/>
-      <c r="F23" s="44"/>
-      <c r="G23" s="44"/>
+        <v>93</v>
+      </c>
+      <c r="B21" s="22"/>
+      <c r="C21" s="22"/>
+      <c r="D21" s="22"/>
+      <c r="E21" s="22"/>
+      <c r="F21" s="22"/>
+      <c r="G21" s="22"/>
+    </row>
+    <row r="22" spans="1:7" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="B22" s="17" t="str">
+        <f>IFERROR(VLOOKUP(B21,Database!$A$3:$G$103,4,FALSE),"-")</f>
+        <v>-</v>
+      </c>
+      <c r="C22" s="17" t="str">
+        <f>IFERROR(VLOOKUP(C21,Database!$A$3:$G$103,4,FALSE),"-")</f>
+        <v>-</v>
+      </c>
+      <c r="D22" s="17" t="str">
+        <f>IFERROR(VLOOKUP(D21,Database!$A$3:$G$103,4,FALSE),"-")</f>
+        <v>-</v>
+      </c>
+      <c r="E22" s="17" t="str">
+        <f>IFERROR(VLOOKUP(E21,Database!$A$3:$G$103,4,FALSE),"-")</f>
+        <v>-</v>
+      </c>
+      <c r="F22" s="17" t="str">
+        <f>IFERROR(VLOOKUP(F21,Database!$A$3:$G$103,4,FALSE),"-")</f>
+        <v>-</v>
+      </c>
+      <c r="G22" s="17" t="str">
+        <f>IFERROR(VLOOKUP(G21,Database!$A$3:$G$103,4,FALSE),"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="17.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="B23" s="17" t="str">
+        <f>IFERROR(VLOOKUP(B21,Database!$A$3:$G$103,5,FALSE),"-")</f>
+        <v>-</v>
+      </c>
+      <c r="C23" s="17" t="str">
+        <f>IFERROR(VLOOKUP(C21,Database!$A$3:$G$103,5,FALSE),"-")</f>
+        <v>-</v>
+      </c>
+      <c r="D23" s="17" t="str">
+        <f>IFERROR(VLOOKUP(D21,Database!$A$3:$G$103,5,FALSE),"-")</f>
+        <v>-</v>
+      </c>
+      <c r="E23" s="17" t="str">
+        <f>IFERROR(VLOOKUP(E21,Database!$A$3:$G$103,5,FALSE),"-")</f>
+        <v>-</v>
+      </c>
+      <c r="F23" s="17" t="str">
+        <f>IFERROR(VLOOKUP(F21,Database!$A$3:$G$103,5,FALSE),"-")</f>
+        <v>-</v>
+      </c>
+      <c r="G23" s="17" t="str">
+        <f>IFERROR(VLOOKUP(G21,Database!$A$3:$G$103,5,FALSE),"-")</f>
+        <v>-</v>
+      </c>
     </row>
     <row r="24" spans="1:7" ht="16.5" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A24" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="B24" s="20" t="str">
-        <f>IF($B$12&gt;$B$21,"Input excesive",IF($B$12&lt;$B$21,"Output excessive","Equal"))</f>
+        <v>86</v>
+      </c>
+      <c r="B24" s="15">
+        <f>IFERROR(B20*B22,0)</f>
+        <v>0</v>
+      </c>
+      <c r="C24" s="15" t="str">
+        <f>IFERROR(C20*C22,"-")</f>
+        <v>-</v>
+      </c>
+      <c r="D24" s="15" t="str">
+        <f>IFERROR(D20*D22,"-")</f>
+        <v>-</v>
+      </c>
+      <c r="E24" s="15" t="str">
+        <f>IFERROR(E20*E22,"-")</f>
+        <v>-</v>
+      </c>
+      <c r="F24" s="15" t="str">
+        <f>IFERROR(F20*F22,"-")</f>
+        <v>-</v>
+      </c>
+      <c r="G24" s="15" t="str">
+        <f>IFERROR(G20*G22,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A25" s="21" t="s">
+        <v>87</v>
+      </c>
+      <c r="B25" s="28" t="str">
+        <f t="shared" ref="B25:G25" si="2">IFERROR(B24/(B23*1000),"-")</f>
+        <v>-</v>
+      </c>
+      <c r="C25" s="28" t="str">
+        <f t="shared" si="2"/>
+        <v>-</v>
+      </c>
+      <c r="D25" s="28" t="str">
+        <f t="shared" si="2"/>
+        <v>-</v>
+      </c>
+      <c r="E25" s="28" t="str">
+        <f t="shared" si="2"/>
+        <v>-</v>
+      </c>
+      <c r="F25" s="28" t="str">
+        <f t="shared" si="2"/>
+        <v>-</v>
+      </c>
+      <c r="G25" s="28" t="str">
+        <f t="shared" si="2"/>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A26" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="B26" s="20">
+        <f>SUM(B24:G24)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A27" s="7"/>
+    </row>
+    <row r="28" spans="1:7" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="42" t="s">
+        <v>424</v>
+      </c>
+      <c r="B28" s="17" t="str">
+        <f>IFERROR(VLOOKUP(B21,Database!$A$3:$G$103,7,FALSE),"-")</f>
+        <v>-</v>
+      </c>
+      <c r="C28" s="17" t="str">
+        <f>IFERROR(VLOOKUP(C21,Database!$A$3:$G$103,7,FALSE),"-")</f>
+        <v>-</v>
+      </c>
+      <c r="D28" s="17" t="str">
+        <f>IFERROR(VLOOKUP(D21,Database!$A$3:$G$103,7,FALSE),"-")</f>
+        <v>-</v>
+      </c>
+      <c r="E28" s="17" t="str">
+        <f>IFERROR(VLOOKUP(E21,Database!$A$3:$G$103,7,FALSE),"-")</f>
+        <v>-</v>
+      </c>
+      <c r="F28" s="17" t="str">
+        <f>IFERROR(VLOOKUP(F21,Database!$A$3:$G$103,7,FALSE),"-")</f>
+        <v>-</v>
+      </c>
+      <c r="G28" s="17" t="str">
+        <f>IFERROR(VLOOKUP(G21,Database!$A$3:$G$103,7,FALSE),"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" ht="16.5" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="B29" s="15">
+        <f>IFERROR(B20*B28,0)</f>
+        <v>0</v>
+      </c>
+      <c r="C29" s="15">
+        <f t="shared" ref="C29:G29" si="3">IFERROR(C20*C28,0)</f>
+        <v>0</v>
+      </c>
+      <c r="D29" s="15">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="E29" s="15">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="F29" s="15">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="G29" s="15">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A30" s="7" t="s">
+        <v>428</v>
+      </c>
+      <c r="B30" s="41">
+        <f>SUM(B29:G29)/20</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" ht="18" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A33" s="38" t="s">
+        <v>68</v>
+      </c>
+      <c r="B33" s="38"/>
+      <c r="C33" s="38"/>
+      <c r="D33" s="38"/>
+      <c r="E33" s="38"/>
+      <c r="F33" s="38"/>
+      <c r="G33" s="38"/>
+    </row>
+    <row r="34" spans="1:7" ht="16.5" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="B34" s="16" t="str">
+        <f>IF($B$12&gt;$B$26,"Input excesive",IF($B$12&lt;$B$26,"Output excessive","Equal"))</f>
         <v>Equal</v>
       </c>
-      <c r="C24" s="33">
-        <f>IF($B$12&gt;$B$21,B12/B21,IF($B$12&lt;$B$21,B21/B12,1))</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A25" s="7"/>
+      <c r="C34" s="27">
+        <f>IF($B$12&gt;$B$26,B12/B26,IF($B$12&lt;$B$26,B26/B12,1))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G36" s="1"/>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B37" s="45"/>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B39" s="44"/>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:G1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
-            <xm:f>Database!$A$3:$A$140</xm:f>
+            <xm:f>Database!$A$3:$A$141</xm:f>
           </x14:formula1>
-          <xm:sqref>B16:G16</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
-          <x14:formula1>
-            <xm:f>Database!$A$3:$A$140</xm:f>
-          </x14:formula1>
-          <xm:sqref>B7:G7</xm:sqref>
+          <xm:sqref>B21:G21 B7:G7</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -2322,7 +3112,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L140"/>
+  <dimension ref="A1:L141"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.5" customWidth="1"/>
@@ -2352,7 +3142,10 @@
         <v>4</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>212</v>
+        <v>208</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>423</v>
       </c>
     </row>
     <row r="2" spans="1:12" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -2365,16 +3158,16 @@
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>64</v>
+        <v>238</v>
       </c>
       <c r="C3" s="1">
         <v>1</v>
       </c>
       <c r="D3" s="5">
-        <v>207.2</v>
+        <v>576.85</v>
       </c>
       <c r="E3" s="4">
         <f>0.01*1000</f>
@@ -2382,20 +3175,22 @@
       </c>
       <c r="F3" s="6">
         <f>C3*D3/(E3 * 1000)</f>
-        <v>2.0719999999999999E-2</v>
-      </c>
-      <c r="G3" s="8"/>
+        <v>5.7685E-2</v>
+      </c>
+      <c r="G3" s="8">
+        <v>283.27</v>
+      </c>
       <c r="I3" t="s">
         <v>0</v>
       </c>
       <c r="J3" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="K3" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="L3" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
@@ -2419,60 +3214,66 @@
         <f>C4*D4/(E4 * 1000)</f>
         <v>3.4068000000000001E-2</v>
       </c>
+      <c r="G4">
+        <v>488.46</v>
+      </c>
       <c r="I4" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="J4" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="K4">
         <v>117.49</v>
       </c>
-      <c r="L4" s="22">
+      <c r="L4" s="18">
         <v>0.69599999999999995</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A5" s="13" t="s">
+      <c r="A5" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="13" t="s">
-        <v>8</v>
-      </c>
-      <c r="C5" s="13">
-        <v>1</v>
-      </c>
-      <c r="D5" s="14">
-        <f>16*2</f>
-        <v>32</v>
-      </c>
-      <c r="E5" s="15">
+      <c r="B5" s="9" t="s">
+        <v>180</v>
+      </c>
+      <c r="C5" s="9">
+        <v>1</v>
+      </c>
+      <c r="D5" s="10">
+        <f>54.4</f>
+        <v>54.4</v>
+      </c>
+      <c r="E5" s="11">
         <f>0.005*1000</f>
         <v>5</v>
       </c>
-      <c r="F5" s="16">
+      <c r="F5" s="12">
         <f>C5*D5/(E5 * 1000)</f>
-        <v>6.4000000000000003E-3</v>
+        <v>1.0879999999999999E-2</v>
+      </c>
+      <c r="G5">
+        <v>54.4</v>
       </c>
       <c r="I5" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="J5" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="K5">
         <v>26.98</v>
       </c>
-      <c r="L5" s="23">
+      <c r="L5" s="19">
         <v>0.16</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" s="1" t="s">
         <v>9</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>10</v>
       </c>
       <c r="C6" s="1">
         <v>1</v>
@@ -2489,25 +3290,28 @@
         <f>C6*D6/(E6 * 1000)</f>
         <v>8.0114999999999995E-3</v>
       </c>
+      <c r="G6">
+        <v>83.42</v>
+      </c>
       <c r="I6" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="J6" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="K6">
         <v>71.84</v>
       </c>
-      <c r="L6" s="22">
+      <c r="L6" s="18">
         <v>0.4</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7" s="1" t="s">
         <v>13</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>14</v>
       </c>
       <c r="C7" s="1">
         <v>1</v>
@@ -2524,11 +3328,14 @@
         <f>C7*D7/(E7 * 1000)</f>
         <v>1.3129</v>
       </c>
-      <c r="L7" s="22"/>
+      <c r="G7">
+        <v>12.12</v>
+      </c>
+      <c r="L7" s="18"/>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="B8" s="1"/>
       <c r="C8" s="1">
@@ -2540,31 +3347,31 @@
         <v>7.5</v>
       </c>
       <c r="F8" s="6"/>
-      <c r="L8" s="22"/>
+      <c r="L8" s="18"/>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="I9" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="J9" t="s">
-        <v>35</v>
-      </c>
-      <c r="L9" s="23">
+        <v>32</v>
+      </c>
+      <c r="L9" s="19">
         <v>0.12</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="C10" s="1">
         <v>1</v>
       </c>
       <c r="D10" s="5">
-        <f>SUM(($D$47*0.5)+($D$98*0.5))</f>
+        <f>SUM(($D$47*0.5)+($D$99*0.5))</f>
         <v>46.073</v>
       </c>
       <c r="E10" s="4">
@@ -2575,22 +3382,26 @@
         <f t="shared" ref="F10:F20" si="0">C10*D10/(E10 * 1000)</f>
         <v>5.1192222222222222E-2</v>
       </c>
+      <c r="G10">
+        <f>(G47/2)+(G99/2)</f>
+        <v>1623.855</v>
+      </c>
       <c r="I10" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="J10" t="s">
-        <v>35</v>
-      </c>
-      <c r="L10" s="22">
+        <v>32</v>
+      </c>
+      <c r="L10" s="18">
         <v>1.9599999999999999E-2</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C11" s="1">
         <v>1</v>
@@ -2606,13 +3417,16 @@
         <f t="shared" si="0"/>
         <v>2.5618090452261304E-2</v>
       </c>
+      <c r="G11">
+        <v>52.79</v>
+      </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="C12" s="1">
         <v>1</v>
@@ -2628,13 +3442,16 @@
         <f t="shared" si="0"/>
         <v>9.7400722021660658E-3</v>
       </c>
+      <c r="G12">
+        <v>5.98</v>
+      </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C13" s="1">
         <v>1</v>
@@ -2650,13 +3467,16 @@
         <f t="shared" si="0"/>
         <v>22.145643693107935</v>
       </c>
+      <c r="G13">
+        <v>55.3</v>
+      </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B14" s="1" t="s">
         <v>11</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>12</v>
       </c>
       <c r="C14" s="1">
         <v>1</v>
@@ -2672,85 +3492,97 @@
         <f t="shared" si="0"/>
         <v>22.393497757847534</v>
       </c>
+      <c r="G14">
+        <v>15.75</v>
+      </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A15" s="35" t="s">
-        <v>204</v>
-      </c>
-      <c r="B15" s="35" t="s">
-        <v>205</v>
-      </c>
-      <c r="C15" s="35">
-        <v>1</v>
-      </c>
-      <c r="D15" s="36">
+      <c r="A15" s="29" t="s">
+        <v>200</v>
+      </c>
+      <c r="B15" s="29" t="s">
+        <v>201</v>
+      </c>
+      <c r="C15" s="29">
+        <v>1</v>
+      </c>
+      <c r="D15" s="30">
         <v>9.01</v>
       </c>
-      <c r="E15" s="37">
+      <c r="E15" s="31">
         <f>0.0007508*1000</f>
         <v>0.75080000000000002</v>
       </c>
-      <c r="F15" s="38">
+      <c r="F15" s="32">
         <f t="shared" si="0"/>
         <v>1.2000532765050611E-2</v>
       </c>
+      <c r="G15">
+        <v>9.32</v>
+      </c>
       <c r="H15">
         <v>12</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A16" s="35" t="s">
-        <v>206</v>
-      </c>
-      <c r="B16" s="35" t="s">
-        <v>207</v>
-      </c>
-      <c r="C16" s="35">
-        <v>1</v>
-      </c>
-      <c r="D16" s="36">
+      <c r="A16" s="29" t="s">
+        <v>202</v>
+      </c>
+      <c r="B16" s="29" t="s">
+        <v>203</v>
+      </c>
+      <c r="C16" s="29">
+        <v>1</v>
+      </c>
+      <c r="D16" s="30">
         <v>66.02</v>
       </c>
-      <c r="E16" s="37">
+      <c r="E16" s="31">
         <f>0.00244518*1000</f>
         <v>2.4451800000000001</v>
       </c>
-      <c r="F16" s="38">
+      <c r="F16" s="32">
         <f t="shared" si="0"/>
         <v>2.7000057255498568E-2</v>
       </c>
+      <c r="G16">
+        <v>59.47</v>
+      </c>
       <c r="H16">
         <v>27</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A17" s="35" t="s">
-        <v>239</v>
-      </c>
-      <c r="B17" s="35" t="s">
-        <v>234</v>
-      </c>
-      <c r="C17" s="35">
-        <v>1</v>
-      </c>
-      <c r="D17" s="36">
+      <c r="A17" s="29" t="s">
+        <v>235</v>
+      </c>
+      <c r="B17" s="29" t="s">
+        <v>230</v>
+      </c>
+      <c r="C17" s="29">
+        <v>1</v>
+      </c>
+      <c r="D17" s="30">
         <v>720.6</v>
       </c>
-      <c r="E17" s="37">
+      <c r="E17" s="31">
         <f>0.126*1000</f>
         <v>126</v>
       </c>
-      <c r="F17" s="38">
+      <c r="F17" s="32">
         <f t="shared" si="0"/>
         <v>5.7190476190476193E-3</v>
       </c>
+      <c r="G17">
+        <v>675.6</v>
+      </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" s="9" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="C18" s="9">
         <v>1</v>
@@ -2766,16 +3598,19 @@
         <f t="shared" si="0"/>
         <v>1.2E-2</v>
       </c>
+      <c r="G18">
+        <v>8.2899999999999991</v>
+      </c>
       <c r="H18">
         <v>12</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="9" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="C19" s="9">
         <v>1</v>
@@ -2791,15 +3626,17 @@
         <f t="shared" si="0"/>
         <v>6.8865284974093249E-2</v>
       </c>
-      <c r="G19" s="39"/>
-      <c r="H19" s="39"/>
+      <c r="G19" s="33">
+        <v>3.89</v>
+      </c>
+      <c r="H19" s="33"/>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="C20" s="1">
         <v>1</v>
@@ -2815,13 +3652,16 @@
         <f t="shared" si="0"/>
         <v>5.7190476190476193E-3</v>
       </c>
+      <c r="G20">
+        <v>11.26</v>
+      </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C21" s="1">
         <v>1</v>
@@ -2837,13 +3677,16 @@
         <f t="shared" ref="F21:F47" si="1">C21*D21/(E21 * 1000)</f>
         <v>22.557662737057917</v>
       </c>
+      <c r="G21">
+        <v>38.479999999999997</v>
+      </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="C22" s="1">
         <v>1</v>
@@ -2859,10 +3702,13 @@
         <f t="shared" si="1"/>
         <v>22.408000000000001</v>
       </c>
+      <c r="G22">
+        <v>24.87</v>
+      </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="B23" s="1"/>
       <c r="C23" s="1">
@@ -2877,10 +3723,10 @@
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="C24" s="1">
         <v>1</v>
@@ -2896,10 +3742,13 @@
         <f t="shared" si="1"/>
         <v>1.1078125000000001E-2</v>
       </c>
+      <c r="G24">
+        <v>12.96</v>
+      </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="B25" s="1"/>
       <c r="C25" s="1">
@@ -2914,10 +3763,10 @@
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="C26" s="1">
         <v>1</v>
@@ -2933,13 +3782,16 @@
         <f t="shared" si="1"/>
         <v>2.1698268003646309E-2</v>
       </c>
+      <c r="G26">
+        <v>6.19</v>
+      </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="C27" s="1">
         <v>1</v>
@@ -2955,13 +3807,16 @@
         <f t="shared" si="1"/>
         <v>11.188888888888888</v>
       </c>
+      <c r="G27" s="8">
+        <v>13.59</v>
+      </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="C28" s="1">
         <v>1</v>
@@ -2977,13 +3832,16 @@
         <f t="shared" si="1"/>
         <v>3.755E-2</v>
       </c>
+      <c r="G28">
+        <v>35.369999999999997</v>
+      </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="C29" s="1">
         <v>1</v>
@@ -2999,13 +3857,16 @@
         <f t="shared" si="1"/>
         <v>2.1698268003646309E-2</v>
       </c>
+      <c r="G29">
+        <v>6.19</v>
+      </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="C30" s="1">
         <v>1</v>
@@ -3021,13 +3882,16 @@
         <f>C30*D30/(E30 * 1000)</f>
         <v>5.8390367553865653E-2</v>
       </c>
+      <c r="G30">
+        <v>117.67</v>
+      </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="C31" s="1">
         <v>1</v>
@@ -3043,13 +3907,16 @@
         <f>C31*D31/(E31 * 1000)</f>
         <v>7.2713751113751113E-2</v>
       </c>
+      <c r="G31">
+        <v>393.8</v>
+      </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="C32" s="1">
         <v>1</v>
@@ -3065,10 +3932,13 @@
         <f t="shared" si="1"/>
         <v>0.26733600000000002</v>
       </c>
+      <c r="G32">
+        <v>333.76</v>
+      </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="B33" s="1"/>
       <c r="C33" s="1">
@@ -3085,52 +3955,52 @@
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A34" s="35" t="s">
-        <v>213</v>
-      </c>
-      <c r="B34" s="35" t="s">
-        <v>215</v>
-      </c>
-      <c r="C34" s="35">
-        <v>1</v>
-      </c>
-      <c r="D34" s="36">
+      <c r="A34" s="29" t="s">
+        <v>209</v>
+      </c>
+      <c r="B34" s="29" t="s">
+        <v>211</v>
+      </c>
+      <c r="C34" s="29">
+        <v>1</v>
+      </c>
+      <c r="D34" s="30">
         <v>412.91</v>
       </c>
-      <c r="E34" s="37">
+      <c r="E34" s="31">
         <f>0.001556*1000</f>
         <v>1.556</v>
       </c>
-      <c r="F34" s="38">
+      <c r="F34" s="32">
         <f t="shared" si="1"/>
         <v>0.26536632390745502</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A35" s="35" t="s">
-        <v>214</v>
-      </c>
-      <c r="B35" s="35" t="s">
-        <v>216</v>
-      </c>
-      <c r="C35" s="35">
-        <v>1</v>
-      </c>
-      <c r="D35" s="36">
+      <c r="A35" s="29" t="s">
+        <v>210</v>
+      </c>
+      <c r="B35" s="29" t="s">
+        <v>212</v>
+      </c>
+      <c r="C35" s="29">
+        <v>1</v>
+      </c>
+      <c r="D35" s="30">
         <v>278.13</v>
       </c>
-      <c r="E35" s="37">
+      <c r="E35" s="31">
         <f>0.00321*1000</f>
         <v>3.21</v>
       </c>
-      <c r="F35" s="38">
+      <c r="F35" s="32">
         <f t="shared" si="1"/>
         <v>8.6644859813084105E-2</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="B36" s="1"/>
       <c r="C36" s="1">
@@ -3145,10 +4015,10 @@
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="C37" s="1">
         <v>1</v>
@@ -3167,10 +4037,10 @@
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>170</v>
+        <v>242</v>
       </c>
       <c r="C38" s="1">
         <v>1</v>
@@ -3186,10 +4056,13 @@
         <f t="shared" si="1"/>
         <v>5.9375000000000001E-3</v>
       </c>
+      <c r="G38">
+        <v>34.840000000000003</v>
+      </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="B39" s="1"/>
       <c r="C39" s="1"/>
@@ -3202,10 +4075,10 @@
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="C40" s="1">
         <v>1</v>
@@ -3225,10 +4098,10 @@
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="C41" s="1">
         <v>1</v>
@@ -3244,13 +4117,16 @@
         <f t="shared" si="1"/>
         <v>7.6741666666666668E-3</v>
       </c>
+      <c r="G41">
+        <v>3299.94</v>
+      </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>27</v>
+        <v>429</v>
       </c>
       <c r="C42" s="1">
         <v>1</v>
@@ -3266,13 +4142,16 @@
         <f t="shared" si="1"/>
         <v>3.1298181818181815E-2</v>
       </c>
+      <c r="G42">
+        <v>1764.9</v>
+      </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="C43" s="1">
         <v>1</v>
@@ -3288,13 +4167,16 @@
         <f>C43*D43/(E43 * 1000)</f>
         <v>24.128</v>
       </c>
+      <c r="G43">
+        <v>24.58</v>
+      </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="C44" s="1">
         <v>1</v>
@@ -3310,13 +4192,16 @@
         <f>C44*D44/(E44 * 1000)</f>
         <v>22.407614781634937</v>
       </c>
+      <c r="G44">
+        <v>24.58</v>
+      </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="C45" s="1">
         <v>1</v>
@@ -3332,13 +4217,16 @@
         <f>C45*D45/(E45 * 1000)</f>
         <v>2.3766596785464708E-2</v>
       </c>
+      <c r="G45">
+        <v>54.4</v>
+      </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C46" s="1">
         <v>1</v>
@@ -3354,13 +4242,16 @@
         <f t="shared" si="1"/>
         <v>0.11246</v>
       </c>
+      <c r="G46">
+        <v>77.025000000000006</v>
+      </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="C47" s="1">
         <v>1</v>
@@ -3377,33 +4268,38 @@
         <f t="shared" si="1"/>
         <v>3.1918326693227091E-2</v>
       </c>
+      <c r="G47">
+        <v>41.71</v>
+      </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>15</v>
+        <v>384</v>
       </c>
       <c r="C48" s="1">
         <v>1</v>
       </c>
       <c r="D48" s="5">
-        <v>2.02</v>
+        <v>1.01</v>
       </c>
       <c r="E48" s="4">
         <f>0.0000000899*1000</f>
         <v>8.9900000000000003E-5</v>
       </c>
       <c r="F48" s="6">
-        <f t="shared" ref="F48:F62" si="2">C48*D48/(E48 * 1000)</f>
-        <v>22.469410456062288</v>
-      </c>
-      <c r="G48" s="8"/>
+        <f t="shared" ref="F48:F61" si="2">C48*D48/(E48 * 1000)</f>
+        <v>11.234705228031144</v>
+      </c>
+      <c r="G48" s="8">
+        <v>13.59</v>
+      </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="B49" s="1" t="s">
         <v>6</v>
@@ -3422,14 +4318,16 @@
         <f>C49*D49/(E49 * 1000)</f>
         <v>0.20773170731707319</v>
       </c>
-      <c r="G49" s="8"/>
+      <c r="G49">
+        <v>488.46</v>
+      </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="C50" s="1">
         <v>1</v>
@@ -3445,37 +4343,41 @@
         <f t="shared" si="2"/>
         <v>1.2996254681647943E-2</v>
       </c>
-      <c r="G50" s="8"/>
+      <c r="G50" s="8">
+        <v>5.39</v>
+      </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A51" s="35" t="s">
-        <v>237</v>
-      </c>
-      <c r="B51" s="35" t="s">
-        <v>238</v>
-      </c>
-      <c r="C51" s="35">
-        <v>1</v>
-      </c>
-      <c r="D51" s="36">
+      <c r="A51" s="29" t="s">
+        <v>233</v>
+      </c>
+      <c r="B51" s="29" t="s">
+        <v>234</v>
+      </c>
+      <c r="C51" s="29">
+        <v>1</v>
+      </c>
+      <c r="D51" s="30">
         <v>153.114</v>
       </c>
-      <c r="E51" s="37">
+      <c r="E51" s="31">
         <f>0.0086964*1000</f>
         <v>8.6964000000000006</v>
       </c>
-      <c r="F51" s="38">
+      <c r="F51" s="32">
         <f t="shared" si="2"/>
         <v>1.7606595832758379E-2</v>
       </c>
-      <c r="G51" s="8"/>
+      <c r="G51" s="44">
+        <v>6215.4</v>
+      </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C52" s="1">
         <v>1</v>
@@ -3491,365 +4393,409 @@
         <f t="shared" si="2"/>
         <v>2.4255804016521866E-2</v>
       </c>
+      <c r="G52">
+        <v>55.3</v>
+      </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
-        <v>182</v>
+        <v>394</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>183</v>
+        <v>11</v>
       </c>
       <c r="C53" s="1">
         <v>1</v>
       </c>
       <c r="D53" s="5">
+        <v>39.950000000000003</v>
+      </c>
+      <c r="E53" s="4">
+        <f>0.0013954*1000</f>
+        <v>1.3954</v>
+      </c>
+      <c r="F53" s="6">
+        <f t="shared" si="2"/>
+        <v>2.8629783574602271E-2</v>
+      </c>
+      <c r="G53">
+        <v>15.75</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A54" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="C54" s="1">
+        <v>1</v>
+      </c>
+      <c r="D54" s="5">
         <v>28.01</v>
       </c>
-      <c r="E53" s="4">
+      <c r="E54" s="4">
         <f>0.00079*1000</f>
         <v>0.79</v>
       </c>
-      <c r="F53" s="6">
-        <f>C53*D53/(E53 * 1000)</f>
+      <c r="F54" s="6">
+        <f>C54*D54/(E54 * 1000)</f>
         <v>3.5455696202531646E-2</v>
       </c>
-    </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A54" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B54" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C54" s="1">
-        <v>1</v>
-      </c>
-      <c r="D54" s="5">
+      <c r="G54">
+        <v>24.87</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A55" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C55" s="1">
+        <v>1</v>
+      </c>
+      <c r="D55" s="5">
         <v>44.01</v>
       </c>
-      <c r="E54" s="4">
+      <c r="E55" s="4">
         <f>0.00117325*1000</f>
         <v>1.1732500000000001</v>
       </c>
-      <c r="F54" s="6">
+      <c r="F55" s="6">
         <f t="shared" si="2"/>
         <v>3.7511186874067751E-2</v>
       </c>
-    </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A55" s="1" t="s">
+      <c r="G55">
+        <v>38.479999999999997</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A56" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="B56" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="B55" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="C55" s="1">
-        <v>1</v>
-      </c>
-      <c r="D55" s="5">
+      <c r="C56" s="1">
+        <v>1</v>
+      </c>
+      <c r="D56" s="5">
         <v>2.0139999999999998</v>
       </c>
-      <c r="E55" s="4">
+      <c r="E56" s="4">
         <f>0.0001624*1000</f>
         <v>0.16239999999999999</v>
       </c>
-      <c r="F55" s="6">
+      <c r="F56" s="6">
         <f t="shared" si="2"/>
         <v>1.2401477832512315E-2</v>
       </c>
-    </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A56" s="1" t="s">
-        <v>241</v>
-      </c>
-      <c r="B56" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="C56" s="1">
-        <v>1</v>
-      </c>
-      <c r="D56" s="5">
+      <c r="G56">
+        <v>13.59</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A57" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="C57" s="1">
+        <v>1</v>
+      </c>
+      <c r="D57" s="5">
         <v>19</v>
       </c>
-      <c r="E56" s="4">
+      <c r="E57" s="4">
         <f>0.001505*1000</f>
         <v>1.5050000000000001</v>
       </c>
-      <c r="F56" s="6">
+      <c r="F57" s="6">
         <f t="shared" si="2"/>
         <v>1.2624584717607971E-2</v>
       </c>
-    </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A57" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="B57" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="C57" s="1">
-        <v>1</v>
-      </c>
-      <c r="D57" s="5">
+      <c r="G57">
+        <v>34.840000000000003</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A58" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="C58" s="1">
+        <v>1</v>
+      </c>
+      <c r="D58" s="5">
         <v>3.016</v>
       </c>
-      <c r="E57" s="4">
+      <c r="E58" s="4">
         <f>0.000059*1000</f>
         <v>5.8999999999999997E-2</v>
       </c>
-      <c r="F57" s="6">
-        <f>C57*D57/(E57 * 1000)</f>
+      <c r="F58" s="6">
+        <f>C58*D58/(E58 * 1000)</f>
         <v>5.1118644067796613E-2</v>
       </c>
-    </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A58" s="1" t="s">
-        <v>174</v>
-      </c>
-      <c r="B58" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="C58" s="1">
-        <v>1</v>
-      </c>
-      <c r="D58" s="5">
+      <c r="G58">
+        <v>24.58</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A59" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="C59" s="1">
+        <v>1</v>
+      </c>
+      <c r="D59" s="5">
         <v>4.0019999999999998</v>
       </c>
-      <c r="E58" s="4">
+      <c r="E59" s="4">
         <f>0.0001786*1000</f>
         <v>0.17860000000000001</v>
       </c>
-      <c r="F58" s="6">
-        <f>C58*D58/(E58 * 1000)</f>
+      <c r="F59" s="6">
+        <f>C59*D59/(E59 * 1000)</f>
         <v>2.2407614781634933E-2</v>
       </c>
-    </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A59" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="B59" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C59" s="1">
-        <v>1</v>
-      </c>
-      <c r="D59" s="5">
-        <v>2.02</v>
-      </c>
-      <c r="E59" s="4">
+      <c r="G59">
+        <v>24.58</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A60" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>384</v>
+      </c>
+      <c r="C60" s="1">
+        <v>1</v>
+      </c>
+      <c r="D60" s="5">
+        <v>1.01</v>
+      </c>
+      <c r="E60" s="4">
         <f>0.00007085*1000</f>
         <v>7.0849999999999996E-2</v>
       </c>
-      <c r="F59" s="6">
-        <f>C59*D59/(E59 * 1000)</f>
-        <v>2.8510938602681724E-2</v>
-      </c>
-    </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A60" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B60" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C60" s="1">
-        <v>1</v>
-      </c>
-      <c r="D60" s="5">
+      <c r="F60" s="6">
+        <f>C60*D60/(E60 * 1000)</f>
+        <v>1.4255469301340862E-2</v>
+      </c>
+      <c r="G60">
+        <v>13.59</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A61" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B61" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C61" s="1">
+        <v>1</v>
+      </c>
+      <c r="D61" s="5">
         <v>16.05</v>
       </c>
-      <c r="E60" s="4">
+      <c r="E61" s="4">
         <f>0.00042561*1000</f>
         <v>0.42560999999999999</v>
       </c>
-      <c r="F60" s="6">
+      <c r="F61" s="6">
         <f t="shared" si="2"/>
         <v>3.7710580108550079E-2</v>
       </c>
-    </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A61" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="B61" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="C61" s="9">
-        <v>1</v>
-      </c>
-      <c r="D61" s="10">
-        <v>32</v>
-      </c>
-      <c r="E61" s="11">
-        <f>0.001141*1000</f>
-        <v>1.141</v>
-      </c>
-      <c r="F61" s="12">
-        <f t="shared" si="2"/>
-        <v>2.8045574057843997E-2</v>
+      <c r="G61">
+        <v>65.62</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>21</v>
+        <v>382</v>
       </c>
       <c r="C62" s="1">
         <v>1</v>
       </c>
       <c r="D62" s="5">
-        <v>28.01</v>
+        <v>14.01</v>
       </c>
       <c r="E62" s="4">
         <f>0.000824907*1000</f>
         <v>0.82490700000000006</v>
       </c>
       <c r="F62" s="6">
-        <f t="shared" si="2"/>
-        <v>3.3955342844708553E-2</v>
+        <f>C62*D62/(E62 * 1000)</f>
+        <v>1.6983732711687499E-2</v>
+      </c>
+      <c r="G62">
+        <v>14.53</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="B63" s="1"/>
-      <c r="C63" s="1">
-        <v>1</v>
-      </c>
-      <c r="D63" s="5"/>
-      <c r="E63" s="4">
+        <v>70</v>
+      </c>
+      <c r="B63" s="9" t="s">
+        <v>241</v>
+      </c>
+      <c r="C63" s="9">
+        <v>1</v>
+      </c>
+      <c r="D63" s="10">
+        <v>16</v>
+      </c>
+      <c r="E63" s="11">
+        <f>0.001141*1000</f>
+        <v>1.141</v>
+      </c>
+      <c r="F63" s="12">
+        <f t="shared" ref="F63" si="3">C63*D63/(E63 * 1000)</f>
+        <v>1.4022787028921999E-2</v>
+      </c>
+      <c r="G63">
+        <v>13.61</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A64" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="B64" s="1"/>
+      <c r="C64" s="1">
+        <v>1</v>
+      </c>
+      <c r="D64" s="5"/>
+      <c r="E64" s="4">
         <f>0.00378*1000</f>
         <v>3.78</v>
       </c>
-      <c r="F63" s="6"/>
-    </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A64" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="B64" s="1"/>
-      <c r="C64" s="1">
-        <v>1</v>
-      </c>
-      <c r="D64" s="5"/>
-      <c r="E64" s="4">
-        <f>0.001*1000</f>
-        <v>1</v>
-      </c>
       <c r="F64" s="6"/>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="B65" s="1" t="s">
-        <v>15</v>
-      </c>
+        <v>114</v>
+      </c>
+      <c r="B65" s="1"/>
       <c r="C65" s="1">
         <v>1</v>
       </c>
-      <c r="D65" s="5">
-        <f>D59</f>
-        <v>2.02</v>
-      </c>
+      <c r="D65" s="5"/>
       <c r="E65" s="4">
+        <f>0.001*1000</f>
+        <v>1</v>
+      </c>
+      <c r="F65" s="6"/>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A66" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="B66" s="1" t="s">
+        <v>384</v>
+      </c>
+      <c r="C66" s="1">
+        <v>1</v>
+      </c>
+      <c r="D66" s="5">
+        <f>D60</f>
+        <v>1.01</v>
+      </c>
+      <c r="E66" s="4">
         <f>0.007085*1000</f>
         <v>7.085</v>
       </c>
-      <c r="F65" s="6">
-        <f t="shared" ref="F65:F74" si="3">C65*D65/(E65 * 1000)</f>
-        <v>2.851093860268172E-4</v>
-      </c>
-      <c r="H65">
+      <c r="F66" s="6">
+        <f t="shared" ref="F66:F75" si="4">C66*D66/(E66 * 1000)</f>
+        <v>1.425546930134086E-4</v>
+      </c>
+      <c r="G66">
+        <v>13.59</v>
+      </c>
+      <c r="H66">
         <f>0.000824907*4</f>
         <v>3.2996280000000002E-3</v>
       </c>
     </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A66" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="B66" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="C66" s="1">
-        <v>1</v>
-      </c>
-      <c r="D66" s="5">
+    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A67" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="B67" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="C67" s="1">
+        <v>1</v>
+      </c>
+      <c r="D67" s="5">
         <v>159.69</v>
       </c>
-      <c r="E66" s="4">
+      <c r="E67" s="4">
         <f>0.0055*1000</f>
         <v>5.5</v>
       </c>
-      <c r="F66" s="6">
-        <f t="shared" si="3"/>
+      <c r="F67" s="6">
+        <f t="shared" si="4"/>
         <v>2.9034545454545455E-2</v>
       </c>
-      <c r="H66">
+      <c r="G67">
+        <v>56.63</v>
+      </c>
+      <c r="H67">
         <f>0.000001784*6</f>
         <v>1.0703999999999999E-5</v>
       </c>
     </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A67" s="1" t="s">
-        <v>199</v>
-      </c>
-      <c r="B67" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="C67" s="1">
-        <v>1</v>
-      </c>
-      <c r="D67" s="5">
+    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A68" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="B68" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="C68" s="1">
+        <v>1</v>
+      </c>
+      <c r="D68" s="5">
         <v>159.69</v>
       </c>
-      <c r="E67" s="4">
+      <c r="E68" s="4">
         <f>0.026*1000</f>
         <v>26</v>
       </c>
-      <c r="F67" s="6">
-        <f t="shared" si="3"/>
+      <c r="F68" s="6">
+        <f t="shared" si="4"/>
         <v>6.1419230769230769E-3</v>
       </c>
-      <c r="H67">
-        <f>H65+H66</f>
+      <c r="G68">
+        <v>56.63</v>
+      </c>
+      <c r="H68">
+        <f>H66+H67</f>
         <v>3.310332E-3</v>
-      </c>
-    </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A68" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="B68" s="1" t="s">
-        <v>200</v>
-      </c>
-      <c r="C68" s="1">
-        <v>1</v>
-      </c>
-      <c r="D68" s="5">
-        <f>55.845*2</f>
-        <v>111.69</v>
-      </c>
-      <c r="E68" s="4">
-        <f>0.039*1000</f>
-        <v>39</v>
-      </c>
-      <c r="F68" s="6">
-        <f t="shared" si="3"/>
-        <v>2.8638461538461539E-3</v>
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="C69" s="1">
         <v>1</v>
@@ -3859,1057 +4805,1138 @@
         <v>111.69</v>
       </c>
       <c r="E69" s="4">
+        <f>0.039*1000</f>
+        <v>39</v>
+      </c>
+      <c r="F69" s="6">
+        <f t="shared" si="4"/>
+        <v>2.8638461538461539E-3</v>
+      </c>
+      <c r="G69">
+        <v>7.9</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A70" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="B70" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="C70" s="1">
+        <v>1</v>
+      </c>
+      <c r="D70" s="5">
+        <f>55.845*2</f>
+        <v>111.69</v>
+      </c>
+      <c r="E70" s="4">
         <f>0.0078*1000</f>
         <v>7.8</v>
       </c>
-      <c r="F69" s="6">
-        <f t="shared" si="3"/>
+      <c r="F70" s="6">
+        <f t="shared" si="4"/>
         <v>1.4319230769230768E-2</v>
       </c>
-    </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A70" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B70" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C70" s="1">
-        <v>1</v>
-      </c>
-      <c r="D70" s="5">
+      <c r="G70">
+        <v>7.9</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A71" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B71" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C71" s="1">
+        <v>1</v>
+      </c>
+      <c r="D71" s="5">
         <f>12.02+4*1.008</f>
         <v>16.052</v>
       </c>
-      <c r="E70" s="4">
+      <c r="E71" s="4">
         <f>0.000000717*1000</f>
         <v>7.1699999999999997E-4</v>
       </c>
-      <c r="F70" s="6">
-        <f t="shared" si="3"/>
+      <c r="F71" s="6">
+        <f t="shared" si="4"/>
         <v>22.387726638772666</v>
       </c>
-    </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A71" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="B71" s="1" t="s">
-        <v>223</v>
-      </c>
-      <c r="C71" s="1">
-        <v>1</v>
-      </c>
-      <c r="D71" s="5">
+      <c r="G71">
+        <v>16.042999999999999</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A72" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B72" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="C72" s="1">
+        <v>1</v>
+      </c>
+      <c r="D72" s="5">
         <f>323.31+78.07</f>
         <v>401.38</v>
       </c>
-      <c r="E71" s="4">
+      <c r="E72" s="4">
         <f>0.0027*1000</f>
         <v>2.7</v>
       </c>
-      <c r="F71" s="6">
-        <f t="shared" si="3"/>
+      <c r="F72" s="6">
+        <f t="shared" si="4"/>
         <v>0.14865925925925927</v>
       </c>
-    </row>
-    <row r="72" spans="1:8" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A72" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="B72" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="C72" s="1">
-        <v>1</v>
-      </c>
-      <c r="D72" s="5">
+      <c r="G72">
+        <v>76.040000000000006</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="A73" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="B73" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="C73" s="1">
+        <v>1</v>
+      </c>
+      <c r="D73" s="5">
         <v>46.07</v>
       </c>
-      <c r="E72" s="4">
+      <c r="E73" s="4">
         <f>0.00088*1000</f>
         <v>0.88</v>
       </c>
-      <c r="F72" s="6">
-        <f t="shared" si="3"/>
+      <c r="F73" s="6">
+        <f t="shared" si="4"/>
         <v>5.2352272727272726E-2</v>
       </c>
-    </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A73" s="35" t="s">
-        <v>202</v>
-      </c>
-      <c r="B73" s="35" t="s">
-        <v>203</v>
-      </c>
-      <c r="C73" s="35">
-        <v>1</v>
-      </c>
-      <c r="D73" s="36">
+      <c r="G73">
+        <v>121.86</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A74" s="29" t="s">
+        <v>198</v>
+      </c>
+      <c r="B74" s="29" t="s">
+        <v>199</v>
+      </c>
+      <c r="C74" s="29">
+        <v>1</v>
+      </c>
+      <c r="D74" s="30">
         <v>60.08</v>
       </c>
-      <c r="E73" s="37">
+      <c r="E74" s="31">
         <f>0.00347*1000</f>
         <v>3.47</v>
       </c>
-      <c r="F73" s="38">
-        <f>C73*D73/(E73 * 1000)</f>
+      <c r="F74" s="32">
+        <f>C74*D74/(E74 * 1000)</f>
         <v>1.7314121037463978E-2</v>
       </c>
-    </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A74" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="B74" s="1" t="s">
-        <v>217</v>
-      </c>
-      <c r="C74" s="1">
-        <v>1</v>
-      </c>
-      <c r="D74" s="5">
+      <c r="G74">
+        <v>35.369999999999997</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A75" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B75" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="C75" s="1">
+        <v>1</v>
+      </c>
+      <c r="D75" s="5">
         <v>750.27</v>
       </c>
-      <c r="E74" s="4">
+      <c r="E75" s="4">
         <f>0.005*1000</f>
         <v>5</v>
       </c>
-      <c r="F74" s="6">
-        <f t="shared" si="3"/>
+      <c r="F75" s="6">
+        <f t="shared" si="4"/>
         <v>0.15005399999999999</v>
       </c>
-    </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A75" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="B75" s="1"/>
-      <c r="C75" s="1">
-        <v>1</v>
-      </c>
-      <c r="D75" s="5"/>
-      <c r="E75" s="4">
-        <f>0.001*1000</f>
-        <v>1</v>
-      </c>
-      <c r="F75" s="6"/>
+      <c r="G75">
+        <v>71.22</v>
+      </c>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="B76" s="1" t="s">
-        <v>21</v>
-      </c>
+        <v>132</v>
+      </c>
+      <c r="B76" s="1"/>
       <c r="C76" s="1">
         <v>1</v>
       </c>
-      <c r="D76" s="5">
-        <f>14.007*2</f>
-        <v>28.013999999999999</v>
-      </c>
+      <c r="D76" s="5"/>
       <c r="E76" s="4">
+        <f>0.001*1000</f>
+        <v>1</v>
+      </c>
+      <c r="F76" s="6"/>
+    </row>
+    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A77" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B77" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C77" s="1">
+        <v>1</v>
+      </c>
+      <c r="D77" s="5">
+        <v>14.01</v>
+      </c>
+      <c r="E77" s="4">
         <f>0.000001251*1000</f>
         <v>1.2509999999999999E-3</v>
       </c>
-      <c r="F76" s="6">
-        <f>C76*D76/(E76 * 1000)</f>
-        <v>22.393285371702639</v>
-      </c>
-    </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A77" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="B77" s="1" t="s">
-        <v>172</v>
-      </c>
-      <c r="C77" s="1">
-        <v>1</v>
-      </c>
-      <c r="D77" s="5">
+      <c r="F77" s="6">
+        <f>C77*D77/(E77 * 1000)</f>
+        <v>11.199040767386093</v>
+      </c>
+      <c r="G77">
+        <v>14.53</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A78" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="B78" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="C78" s="1">
+        <v>1</v>
+      </c>
+      <c r="D78" s="5">
         <v>92.04</v>
       </c>
-      <c r="E77" s="4">
+      <c r="E78" s="4">
         <f>0.00145*1000</f>
         <v>1.45</v>
       </c>
-      <c r="F77" s="6">
-        <f>C77*D77/(E77 * 1000)</f>
+      <c r="F78" s="6">
+        <f>C78*D78/(E78 * 1000)</f>
         <v>6.3475862068965522E-2</v>
       </c>
-    </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A78" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="B78" s="1"/>
-      <c r="C78" s="1">
-        <v>1</v>
-      </c>
-      <c r="D78" s="5"/>
-      <c r="E78" s="4">
+      <c r="G78">
+        <v>83.5</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A79" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B79" s="1"/>
+      <c r="C79" s="1">
+        <v>1</v>
+      </c>
+      <c r="D79" s="5"/>
+      <c r="E79" s="4">
         <f>0.00105*1000</f>
         <v>1.05</v>
       </c>
-      <c r="F78" s="6"/>
-    </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A79" s="35" t="s">
-        <v>235</v>
-      </c>
-      <c r="B79" s="35" t="s">
-        <v>236</v>
-      </c>
-      <c r="C79" s="35">
-        <v>1</v>
-      </c>
-      <c r="D79" s="36">
+      <c r="F79" s="6"/>
+    </row>
+    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A80" s="29" t="s">
+        <v>231</v>
+      </c>
+      <c r="B80" s="29" t="s">
+        <v>232</v>
+      </c>
+      <c r="C80" s="29">
+        <v>1</v>
+      </c>
+      <c r="D80" s="30">
         <f>(14.005*8)+(39.95*6)</f>
         <v>351.74</v>
       </c>
-      <c r="E79" s="37">
+      <c r="E80" s="31">
         <f>0.003310332*1000</f>
         <v>3.3103319999999998</v>
       </c>
-      <c r="F79" s="38">
-        <f>C79*D79/(E79 * 1000)</f>
+      <c r="F80" s="32">
+        <f>C80*D80/(E80 * 1000)</f>
         <v>0.10625520340557987</v>
       </c>
-    </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A80" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="B80" s="1"/>
-      <c r="C80" s="1">
-        <v>1</v>
-      </c>
-      <c r="D80" s="5"/>
-      <c r="E80" s="4">
+      <c r="G80">
+        <v>210.74</v>
+      </c>
+    </row>
+    <row r="81" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A81" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="B81" s="1"/>
+      <c r="C81" s="1">
+        <v>1</v>
+      </c>
+      <c r="D81" s="5"/>
+      <c r="E81" s="4">
         <f>0.001*1000</f>
         <v>1</v>
       </c>
-      <c r="F80" s="6"/>
-    </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A81" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="B81" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C81" s="1">
-        <v>1</v>
-      </c>
-      <c r="D81" s="5">
-        <v>32</v>
-      </c>
-      <c r="E81" s="4">
+      <c r="F81" s="6"/>
+    </row>
+    <row r="82" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A82" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B82" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="C82" s="1">
+        <v>1</v>
+      </c>
+      <c r="D82" s="5">
+        <v>16</v>
+      </c>
+      <c r="E82" s="4">
         <f>0.00000141*1000</f>
         <v>1.41E-3</v>
       </c>
-      <c r="F81" s="6">
-        <f>C81*D81/(E81 * 1000)</f>
-        <v>22.695035460992909</v>
-      </c>
-    </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A82" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="B82" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="C82" s="1">
-        <v>1</v>
-      </c>
-      <c r="D82" s="5">
+      <c r="F82" s="6">
+        <f>C82*D82/(E82 * 1000)</f>
+        <v>11.347517730496454</v>
+      </c>
+      <c r="G82">
+        <v>13.61</v>
+      </c>
+    </row>
+    <row r="83" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A83" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B83" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C83" s="1">
+        <v>1</v>
+      </c>
+      <c r="D83" s="5">
         <v>30.97</v>
       </c>
-      <c r="E82" s="17">
+      <c r="E83" s="13">
         <f>$E$4</f>
         <v>5</v>
       </c>
-      <c r="F82" s="6">
-        <f>C82*D82/(E82 * 1000)</f>
+      <c r="F83" s="6">
+        <f>C83*D83/(E83 * 1000)</f>
         <v>6.1939999999999999E-3</v>
       </c>
-    </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A83" s="1" t="s">
-        <v>210</v>
-      </c>
-      <c r="B83" s="1" t="s">
-        <v>211</v>
-      </c>
-      <c r="C83" s="1">
-        <v>1</v>
-      </c>
-      <c r="D83" s="5">
+      <c r="G83">
+        <v>10.48</v>
+      </c>
+    </row>
+    <row r="84" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A84" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="B84" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="C84" s="1">
+        <v>1</v>
+      </c>
+      <c r="D84" s="5">
         <v>244</v>
       </c>
-      <c r="E83" s="4">
+      <c r="E84" s="4">
         <f>0.019816*1000</f>
         <v>19.815999999999999</v>
       </c>
-      <c r="F83" s="6">
-        <f>C83*D83/(E83 * 1000)</f>
+      <c r="F84" s="6">
+        <f>C84*D84/(E84 * 1000)</f>
         <v>1.2313282196205087E-2</v>
       </c>
-    </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A84" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="B84" s="1"/>
-      <c r="C84" s="1">
-        <v>1</v>
-      </c>
-      <c r="D84" s="5"/>
-      <c r="E84" s="4">
+      <c r="G84">
+        <v>6.02</v>
+      </c>
+    </row>
+    <row r="85" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A85" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="B85" s="1"/>
+      <c r="C85" s="1">
+        <v>1</v>
+      </c>
+      <c r="D85" s="5"/>
+      <c r="E85" s="4">
         <f>0.00104*1000</f>
         <v>1.0399999999999998</v>
       </c>
-      <c r="F84" s="6"/>
-    </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A85" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="B85" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="C85" s="1">
-        <v>1</v>
-      </c>
-      <c r="D85" s="5">
+      <c r="F85" s="6"/>
+    </row>
+    <row r="86" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A86" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B86" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C86" s="1">
+        <v>1</v>
+      </c>
+      <c r="D86" s="5">
         <f>195.078</f>
         <v>195.078</v>
       </c>
-      <c r="E85" s="4">
+      <c r="E86" s="4">
         <f>0.0078*1000</f>
         <v>7.8</v>
       </c>
-      <c r="F85" s="6">
-        <f>C85*D85/(E85 * 1000)</f>
+      <c r="F86" s="6">
+        <f>C86*D86/(E86 * 1000)</f>
         <v>2.5010000000000001E-2</v>
       </c>
-    </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A86" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="B86" s="1"/>
-      <c r="C86" s="1">
-        <v>1</v>
-      </c>
-      <c r="D86" s="5"/>
-      <c r="E86" s="4">
+      <c r="G86">
+        <v>8.9499999999999993</v>
+      </c>
+    </row>
+    <row r="87" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A87" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="B87" s="1"/>
+      <c r="C87" s="1">
+        <v>1</v>
+      </c>
+      <c r="D87" s="5"/>
+      <c r="E87" s="4">
         <f>0.00378*1000</f>
         <v>3.78</v>
       </c>
-      <c r="F86" s="6"/>
-    </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A87" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="B87" s="1"/>
-      <c r="C87" s="1">
-        <v>1</v>
-      </c>
-      <c r="D87" s="5"/>
-      <c r="E87" s="4">
+      <c r="F87" s="6"/>
+    </row>
+    <row r="88" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A88" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="B88" s="1"/>
+      <c r="C88" s="1">
+        <v>1</v>
+      </c>
+      <c r="D88" s="5"/>
+      <c r="E88" s="4">
         <f>0.0052*1000</f>
         <v>5.2</v>
       </c>
-      <c r="F87" s="6"/>
-    </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A88" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="B88" s="1"/>
-      <c r="C88" s="1">
-        <v>1</v>
-      </c>
-      <c r="D88" s="5"/>
-      <c r="E88" s="4">
+      <c r="F88" s="6"/>
+    </row>
+    <row r="89" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A89" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="B89" s="1"/>
+      <c r="C89" s="1">
+        <v>1</v>
+      </c>
+      <c r="D89" s="5"/>
+      <c r="E89" s="4">
         <f>0.0025*1000</f>
         <v>2.5</v>
       </c>
-      <c r="F88" s="6"/>
-    </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A89" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="B89" s="1"/>
-      <c r="C89" s="1">
-        <v>1</v>
-      </c>
-      <c r="D89" s="5"/>
-      <c r="E89" s="4">
+      <c r="F89" s="6"/>
+    </row>
+    <row r="90" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A90" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="B90" s="1"/>
+      <c r="C90" s="1">
+        <v>1</v>
+      </c>
+      <c r="D90" s="5"/>
+      <c r="E90" s="4">
         <f>0.004*1000</f>
         <v>4</v>
       </c>
-      <c r="F89" s="6"/>
-    </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A90" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B90" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="C90" s="1">
-        <v>1</v>
-      </c>
-      <c r="D90" s="5">
+      <c r="F90" s="6"/>
+    </row>
+    <row r="91" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A91" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B91" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="C91" s="1">
+        <v>1</v>
+      </c>
+      <c r="D91" s="5">
         <v>76.08</v>
       </c>
-      <c r="E90" s="4">
+      <c r="E91" s="4">
         <f>0.0025*1000</f>
         <v>2.5</v>
       </c>
-      <c r="F90" s="6">
-        <f>C90*D90/(E90 * 1000)</f>
+      <c r="F91" s="6">
+        <f>C91*D91/(E91 * 1000)</f>
         <v>3.0432000000000001E-2</v>
       </c>
-    </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A91" s="1" t="s">
-        <v>166</v>
-      </c>
-      <c r="B91" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="C91" s="1">
-        <v>1</v>
-      </c>
-      <c r="D91" s="5">
+      <c r="G91">
+        <v>48.98</v>
+      </c>
+    </row>
+    <row r="92" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A92" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="B92" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="C92" s="1">
+        <v>1</v>
+      </c>
+      <c r="D92" s="5">
         <v>28.09</v>
       </c>
-      <c r="E91" s="4">
+      <c r="E92" s="4">
         <f>0.002329*1000</f>
         <v>2.3289999999999997</v>
       </c>
-      <c r="F91" s="6">
-        <f>C91*D91/(E91 * 1000)</f>
+      <c r="F92" s="6">
+        <f>C92*D92/(E92 * 1000)</f>
         <v>1.2060970373550882E-2</v>
       </c>
-    </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A92" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="B92" s="1"/>
-      <c r="C92" s="1">
-        <v>1</v>
-      </c>
-      <c r="D92" s="5"/>
-      <c r="E92" s="4">
+      <c r="G92">
+        <v>8.15</v>
+      </c>
+    </row>
+    <row r="93" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A93" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B93" s="1"/>
+      <c r="C93" s="1">
+        <v>1</v>
+      </c>
+      <c r="D93" s="5"/>
+      <c r="E93" s="4">
         <f>0.00378*1000</f>
         <v>3.78</v>
       </c>
-      <c r="F92" s="6"/>
-    </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A93" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="B93" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="C93" s="1">
-        <v>1</v>
-      </c>
-      <c r="D93" s="5">
+      <c r="F93" s="6"/>
+    </row>
+    <row r="94" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A94" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="B94" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="C94" s="1">
+        <v>1</v>
+      </c>
+      <c r="D94" s="5">
         <v>186.09</v>
       </c>
-      <c r="E93" s="4">
+      <c r="E94" s="4">
         <f>0.0031*1000</f>
         <v>3.1</v>
       </c>
-      <c r="F93" s="6">
-        <f>C93*D93/(E93 * 1000)</f>
+      <c r="F94" s="6">
+        <f>C94*D94/(E94 * 1000)</f>
         <v>6.0029032258064517E-2</v>
       </c>
-    </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A94" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="B94" s="1"/>
-      <c r="C94" s="1">
-        <v>1</v>
-      </c>
-      <c r="D94" s="5"/>
-      <c r="E94" s="4">
+      <c r="G94">
+        <v>109.33</v>
+      </c>
+    </row>
+    <row r="95" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A95" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B95" s="1"/>
+      <c r="C95" s="1">
+        <v>1</v>
+      </c>
+      <c r="D95" s="5"/>
+      <c r="E95" s="4">
         <f>0.0016*1000</f>
         <v>1.6</v>
       </c>
-      <c r="F94" s="6"/>
-    </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A95" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="B95" s="1"/>
-      <c r="C95" s="1">
-        <v>1</v>
-      </c>
-      <c r="D95" s="5"/>
-      <c r="E95" s="4">
+      <c r="F95" s="6"/>
+    </row>
+    <row r="96" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A96" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="B96" s="1"/>
+      <c r="C96" s="1">
+        <v>1</v>
+      </c>
+      <c r="D96" s="5"/>
+      <c r="E96" s="4">
         <f>0.001*1000</f>
         <v>1</v>
       </c>
-      <c r="F95" s="6"/>
-    </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A96" s="1" t="s">
-        <v>218</v>
-      </c>
-      <c r="B96" s="1" t="s">
-        <v>219</v>
-      </c>
-      <c r="C96" s="1">
-        <v>1</v>
-      </c>
-      <c r="D96" s="5">
+      <c r="F96" s="6"/>
+    </row>
+    <row r="97" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A97" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="B97" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="C97" s="1">
+        <v>1</v>
+      </c>
+      <c r="D97" s="5">
         <v>232.04</v>
       </c>
-      <c r="E96" s="4">
+      <c r="E97" s="4">
         <f>0.0117*1000</f>
         <v>11.700000000000001</v>
       </c>
-      <c r="F96" s="6">
-        <f>C96*D96/(E96 * 1000)</f>
+      <c r="F97" s="6">
+        <f>C97*D97/(E97 * 1000)</f>
         <v>1.9832478632478629E-2</v>
       </c>
-    </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A97" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="B97" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="C97" s="1">
-        <v>1</v>
-      </c>
-      <c r="D97" s="5">
+      <c r="G97">
+        <v>6.3</v>
+      </c>
+    </row>
+    <row r="98" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A98" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="B98" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="C98" s="1">
+        <v>1</v>
+      </c>
+      <c r="D98" s="5">
         <v>270.02999999999997</v>
       </c>
-      <c r="E97" s="4">
+      <c r="E98" s="4">
         <f>0.0075*1000</f>
         <v>7.5</v>
       </c>
-      <c r="F97" s="6">
-        <f>C97*D97/(E97 * 1000)</f>
+      <c r="F98" s="6">
+        <f>C98*D98/(E98 * 1000)</f>
         <v>3.6003999999999994E-2</v>
       </c>
-    </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A98" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="B98" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="C98" s="1">
-        <v>1</v>
-      </c>
-      <c r="D98" s="5">
+      <c r="G98">
+        <v>33.409999999999997</v>
+      </c>
+    </row>
+    <row r="99" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A99" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="B99" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="C99" s="1">
+        <v>1</v>
+      </c>
+      <c r="D99" s="5">
         <v>60.1</v>
       </c>
-      <c r="E98" s="4">
+      <c r="E99" s="4">
         <f>0.000791*1000</f>
         <v>0.79100000000000004</v>
       </c>
-      <c r="F98" s="6">
-        <f>C98*D98/(E98 * 1000)</f>
+      <c r="F99" s="6">
+        <f>C99*D99/(E99 * 1000)</f>
         <v>7.5979772439949439E-2</v>
       </c>
-    </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A99" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="B99" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="C99" s="1">
-        <v>1</v>
-      </c>
-      <c r="D99" s="5">
-        <f>SUM(($D$47*0.25)+($D$98*0.75))</f>
+      <c r="G99">
+        <v>3206</v>
+      </c>
+    </row>
+    <row r="100" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A100" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="B100" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="C100" s="1">
+        <v>1</v>
+      </c>
+      <c r="D100" s="5">
+        <f>SUM(($D$47*0.25)+($D$99*0.75))</f>
         <v>53.086500000000001</v>
       </c>
-      <c r="E99" s="4">
+      <c r="E100" s="4">
         <f>0.000829*1000</f>
         <v>0.82899999999999996</v>
       </c>
-      <c r="F99" s="6">
-        <f>C99*D99/(E99 * 1000)</f>
+      <c r="F100" s="6">
+        <f>C100*D100/(E100 * 1000)</f>
         <v>6.4036791314837152E-2</v>
       </c>
-    </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A100" s="1" t="s">
-        <v>194</v>
-      </c>
-      <c r="B100" s="1"/>
-      <c r="C100" s="1">
-        <v>1</v>
-      </c>
-      <c r="D100" s="5"/>
-      <c r="E100" s="4">
+      <c r="G100">
+        <f>(G47*0.25)+(G99*0.75)</f>
+        <v>2414.9274999999998</v>
+      </c>
+    </row>
+    <row r="101" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A101" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="B101" s="1"/>
+      <c r="C101" s="1">
+        <v>1</v>
+      </c>
+      <c r="D101" s="5"/>
+      <c r="E101" s="4">
         <f>0.00075*1000</f>
         <v>0.75</v>
       </c>
-      <c r="F100" s="6"/>
-    </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A101" s="1" t="s">
-        <v>195</v>
-      </c>
-      <c r="B101" s="1"/>
-      <c r="C101" s="1">
-        <v>1</v>
-      </c>
-      <c r="D101" s="5"/>
-      <c r="E101" s="4">
+      <c r="F101" s="6"/>
+    </row>
+    <row r="102" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A102" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="B102" s="1" t="s">
+        <v>422</v>
+      </c>
+      <c r="C102" s="1">
+        <v>1</v>
+      </c>
+      <c r="D102" s="5">
+        <v>78.08</v>
+      </c>
+      <c r="E102" s="4">
         <f>0.001005*1000</f>
         <v>1.0050000000000001</v>
       </c>
-      <c r="F101" s="6"/>
-    </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A102" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="B102" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="C102" s="1">
-        <v>1</v>
-      </c>
-      <c r="D102" s="5">
+      <c r="F102" s="6"/>
+    </row>
+    <row r="103" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A103" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="B103" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C103" s="1">
+        <v>1</v>
+      </c>
+      <c r="D103" s="5">
         <v>18.02</v>
       </c>
-      <c r="E102" s="4">
+      <c r="E103" s="4">
         <f>0.001*1000</f>
         <v>1</v>
       </c>
-      <c r="F102" s="6">
-        <f>C102*D102/(E102 * 1000)</f>
+      <c r="F103" s="6">
+        <f>C103*D103/(E103 * 1000)</f>
         <v>1.8020000000000001E-2</v>
       </c>
-    </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A104" s="1" t="s">
+      <c r="G103">
+        <v>40.79</v>
+      </c>
+    </row>
+    <row r="105" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A105" s="1" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="106" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A106" s="24" t="s">
+        <v>95</v>
+      </c>
+      <c r="D106" s="25"/>
+      <c r="E106" s="4">
+        <f t="shared" ref="E106:E141" si="5">F106*1000</f>
+        <v>5</v>
+      </c>
+      <c r="F106" s="6">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="107" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A107" s="24" t="s">
+        <v>103</v>
+      </c>
+      <c r="E107" s="4">
+        <f t="shared" si="5"/>
+        <v>19.3</v>
+      </c>
+      <c r="F107" s="6">
+        <v>1.9300000000000001E-2</v>
+      </c>
+    </row>
+    <row r="108" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A108" s="24" t="s">
+        <v>48</v>
+      </c>
+      <c r="E108" s="4">
+        <f t="shared" si="5"/>
+        <v>54.4</v>
+      </c>
+      <c r="F108" s="6">
+        <v>5.4399999999999997E-2</v>
+      </c>
+    </row>
+    <row r="109" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A109" s="24" t="s">
+        <v>96</v>
+      </c>
+      <c r="E109" s="4">
+        <f t="shared" si="5"/>
+        <v>5</v>
+      </c>
+      <c r="F109" s="6">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="110" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A110" s="24" t="s">
+        <v>105</v>
+      </c>
+      <c r="E110" s="4">
+        <f t="shared" si="5"/>
+        <v>7</v>
+      </c>
+      <c r="F110" s="6">
+        <v>7.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="111" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A111" s="24" t="s">
+        <v>139</v>
+      </c>
+      <c r="E111" s="4">
+        <f t="shared" si="5"/>
+        <v>0.53399999999999992</v>
+      </c>
+      <c r="F111" s="6">
+        <v>5.3399999999999997E-4</v>
+      </c>
+    </row>
+    <row r="112" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A112" s="24" t="s">
         <v>97</v>
       </c>
-    </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A105" s="29" t="s">
-        <v>98</v>
-      </c>
-      <c r="D105" s="30"/>
-      <c r="E105" s="4">
-        <f t="shared" ref="E105:E140" si="4">F105*1000</f>
+      <c r="E112" s="4">
+        <f t="shared" si="5"/>
+        <v>6.0000000000000005E-2</v>
+      </c>
+      <c r="F112" s="6">
+        <v>6.0000000000000002E-5</v>
+      </c>
+    </row>
+    <row r="113" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A113" s="24" t="s">
+        <v>101</v>
+      </c>
+      <c r="E113" s="4">
+        <f t="shared" si="5"/>
+        <v>2.5</v>
+      </c>
+      <c r="F113" s="6">
+        <v>2.5000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="114" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A114" s="24" t="s">
+        <v>58</v>
+      </c>
+      <c r="E114" s="4">
+        <f t="shared" si="5"/>
+        <v>5.0108799999999993</v>
+      </c>
+      <c r="F114" s="6">
+        <v>5.0108799999999997E-3</v>
+      </c>
+    </row>
+    <row r="115" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A115" s="24" t="s">
+        <v>106</v>
+      </c>
+      <c r="E115" s="4">
+        <f t="shared" si="5"/>
+        <v>4.3499999999999996</v>
+      </c>
+      <c r="F115" s="6">
+        <v>4.3499999999999997E-3</v>
+      </c>
+    </row>
+    <row r="116" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A116" s="24" t="s">
+        <v>100</v>
+      </c>
+      <c r="E116" s="4">
+        <f t="shared" si="5"/>
+        <v>0.216</v>
+      </c>
+      <c r="F116" s="6">
+        <v>2.1599999999999999E-4</v>
+      </c>
+    </row>
+    <row r="117" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A117" s="24" t="s">
+        <v>49</v>
+      </c>
+      <c r="E117" s="4">
+        <f t="shared" si="5"/>
+        <v>23.125</v>
+      </c>
+      <c r="F117" s="6">
+        <v>2.3125E-2</v>
+      </c>
+    </row>
+    <row r="118" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A118" s="24" t="s">
+        <v>50</v>
+      </c>
+      <c r="E118" s="4">
+        <f t="shared" si="5"/>
+        <v>5.25</v>
+      </c>
+      <c r="F118" s="6">
+        <v>5.2500000000000003E-3</v>
+      </c>
+    </row>
+    <row r="119" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A119" s="24" t="s">
+        <v>220</v>
+      </c>
+      <c r="E119" s="4">
+        <f t="shared" si="5"/>
+        <v>6.24</v>
+      </c>
+      <c r="F119" s="6">
+        <v>6.2399999999999999E-3</v>
+      </c>
+    </row>
+    <row r="120" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A120" s="24" t="s">
+        <v>51</v>
+      </c>
+      <c r="E120" s="4">
+        <f t="shared" si="5"/>
         <v>5</v>
       </c>
-      <c r="F105" s="6">
+      <c r="F120" s="6">
         <v>5.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A106" s="29" t="s">
-        <v>106</v>
-      </c>
-      <c r="E106" s="4">
-        <f t="shared" si="4"/>
-        <v>19.3</v>
-      </c>
-      <c r="F106" s="6">
-        <v>1.9300000000000001E-2</v>
-      </c>
-    </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A107" s="29" t="s">
-        <v>51</v>
-      </c>
-      <c r="E107" s="4">
-        <f t="shared" si="4"/>
-        <v>54.4</v>
-      </c>
-      <c r="F107" s="6">
-        <v>5.4399999999999997E-2</v>
-      </c>
-    </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A108" s="29" t="s">
-        <v>99</v>
-      </c>
-      <c r="E108" s="4">
-        <f t="shared" si="4"/>
-        <v>5</v>
-      </c>
-      <c r="F108" s="6">
-        <v>5.0000000000000001E-3</v>
-      </c>
-    </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A109" s="29" t="s">
-        <v>108</v>
-      </c>
-      <c r="E109" s="4">
-        <f t="shared" si="4"/>
-        <v>7</v>
-      </c>
-      <c r="F109" s="6">
-        <v>7.0000000000000001E-3</v>
-      </c>
-    </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A110" s="29" t="s">
-        <v>142</v>
-      </c>
-      <c r="E110" s="4">
-        <f t="shared" si="4"/>
-        <v>0.53399999999999992</v>
-      </c>
-      <c r="F110" s="6">
-        <v>5.3399999999999997E-4</v>
-      </c>
-    </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A111" s="29" t="s">
-        <v>100</v>
-      </c>
-      <c r="E111" s="4">
-        <f t="shared" si="4"/>
-        <v>6.0000000000000005E-2</v>
-      </c>
-      <c r="F111" s="6">
-        <v>6.0000000000000002E-5</v>
-      </c>
-    </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A112" s="29" t="s">
-        <v>104</v>
-      </c>
-      <c r="E112" s="4">
-        <f t="shared" si="4"/>
-        <v>2.5</v>
-      </c>
-      <c r="F112" s="6">
-        <v>2.5000000000000001E-3</v>
-      </c>
-    </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A113" s="29" t="s">
-        <v>61</v>
-      </c>
-      <c r="E113" s="4">
-        <f t="shared" si="4"/>
-        <v>5.0108799999999993</v>
-      </c>
-      <c r="F113" s="6">
-        <v>5.0108799999999997E-3</v>
-      </c>
-    </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A114" s="29" t="s">
-        <v>109</v>
-      </c>
-      <c r="E114" s="4">
-        <f t="shared" si="4"/>
-        <v>4.3499999999999996</v>
-      </c>
-      <c r="F114" s="6">
-        <v>4.3499999999999997E-3</v>
-      </c>
-    </row>
-    <row r="115" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A115" s="29" t="s">
-        <v>103</v>
-      </c>
-      <c r="E115" s="4">
-        <f t="shared" si="4"/>
-        <v>0.216</v>
-      </c>
-      <c r="F115" s="6">
-        <v>2.1599999999999999E-4</v>
-      </c>
-    </row>
-    <row r="116" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A116" s="29" t="s">
+    <row r="121" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A121" s="24" t="s">
+        <v>138</v>
+      </c>
+      <c r="E121" s="4">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="F121" s="6">
+        <v>1E-3</v>
+      </c>
+    </row>
+    <row r="122" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A122" s="24" t="s">
         <v>52</v>
       </c>
-      <c r="E116" s="4">
-        <f t="shared" si="4"/>
-        <v>23.125</v>
-      </c>
-      <c r="F116" s="6">
-        <v>2.3125E-2</v>
-      </c>
-    </row>
-    <row r="117" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A117" s="29" t="s">
+      <c r="E122" s="4">
+        <f t="shared" si="5"/>
+        <v>12.5</v>
+      </c>
+      <c r="F122" s="6">
+        <v>1.2500000000000001E-2</v>
+      </c>
+    </row>
+    <row r="123" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A123" s="24" t="s">
+        <v>102</v>
+      </c>
+      <c r="E123" s="4">
+        <f t="shared" si="5"/>
+        <v>2.4</v>
+      </c>
+      <c r="F123" s="6">
+        <v>2.3999999999999998E-3</v>
+      </c>
+    </row>
+    <row r="124" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A124" s="24" t="s">
         <v>53</v>
       </c>
-      <c r="E117" s="4">
-        <f t="shared" si="4"/>
-        <v>5.25</v>
-      </c>
-      <c r="F117" s="6">
-        <v>5.2500000000000003E-3</v>
-      </c>
-    </row>
-    <row r="118" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A118" s="29" t="s">
-        <v>224</v>
-      </c>
-      <c r="E118" s="4">
-        <f t="shared" si="4"/>
-        <v>6.24</v>
-      </c>
-      <c r="F118" s="6">
-        <v>6.2399999999999999E-3</v>
-      </c>
-    </row>
-    <row r="119" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A119" s="29" t="s">
+      <c r="E124" s="4">
+        <f t="shared" si="5"/>
+        <v>13.5</v>
+      </c>
+      <c r="F124" s="6">
+        <v>1.35E-2</v>
+      </c>
+    </row>
+    <row r="125" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A125" s="24" t="s">
         <v>54</v>
       </c>
-      <c r="E119" s="4">
-        <f t="shared" si="4"/>
-        <v>5</v>
-      </c>
-      <c r="F119" s="6">
-        <v>5.0000000000000001E-3</v>
-      </c>
-    </row>
-    <row r="120" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A120" s="29" t="s">
-        <v>141</v>
-      </c>
-      <c r="E120" s="4">
-        <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
-      <c r="F120" s="6">
-        <v>1E-3</v>
-      </c>
-    </row>
-    <row r="121" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A121" s="29" t="s">
+      <c r="E125" s="4">
+        <f t="shared" si="5"/>
+        <v>8.6</v>
+      </c>
+      <c r="F125" s="6">
+        <v>8.6E-3</v>
+      </c>
+    </row>
+    <row r="126" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A126" s="24" t="s">
+        <v>161</v>
+      </c>
+      <c r="E126" s="4">
+        <f t="shared" si="5"/>
+        <v>19.099999999999998</v>
+      </c>
+      <c r="F126" s="6">
+        <v>1.9099999999999999E-2</v>
+      </c>
+    </row>
+    <row r="127" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A127" s="24" t="s">
+        <v>162</v>
+      </c>
+      <c r="E127" s="4">
+        <f t="shared" si="5"/>
+        <v>10.97</v>
+      </c>
+      <c r="F127" s="6">
+        <v>1.0970000000000001E-2</v>
+      </c>
+    </row>
+    <row r="128" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A128" s="24" t="s">
         <v>55</v>
-      </c>
-      <c r="E121" s="4">
-        <f t="shared" si="4"/>
-        <v>12.5</v>
-      </c>
-      <c r="F121" s="6">
-        <v>1.2500000000000001E-2</v>
-      </c>
-    </row>
-    <row r="122" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A122" s="29" t="s">
-        <v>105</v>
-      </c>
-      <c r="E122" s="4">
-        <f t="shared" si="4"/>
-        <v>2.4</v>
-      </c>
-      <c r="F122" s="6">
-        <v>2.3999999999999998E-3</v>
-      </c>
-    </row>
-    <row r="123" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A123" s="29" t="s">
-        <v>56</v>
-      </c>
-      <c r="E123" s="4">
-        <f t="shared" si="4"/>
-        <v>13.5</v>
-      </c>
-      <c r="F123" s="6">
-        <v>1.35E-2</v>
-      </c>
-    </row>
-    <row r="124" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A124" s="29" t="s">
-        <v>57</v>
-      </c>
-      <c r="E124" s="4">
-        <f t="shared" si="4"/>
-        <v>8.6</v>
-      </c>
-      <c r="F124" s="6">
-        <v>8.6E-3</v>
-      </c>
-    </row>
-    <row r="125" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A125" s="29" t="s">
-        <v>164</v>
-      </c>
-      <c r="E125" s="4">
-        <f t="shared" si="4"/>
-        <v>19.099999999999998</v>
-      </c>
-      <c r="F125" s="6">
-        <v>1.9099999999999999E-2</v>
-      </c>
-    </row>
-    <row r="126" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A126" s="29" t="s">
-        <v>165</v>
-      </c>
-      <c r="E126" s="4">
-        <f t="shared" si="4"/>
-        <v>10.97</v>
-      </c>
-      <c r="F126" s="6">
-        <v>1.0970000000000001E-2</v>
-      </c>
-    </row>
-    <row r="127" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A127" s="29" t="s">
-        <v>58</v>
-      </c>
-      <c r="B127" s="1"/>
-      <c r="C127" s="1"/>
-      <c r="D127" s="3"/>
-      <c r="E127" s="4">
-        <f t="shared" si="4"/>
-        <v>5.7050000000000001</v>
-      </c>
-      <c r="F127" s="6">
-        <v>5.705E-3</v>
-      </c>
-    </row>
-    <row r="128" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A128" s="29" t="s">
-        <v>59</v>
       </c>
       <c r="B128" s="1"/>
       <c r="C128" s="1"/>
       <c r="D128" s="3"/>
       <c r="E128" s="4">
-        <f t="shared" si="4"/>
-        <v>13.5</v>
+        <f t="shared" si="5"/>
+        <v>5.7050000000000001</v>
       </c>
       <c r="F128" s="6">
-        <v>1.35E-2</v>
+        <v>5.705E-3</v>
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A129" s="29" t="s">
-        <v>63</v>
+      <c r="A129" s="24" t="s">
+        <v>56</v>
       </c>
       <c r="B129" s="1"/>
       <c r="C129" s="1"/>
       <c r="D129" s="3"/>
       <c r="E129" s="4">
-        <f t="shared" si="4"/>
-        <v>0.35399999999999998</v>
+        <f t="shared" si="5"/>
+        <v>13.5</v>
       </c>
       <c r="F129" s="6">
-        <v>3.5399999999999999E-4</v>
+        <v>1.35E-2</v>
       </c>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A130" s="29" t="s">
-        <v>101</v>
+      <c r="A130" s="24" t="s">
+        <v>60</v>
       </c>
       <c r="B130" s="1"/>
       <c r="C130" s="1"/>
       <c r="D130" s="3"/>
       <c r="E130" s="4">
-        <f t="shared" si="4"/>
-        <v>2.12805</v>
+        <f t="shared" si="5"/>
+        <v>0.35399999999999998</v>
       </c>
       <c r="F130" s="6">
-        <v>2.1280499999999998E-3</v>
+        <v>3.5399999999999999E-4</v>
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A131" s="29" t="s">
-        <v>111</v>
+      <c r="A131" s="24" t="s">
+        <v>98</v>
       </c>
       <c r="B131" s="1"/>
       <c r="C131" s="1"/>
       <c r="D131" s="3"/>
       <c r="E131" s="4">
-        <f t="shared" si="4"/>
-        <v>1.08</v>
+        <f t="shared" si="5"/>
+        <v>2.12805</v>
       </c>
       <c r="F131" s="6">
-        <v>1.08E-3</v>
+        <v>2.1280499999999998E-3</v>
       </c>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A132" s="29" t="s">
-        <v>102</v>
+      <c r="A132" s="24" t="s">
+        <v>108</v>
       </c>
       <c r="B132" s="1"/>
       <c r="C132" s="1"/>
       <c r="D132" s="3"/>
       <c r="E132" s="4">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
+        <v>1.08</v>
+      </c>
+      <c r="F132" s="6">
+        <v>1.08E-3</v>
+      </c>
+    </row>
+    <row r="133" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A133" s="24" t="s">
+        <v>99</v>
+      </c>
+      <c r="B133" s="1"/>
+      <c r="C133" s="1"/>
+      <c r="D133" s="3"/>
+      <c r="E133" s="4">
+        <f t="shared" si="5"/>
         <v>4.1000000000000005</v>
       </c>
-      <c r="F132" s="6">
+      <c r="F133" s="6">
         <v>4.1000000000000003E-3</v>
       </c>
     </row>
-    <row r="133" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A133" s="29" t="s">
-        <v>46</v>
-      </c>
-      <c r="E133" s="4">
-        <f t="shared" si="4"/>
+    <row r="134" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A134" s="24" t="s">
+        <v>43</v>
+      </c>
+      <c r="E134" s="4">
+        <f t="shared" si="5"/>
         <v>12.5</v>
       </c>
-      <c r="F133" s="6">
+      <c r="F134" s="6">
         <v>1.2500000000000001E-2</v>
       </c>
     </row>
-    <row r="134" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A134" s="29" t="s">
-        <v>65</v>
-      </c>
-      <c r="E134" s="4">
-        <f t="shared" si="4"/>
+    <row r="135" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A135" s="24" t="s">
+        <v>62</v>
+      </c>
+      <c r="E135" s="4">
+        <f t="shared" si="5"/>
         <v>4.5999999999999996</v>
       </c>
-      <c r="F134" s="6">
+      <c r="F135" s="6">
         <v>4.5999999999999999E-3</v>
       </c>
     </row>
-    <row r="135" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A135" s="29" t="s">
-        <v>112</v>
-      </c>
-      <c r="E135" s="4">
-        <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
-      <c r="F135" s="6">
-        <v>1E-3</v>
-      </c>
-    </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A136" s="29" t="s">
-        <v>113</v>
+      <c r="A136" s="24" t="s">
+        <v>109</v>
       </c>
       <c r="E136" s="4">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="F136" s="6">
@@ -4917,50 +5944,62 @@
       </c>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A137" s="29" t="s">
+      <c r="A137" s="24" t="s">
+        <v>110</v>
+      </c>
+      <c r="E137" s="4">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="F137" s="6">
+        <v>1E-3</v>
+      </c>
+    </row>
+    <row r="138" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A138" s="24" t="s">
+        <v>104</v>
+      </c>
+      <c r="E138" s="4">
+        <f t="shared" si="5"/>
+        <v>7.5</v>
+      </c>
+      <c r="F138" s="6">
+        <v>7.4999999999999997E-3</v>
+      </c>
+    </row>
+    <row r="139" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A139" s="24" t="s">
         <v>107</v>
       </c>
-      <c r="E137" s="4">
-        <f t="shared" si="4"/>
-        <v>7.5</v>
-      </c>
-      <c r="F137" s="6">
-        <v>7.4999999999999997E-3</v>
-      </c>
-    </row>
-    <row r="138" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A138" s="29" t="s">
-        <v>110</v>
-      </c>
-      <c r="E138" s="4">
-        <f t="shared" si="4"/>
+      <c r="E139" s="4">
+        <f t="shared" si="5"/>
         <v>4.3499999999999996</v>
       </c>
-      <c r="F138" s="6">
+      <c r="F139" s="6">
         <v>4.3499999999999997E-3</v>
       </c>
     </row>
-    <row r="139" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A139" s="29" t="s">
-        <v>115</v>
-      </c>
-      <c r="E139" s="4">
-        <f t="shared" si="4"/>
+    <row r="140" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A140" s="24" t="s">
+        <v>112</v>
+      </c>
+      <c r="E140" s="4">
+        <f t="shared" si="5"/>
         <v>5</v>
       </c>
-      <c r="F139" s="6">
+      <c r="F140" s="6">
         <v>5.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="140" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A140" s="29" t="s">
-        <v>60</v>
-      </c>
-      <c r="E140" s="4">
-        <f t="shared" si="4"/>
+    <row r="141" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A141" s="24" t="s">
+        <v>57</v>
+      </c>
+      <c r="E141" s="4">
+        <f t="shared" si="5"/>
         <v>5</v>
       </c>
-      <c r="F140" s="6">
+      <c r="F141" s="6">
         <v>5.0000000000000001E-3</v>
       </c>
     </row>
@@ -4968,4 +6007,1985 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:L124"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="8.25" customWidth="1"/>
+    <col min="2" max="2" width="13.375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" ht="20.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="40" t="s">
+        <v>425</v>
+      </c>
+      <c r="B1" s="40"/>
+      <c r="C1" s="40"/>
+      <c r="D1" s="40"/>
+      <c r="E1" s="40"/>
+      <c r="F1" s="40"/>
+      <c r="G1" s="40"/>
+    </row>
+    <row r="2" spans="1:12" ht="16.5" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>426</v>
+      </c>
+      <c r="D2" t="s">
+        <v>387</v>
+      </c>
+      <c r="F2" t="s">
+        <v>389</v>
+      </c>
+      <c r="G2" t="s">
+        <v>427</v>
+      </c>
+      <c r="J2" t="s">
+        <v>389</v>
+      </c>
+      <c r="K2" t="s">
+        <v>427</v>
+      </c>
+      <c r="L2" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A3" s="23" t="s">
+        <v>385</v>
+      </c>
+      <c r="B3" s="23" t="s">
+        <v>386</v>
+      </c>
+      <c r="C3" s="23" t="s">
+        <v>418</v>
+      </c>
+      <c r="F3" s="23" t="s">
+        <v>392</v>
+      </c>
+      <c r="G3" s="23" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="14" t="s">
+        <v>384</v>
+      </c>
+      <c r="B4" s="17" t="str">
+        <f>IFERROR(VLOOKUP(A4,$A$25:$D$124,2,FALSE),"-")</f>
+        <v>Hydrogen</v>
+      </c>
+      <c r="C4" s="17" t="str">
+        <f t="shared" ref="C4:C15" si="0">IF(L4="Y","Yes","-")</f>
+        <v>Yes</v>
+      </c>
+      <c r="D4" s="14"/>
+      <c r="E4" s="15">
+        <f t="shared" ref="E4:E15" si="1">D4*$D$18</f>
+        <v>0</v>
+      </c>
+      <c r="F4" s="15">
+        <f t="shared" ref="F4:F15" si="2">IFERROR(E4*J4,0)</f>
+        <v>0</v>
+      </c>
+      <c r="G4" s="15">
+        <f t="shared" ref="G4:G15" si="3">IFERROR(E4*K4,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J4" s="17">
+        <f t="shared" ref="J4:J15" si="4">IFERROR(VLOOKUP(A4,$A$25:$D$124,3,FALSE),"-")</f>
+        <v>13.59</v>
+      </c>
+      <c r="K4" s="17">
+        <f t="shared" ref="K4:K15" si="5">IFERROR(VLOOKUP(A4,$A$25:$D$124,4,FALSE),"-")</f>
+        <v>1.008</v>
+      </c>
+      <c r="L4" s="17" t="str">
+        <f t="shared" ref="L4:L15" si="6">IFERROR(VLOOKUP(A4,$A$25:$E$124,5,FALSE),"-")</f>
+        <v>Y</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" ht="17.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="14"/>
+      <c r="B5" s="17" t="str">
+        <f t="shared" ref="B5:B15" si="7">IFERROR(VLOOKUP(A5,$A$25:$D$124,2,FALSE),"-")</f>
+        <v>-</v>
+      </c>
+      <c r="C5" s="17" t="str">
+        <f t="shared" si="0"/>
+        <v>-</v>
+      </c>
+      <c r="D5" s="14"/>
+      <c r="E5" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F5" s="15">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G5" s="15">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="J5" s="17" t="str">
+        <f t="shared" si="4"/>
+        <v>-</v>
+      </c>
+      <c r="K5" s="17" t="str">
+        <f t="shared" si="5"/>
+        <v>-</v>
+      </c>
+      <c r="L5" s="17" t="str">
+        <f t="shared" si="6"/>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" ht="17.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="14"/>
+      <c r="B6" s="17" t="str">
+        <f t="shared" si="7"/>
+        <v>-</v>
+      </c>
+      <c r="C6" s="17" t="str">
+        <f t="shared" si="0"/>
+        <v>-</v>
+      </c>
+      <c r="D6" s="14"/>
+      <c r="E6" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F6" s="15">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G6" s="15">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="J6" s="17" t="str">
+        <f t="shared" si="4"/>
+        <v>-</v>
+      </c>
+      <c r="K6" s="17" t="str">
+        <f t="shared" si="5"/>
+        <v>-</v>
+      </c>
+      <c r="L6" s="17" t="str">
+        <f t="shared" si="6"/>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" ht="17.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="14"/>
+      <c r="B7" s="17" t="str">
+        <f t="shared" si="7"/>
+        <v>-</v>
+      </c>
+      <c r="C7" s="17" t="str">
+        <f t="shared" si="0"/>
+        <v>-</v>
+      </c>
+      <c r="D7" s="14"/>
+      <c r="E7" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F7" s="15">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G7" s="15">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="J7" s="17" t="str">
+        <f t="shared" si="4"/>
+        <v>-</v>
+      </c>
+      <c r="K7" s="17" t="str">
+        <f t="shared" si="5"/>
+        <v>-</v>
+      </c>
+      <c r="L7" s="17" t="str">
+        <f t="shared" si="6"/>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" ht="17.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="14"/>
+      <c r="B8" s="17" t="str">
+        <f t="shared" si="7"/>
+        <v>-</v>
+      </c>
+      <c r="C8" s="17" t="str">
+        <f t="shared" si="0"/>
+        <v>-</v>
+      </c>
+      <c r="D8" s="14"/>
+      <c r="E8" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F8" s="15">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G8" s="15">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="J8" s="17" t="str">
+        <f t="shared" si="4"/>
+        <v>-</v>
+      </c>
+      <c r="K8" s="17" t="str">
+        <f t="shared" si="5"/>
+        <v>-</v>
+      </c>
+      <c r="L8" s="17" t="str">
+        <f t="shared" si="6"/>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" ht="17.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="14"/>
+      <c r="B9" s="17" t="str">
+        <f t="shared" si="7"/>
+        <v>-</v>
+      </c>
+      <c r="C9" s="17" t="str">
+        <f t="shared" si="0"/>
+        <v>-</v>
+      </c>
+      <c r="D9" s="14"/>
+      <c r="E9" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F9" s="15">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G9" s="15">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="J9" s="17" t="str">
+        <f t="shared" si="4"/>
+        <v>-</v>
+      </c>
+      <c r="K9" s="17" t="str">
+        <f t="shared" si="5"/>
+        <v>-</v>
+      </c>
+      <c r="L9" s="17" t="str">
+        <f t="shared" si="6"/>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" ht="17.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="14"/>
+      <c r="B10" s="17" t="str">
+        <f t="shared" si="7"/>
+        <v>-</v>
+      </c>
+      <c r="C10" s="17" t="str">
+        <f t="shared" si="0"/>
+        <v>-</v>
+      </c>
+      <c r="D10" s="14"/>
+      <c r="E10" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F10" s="15">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G10" s="15">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="J10" s="17" t="str">
+        <f t="shared" si="4"/>
+        <v>-</v>
+      </c>
+      <c r="K10" s="17" t="str">
+        <f t="shared" si="5"/>
+        <v>-</v>
+      </c>
+      <c r="L10" s="17" t="str">
+        <f t="shared" si="6"/>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" ht="17.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="14"/>
+      <c r="B11" s="17" t="str">
+        <f t="shared" si="7"/>
+        <v>-</v>
+      </c>
+      <c r="C11" s="17" t="str">
+        <f t="shared" si="0"/>
+        <v>-</v>
+      </c>
+      <c r="D11" s="14"/>
+      <c r="E11" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F11" s="15">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G11" s="15">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="J11" s="17" t="str">
+        <f t="shared" si="4"/>
+        <v>-</v>
+      </c>
+      <c r="K11" s="17" t="str">
+        <f t="shared" si="5"/>
+        <v>-</v>
+      </c>
+      <c r="L11" s="17" t="str">
+        <f t="shared" si="6"/>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" ht="17.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="14"/>
+      <c r="B12" s="17" t="str">
+        <f t="shared" si="7"/>
+        <v>-</v>
+      </c>
+      <c r="C12" s="17" t="str">
+        <f t="shared" si="0"/>
+        <v>-</v>
+      </c>
+      <c r="D12" s="14"/>
+      <c r="E12" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F12" s="15">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G12" s="15">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="J12" s="17" t="str">
+        <f t="shared" si="4"/>
+        <v>-</v>
+      </c>
+      <c r="K12" s="17" t="str">
+        <f t="shared" si="5"/>
+        <v>-</v>
+      </c>
+      <c r="L12" s="17" t="str">
+        <f t="shared" si="6"/>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" ht="17.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="14"/>
+      <c r="B13" s="17" t="str">
+        <f t="shared" si="7"/>
+        <v>-</v>
+      </c>
+      <c r="C13" s="17" t="str">
+        <f t="shared" si="0"/>
+        <v>-</v>
+      </c>
+      <c r="D13" s="14"/>
+      <c r="E13" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F13" s="15">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G13" s="15">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="J13" s="17" t="str">
+        <f t="shared" si="4"/>
+        <v>-</v>
+      </c>
+      <c r="K13" s="17" t="str">
+        <f t="shared" si="5"/>
+        <v>-</v>
+      </c>
+      <c r="L13" s="17" t="str">
+        <f t="shared" si="6"/>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" ht="17.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="14"/>
+      <c r="B14" s="17" t="str">
+        <f t="shared" si="7"/>
+        <v>-</v>
+      </c>
+      <c r="C14" s="17" t="str">
+        <f t="shared" si="0"/>
+        <v>-</v>
+      </c>
+      <c r="D14" s="14"/>
+      <c r="E14" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F14" s="15">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G14" s="15">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="J14" s="17" t="str">
+        <f t="shared" si="4"/>
+        <v>-</v>
+      </c>
+      <c r="K14" s="17" t="str">
+        <f t="shared" si="5"/>
+        <v>-</v>
+      </c>
+      <c r="L14" s="17" t="str">
+        <f t="shared" si="6"/>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" ht="17.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="14"/>
+      <c r="B15" s="17" t="str">
+        <f t="shared" si="7"/>
+        <v>-</v>
+      </c>
+      <c r="C15" s="17" t="str">
+        <f t="shared" si="0"/>
+        <v>-</v>
+      </c>
+      <c r="D15" s="14"/>
+      <c r="E15" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F15" s="15">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G15" s="15">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="J15" s="17" t="str">
+        <f t="shared" si="4"/>
+        <v>-</v>
+      </c>
+      <c r="K15" s="17" t="str">
+        <f t="shared" si="5"/>
+        <v>-</v>
+      </c>
+      <c r="L15" s="17" t="str">
+        <f t="shared" si="6"/>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" ht="16.5" thickTop="1" x14ac:dyDescent="0.25"/>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="D17" t="s">
+        <v>393</v>
+      </c>
+      <c r="F17" s="23" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="D18" s="14">
+        <v>1</v>
+      </c>
+      <c r="F18" s="39">
+        <f>SUM(F4:F15)</f>
+        <v>0</v>
+      </c>
+      <c r="G18" s="15">
+        <f>SUM(G4:G15)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="F19" s="43">
+        <f>F18/20</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="L21" s="1"/>
+    </row>
+    <row r="22" spans="1:12" ht="20.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="40" t="s">
+        <v>421</v>
+      </c>
+      <c r="B22" s="40"/>
+      <c r="C22" s="40"/>
+      <c r="D22" s="40"/>
+      <c r="E22" s="40"/>
+      <c r="H22" s="46"/>
+    </row>
+    <row r="23" spans="1:12" ht="16.5" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="C23" t="s">
+        <v>389</v>
+      </c>
+      <c r="D23" t="s">
+        <v>390</v>
+      </c>
+      <c r="E23" t="s">
+        <v>418</v>
+      </c>
+      <c r="J23" s="1"/>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C24" t="s">
+        <v>250</v>
+      </c>
+      <c r="D24" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>384</v>
+      </c>
+      <c r="B25" t="s">
+        <v>59</v>
+      </c>
+      <c r="C25">
+        <v>13.59</v>
+      </c>
+      <c r="D25">
+        <v>1.008</v>
+      </c>
+      <c r="E25" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>383</v>
+      </c>
+      <c r="B26" t="s">
+        <v>172</v>
+      </c>
+      <c r="C26">
+        <v>24.58</v>
+      </c>
+      <c r="D26">
+        <v>4.0026000000000002</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>134</v>
+      </c>
+      <c r="B27" t="s">
+        <v>133</v>
+      </c>
+      <c r="C27">
+        <v>5.39</v>
+      </c>
+      <c r="D27">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>201</v>
+      </c>
+      <c r="B28" t="s">
+        <v>200</v>
+      </c>
+      <c r="C28">
+        <v>9.32</v>
+      </c>
+      <c r="D28">
+        <v>9.0121000000000002</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>205</v>
+      </c>
+      <c r="B29" t="s">
+        <v>204</v>
+      </c>
+      <c r="C29">
+        <v>8.2899999999999991</v>
+      </c>
+      <c r="D29">
+        <v>10.81</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>40</v>
+      </c>
+      <c r="B30" t="s">
+        <v>39</v>
+      </c>
+      <c r="C30">
+        <v>11.26</v>
+      </c>
+      <c r="D30">
+        <v>12.010999999999999</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>382</v>
+      </c>
+      <c r="B31" t="s">
+        <v>45</v>
+      </c>
+      <c r="C31">
+        <v>14.53</v>
+      </c>
+      <c r="D31">
+        <v>14.007</v>
+      </c>
+      <c r="E31" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>241</v>
+      </c>
+      <c r="B32" t="s">
+        <v>47</v>
+      </c>
+      <c r="C32">
+        <v>13.61</v>
+      </c>
+      <c r="D32">
+        <v>15.999000000000001</v>
+      </c>
+      <c r="E32" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>242</v>
+      </c>
+      <c r="B33" t="s">
+        <v>166</v>
+      </c>
+      <c r="C33">
+        <v>17.420000000000002</v>
+      </c>
+      <c r="D33">
+        <v>18.998000000000001</v>
+      </c>
+      <c r="E33" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>381</v>
+      </c>
+      <c r="B34" t="s">
+        <v>243</v>
+      </c>
+      <c r="C34">
+        <v>21.56</v>
+      </c>
+      <c r="D34">
+        <v>20.18</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>380</v>
+      </c>
+      <c r="B35" t="s">
+        <v>244</v>
+      </c>
+      <c r="C35">
+        <v>5.13</v>
+      </c>
+      <c r="D35">
+        <v>22.989699999999999</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>379</v>
+      </c>
+      <c r="B36" t="s">
+        <v>245</v>
+      </c>
+      <c r="C36">
+        <v>7.64</v>
+      </c>
+      <c r="D36">
+        <v>24.305</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>42</v>
+      </c>
+      <c r="B37" t="s">
+        <v>41</v>
+      </c>
+      <c r="C37">
+        <v>5.98</v>
+      </c>
+      <c r="D37">
+        <v>26.9815</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>164</v>
+      </c>
+      <c r="B38" t="s">
+        <v>163</v>
+      </c>
+      <c r="C38">
+        <v>8.15</v>
+      </c>
+      <c r="D38">
+        <v>28.085000000000001</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>37</v>
+      </c>
+      <c r="B39" t="s">
+        <v>36</v>
+      </c>
+      <c r="C39">
+        <v>10.48</v>
+      </c>
+      <c r="D39">
+        <v>90.973699999999994</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>378</v>
+      </c>
+      <c r="B40" t="s">
+        <v>246</v>
+      </c>
+      <c r="C40">
+        <v>10.36</v>
+      </c>
+      <c r="D40">
+        <v>32.07</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>377</v>
+      </c>
+      <c r="B41" t="s">
+        <v>165</v>
+      </c>
+      <c r="C41">
+        <v>12.96</v>
+      </c>
+      <c r="D41">
+        <v>18.9984</v>
+      </c>
+      <c r="E41" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>11</v>
+      </c>
+      <c r="B42" t="s">
+        <v>247</v>
+      </c>
+      <c r="C42">
+        <v>15.75</v>
+      </c>
+      <c r="D42">
+        <v>39.9</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>361</v>
+      </c>
+      <c r="B43" t="s">
+        <v>248</v>
+      </c>
+      <c r="C43">
+        <v>4.34</v>
+      </c>
+      <c r="D43">
+        <v>39.098300000000002</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>240</v>
+      </c>
+      <c r="B44" t="s">
+        <v>251</v>
+      </c>
+      <c r="C44">
+        <v>6.11</v>
+      </c>
+      <c r="D44">
+        <v>40.08</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>376</v>
+      </c>
+      <c r="B45" t="s">
+        <v>253</v>
+      </c>
+      <c r="C45">
+        <v>6.56</v>
+      </c>
+      <c r="D45">
+        <v>44.9559</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>375</v>
+      </c>
+      <c r="B46" t="s">
+        <v>252</v>
+      </c>
+      <c r="C46">
+        <v>6.82</v>
+      </c>
+      <c r="D46">
+        <v>47.866999999999997</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>374</v>
+      </c>
+      <c r="B47" t="s">
+        <v>254</v>
+      </c>
+      <c r="C47">
+        <v>6.74</v>
+      </c>
+      <c r="D47">
+        <v>50.941499999999998</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>373</v>
+      </c>
+      <c r="B48" t="s">
+        <v>255</v>
+      </c>
+      <c r="C48">
+        <v>6.76</v>
+      </c>
+      <c r="D48">
+        <v>51.996000000000002</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>372</v>
+      </c>
+      <c r="B49" t="s">
+        <v>256</v>
+      </c>
+      <c r="C49">
+        <v>7.43</v>
+      </c>
+      <c r="D49">
+        <v>54.938000000000002</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>239</v>
+      </c>
+      <c r="B50" t="s">
+        <v>249</v>
+      </c>
+      <c r="C50">
+        <v>7.9</v>
+      </c>
+      <c r="D50">
+        <v>55.84</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>371</v>
+      </c>
+      <c r="B51" t="s">
+        <v>257</v>
+      </c>
+      <c r="C51">
+        <v>7.88</v>
+      </c>
+      <c r="D51">
+        <v>58.933199999999999</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>370</v>
+      </c>
+      <c r="B52" t="s">
+        <v>369</v>
+      </c>
+      <c r="C52">
+        <v>7.63</v>
+      </c>
+      <c r="D52">
+        <v>58.692999999999998</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>368</v>
+      </c>
+      <c r="B53" t="s">
+        <v>258</v>
+      </c>
+      <c r="C53">
+        <v>7.72</v>
+      </c>
+      <c r="D53">
+        <v>63.55</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>367</v>
+      </c>
+      <c r="B54" t="s">
+        <v>259</v>
+      </c>
+      <c r="C54">
+        <v>9.39</v>
+      </c>
+      <c r="D54">
+        <v>65.400000000000006</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>366</v>
+      </c>
+      <c r="B55" t="s">
+        <v>260</v>
+      </c>
+      <c r="C55">
+        <v>5.99</v>
+      </c>
+      <c r="D55">
+        <v>69.722999999999999</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>365</v>
+      </c>
+      <c r="B56" t="s">
+        <v>261</v>
+      </c>
+      <c r="C56">
+        <v>7.89</v>
+      </c>
+      <c r="D56">
+        <v>72.63</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>364</v>
+      </c>
+      <c r="B57" t="s">
+        <v>262</v>
+      </c>
+      <c r="C57">
+        <v>9.7799999999999994</v>
+      </c>
+      <c r="D57">
+        <v>74.921599999999998</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>363</v>
+      </c>
+      <c r="B58" t="s">
+        <v>263</v>
+      </c>
+      <c r="C58">
+        <v>9.75</v>
+      </c>
+      <c r="D58">
+        <v>78.97</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>362</v>
+      </c>
+      <c r="B59" t="s">
+        <v>264</v>
+      </c>
+      <c r="C59">
+        <v>11.81</v>
+      </c>
+      <c r="D59">
+        <v>79.900000000000006</v>
+      </c>
+      <c r="E59" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>361</v>
+      </c>
+      <c r="B60" t="s">
+        <v>265</v>
+      </c>
+      <c r="C60">
+        <v>13.99</v>
+      </c>
+      <c r="D60">
+        <v>83.8</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>360</v>
+      </c>
+      <c r="B61" t="s">
+        <v>266</v>
+      </c>
+      <c r="C61">
+        <v>4.17</v>
+      </c>
+      <c r="D61">
+        <v>85.468000000000004</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>359</v>
+      </c>
+      <c r="B62" t="s">
+        <v>267</v>
+      </c>
+      <c r="C62">
+        <v>5.69</v>
+      </c>
+      <c r="D62">
+        <v>87.62</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>331</v>
+      </c>
+      <c r="B63" t="s">
+        <v>268</v>
+      </c>
+      <c r="C63">
+        <v>6.21</v>
+      </c>
+      <c r="D63">
+        <v>89.905799999999999</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>358</v>
+      </c>
+      <c r="B64" t="s">
+        <v>269</v>
+      </c>
+      <c r="C64">
+        <v>6.63</v>
+      </c>
+      <c r="D64">
+        <v>91.22</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>357</v>
+      </c>
+      <c r="B65" t="s">
+        <v>270</v>
+      </c>
+      <c r="C65">
+        <v>6.75</v>
+      </c>
+      <c r="D65">
+        <v>92.906400000000005</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>356</v>
+      </c>
+      <c r="B66" t="s">
+        <v>271</v>
+      </c>
+      <c r="C66">
+        <v>7.09</v>
+      </c>
+      <c r="D66">
+        <v>95.95</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>355</v>
+      </c>
+      <c r="B67" t="s">
+        <v>272</v>
+      </c>
+      <c r="C67">
+        <v>7.28</v>
+      </c>
+      <c r="D67">
+        <v>96.906400000000005</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>354</v>
+      </c>
+      <c r="B68" t="s">
+        <v>273</v>
+      </c>
+      <c r="C68">
+        <v>7.36</v>
+      </c>
+      <c r="D68">
+        <v>101.1</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>353</v>
+      </c>
+      <c r="B69" t="s">
+        <v>274</v>
+      </c>
+      <c r="C69">
+        <v>7.45</v>
+      </c>
+      <c r="D69">
+        <v>102.9055</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>352</v>
+      </c>
+      <c r="B70" t="s">
+        <v>275</v>
+      </c>
+      <c r="C70">
+        <v>8.33</v>
+      </c>
+      <c r="D70">
+        <v>106.42</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>351</v>
+      </c>
+      <c r="B71" t="s">
+        <v>276</v>
+      </c>
+      <c r="C71">
+        <v>7.57</v>
+      </c>
+      <c r="D71">
+        <v>107.86799999999999</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>350</v>
+      </c>
+      <c r="B72" t="s">
+        <v>277</v>
+      </c>
+      <c r="C72">
+        <v>8.99</v>
+      </c>
+      <c r="D72">
+        <v>112.41</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>349</v>
+      </c>
+      <c r="B73" t="s">
+        <v>278</v>
+      </c>
+      <c r="C73">
+        <v>5.78</v>
+      </c>
+      <c r="D73">
+        <v>114.818</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>348</v>
+      </c>
+      <c r="B74" t="s">
+        <v>279</v>
+      </c>
+      <c r="C74">
+        <v>7.34</v>
+      </c>
+      <c r="D74">
+        <v>118.71</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>347</v>
+      </c>
+      <c r="B75" t="s">
+        <v>280</v>
+      </c>
+      <c r="C75">
+        <v>8.6</v>
+      </c>
+      <c r="D75">
+        <v>121.76</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>346</v>
+      </c>
+      <c r="B76" t="s">
+        <v>281</v>
+      </c>
+      <c r="C76">
+        <v>9</v>
+      </c>
+      <c r="D76">
+        <v>127.6</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>420</v>
+      </c>
+      <c r="B77" t="s">
+        <v>282</v>
+      </c>
+      <c r="C77">
+        <v>10.45</v>
+      </c>
+      <c r="D77">
+        <v>126.9045</v>
+      </c>
+      <c r="E77" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>13</v>
+      </c>
+      <c r="B78" t="s">
+        <v>283</v>
+      </c>
+      <c r="C78">
+        <v>12.12</v>
+      </c>
+      <c r="D78">
+        <v>131.29</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>217</v>
+      </c>
+      <c r="B79" t="s">
+        <v>284</v>
+      </c>
+      <c r="C79">
+        <v>3.89</v>
+      </c>
+      <c r="D79">
+        <v>132.90549999999999</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>345</v>
+      </c>
+      <c r="B80" t="s">
+        <v>285</v>
+      </c>
+      <c r="C80">
+        <v>5.21</v>
+      </c>
+      <c r="D80">
+        <v>137.33000000000001</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>344</v>
+      </c>
+      <c r="B81" t="s">
+        <v>286</v>
+      </c>
+      <c r="C81">
+        <v>5.57</v>
+      </c>
+      <c r="D81">
+        <v>138.90549999999999</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>343</v>
+      </c>
+      <c r="B82" t="s">
+        <v>287</v>
+      </c>
+      <c r="C82">
+        <v>5.53</v>
+      </c>
+      <c r="D82">
+        <v>140.11600000000001</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>342</v>
+      </c>
+      <c r="B83" t="s">
+        <v>288</v>
+      </c>
+      <c r="C83">
+        <v>5.47</v>
+      </c>
+      <c r="D83">
+        <v>140.90770000000001</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>341</v>
+      </c>
+      <c r="B84" t="s">
+        <v>289</v>
+      </c>
+      <c r="C84">
+        <v>5.52</v>
+      </c>
+      <c r="D84">
+        <v>144.24</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>340</v>
+      </c>
+      <c r="B85" t="s">
+        <v>290</v>
+      </c>
+      <c r="C85">
+        <v>5.58</v>
+      </c>
+      <c r="D85">
+        <v>144.9128</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>339</v>
+      </c>
+      <c r="B86" t="s">
+        <v>291</v>
+      </c>
+      <c r="C86">
+        <v>5.64</v>
+      </c>
+      <c r="D86">
+        <v>150.4</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>338</v>
+      </c>
+      <c r="B87" t="s">
+        <v>292</v>
+      </c>
+      <c r="C87">
+        <v>5.67</v>
+      </c>
+      <c r="D87">
+        <v>151.964</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>337</v>
+      </c>
+      <c r="B88" t="s">
+        <v>293</v>
+      </c>
+      <c r="C88">
+        <v>6.15</v>
+      </c>
+      <c r="D88">
+        <v>157.25</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>336</v>
+      </c>
+      <c r="B89" t="s">
+        <v>294</v>
+      </c>
+      <c r="C89">
+        <v>5.86</v>
+      </c>
+      <c r="D89">
+        <v>158.9254</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>335</v>
+      </c>
+      <c r="B90" t="s">
+        <v>295</v>
+      </c>
+      <c r="C90">
+        <v>5.93</v>
+      </c>
+      <c r="D90">
+        <v>162.5</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>334</v>
+      </c>
+      <c r="B91" t="s">
+        <v>296</v>
+      </c>
+      <c r="C91">
+        <v>6.02</v>
+      </c>
+      <c r="D91">
+        <v>164.93029999999999</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>333</v>
+      </c>
+      <c r="B92" t="s">
+        <v>297</v>
+      </c>
+      <c r="C92">
+        <v>6.1</v>
+      </c>
+      <c r="D92">
+        <v>167.26</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>332</v>
+      </c>
+      <c r="B93" t="s">
+        <v>298</v>
+      </c>
+      <c r="C93">
+        <v>6.18</v>
+      </c>
+      <c r="D93">
+        <v>168.9342</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>331</v>
+      </c>
+      <c r="B94" t="s">
+        <v>299</v>
+      </c>
+      <c r="C94">
+        <v>6.25</v>
+      </c>
+      <c r="D94">
+        <v>173.05</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>330</v>
+      </c>
+      <c r="B95" t="s">
+        <v>300</v>
+      </c>
+      <c r="C95">
+        <v>5.42</v>
+      </c>
+      <c r="D95">
+        <v>174.9667</v>
+      </c>
+    </row>
+    <row r="96" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>329</v>
+      </c>
+      <c r="B96" t="s">
+        <v>301</v>
+      </c>
+      <c r="C96">
+        <v>6.82</v>
+      </c>
+      <c r="D96">
+        <v>178.49</v>
+      </c>
+    </row>
+    <row r="97" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>328</v>
+      </c>
+      <c r="B97" t="s">
+        <v>302</v>
+      </c>
+      <c r="C97">
+        <v>7.54</v>
+      </c>
+      <c r="D97">
+        <v>180.9479</v>
+      </c>
+    </row>
+    <row r="98" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>327</v>
+      </c>
+      <c r="B98" t="s">
+        <v>303</v>
+      </c>
+      <c r="C98">
+        <v>7.86</v>
+      </c>
+      <c r="D98">
+        <v>183.84</v>
+      </c>
+    </row>
+    <row r="99" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>326</v>
+      </c>
+      <c r="B99" t="s">
+        <v>304</v>
+      </c>
+      <c r="C99">
+        <v>7.83</v>
+      </c>
+      <c r="D99">
+        <v>186.20699999999999</v>
+      </c>
+    </row>
+    <row r="100" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>325</v>
+      </c>
+      <c r="B100" t="s">
+        <v>305</v>
+      </c>
+      <c r="C100">
+        <v>8.43</v>
+      </c>
+      <c r="D100">
+        <v>190.2</v>
+      </c>
+    </row>
+    <row r="101" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>324</v>
+      </c>
+      <c r="B101" t="s">
+        <v>306</v>
+      </c>
+      <c r="C101">
+        <v>8.9600000000000009</v>
+      </c>
+      <c r="D101">
+        <v>192.22</v>
+      </c>
+    </row>
+    <row r="102" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>323</v>
+      </c>
+      <c r="B102" t="s">
+        <v>307</v>
+      </c>
+      <c r="C102">
+        <v>8.9499999999999993</v>
+      </c>
+      <c r="D102">
+        <v>195.08</v>
+      </c>
+    </row>
+    <row r="103" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>322</v>
+      </c>
+      <c r="B103" t="s">
+        <v>308</v>
+      </c>
+      <c r="C103">
+        <v>9.2200000000000006</v>
+      </c>
+      <c r="D103">
+        <v>196.9666</v>
+      </c>
+    </row>
+    <row r="104" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>321</v>
+      </c>
+      <c r="B104" t="s">
+        <v>309</v>
+      </c>
+      <c r="C104">
+        <v>10.43</v>
+      </c>
+      <c r="D104">
+        <v>200.59</v>
+      </c>
+    </row>
+    <row r="105" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>320</v>
+      </c>
+      <c r="B105" t="s">
+        <v>310</v>
+      </c>
+      <c r="C105">
+        <v>6.1</v>
+      </c>
+      <c r="D105">
+        <v>204.38300000000001</v>
+      </c>
+    </row>
+    <row r="106" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>61</v>
+      </c>
+      <c r="B106" t="s">
+        <v>311</v>
+      </c>
+      <c r="C106">
+        <v>7.41</v>
+      </c>
+      <c r="D106">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="107" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
+        <v>319</v>
+      </c>
+      <c r="B107" t="s">
+        <v>312</v>
+      </c>
+      <c r="C107">
+        <v>7.28</v>
+      </c>
+      <c r="D107">
+        <v>208.9804</v>
+      </c>
+    </row>
+    <row r="108" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
+        <v>318</v>
+      </c>
+      <c r="B108" t="s">
+        <v>313</v>
+      </c>
+      <c r="C108">
+        <v>8.41</v>
+      </c>
+      <c r="D108">
+        <v>208.98240000000001</v>
+      </c>
+    </row>
+    <row r="109" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
+        <v>317</v>
+      </c>
+      <c r="B109" t="s">
+        <v>314</v>
+      </c>
+      <c r="C109">
+        <v>9.31</v>
+      </c>
+      <c r="D109">
+        <v>209.9872</v>
+      </c>
+    </row>
+    <row r="110" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
+        <v>395</v>
+      </c>
+      <c r="B110" t="s">
+        <v>315</v>
+      </c>
+      <c r="C110">
+        <v>10.74</v>
+      </c>
+      <c r="D110">
+        <v>222.01759999999999</v>
+      </c>
+    </row>
+    <row r="111" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
+        <v>396</v>
+      </c>
+      <c r="B111" t="s">
+        <v>406</v>
+      </c>
+      <c r="C111">
+        <v>4.07</v>
+      </c>
+      <c r="D111">
+        <v>223.0197</v>
+      </c>
+    </row>
+    <row r="112" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
+        <v>316</v>
+      </c>
+      <c r="B112" t="s">
+        <v>407</v>
+      </c>
+      <c r="C112">
+        <v>5.27</v>
+      </c>
+      <c r="D112">
+        <v>226.02539999999999</v>
+      </c>
+    </row>
+    <row r="113" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
+        <v>397</v>
+      </c>
+      <c r="B113" t="s">
+        <v>408</v>
+      </c>
+      <c r="C113">
+        <v>5.17</v>
+      </c>
+      <c r="D113">
+        <v>227.02780000000001</v>
+      </c>
+    </row>
+    <row r="114" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A114" t="s">
+        <v>215</v>
+      </c>
+      <c r="B114" t="s">
+        <v>214</v>
+      </c>
+      <c r="C114">
+        <v>6.3</v>
+      </c>
+      <c r="D114">
+        <v>232.03800000000001</v>
+      </c>
+    </row>
+    <row r="115" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A115" t="s">
+        <v>398</v>
+      </c>
+      <c r="B115" t="s">
+        <v>409</v>
+      </c>
+      <c r="C115">
+        <v>5.89</v>
+      </c>
+      <c r="D115">
+        <v>231.0359</v>
+      </c>
+    </row>
+    <row r="116" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A116" t="s">
+        <v>130</v>
+      </c>
+      <c r="B116" t="s">
+        <v>410</v>
+      </c>
+      <c r="C116">
+        <v>6.19</v>
+      </c>
+      <c r="D116">
+        <v>238.02889999999999</v>
+      </c>
+    </row>
+    <row r="117" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A117" t="s">
+        <v>399</v>
+      </c>
+      <c r="B117" t="s">
+        <v>411</v>
+      </c>
+      <c r="C117">
+        <v>6.26</v>
+      </c>
+      <c r="D117">
+        <v>237.04820000000001</v>
+      </c>
+    </row>
+    <row r="118" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A118" t="s">
+        <v>207</v>
+      </c>
+      <c r="B118" t="s">
+        <v>206</v>
+      </c>
+      <c r="C118">
+        <v>6.02</v>
+      </c>
+      <c r="D118">
+        <v>244.0642</v>
+      </c>
+    </row>
+    <row r="119" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A119" t="s">
+        <v>400</v>
+      </c>
+      <c r="B119" t="s">
+        <v>412</v>
+      </c>
+      <c r="C119">
+        <v>5.97</v>
+      </c>
+      <c r="D119">
+        <v>243.06139999999999</v>
+      </c>
+    </row>
+    <row r="120" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A120" t="s">
+        <v>401</v>
+      </c>
+      <c r="B120" t="s">
+        <v>413</v>
+      </c>
+      <c r="C120">
+        <v>5.99</v>
+      </c>
+      <c r="D120">
+        <v>247.07040000000001</v>
+      </c>
+    </row>
+    <row r="121" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A121" t="s">
+        <v>402</v>
+      </c>
+      <c r="B121" t="s">
+        <v>414</v>
+      </c>
+      <c r="C121">
+        <v>6.19</v>
+      </c>
+      <c r="D121">
+        <v>247.0703</v>
+      </c>
+    </row>
+    <row r="122" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A122" t="s">
+        <v>403</v>
+      </c>
+      <c r="B122" t="s">
+        <v>415</v>
+      </c>
+      <c r="C122">
+        <v>6.28</v>
+      </c>
+      <c r="D122">
+        <v>251.08</v>
+      </c>
+    </row>
+    <row r="123" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A123" t="s">
+        <v>404</v>
+      </c>
+      <c r="B123" t="s">
+        <v>416</v>
+      </c>
+      <c r="C123">
+        <v>6.42</v>
+      </c>
+      <c r="D123">
+        <v>252.083</v>
+      </c>
+    </row>
+    <row r="124" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A124" t="s">
+        <v>405</v>
+      </c>
+      <c r="B124" t="s">
+        <v>417</v>
+      </c>
+      <c r="C124">
+        <v>6.5</v>
+      </c>
+      <c r="D124">
+        <v>257.09500000000003</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/RR_ISRU.xlsx
+++ b/RR_ISRU.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="31620" yWindow="0" windowWidth="17700" windowHeight="10485"/>
+    <workbookView xWindow="31620" yWindow="0" windowWidth="17700" windowHeight="10485" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Calc (Kg)" sheetId="6" r:id="rId1"/>
@@ -26,8 +26,187 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Jade</author>
+  </authors>
+  <commentList>
+    <comment ref="B8" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Jade:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Or Chemicals[2.0828] + Aluminium[9.2] + HTPB[0.1]</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B25" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Jade:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Na3Mg4CaO6 + CaSO4.(H2O)2 + N6</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B35" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Jade:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+R = light Lanthanides
+OG Loparite = (R,Na,Sr,Ca)(Ti,Nb,Ta,Fe)O3</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B42" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Jade:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Carboxyl group ( C(O)OH ) + R-group ( C[n].H[2n+1] ) --&gt; Iso-butane ( (CH3)3CH )</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B95" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Jade:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Rather, just this minimum portion of the Thiokol complex chain, HS(CH2CH2OCH2OCH2CH2SS)n</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B96" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Jade:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+R is any rare earth element including Scandium, Yttrium and any of the Lanthanide group</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B98" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Jade:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Any Lanthanide, preferrably heavy ones</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="531" uniqueCount="432">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="603" uniqueCount="496">
   <si>
     <t>Resource</t>
   </si>
@@ -35,9 +214,6 @@
     <t>Real world chemical</t>
   </si>
   <si>
-    <t>moles</t>
-  </si>
-  <si>
     <t>molar mass</t>
   </si>
   <si>
@@ -86,9 +262,6 @@
     <t>NH3</t>
   </si>
   <si>
-    <t>N2</t>
-  </si>
-  <si>
     <t>H2O</t>
   </si>
   <si>
@@ -107,9 +280,6 @@
     <t>Hydrates</t>
   </si>
   <si>
-    <t>Ferrihydrite (Fe2O3+0.5(H2O))</t>
-  </si>
-  <si>
     <t>Minerals</t>
   </si>
   <si>
@@ -125,9 +295,6 @@
     <t>Substrate</t>
   </si>
   <si>
-    <t>?</t>
-  </si>
-  <si>
     <t>Alumina</t>
   </si>
   <si>
@@ -143,9 +310,6 @@
     <t>P</t>
   </si>
   <si>
-    <t>Platinum (Pt)</t>
-  </si>
-  <si>
     <t>Carbon</t>
   </si>
   <si>
@@ -230,9 +394,6 @@
     <t>Gross kg/s</t>
   </si>
   <si>
-    <t>Mass (kg)</t>
-  </si>
-  <si>
     <t>I/O Ratio</t>
   </si>
   <si>
@@ -260,15 +421,6 @@
     <t>Aluminum</t>
   </si>
   <si>
-    <t>Iron Oxide</t>
-  </si>
-  <si>
-    <t>PBAN (binder, fuel)</t>
-  </si>
-  <si>
-    <t>Epoxy</t>
-  </si>
-  <si>
     <t>Notation</t>
   </si>
   <si>
@@ -278,9 +430,6 @@
     <t>%</t>
   </si>
   <si>
-    <t>FeO</t>
-  </si>
-  <si>
     <t>Moles</t>
   </si>
   <si>
@@ -528,9 +677,6 @@
   </si>
   <si>
     <t>Fluorine</t>
-  </si>
-  <si>
-    <t>Cl2</t>
   </si>
   <si>
     <t>N2O4</t>
@@ -639,9 +785,6 @@
     <t>WasteWater</t>
   </si>
   <si>
-    <t>D+He3</t>
-  </si>
-  <si>
     <t>Metals</t>
   </si>
   <si>
@@ -702,9 +845,6 @@
     <t>U + SiC</t>
   </si>
   <si>
-    <t>(CeLaNdTh)PO4</t>
-  </si>
-  <si>
     <t>Thorium</t>
   </si>
   <si>
@@ -717,15 +857,6 @@
     <t>Cs</t>
   </si>
   <si>
-    <t>Pezzottaite (Cs(Be2Li)Al2Si6O18)</t>
-  </si>
-  <si>
-    <t>Smaltite ((CoFeNi)As2) + Fluorite (CaF2)</t>
-  </si>
-  <si>
-    <t>HalideCider</t>
-  </si>
-  <si>
     <t>FissionPulses</t>
   </si>
   <si>
@@ -765,9 +896,6 @@
     <t>LithiumSaltWater</t>
   </si>
   <si>
-    <t>LiD + 8(H2O)</t>
-  </si>
-  <si>
     <t>Buckminsterfullerene</t>
   </si>
   <si>
@@ -1350,20 +1478,263 @@
     <t>Net (kW)</t>
   </si>
   <si>
-    <t>Gypsum (CaSO4+2(H2O))</t>
-  </si>
-  <si>
     <t>Mass (mol)</t>
   </si>
   <si>
     <t>Gross moles</t>
+  </si>
+  <si>
+    <t>FumingButterscotch</t>
+  </si>
+  <si>
+    <t>Iron (Fe)</t>
+  </si>
+  <si>
+    <t>Diborane</t>
+  </si>
+  <si>
+    <t>B2H6</t>
+  </si>
+  <si>
+    <t>Pentaborane</t>
+  </si>
+  <si>
+    <t>B5H9</t>
+  </si>
+  <si>
+    <t>N2F4</t>
+  </si>
+  <si>
+    <t>Dinitrogen Tetrafluoride</t>
+  </si>
+  <si>
+    <t>Aniline</t>
+  </si>
+  <si>
+    <t>C6H5+NH2</t>
+  </si>
+  <si>
+    <t>IWFNA</t>
+  </si>
+  <si>
+    <t>HNO3</t>
+  </si>
+  <si>
+    <t>PSPC</t>
+  </si>
+  <si>
+    <t>HTPB</t>
+  </si>
+  <si>
+    <t>Polystyrene (C8H8)n</t>
+  </si>
+  <si>
+    <t>Isoleucine (C6H13NO2)</t>
+  </si>
+  <si>
+    <t>K</t>
+  </si>
+  <si>
+    <t>Fatty acid complex (C5O2H11)</t>
+  </si>
+  <si>
+    <t>Thiokol + Ammonium Perchlorate (C5H11O2S2 + NH4ClO4)</t>
+  </si>
+  <si>
+    <t>unit cost</t>
+  </si>
+  <si>
+    <t>Lithium6</t>
+  </si>
+  <si>
+    <t>LithiumDeuteride</t>
+  </si>
+  <si>
+    <t>LiD + (H2O)8</t>
+  </si>
+  <si>
+    <t>6Li</t>
+  </si>
+  <si>
+    <t>6LiD</t>
+  </si>
+  <si>
+    <t>D+3He</t>
+  </si>
+  <si>
+    <t>Md</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>Lr</t>
+  </si>
+  <si>
+    <t>Mendelevium</t>
+  </si>
+  <si>
+    <t>Nobelium</t>
+  </si>
+  <si>
+    <t>Lawrencium</t>
+  </si>
+  <si>
+    <t>Rf</t>
+  </si>
+  <si>
+    <t>Db</t>
+  </si>
+  <si>
+    <t>Sg</t>
+  </si>
+  <si>
+    <t>Bh</t>
+  </si>
+  <si>
+    <t>Hs</t>
+  </si>
+  <si>
+    <t>Mt</t>
+  </si>
+  <si>
+    <t>Ds</t>
+  </si>
+  <si>
+    <t>Rg</t>
+  </si>
+  <si>
+    <t>Cn</t>
+  </si>
+  <si>
+    <t>Hn</t>
+  </si>
+  <si>
+    <t>Fl</t>
+  </si>
+  <si>
+    <t>Mc</t>
+  </si>
+  <si>
+    <t>Lv</t>
+  </si>
+  <si>
+    <t>Ts</t>
+  </si>
+  <si>
+    <t>Og</t>
+  </si>
+  <si>
+    <t>Oganesson</t>
+  </si>
+  <si>
+    <t>Tennessine</t>
+  </si>
+  <si>
+    <t>Livermorium</t>
+  </si>
+  <si>
+    <t>Moscovium</t>
+  </si>
+  <si>
+    <t>Flerovium</t>
+  </si>
+  <si>
+    <t>Nihonium</t>
+  </si>
+  <si>
+    <t>Copernicium</t>
+  </si>
+  <si>
+    <t>Roentgium</t>
+  </si>
+  <si>
+    <t>Darmastadtium</t>
+  </si>
+  <si>
+    <t>Meitnerium</t>
+  </si>
+  <si>
+    <t>Hassium</t>
+  </si>
+  <si>
+    <t>Bohrium</t>
+  </si>
+  <si>
+    <t>Seaborgium</t>
+  </si>
+  <si>
+    <t>Dubnium</t>
+  </si>
+  <si>
+    <t>Rutherfordium</t>
+  </si>
+  <si>
+    <t>R</t>
+  </si>
+  <si>
+    <t>Gadolinite (R2 + (Fe,Be)3 + Si2O10)</t>
+  </si>
+  <si>
+    <t>(Ce,La,Nd,Th)PO4</t>
+  </si>
+  <si>
+    <t>Arfvedsonite (Na3Mg4FeSi8O22(OH)2) + Fluorite (CaF2)</t>
+  </si>
+  <si>
+    <t>N-P-K concentrate (N22.P2O5.(K2O)3)</t>
+  </si>
+  <si>
+    <t>Ferrihydrite ((Fe2O3)2.(H2O)) + Borax (Na2B4O5(OH)4.(H2O)8) + Noble soup (Ar3Xe)</t>
+  </si>
+  <si>
+    <t>Plain Steel (Fe10C)</t>
+  </si>
+  <si>
+    <t>Minerals + Gypsum + Nitrogen</t>
+  </si>
+  <si>
+    <t>Gypsum (CaSO4.(H2O)2)</t>
+  </si>
+  <si>
+    <t>Pezzottaite (Cs(Be2Li)Al2Si6O18) + Loparite custom (RNbO3)</t>
+  </si>
+  <si>
+    <t>Minerals + Carbon[6]</t>
+  </si>
+  <si>
+    <t>Cholestorol + Skatole + Thiol (C27H46O + C9H9N + CH3SH)</t>
+  </si>
+  <si>
+    <t>Food[4] + Polymers</t>
+  </si>
+  <si>
+    <t>Uranyl Nitrate ((UO2(NO3)2.(H2O)6)</t>
+  </si>
+  <si>
+    <t>(OH)2.(C4H6)45</t>
+  </si>
+  <si>
+    <t>Fuel</t>
+  </si>
+  <si>
+    <t>Binder</t>
+  </si>
+  <si>
+    <t>APCP</t>
+  </si>
+  <si>
+    <t>Ammonium Perchlorate[99] + Aluminium[92] + HTPB[1]</t>
+  </si>
+  <si>
+    <t>zCustom</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <numFmts count="10">
+  <numFmts count="11">
     <numFmt numFmtId="164" formatCode="#,##0.00\ &quot;kg/mol&quot;"/>
     <numFmt numFmtId="165" formatCode="#,##0.000\ &quot;kg/unit&quot;"/>
     <numFmt numFmtId="166" formatCode="#,##0.00\ &quot;g/mol&quot;"/>
@@ -1374,8 +1745,9 @@
     <numFmt numFmtId="171" formatCode="#,##0.0000&quot;:1&quot;"/>
     <numFmt numFmtId="172" formatCode="0.000"/>
     <numFmt numFmtId="173" formatCode="0.0"/>
+    <numFmt numFmtId="180" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="15" x14ac:knownFonts="1">
+  <fonts count="19" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1486,8 +1858,35 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="12">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1513,6 +1912,42 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFC6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -1582,7 +2017,7 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="9">
+  <cellStyleXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
@@ -1592,8 +2027,9 @@
     <xf numFmtId="0" fontId="8" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="49">
+  <cellXfs count="59">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1676,11 +2112,23 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="4" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="4" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="3" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="1" applyNumberFormat="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="18" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="180" fontId="0" fillId="0" borderId="0" xfId="9" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="9">
+  <cellStyles count="10">
     <cellStyle name="Calculation" xfId="2" builtinId="22"/>
     <cellStyle name="Explanatory Text" xfId="8" builtinId="53"/>
     <cellStyle name="Good" xfId="5" builtinId="26"/>
@@ -1690,6 +2138,7 @@
     <cellStyle name="Linked Cell" xfId="7" builtinId="24"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Output" xfId="6" builtinId="21"/>
+    <cellStyle name="Percent" xfId="9" builtinId="5"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -2004,40 +2453,40 @@
   <dimension ref="A1:L27"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="7" width="18.625" customWidth="1"/>
+    <col min="1" max="7" width="16" customWidth="1"/>
     <col min="9" max="9" width="9" customWidth="1"/>
     <col min="11" max="11" width="7.875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="20.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="47" t="s">
-        <v>89</v>
-      </c>
-      <c r="B1" s="47"/>
-      <c r="C1" s="47"/>
-      <c r="D1" s="47"/>
-      <c r="E1" s="47"/>
-      <c r="F1" s="47"/>
-      <c r="G1" s="47"/>
+      <c r="A1" s="48" t="s">
+        <v>79</v>
+      </c>
+      <c r="B1" s="48"/>
+      <c r="C1" s="48"/>
+      <c r="D1" s="48"/>
+      <c r="E1" s="48"/>
+      <c r="F1" s="48"/>
+      <c r="G1" s="48"/>
     </row>
     <row r="2" spans="1:12" ht="16.5" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A2" s="23" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" s="23" t="s">
-        <v>186</v>
+        <v>175</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" s="23" t="s">
-        <v>187</v>
+        <v>176</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="18" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="36" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="B5" s="36"/>
       <c r="C5" s="36"/>
@@ -2053,7 +2502,7 @@
     </row>
     <row r="6" spans="1:12" ht="16.5" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A6" s="21" t="s">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="B6" s="14">
         <v>0</v>
@@ -2074,13 +2523,13 @@
         <v>0</v>
       </c>
       <c r="I6" t="s">
-        <v>226</v>
+        <v>210</v>
       </c>
       <c r="J6" s="14">
         <v>1</v>
       </c>
       <c r="K6" s="23" t="s">
-        <v>227</v>
+        <v>211</v>
       </c>
       <c r="L6" s="15">
         <f>J7/J6</f>
@@ -2089,7 +2538,7 @@
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="B7" s="22"/>
       <c r="C7" s="22"/>
@@ -2098,13 +2547,13 @@
       <c r="F7" s="22"/>
       <c r="G7" s="22"/>
       <c r="I7" t="s">
-        <v>228</v>
+        <v>212</v>
       </c>
       <c r="J7" s="14">
         <v>1</v>
       </c>
       <c r="K7" s="23" t="s">
-        <v>236</v>
+        <v>219</v>
       </c>
       <c r="L7" s="15">
         <f>IF(J8&gt;0,L6-(J8*3600),0)</f>
@@ -2113,41 +2562,41 @@
     </row>
     <row r="8" spans="1:12" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="7" t="s">
-        <v>67</v>
+        <v>80</v>
       </c>
       <c r="B8" s="17" t="str">
-        <f>IFERROR(VLOOKUP(B7,Database!$A$3:$E$141,5,FALSE),"-")</f>
+        <f>IFERROR(VLOOKUP(B7,Database!$A$3:$E$152,5,FALSE),"-")</f>
         <v>-</v>
       </c>
       <c r="C8" s="17" t="str">
-        <f>IFERROR(VLOOKUP(C7,Database!$A$3:$E$141,5,FALSE),"-")</f>
+        <f>IFERROR(VLOOKUP(C7,Database!$A$3:$E$152,5,FALSE),"-")</f>
         <v>-</v>
       </c>
       <c r="D8" s="17" t="str">
-        <f>IFERROR(VLOOKUP(D7,Database!$A$3:$E$141,5,FALSE),"-")</f>
+        <f>IFERROR(VLOOKUP(D7,Database!$A$3:$E$152,5,FALSE),"-")</f>
         <v>-</v>
       </c>
       <c r="E8" s="17" t="str">
-        <f>IFERROR(VLOOKUP(E7,Database!$A$3:$E$141,5,FALSE),"-")</f>
+        <f>IFERROR(VLOOKUP(E7,Database!$A$3:$E$152,5,FALSE),"-")</f>
         <v>-</v>
       </c>
       <c r="F8" s="17" t="str">
-        <f>IFERROR(VLOOKUP(F7,Database!$A$3:$E$141,5,FALSE),"-")</f>
+        <f>IFERROR(VLOOKUP(F7,Database!$A$3:$E$152,5,FALSE),"-")</f>
         <v>-</v>
       </c>
       <c r="G8" s="17" t="str">
-        <f>IFERROR(VLOOKUP(G7,Database!$A$3:$E$141,5,FALSE),"-")</f>
+        <f>IFERROR(VLOOKUP(G7,Database!$A$3:$E$152,5,FALSE),"-")</f>
         <v>-</v>
       </c>
       <c r="I8" s="34" t="s">
-        <v>229</v>
+        <v>213</v>
       </c>
       <c r="J8" s="35">
         <f>ROUNDDOWN(IF(L6&gt;3600,L6/3600,0),0)</f>
         <v>0</v>
       </c>
       <c r="K8" s="23" t="s">
-        <v>223</v>
+        <v>207</v>
       </c>
       <c r="L8" s="15">
         <f>ROUNDDOWN(IF(L7&gt;0,L7/60,L6/60),0)</f>
@@ -2156,30 +2605,30 @@
     </row>
     <row r="9" spans="1:12" ht="17.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="42" t="s">
-        <v>430</v>
+        <v>412</v>
       </c>
       <c r="B9" s="17" t="str">
-        <f>IFERROR(VLOOKUP(B7,Database!$A$3:$E$141,4,FALSE),"-")</f>
+        <f>IFERROR(VLOOKUP(B7,Database!$A$3:$E$152,4,FALSE),"-")</f>
         <v>-</v>
       </c>
       <c r="C9" s="17" t="str">
-        <f>IFERROR(VLOOKUP(C7,Database!$A$3:$E$141,4,FALSE),"-")</f>
+        <f>IFERROR(VLOOKUP(C7,Database!$A$3:$E$152,4,FALSE),"-")</f>
         <v>-</v>
       </c>
       <c r="D9" s="17" t="str">
-        <f>IFERROR(VLOOKUP(D7,Database!$A$3:$E$141,4,FALSE),"-")</f>
+        <f>IFERROR(VLOOKUP(D7,Database!$A$3:$E$152,4,FALSE),"-")</f>
         <v>-</v>
       </c>
       <c r="E9" s="17" t="str">
-        <f>IFERROR(VLOOKUP(E7,Database!$A$3:$E$141,4,FALSE),"-")</f>
+        <f>IFERROR(VLOOKUP(E7,Database!$A$3:$E$152,4,FALSE),"-")</f>
         <v>-</v>
       </c>
       <c r="F9" s="17" t="str">
-        <f>IFERROR(VLOOKUP(F7,Database!$A$3:$E$141,4,FALSE),"-")</f>
+        <f>IFERROR(VLOOKUP(F7,Database!$A$3:$E$152,4,FALSE),"-")</f>
         <v>-</v>
       </c>
       <c r="G9" s="17" t="str">
-        <f>IFERROR(VLOOKUP(G7,Database!$A$3:$E$141,4,FALSE),"-")</f>
+        <f>IFERROR(VLOOKUP(G7,Database!$A$3:$E$152,4,FALSE),"-")</f>
         <v>-</v>
       </c>
       <c r="J9" s="35">
@@ -2187,7 +2636,7 @@
         <v>0</v>
       </c>
       <c r="K9" s="23" t="s">
-        <v>224</v>
+        <v>208</v>
       </c>
       <c r="L9" s="15">
         <f>IF(L6&gt;0,L6-((J8*3600)+(L8*60)),0)</f>
@@ -2196,7 +2645,7 @@
     </row>
     <row r="10" spans="1:12" ht="16.5" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="B10" s="20" t="str">
         <f t="shared" ref="B10:G10" si="0">IFERROR(B6*B8,"-")</f>
@@ -2227,12 +2676,12 @@
         <v>1</v>
       </c>
       <c r="K10" s="23" t="s">
-        <v>225</v>
+        <v>209</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" s="42" t="s">
-        <v>431</v>
+        <v>413</v>
       </c>
       <c r="B11" s="20" t="str">
         <f t="shared" ref="B11:C11" si="1">IFERROR((B6*(B8*1000))/B9,"-")</f>
@@ -2261,7 +2710,7 @@
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="B12" s="28">
         <f>SUM(B10:G10)</f>
@@ -2270,7 +2719,7 @@
     </row>
     <row r="15" spans="1:12" ht="18" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="36" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="B15" s="36"/>
       <c r="C15" s="36"/>
@@ -2286,7 +2735,7 @@
     </row>
     <row r="16" spans="1:12" ht="16.5" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A16" s="21" t="s">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="B16" s="14">
         <v>0</v>
@@ -2307,13 +2756,13 @@
         <v>0</v>
       </c>
       <c r="I16" t="s">
-        <v>226</v>
+        <v>210</v>
       </c>
       <c r="J16" s="14">
         <v>1</v>
       </c>
       <c r="K16" s="23" t="s">
-        <v>227</v>
+        <v>211</v>
       </c>
       <c r="L16" s="15">
         <f>J17/J16</f>
@@ -2322,7 +2771,7 @@
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17" s="7" t="s">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="B17" s="22"/>
       <c r="C17" s="22"/>
@@ -2331,13 +2780,13 @@
       <c r="F17" s="22"/>
       <c r="G17" s="22"/>
       <c r="I17" t="s">
-        <v>228</v>
+        <v>212</v>
       </c>
       <c r="J17" s="14">
         <v>1</v>
       </c>
       <c r="K17" s="23" t="s">
-        <v>236</v>
+        <v>219</v>
       </c>
       <c r="L17" s="15">
         <f>IF(J18&gt;0,L16-(J18*3600),0)</f>
@@ -2346,41 +2795,41 @@
     </row>
     <row r="18" spans="1:12" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="7" t="s">
-        <v>67</v>
+        <v>80</v>
       </c>
       <c r="B18" s="17" t="str">
-        <f>IFERROR(VLOOKUP(B17,Database!$A$3:$E$141,5,FALSE),"-")</f>
+        <f>IFERROR(VLOOKUP(B17,Database!$A$3:$E$152,5,FALSE),"-")</f>
         <v>-</v>
       </c>
       <c r="C18" s="17" t="str">
-        <f>IFERROR(VLOOKUP(C17,Database!$A$3:$E$141,5,FALSE),"-")</f>
+        <f>IFERROR(VLOOKUP(C17,Database!$A$3:$E$152,5,FALSE),"-")</f>
         <v>-</v>
       </c>
       <c r="D18" s="17" t="str">
-        <f>IFERROR(VLOOKUP(D17,Database!$A$3:$E$141,5,FALSE),"-")</f>
+        <f>IFERROR(VLOOKUP(D17,Database!$A$3:$E$152,5,FALSE),"-")</f>
         <v>-</v>
       </c>
       <c r="E18" s="17" t="str">
-        <f>IFERROR(VLOOKUP(E17,Database!$A$3:$E$141,5,FALSE),"-")</f>
+        <f>IFERROR(VLOOKUP(E17,Database!$A$3:$E$152,5,FALSE),"-")</f>
         <v>-</v>
       </c>
       <c r="F18" s="17" t="str">
-        <f>IFERROR(VLOOKUP(F17,Database!$A$3:$E$141,5,FALSE),"-")</f>
+        <f>IFERROR(VLOOKUP(F17,Database!$A$3:$E$152,5,FALSE),"-")</f>
         <v>-</v>
       </c>
       <c r="G18" s="17" t="str">
-        <f>IFERROR(VLOOKUP(G17,Database!$A$3:$E$141,5,FALSE),"-")</f>
+        <f>IFERROR(VLOOKUP(G17,Database!$A$3:$E$152,5,FALSE),"-")</f>
         <v>-</v>
       </c>
       <c r="I18" s="34" t="s">
-        <v>229</v>
+        <v>213</v>
       </c>
       <c r="J18" s="35">
         <f>ROUNDDOWN(IF(L16&gt;3600,L16/3600,0),0)</f>
         <v>0</v>
       </c>
       <c r="K18" s="23" t="s">
-        <v>223</v>
+        <v>207</v>
       </c>
       <c r="L18" s="15">
         <f>ROUNDDOWN(IF(L17&gt;0,L17/60,L16/60),0)</f>
@@ -2389,30 +2838,30 @@
     </row>
     <row r="19" spans="1:12" ht="17.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="42" t="s">
-        <v>430</v>
+        <v>412</v>
       </c>
       <c r="B19" s="17" t="str">
-        <f>IFERROR(VLOOKUP(B17,Database!$A$3:$E$141,4,FALSE),"-")</f>
+        <f>IFERROR(VLOOKUP(B17,Database!$A$3:$E$152,4,FALSE),"-")</f>
         <v>-</v>
       </c>
       <c r="C19" s="17" t="str">
-        <f>IFERROR(VLOOKUP(C17,Database!$A$3:$E$141,4,FALSE),"-")</f>
+        <f>IFERROR(VLOOKUP(C17,Database!$A$3:$E$152,4,FALSE),"-")</f>
         <v>-</v>
       </c>
       <c r="D19" s="17" t="str">
-        <f>IFERROR(VLOOKUP(D17,Database!$A$3:$E$141,4,FALSE),"-")</f>
+        <f>IFERROR(VLOOKUP(D17,Database!$A$3:$E$152,4,FALSE),"-")</f>
         <v>-</v>
       </c>
       <c r="E19" s="17" t="str">
-        <f>IFERROR(VLOOKUP(E17,Database!$A$3:$E$141,4,FALSE),"-")</f>
+        <f>IFERROR(VLOOKUP(E17,Database!$A$3:$E$152,4,FALSE),"-")</f>
         <v>-</v>
       </c>
       <c r="F19" s="17" t="str">
-        <f>IFERROR(VLOOKUP(F17,Database!$A$3:$E$141,4,FALSE),"-")</f>
+        <f>IFERROR(VLOOKUP(F17,Database!$A$3:$E$152,4,FALSE),"-")</f>
         <v>-</v>
       </c>
       <c r="G19" s="17" t="str">
-        <f>IFERROR(VLOOKUP(G17,Database!$A$3:$E$141,4,FALSE),"-")</f>
+        <f>IFERROR(VLOOKUP(G17,Database!$A$3:$E$152,4,FALSE),"-")</f>
         <v>-</v>
       </c>
       <c r="J19" s="35">
@@ -2420,7 +2869,7 @@
         <v>0</v>
       </c>
       <c r="K19" s="23" t="s">
-        <v>224</v>
+        <v>208</v>
       </c>
       <c r="L19" s="15">
         <f>IF(L16&gt;0,L16-((J18*3600)+(L18*60)),0)</f>
@@ -2429,7 +2878,7 @@
     </row>
     <row r="20" spans="1:12" ht="16.5" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A20" s="7" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="B20" s="26" t="str">
         <f t="shared" ref="B20:G20" si="3">IFERROR(B16*B18,"-")</f>
@@ -2460,12 +2909,12 @@
         <v>1</v>
       </c>
       <c r="K20" s="23" t="s">
-        <v>225</v>
+        <v>209</v>
       </c>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A21" s="42" t="s">
-        <v>431</v>
+        <v>413</v>
       </c>
       <c r="B21" s="20" t="str">
         <f t="shared" ref="B21:G21" si="4">IFERROR((B16*(B18*1000))/B19,"-")</f>
@@ -2494,7 +2943,7 @@
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A22" s="7" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="B22" s="28">
         <f>SUM(B20:G20)</f>
@@ -2502,19 +2951,19 @@
       </c>
     </row>
     <row r="25" spans="1:12" ht="18" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="48" t="s">
-        <v>68</v>
-      </c>
-      <c r="B25" s="48"/>
-      <c r="C25" s="48"/>
-      <c r="D25" s="48"/>
-      <c r="E25" s="48"/>
-      <c r="F25" s="48"/>
-      <c r="G25" s="48"/>
+      <c r="A25" s="49" t="s">
+        <v>62</v>
+      </c>
+      <c r="B25" s="49"/>
+      <c r="C25" s="49"/>
+      <c r="D25" s="49"/>
+      <c r="E25" s="49"/>
+      <c r="F25" s="49"/>
+      <c r="G25" s="49"/>
     </row>
     <row r="26" spans="1:12" ht="16.5" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A26" s="7" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="B26" s="16" t="str">
         <f>IF($B$12&gt;$B$22,"Input excesive",IF($B$12&lt;$B$22,"Output excessive","Equal"))</f>
@@ -2536,12 +2985,18 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
-            <xm:f>Database!$A$3:$A$141</xm:f>
+            <xm:f>Database!$A$3:$A$152</xm:f>
           </x14:formula1>
-          <xm:sqref>B7:G7 B17:G17</xm:sqref>
+          <xm:sqref>B7:G7</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>Database!$A$3:$A$152</xm:f>
+          </x14:formula1>
+          <xm:sqref>B17:G17</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -2551,41 +3006,43 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J39"/>
+  <dimension ref="A1:L39"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="7" width="18.625" customWidth="1"/>
+    <col min="1" max="9" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="20.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="47" t="s">
-        <v>88</v>
-      </c>
-      <c r="B1" s="47"/>
-      <c r="C1" s="47"/>
-      <c r="D1" s="47"/>
-      <c r="E1" s="47"/>
-      <c r="F1" s="47"/>
-      <c r="G1" s="47"/>
-    </row>
-    <row r="2" spans="1:10" ht="16.5" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" ht="20.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="48" t="s">
+        <v>78</v>
+      </c>
+      <c r="B1" s="48"/>
+      <c r="C1" s="48"/>
+      <c r="D1" s="48"/>
+      <c r="E1" s="48"/>
+      <c r="F1" s="48"/>
+      <c r="G1" s="48"/>
+      <c r="H1" s="47"/>
+      <c r="I1" s="47"/>
+    </row>
+    <row r="2" spans="1:12" ht="16.5" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A2" s="23" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" s="23" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" s="23" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" ht="18" thickBot="1" x14ac:dyDescent="0.35">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" ht="18" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="36" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="B5" s="36"/>
       <c r="C5" s="36"/>
@@ -2593,11 +3050,13 @@
       <c r="E5" s="36"/>
       <c r="F5" s="36"/>
       <c r="G5" s="36"/>
-      <c r="J5" s="1"/>
-    </row>
-    <row r="6" spans="1:10" ht="16.5" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="H5" s="36"/>
+      <c r="I5" s="36"/>
+      <c r="L5" s="1"/>
+    </row>
+    <row r="6" spans="1:12" ht="16.5" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="B6" s="14">
         <v>0</v>
@@ -2617,10 +3076,16 @@
       <c r="G6" s="14">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="H6" s="14">
+        <v>0</v>
+      </c>
+      <c r="I6" s="14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="B7" s="22"/>
       <c r="C7" s="22"/>
@@ -2628,68 +3093,86 @@
       <c r="E7" s="22"/>
       <c r="F7" s="22"/>
       <c r="G7" s="22"/>
-    </row>
-    <row r="8" spans="1:10" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H7" s="22"/>
+      <c r="I7" s="22"/>
+    </row>
+    <row r="8" spans="1:12" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="7" t="s">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="B8" s="17" t="str">
-        <f>IFERROR(VLOOKUP(B7,Database!$A$3:$E$103,4,FALSE),"-")</f>
+        <f>IFERROR(VLOOKUP(B7,Database!$A$3:$E$113,4,FALSE),"-")</f>
         <v>-</v>
       </c>
       <c r="C8" s="17" t="str">
-        <f>IFERROR(VLOOKUP(C7,Database!$A$3:$E$103,4,FALSE),"-")</f>
+        <f>IFERROR(VLOOKUP(C7,Database!$A$3:$E$113,4,FALSE),"-")</f>
         <v>-</v>
       </c>
       <c r="D8" s="17" t="str">
-        <f>IFERROR(VLOOKUP(D7,Database!$A$3:$E$103,4,FALSE),"-")</f>
+        <f>IFERROR(VLOOKUP(D7,Database!$A$3:$E$113,4,FALSE),"-")</f>
         <v>-</v>
       </c>
       <c r="E8" s="17" t="str">
-        <f>IFERROR(VLOOKUP(E7,Database!$A$3:$E$103,4,FALSE),"-")</f>
+        <f>IFERROR(VLOOKUP(E7,Database!$A$3:$E$113,4,FALSE),"-")</f>
         <v>-</v>
       </c>
       <c r="F8" s="17" t="str">
-        <f>IFERROR(VLOOKUP(F7,Database!$A$3:$E$103,4,FALSE),"-")</f>
+        <f>IFERROR(VLOOKUP(F7,Database!$A$3:$E$113,4,FALSE),"-")</f>
         <v>-</v>
       </c>
       <c r="G8" s="17" t="str">
-        <f>IFERROR(VLOOKUP(G7,Database!$A$3:$E$103,4,FALSE),"-")</f>
-        <v>-</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" ht="17.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+        <f>IFERROR(VLOOKUP(G7,Database!$A$3:$E$113,4,FALSE),"-")</f>
+        <v>-</v>
+      </c>
+      <c r="H8" s="17" t="str">
+        <f>IFERROR(VLOOKUP(H7,Database!$A$3:$E$113,4,FALSE),"-")</f>
+        <v>-</v>
+      </c>
+      <c r="I8" s="17" t="str">
+        <f>IFERROR(VLOOKUP(I7,Database!$A$3:$E$113,4,FALSE),"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" ht="17.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="7" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="B9" s="17" t="str">
-        <f>IFERROR(VLOOKUP(B7,Database!$A$3:$E$103,5,FALSE),"-")</f>
+        <f>IFERROR(VLOOKUP(B7,Database!$A$3:$E$113,5,FALSE),"-")</f>
         <v>-</v>
       </c>
       <c r="C9" s="17" t="str">
-        <f>IFERROR(VLOOKUP(C7,Database!$A$3:$E$103,5,FALSE),"-")</f>
+        <f>IFERROR(VLOOKUP(C7,Database!$A$3:$E$113,5,FALSE),"-")</f>
         <v>-</v>
       </c>
       <c r="D9" s="17" t="str">
-        <f>IFERROR(VLOOKUP(D7,Database!$A$3:$E$103,5,FALSE),"-")</f>
+        <f>IFERROR(VLOOKUP(D7,Database!$A$3:$E$113,5,FALSE),"-")</f>
         <v>-</v>
       </c>
       <c r="E9" s="17" t="str">
-        <f>IFERROR(VLOOKUP(E7,Database!$A$3:$E$103,5,FALSE),"-")</f>
+        <f>IFERROR(VLOOKUP(E7,Database!$A$3:$E$113,5,FALSE),"-")</f>
         <v>-</v>
       </c>
       <c r="F9" s="17" t="str">
-        <f>IFERROR(VLOOKUP(F7,Database!$A$3:$E$103,5,FALSE),"-")</f>
+        <f>IFERROR(VLOOKUP(F7,Database!$A$3:$E$113,5,FALSE),"-")</f>
         <v>-</v>
       </c>
       <c r="G9" s="17" t="str">
-        <f>IFERROR(VLOOKUP(G7,Database!$A$3:$E$103,5,FALSE),"-")</f>
-        <v>-</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" ht="16.5" thickTop="1" x14ac:dyDescent="0.25">
+        <f>IFERROR(VLOOKUP(G7,Database!$A$3:$E$113,5,FALSE),"-")</f>
+        <v>-</v>
+      </c>
+      <c r="H9" s="17" t="str">
+        <f>IFERROR(VLOOKUP(H7,Database!$A$3:$E$113,5,FALSE),"-")</f>
+        <v>-</v>
+      </c>
+      <c r="I9" s="17" t="str">
+        <f>IFERROR(VLOOKUP(I7,Database!$A$3:$E$113,5,FALSE),"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" ht="16.5" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="B10" s="39">
         <f>IFERROR(B6*B8,0)</f>
@@ -2715,113 +3198,145 @@
         <f>IFERROR(G6*G8,"-")</f>
         <v>-</v>
       </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="H10" s="15" t="str">
+        <f t="shared" ref="H10:I10" si="0">IFERROR(H6*H8,"-")</f>
+        <v>-</v>
+      </c>
+      <c r="I10" s="15" t="str">
+        <f t="shared" si="0"/>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" s="21" t="s">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="B11" s="28" t="str">
-        <f t="shared" ref="B11:G11" si="0">IFERROR(B10/(B9*1000),"-")</f>
+        <f t="shared" ref="B11:G11" si="1">IFERROR(B10/(B9*1000),"-")</f>
         <v>-</v>
       </c>
       <c r="C11" s="28" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>-</v>
       </c>
       <c r="D11" s="28" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>-</v>
       </c>
       <c r="E11" s="28" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>-</v>
       </c>
       <c r="F11" s="28" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>-</v>
       </c>
       <c r="G11" s="28" t="str">
-        <f t="shared" si="0"/>
-        <v>-</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+        <f t="shared" si="1"/>
+        <v>-</v>
+      </c>
+      <c r="H11" s="28" t="str">
+        <f t="shared" ref="H11:I11" si="2">IFERROR(H10/(H9*1000),"-")</f>
+        <v>-</v>
+      </c>
+      <c r="I11" s="28" t="str">
+        <f t="shared" si="2"/>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="B12" s="20">
-        <f>SUM(B10:G10)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+        <f>SUM(B10:I10)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="42" t="s">
-        <v>424</v>
+        <v>407</v>
       </c>
       <c r="B14" s="17" t="str">
-        <f>IFERROR(VLOOKUP(B7,Database!$A$3:$G$103,7,FALSE),"-")</f>
+        <f>IFERROR(VLOOKUP(B7,Database!$A$3:$G$113,7,FALSE),"-")</f>
         <v>-</v>
       </c>
       <c r="C14" s="17" t="str">
-        <f>IFERROR(VLOOKUP(C7,Database!$A$3:$G$103,7,FALSE),"-")</f>
+        <f>IFERROR(VLOOKUP(C7,Database!$A$3:$G$113,7,FALSE),"-")</f>
         <v>-</v>
       </c>
       <c r="D14" s="17" t="str">
-        <f>IFERROR(VLOOKUP(D7,Database!$A$3:$G$103,7,FALSE),"-")</f>
+        <f>IFERROR(VLOOKUP(D7,Database!$A$3:$G$113,7,FALSE),"-")</f>
         <v>-</v>
       </c>
       <c r="E14" s="17" t="str">
-        <f>IFERROR(VLOOKUP(E7,Database!$A$3:$G$103,7,FALSE),"-")</f>
+        <f>IFERROR(VLOOKUP(E7,Database!$A$3:$G$113,7,FALSE),"-")</f>
         <v>-</v>
       </c>
       <c r="F14" s="17" t="str">
-        <f>IFERROR(VLOOKUP(F7,Database!$A$3:$G$103,7,FALSE),"-")</f>
+        <f>IFERROR(VLOOKUP(F7,Database!$A$3:$G$113,7,FALSE),"-")</f>
         <v>-</v>
       </c>
       <c r="G14" s="17" t="str">
-        <f>IFERROR(VLOOKUP(G7,Database!$A$3:$G$103,7,FALSE),"-")</f>
-        <v>-</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" ht="16.5" thickTop="1" x14ac:dyDescent="0.25">
+        <f>IFERROR(VLOOKUP(G7,Database!$A$3:$G$113,7,FALSE),"-")</f>
+        <v>-</v>
+      </c>
+      <c r="H14" s="17" t="str">
+        <f>IFERROR(VLOOKUP(H7,Database!$A$3:$G$113,7,FALSE),"-")</f>
+        <v>-</v>
+      </c>
+      <c r="I14" s="17" t="str">
+        <f>IFERROR(VLOOKUP(I7,Database!$A$3:$G$113,7,FALSE),"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" ht="16.5" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B15" s="15">
         <f>IFERROR(B6*B14,0)</f>
         <v>0</v>
       </c>
       <c r="C15" s="15">
-        <f t="shared" ref="C15:G15" si="1">IFERROR(C6*C14,0)</f>
+        <f t="shared" ref="C15:G15" si="3">IFERROR(C6*C14,0)</f>
         <v>0</v>
       </c>
       <c r="D15" s="15">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="E15" s="15">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="F15" s="15">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="G15" s="15">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H15" s="15">
+        <f t="shared" ref="H15:I15" si="4">IFERROR(H6*H14,0)</f>
+        <v>0</v>
+      </c>
+      <c r="I15" s="15">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16" s="7" t="s">
-        <v>428</v>
+        <v>411</v>
       </c>
       <c r="B16" s="41">
-        <f>SUM(B15:G15)/20</f>
-        <v>0</v>
-      </c>
-      <c r="I16" s="1"/>
-    </row>
-    <row r="19" spans="1:7" ht="18" thickBot="1" x14ac:dyDescent="0.35">
+        <f>SUM(B15:I15)/20</f>
+        <v>0</v>
+      </c>
+      <c r="K16" s="1"/>
+    </row>
+    <row r="19" spans="1:11" ht="18" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19" s="36" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="B19" s="36"/>
       <c r="C19" s="36"/>
@@ -2829,12 +3344,14 @@
       <c r="E19" s="36"/>
       <c r="F19" s="36"/>
       <c r="G19" s="36"/>
-    </row>
-    <row r="20" spans="1:7" ht="16.5" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="H19" s="36"/>
+      <c r="I19" s="36"/>
+    </row>
+    <row r="20" spans="1:11" ht="16.5" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A20" s="7" t="s">
-        <v>84</v>
-      </c>
-      <c r="B20" s="14">
+        <v>74</v>
+      </c>
+      <c r="B20" s="50">
         <v>0</v>
       </c>
       <c r="C20" s="14">
@@ -2852,10 +3369,16 @@
       <c r="G20" s="14">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H20" s="14">
+        <v>0</v>
+      </c>
+      <c r="I20" s="14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" s="7" t="s">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="B21" s="22"/>
       <c r="C21" s="22"/>
@@ -2863,68 +3386,86 @@
       <c r="E21" s="22"/>
       <c r="F21" s="22"/>
       <c r="G21" s="22"/>
-    </row>
-    <row r="22" spans="1:7" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H21" s="22"/>
+      <c r="I21" s="22"/>
+    </row>
+    <row r="22" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" s="7" t="s">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="B22" s="17" t="str">
-        <f>IFERROR(VLOOKUP(B21,Database!$A$3:$G$103,4,FALSE),"-")</f>
+        <f>IFERROR(VLOOKUP(B21,Database!$A$3:$G$113,4,FALSE),"-")</f>
         <v>-</v>
       </c>
       <c r="C22" s="17" t="str">
-        <f>IFERROR(VLOOKUP(C21,Database!$A$3:$G$103,4,FALSE),"-")</f>
+        <f>IFERROR(VLOOKUP(C21,Database!$A$3:$G$113,4,FALSE),"-")</f>
         <v>-</v>
       </c>
       <c r="D22" s="17" t="str">
-        <f>IFERROR(VLOOKUP(D21,Database!$A$3:$G$103,4,FALSE),"-")</f>
+        <f>IFERROR(VLOOKUP(D21,Database!$A$3:$G$113,4,FALSE),"-")</f>
         <v>-</v>
       </c>
       <c r="E22" s="17" t="str">
-        <f>IFERROR(VLOOKUP(E21,Database!$A$3:$G$103,4,FALSE),"-")</f>
+        <f>IFERROR(VLOOKUP(E21,Database!$A$3:$G$113,4,FALSE),"-")</f>
         <v>-</v>
       </c>
       <c r="F22" s="17" t="str">
-        <f>IFERROR(VLOOKUP(F21,Database!$A$3:$G$103,4,FALSE),"-")</f>
+        <f>IFERROR(VLOOKUP(F21,Database!$A$3:$G$113,4,FALSE),"-")</f>
         <v>-</v>
       </c>
       <c r="G22" s="17" t="str">
-        <f>IFERROR(VLOOKUP(G21,Database!$A$3:$G$103,4,FALSE),"-")</f>
-        <v>-</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" ht="17.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+        <f>IFERROR(VLOOKUP(G21,Database!$A$3:$G$113,4,FALSE),"-")</f>
+        <v>-</v>
+      </c>
+      <c r="H22" s="17" t="str">
+        <f>IFERROR(VLOOKUP(H21,Database!$A$3:$G$113,4,FALSE),"-")</f>
+        <v>-</v>
+      </c>
+      <c r="I22" s="17" t="str">
+        <f>IFERROR(VLOOKUP(I21,Database!$A$3:$G$113,4,FALSE),"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" ht="17.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="7" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="B23" s="17" t="str">
-        <f>IFERROR(VLOOKUP(B21,Database!$A$3:$G$103,5,FALSE),"-")</f>
+        <f>IFERROR(VLOOKUP(B21,Database!$A$3:$G$113,5,FALSE),"-")</f>
         <v>-</v>
       </c>
       <c r="C23" s="17" t="str">
-        <f>IFERROR(VLOOKUP(C21,Database!$A$3:$G$103,5,FALSE),"-")</f>
+        <f>IFERROR(VLOOKUP(C21,Database!$A$3:$G$113,5,FALSE),"-")</f>
         <v>-</v>
       </c>
       <c r="D23" s="17" t="str">
-        <f>IFERROR(VLOOKUP(D21,Database!$A$3:$G$103,5,FALSE),"-")</f>
+        <f>IFERROR(VLOOKUP(D21,Database!$A$3:$G$113,5,FALSE),"-")</f>
         <v>-</v>
       </c>
       <c r="E23" s="17" t="str">
-        <f>IFERROR(VLOOKUP(E21,Database!$A$3:$G$103,5,FALSE),"-")</f>
+        <f>IFERROR(VLOOKUP(E21,Database!$A$3:$G$113,5,FALSE),"-")</f>
         <v>-</v>
       </c>
       <c r="F23" s="17" t="str">
-        <f>IFERROR(VLOOKUP(F21,Database!$A$3:$G$103,5,FALSE),"-")</f>
+        <f>IFERROR(VLOOKUP(F21,Database!$A$3:$G$113,5,FALSE),"-")</f>
         <v>-</v>
       </c>
       <c r="G23" s="17" t="str">
-        <f>IFERROR(VLOOKUP(G21,Database!$A$3:$G$103,5,FALSE),"-")</f>
-        <v>-</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" ht="16.5" thickTop="1" x14ac:dyDescent="0.25">
+        <f>IFERROR(VLOOKUP(G21,Database!$A$3:$G$113,5,FALSE),"-")</f>
+        <v>-</v>
+      </c>
+      <c r="H23" s="17" t="str">
+        <f>IFERROR(VLOOKUP(H21,Database!$A$3:$G$113,5,FALSE),"-")</f>
+        <v>-</v>
+      </c>
+      <c r="I23" s="17" t="str">
+        <f>IFERROR(VLOOKUP(I21,Database!$A$3:$G$113,5,FALSE),"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" ht="16.5" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A24" s="7" t="s">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="B24" s="15">
         <f>IFERROR(B20*B22,0)</f>
@@ -2950,115 +3491,144 @@
         <f>IFERROR(G20*G22,"-")</f>
         <v>-</v>
       </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H24" s="15" t="str">
+        <f t="shared" ref="H24:I24" si="5">IFERROR(H20*H22,"-")</f>
+        <v>-</v>
+      </c>
+      <c r="I24" s="15" t="str">
+        <f t="shared" si="5"/>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25" s="21" t="s">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="B25" s="28" t="str">
-        <f t="shared" ref="B25:G25" si="2">IFERROR(B24/(B23*1000),"-")</f>
+        <f t="shared" ref="B25:G25" si="6">IFERROR(B24/(B23*1000),"-")</f>
         <v>-</v>
       </c>
       <c r="C25" s="28" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>-</v>
       </c>
       <c r="D25" s="28" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>-</v>
       </c>
       <c r="E25" s="28" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>-</v>
       </c>
       <c r="F25" s="28" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>-</v>
       </c>
       <c r="G25" s="28" t="str">
-        <f t="shared" si="2"/>
-        <v>-</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+        <f t="shared" si="6"/>
+        <v>-</v>
+      </c>
+      <c r="H25" s="28" t="str">
+        <f t="shared" ref="H25:I25" si="7">IFERROR(H24/(H23*1000),"-")</f>
+        <v>-</v>
+      </c>
+      <c r="I25" s="28" t="str">
+        <f t="shared" si="7"/>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26" s="7" t="s">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="B26" s="20">
-        <f>SUM(B24:G24)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+        <f>SUM(B24:I24)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A27" s="7"/>
     </row>
-    <row r="28" spans="1:7" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A28" s="42" t="s">
-        <v>424</v>
+        <v>407</v>
       </c>
       <c r="B28" s="17" t="str">
-        <f>IFERROR(VLOOKUP(B21,Database!$A$3:$G$103,7,FALSE),"-")</f>
+        <f>IFERROR(VLOOKUP(B21,Database!$A$3:$G$113,7,FALSE),"-")</f>
         <v>-</v>
       </c>
       <c r="C28" s="17" t="str">
-        <f>IFERROR(VLOOKUP(C21,Database!$A$3:$G$103,7,FALSE),"-")</f>
+        <f>IFERROR(VLOOKUP(C21,Database!$A$3:$G$113,7,FALSE),"-")</f>
         <v>-</v>
       </c>
       <c r="D28" s="17" t="str">
-        <f>IFERROR(VLOOKUP(D21,Database!$A$3:$G$103,7,FALSE),"-")</f>
+        <f>IFERROR(VLOOKUP(D21,Database!$A$3:$G$113,7,FALSE),"-")</f>
         <v>-</v>
       </c>
       <c r="E28" s="17" t="str">
-        <f>IFERROR(VLOOKUP(E21,Database!$A$3:$G$103,7,FALSE),"-")</f>
+        <f>IFERROR(VLOOKUP(E21,Database!$A$3:$G$113,7,FALSE),"-")</f>
         <v>-</v>
       </c>
       <c r="F28" s="17" t="str">
-        <f>IFERROR(VLOOKUP(F21,Database!$A$3:$G$103,7,FALSE),"-")</f>
+        <f>IFERROR(VLOOKUP(F21,Database!$A$3:$G$113,7,FALSE),"-")</f>
         <v>-</v>
       </c>
       <c r="G28" s="17" t="str">
-        <f>IFERROR(VLOOKUP(G21,Database!$A$3:$G$103,7,FALSE),"-")</f>
-        <v>-</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" ht="16.5" thickTop="1" x14ac:dyDescent="0.25">
+        <f>IFERROR(VLOOKUP(G21,Database!$A$3:$G$113,7,FALSE),"-")</f>
+        <v>-</v>
+      </c>
+      <c r="H28" s="17"/>
+      <c r="I28" s="17"/>
+    </row>
+    <row r="29" spans="1:11" ht="16.5" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B29" s="15">
         <f>IFERROR(B20*B28,0)</f>
         <v>0</v>
       </c>
       <c r="C29" s="15">
-        <f t="shared" ref="C29:G29" si="3">IFERROR(C20*C28,0)</f>
+        <f t="shared" ref="C29:I29" si="8">IFERROR(C20*C28,0)</f>
         <v>0</v>
       </c>
       <c r="D29" s="15">
-        <f t="shared" si="3"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="E29" s="15">
-        <f t="shared" si="3"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="F29" s="15">
-        <f t="shared" si="3"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="G29" s="15">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="H29" s="15">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="I29" s="15">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A30" s="7" t="s">
-        <v>428</v>
+        <v>411</v>
       </c>
       <c r="B30" s="41">
-        <f>SUM(B29:G29)/20</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7" ht="18" thickBot="1" x14ac:dyDescent="0.35">
+        <f>SUM(B29:I29)/20</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="K31" s="1"/>
+    </row>
+    <row r="33" spans="1:9" ht="18" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A33" s="38" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="B33" s="38"/>
       <c r="C33" s="38"/>
@@ -3066,10 +3636,12 @@
       <c r="E33" s="38"/>
       <c r="F33" s="38"/>
       <c r="G33" s="38"/>
-    </row>
-    <row r="34" spans="1:7" ht="16.5" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="H33" s="38"/>
+      <c r="I33" s="38"/>
+    </row>
+    <row r="34" spans="1:9" ht="16.5" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A34" s="7" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="B34" s="16" t="str">
         <f>IF($B$12&gt;$B$26,"Input excesive",IF($B$12&lt;$B$26,"Output excessive","Equal"))</f>
@@ -3080,13 +3652,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
       <c r="G36" s="1"/>
-    </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H36" s="1"/>
+      <c r="I36" s="1"/>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B37" s="45"/>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B39" s="44"/>
     </row>
   </sheetData>
@@ -3100,9 +3674,9 @@
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
-            <xm:f>Database!$A$3:$A$141</xm:f>
+            <xm:f>Database!$A$3:$A$152</xm:f>
           </x14:formula1>
-          <xm:sqref>B21:G21 B7:G7</xm:sqref>
+          <xm:sqref>B21:I21 B7:I7</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -3111,12 +3685,12 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L141"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:Q152"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.5" customWidth="1"/>
-    <col min="2" max="2" width="36.5" customWidth="1"/>
+    <col min="2" max="2" width="49.75" customWidth="1"/>
     <col min="3" max="3" width="13.625" customWidth="1"/>
     <col min="4" max="4" width="17" customWidth="1"/>
     <col min="5" max="5" width="18.125" customWidth="1"/>
@@ -3125,7 +3699,7 @@
     <col min="8" max="8" width="11.875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="47.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:17" ht="47.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3133,22 +3707,22 @@
         <v>1</v>
       </c>
       <c r="C1" s="2" t="s">
+        <v>433</v>
+      </c>
+      <c r="D1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="E1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
-        <v>4</v>
-      </c>
       <c r="F1" s="2" t="s">
-        <v>208</v>
+        <v>196</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>423</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1"/>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -3156,15 +3730,15 @@
       <c r="E2" s="2"/>
       <c r="F2" s="2"/>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>238</v>
+        <v>221</v>
       </c>
       <c r="C3" s="1">
-        <v>1</v>
+        <v>0.02</v>
       </c>
       <c r="D3" s="5">
         <v>576.85</v>
@@ -3174,34 +3748,22 @@
         <v>10</v>
       </c>
       <c r="F3" s="6">
-        <f>C3*D3/(E3 * 1000)</f>
+        <f>D3/(E3 * 1000)</f>
         <v>5.7685E-2</v>
       </c>
       <c r="G3" s="8">
         <v>283.27</v>
       </c>
-      <c r="I3" t="s">
-        <v>0</v>
-      </c>
-      <c r="J3" t="s">
-        <v>80</v>
-      </c>
-      <c r="K3" t="s">
-        <v>81</v>
-      </c>
-      <c r="L3" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+    </row>
+    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="1" t="s">
-        <v>6</v>
-      </c>
       <c r="C4" s="1">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="D4" s="5">
         <v>170.34</v>
@@ -3211,34 +3773,37 @@
         <v>5</v>
       </c>
       <c r="F4" s="6">
-        <f>C4*D4/(E4 * 1000)</f>
+        <f t="shared" ref="F4:F8" si="0">D4/(E4 * 1000)</f>
         <v>3.4068000000000001E-2</v>
       </c>
       <c r="G4">
         <v>488.46</v>
       </c>
-      <c r="I4" t="s">
-        <v>74</v>
-      </c>
       <c r="J4" t="s">
-        <v>75</v>
-      </c>
-      <c r="K4">
-        <v>117.49</v>
-      </c>
-      <c r="L4" s="18">
-        <v>0.69599999999999995</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+        <v>493</v>
+      </c>
+      <c r="K4" t="s">
+        <v>0</v>
+      </c>
+      <c r="L4" t="s">
+        <v>71</v>
+      </c>
+      <c r="M4" t="s">
+        <v>72</v>
+      </c>
+      <c r="N4" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A5" s="9" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>180</v>
+        <v>169</v>
       </c>
       <c r="C5" s="9">
-        <v>1</v>
+        <v>0.18</v>
       </c>
       <c r="D5" s="10">
         <f>54.4</f>
@@ -3248,35 +3813,49 @@
         <f>0.005*1000</f>
         <v>5</v>
       </c>
-      <c r="F5" s="12">
-        <f>C5*D5/(E5 * 1000)</f>
+      <c r="F5" s="6">
+        <f t="shared" si="0"/>
         <v>1.0879999999999999E-2</v>
       </c>
       <c r="G5">
         <v>54.4</v>
       </c>
-      <c r="I5" t="s">
-        <v>76</v>
-      </c>
       <c r="J5" t="s">
-        <v>42</v>
-      </c>
-      <c r="K5">
-        <v>26.98</v>
-      </c>
-      <c r="L5" s="19">
-        <v>0.16</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+        <v>6</v>
+      </c>
+      <c r="K5" t="s">
+        <v>68</v>
+      </c>
+      <c r="L5" t="s">
+        <v>69</v>
+      </c>
+      <c r="M5">
+        <v>117.49</v>
+      </c>
+      <c r="N5" s="18">
+        <v>0.7</v>
+      </c>
+      <c r="O5">
+        <v>99</v>
+      </c>
+      <c r="P5">
+        <f>M5*O5</f>
+        <v>11631.51</v>
+      </c>
+      <c r="Q5" s="58">
+        <f>P5/$P$8</f>
+        <v>0.70146498497745102</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B6" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="1" t="s">
-        <v>9</v>
-      </c>
       <c r="C6" s="1">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="D6" s="5">
         <f>(14.007*2)+(1.008*4)</f>
@@ -3287,34 +3866,48 @@
         <v>4</v>
       </c>
       <c r="F6" s="6">
-        <f>C6*D6/(E6 * 1000)</f>
+        <f t="shared" si="0"/>
         <v>8.0114999999999995E-3</v>
       </c>
       <c r="G6">
         <v>83.42</v>
       </c>
-      <c r="I6" t="s">
-        <v>77</v>
-      </c>
       <c r="J6" t="s">
-        <v>83</v>
-      </c>
-      <c r="K6">
-        <v>71.84</v>
-      </c>
-      <c r="L6" s="18">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+        <v>491</v>
+      </c>
+      <c r="K6" t="s">
+        <v>70</v>
+      </c>
+      <c r="L6" t="s">
+        <v>37</v>
+      </c>
+      <c r="M6">
+        <v>26.98</v>
+      </c>
+      <c r="N6" s="19">
+        <v>0.15</v>
+      </c>
+      <c r="O6">
+        <v>92</v>
+      </c>
+      <c r="P6">
+        <f t="shared" ref="P6:P7" si="1">M6*O6</f>
+        <v>2482.16</v>
+      </c>
+      <c r="Q6" s="58">
+        <f>P6/$P$8</f>
+        <v>0.14969237245307185</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B7" s="1" t="s">
-        <v>13</v>
-      </c>
       <c r="C7" s="1">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D7" s="5">
         <f>131.29</f>
@@ -3325,53 +3918,81 @@
         <v>0.1</v>
       </c>
       <c r="F7" s="6">
-        <f>C7*D7/(E7 * 1000)</f>
+        <f t="shared" si="0"/>
         <v>1.3129</v>
       </c>
       <c r="G7">
         <v>12.12</v>
       </c>
-      <c r="L7" s="18"/>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="J7" t="s">
+        <v>492</v>
+      </c>
+      <c r="K7" t="s">
+        <v>427</v>
+      </c>
+      <c r="L7" t="s">
+        <v>490</v>
+      </c>
+      <c r="M7">
+        <v>2468.0700000000002</v>
+      </c>
+      <c r="N7" s="18">
+        <v>0.15</v>
+      </c>
+      <c r="O7">
+        <v>1</v>
+      </c>
+      <c r="P7">
+        <f t="shared" si="1"/>
+        <v>2468.0700000000002</v>
+      </c>
+      <c r="Q7" s="58">
+        <f>P7/$P$8</f>
+        <v>0.14884264256947702</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="B8" s="1"/>
+        <v>67</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>494</v>
+      </c>
       <c r="C8" s="1">
-        <v>1</v>
-      </c>
-      <c r="D8" s="5"/>
+        <v>0.6</v>
+      </c>
+      <c r="D8" s="5">
+        <v>1658.174</v>
+      </c>
       <c r="E8" s="4">
         <f>0.0075*1000</f>
         <v>7.5</v>
       </c>
-      <c r="F8" s="6"/>
-      <c r="L8" s="18"/>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="I9" t="s">
-        <v>78</v>
-      </c>
-      <c r="J9" t="s">
-        <v>32</v>
-      </c>
-      <c r="L9" s="19">
-        <v>0.12</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="F8" s="6">
+        <f t="shared" si="0"/>
+        <v>0.22108986666666666</v>
+      </c>
+      <c r="N8" s="18"/>
+      <c r="P8">
+        <f>SUM(P5:P7)</f>
+        <v>16581.740000000002</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="L9" s="19"/>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>184</v>
+        <v>173</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>153</v>
+        <v>143</v>
       </c>
       <c r="C10" s="1">
-        <v>1</v>
+        <v>1.35</v>
       </c>
       <c r="D10" s="5">
-        <f>SUM(($D$47*0.5)+($D$99*0.5))</f>
+        <f>SUM(($D$51*0.5)+($D$109*0.5))</f>
         <v>46.073</v>
       </c>
       <c r="E10" s="4">
@@ -3379,32 +4000,24 @@
         <v>0.9</v>
       </c>
       <c r="F10" s="6">
-        <f t="shared" ref="F10:F20" si="0">C10*D10/(E10 * 1000)</f>
+        <f>D10/(E10 * 1000)</f>
         <v>5.1192222222222222E-2</v>
       </c>
       <c r="G10">
-        <f>(G47/2)+(G99/2)</f>
+        <f>(G51/2)+(G109/2)</f>
         <v>1623.855</v>
       </c>
-      <c r="I10" t="s">
-        <v>79</v>
-      </c>
-      <c r="J10" t="s">
-        <v>32</v>
-      </c>
-      <c r="L10" s="18">
-        <v>1.9599999999999999E-2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="L10" s="18"/>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="C11" s="1">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="D11" s="5">
         <v>101.96</v>
@@ -3414,22 +4027,22 @@
         <v>3.98</v>
       </c>
       <c r="F11" s="6">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="F11:F15" si="2">D11/(E11 * 1000)</f>
         <v>2.5618090452261304E-2</v>
       </c>
       <c r="G11">
         <v>52.79</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="C12" s="1">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="D12" s="5">
         <v>26.98</v>
@@ -3439,22 +4052,22 @@
         <v>2.77</v>
       </c>
       <c r="F12" s="6">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>9.7400722021660658E-3</v>
       </c>
       <c r="G12">
         <v>5.98</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B13" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B13" s="1" t="s">
-        <v>18</v>
-      </c>
       <c r="C13" s="1">
-        <v>1</v>
+        <v>1.4999999999999999E-4</v>
       </c>
       <c r="D13" s="5">
         <v>17.03</v>
@@ -3464,22 +4077,22 @@
         <v>7.6899999999999994E-4</v>
       </c>
       <c r="F13" s="6">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>22.145643693107935</v>
       </c>
       <c r="G13">
         <v>55.3</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B14" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="C14" s="1">
-        <v>1</v>
+        <v>1.0500000000000001E-2</v>
       </c>
       <c r="D14" s="5">
         <v>39.950000000000003</v>
@@ -3489,2529 +4102,2906 @@
         <v>1.784E-3</v>
       </c>
       <c r="F14" s="6">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>22.393497757847534</v>
       </c>
       <c r="G14">
         <v>15.75</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A15" s="29" t="s">
-        <v>200</v>
-      </c>
-      <c r="B15" s="29" t="s">
-        <v>201</v>
-      </c>
-      <c r="C15" s="29">
-        <v>1</v>
-      </c>
-      <c r="D15" s="30">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A15" s="1" t="s">
+        <v>422</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="C15" s="1">
+        <v>0.5213333</v>
+      </c>
+      <c r="D15" s="5">
+        <v>93.13</v>
+      </c>
+      <c r="E15" s="4">
+        <f>0.00102*1000</f>
+        <v>1.02</v>
+      </c>
+      <c r="F15" s="6">
+        <f t="shared" si="2"/>
+        <v>9.1303921568627447E-2</v>
+      </c>
+      <c r="G15">
+        <v>177.22</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A16" s="29" t="s">
+        <v>188</v>
+      </c>
+      <c r="B16" s="29" t="s">
+        <v>189</v>
+      </c>
+      <c r="C16" s="29">
+        <v>250</v>
+      </c>
+      <c r="D16" s="30">
         <v>9.01</v>
       </c>
-      <c r="E15" s="31">
+      <c r="E16" s="31">
         <f>0.0007508*1000</f>
         <v>0.75080000000000002</v>
       </c>
-      <c r="F15" s="32">
-        <f t="shared" si="0"/>
+      <c r="F16" s="32">
+        <f>D16/(E16 * 1000)</f>
         <v>1.2000532765050611E-2</v>
       </c>
-      <c r="G15">
+      <c r="G16">
         <v>9.32</v>
       </c>
-      <c r="H15">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A16" s="29" t="s">
-        <v>202</v>
-      </c>
-      <c r="B16" s="29" t="s">
-        <v>203</v>
-      </c>
-      <c r="C16" s="29">
-        <v>1</v>
-      </c>
-      <c r="D16" s="30">
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" s="29" t="s">
+        <v>190</v>
+      </c>
+      <c r="B17" s="29" t="s">
+        <v>191</v>
+      </c>
+      <c r="C17" s="29">
+        <v>0.8</v>
+      </c>
+      <c r="D17" s="30">
         <v>66.02</v>
       </c>
-      <c r="E16" s="31">
+      <c r="E17" s="31">
         <f>0.00244518*1000</f>
         <v>2.4451800000000001</v>
       </c>
-      <c r="F16" s="32">
-        <f t="shared" si="0"/>
+      <c r="F17" s="32">
+        <f t="shared" ref="F17:F18" si="3">D17/(E17 * 1000)</f>
         <v>2.7000057255498568E-2</v>
       </c>
-      <c r="G16">
+      <c r="G17">
         <v>59.47</v>
       </c>
-      <c r="H16">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A17" s="29" t="s">
-        <v>235</v>
-      </c>
-      <c r="B17" s="29" t="s">
-        <v>230</v>
-      </c>
-      <c r="C17" s="29">
-        <v>1</v>
-      </c>
-      <c r="D17" s="30">
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" s="29" t="s">
+        <v>218</v>
+      </c>
+      <c r="B18" s="29" t="s">
+        <v>214</v>
+      </c>
+      <c r="C18" s="29"/>
+      <c r="D18" s="30">
         <v>720.6</v>
       </c>
-      <c r="E17" s="31">
+      <c r="E18" s="31">
         <f>0.126*1000</f>
         <v>126</v>
       </c>
-      <c r="F17" s="32">
-        <f t="shared" si="0"/>
+      <c r="F18" s="32">
+        <f t="shared" si="3"/>
         <v>5.7190476190476193E-3</v>
       </c>
-      <c r="G17">
+      <c r="G18">
         <v>675.6</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A18" s="9" t="s">
-        <v>204</v>
-      </c>
-      <c r="B18" s="9" t="s">
-        <v>205</v>
-      </c>
-      <c r="C18" s="9">
-        <v>1</v>
-      </c>
-      <c r="D18" s="10">
-        <v>10.81</v>
-      </c>
-      <c r="E18" s="11">
-        <f>D18/H18</f>
-        <v>0.90083333333333337</v>
-      </c>
-      <c r="F18" s="12">
-        <f t="shared" si="0"/>
-        <v>1.2E-2</v>
-      </c>
-      <c r="G18">
-        <v>8.2899999999999991</v>
-      </c>
-      <c r="H18">
-        <v>12</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="9" t="s">
-        <v>216</v>
+        <v>192</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>217</v>
+        <v>193</v>
       </c>
       <c r="C19" s="9">
-        <v>1</v>
+        <v>0.85099999999999998</v>
       </c>
       <c r="D19" s="10">
+        <v>10.81</v>
+      </c>
+      <c r="E19" s="11">
+        <f>0.00246*1000</f>
+        <v>2.46</v>
+      </c>
+      <c r="F19" s="12">
+        <f>D19/(E19 * 1000)</f>
+        <v>4.3943089430894307E-3</v>
+      </c>
+      <c r="G19">
+        <v>8.2899999999999991</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" s="9" t="s">
+        <v>203</v>
+      </c>
+      <c r="B20" s="9" t="s">
+        <v>204</v>
+      </c>
+      <c r="C20" s="9">
+        <v>77</v>
+      </c>
+      <c r="D20" s="10">
         <v>132.91</v>
       </c>
-      <c r="E19" s="11">
+      <c r="E20" s="11">
         <f>0.00193*1000</f>
         <v>1.9300000000000002</v>
       </c>
-      <c r="F19" s="12">
-        <f t="shared" si="0"/>
+      <c r="F20" s="12">
+        <f t="shared" ref="F20:F36" si="4">D20/(E20 * 1000)</f>
         <v>6.8865284974093249E-2</v>
       </c>
-      <c r="G19" s="33">
+      <c r="G20" s="33">
         <v>3.89</v>
       </c>
-      <c r="H19" s="33"/>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A20" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="C20" s="1">
-        <v>1</v>
-      </c>
-      <c r="D20" s="5">
+      <c r="H20" s="33"/>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" s="9" t="s">
+        <v>234</v>
+      </c>
+      <c r="B21" s="9" t="s">
+        <v>223</v>
+      </c>
+      <c r="C21" s="9">
+        <v>1.4999999999999999E-4</v>
+      </c>
+      <c r="D21" s="10">
+        <v>40.08</v>
+      </c>
+      <c r="E21" s="11">
+        <f>0.00155*1000</f>
+        <v>1.55</v>
+      </c>
+      <c r="F21" s="12">
+        <f t="shared" si="4"/>
+        <v>2.5858064516129032E-2</v>
+      </c>
+      <c r="G21" s="33">
+        <v>6.11</v>
+      </c>
+      <c r="H21" s="33"/>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C22" s="1">
+        <v>0</v>
+      </c>
+      <c r="D22" s="5">
         <v>12.01</v>
       </c>
-      <c r="E20" s="4">
+      <c r="E22" s="4">
         <f>0.0021*1000</f>
         <v>2.1</v>
       </c>
-      <c r="F20" s="6">
-        <f t="shared" si="0"/>
+      <c r="F22" s="12">
+        <f t="shared" si="4"/>
         <v>5.7190476190476193E-3</v>
       </c>
-      <c r="G20">
+      <c r="G22">
         <v>11.26</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A21" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="C21" s="1">
-        <v>1</v>
-      </c>
-      <c r="D21" s="5">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C23" s="1">
+        <v>2.8636999999999998E-6</v>
+      </c>
+      <c r="D23" s="5">
         <v>44.01</v>
       </c>
-      <c r="E21" s="4">
+      <c r="E23" s="4">
         <f>0.000001951*1000</f>
         <v>1.951E-3</v>
       </c>
-      <c r="F21" s="6">
-        <f t="shared" ref="F21:F47" si="1">C21*D21/(E21 * 1000)</f>
+      <c r="F23" s="12">
+        <f t="shared" si="4"/>
         <v>22.557662737057917</v>
       </c>
-      <c r="G21">
+      <c r="G23">
         <v>38.479999999999997</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A22" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>179</v>
-      </c>
-      <c r="C22" s="1">
-        <v>1</v>
-      </c>
-      <c r="D22" s="5">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="C24" s="1">
+        <v>3.32E-6</v>
+      </c>
+      <c r="D24" s="5">
         <v>28.01</v>
       </c>
-      <c r="E22" s="4">
+      <c r="E24" s="4">
         <f>0.00000125*1000</f>
         <v>1.25E-3</v>
       </c>
-      <c r="F22" s="6">
-        <f t="shared" si="1"/>
+      <c r="F24" s="12">
+        <f t="shared" si="4"/>
         <v>22.408000000000001</v>
       </c>
-      <c r="G22">
+      <c r="G24">
         <v>24.87</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A23" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="B23" s="1"/>
-      <c r="C23" s="1">
-        <v>1</v>
-      </c>
-      <c r="D23" s="5"/>
-      <c r="E23" s="4">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A25" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>483</v>
+      </c>
+      <c r="C25" s="1">
+        <v>16</v>
+      </c>
+      <c r="D25" s="5">
+        <v>558.47</v>
+      </c>
+      <c r="E25" s="4">
         <f>0.0025*1000</f>
         <v>2.5</v>
       </c>
-      <c r="F23" s="6"/>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A24" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="C24" s="1">
-        <v>1</v>
-      </c>
-      <c r="D24" s="5">
+      <c r="F25" s="6">
+        <f t="shared" si="4"/>
+        <v>0.223388</v>
+      </c>
+      <c r="G25">
+        <v>373.39</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A26" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>360</v>
+      </c>
+      <c r="C26" s="1">
+        <v>1.4999999999999999E-4</v>
+      </c>
+      <c r="D26" s="5">
         <v>35.450000000000003</v>
       </c>
-      <c r="E24" s="4">
+      <c r="E26" s="4">
         <f>0.0032*1000</f>
         <v>3.2</v>
       </c>
-      <c r="F24" s="6">
-        <f t="shared" si="1"/>
+      <c r="F26" s="12">
+        <f t="shared" si="4"/>
         <v>1.1078125000000001E-2</v>
       </c>
-      <c r="G24">
+      <c r="G26">
         <v>12.96</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A25" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="B25" s="1"/>
-      <c r="C25" s="1">
-        <v>1</v>
-      </c>
-      <c r="D25" s="5"/>
-      <c r="E25" s="4">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A27" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="B27" s="1"/>
+      <c r="C27" s="1">
+        <v>15</v>
+      </c>
+      <c r="D27" s="5"/>
+      <c r="E27" s="4">
         <f>0.001556*1000</f>
         <v>1.556</v>
       </c>
-      <c r="F25" s="6"/>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A26" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="C26" s="1">
-        <v>1</v>
-      </c>
-      <c r="D26" s="5">
+      <c r="F27" s="6"/>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A28" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="C28" s="1">
+        <v>0</v>
+      </c>
+      <c r="D28" s="5">
         <v>238.03</v>
       </c>
-      <c r="E26" s="4">
+      <c r="E28" s="4">
         <f>0.01097*1000</f>
         <v>10.97</v>
       </c>
-      <c r="F26" s="6">
-        <f t="shared" si="1"/>
+      <c r="F28" s="12">
+        <f t="shared" si="4"/>
         <v>2.1698268003646309E-2</v>
       </c>
-      <c r="G26">
+      <c r="G28">
         <v>6.19</v>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A27" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="C27" s="1">
-        <v>1</v>
-      </c>
-      <c r="D27" s="5">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A29" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="C29" s="1">
+        <v>2.7999999999999998E-4</v>
+      </c>
+      <c r="D29" s="5">
         <v>2.0139999999999998</v>
       </c>
-      <c r="E27" s="4">
+      <c r="E29" s="4">
         <f>0.00000018*1000</f>
         <v>1.7999999999999998E-4</v>
       </c>
-      <c r="F27" s="6">
-        <f t="shared" si="1"/>
+      <c r="F29" s="12">
+        <f t="shared" si="4"/>
         <v>11.188888888888888</v>
       </c>
-      <c r="G27" s="8">
+      <c r="G29" s="8">
         <v>13.59</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A28" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="C28" s="1">
-        <v>1</v>
-      </c>
-      <c r="D28" s="5">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A30" s="1" t="s">
+        <v>416</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>417</v>
+      </c>
+      <c r="C30" s="1">
+        <v>4.21</v>
+      </c>
+      <c r="D30" s="5">
+        <v>27.67</v>
+      </c>
+      <c r="E30" s="4">
+        <f>0.000421*1000</f>
+        <v>0.42099999999999999</v>
+      </c>
+      <c r="F30" s="12">
+        <f t="shared" si="4"/>
+        <v>6.5724465558194778E-2</v>
+      </c>
+      <c r="G30" s="8">
+        <v>98.12</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A31" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="C31" s="1">
+        <v>0.3</v>
+      </c>
+      <c r="D31" s="5">
         <v>60.08</v>
       </c>
-      <c r="E28" s="4">
+      <c r="E31" s="4">
         <f>0.0016*1000</f>
         <v>1.6</v>
       </c>
-      <c r="F28" s="6">
-        <f t="shared" si="1"/>
+      <c r="F31" s="12">
+        <f t="shared" si="4"/>
         <v>3.755E-2</v>
       </c>
-      <c r="G28">
+      <c r="G31">
         <v>35.369999999999997</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A29" s="1" t="s">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A32" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="B32" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="B29" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="C29" s="1">
-        <v>1</v>
-      </c>
-      <c r="D29" s="5">
+      <c r="C32" s="1">
+        <v>865</v>
+      </c>
+      <c r="D32" s="5">
         <v>238.03</v>
       </c>
-      <c r="E29" s="4">
+      <c r="E32" s="4">
         <f>0.01097*1000</f>
         <v>10.97</v>
       </c>
-      <c r="F29" s="6">
-        <f t="shared" si="1"/>
+      <c r="F32" s="12">
+        <f t="shared" si="4"/>
         <v>2.1698268003646309E-2</v>
       </c>
-      <c r="G29">
+      <c r="G32">
         <v>6.19</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A30" s="1" t="s">
-        <v>175</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>176</v>
-      </c>
-      <c r="C30" s="1">
-        <v>1</v>
-      </c>
-      <c r="D30" s="5">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A33" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="C33" s="1">
+        <v>0.12623999999999999</v>
+      </c>
+      <c r="D33" s="5">
         <v>46.07</v>
       </c>
-      <c r="E30" s="4">
+      <c r="E33" s="4">
         <f>0.000789*1000</f>
         <v>0.78900000000000003</v>
       </c>
-      <c r="F30" s="6">
-        <f>C30*D30/(E30 * 1000)</f>
+      <c r="F33" s="12">
+        <f t="shared" si="4"/>
         <v>5.8390367553865653E-2</v>
       </c>
-      <c r="G30">
+      <c r="G33">
         <v>117.67</v>
       </c>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A31" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="B31" s="1" t="s">
-        <v>183</v>
-      </c>
-      <c r="C31" s="1">
-        <v>1</v>
-      </c>
-      <c r="D31" s="5">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A34" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="C34" s="1">
+        <v>0.12623999999999999</v>
+      </c>
+      <c r="D34" s="5">
         <v>61.206800000000001</v>
       </c>
-      <c r="E31" s="4">
+      <c r="E34" s="4">
         <f>0.00084175*1000</f>
         <v>0.84175</v>
       </c>
-      <c r="F31" s="6">
-        <f>C31*D31/(E31 * 1000)</f>
+      <c r="F34" s="12">
+        <f t="shared" si="4"/>
         <v>7.2713751113751113E-2</v>
       </c>
-      <c r="G31">
+      <c r="G34">
         <v>393.8</v>
       </c>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A32" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="B32" s="1" t="s">
-        <v>218</v>
-      </c>
-      <c r="C32" s="1">
-        <v>1</v>
-      </c>
-      <c r="D32" s="5">
-        <v>668.34</v>
-      </c>
-      <c r="E32" s="4">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A35" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>485</v>
+      </c>
+      <c r="C35" s="1">
+        <v>160</v>
+      </c>
+      <c r="D35" s="5">
+        <v>953.52809999999999</v>
+      </c>
+      <c r="E35" s="4">
         <f>0.0025*1000</f>
         <v>2.5</v>
       </c>
-      <c r="F32" s="6">
-        <f t="shared" si="1"/>
-        <v>0.26733600000000002</v>
-      </c>
-      <c r="G32">
-        <v>333.76</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A33" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="B33" s="1"/>
-      <c r="C33" s="1">
-        <v>1</v>
-      </c>
-      <c r="D33" s="5"/>
-      <c r="E33" s="4">
-        <f>0.001*1000</f>
-        <v>1</v>
-      </c>
-      <c r="F33" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A34" s="29" t="s">
-        <v>209</v>
-      </c>
-      <c r="B34" s="29" t="s">
-        <v>211</v>
-      </c>
-      <c r="C34" s="29">
-        <v>1</v>
-      </c>
-      <c r="D34" s="30">
-        <v>412.91</v>
-      </c>
-      <c r="E34" s="31">
-        <f>0.001556*1000</f>
-        <v>1.556</v>
-      </c>
-      <c r="F34" s="32">
-        <f t="shared" si="1"/>
-        <v>0.26536632390745502</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A35" s="29" t="s">
-        <v>210</v>
-      </c>
-      <c r="B35" s="29" t="s">
-        <v>212</v>
-      </c>
-      <c r="C35" s="29">
-        <v>1</v>
-      </c>
-      <c r="D35" s="30">
-        <v>278.13</v>
-      </c>
-      <c r="E35" s="31">
-        <f>0.00321*1000</f>
-        <v>3.21</v>
-      </c>
-      <c r="F35" s="32">
-        <f t="shared" si="1"/>
-        <v>8.6644859813084105E-2</v>
+      <c r="F35" s="12">
+        <f t="shared" si="4"/>
+        <v>0.38141123999999998</v>
+      </c>
+      <c r="G35">
+        <v>386.86</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="B36" s="1"/>
+        <v>117</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>480</v>
+      </c>
       <c r="C36" s="1">
-        <v>1</v>
-      </c>
-      <c r="D36" s="5"/>
+        <v>2</v>
+      </c>
+      <c r="D36" s="5">
+        <v>852.68320000000006</v>
+      </c>
       <c r="E36" s="4">
         <f>0.001*1000</f>
         <v>1</v>
       </c>
-      <c r="F36" s="6"/>
+      <c r="F36" s="12">
+        <f t="shared" si="4"/>
+        <v>0.85268320000000009</v>
+      </c>
+      <c r="G36">
+        <v>475.54</v>
+      </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A37" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="B37" s="1" t="s">
-        <v>222</v>
-      </c>
-      <c r="C37" s="1">
+      <c r="A37" s="29" t="s">
+        <v>197</v>
+      </c>
+      <c r="B37" s="29" t="s">
+        <v>199</v>
+      </c>
+      <c r="C37" s="29">
+        <v>920</v>
+      </c>
+      <c r="D37" s="30">
+        <v>412.91</v>
+      </c>
+      <c r="E37" s="31">
+        <f>0.001556*1000</f>
+        <v>1.556</v>
+      </c>
+      <c r="F37" s="32">
+        <f>D37/(E37 * 1000)</f>
+        <v>0.26536632390745502</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A38" s="29" t="s">
+        <v>198</v>
+      </c>
+      <c r="B38" s="29" t="s">
+        <v>200</v>
+      </c>
+      <c r="C38" s="29">
+        <v>1150</v>
+      </c>
+      <c r="D38" s="30">
+        <v>278.13</v>
+      </c>
+      <c r="E38" s="31">
+        <f>0.00321*1000</f>
+        <v>3.21</v>
+      </c>
+      <c r="F38" s="32">
+        <f>D38/(E38 * 1000)</f>
+        <v>8.6644859813084105E-2</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A39" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="B39" s="1"/>
+      <c r="C39" s="1">
+        <v>12</v>
+      </c>
+      <c r="D39" s="5"/>
+      <c r="E39" s="4">
+        <f>0.001*1000</f>
         <v>1</v>
       </c>
-      <c r="D37" s="5">
+      <c r="F39" s="6"/>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A40" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="C40" s="1">
+        <v>175</v>
+      </c>
+      <c r="D40" s="5">
         <v>741.30799999999999</v>
       </c>
-      <c r="E37" s="4">
+      <c r="E40" s="4">
         <f>0.05*1000</f>
         <v>50</v>
       </c>
-      <c r="F37" s="6">
-        <f t="shared" si="1"/>
+      <c r="F40" s="12">
+        <f t="shared" ref="F40:F72" si="5">D40/(E40 * 1000)</f>
         <v>1.482616E-2</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A38" s="1" t="s">
-        <v>166</v>
-      </c>
-      <c r="B38" s="1" t="s">
-        <v>242</v>
-      </c>
-      <c r="C38" s="1">
-        <v>1</v>
-      </c>
-      <c r="D38" s="5">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A41" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="C41" s="1">
+        <v>1.0175999999999999E-2</v>
+      </c>
+      <c r="D41" s="5">
         <v>19</v>
       </c>
-      <c r="E38" s="4">
-        <f>0.0032*1000</f>
-        <v>3.2</v>
-      </c>
-      <c r="F38" s="6">
-        <f t="shared" si="1"/>
-        <v>5.9375000000000001E-3</v>
-      </c>
-      <c r="G38">
-        <v>34.840000000000003</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A39" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="B39" s="1"/>
-      <c r="C39" s="1"/>
-      <c r="D39" s="5"/>
-      <c r="E39" s="4">
+      <c r="E41" s="4">
+        <f>0.000001696*1000</f>
+        <v>1.696E-3</v>
+      </c>
+      <c r="F41" s="12">
+        <f t="shared" si="5"/>
+        <v>11.202830188679245</v>
+      </c>
+      <c r="G41">
+        <v>17.420000000000002</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A42" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="C42" s="1">
+        <v>0.238874700854701</v>
+      </c>
+      <c r="D42" s="5">
+        <v>103.14</v>
+      </c>
+      <c r="E42" s="4">
         <f xml:space="preserve"> 0.00028102905982906*1000</f>
         <v>0.28102905982906001</v>
       </c>
-      <c r="F39" s="6"/>
-    </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A40" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="B40" s="1" t="s">
-        <v>192</v>
-      </c>
-      <c r="C40" s="1">
-        <v>1</v>
-      </c>
-      <c r="D40" s="5">
+      <c r="F42" s="12">
+        <f t="shared" si="5"/>
+        <v>0.36700830890135128</v>
+      </c>
+      <c r="G42">
+        <v>233.01</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A43" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>439</v>
+      </c>
+      <c r="C43" s="1">
+        <v>150</v>
+      </c>
+      <c r="D43" s="5">
         <f>5.03</f>
         <v>5.03</v>
       </c>
-      <c r="E40" s="4">
+      <c r="E43" s="4">
         <f>0.000216*1000</f>
         <v>0.216</v>
       </c>
-      <c r="F40" s="6">
-        <f t="shared" si="1"/>
+      <c r="F43" s="12">
+        <f t="shared" si="5"/>
         <v>2.3287037037037037E-2</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A41" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="B41" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="C41" s="1">
-        <v>1</v>
-      </c>
-      <c r="D41" s="5">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A44" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="C44" s="1">
+        <v>2</v>
+      </c>
+      <c r="D44" s="5">
         <v>92.09</v>
       </c>
-      <c r="E41" s="4">
+      <c r="E44" s="4">
         <f>0.012*1000</f>
         <v>12</v>
       </c>
-      <c r="F41" s="6">
-        <f t="shared" si="1"/>
+      <c r="F44" s="12">
+        <f t="shared" si="5"/>
         <v>7.6741666666666668E-3</v>
       </c>
-      <c r="G41">
+      <c r="G44">
         <v>3299.94</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A42" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B42" s="1" t="s">
-        <v>429</v>
-      </c>
-      <c r="C42" s="1">
-        <v>1</v>
-      </c>
-      <c r="D42" s="5">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A45" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>484</v>
+      </c>
+      <c r="C45" s="1">
+        <v>0.01</v>
+      </c>
+      <c r="D45" s="5">
         <v>172.14</v>
       </c>
-      <c r="E42" s="4">
+      <c r="E45" s="4">
         <f>0.0055*1000</f>
         <v>5.5</v>
       </c>
-      <c r="F42" s="6">
-        <f t="shared" si="1"/>
+      <c r="F45" s="12">
+        <f t="shared" si="5"/>
         <v>3.1298181818181815E-2</v>
       </c>
-      <c r="G42">
+      <c r="G45">
         <v>1764.9</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A43" s="1" t="s">
-        <v>171</v>
-      </c>
-      <c r="B43" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="C43" s="1">
-        <v>1</v>
-      </c>
-      <c r="D43" s="5">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A46" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="C46" s="1">
+        <v>0.11126999999999999</v>
+      </c>
+      <c r="D46" s="5">
         <v>3.016</v>
       </c>
-      <c r="E43" s="4">
+      <c r="E46" s="4">
         <f>0.000000125*1000</f>
         <v>1.25E-4</v>
       </c>
-      <c r="F43" s="6">
-        <f>C43*D43/(E43 * 1000)</f>
+      <c r="F46" s="12">
+        <f t="shared" si="5"/>
         <v>24.128</v>
       </c>
-      <c r="G43">
+      <c r="G46">
         <v>24.58</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A44" s="1" t="s">
-        <v>172</v>
-      </c>
-      <c r="B44" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="C44" s="1">
-        <v>1</v>
-      </c>
-      <c r="D44" s="5">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A47" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="C47" s="1">
+        <v>9.0999999999999993E-6</v>
+      </c>
+      <c r="D47" s="5">
         <v>4.0019999999999998</v>
       </c>
-      <c r="E44" s="4">
+      <c r="E47" s="4">
         <f>0.0000001786*1000</f>
         <v>1.786E-4</v>
       </c>
-      <c r="F44" s="6">
-        <f>C44*D44/(E44 * 1000)</f>
+      <c r="F47" s="12">
+        <f t="shared" si="5"/>
         <v>22.407614781634937</v>
       </c>
-      <c r="G44">
+      <c r="G47">
         <v>24.58</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A45" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="B45" s="1" t="s">
-        <v>180</v>
-      </c>
-      <c r="C45" s="1">
-        <v>1</v>
-      </c>
-      <c r="D45" s="5">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A48" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="C48" s="1">
+        <v>2.1465000000000001</v>
+      </c>
+      <c r="D48" s="5">
         <v>34.01</v>
       </c>
-      <c r="E45" s="4">
+      <c r="E48" s="4">
         <f>0.001431*1000</f>
         <v>1.431</v>
       </c>
-      <c r="F45" s="6">
-        <f>C45*D45/(E45 * 1000)</f>
+      <c r="F48" s="12">
+        <f t="shared" si="5"/>
         <v>2.3766596785464708E-2</v>
       </c>
-      <c r="G45">
+      <c r="G48">
         <v>54.4</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A46" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B46" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="C46" s="1">
-        <v>1</v>
-      </c>
-      <c r="D46" s="5">
-        <v>168.69</v>
-      </c>
-      <c r="E46" s="4">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A49" s="1" t="s">
+        <v>427</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>490</v>
+      </c>
+      <c r="C49" s="1">
+        <v>1.8585</v>
+      </c>
+      <c r="D49" s="5">
+        <v>2468.0700000000002</v>
+      </c>
+      <c r="E49" s="4">
+        <f>0.00177*1000</f>
+        <v>1.77</v>
+      </c>
+      <c r="F49" s="12">
+        <f t="shared" si="5"/>
+        <v>1.3943898305084748</v>
+      </c>
+      <c r="G49">
+        <v>5750.5</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A50" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>481</v>
+      </c>
+      <c r="C50" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="D50" s="5">
+        <v>1009.6214</v>
+      </c>
+      <c r="E50" s="4">
         <f>0.0015*1000</f>
         <v>1.5</v>
       </c>
-      <c r="F46" s="6">
-        <f t="shared" si="1"/>
-        <v>0.11246</v>
-      </c>
-      <c r="G46">
-        <v>77.025000000000006</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A47" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="B47" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="C47" s="1">
-        <v>1</v>
-      </c>
-      <c r="D47" s="5">
+      <c r="F50" s="12">
+        <f t="shared" si="5"/>
+        <v>0.6730809333333333</v>
+      </c>
+      <c r="G50">
+        <v>760.01</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A51" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="C51" s="1">
+        <v>2.008</v>
+      </c>
+      <c r="D51" s="5">
         <f>(14.007*2)+(1.008*4)</f>
         <v>32.045999999999999</v>
       </c>
-      <c r="E47" s="4">
+      <c r="E51" s="4">
         <f>0.001004*1000</f>
         <v>1.004</v>
       </c>
-      <c r="F47" s="6">
-        <f t="shared" si="1"/>
+      <c r="F51" s="12">
+        <f t="shared" si="5"/>
         <v>3.1918326693227091E-2</v>
       </c>
-      <c r="G47">
+      <c r="G51">
         <v>41.71</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A48" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="B48" s="1" t="s">
-        <v>384</v>
-      </c>
-      <c r="C48" s="1">
-        <v>1</v>
-      </c>
-      <c r="D48" s="5">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A52" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>367</v>
+      </c>
+      <c r="C52" s="1">
+        <v>5.5835999999999999E-5</v>
+      </c>
+      <c r="D52" s="5">
         <v>1.01</v>
       </c>
-      <c r="E48" s="4">
+      <c r="E52" s="4">
         <f>0.0000000899*1000</f>
         <v>8.9900000000000003E-5</v>
       </c>
-      <c r="F48" s="6">
-        <f t="shared" ref="F48:F61" si="2">C48*D48/(E48 * 1000)</f>
+      <c r="F52" s="12">
+        <f t="shared" si="5"/>
         <v>11.234705228031144</v>
       </c>
-      <c r="G48" s="8">
+      <c r="G52" s="8">
         <v>13.59</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A49" s="1" t="s">
-        <v>174</v>
-      </c>
-      <c r="B49" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C49" s="1">
-        <v>1</v>
-      </c>
-      <c r="D49" s="5">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A53" s="1" t="s">
+        <v>424</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>425</v>
+      </c>
+      <c r="C53" s="1">
+        <v>0.31773000000000001</v>
+      </c>
+      <c r="D53" s="5">
+        <v>63.01</v>
+      </c>
+      <c r="E53" s="4">
+        <f>0.001513*1000</f>
+        <v>1.5130000000000001</v>
+      </c>
+      <c r="F53" s="12">
+        <f t="shared" si="5"/>
+        <v>4.1645736946463972E-2</v>
+      </c>
+      <c r="G53" s="8">
+        <v>68.95</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A54" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C54" s="1">
+        <v>4.1000000000000002E-2</v>
+      </c>
+      <c r="D54" s="5">
         <v>170.34</v>
       </c>
-      <c r="E49" s="4">
+      <c r="E54" s="4">
         <f>0.00082*1000</f>
         <v>0.82</v>
       </c>
-      <c r="F49" s="6">
-        <f>C49*D49/(E49 * 1000)</f>
+      <c r="F54" s="12">
+        <f t="shared" si="5"/>
         <v>0.20773170731707319</v>
       </c>
-      <c r="G49">
+      <c r="G54">
         <v>488.46</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A50" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="B50" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="C50" s="1">
-        <v>1</v>
-      </c>
-      <c r="D50" s="5">
+    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A55" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="C55" s="1">
+        <v>0.60750000000000004</v>
+      </c>
+      <c r="D55" s="5">
         <v>6.94</v>
       </c>
-      <c r="E50" s="4">
+      <c r="E55" s="4">
         <f>0.000534*1000</f>
         <v>0.53399999999999992</v>
       </c>
-      <c r="F50" s="6">
-        <f t="shared" si="2"/>
+      <c r="F55" s="12">
+        <f t="shared" si="5"/>
         <v>1.2996254681647943E-2</v>
       </c>
-      <c r="G50" s="8">
+      <c r="G55" s="8">
         <v>5.39</v>
       </c>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A51" s="29" t="s">
-        <v>233</v>
-      </c>
-      <c r="B51" s="29" t="s">
-        <v>234</v>
-      </c>
-      <c r="C51" s="29">
-        <v>1</v>
-      </c>
-      <c r="D51" s="30">
+    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A56" s="1" t="s">
+        <v>434</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>437</v>
+      </c>
+      <c r="C56" s="1">
+        <v>4</v>
+      </c>
+      <c r="D56" s="5">
+        <v>6.94</v>
+      </c>
+      <c r="E56" s="4">
+        <f>0.000458*1000</f>
+        <v>0.45800000000000002</v>
+      </c>
+      <c r="F56" s="12">
+        <f t="shared" si="5"/>
+        <v>1.5152838427947599E-2</v>
+      </c>
+      <c r="G56" s="8">
+        <v>5.39</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A57" s="1" t="s">
+        <v>435</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>438</v>
+      </c>
+      <c r="C57" s="1">
+        <v>5</v>
+      </c>
+      <c r="D57" s="5">
+        <v>8.0079999999999991</v>
+      </c>
+      <c r="E57" s="4">
+        <f>0.00082*1000</f>
+        <v>0.82</v>
+      </c>
+      <c r="F57" s="12">
+        <f t="shared" si="5"/>
+        <v>9.7658536585365843E-3</v>
+      </c>
+      <c r="G57" s="8">
+        <v>18.98</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A58" s="29" t="s">
+        <v>217</v>
+      </c>
+      <c r="B58" s="29" t="s">
+        <v>436</v>
+      </c>
+      <c r="C58" s="29">
+        <v>7</v>
+      </c>
+      <c r="D58" s="30">
         <v>153.114</v>
       </c>
-      <c r="E51" s="31">
+      <c r="E58" s="31">
         <f>0.0086964*1000</f>
         <v>8.6964000000000006</v>
       </c>
-      <c r="F51" s="32">
-        <f t="shared" si="2"/>
+      <c r="F58" s="32">
+        <f>D58/(E58 * 1000)</f>
         <v>1.7606595832758379E-2</v>
       </c>
-      <c r="G51" s="44">
+      <c r="G58" s="44">
         <v>6215.4</v>
       </c>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A52" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B52" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C52" s="1">
-        <v>1</v>
-      </c>
-      <c r="D52" s="5">
+    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A59" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C59" s="1">
+        <v>0.14199999999999999</v>
+      </c>
+      <c r="D59" s="5">
         <v>17.03</v>
       </c>
-      <c r="E52" s="4">
+      <c r="E59" s="4">
         <f>0.0007021*1000</f>
         <v>0.70209999999999995</v>
       </c>
-      <c r="F52" s="6">
-        <f t="shared" si="2"/>
+      <c r="F59" s="12">
+        <f t="shared" si="5"/>
         <v>2.4255804016521866E-2</v>
       </c>
-      <c r="G52">
+      <c r="G59">
         <v>55.3</v>
       </c>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A53" s="1" t="s">
-        <v>394</v>
-      </c>
-      <c r="B53" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C53" s="1">
-        <v>1</v>
-      </c>
-      <c r="D53" s="5">
+    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A60" s="1" t="s">
+        <v>377</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C60" s="1">
+        <v>1.4</v>
+      </c>
+      <c r="D60" s="5">
         <v>39.950000000000003</v>
       </c>
-      <c r="E53" s="4">
+      <c r="E60" s="4">
         <f>0.0013954*1000</f>
         <v>1.3954</v>
       </c>
-      <c r="F53" s="6">
-        <f t="shared" si="2"/>
+      <c r="F60" s="12">
+        <f t="shared" si="5"/>
         <v>2.8629783574602271E-2</v>
       </c>
-      <c r="G53">
+      <c r="G60">
         <v>15.75</v>
       </c>
     </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A54" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="B54" s="1" t="s">
-        <v>179</v>
-      </c>
-      <c r="C54" s="1">
-        <v>1</v>
-      </c>
-      <c r="D54" s="5">
+    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A61" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="B61" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="C61" s="1">
+        <v>2.0999999999999999E-3</v>
+      </c>
+      <c r="D61" s="5">
         <v>28.01</v>
       </c>
-      <c r="E54" s="4">
+      <c r="E61" s="4">
         <f>0.00079*1000</f>
         <v>0.79</v>
       </c>
-      <c r="F54" s="6">
-        <f>C54*D54/(E54 * 1000)</f>
+      <c r="F61" s="12">
+        <f t="shared" si="5"/>
         <v>3.5455696202531646E-2</v>
       </c>
-      <c r="G54">
+      <c r="G61">
         <v>24.87</v>
       </c>
     </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A55" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B55" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="C55" s="1">
-        <v>1</v>
-      </c>
-      <c r="D55" s="5">
+    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A62" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B62" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C62" s="1">
+        <v>1.7247E-3</v>
+      </c>
+      <c r="D62" s="5">
         <v>44.01</v>
       </c>
-      <c r="E55" s="4">
+      <c r="E62" s="4">
         <f>0.00117325*1000</f>
         <v>1.1732500000000001</v>
       </c>
-      <c r="F55" s="6">
-        <f t="shared" si="2"/>
+      <c r="F62" s="12">
+        <f t="shared" si="5"/>
         <v>3.7511186874067751E-2</v>
       </c>
-      <c r="G55">
+      <c r="G62">
         <v>38.479999999999997</v>
       </c>
     </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A56" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="B56" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="C56" s="1">
-        <v>1</v>
-      </c>
-      <c r="D56" s="5">
+    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A63" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="B63" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="C63" s="1">
+        <v>0.25600000000000001</v>
+      </c>
+      <c r="D63" s="5">
         <v>2.0139999999999998</v>
       </c>
-      <c r="E56" s="4">
+      <c r="E63" s="4">
         <f>0.0001624*1000</f>
         <v>0.16239999999999999</v>
       </c>
-      <c r="F56" s="6">
-        <f t="shared" si="2"/>
+      <c r="F63" s="12">
+        <f t="shared" si="5"/>
         <v>1.2401477832512315E-2</v>
       </c>
-      <c r="G56">
+      <c r="G63">
         <v>13.59</v>
       </c>
     </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A57" s="1" t="s">
-        <v>237</v>
-      </c>
-      <c r="B57" s="1" t="s">
-        <v>242</v>
-      </c>
-      <c r="C57" s="1">
-        <v>1</v>
-      </c>
-      <c r="D57" s="5">
+    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A64" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="C64" s="1">
+        <v>9.0299999999999994</v>
+      </c>
+      <c r="D64" s="5">
         <v>19</v>
       </c>
-      <c r="E57" s="4">
+      <c r="E64" s="4">
         <f>0.001505*1000</f>
         <v>1.5050000000000001</v>
       </c>
-      <c r="F57" s="6">
-        <f t="shared" si="2"/>
+      <c r="F64" s="12">
+        <f t="shared" si="5"/>
         <v>1.2624584717607971E-2</v>
       </c>
-      <c r="G57">
-        <v>34.840000000000003</v>
-      </c>
-    </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A58" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="B58" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="C58" s="1">
-        <v>1</v>
-      </c>
-      <c r="D58" s="5">
+      <c r="G64">
+        <v>17.420000000000002</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A65" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="C65" s="1">
+        <v>52.52</v>
+      </c>
+      <c r="D65" s="5">
         <v>3.016</v>
       </c>
-      <c r="E58" s="4">
+      <c r="E65" s="4">
         <f>0.000059*1000</f>
         <v>5.8999999999999997E-2</v>
       </c>
-      <c r="F58" s="6">
-        <f>C58*D58/(E58 * 1000)</f>
+      <c r="F65" s="12">
+        <f t="shared" si="5"/>
         <v>5.1118644067796613E-2</v>
       </c>
-      <c r="G58">
+      <c r="G65">
         <v>24.58</v>
       </c>
     </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A59" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="B59" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="C59" s="1">
-        <v>1</v>
-      </c>
-      <c r="D59" s="5">
+    <row r="66" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A66" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="B66" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="C66" s="1">
+        <v>1.3299999999999999E-2</v>
+      </c>
+      <c r="D66" s="5">
         <v>4.0019999999999998</v>
       </c>
-      <c r="E59" s="4">
+      <c r="E66" s="4">
         <f>0.0001786*1000</f>
         <v>0.17860000000000001</v>
       </c>
-      <c r="F59" s="6">
-        <f>C59*D59/(E59 * 1000)</f>
+      <c r="F66" s="12">
+        <f t="shared" si="5"/>
         <v>2.2407614781634933E-2</v>
       </c>
-      <c r="G59">
+      <c r="G66">
         <v>24.58</v>
       </c>
     </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A60" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="B60" s="1" t="s">
-        <v>384</v>
-      </c>
-      <c r="C60" s="1">
-        <v>1</v>
-      </c>
-      <c r="D60" s="5">
+    <row r="67" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A67" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B67" s="1" t="s">
+        <v>367</v>
+      </c>
+      <c r="C67" s="1">
+        <v>3.6749999999999998E-2</v>
+      </c>
+      <c r="D67" s="5">
         <v>1.01</v>
       </c>
-      <c r="E60" s="4">
+      <c r="E67" s="4">
         <f>0.00007085*1000</f>
         <v>7.0849999999999996E-2</v>
       </c>
-      <c r="F60" s="6">
-        <f>C60*D60/(E60 * 1000)</f>
+      <c r="F67" s="12">
+        <f t="shared" si="5"/>
         <v>1.4255469301340862E-2</v>
       </c>
-      <c r="G60">
+      <c r="G67">
         <v>13.59</v>
       </c>
     </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A61" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B61" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C61" s="1">
-        <v>1</v>
-      </c>
-      <c r="D61" s="5">
+    <row r="68" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A68" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B68" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C68" s="1"/>
+      <c r="D68" s="5">
         <v>16.05</v>
       </c>
-      <c r="E61" s="4">
+      <c r="E68" s="4">
         <f>0.00042561*1000</f>
         <v>0.42560999999999999</v>
       </c>
-      <c r="F61" s="6">
-        <f t="shared" si="2"/>
+      <c r="F68" s="12">
+        <f t="shared" si="5"/>
         <v>3.7710580108550079E-2</v>
       </c>
-      <c r="G61">
+      <c r="G68">
         <v>65.62</v>
       </c>
     </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A62" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="B62" s="1" t="s">
-        <v>382</v>
-      </c>
-      <c r="C62" s="1">
-        <v>1</v>
-      </c>
-      <c r="D62" s="5">
+    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A69" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B69" s="1" t="s">
+        <v>365</v>
+      </c>
+      <c r="C69" s="1">
+        <v>8.2399999999999997E-4</v>
+      </c>
+      <c r="D69" s="5">
         <v>14.01</v>
       </c>
-      <c r="E62" s="4">
+      <c r="E69" s="4">
         <f>0.000824907*1000</f>
         <v>0.82490700000000006</v>
       </c>
-      <c r="F62" s="6">
-        <f>C62*D62/(E62 * 1000)</f>
+      <c r="F69" s="12">
+        <f t="shared" si="5"/>
         <v>1.6983732711687499E-2</v>
       </c>
-      <c r="G62">
+      <c r="G69">
         <v>14.53</v>
       </c>
     </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A63" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="B63" s="9" t="s">
-        <v>241</v>
-      </c>
-      <c r="C63" s="9">
-        <v>1</v>
-      </c>
-      <c r="D63" s="10">
+    <row r="70" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A70" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B70" s="9" t="s">
+        <v>224</v>
+      </c>
+      <c r="C70" s="9">
+        <v>4.564E-2</v>
+      </c>
+      <c r="D70" s="10">
         <v>16</v>
       </c>
-      <c r="E63" s="11">
+      <c r="E70" s="11">
         <f>0.001141*1000</f>
         <v>1.141</v>
       </c>
-      <c r="F63" s="12">
-        <f t="shared" ref="F63" si="3">C63*D63/(E63 * 1000)</f>
+      <c r="F70" s="12">
+        <f t="shared" si="5"/>
         <v>1.4022787028921999E-2</v>
       </c>
-      <c r="G63">
+      <c r="G70">
         <v>13.61</v>
       </c>
     </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A64" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="B64" s="1"/>
-      <c r="C64" s="1">
-        <v>1</v>
-      </c>
-      <c r="D64" s="5"/>
-      <c r="E64" s="4">
+    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A71" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="B71" s="1" t="s">
+        <v>482</v>
+      </c>
+      <c r="C71" s="1">
+        <v>15.8</v>
+      </c>
+      <c r="D71" s="5">
+        <v>570.41099999999994</v>
+      </c>
+      <c r="E71" s="4">
         <f>0.00378*1000</f>
         <v>3.78</v>
       </c>
-      <c r="F64" s="6"/>
-    </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A65" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="B65" s="1"/>
-      <c r="C65" s="1">
-        <v>1</v>
-      </c>
-      <c r="D65" s="5"/>
-      <c r="E65" s="4">
+      <c r="F71" s="6">
+        <f t="shared" si="5"/>
+        <v>0.15090238095238093</v>
+      </c>
+      <c r="G71">
+        <v>90.26</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A72" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="B72" s="1" t="s">
+        <v>486</v>
+      </c>
+      <c r="C72" s="1">
+        <v>2</v>
+      </c>
+      <c r="D72" s="5">
+        <v>510.40309999999999</v>
+      </c>
+      <c r="E72" s="4">
         <f>0.001*1000</f>
         <v>1</v>
       </c>
-      <c r="F65" s="6"/>
-    </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A66" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="B66" s="1" t="s">
-        <v>384</v>
-      </c>
-      <c r="C66" s="1">
-        <v>1</v>
-      </c>
-      <c r="D66" s="5">
-        <f>D60</f>
+      <c r="F72" s="6">
+        <f t="shared" si="5"/>
+        <v>0.5104031</v>
+      </c>
+      <c r="G72">
+        <v>289.05</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A73" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="B73" s="1" t="s">
+        <v>367</v>
+      </c>
+      <c r="C73" s="1">
+        <v>1.25</v>
+      </c>
+      <c r="D73" s="5">
+        <f>D67</f>
         <v>1.01</v>
       </c>
-      <c r="E66" s="4">
+      <c r="E73" s="4">
         <f>0.007085*1000</f>
         <v>7.085</v>
       </c>
-      <c r="F66" s="6">
-        <f t="shared" ref="F66:F75" si="4">C66*D66/(E66 * 1000)</f>
+      <c r="F73" s="12">
+        <f t="shared" ref="F73:F99" si="6">D73/(E73 * 1000)</f>
         <v>1.425546930134086E-4</v>
       </c>
-      <c r="G66">
+      <c r="G73">
         <v>13.59</v>
       </c>
-      <c r="H66">
-        <f>0.000824907*4</f>
-        <v>3.2996280000000002E-3</v>
-      </c>
-    </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A67" s="1" t="s">
+    </row>
+    <row r="74" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A74" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="B74" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="B67" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="C67" s="1">
-        <v>1</v>
-      </c>
-      <c r="D67" s="5">
+      <c r="C74" s="1">
+        <v>1.76</v>
+      </c>
+      <c r="D74" s="5">
         <v>159.69</v>
       </c>
-      <c r="E67" s="4">
+      <c r="E74" s="4">
         <f>0.0055*1000</f>
         <v>5.5</v>
       </c>
-      <c r="F67" s="6">
-        <f t="shared" si="4"/>
+      <c r="F74" s="12">
+        <f t="shared" si="6"/>
         <v>2.9034545454545455E-2</v>
       </c>
-      <c r="G67">
+      <c r="G74">
         <v>56.63</v>
       </c>
-      <c r="H67">
-        <f>0.000001784*6</f>
-        <v>1.0703999999999999E-5</v>
-      </c>
-    </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A68" s="1" t="s">
-        <v>195</v>
-      </c>
-      <c r="B68" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="C68" s="1">
-        <v>1</v>
-      </c>
-      <c r="D68" s="5">
+    </row>
+    <row r="75" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A75" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="B75" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="C75" s="1"/>
+      <c r="D75" s="5">
         <v>159.69</v>
       </c>
-      <c r="E68" s="4">
+      <c r="E75" s="4">
         <f>0.026*1000</f>
         <v>26</v>
       </c>
-      <c r="F68" s="6">
-        <f t="shared" si="4"/>
+      <c r="F75" s="12">
+        <f t="shared" si="6"/>
         <v>6.1419230769230769E-3</v>
       </c>
-      <c r="G68">
+      <c r="G75">
         <v>56.63</v>
       </c>
-      <c r="H68">
-        <f>H66+H67</f>
-        <v>3.310332E-3</v>
-      </c>
-    </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A69" s="1" t="s">
+    </row>
+    <row r="76" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A76" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="B76" s="1" t="s">
+        <v>415</v>
+      </c>
+      <c r="C76" s="1"/>
+      <c r="D76" s="5">
+        <f>55.845</f>
+        <v>55.844999999999999</v>
+      </c>
+      <c r="E76" s="4">
+        <f>0.039*1000</f>
+        <v>39</v>
+      </c>
+      <c r="F76" s="12">
+        <f t="shared" si="6"/>
+        <v>1.4319230769230769E-3</v>
+      </c>
+      <c r="G76">
+        <v>7.9</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A77" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="B77" s="1" t="s">
+        <v>415</v>
+      </c>
+      <c r="C77" s="1">
+        <v>14.24</v>
+      </c>
+      <c r="D77" s="5">
+        <f>55.845</f>
+        <v>55.844999999999999</v>
+      </c>
+      <c r="E77" s="4">
+        <f>0.0078*1000</f>
+        <v>7.8</v>
+      </c>
+      <c r="F77" s="12">
+        <f t="shared" si="6"/>
+        <v>7.1596153846153841E-3</v>
+      </c>
+      <c r="G77">
+        <v>7.9</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A78" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B78" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C78" s="1">
+        <v>1.8642000000000001E-3</v>
+      </c>
+      <c r="D78" s="5">
+        <f>12.02+4*1.008</f>
+        <v>16.052</v>
+      </c>
+      <c r="E78" s="4">
+        <f>0.000000717*1000</f>
+        <v>7.1699999999999997E-4</v>
+      </c>
+      <c r="F78" s="12">
+        <f t="shared" si="6"/>
+        <v>22.387726638772666</v>
+      </c>
+      <c r="G78">
+        <v>16.042999999999999</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A79" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B79" s="1" t="s">
+        <v>479</v>
+      </c>
+      <c r="C79" s="1">
+        <v>0.8</v>
+      </c>
+      <c r="D79" s="5">
+        <v>910.77710000000002</v>
+      </c>
+      <c r="E79" s="4">
+        <f>0.0027*1000</f>
+        <v>2.7</v>
+      </c>
+      <c r="F79" s="12">
+        <f t="shared" si="6"/>
+        <v>0.33732485185185185</v>
+      </c>
+      <c r="G79">
+        <v>513.82000000000005</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="A80" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="B80" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="C80" s="1">
+        <v>1.748</v>
+      </c>
+      <c r="D80" s="5">
+        <v>46.07</v>
+      </c>
+      <c r="E80" s="4">
+        <f>0.00088*1000</f>
+        <v>0.88</v>
+      </c>
+      <c r="F80" s="12">
+        <f t="shared" si="6"/>
+        <v>5.2352272727272726E-2</v>
+      </c>
+      <c r="G80">
+        <v>121.86</v>
+      </c>
+    </row>
+    <row r="81" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A81" s="29" t="s">
+        <v>186</v>
+      </c>
+      <c r="B81" s="29" t="s">
+        <v>187</v>
+      </c>
+      <c r="C81" s="29"/>
+      <c r="D81" s="30">
+        <v>60.08</v>
+      </c>
+      <c r="E81" s="31">
+        <f>0.00347*1000</f>
+        <v>3.47</v>
+      </c>
+      <c r="F81" s="32">
+        <f>C81*D81/(E81 * 1000)</f>
+        <v>0</v>
+      </c>
+      <c r="G81">
+        <v>35.369999999999997</v>
+      </c>
+    </row>
+    <row r="82" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A82" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B82" s="1" t="s">
+        <v>478</v>
+      </c>
+      <c r="C82" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="D82" s="5">
+        <v>387.0077</v>
+      </c>
+      <c r="E82" s="4">
+        <f>0.005*1000</f>
+        <v>5</v>
+      </c>
+      <c r="F82" s="12">
+        <f t="shared" si="6"/>
+        <v>7.7401540000000005E-2</v>
+      </c>
+      <c r="G82">
+        <v>71.22</v>
+      </c>
+    </row>
+    <row r="83" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A83" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="B83" s="1" t="s">
+        <v>487</v>
+      </c>
+      <c r="C83" s="1">
+        <v>0</v>
+      </c>
+      <c r="D83" s="5">
+        <v>565.95500000000004</v>
+      </c>
+      <c r="E83" s="4">
+        <f>0.001*1000</f>
+        <v>1</v>
+      </c>
+      <c r="F83" s="12">
+        <f t="shared" si="6"/>
+        <v>0.56595499999999999</v>
+      </c>
+      <c r="G83">
+        <v>1256.93</v>
+      </c>
+    </row>
+    <row r="84" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A84" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B84" s="1" t="s">
+        <v>365</v>
+      </c>
+      <c r="C84" s="1">
+        <v>5.0000000000000002E-5</v>
+      </c>
+      <c r="D84" s="5">
+        <v>14.01</v>
+      </c>
+      <c r="E84" s="4">
+        <f>0.000001251*1000</f>
+        <v>1.2509999999999999E-3</v>
+      </c>
+      <c r="F84" s="12">
+        <f t="shared" si="6"/>
+        <v>11.199040767386093</v>
+      </c>
+      <c r="G84">
+        <v>14.53</v>
+      </c>
+    </row>
+    <row r="85" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A85" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="B85" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="C85" s="1">
+        <v>0.2175</v>
+      </c>
+      <c r="D85" s="5">
+        <v>92.04</v>
+      </c>
+      <c r="E85" s="4">
+        <f>0.00145*1000</f>
+        <v>1.45</v>
+      </c>
+      <c r="F85" s="12">
+        <f t="shared" si="6"/>
+        <v>6.3475862068965522E-2</v>
+      </c>
+      <c r="G85">
+        <v>83.5</v>
+      </c>
+    </row>
+    <row r="86" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A86" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="B86" s="1" t="s">
+        <v>489</v>
+      </c>
+      <c r="C86" s="1">
+        <v>4</v>
+      </c>
+      <c r="D86" s="5">
+        <v>1004.26</v>
+      </c>
+      <c r="E86" s="4">
+        <f>0.00105*1000</f>
+        <v>1.05</v>
+      </c>
+      <c r="F86" s="12">
+        <f t="shared" si="6"/>
+        <v>0.9564380952380952</v>
+      </c>
+      <c r="G86">
+        <v>777.74</v>
+      </c>
+    </row>
+    <row r="87" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A87" s="1" t="s">
+        <v>420</v>
+      </c>
+      <c r="B87" s="1" t="s">
+        <v>421</v>
+      </c>
+      <c r="C87" s="1">
+        <v>24.06</v>
+      </c>
+      <c r="D87" s="5">
+        <v>104.01</v>
+      </c>
+      <c r="E87" s="4">
+        <f>0.001604*1000</f>
+        <v>1.6039999999999999</v>
+      </c>
+      <c r="F87" s="12">
+        <f t="shared" si="6"/>
+        <v>6.4844139650872837E-2</v>
+      </c>
+      <c r="G87">
+        <v>98.74</v>
+      </c>
+    </row>
+    <row r="88" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A88" s="29" t="s">
+        <v>215</v>
+      </c>
+      <c r="B88" s="29" t="s">
+        <v>216</v>
+      </c>
+      <c r="C88" s="29"/>
+      <c r="D88" s="30">
+        <f>(14.005*8)+(39.95*6)</f>
+        <v>351.74</v>
+      </c>
+      <c r="E88" s="31">
+        <f>0.003310332*1000</f>
+        <v>3.3103319999999998</v>
+      </c>
+      <c r="F88" s="32">
+        <f>C88*D88/(E88 * 1000)</f>
+        <v>0</v>
+      </c>
+      <c r="G88">
+        <v>210.74</v>
+      </c>
+    </row>
+    <row r="89" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A89" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="B89" s="1" t="s">
+        <v>429</v>
+      </c>
+      <c r="C89" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="D89" s="5">
+        <v>131.16999999999999</v>
+      </c>
+      <c r="E89" s="4">
+        <f>0.001*1000</f>
+        <v>1</v>
+      </c>
+      <c r="F89" s="12">
+        <f t="shared" si="6"/>
+        <v>0.13116999999999998</v>
+      </c>
+      <c r="G89">
+        <v>285.98</v>
+      </c>
+    </row>
+    <row r="90" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A90" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B90" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="C90" s="1">
+        <v>5.5835999999999999E-5</v>
+      </c>
+      <c r="D90" s="5">
+        <v>16</v>
+      </c>
+      <c r="E90" s="4">
+        <f>0.00000141*1000</f>
+        <v>1.41E-3</v>
+      </c>
+      <c r="F90" s="12">
+        <f t="shared" si="6"/>
+        <v>11.347517730496454</v>
+      </c>
+      <c r="G90">
+        <v>13.61</v>
+      </c>
+    </row>
+    <row r="91" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A91" s="1" t="s">
+        <v>418</v>
+      </c>
+      <c r="B91" s="1" t="s">
+        <v>419</v>
+      </c>
+      <c r="C91" s="1">
+        <v>6.18</v>
+      </c>
+      <c r="D91" s="5">
+        <v>63.13</v>
+      </c>
+      <c r="E91" s="4">
+        <f>0.000618*1000</f>
+        <v>0.61799999999999999</v>
+      </c>
+      <c r="F91" s="12">
+        <f t="shared" si="6"/>
+        <v>0.10215210355987056</v>
+      </c>
+      <c r="G91">
+        <v>163.76</v>
+      </c>
+    </row>
+    <row r="92" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A92" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B92" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C92" s="1"/>
+      <c r="D92" s="5">
+        <v>30.97</v>
+      </c>
+      <c r="E92" s="13">
+        <f>$E$4</f>
+        <v>5</v>
+      </c>
+      <c r="F92" s="12">
+        <f t="shared" si="6"/>
+        <v>6.1939999999999999E-3</v>
+      </c>
+      <c r="G92">
+        <v>10.48</v>
+      </c>
+    </row>
+    <row r="93" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A93" s="1" t="s">
         <v>194</v>
       </c>
-      <c r="B69" s="1" t="s">
-        <v>196</v>
-      </c>
-      <c r="C69" s="1">
-        <v>1</v>
-      </c>
-      <c r="D69" s="5">
+      <c r="B93" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="C93" s="1"/>
+      <c r="D93" s="5">
+        <v>244</v>
+      </c>
+      <c r="E93" s="4">
+        <f>0.019816*1000</f>
+        <v>19.815999999999999</v>
+      </c>
+      <c r="F93" s="12">
+        <f t="shared" si="6"/>
+        <v>1.2313282196205087E-2</v>
+      </c>
+      <c r="G93">
+        <v>6.02</v>
+      </c>
+    </row>
+    <row r="94" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A94" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="B94" s="1" t="s">
+        <v>428</v>
+      </c>
+      <c r="C94" s="1">
+        <v>8</v>
+      </c>
+      <c r="D94" s="5">
+        <v>104.15</v>
+      </c>
+      <c r="E94" s="4">
+        <f>0.00104*1000</f>
+        <v>1.0399999999999998</v>
+      </c>
+      <c r="F94" s="12">
+        <f t="shared" si="6"/>
+        <v>0.10014423076923079</v>
+      </c>
+      <c r="G94">
+        <v>198.8</v>
+      </c>
+    </row>
+    <row r="95" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A95" s="1" t="s">
+        <v>426</v>
+      </c>
+      <c r="B95" s="1" t="s">
+        <v>432</v>
+      </c>
+      <c r="C95" s="1">
+        <v>0.01</v>
+      </c>
+      <c r="D95" s="5">
+        <v>284.77100000000002</v>
+      </c>
+      <c r="E95" s="4">
+        <f>0.00174*1000</f>
+        <v>1.74</v>
+      </c>
+      <c r="F95" s="12">
+        <f t="shared" si="6"/>
+        <v>0.16366149425287357</v>
+      </c>
+      <c r="G95">
+        <v>390.02</v>
+      </c>
+    </row>
+    <row r="96" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A96" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B96" s="1" t="s">
+        <v>477</v>
+      </c>
+      <c r="C96" s="1">
+        <v>140</v>
+      </c>
+      <c r="D96" s="5">
+        <v>589.29629999999997</v>
+      </c>
+      <c r="E96" s="4">
+        <f>0.0078*1000</f>
+        <v>7.8</v>
+      </c>
+      <c r="F96" s="12">
+        <f t="shared" si="6"/>
+        <v>7.5550807692307695E-2</v>
+      </c>
+      <c r="G96">
+        <v>192.86</v>
+      </c>
+    </row>
+    <row r="97" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A97" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="B97" s="1" t="s">
+        <v>428</v>
+      </c>
+      <c r="C97" s="1">
+        <v>7</v>
+      </c>
+      <c r="D97" s="5">
+        <v>104.15</v>
+      </c>
+      <c r="E97" s="4">
+        <f>0.00378*1000</f>
+        <v>3.78</v>
+      </c>
+      <c r="F97" s="12">
+        <f t="shared" si="6"/>
+        <v>2.7552910052910055E-2</v>
+      </c>
+      <c r="G97">
+        <v>198.8</v>
+      </c>
+    </row>
+    <row r="98" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A98" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="B98" s="1" t="s">
+        <v>476</v>
+      </c>
+      <c r="C98" s="1">
+        <v>250</v>
+      </c>
+      <c r="D98" s="5">
+        <v>173.05</v>
+      </c>
+      <c r="E98" s="4">
+        <f>0.0052*1000</f>
+        <v>5.2</v>
+      </c>
+      <c r="F98" s="12">
+        <f t="shared" si="6"/>
+        <v>3.3278846153846159E-2</v>
+      </c>
+      <c r="G98">
+        <v>6.25</v>
+      </c>
+    </row>
+    <row r="99" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A99" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="B99" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="C99" s="1">
+        <v>1.5</v>
+      </c>
+      <c r="D99" s="5">
+        <f>55.845</f>
+        <v>55.844999999999999</v>
+      </c>
+      <c r="E99" s="4">
+        <f>0.0025*1000</f>
+        <v>2.5</v>
+      </c>
+      <c r="F99" s="12">
+        <f t="shared" si="6"/>
+        <v>2.2338E-2</v>
+      </c>
+      <c r="G99">
+        <v>7.9</v>
+      </c>
+    </row>
+    <row r="100" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A100" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="B100" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="C100" s="1"/>
+      <c r="D100" s="5">
         <f>55.845*2</f>
         <v>111.69</v>
       </c>
-      <c r="E69" s="4">
-        <f>0.039*1000</f>
-        <v>39</v>
-      </c>
-      <c r="F69" s="6">
-        <f t="shared" si="4"/>
-        <v>2.8638461538461539E-3</v>
-      </c>
-      <c r="G69">
+      <c r="E100" s="4">
+        <f>0.004*1000</f>
+        <v>4</v>
+      </c>
+      <c r="F100" s="12">
+        <f t="shared" ref="F100:F104" si="7">D100/(E100 * 1000)</f>
+        <v>2.7922499999999999E-2</v>
+      </c>
+      <c r="G100">
         <v>7.9</v>
       </c>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A70" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="B70" s="1" t="s">
-        <v>196</v>
-      </c>
-      <c r="C70" s="1">
-        <v>1</v>
-      </c>
-      <c r="D70" s="5">
-        <f>55.845*2</f>
-        <v>111.69</v>
-      </c>
-      <c r="E70" s="4">
-        <f>0.0078*1000</f>
-        <v>7.8</v>
-      </c>
-      <c r="F70" s="6">
-        <f t="shared" si="4"/>
-        <v>1.4319230769230768E-2</v>
-      </c>
-      <c r="G70">
-        <v>7.9</v>
-      </c>
-    </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A71" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B71" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C71" s="1">
-        <v>1</v>
-      </c>
-      <c r="D71" s="5">
-        <f>12.02+4*1.008</f>
-        <v>16.052</v>
-      </c>
-      <c r="E71" s="4">
-        <f>0.000000717*1000</f>
-        <v>7.1699999999999997E-4</v>
-      </c>
-      <c r="F71" s="6">
-        <f t="shared" si="4"/>
-        <v>22.387726638772666</v>
-      </c>
-      <c r="G71">
-        <v>16.042999999999999</v>
-      </c>
-    </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A72" s="1" t="s">
+    <row r="101" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A101" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="B72" s="1" t="s">
-        <v>219</v>
-      </c>
-      <c r="C72" s="1">
-        <v>1</v>
-      </c>
-      <c r="D72" s="5">
-        <f>323.31+78.07</f>
-        <v>401.38</v>
-      </c>
-      <c r="E72" s="4">
-        <f>0.0027*1000</f>
-        <v>2.7</v>
-      </c>
-      <c r="F72" s="6">
-        <f t="shared" si="4"/>
-        <v>0.14865925925925927</v>
-      </c>
-      <c r="G72">
-        <v>76.040000000000006</v>
-      </c>
-    </row>
-    <row r="73" spans="1:8" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A73" s="1" t="s">
+      <c r="B101" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="C101" s="1">
+        <v>0.01</v>
+      </c>
+      <c r="D101" s="5">
+        <v>76.08</v>
+      </c>
+      <c r="E101" s="4">
+        <f>0.0025*1000</f>
+        <v>2.5</v>
+      </c>
+      <c r="F101" s="12">
+        <f t="shared" si="7"/>
+        <v>3.0432000000000001E-2</v>
+      </c>
+      <c r="G101">
+        <v>48.98</v>
+      </c>
+    </row>
+    <row r="102" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A102" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="B102" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="C102" s="1">
+        <v>0.02</v>
+      </c>
+      <c r="D102" s="5">
+        <v>28.09</v>
+      </c>
+      <c r="E102" s="4">
+        <f>0.002329*1000</f>
+        <v>2.3289999999999997</v>
+      </c>
+      <c r="F102" s="12">
+        <f t="shared" si="7"/>
+        <v>1.2060970373550882E-2</v>
+      </c>
+      <c r="G102">
+        <v>8.15</v>
+      </c>
+    </row>
+    <row r="103" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A103" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="B103" s="1"/>
+      <c r="C103" s="1">
+        <v>32</v>
+      </c>
+      <c r="D103" s="5"/>
+      <c r="E103" s="4">
+        <f>0.00378*1000</f>
+        <v>3.78</v>
+      </c>
+      <c r="F103" s="6"/>
+    </row>
+    <row r="104" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A104" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="B104" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="B73" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="C73" s="1">
-        <v>1</v>
-      </c>
-      <c r="D73" s="5">
-        <v>46.07</v>
-      </c>
-      <c r="E73" s="4">
-        <f>0.00088*1000</f>
-        <v>0.88</v>
-      </c>
-      <c r="F73" s="6">
-        <f t="shared" si="4"/>
-        <v>5.2352272727272726E-2</v>
-      </c>
-      <c r="G73">
-        <v>121.86</v>
-      </c>
-    </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A74" s="29" t="s">
-        <v>198</v>
-      </c>
-      <c r="B74" s="29" t="s">
-        <v>199</v>
-      </c>
-      <c r="C74" s="29">
-        <v>1</v>
-      </c>
-      <c r="D74" s="30">
-        <v>60.08</v>
-      </c>
-      <c r="E74" s="31">
-        <f>0.00347*1000</f>
-        <v>3.47</v>
-      </c>
-      <c r="F74" s="32">
-        <f>C74*D74/(E74 * 1000)</f>
-        <v>1.7314121037463978E-2</v>
-      </c>
-      <c r="G74">
-        <v>35.369999999999997</v>
-      </c>
-    </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A75" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="B75" s="1" t="s">
-        <v>213</v>
-      </c>
-      <c r="C75" s="1">
-        <v>1</v>
-      </c>
-      <c r="D75" s="5">
-        <v>750.27</v>
-      </c>
-      <c r="E75" s="4">
-        <f>0.005*1000</f>
-        <v>5</v>
-      </c>
-      <c r="F75" s="6">
-        <f t="shared" si="4"/>
-        <v>0.15005399999999999</v>
-      </c>
-      <c r="G75">
-        <v>71.22</v>
-      </c>
-    </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A76" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="B76" s="1"/>
-      <c r="C76" s="1">
-        <v>1</v>
-      </c>
-      <c r="D76" s="5"/>
-      <c r="E76" s="4">
+      <c r="C104" s="1">
+        <v>0.17399999999999999</v>
+      </c>
+      <c r="D104" s="5">
+        <v>186.09</v>
+      </c>
+      <c r="E104" s="4">
+        <f>0.0031*1000</f>
+        <v>3.1</v>
+      </c>
+      <c r="F104" s="12">
+        <f t="shared" si="7"/>
+        <v>6.0029032258064517E-2</v>
+      </c>
+      <c r="G104">
+        <v>109.33</v>
+      </c>
+    </row>
+    <row r="105" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A105" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B105" s="1"/>
+      <c r="C105" s="1">
+        <v>0.3</v>
+      </c>
+      <c r="D105" s="5"/>
+      <c r="E105" s="4">
+        <f>0.0016*1000</f>
+        <v>1.6</v>
+      </c>
+      <c r="F105" s="6"/>
+    </row>
+    <row r="106" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A106" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="B106" s="1" t="s">
+        <v>488</v>
+      </c>
+      <c r="C106" s="1">
+        <v>2.5</v>
+      </c>
+      <c r="D106" s="5">
+        <v>516.76</v>
+      </c>
+      <c r="E106" s="4">
         <f>0.001*1000</f>
         <v>1</v>
       </c>
-      <c r="F76" s="6"/>
-    </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A77" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="B77" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C77" s="1">
-        <v>1</v>
-      </c>
-      <c r="D77" s="5">
-        <v>14.01</v>
-      </c>
-      <c r="E77" s="4">
-        <f>0.000001251*1000</f>
-        <v>1.2509999999999999E-3</v>
-      </c>
-      <c r="F77" s="6">
-        <f>C77*D77/(E77 * 1000)</f>
-        <v>11.199040767386093</v>
-      </c>
-      <c r="G77">
-        <v>14.53</v>
-      </c>
-    </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A78" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="B78" s="1" t="s">
-        <v>168</v>
-      </c>
-      <c r="C78" s="1">
-        <v>1</v>
-      </c>
-      <c r="D78" s="5">
-        <v>92.04</v>
-      </c>
-      <c r="E78" s="4">
-        <f>0.00145*1000</f>
-        <v>1.45</v>
-      </c>
-      <c r="F78" s="6">
-        <f>C78*D78/(E78 * 1000)</f>
-        <v>6.3475862068965522E-2</v>
-      </c>
-      <c r="G78">
-        <v>83.5</v>
-      </c>
-    </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A79" s="1" t="s">
+      <c r="F106" s="12">
+        <f t="shared" ref="F106:F111" si="8">D106/(E106 * 1000)</f>
+        <v>0.51676</v>
+      </c>
+      <c r="G106">
+        <v>1130.8399999999999</v>
+      </c>
+    </row>
+    <row r="107" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A107" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="B107" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="C107" s="1">
+        <v>46.8</v>
+      </c>
+      <c r="D107" s="5">
+        <v>232.04</v>
+      </c>
+      <c r="E107" s="4">
+        <f>0.0117*1000</f>
+        <v>11.700000000000001</v>
+      </c>
+      <c r="F107" s="12">
+        <f t="shared" si="8"/>
+        <v>1.9832478632478629E-2</v>
+      </c>
+      <c r="G107">
+        <v>6.3</v>
+      </c>
+    </row>
+    <row r="108" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A108" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B108" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="C108" s="1">
+        <v>0.7</v>
+      </c>
+      <c r="D108" s="5">
+        <v>270.02999999999997</v>
+      </c>
+      <c r="E108" s="4">
+        <f>0.0075*1000</f>
+        <v>7.5</v>
+      </c>
+      <c r="F108" s="12">
+        <f t="shared" si="8"/>
+        <v>3.6003999999999994E-2</v>
+      </c>
+      <c r="G108">
+        <v>33.409999999999997</v>
+      </c>
+    </row>
+    <row r="109" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A109" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="B109" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="C109" s="1">
+        <v>0.79100000000000004</v>
+      </c>
+      <c r="D109" s="5">
+        <v>60.1</v>
+      </c>
+      <c r="E109" s="4">
+        <f>0.000791*1000</f>
+        <v>0.79100000000000004</v>
+      </c>
+      <c r="F109" s="12">
+        <f t="shared" si="8"/>
+        <v>7.5979772439949439E-2</v>
+      </c>
+      <c r="G109">
+        <v>3206</v>
+      </c>
+    </row>
+    <row r="110" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A110" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="B110" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B79" s="1"/>
-      <c r="C79" s="1">
-        <v>1</v>
-      </c>
-      <c r="D79" s="5"/>
-      <c r="E79" s="4">
-        <f>0.00105*1000</f>
-        <v>1.05</v>
-      </c>
-      <c r="F79" s="6"/>
-    </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A80" s="29" t="s">
-        <v>231</v>
-      </c>
-      <c r="B80" s="29" t="s">
-        <v>232</v>
-      </c>
-      <c r="C80" s="29">
-        <v>1</v>
-      </c>
-      <c r="D80" s="30">
-        <f>(14.005*8)+(39.95*6)</f>
-        <v>351.74</v>
-      </c>
-      <c r="E80" s="31">
-        <f>0.003310332*1000</f>
-        <v>3.3103319999999998</v>
-      </c>
-      <c r="F80" s="32">
-        <f>C80*D80/(E80 * 1000)</f>
-        <v>0.10625520340557987</v>
-      </c>
-      <c r="G80">
-        <v>210.74</v>
-      </c>
-    </row>
-    <row r="81" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A81" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="B81" s="1"/>
-      <c r="C81" s="1">
-        <v>1</v>
-      </c>
-      <c r="D81" s="5"/>
-      <c r="E81" s="4">
+      <c r="C110" s="1">
+        <v>8.2899999999999998E-4</v>
+      </c>
+      <c r="D110" s="5">
+        <f>SUM(($D$51*0.25)+($D$109*0.75))</f>
+        <v>53.086500000000001</v>
+      </c>
+      <c r="E110" s="4">
+        <f>0.000829*1000</f>
+        <v>0.82899999999999996</v>
+      </c>
+      <c r="F110" s="12">
+        <f t="shared" si="8"/>
+        <v>6.4036791314837152E-2</v>
+      </c>
+      <c r="G110">
+        <f>(G51*0.25)+(G109*0.75)</f>
+        <v>2414.9274999999998</v>
+      </c>
+    </row>
+    <row r="111" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A111" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="B111" s="1" t="s">
+        <v>487</v>
+      </c>
+      <c r="C111" s="1">
+        <v>0</v>
+      </c>
+      <c r="D111" s="5">
+        <v>565.95500000000004</v>
+      </c>
+      <c r="E111" s="4">
+        <f>0.00075*1000</f>
+        <v>0.75</v>
+      </c>
+      <c r="F111" s="12">
+        <f t="shared" si="8"/>
+        <v>0.75460666666666676</v>
+      </c>
+      <c r="G111">
+        <v>1256.93</v>
+      </c>
+    </row>
+    <row r="112" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A112" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="B112" s="1" t="s">
+        <v>405</v>
+      </c>
+      <c r="C112" s="1">
+        <v>0</v>
+      </c>
+      <c r="D112" s="5">
+        <v>78.08</v>
+      </c>
+      <c r="E112" s="4">
+        <f>0.001005*1000</f>
+        <v>1.0050000000000001</v>
+      </c>
+      <c r="F112" s="6"/>
+    </row>
+    <row r="113" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A113" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="B113" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C113" s="1">
+        <v>8.0000000000000004E-4</v>
+      </c>
+      <c r="D113" s="5">
+        <v>18.02</v>
+      </c>
+      <c r="E113" s="4">
         <f>0.001*1000</f>
         <v>1</v>
       </c>
-      <c r="F81" s="6"/>
-    </row>
-    <row r="82" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A82" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="B82" s="1" t="s">
-        <v>241</v>
-      </c>
-      <c r="C82" s="1">
-        <v>1</v>
-      </c>
-      <c r="D82" s="5">
-        <v>16</v>
-      </c>
-      <c r="E82" s="4">
-        <f>0.00000141*1000</f>
-        <v>1.41E-3</v>
-      </c>
-      <c r="F82" s="6">
-        <f>C82*D82/(E82 * 1000)</f>
-        <v>11.347517730496454</v>
-      </c>
-      <c r="G82">
-        <v>13.61</v>
-      </c>
-    </row>
-    <row r="83" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A83" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="B83" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="C83" s="1">
-        <v>1</v>
-      </c>
-      <c r="D83" s="5">
-        <v>30.97</v>
-      </c>
-      <c r="E83" s="13">
-        <f>$E$4</f>
+      <c r="F113" s="12">
+        <f t="shared" ref="F113:F114" si="9">D113/(E113 * 1000)</f>
+        <v>1.8020000000000001E-2</v>
+      </c>
+      <c r="G113">
+        <v>40.79</v>
+      </c>
+    </row>
+    <row r="114" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A114" s="1" t="s">
+        <v>495</v>
+      </c>
+      <c r="B114" s="1"/>
+      <c r="C114" s="1"/>
+      <c r="D114" s="5">
+        <v>117.49</v>
+      </c>
+      <c r="E114" s="4"/>
+      <c r="F114" s="12" t="e">
+        <f t="shared" si="9"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="116" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A116" s="1" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="117" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A117" s="24" t="s">
+        <v>85</v>
+      </c>
+      <c r="D117" s="25"/>
+      <c r="E117" s="4">
+        <f t="shared" ref="E117:E126" si="10">F117*1000</f>
         <v>5</v>
       </c>
-      <c r="F83" s="6">
-        <f>C83*D83/(E83 * 1000)</f>
-        <v>6.1939999999999999E-3</v>
-      </c>
-      <c r="G83">
-        <v>10.48</v>
-      </c>
-    </row>
-    <row r="84" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A84" s="1" t="s">
-        <v>206</v>
-      </c>
-      <c r="B84" s="1" t="s">
-        <v>207</v>
-      </c>
-      <c r="C84" s="1">
-        <v>1</v>
-      </c>
-      <c r="D84" s="5">
-        <v>244</v>
-      </c>
-      <c r="E84" s="4">
-        <f>0.019816*1000</f>
-        <v>19.815999999999999</v>
-      </c>
-      <c r="F84" s="6">
-        <f>C84*D84/(E84 * 1000)</f>
-        <v>1.2313282196205087E-2</v>
-      </c>
-      <c r="G84">
-        <v>6.02</v>
-      </c>
-    </row>
-    <row r="85" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A85" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="B85" s="1"/>
-      <c r="C85" s="1">
-        <v>1</v>
-      </c>
-      <c r="D85" s="5"/>
-      <c r="E85" s="4">
-        <f>0.00104*1000</f>
-        <v>1.0399999999999998</v>
-      </c>
-      <c r="F85" s="6"/>
-    </row>
-    <row r="86" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A86" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="B86" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="C86" s="1">
-        <v>1</v>
-      </c>
-      <c r="D86" s="5">
-        <f>195.078</f>
-        <v>195.078</v>
-      </c>
-      <c r="E86" s="4">
-        <f>0.0078*1000</f>
-        <v>7.8</v>
-      </c>
-      <c r="F86" s="6">
-        <f>C86*D86/(E86 * 1000)</f>
-        <v>2.5010000000000001E-2</v>
-      </c>
-      <c r="G86">
-        <v>8.9499999999999993</v>
-      </c>
-    </row>
-    <row r="87" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A87" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="B87" s="1"/>
-      <c r="C87" s="1">
-        <v>1</v>
-      </c>
-      <c r="D87" s="5"/>
-      <c r="E87" s="4">
-        <f>0.00378*1000</f>
-        <v>3.78</v>
-      </c>
-      <c r="F87" s="6"/>
-    </row>
-    <row r="88" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A88" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="B88" s="1"/>
-      <c r="C88" s="1">
-        <v>1</v>
-      </c>
-      <c r="D88" s="5"/>
-      <c r="E88" s="4">
-        <f>0.0052*1000</f>
-        <v>5.2</v>
-      </c>
-      <c r="F88" s="6"/>
-    </row>
-    <row r="89" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A89" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="B89" s="1"/>
-      <c r="C89" s="1">
-        <v>1</v>
-      </c>
-      <c r="D89" s="5"/>
-      <c r="E89" s="4">
-        <f>0.0025*1000</f>
-        <v>2.5</v>
-      </c>
-      <c r="F89" s="6"/>
-    </row>
-    <row r="90" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A90" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="B90" s="1"/>
-      <c r="C90" s="1">
-        <v>1</v>
-      </c>
-      <c r="D90" s="5"/>
-      <c r="E90" s="4">
-        <f>0.004*1000</f>
-        <v>4</v>
-      </c>
-      <c r="F90" s="6"/>
-    </row>
-    <row r="91" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A91" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="B91" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="C91" s="1">
-        <v>1</v>
-      </c>
-      <c r="D91" s="5">
-        <v>76.08</v>
-      </c>
-      <c r="E91" s="4">
-        <f>0.0025*1000</f>
-        <v>2.5</v>
-      </c>
-      <c r="F91" s="6">
-        <f>C91*D91/(E91 * 1000)</f>
-        <v>3.0432000000000001E-2</v>
-      </c>
-      <c r="G91">
-        <v>48.98</v>
-      </c>
-    </row>
-    <row r="92" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A92" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="B92" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="C92" s="1">
-        <v>1</v>
-      </c>
-      <c r="D92" s="5">
-        <v>28.09</v>
-      </c>
-      <c r="E92" s="4">
-        <f>0.002329*1000</f>
-        <v>2.3289999999999997</v>
-      </c>
-      <c r="F92" s="6">
-        <f>C92*D92/(E92 * 1000)</f>
-        <v>1.2060970373550882E-2</v>
-      </c>
-      <c r="G92">
-        <v>8.15</v>
-      </c>
-    </row>
-    <row r="93" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A93" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="B93" s="1"/>
-      <c r="C93" s="1">
-        <v>1</v>
-      </c>
-      <c r="D93" s="5"/>
-      <c r="E93" s="4">
-        <f>0.00378*1000</f>
-        <v>3.78</v>
-      </c>
-      <c r="F93" s="6"/>
-    </row>
-    <row r="94" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A94" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="B94" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="C94" s="1">
-        <v>1</v>
-      </c>
-      <c r="D94" s="5">
-        <v>186.09</v>
-      </c>
-      <c r="E94" s="4">
-        <f>0.0031*1000</f>
-        <v>3.1</v>
-      </c>
-      <c r="F94" s="6">
-        <f>C94*D94/(E94 * 1000)</f>
-        <v>6.0029032258064517E-2</v>
-      </c>
-      <c r="G94">
-        <v>109.33</v>
-      </c>
-    </row>
-    <row r="95" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A95" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="B95" s="1"/>
-      <c r="C95" s="1">
-        <v>1</v>
-      </c>
-      <c r="D95" s="5"/>
-      <c r="E95" s="4">
-        <f>0.0016*1000</f>
-        <v>1.6</v>
-      </c>
-      <c r="F95" s="6"/>
-    </row>
-    <row r="96" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A96" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="B96" s="1"/>
-      <c r="C96" s="1">
-        <v>1</v>
-      </c>
-      <c r="D96" s="5"/>
-      <c r="E96" s="4">
-        <f>0.001*1000</f>
-        <v>1</v>
-      </c>
-      <c r="F96" s="6"/>
-    </row>
-    <row r="97" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A97" s="1" t="s">
-        <v>214</v>
-      </c>
-      <c r="B97" s="1" t="s">
-        <v>215</v>
-      </c>
-      <c r="C97" s="1">
-        <v>1</v>
-      </c>
-      <c r="D97" s="5">
-        <v>232.04</v>
-      </c>
-      <c r="E97" s="4">
-        <f>0.0117*1000</f>
-        <v>11.700000000000001</v>
-      </c>
-      <c r="F97" s="6">
-        <f>C97*D97/(E97 * 1000)</f>
-        <v>1.9832478632478629E-2</v>
-      </c>
-      <c r="G97">
-        <v>6.3</v>
-      </c>
-    </row>
-    <row r="98" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A98" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="B98" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="C98" s="1">
-        <v>1</v>
-      </c>
-      <c r="D98" s="5">
-        <v>270.02999999999997</v>
-      </c>
-      <c r="E98" s="4">
-        <f>0.0075*1000</f>
-        <v>7.5</v>
-      </c>
-      <c r="F98" s="6">
-        <f>C98*D98/(E98 * 1000)</f>
-        <v>3.6003999999999994E-2</v>
-      </c>
-      <c r="G98">
-        <v>33.409999999999997</v>
-      </c>
-    </row>
-    <row r="99" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A99" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="B99" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="C99" s="1">
-        <v>1</v>
-      </c>
-      <c r="D99" s="5">
-        <v>60.1</v>
-      </c>
-      <c r="E99" s="4">
-        <f>0.000791*1000</f>
-        <v>0.79100000000000004</v>
-      </c>
-      <c r="F99" s="6">
-        <f>C99*D99/(E99 * 1000)</f>
-        <v>7.5979772439949439E-2</v>
-      </c>
-      <c r="G99">
-        <v>3206</v>
-      </c>
-    </row>
-    <row r="100" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A100" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="B100" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="C100" s="1">
-        <v>1</v>
-      </c>
-      <c r="D100" s="5">
-        <f>SUM(($D$47*0.25)+($D$99*0.75))</f>
-        <v>53.086500000000001</v>
-      </c>
-      <c r="E100" s="4">
-        <f>0.000829*1000</f>
-        <v>0.82899999999999996</v>
-      </c>
-      <c r="F100" s="6">
-        <f>C100*D100/(E100 * 1000)</f>
-        <v>6.4036791314837152E-2</v>
-      </c>
-      <c r="G100">
-        <f>(G47*0.25)+(G99*0.75)</f>
-        <v>2414.9274999999998</v>
-      </c>
-    </row>
-    <row r="101" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A101" s="1" t="s">
-        <v>190</v>
-      </c>
-      <c r="B101" s="1"/>
-      <c r="C101" s="1">
-        <v>1</v>
-      </c>
-      <c r="D101" s="5"/>
-      <c r="E101" s="4">
-        <f>0.00075*1000</f>
-        <v>0.75</v>
-      </c>
-      <c r="F101" s="6"/>
-    </row>
-    <row r="102" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A102" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="B102" s="1" t="s">
-        <v>422</v>
-      </c>
-      <c r="C102" s="1">
-        <v>1</v>
-      </c>
-      <c r="D102" s="5">
-        <v>78.08</v>
-      </c>
-      <c r="E102" s="4">
-        <f>0.001005*1000</f>
-        <v>1.0050000000000001</v>
-      </c>
-      <c r="F102" s="6"/>
-    </row>
-    <row r="103" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A103" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="B103" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C103" s="1">
-        <v>1</v>
-      </c>
-      <c r="D103" s="5">
-        <v>18.02</v>
-      </c>
-      <c r="E103" s="4">
-        <f>0.001*1000</f>
-        <v>1</v>
-      </c>
-      <c r="F103" s="6">
-        <f>C103*D103/(E103 * 1000)</f>
-        <v>1.8020000000000001E-2</v>
-      </c>
-      <c r="G103">
-        <v>40.79</v>
-      </c>
-    </row>
-    <row r="105" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A105" s="1" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="106" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A106" s="24" t="s">
-        <v>95</v>
-      </c>
-      <c r="D106" s="25"/>
-      <c r="E106" s="4">
-        <f t="shared" ref="E106:E141" si="5">F106*1000</f>
-        <v>5</v>
-      </c>
-      <c r="F106" s="6">
+      <c r="F117" s="6">
         <v>5.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="107" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A107" s="24" t="s">
-        <v>103</v>
-      </c>
-      <c r="E107" s="4">
-        <f t="shared" si="5"/>
+    <row r="118" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A118" s="24" t="s">
+        <v>93</v>
+      </c>
+      <c r="E118" s="4">
+        <f t="shared" si="10"/>
         <v>19.3</v>
       </c>
-      <c r="F107" s="6">
+      <c r="F118" s="6">
         <v>1.9300000000000001E-2</v>
       </c>
     </row>
-    <row r="108" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A108" s="24" t="s">
-        <v>48</v>
-      </c>
-      <c r="E108" s="4">
-        <f t="shared" si="5"/>
+    <row r="119" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A119" s="24" t="s">
+        <v>43</v>
+      </c>
+      <c r="E119" s="4">
+        <f t="shared" si="10"/>
         <v>54.4</v>
       </c>
-      <c r="F108" s="6">
+      <c r="F119" s="6">
         <v>5.4399999999999997E-2</v>
       </c>
     </row>
-    <row r="109" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A109" s="24" t="s">
-        <v>96</v>
-      </c>
-      <c r="E109" s="4">
-        <f t="shared" si="5"/>
-        <v>5</v>
-      </c>
-      <c r="F109" s="6">
-        <v>5.0000000000000001E-3</v>
-      </c>
-    </row>
-    <row r="110" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A110" s="24" t="s">
-        <v>105</v>
-      </c>
-      <c r="E110" s="4">
-        <f t="shared" si="5"/>
-        <v>7</v>
-      </c>
-      <c r="F110" s="6">
-        <v>7.0000000000000001E-3</v>
-      </c>
-    </row>
-    <row r="111" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A111" s="24" t="s">
-        <v>139</v>
-      </c>
-      <c r="E111" s="4">
-        <f t="shared" si="5"/>
-        <v>0.53399999999999992</v>
-      </c>
-      <c r="F111" s="6">
-        <v>5.3399999999999997E-4</v>
-      </c>
-    </row>
-    <row r="112" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A112" s="24" t="s">
-        <v>97</v>
-      </c>
-      <c r="E112" s="4">
-        <f t="shared" si="5"/>
-        <v>6.0000000000000005E-2</v>
-      </c>
-      <c r="F112" s="6">
-        <v>6.0000000000000002E-5</v>
-      </c>
-    </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A113" s="24" t="s">
-        <v>101</v>
-      </c>
-      <c r="E113" s="4">
-        <f t="shared" si="5"/>
-        <v>2.5</v>
-      </c>
-      <c r="F113" s="6">
-        <v>2.5000000000000001E-3</v>
-      </c>
-    </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A114" s="24" t="s">
-        <v>58</v>
-      </c>
-      <c r="E114" s="4">
-        <f t="shared" si="5"/>
-        <v>5.0108799999999993</v>
-      </c>
-      <c r="F114" s="6">
-        <v>5.0108799999999997E-3</v>
-      </c>
-    </row>
-    <row r="115" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A115" s="24" t="s">
-        <v>106</v>
-      </c>
-      <c r="E115" s="4">
-        <f t="shared" si="5"/>
-        <v>4.3499999999999996</v>
-      </c>
-      <c r="F115" s="6">
-        <v>4.3499999999999997E-3</v>
-      </c>
-    </row>
-    <row r="116" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A116" s="24" t="s">
-        <v>100</v>
-      </c>
-      <c r="E116" s="4">
-        <f t="shared" si="5"/>
-        <v>0.216</v>
-      </c>
-      <c r="F116" s="6">
-        <v>2.1599999999999999E-4</v>
-      </c>
-    </row>
-    <row r="117" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A117" s="24" t="s">
-        <v>49</v>
-      </c>
-      <c r="E117" s="4">
-        <f t="shared" si="5"/>
-        <v>23.125</v>
-      </c>
-      <c r="F117" s="6">
-        <v>2.3125E-2</v>
-      </c>
-    </row>
-    <row r="118" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A118" s="24" t="s">
-        <v>50</v>
-      </c>
-      <c r="E118" s="4">
-        <f t="shared" si="5"/>
-        <v>5.25</v>
-      </c>
-      <c r="F118" s="6">
-        <v>5.2500000000000003E-3</v>
-      </c>
-    </row>
-    <row r="119" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A119" s="24" t="s">
-        <v>220</v>
-      </c>
-      <c r="E119" s="4">
-        <f t="shared" si="5"/>
-        <v>6.24</v>
-      </c>
-      <c r="F119" s="6">
-        <v>6.2399999999999999E-3</v>
-      </c>
-    </row>
-    <row r="120" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A120" s="24" t="s">
-        <v>51</v>
+        <v>86</v>
       </c>
       <c r="E120" s="4">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>5</v>
       </c>
       <c r="F120" s="6">
         <v>5.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="121" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A121" s="24" t="s">
-        <v>138</v>
+        <v>95</v>
       </c>
       <c r="E121" s="4">
-        <f t="shared" si="5"/>
-        <v>1</v>
+        <f t="shared" si="10"/>
+        <v>7</v>
       </c>
       <c r="F121" s="6">
-        <v>1E-3</v>
-      </c>
-    </row>
-    <row r="122" spans="1:6" x14ac:dyDescent="0.25">
+        <v>7.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="122" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A122" s="24" t="s">
-        <v>52</v>
+        <v>129</v>
       </c>
       <c r="E122" s="4">
-        <f t="shared" si="5"/>
-        <v>12.5</v>
+        <f t="shared" si="10"/>
+        <v>0.53399999999999992</v>
       </c>
       <c r="F122" s="6">
-        <v>1.2500000000000001E-2</v>
-      </c>
-    </row>
-    <row r="123" spans="1:6" x14ac:dyDescent="0.25">
+        <v>5.3399999999999997E-4</v>
+      </c>
+    </row>
+    <row r="123" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A123" s="24" t="s">
-        <v>102</v>
+        <v>87</v>
       </c>
       <c r="E123" s="4">
-        <f t="shared" si="5"/>
-        <v>2.4</v>
+        <f t="shared" si="10"/>
+        <v>6.0000000000000005E-2</v>
       </c>
       <c r="F123" s="6">
-        <v>2.3999999999999998E-3</v>
-      </c>
-    </row>
-    <row r="124" spans="1:6" x14ac:dyDescent="0.25">
+        <v>6.0000000000000002E-5</v>
+      </c>
+    </row>
+    <row r="124" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A124" s="24" t="s">
+        <v>91</v>
+      </c>
+      <c r="E124" s="4">
+        <f t="shared" si="10"/>
+        <v>2.5</v>
+      </c>
+      <c r="F124" s="6">
+        <v>2.5000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="125" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A125" s="24" t="s">
         <v>53</v>
       </c>
-      <c r="E124" s="4">
-        <f t="shared" si="5"/>
-        <v>13.5</v>
-      </c>
-      <c r="F124" s="6">
-        <v>1.35E-2</v>
-      </c>
-    </row>
-    <row r="125" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A125" s="24" t="s">
-        <v>54</v>
-      </c>
       <c r="E125" s="4">
-        <f t="shared" si="5"/>
-        <v>8.6</v>
+        <f t="shared" si="10"/>
+        <v>5.0108799999999993</v>
       </c>
       <c r="F125" s="6">
-        <v>8.6E-3</v>
-      </c>
-    </row>
-    <row r="126" spans="1:6" x14ac:dyDescent="0.25">
+        <v>5.0108799999999997E-3</v>
+      </c>
+    </row>
+    <row r="126" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A126" s="24" t="s">
-        <v>161</v>
+        <v>96</v>
       </c>
       <c r="E126" s="4">
-        <f t="shared" si="5"/>
-        <v>19.099999999999998</v>
+        <f t="shared" si="10"/>
+        <v>4.3499999999999996</v>
       </c>
       <c r="F126" s="6">
-        <v>1.9099999999999999E-2</v>
-      </c>
-    </row>
-    <row r="127" spans="1:6" x14ac:dyDescent="0.25">
+        <v>4.3499999999999997E-3</v>
+      </c>
+    </row>
+    <row r="127" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A127" s="24" t="s">
-        <v>162</v>
+        <v>414</v>
       </c>
       <c r="E127" s="4">
-        <f t="shared" si="5"/>
-        <v>10.97</v>
+        <f t="shared" ref="E127:E152" si="11">F127*1000</f>
+        <v>6.24</v>
       </c>
       <c r="F127" s="6">
-        <v>1.0970000000000001E-2</v>
-      </c>
-    </row>
-    <row r="128" spans="1:6" x14ac:dyDescent="0.25">
+        <v>6.2399999999999999E-3</v>
+      </c>
+    </row>
+    <row r="128" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A128" s="24" t="s">
-        <v>55</v>
-      </c>
-      <c r="B128" s="1"/>
-      <c r="C128" s="1"/>
-      <c r="D128" s="3"/>
+        <v>90</v>
+      </c>
       <c r="E128" s="4">
-        <f t="shared" si="5"/>
-        <v>5.7050000000000001</v>
+        <f t="shared" si="11"/>
+        <v>0.216</v>
       </c>
       <c r="F128" s="6">
-        <v>5.705E-3</v>
+        <v>2.1599999999999999E-4</v>
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A129" s="24" t="s">
-        <v>56</v>
-      </c>
-      <c r="B129" s="1"/>
-      <c r="C129" s="1"/>
-      <c r="D129" s="3"/>
+        <v>44</v>
+      </c>
       <c r="E129" s="4">
-        <f t="shared" si="5"/>
-        <v>13.5</v>
+        <f t="shared" si="11"/>
+        <v>23.125</v>
       </c>
       <c r="F129" s="6">
-        <v>1.35E-2</v>
+        <v>2.3125E-2</v>
       </c>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A130" s="24" t="s">
-        <v>60</v>
-      </c>
-      <c r="B130" s="1"/>
-      <c r="C130" s="1"/>
-      <c r="D130" s="3"/>
+        <v>45</v>
+      </c>
       <c r="E130" s="4">
-        <f t="shared" si="5"/>
-        <v>0.35399999999999998</v>
+        <f t="shared" si="11"/>
+        <v>5.25</v>
       </c>
       <c r="F130" s="6">
-        <v>3.5399999999999999E-4</v>
+        <v>5.2500000000000003E-3</v>
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A131" s="24" t="s">
-        <v>98</v>
-      </c>
-      <c r="B131" s="1"/>
-      <c r="C131" s="1"/>
-      <c r="D131" s="3"/>
+        <v>46</v>
+      </c>
       <c r="E131" s="4">
-        <f t="shared" si="5"/>
-        <v>2.12805</v>
+        <f t="shared" si="11"/>
+        <v>5</v>
       </c>
       <c r="F131" s="6">
-        <v>2.1280499999999998E-3</v>
+        <v>5.0000000000000001E-3</v>
       </c>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A132" s="24" t="s">
-        <v>108</v>
-      </c>
-      <c r="B132" s="1"/>
-      <c r="C132" s="1"/>
-      <c r="D132" s="3"/>
+        <v>128</v>
+      </c>
       <c r="E132" s="4">
-        <f t="shared" si="5"/>
-        <v>1.08</v>
+        <f t="shared" si="11"/>
+        <v>1</v>
       </c>
       <c r="F132" s="6">
-        <v>1.08E-3</v>
+        <v>1E-3</v>
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A133" s="24" t="s">
-        <v>99</v>
-      </c>
-      <c r="B133" s="1"/>
-      <c r="C133" s="1"/>
-      <c r="D133" s="3"/>
+        <v>47</v>
+      </c>
       <c r="E133" s="4">
-        <f t="shared" si="5"/>
-        <v>4.1000000000000005</v>
+        <f t="shared" si="11"/>
+        <v>12.5</v>
       </c>
       <c r="F133" s="6">
-        <v>4.1000000000000003E-3</v>
+        <v>1.2500000000000001E-2</v>
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A134" s="24" t="s">
-        <v>43</v>
+        <v>92</v>
       </c>
       <c r="E134" s="4">
-        <f t="shared" si="5"/>
-        <v>12.5</v>
+        <f t="shared" si="11"/>
+        <v>2.4</v>
       </c>
       <c r="F134" s="6">
-        <v>1.2500000000000001E-2</v>
+        <v>2.3999999999999998E-3</v>
       </c>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A135" s="24" t="s">
-        <v>62</v>
+        <v>48</v>
       </c>
       <c r="E135" s="4">
-        <f t="shared" si="5"/>
-        <v>4.5999999999999996</v>
+        <f t="shared" si="11"/>
+        <v>13.5</v>
       </c>
       <c r="F135" s="6">
-        <v>4.5999999999999999E-3</v>
+        <v>1.35E-2</v>
       </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A136" s="24" t="s">
-        <v>109</v>
+        <v>49</v>
       </c>
       <c r="E136" s="4">
-        <f t="shared" si="5"/>
-        <v>1</v>
+        <f t="shared" si="11"/>
+        <v>8.6</v>
       </c>
       <c r="F136" s="6">
-        <v>1E-3</v>
+        <v>8.6E-3</v>
       </c>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A137" s="24" t="s">
-        <v>110</v>
+        <v>151</v>
       </c>
       <c r="E137" s="4">
-        <f t="shared" si="5"/>
-        <v>1</v>
+        <f t="shared" si="11"/>
+        <v>19.099999999999998</v>
       </c>
       <c r="F137" s="6">
-        <v>1E-3</v>
+        <v>1.9099999999999999E-2</v>
       </c>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A138" s="24" t="s">
-        <v>104</v>
+        <v>152</v>
       </c>
       <c r="E138" s="4">
-        <f t="shared" si="5"/>
-        <v>7.5</v>
+        <f t="shared" si="11"/>
+        <v>10.97</v>
       </c>
       <c r="F138" s="6">
-        <v>7.4999999999999997E-3</v>
+        <v>1.0970000000000001E-2</v>
       </c>
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A139" s="24" t="s">
-        <v>107</v>
-      </c>
+        <v>50</v>
+      </c>
+      <c r="B139" s="1"/>
+      <c r="C139" s="1"/>
+      <c r="D139" s="3"/>
       <c r="E139" s="4">
-        <f t="shared" si="5"/>
-        <v>4.3499999999999996</v>
+        <f t="shared" si="11"/>
+        <v>5.7050000000000001</v>
       </c>
       <c r="F139" s="6">
-        <v>4.3499999999999997E-3</v>
+        <v>5.705E-3</v>
       </c>
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A140" s="24" t="s">
-        <v>112</v>
-      </c>
+        <v>51</v>
+      </c>
+      <c r="B140" s="1"/>
+      <c r="C140" s="1"/>
+      <c r="D140" s="3"/>
       <c r="E140" s="4">
-        <f t="shared" si="5"/>
-        <v>5</v>
+        <f t="shared" si="11"/>
+        <v>13.5</v>
       </c>
       <c r="F140" s="6">
-        <v>5.0000000000000001E-3</v>
+        <v>1.35E-2</v>
       </c>
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A141" s="24" t="s">
+        <v>55</v>
+      </c>
+      <c r="B141" s="1"/>
+      <c r="C141" s="1"/>
+      <c r="D141" s="3"/>
+      <c r="E141" s="4">
+        <f t="shared" si="11"/>
+        <v>0.35399999999999998</v>
+      </c>
+      <c r="F141" s="6">
+        <v>3.5399999999999999E-4</v>
+      </c>
+    </row>
+    <row r="142" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A142" s="24" t="s">
+        <v>88</v>
+      </c>
+      <c r="B142" s="1"/>
+      <c r="C142" s="1"/>
+      <c r="D142" s="3"/>
+      <c r="E142" s="4">
+        <f t="shared" si="11"/>
+        <v>2.12805</v>
+      </c>
+      <c r="F142" s="6">
+        <v>2.1280499999999998E-3</v>
+      </c>
+    </row>
+    <row r="143" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A143" s="24" t="s">
+        <v>98</v>
+      </c>
+      <c r="B143" s="1"/>
+      <c r="C143" s="1"/>
+      <c r="D143" s="3"/>
+      <c r="E143" s="4">
+        <f t="shared" si="11"/>
+        <v>1.08</v>
+      </c>
+      <c r="F143" s="6">
+        <v>1.08E-3</v>
+      </c>
+    </row>
+    <row r="144" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A144" s="24" t="s">
+        <v>89</v>
+      </c>
+      <c r="B144" s="1"/>
+      <c r="C144" s="1"/>
+      <c r="D144" s="3"/>
+      <c r="E144" s="4">
+        <f t="shared" si="11"/>
+        <v>4.1000000000000005</v>
+      </c>
+      <c r="F144" s="6">
+        <v>4.1000000000000003E-3</v>
+      </c>
+    </row>
+    <row r="145" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A145" s="24" t="s">
+        <v>38</v>
+      </c>
+      <c r="E145" s="4">
+        <f t="shared" si="11"/>
+        <v>12.5</v>
+      </c>
+      <c r="F145" s="6">
+        <v>1.2500000000000001E-2</v>
+      </c>
+    </row>
+    <row r="146" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A146" s="24" t="s">
         <v>57</v>
       </c>
-      <c r="E141" s="4">
-        <f t="shared" si="5"/>
+      <c r="E146" s="4">
+        <f t="shared" si="11"/>
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="F146" s="6">
+        <v>4.5999999999999999E-3</v>
+      </c>
+    </row>
+    <row r="147" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A147" s="24" t="s">
+        <v>99</v>
+      </c>
+      <c r="E147" s="4">
+        <f t="shared" si="11"/>
+        <v>1</v>
+      </c>
+      <c r="F147" s="6">
+        <v>1E-3</v>
+      </c>
+    </row>
+    <row r="148" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A148" s="24" t="s">
+        <v>100</v>
+      </c>
+      <c r="E148" s="4">
+        <f t="shared" si="11"/>
+        <v>1</v>
+      </c>
+      <c r="F148" s="6">
+        <v>1E-3</v>
+      </c>
+    </row>
+    <row r="149" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A149" s="24" t="s">
+        <v>94</v>
+      </c>
+      <c r="E149" s="4">
+        <f t="shared" si="11"/>
+        <v>7.5</v>
+      </c>
+      <c r="F149" s="6">
+        <v>7.4999999999999997E-3</v>
+      </c>
+    </row>
+    <row r="150" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A150" s="24" t="s">
+        <v>97</v>
+      </c>
+      <c r="E150" s="4">
+        <f t="shared" si="11"/>
+        <v>4.3499999999999996</v>
+      </c>
+      <c r="F150" s="6">
+        <v>4.3499999999999997E-3</v>
+      </c>
+    </row>
+    <row r="151" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A151" s="24" t="s">
+        <v>102</v>
+      </c>
+      <c r="E151" s="4">
+        <f t="shared" si="11"/>
         <v>5</v>
       </c>
-      <c r="F141" s="6">
+      <c r="F151" s="6">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="152" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A152" s="24" t="s">
+        <v>52</v>
+      </c>
+      <c r="E152" s="4">
+        <f t="shared" si="11"/>
+        <v>5</v>
+      </c>
+      <c r="F152" s="6">
         <v>5.0000000000000001E-3</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L124"/>
+  <dimension ref="A1:Q142"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8.25" customWidth="1"/>
@@ -6020,7 +7010,7 @@
   <sheetData>
     <row r="1" spans="1:12" ht="20.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="40" t="s">
-        <v>425</v>
+        <v>408</v>
       </c>
       <c r="B1" s="40"/>
       <c r="C1" s="40"/>
@@ -6031,55 +7021,53 @@
     </row>
     <row r="2" spans="1:12" ht="16.5" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>426</v>
+        <v>409</v>
       </c>
       <c r="D2" t="s">
-        <v>387</v>
+        <v>370</v>
       </c>
       <c r="F2" t="s">
-        <v>389</v>
+        <v>372</v>
       </c>
       <c r="G2" t="s">
-        <v>427</v>
+        <v>410</v>
       </c>
       <c r="J2" t="s">
-        <v>389</v>
+        <v>372</v>
       </c>
       <c r="K2" t="s">
-        <v>427</v>
+        <v>410</v>
       </c>
       <c r="L2" t="s">
-        <v>418</v>
+        <v>401</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" s="23" t="s">
-        <v>385</v>
+        <v>368</v>
       </c>
       <c r="B3" s="23" t="s">
-        <v>386</v>
+        <v>369</v>
       </c>
       <c r="C3" s="23" t="s">
-        <v>418</v>
+        <v>401</v>
       </c>
       <c r="F3" s="23" t="s">
-        <v>392</v>
+        <v>375</v>
       </c>
       <c r="G3" s="23" t="s">
-        <v>388</v>
+        <v>371</v>
       </c>
     </row>
     <row r="4" spans="1:12" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="14" t="s">
-        <v>384</v>
-      </c>
+      <c r="A4" s="14"/>
       <c r="B4" s="17" t="str">
-        <f>IFERROR(VLOOKUP(A4,$A$25:$D$124,2,FALSE),"-")</f>
-        <v>Hydrogen</v>
+        <f>IFERROR(VLOOKUP(A4,$A$25:$D$139,2,FALSE),"-")</f>
+        <v>-</v>
       </c>
       <c r="C4" s="17" t="str">
         <f t="shared" ref="C4:C15" si="0">IF(L4="Y","Yes","-")</f>
-        <v>Yes</v>
+        <v>-</v>
       </c>
       <c r="D4" s="14"/>
       <c r="E4" s="15">
@@ -6094,23 +7082,23 @@
         <f t="shared" ref="G4:G15" si="3">IFERROR(E4*K4,0)</f>
         <v>0</v>
       </c>
-      <c r="J4" s="17">
-        <f t="shared" ref="J4:J15" si="4">IFERROR(VLOOKUP(A4,$A$25:$D$124,3,FALSE),"-")</f>
-        <v>13.59</v>
-      </c>
-      <c r="K4" s="17">
-        <f t="shared" ref="K4:K15" si="5">IFERROR(VLOOKUP(A4,$A$25:$D$124,4,FALSE),"-")</f>
-        <v>1.008</v>
+      <c r="J4" s="17" t="str">
+        <f>IFERROR(VLOOKUP(A4,$A$25:$D$139,3,FALSE),"-")</f>
+        <v>-</v>
+      </c>
+      <c r="K4" s="17" t="str">
+        <f>IFERROR(VLOOKUP(A4,$A$25:$D$139,4,FALSE),"-")</f>
+        <v>-</v>
       </c>
       <c r="L4" s="17" t="str">
-        <f t="shared" ref="L4:L15" si="6">IFERROR(VLOOKUP(A4,$A$25:$E$124,5,FALSE),"-")</f>
-        <v>Y</v>
+        <f t="shared" ref="L4:L15" si="4">IFERROR(VLOOKUP(A4,$A$25:$E$124,5,FALSE),"-")</f>
+        <v>-</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="17.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="14"/>
       <c r="B5" s="17" t="str">
-        <f t="shared" ref="B5:B15" si="7">IFERROR(VLOOKUP(A5,$A$25:$D$124,2,FALSE),"-")</f>
+        <f>IFERROR(VLOOKUP(A5,$A$25:$D$139,2,FALSE),"-")</f>
         <v>-</v>
       </c>
       <c r="C5" s="17" t="str">
@@ -6130,23 +7118,24 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
+      <c r="H5" s="58"/>
       <c r="J5" s="17" t="str">
+        <f>IFERROR(VLOOKUP(A5,$A$25:$D$139,3,FALSE),"-")</f>
+        <v>-</v>
+      </c>
+      <c r="K5" s="17" t="str">
+        <f>IFERROR(VLOOKUP(A5,$A$25:$D$139,4,FALSE),"-")</f>
+        <v>-</v>
+      </c>
+      <c r="L5" s="17" t="str">
         <f t="shared" si="4"/>
-        <v>-</v>
-      </c>
-      <c r="K5" s="17" t="str">
-        <f t="shared" si="5"/>
-        <v>-</v>
-      </c>
-      <c r="L5" s="17" t="str">
-        <f t="shared" si="6"/>
         <v>-</v>
       </c>
     </row>
     <row r="6" spans="1:12" ht="17.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="14"/>
       <c r="B6" s="17" t="str">
-        <f t="shared" si="7"/>
+        <f>IFERROR(VLOOKUP(A6,$A$25:$D$139,2,FALSE),"-")</f>
         <v>-</v>
       </c>
       <c r="C6" s="17" t="str">
@@ -6167,22 +7156,22 @@
         <v>0</v>
       </c>
       <c r="J6" s="17" t="str">
+        <f>IFERROR(VLOOKUP(A6,$A$25:$D$139,3,FALSE),"-")</f>
+        <v>-</v>
+      </c>
+      <c r="K6" s="17" t="str">
+        <f>IFERROR(VLOOKUP(A6,$A$25:$D$139,4,FALSE),"-")</f>
+        <v>-</v>
+      </c>
+      <c r="L6" s="17" t="str">
         <f t="shared" si="4"/>
-        <v>-</v>
-      </c>
-      <c r="K6" s="17" t="str">
-        <f t="shared" si="5"/>
-        <v>-</v>
-      </c>
-      <c r="L6" s="17" t="str">
-        <f t="shared" si="6"/>
         <v>-</v>
       </c>
     </row>
     <row r="7" spans="1:12" ht="17.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="14"/>
       <c r="B7" s="17" t="str">
-        <f t="shared" si="7"/>
+        <f>IFERROR(VLOOKUP(A7,$A$25:$D$139,2,FALSE),"-")</f>
         <v>-</v>
       </c>
       <c r="C7" s="17" t="str">
@@ -6203,22 +7192,22 @@
         <v>0</v>
       </c>
       <c r="J7" s="17" t="str">
+        <f>IFERROR(VLOOKUP(A7,$A$25:$D$139,3,FALSE),"-")</f>
+        <v>-</v>
+      </c>
+      <c r="K7" s="17" t="str">
+        <f>IFERROR(VLOOKUP(A7,$A$25:$D$139,4,FALSE),"-")</f>
+        <v>-</v>
+      </c>
+      <c r="L7" s="17" t="str">
         <f t="shared" si="4"/>
-        <v>-</v>
-      </c>
-      <c r="K7" s="17" t="str">
-        <f t="shared" si="5"/>
-        <v>-</v>
-      </c>
-      <c r="L7" s="17" t="str">
-        <f t="shared" si="6"/>
         <v>-</v>
       </c>
     </row>
     <row r="8" spans="1:12" ht="17.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="14"/>
       <c r="B8" s="17" t="str">
-        <f t="shared" si="7"/>
+        <f>IFERROR(VLOOKUP(A8,$A$25:$D$139,2,FALSE),"-")</f>
         <v>-</v>
       </c>
       <c r="C8" s="17" t="str">
@@ -6239,22 +7228,22 @@
         <v>0</v>
       </c>
       <c r="J8" s="17" t="str">
+        <f>IFERROR(VLOOKUP(A8,$A$25:$D$139,3,FALSE),"-")</f>
+        <v>-</v>
+      </c>
+      <c r="K8" s="17" t="str">
+        <f>IFERROR(VLOOKUP(A8,$A$25:$D$139,4,FALSE),"-")</f>
+        <v>-</v>
+      </c>
+      <c r="L8" s="17" t="str">
         <f t="shared" si="4"/>
-        <v>-</v>
-      </c>
-      <c r="K8" s="17" t="str">
-        <f t="shared" si="5"/>
-        <v>-</v>
-      </c>
-      <c r="L8" s="17" t="str">
-        <f t="shared" si="6"/>
         <v>-</v>
       </c>
     </row>
     <row r="9" spans="1:12" ht="17.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="14"/>
       <c r="B9" s="17" t="str">
-        <f t="shared" si="7"/>
+        <f>IFERROR(VLOOKUP(A9,$A$25:$D$139,2,FALSE),"-")</f>
         <v>-</v>
       </c>
       <c r="C9" s="17" t="str">
@@ -6275,22 +7264,22 @@
         <v>0</v>
       </c>
       <c r="J9" s="17" t="str">
+        <f>IFERROR(VLOOKUP(A9,$A$25:$D$139,3,FALSE),"-")</f>
+        <v>-</v>
+      </c>
+      <c r="K9" s="17" t="str">
+        <f>IFERROR(VLOOKUP(A9,$A$25:$D$139,4,FALSE),"-")</f>
+        <v>-</v>
+      </c>
+      <c r="L9" s="17" t="str">
         <f t="shared" si="4"/>
-        <v>-</v>
-      </c>
-      <c r="K9" s="17" t="str">
-        <f t="shared" si="5"/>
-        <v>-</v>
-      </c>
-      <c r="L9" s="17" t="str">
-        <f t="shared" si="6"/>
         <v>-</v>
       </c>
     </row>
     <row r="10" spans="1:12" ht="17.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="14"/>
       <c r="B10" s="17" t="str">
-        <f t="shared" si="7"/>
+        <f>IFERROR(VLOOKUP(A10,$A$25:$D$139,2,FALSE),"-")</f>
         <v>-</v>
       </c>
       <c r="C10" s="17" t="str">
@@ -6311,22 +7300,22 @@
         <v>0</v>
       </c>
       <c r="J10" s="17" t="str">
+        <f>IFERROR(VLOOKUP(A10,$A$25:$D$139,3,FALSE),"-")</f>
+        <v>-</v>
+      </c>
+      <c r="K10" s="17" t="str">
+        <f>IFERROR(VLOOKUP(A10,$A$25:$D$139,4,FALSE),"-")</f>
+        <v>-</v>
+      </c>
+      <c r="L10" s="17" t="str">
         <f t="shared" si="4"/>
-        <v>-</v>
-      </c>
-      <c r="K10" s="17" t="str">
-        <f t="shared" si="5"/>
-        <v>-</v>
-      </c>
-      <c r="L10" s="17" t="str">
-        <f t="shared" si="6"/>
         <v>-</v>
       </c>
     </row>
     <row r="11" spans="1:12" ht="17.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="14"/>
       <c r="B11" s="17" t="str">
-        <f t="shared" si="7"/>
+        <f>IFERROR(VLOOKUP(A11,$A$25:$D$139,2,FALSE),"-")</f>
         <v>-</v>
       </c>
       <c r="C11" s="17" t="str">
@@ -6347,22 +7336,22 @@
         <v>0</v>
       </c>
       <c r="J11" s="17" t="str">
+        <f>IFERROR(VLOOKUP(A11,$A$25:$D$139,3,FALSE),"-")</f>
+        <v>-</v>
+      </c>
+      <c r="K11" s="17" t="str">
+        <f>IFERROR(VLOOKUP(A11,$A$25:$D$139,4,FALSE),"-")</f>
+        <v>-</v>
+      </c>
+      <c r="L11" s="17" t="str">
         <f t="shared" si="4"/>
-        <v>-</v>
-      </c>
-      <c r="K11" s="17" t="str">
-        <f t="shared" si="5"/>
-        <v>-</v>
-      </c>
-      <c r="L11" s="17" t="str">
-        <f t="shared" si="6"/>
         <v>-</v>
       </c>
     </row>
     <row r="12" spans="1:12" ht="17.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="14"/>
       <c r="B12" s="17" t="str">
-        <f t="shared" si="7"/>
+        <f>IFERROR(VLOOKUP(A12,$A$25:$D$139,2,FALSE),"-")</f>
         <v>-</v>
       </c>
       <c r="C12" s="17" t="str">
@@ -6383,22 +7372,22 @@
         <v>0</v>
       </c>
       <c r="J12" s="17" t="str">
+        <f>IFERROR(VLOOKUP(A12,$A$25:$D$139,3,FALSE),"-")</f>
+        <v>-</v>
+      </c>
+      <c r="K12" s="17" t="str">
+        <f>IFERROR(VLOOKUP(A12,$A$25:$D$139,4,FALSE),"-")</f>
+        <v>-</v>
+      </c>
+      <c r="L12" s="17" t="str">
         <f t="shared" si="4"/>
-        <v>-</v>
-      </c>
-      <c r="K12" s="17" t="str">
-        <f t="shared" si="5"/>
-        <v>-</v>
-      </c>
-      <c r="L12" s="17" t="str">
-        <f t="shared" si="6"/>
         <v>-</v>
       </c>
     </row>
     <row r="13" spans="1:12" ht="17.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="14"/>
       <c r="B13" s="17" t="str">
-        <f t="shared" si="7"/>
+        <f>IFERROR(VLOOKUP(A13,$A$25:$D$139,2,FALSE),"-")</f>
         <v>-</v>
       </c>
       <c r="C13" s="17" t="str">
@@ -6419,22 +7408,22 @@
         <v>0</v>
       </c>
       <c r="J13" s="17" t="str">
+        <f>IFERROR(VLOOKUP(A13,$A$25:$D$139,3,FALSE),"-")</f>
+        <v>-</v>
+      </c>
+      <c r="K13" s="17" t="str">
+        <f>IFERROR(VLOOKUP(A13,$A$25:$D$139,4,FALSE),"-")</f>
+        <v>-</v>
+      </c>
+      <c r="L13" s="17" t="str">
         <f t="shared" si="4"/>
-        <v>-</v>
-      </c>
-      <c r="K13" s="17" t="str">
-        <f t="shared" si="5"/>
-        <v>-</v>
-      </c>
-      <c r="L13" s="17" t="str">
-        <f t="shared" si="6"/>
         <v>-</v>
       </c>
     </row>
     <row r="14" spans="1:12" ht="17.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="14"/>
       <c r="B14" s="17" t="str">
-        <f t="shared" si="7"/>
+        <f>IFERROR(VLOOKUP(A14,$A$25:$D$139,2,FALSE),"-")</f>
         <v>-</v>
       </c>
       <c r="C14" s="17" t="str">
@@ -6455,22 +7444,22 @@
         <v>0</v>
       </c>
       <c r="J14" s="17" t="str">
+        <f>IFERROR(VLOOKUP(A14,$A$25:$D$139,3,FALSE),"-")</f>
+        <v>-</v>
+      </c>
+      <c r="K14" s="17" t="str">
+        <f>IFERROR(VLOOKUP(A14,$A$25:$D$139,4,FALSE),"-")</f>
+        <v>-</v>
+      </c>
+      <c r="L14" s="17" t="str">
         <f t="shared" si="4"/>
-        <v>-</v>
-      </c>
-      <c r="K14" s="17" t="str">
-        <f t="shared" si="5"/>
-        <v>-</v>
-      </c>
-      <c r="L14" s="17" t="str">
-        <f t="shared" si="6"/>
         <v>-</v>
       </c>
     </row>
     <row r="15" spans="1:12" ht="17.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="14"/>
       <c r="B15" s="17" t="str">
-        <f t="shared" si="7"/>
+        <f>IFERROR(VLOOKUP(A15,$A$25:$D$139,2,FALSE),"-")</f>
         <v>-</v>
       </c>
       <c r="C15" s="17" t="str">
@@ -6491,28 +7480,28 @@
         <v>0</v>
       </c>
       <c r="J15" s="17" t="str">
+        <f>IFERROR(VLOOKUP(A15,$A$25:$D$139,3,FALSE),"-")</f>
+        <v>-</v>
+      </c>
+      <c r="K15" s="17" t="str">
+        <f>IFERROR(VLOOKUP(A15,$A$25:$D$139,4,FALSE),"-")</f>
+        <v>-</v>
+      </c>
+      <c r="L15" s="17" t="str">
         <f t="shared" si="4"/>
         <v>-</v>
       </c>
-      <c r="K15" s="17" t="str">
-        <f t="shared" si="5"/>
-        <v>-</v>
-      </c>
-      <c r="L15" s="17" t="str">
-        <f t="shared" si="6"/>
-        <v>-</v>
-      </c>
     </row>
     <row r="16" spans="1:12" ht="16.5" thickTop="1" x14ac:dyDescent="0.25"/>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:17" x14ac:dyDescent="0.25">
       <c r="D17" t="s">
-        <v>393</v>
+        <v>376</v>
       </c>
       <c r="F17" s="23" t="s">
-        <v>391</v>
-      </c>
-    </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="18" spans="1:17" x14ac:dyDescent="0.25">
       <c r="D18" s="14">
         <v>1</v>
       </c>
@@ -6525,18 +7514,28 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:17" x14ac:dyDescent="0.25">
       <c r="F19" s="43">
         <f>F18/20</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="L21" s="1"/>
-    </row>
-    <row r="22" spans="1:12" ht="20.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="N19" s="51"/>
+      <c r="P19" s="18"/>
+      <c r="Q19" s="18"/>
+    </row>
+    <row r="20" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="N20" s="51"/>
+      <c r="P20" s="18"/>
+      <c r="Q20" s="18"/>
+    </row>
+    <row r="21" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="N21" s="51"/>
+      <c r="P21" s="18"/>
+      <c r="Q21" s="18"/>
+    </row>
+    <row r="22" spans="1:17" ht="20.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A22" s="40" t="s">
-        <v>421</v>
+        <v>404</v>
       </c>
       <c r="B22" s="40"/>
       <c r="C22" s="40"/>
@@ -6544,32 +7543,34 @@
       <c r="E22" s="40"/>
       <c r="H22" s="46"/>
     </row>
-    <row r="23" spans="1:12" ht="16.5" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:17" ht="16.5" thickTop="1" x14ac:dyDescent="0.25">
       <c r="C23" t="s">
-        <v>389</v>
+        <v>372</v>
       </c>
       <c r="D23" t="s">
-        <v>390</v>
+        <v>373</v>
       </c>
       <c r="E23" t="s">
-        <v>418</v>
+        <v>401</v>
       </c>
       <c r="J23" s="1"/>
-    </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="N23" s="51"/>
+    </row>
+    <row r="24" spans="1:17" x14ac:dyDescent="0.25">
       <c r="C24" t="s">
-        <v>250</v>
+        <v>233</v>
       </c>
       <c r="D24" t="s">
-        <v>388</v>
-      </c>
-    </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>384</v>
+        <v>371</v>
+      </c>
+      <c r="N24" s="51"/>
+    </row>
+    <row r="25" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A25" s="56" t="s">
+        <v>367</v>
       </c>
       <c r="B25" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="C25">
         <v>13.59</v>
@@ -6578,15 +7579,16 @@
         <v>1.008</v>
       </c>
       <c r="E25" t="s">
-        <v>419</v>
-      </c>
-    </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
+        <v>402</v>
+      </c>
+      <c r="N25" s="51"/>
+    </row>
+    <row r="26" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>383</v>
+        <v>366</v>
       </c>
       <c r="B26" t="s">
-        <v>172</v>
+        <v>161</v>
       </c>
       <c r="C26">
         <v>24.58</v>
@@ -6595,12 +7597,12 @@
         <v>4.0026000000000002</v>
       </c>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>134</v>
+    <row r="27" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A27" s="54" t="s">
+        <v>124</v>
       </c>
       <c r="B27" t="s">
-        <v>133</v>
+        <v>123</v>
       </c>
       <c r="C27">
         <v>5.39</v>
@@ -6609,12 +7611,12 @@
         <v>7</v>
       </c>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>201</v>
+    <row r="28" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A28" s="55" t="s">
+        <v>189</v>
       </c>
       <c r="B28" t="s">
-        <v>200</v>
+        <v>188</v>
       </c>
       <c r="C28">
         <v>9.32</v>
@@ -6623,12 +7625,12 @@
         <v>9.0121000000000002</v>
       </c>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>205</v>
+        <v>193</v>
       </c>
       <c r="B29" t="s">
-        <v>204</v>
+        <v>192</v>
       </c>
       <c r="C29">
         <v>8.2899999999999991</v>
@@ -6637,12 +7639,12 @@
         <v>10.81</v>
       </c>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>40</v>
+    <row r="30" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A30" s="56" t="s">
+        <v>35</v>
       </c>
       <c r="B30" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="C30">
         <v>11.26</v>
@@ -6651,12 +7653,12 @@
         <v>12.010999999999999</v>
       </c>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>382</v>
+    <row r="31" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A31" s="56" t="s">
+        <v>365</v>
       </c>
       <c r="B31" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="C31">
         <v>14.53</v>
@@ -6665,15 +7667,15 @@
         <v>14.007</v>
       </c>
       <c r="E31" t="s">
-        <v>419</v>
-      </c>
-    </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
-        <v>241</v>
+        <v>402</v>
+      </c>
+    </row>
+    <row r="32" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A32" s="56" t="s">
+        <v>224</v>
       </c>
       <c r="B32" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C32">
         <v>13.61</v>
@@ -6682,15 +7684,15 @@
         <v>15.999000000000001</v>
       </c>
       <c r="E32" t="s">
-        <v>419</v>
+        <v>402</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
-        <v>242</v>
+      <c r="A33" s="56" t="s">
+        <v>225</v>
       </c>
       <c r="B33" t="s">
-        <v>166</v>
+        <v>156</v>
       </c>
       <c r="C33">
         <v>17.420000000000002</v>
@@ -6699,15 +7701,15 @@
         <v>18.998000000000001</v>
       </c>
       <c r="E33" t="s">
-        <v>419</v>
+        <v>402</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>381</v>
+        <v>364</v>
       </c>
       <c r="B34" t="s">
-        <v>243</v>
+        <v>226</v>
       </c>
       <c r="C34">
         <v>21.56</v>
@@ -6717,11 +7719,11 @@
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
-        <v>380</v>
+      <c r="A35" s="54" t="s">
+        <v>363</v>
       </c>
       <c r="B35" t="s">
-        <v>244</v>
+        <v>227</v>
       </c>
       <c r="C35">
         <v>5.13</v>
@@ -6731,11 +7733,11 @@
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
-        <v>379</v>
+      <c r="A36" s="55" t="s">
+        <v>362</v>
       </c>
       <c r="B36" t="s">
-        <v>245</v>
+        <v>228</v>
       </c>
       <c r="C36">
         <v>7.64</v>
@@ -6746,10 +7748,10 @@
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="B37" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="C37">
         <v>5.98</v>
@@ -6760,10 +7762,10 @@
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>164</v>
+        <v>154</v>
       </c>
       <c r="B38" t="s">
-        <v>163</v>
+        <v>153</v>
       </c>
       <c r="C38">
         <v>8.15</v>
@@ -6773,11 +7775,11 @@
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
-        <v>37</v>
+      <c r="A39" s="56" t="s">
+        <v>33</v>
       </c>
       <c r="B39" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="C39">
         <v>10.48</v>
@@ -6787,11 +7789,11 @@
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
-        <v>378</v>
+      <c r="A40" s="56" t="s">
+        <v>361</v>
       </c>
       <c r="B40" t="s">
-        <v>246</v>
+        <v>229</v>
       </c>
       <c r="C40">
         <v>10.36</v>
@@ -6801,11 +7803,11 @@
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
-        <v>377</v>
+      <c r="A41" s="56" t="s">
+        <v>360</v>
       </c>
       <c r="B41" t="s">
-        <v>165</v>
+        <v>155</v>
       </c>
       <c r="C41">
         <v>12.96</v>
@@ -6814,15 +7816,15 @@
         <v>18.9984</v>
       </c>
       <c r="E41" t="s">
-        <v>419</v>
+        <v>402</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
-        <v>11</v>
+      <c r="A42" s="57" t="s">
+        <v>10</v>
       </c>
       <c r="B42" t="s">
-        <v>247</v>
+        <v>230</v>
       </c>
       <c r="C42">
         <v>15.75</v>
@@ -6832,11 +7834,11 @@
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A43" t="s">
-        <v>361</v>
+      <c r="A43" s="54" t="s">
+        <v>430</v>
       </c>
       <c r="B43" t="s">
-        <v>248</v>
+        <v>231</v>
       </c>
       <c r="C43">
         <v>4.34</v>
@@ -6846,11 +7848,11 @@
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A44" t="s">
-        <v>240</v>
+      <c r="A44" s="55" t="s">
+        <v>223</v>
       </c>
       <c r="B44" t="s">
-        <v>251</v>
+        <v>234</v>
       </c>
       <c r="C44">
         <v>6.11</v>
@@ -6860,11 +7862,11 @@
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A45" t="s">
-        <v>376</v>
+      <c r="A45" s="56" t="s">
+        <v>359</v>
       </c>
       <c r="B45" t="s">
-        <v>253</v>
+        <v>236</v>
       </c>
       <c r="C45">
         <v>6.56</v>
@@ -6875,10 +7877,10 @@
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>375</v>
+        <v>358</v>
       </c>
       <c r="B46" t="s">
-        <v>252</v>
+        <v>235</v>
       </c>
       <c r="C46">
         <v>6.82</v>
@@ -6889,10 +7891,10 @@
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>374</v>
+        <v>357</v>
       </c>
       <c r="B47" t="s">
-        <v>254</v>
+        <v>237</v>
       </c>
       <c r="C47">
         <v>6.74</v>
@@ -6903,10 +7905,10 @@
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>373</v>
+        <v>356</v>
       </c>
       <c r="B48" t="s">
-        <v>255</v>
+        <v>238</v>
       </c>
       <c r="C48">
         <v>6.76</v>
@@ -6917,10 +7919,10 @@
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>372</v>
+        <v>355</v>
       </c>
       <c r="B49" t="s">
-        <v>256</v>
+        <v>239</v>
       </c>
       <c r="C49">
         <v>7.43</v>
@@ -6931,10 +7933,10 @@
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>239</v>
+        <v>222</v>
       </c>
       <c r="B50" t="s">
-        <v>249</v>
+        <v>232</v>
       </c>
       <c r="C50">
         <v>7.9</v>
@@ -6945,10 +7947,10 @@
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>371</v>
+        <v>354</v>
       </c>
       <c r="B51" t="s">
-        <v>257</v>
+        <v>240</v>
       </c>
       <c r="C51">
         <v>7.88</v>
@@ -6959,10 +7961,10 @@
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>370</v>
+        <v>353</v>
       </c>
       <c r="B52" t="s">
-        <v>369</v>
+        <v>352</v>
       </c>
       <c r="C52">
         <v>7.63</v>
@@ -6973,10 +7975,10 @@
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>368</v>
+        <v>351</v>
       </c>
       <c r="B53" t="s">
-        <v>258</v>
+        <v>241</v>
       </c>
       <c r="C53">
         <v>7.72</v>
@@ -6987,10 +7989,10 @@
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>367</v>
+        <v>350</v>
       </c>
       <c r="B54" t="s">
-        <v>259</v>
+        <v>242</v>
       </c>
       <c r="C54">
         <v>9.39</v>
@@ -7001,10 +8003,10 @@
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>366</v>
+        <v>349</v>
       </c>
       <c r="B55" t="s">
-        <v>260</v>
+        <v>243</v>
       </c>
       <c r="C55">
         <v>5.99</v>
@@ -7015,10 +8017,10 @@
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>365</v>
+        <v>348</v>
       </c>
       <c r="B56" t="s">
-        <v>261</v>
+        <v>244</v>
       </c>
       <c r="C56">
         <v>7.89</v>
@@ -7029,10 +8031,10 @@
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>364</v>
+        <v>347</v>
       </c>
       <c r="B57" t="s">
-        <v>262</v>
+        <v>245</v>
       </c>
       <c r="C57">
         <v>9.7799999999999994</v>
@@ -7042,11 +8044,11 @@
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A58" t="s">
-        <v>363</v>
+      <c r="A58" s="56" t="s">
+        <v>346</v>
       </c>
       <c r="B58" t="s">
-        <v>263</v>
+        <v>246</v>
       </c>
       <c r="C58">
         <v>9.75</v>
@@ -7056,11 +8058,11 @@
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A59" t="s">
-        <v>362</v>
+      <c r="A59" s="56" t="s">
+        <v>345</v>
       </c>
       <c r="B59" t="s">
-        <v>264</v>
+        <v>247</v>
       </c>
       <c r="C59">
         <v>11.81</v>
@@ -7069,15 +8071,15 @@
         <v>79.900000000000006</v>
       </c>
       <c r="E59" t="s">
-        <v>419</v>
+        <v>402</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A60" t="s">
-        <v>361</v>
+      <c r="A60" s="57" t="s">
+        <v>344</v>
       </c>
       <c r="B60" t="s">
-        <v>265</v>
+        <v>248</v>
       </c>
       <c r="C60">
         <v>13.99</v>
@@ -7087,11 +8089,11 @@
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A61" t="s">
-        <v>360</v>
+      <c r="A61" s="54" t="s">
+        <v>343</v>
       </c>
       <c r="B61" t="s">
-        <v>266</v>
+        <v>249</v>
       </c>
       <c r="C61">
         <v>4.17</v>
@@ -7101,11 +8103,11 @@
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A62" t="s">
-        <v>359</v>
+      <c r="A62" s="55" t="s">
+        <v>342</v>
       </c>
       <c r="B62" t="s">
-        <v>267</v>
+        <v>250</v>
       </c>
       <c r="C62">
         <v>5.69</v>
@@ -7116,10 +8118,10 @@
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>331</v>
+        <v>402</v>
       </c>
       <c r="B63" t="s">
-        <v>268</v>
+        <v>251</v>
       </c>
       <c r="C63">
         <v>6.21</v>
@@ -7130,10 +8132,10 @@
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>358</v>
+        <v>341</v>
       </c>
       <c r="B64" t="s">
-        <v>269</v>
+        <v>252</v>
       </c>
       <c r="C64">
         <v>6.63</v>
@@ -7144,10 +8146,10 @@
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>357</v>
+        <v>340</v>
       </c>
       <c r="B65" t="s">
-        <v>270</v>
+        <v>253</v>
       </c>
       <c r="C65">
         <v>6.75</v>
@@ -7158,10 +8160,10 @@
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>356</v>
+        <v>339</v>
       </c>
       <c r="B66" t="s">
-        <v>271</v>
+        <v>254</v>
       </c>
       <c r="C66">
         <v>7.09</v>
@@ -7172,10 +8174,10 @@
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>355</v>
+        <v>338</v>
       </c>
       <c r="B67" t="s">
-        <v>272</v>
+        <v>255</v>
       </c>
       <c r="C67">
         <v>7.28</v>
@@ -7186,10 +8188,10 @@
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>354</v>
+        <v>337</v>
       </c>
       <c r="B68" t="s">
-        <v>273</v>
+        <v>256</v>
       </c>
       <c r="C68">
         <v>7.36</v>
@@ -7200,10 +8202,10 @@
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>353</v>
+        <v>336</v>
       </c>
       <c r="B69" t="s">
-        <v>274</v>
+        <v>257</v>
       </c>
       <c r="C69">
         <v>7.45</v>
@@ -7214,10 +8216,10 @@
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>352</v>
+        <v>335</v>
       </c>
       <c r="B70" t="s">
-        <v>275</v>
+        <v>258</v>
       </c>
       <c r="C70">
         <v>8.33</v>
@@ -7228,10 +8230,10 @@
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>351</v>
+        <v>334</v>
       </c>
       <c r="B71" t="s">
-        <v>276</v>
+        <v>259</v>
       </c>
       <c r="C71">
         <v>7.57</v>
@@ -7242,10 +8244,10 @@
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>350</v>
+        <v>333</v>
       </c>
       <c r="B72" t="s">
-        <v>277</v>
+        <v>260</v>
       </c>
       <c r="C72">
         <v>8.99</v>
@@ -7256,10 +8258,10 @@
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>349</v>
+        <v>332</v>
       </c>
       <c r="B73" t="s">
-        <v>278</v>
+        <v>261</v>
       </c>
       <c r="C73">
         <v>5.78</v>
@@ -7270,10 +8272,10 @@
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>348</v>
+        <v>331</v>
       </c>
       <c r="B74" t="s">
-        <v>279</v>
+        <v>262</v>
       </c>
       <c r="C74">
         <v>7.34</v>
@@ -7284,10 +8286,10 @@
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>347</v>
+        <v>330</v>
       </c>
       <c r="B75" t="s">
-        <v>280</v>
+        <v>263</v>
       </c>
       <c r="C75">
         <v>8.6</v>
@@ -7298,10 +8300,10 @@
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>346</v>
+        <v>329</v>
       </c>
       <c r="B76" t="s">
-        <v>281</v>
+        <v>264</v>
       </c>
       <c r="C76">
         <v>9</v>
@@ -7311,11 +8313,11 @@
       </c>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A77" t="s">
-        <v>420</v>
+      <c r="A77" s="56" t="s">
+        <v>403</v>
       </c>
       <c r="B77" t="s">
-        <v>282</v>
+        <v>265</v>
       </c>
       <c r="C77">
         <v>10.45</v>
@@ -7324,15 +8326,15 @@
         <v>126.9045</v>
       </c>
       <c r="E77" t="s">
-        <v>419</v>
+        <v>402</v>
       </c>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A78" t="s">
-        <v>13</v>
+      <c r="A78" s="57" t="s">
+        <v>12</v>
       </c>
       <c r="B78" t="s">
-        <v>283</v>
+        <v>266</v>
       </c>
       <c r="C78">
         <v>12.12</v>
@@ -7342,11 +8344,11 @@
       </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A79" t="s">
-        <v>217</v>
+      <c r="A79" s="54" t="s">
+        <v>204</v>
       </c>
       <c r="B79" t="s">
-        <v>284</v>
+        <v>267</v>
       </c>
       <c r="C79">
         <v>3.89</v>
@@ -7356,11 +8358,11 @@
       </c>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A80" t="s">
-        <v>345</v>
+      <c r="A80" s="55" t="s">
+        <v>328</v>
       </c>
       <c r="B80" t="s">
-        <v>285</v>
+        <v>268</v>
       </c>
       <c r="C80">
         <v>5.21</v>
@@ -7370,11 +8372,11 @@
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A81" t="s">
-        <v>344</v>
+      <c r="A81" s="53" t="s">
+        <v>327</v>
       </c>
       <c r="B81" t="s">
-        <v>286</v>
+        <v>269</v>
       </c>
       <c r="C81">
         <v>5.57</v>
@@ -7384,11 +8386,11 @@
       </c>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A82" t="s">
-        <v>343</v>
+      <c r="A82" s="53" t="s">
+        <v>326</v>
       </c>
       <c r="B82" t="s">
-        <v>287</v>
+        <v>270</v>
       </c>
       <c r="C82">
         <v>5.53</v>
@@ -7398,11 +8400,11 @@
       </c>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A83" t="s">
-        <v>342</v>
+      <c r="A83" s="53" t="s">
+        <v>325</v>
       </c>
       <c r="B83" t="s">
-        <v>288</v>
+        <v>271</v>
       </c>
       <c r="C83">
         <v>5.47</v>
@@ -7412,11 +8414,11 @@
       </c>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A84" t="s">
-        <v>341</v>
+      <c r="A84" s="53" t="s">
+        <v>324</v>
       </c>
       <c r="B84" t="s">
-        <v>289</v>
+        <v>272</v>
       </c>
       <c r="C84">
         <v>5.52</v>
@@ -7426,11 +8428,11 @@
       </c>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A85" t="s">
-        <v>340</v>
+      <c r="A85" s="53" t="s">
+        <v>323</v>
       </c>
       <c r="B85" t="s">
-        <v>290</v>
+        <v>273</v>
       </c>
       <c r="C85">
         <v>5.58</v>
@@ -7440,11 +8442,11 @@
       </c>
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A86" t="s">
-        <v>339</v>
+      <c r="A86" s="53" t="s">
+        <v>322</v>
       </c>
       <c r="B86" t="s">
-        <v>291</v>
+        <v>274</v>
       </c>
       <c r="C86">
         <v>5.64</v>
@@ -7454,11 +8456,11 @@
       </c>
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A87" t="s">
-        <v>338</v>
+      <c r="A87" s="53" t="s">
+        <v>321</v>
       </c>
       <c r="B87" t="s">
-        <v>292</v>
+        <v>275</v>
       </c>
       <c r="C87">
         <v>5.67</v>
@@ -7468,11 +8470,11 @@
       </c>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A88" t="s">
-        <v>337</v>
+      <c r="A88" s="53" t="s">
+        <v>320</v>
       </c>
       <c r="B88" t="s">
-        <v>293</v>
+        <v>276</v>
       </c>
       <c r="C88">
         <v>6.15</v>
@@ -7482,11 +8484,11 @@
       </c>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A89" t="s">
-        <v>336</v>
+      <c r="A89" s="53" t="s">
+        <v>319</v>
       </c>
       <c r="B89" t="s">
-        <v>294</v>
+        <v>277</v>
       </c>
       <c r="C89">
         <v>5.86</v>
@@ -7496,11 +8498,11 @@
       </c>
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A90" t="s">
-        <v>335</v>
+      <c r="A90" s="53" t="s">
+        <v>318</v>
       </c>
       <c r="B90" t="s">
-        <v>295</v>
+        <v>278</v>
       </c>
       <c r="C90">
         <v>5.93</v>
@@ -7510,11 +8512,11 @@
       </c>
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A91" t="s">
-        <v>334</v>
+      <c r="A91" s="53" t="s">
+        <v>317</v>
       </c>
       <c r="B91" t="s">
-        <v>296</v>
+        <v>279</v>
       </c>
       <c r="C91">
         <v>6.02</v>
@@ -7524,11 +8526,11 @@
       </c>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A92" t="s">
-        <v>333</v>
+      <c r="A92" s="53" t="s">
+        <v>316</v>
       </c>
       <c r="B92" t="s">
-        <v>297</v>
+        <v>280</v>
       </c>
       <c r="C92">
         <v>6.1</v>
@@ -7538,11 +8540,11 @@
       </c>
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A93" t="s">
-        <v>332</v>
+      <c r="A93" s="53" t="s">
+        <v>315</v>
       </c>
       <c r="B93" t="s">
-        <v>298</v>
+        <v>281</v>
       </c>
       <c r="C93">
         <v>6.18</v>
@@ -7552,11 +8554,11 @@
       </c>
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A94" t="s">
-        <v>331</v>
+      <c r="A94" s="53" t="s">
+        <v>314</v>
       </c>
       <c r="B94" t="s">
-        <v>299</v>
+        <v>282</v>
       </c>
       <c r="C94">
         <v>6.25</v>
@@ -7566,11 +8568,11 @@
       </c>
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A95" t="s">
-        <v>330</v>
+      <c r="A95" s="53" t="s">
+        <v>313</v>
       </c>
       <c r="B95" t="s">
-        <v>300</v>
+        <v>283</v>
       </c>
       <c r="C95">
         <v>5.42</v>
@@ -7581,10 +8583,10 @@
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>329</v>
+        <v>312</v>
       </c>
       <c r="B96" t="s">
-        <v>301</v>
+        <v>284</v>
       </c>
       <c r="C96">
         <v>6.82</v>
@@ -7595,10 +8597,10 @@
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>328</v>
+        <v>311</v>
       </c>
       <c r="B97" t="s">
-        <v>302</v>
+        <v>285</v>
       </c>
       <c r="C97">
         <v>7.54</v>
@@ -7609,10 +8611,10 @@
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>327</v>
+        <v>310</v>
       </c>
       <c r="B98" t="s">
-        <v>303</v>
+        <v>286</v>
       </c>
       <c r="C98">
         <v>7.86</v>
@@ -7623,10 +8625,10 @@
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>326</v>
+        <v>309</v>
       </c>
       <c r="B99" t="s">
-        <v>304</v>
+        <v>287</v>
       </c>
       <c r="C99">
         <v>7.83</v>
@@ -7637,10 +8639,10 @@
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>325</v>
+        <v>308</v>
       </c>
       <c r="B100" t="s">
-        <v>305</v>
+        <v>288</v>
       </c>
       <c r="C100">
         <v>8.43</v>
@@ -7651,10 +8653,10 @@
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>324</v>
+        <v>307</v>
       </c>
       <c r="B101" t="s">
-        <v>306</v>
+        <v>289</v>
       </c>
       <c r="C101">
         <v>8.9600000000000009</v>
@@ -7665,10 +8667,10 @@
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>323</v>
+        <v>306</v>
       </c>
       <c r="B102" t="s">
-        <v>307</v>
+        <v>290</v>
       </c>
       <c r="C102">
         <v>8.9499999999999993</v>
@@ -7679,10 +8681,10 @@
     </row>
     <row r="103" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>322</v>
+        <v>305</v>
       </c>
       <c r="B103" t="s">
-        <v>308</v>
+        <v>291</v>
       </c>
       <c r="C103">
         <v>9.2200000000000006</v>
@@ -7693,10 +8695,10 @@
     </row>
     <row r="104" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>321</v>
+        <v>304</v>
       </c>
       <c r="B104" t="s">
-        <v>309</v>
+        <v>292</v>
       </c>
       <c r="C104">
         <v>10.43</v>
@@ -7707,10 +8709,10 @@
     </row>
     <row r="105" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>320</v>
+        <v>303</v>
       </c>
       <c r="B105" t="s">
-        <v>310</v>
+        <v>293</v>
       </c>
       <c r="C105">
         <v>6.1</v>
@@ -7721,10 +8723,10 @@
     </row>
     <row r="106" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="B106" t="s">
-        <v>311</v>
+        <v>294</v>
       </c>
       <c r="C106">
         <v>7.41</v>
@@ -7735,10 +8737,10 @@
     </row>
     <row r="107" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>319</v>
+        <v>302</v>
       </c>
       <c r="B107" t="s">
-        <v>312</v>
+        <v>295</v>
       </c>
       <c r="C107">
         <v>7.28</v>
@@ -7749,10 +8751,10 @@
     </row>
     <row r="108" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>318</v>
+        <v>301</v>
       </c>
       <c r="B108" t="s">
-        <v>313</v>
+        <v>296</v>
       </c>
       <c r="C108">
         <v>8.41</v>
@@ -7762,11 +8764,11 @@
       </c>
     </row>
     <row r="109" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A109" t="s">
-        <v>317</v>
+      <c r="A109" s="56" t="s">
+        <v>300</v>
       </c>
       <c r="B109" t="s">
-        <v>314</v>
+        <v>297</v>
       </c>
       <c r="C109">
         <v>9.31</v>
@@ -7776,11 +8778,11 @@
       </c>
     </row>
     <row r="110" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A110" t="s">
-        <v>395</v>
+      <c r="A110" s="57" t="s">
+        <v>378</v>
       </c>
       <c r="B110" t="s">
-        <v>315</v>
+        <v>298</v>
       </c>
       <c r="C110">
         <v>10.74</v>
@@ -7790,11 +8792,11 @@
       </c>
     </row>
     <row r="111" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A111" t="s">
-        <v>396</v>
+      <c r="A111" s="54" t="s">
+        <v>379</v>
       </c>
       <c r="B111" t="s">
-        <v>406</v>
+        <v>389</v>
       </c>
       <c r="C111">
         <v>4.07</v>
@@ -7804,11 +8806,11 @@
       </c>
     </row>
     <row r="112" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A112" t="s">
-        <v>316</v>
+      <c r="A112" s="55" t="s">
+        <v>299</v>
       </c>
       <c r="B112" t="s">
-        <v>407</v>
+        <v>390</v>
       </c>
       <c r="C112">
         <v>5.27</v>
@@ -7819,173 +8821,384 @@
     </row>
     <row r="113" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>397</v>
+        <v>446</v>
       </c>
       <c r="B113" t="s">
-        <v>408</v>
+        <v>475</v>
       </c>
       <c r="C113">
-        <v>5.17</v>
+        <v>6</v>
       </c>
       <c r="D113">
-        <v>227.02780000000001</v>
+        <v>267.12200000000001</v>
       </c>
     </row>
     <row r="114" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>215</v>
+        <v>447</v>
       </c>
       <c r="B114" t="s">
-        <v>214</v>
-      </c>
-      <c r="C114">
-        <v>6.3</v>
+        <v>474</v>
       </c>
       <c r="D114">
-        <v>232.03800000000001</v>
+        <v>268.12599999999998</v>
       </c>
     </row>
     <row r="115" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>398</v>
+        <v>448</v>
       </c>
       <c r="B115" t="s">
-        <v>409</v>
-      </c>
-      <c r="C115">
-        <v>5.89</v>
+        <v>473</v>
       </c>
       <c r="D115">
-        <v>231.0359</v>
+        <v>269.12799999999999</v>
       </c>
     </row>
     <row r="116" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>130</v>
+        <v>449</v>
       </c>
       <c r="B116" t="s">
-        <v>410</v>
-      </c>
-      <c r="C116">
-        <v>6.19</v>
+        <v>472</v>
       </c>
       <c r="D116">
-        <v>238.02889999999999</v>
+        <v>270.13299999999998</v>
       </c>
     </row>
     <row r="117" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>399</v>
+        <v>450</v>
       </c>
       <c r="B117" t="s">
-        <v>411</v>
-      </c>
-      <c r="C117">
-        <v>6.26</v>
+        <v>471</v>
       </c>
       <c r="D117">
-        <v>237.04820000000001</v>
+        <v>269.1336</v>
       </c>
     </row>
     <row r="118" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>207</v>
+        <v>451</v>
       </c>
       <c r="B118" t="s">
-        <v>206</v>
-      </c>
-      <c r="C118">
-        <v>6.02</v>
+        <v>470</v>
       </c>
       <c r="D118">
-        <v>244.0642</v>
+        <v>277.154</v>
       </c>
     </row>
     <row r="119" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>400</v>
+        <v>452</v>
       </c>
       <c r="B119" t="s">
-        <v>412</v>
-      </c>
-      <c r="C119">
-        <v>5.97</v>
+        <v>469</v>
       </c>
       <c r="D119">
-        <v>243.06139999999999</v>
+        <v>282.166</v>
       </c>
     </row>
     <row r="120" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>401</v>
+        <v>453</v>
       </c>
       <c r="B120" t="s">
-        <v>413</v>
-      </c>
-      <c r="C120">
-        <v>5.99</v>
+        <v>468</v>
       </c>
       <c r="D120">
-        <v>247.07040000000001</v>
+        <v>282.16899999999998</v>
       </c>
     </row>
     <row r="121" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>402</v>
+        <v>454</v>
       </c>
       <c r="B121" t="s">
-        <v>414</v>
-      </c>
-      <c r="C121">
-        <v>6.19</v>
+        <v>467</v>
       </c>
       <c r="D121">
-        <v>247.0703</v>
+        <v>286.17899999999997</v>
       </c>
     </row>
     <row r="122" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>403</v>
+        <v>455</v>
       </c>
       <c r="B122" t="s">
-        <v>415</v>
-      </c>
-      <c r="C122">
-        <v>6.28</v>
+        <v>466</v>
       </c>
       <c r="D122">
-        <v>251.08</v>
+        <v>286.18200000000002</v>
       </c>
     </row>
     <row r="123" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>404</v>
+        <v>456</v>
       </c>
       <c r="B123" t="s">
-        <v>416</v>
-      </c>
-      <c r="C123">
-        <v>6.42</v>
+        <v>465</v>
       </c>
       <c r="D123">
-        <v>252.083</v>
+        <v>290.19200000000001</v>
       </c>
     </row>
     <row r="124" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>405</v>
+        <v>457</v>
       </c>
       <c r="B124" t="s">
-        <v>417</v>
-      </c>
-      <c r="C124">
+        <v>464</v>
+      </c>
+      <c r="D124">
+        <v>290.19600000000003</v>
+      </c>
+    </row>
+    <row r="125" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A125" t="s">
+        <v>458</v>
+      </c>
+      <c r="B125" t="s">
+        <v>463</v>
+      </c>
+      <c r="D125">
+        <v>293.20499999999998</v>
+      </c>
+    </row>
+    <row r="126" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A126" t="s">
+        <v>459</v>
+      </c>
+      <c r="B126" t="s">
+        <v>462</v>
+      </c>
+      <c r="D126">
+        <v>294.21100000000001</v>
+      </c>
+    </row>
+    <row r="127" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A127" s="57" t="s">
+        <v>460</v>
+      </c>
+      <c r="B127" t="s">
+        <v>461</v>
+      </c>
+      <c r="D127">
+        <v>295.21600000000001</v>
+      </c>
+    </row>
+    <row r="128" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A128" s="52" t="s">
+        <v>380</v>
+      </c>
+      <c r="B128" t="s">
+        <v>391</v>
+      </c>
+      <c r="C128">
+        <v>5.17</v>
+      </c>
+      <c r="D128">
+        <v>227.02780000000001</v>
+      </c>
+    </row>
+    <row r="129" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A129" s="52" t="s">
+        <v>202</v>
+      </c>
+      <c r="B129" t="s">
+        <v>201</v>
+      </c>
+      <c r="C129">
+        <v>6.3</v>
+      </c>
+      <c r="D129">
+        <v>232.03800000000001</v>
+      </c>
+    </row>
+    <row r="130" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A130" s="52" t="s">
+        <v>381</v>
+      </c>
+      <c r="B130" t="s">
+        <v>392</v>
+      </c>
+      <c r="C130">
+        <v>5.89</v>
+      </c>
+      <c r="D130">
+        <v>231.0359</v>
+      </c>
+    </row>
+    <row r="131" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A131" s="52" t="s">
+        <v>120</v>
+      </c>
+      <c r="B131" t="s">
+        <v>393</v>
+      </c>
+      <c r="C131">
+        <v>6.19</v>
+      </c>
+      <c r="D131">
+        <v>238.02889999999999</v>
+      </c>
+    </row>
+    <row r="132" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A132" s="52" t="s">
+        <v>382</v>
+      </c>
+      <c r="B132" t="s">
+        <v>394</v>
+      </c>
+      <c r="C132">
+        <v>6.26</v>
+      </c>
+      <c r="D132">
+        <v>237.04820000000001</v>
+      </c>
+    </row>
+    <row r="133" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A133" s="52" t="s">
+        <v>195</v>
+      </c>
+      <c r="B133" t="s">
+        <v>194</v>
+      </c>
+      <c r="C133">
+        <v>6.02</v>
+      </c>
+      <c r="D133">
+        <v>244.0642</v>
+      </c>
+    </row>
+    <row r="134" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A134" s="52" t="s">
+        <v>383</v>
+      </c>
+      <c r="B134" t="s">
+        <v>395</v>
+      </c>
+      <c r="C134">
+        <v>5.97</v>
+      </c>
+      <c r="D134">
+        <v>243.06139999999999</v>
+      </c>
+    </row>
+    <row r="135" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A135" s="52" t="s">
+        <v>384</v>
+      </c>
+      <c r="B135" t="s">
+        <v>396</v>
+      </c>
+      <c r="C135">
+        <v>5.99</v>
+      </c>
+      <c r="D135">
+        <v>247.07040000000001</v>
+      </c>
+    </row>
+    <row r="136" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A136" s="52" t="s">
+        <v>385</v>
+      </c>
+      <c r="B136" t="s">
+        <v>397</v>
+      </c>
+      <c r="C136">
+        <v>6.19</v>
+      </c>
+      <c r="D136">
+        <v>247.0703</v>
+      </c>
+    </row>
+    <row r="137" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A137" s="52" t="s">
+        <v>386</v>
+      </c>
+      <c r="B137" t="s">
+        <v>398</v>
+      </c>
+      <c r="C137">
+        <v>6.28</v>
+      </c>
+      <c r="D137">
+        <v>251.08</v>
+      </c>
+    </row>
+    <row r="138" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A138" s="52" t="s">
+        <v>387</v>
+      </c>
+      <c r="B138" t="s">
+        <v>399</v>
+      </c>
+      <c r="C138">
+        <v>6.42</v>
+      </c>
+      <c r="D138">
+        <v>252.083</v>
+      </c>
+    </row>
+    <row r="139" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A139" s="52" t="s">
+        <v>388</v>
+      </c>
+      <c r="B139" t="s">
+        <v>400</v>
+      </c>
+      <c r="C139">
         <v>6.5</v>
       </c>
-      <c r="D124">
+      <c r="D139">
         <v>257.09500000000003</v>
+      </c>
+    </row>
+    <row r="140" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A140" s="52" t="s">
+        <v>440</v>
+      </c>
+      <c r="B140" t="s">
+        <v>443</v>
+      </c>
+      <c r="C140">
+        <v>6.58</v>
+      </c>
+      <c r="D140">
+        <v>258.09500000000003</v>
+      </c>
+    </row>
+    <row r="141" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A141" s="52" t="s">
+        <v>441</v>
+      </c>
+      <c r="B141" t="s">
+        <v>444</v>
+      </c>
+      <c r="C141">
+        <v>6.65</v>
+      </c>
+      <c r="D141">
+        <v>258.09800000000001</v>
+      </c>
+    </row>
+    <row r="142" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A142" s="52" t="s">
+        <v>442</v>
+      </c>
+      <c r="B142" t="s">
+        <v>445</v>
+      </c>
+      <c r="C142">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="D142">
+        <v>266.12</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
--- a/RR_ISRU.xlsx
+++ b/RR_ISRU.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="31620" yWindow="0" windowWidth="17700" windowHeight="10485" activeTab="2"/>
+    <workbookView xWindow="31620" yWindow="0" windowWidth="17700" windowHeight="10485"/>
   </bookViews>
   <sheets>
     <sheet name="Calc (Kg)" sheetId="6" r:id="rId1"/>
@@ -1745,7 +1745,7 @@
     <numFmt numFmtId="171" formatCode="#,##0.0000&quot;:1&quot;"/>
     <numFmt numFmtId="172" formatCode="0.000"/>
     <numFmt numFmtId="173" formatCode="0.0"/>
-    <numFmt numFmtId="180" formatCode="0.0%"/>
+    <numFmt numFmtId="174" formatCode="0.0%"/>
   </numFmts>
   <fonts count="19" x14ac:knownFonts="1">
     <font>
@@ -2112,12 +2112,6 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="4" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="4" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="3" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="1" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -2126,7 +2120,13 @@
     <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="18" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="180" fontId="0" fillId="0" borderId="0" xfId="9" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="174" fontId="0" fillId="0" borderId="0" xfId="9" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="4" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="3" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="10">
     <cellStyle name="Calculation" xfId="2" builtinId="22"/>
@@ -2459,15 +2459,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="20.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="48" t="s">
+      <c r="A1" s="57" t="s">
         <v>79</v>
       </c>
-      <c r="B1" s="48"/>
-      <c r="C1" s="48"/>
-      <c r="D1" s="48"/>
-      <c r="E1" s="48"/>
-      <c r="F1" s="48"/>
-      <c r="G1" s="48"/>
+      <c r="B1" s="57"/>
+      <c r="C1" s="57"/>
+      <c r="D1" s="57"/>
+      <c r="E1" s="57"/>
+      <c r="F1" s="57"/>
+      <c r="G1" s="57"/>
     </row>
     <row r="2" spans="1:12" ht="16.5" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A2" s="23" t="s">
@@ -2951,15 +2951,15 @@
       </c>
     </row>
     <row r="25" spans="1:12" ht="18" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="49" t="s">
+      <c r="A25" s="58" t="s">
         <v>62</v>
       </c>
-      <c r="B25" s="49"/>
-      <c r="C25" s="49"/>
-      <c r="D25" s="49"/>
-      <c r="E25" s="49"/>
-      <c r="F25" s="49"/>
-      <c r="G25" s="49"/>
+      <c r="B25" s="58"/>
+      <c r="C25" s="58"/>
+      <c r="D25" s="58"/>
+      <c r="E25" s="58"/>
+      <c r="F25" s="58"/>
+      <c r="G25" s="58"/>
     </row>
     <row r="26" spans="1:12" ht="16.5" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A26" s="7" t="s">
@@ -3013,15 +3013,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="20.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="48" t="s">
+      <c r="A1" s="57" t="s">
         <v>78</v>
       </c>
-      <c r="B1" s="48"/>
-      <c r="C1" s="48"/>
-      <c r="D1" s="48"/>
-      <c r="E1" s="48"/>
-      <c r="F1" s="48"/>
-      <c r="G1" s="48"/>
+      <c r="B1" s="57"/>
+      <c r="C1" s="57"/>
+      <c r="D1" s="57"/>
+      <c r="E1" s="57"/>
+      <c r="F1" s="57"/>
+      <c r="G1" s="57"/>
       <c r="H1" s="47"/>
       <c r="I1" s="47"/>
     </row>
@@ -3351,7 +3351,7 @@
       <c r="A20" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="B20" s="50">
+      <c r="B20" s="48">
         <v>0</v>
       </c>
       <c r="C20" s="14">
@@ -3842,7 +3842,7 @@
         <f>M5*O5</f>
         <v>11631.51</v>
       </c>
-      <c r="Q5" s="58">
+      <c r="Q5" s="56">
         <f>P5/$P$8</f>
         <v>0.70146498497745102</v>
       </c>
@@ -3894,7 +3894,7 @@
         <f t="shared" ref="P6:P7" si="1">M6*O6</f>
         <v>2482.16</v>
       </c>
-      <c r="Q6" s="58">
+      <c r="Q6" s="56">
         <f>P6/$P$8</f>
         <v>0.14969237245307185</v>
       </c>
@@ -3946,7 +3946,7 @@
         <f t="shared" si="1"/>
         <v>2468.0700000000002</v>
       </c>
-      <c r="Q7" s="58">
+      <c r="Q7" s="56">
         <f>P7/$P$8</f>
         <v>0.14884264256947702</v>
       </c>
@@ -7062,433 +7062,433 @@
     <row r="4" spans="1:12" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="14"/>
       <c r="B4" s="17" t="str">
-        <f>IFERROR(VLOOKUP(A4,$A$25:$D$139,2,FALSE),"-")</f>
+        <f t="shared" ref="B4:B15" si="0">IFERROR(VLOOKUP(A4,$A$25:$D$139,2,FALSE),"-")</f>
         <v>-</v>
       </c>
       <c r="C4" s="17" t="str">
-        <f t="shared" ref="C4:C15" si="0">IF(L4="Y","Yes","-")</f>
+        <f t="shared" ref="C4:C15" si="1">IF(L4="Y","Yes","-")</f>
         <v>-</v>
       </c>
       <c r="D4" s="14"/>
       <c r="E4" s="15">
-        <f t="shared" ref="E4:E15" si="1">D4*$D$18</f>
+        <f t="shared" ref="E4:E15" si="2">D4*$D$18</f>
         <v>0</v>
       </c>
       <c r="F4" s="15">
-        <f t="shared" ref="F4:F15" si="2">IFERROR(E4*J4,0)</f>
+        <f t="shared" ref="F4:F15" si="3">IFERROR(E4*J4,0)</f>
         <v>0</v>
       </c>
       <c r="G4" s="15">
-        <f t="shared" ref="G4:G15" si="3">IFERROR(E4*K4,0)</f>
+        <f t="shared" ref="G4:G15" si="4">IFERROR(E4*K4,0)</f>
         <v>0</v>
       </c>
       <c r="J4" s="17" t="str">
-        <f>IFERROR(VLOOKUP(A4,$A$25:$D$139,3,FALSE),"-")</f>
+        <f t="shared" ref="J4:J15" si="5">IFERROR(VLOOKUP(A4,$A$25:$D$139,3,FALSE),"-")</f>
         <v>-</v>
       </c>
       <c r="K4" s="17" t="str">
-        <f>IFERROR(VLOOKUP(A4,$A$25:$D$139,4,FALSE),"-")</f>
+        <f t="shared" ref="K4:K15" si="6">IFERROR(VLOOKUP(A4,$A$25:$D$139,4,FALSE),"-")</f>
         <v>-</v>
       </c>
       <c r="L4" s="17" t="str">
-        <f t="shared" ref="L4:L15" si="4">IFERROR(VLOOKUP(A4,$A$25:$E$124,5,FALSE),"-")</f>
+        <f t="shared" ref="L4:L15" si="7">IFERROR(VLOOKUP(A4,$A$25:$E$124,5,FALSE),"-")</f>
         <v>-</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="17.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="14"/>
       <c r="B5" s="17" t="str">
-        <f>IFERROR(VLOOKUP(A5,$A$25:$D$139,2,FALSE),"-")</f>
+        <f t="shared" si="0"/>
         <v>-</v>
       </c>
       <c r="C5" s="17" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>-</v>
       </c>
       <c r="D5" s="14"/>
       <c r="E5" s="15">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="F5" s="15">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="G5" s="15">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="H5" s="58"/>
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="H5" s="56"/>
       <c r="J5" s="17" t="str">
-        <f>IFERROR(VLOOKUP(A5,$A$25:$D$139,3,FALSE),"-")</f>
+        <f t="shared" si="5"/>
         <v>-</v>
       </c>
       <c r="K5" s="17" t="str">
-        <f>IFERROR(VLOOKUP(A5,$A$25:$D$139,4,FALSE),"-")</f>
+        <f t="shared" si="6"/>
         <v>-</v>
       </c>
       <c r="L5" s="17" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>-</v>
       </c>
     </row>
     <row r="6" spans="1:12" ht="17.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="14"/>
       <c r="B6" s="17" t="str">
-        <f>IFERROR(VLOOKUP(A6,$A$25:$D$139,2,FALSE),"-")</f>
+        <f t="shared" si="0"/>
         <v>-</v>
       </c>
       <c r="C6" s="17" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>-</v>
       </c>
       <c r="D6" s="14"/>
       <c r="E6" s="15">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="F6" s="15">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="G6" s="15">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="J6" s="17" t="str">
-        <f>IFERROR(VLOOKUP(A6,$A$25:$D$139,3,FALSE),"-")</f>
+        <f t="shared" si="5"/>
         <v>-</v>
       </c>
       <c r="K6" s="17" t="str">
-        <f>IFERROR(VLOOKUP(A6,$A$25:$D$139,4,FALSE),"-")</f>
+        <f t="shared" si="6"/>
         <v>-</v>
       </c>
       <c r="L6" s="17" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>-</v>
       </c>
     </row>
     <row r="7" spans="1:12" ht="17.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="14"/>
       <c r="B7" s="17" t="str">
-        <f>IFERROR(VLOOKUP(A7,$A$25:$D$139,2,FALSE),"-")</f>
+        <f t="shared" si="0"/>
         <v>-</v>
       </c>
       <c r="C7" s="17" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>-</v>
       </c>
       <c r="D7" s="14"/>
       <c r="E7" s="15">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="F7" s="15">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="G7" s="15">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="J7" s="17" t="str">
-        <f>IFERROR(VLOOKUP(A7,$A$25:$D$139,3,FALSE),"-")</f>
+        <f t="shared" si="5"/>
         <v>-</v>
       </c>
       <c r="K7" s="17" t="str">
-        <f>IFERROR(VLOOKUP(A7,$A$25:$D$139,4,FALSE),"-")</f>
+        <f t="shared" si="6"/>
         <v>-</v>
       </c>
       <c r="L7" s="17" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>-</v>
       </c>
     </row>
     <row r="8" spans="1:12" ht="17.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="14"/>
       <c r="B8" s="17" t="str">
-        <f>IFERROR(VLOOKUP(A8,$A$25:$D$139,2,FALSE),"-")</f>
+        <f t="shared" si="0"/>
         <v>-</v>
       </c>
       <c r="C8" s="17" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>-</v>
       </c>
       <c r="D8" s="14"/>
       <c r="E8" s="15">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="F8" s="15">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="G8" s="15">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="J8" s="17" t="str">
-        <f>IFERROR(VLOOKUP(A8,$A$25:$D$139,3,FALSE),"-")</f>
+        <f t="shared" si="5"/>
         <v>-</v>
       </c>
       <c r="K8" s="17" t="str">
-        <f>IFERROR(VLOOKUP(A8,$A$25:$D$139,4,FALSE),"-")</f>
+        <f t="shared" si="6"/>
         <v>-</v>
       </c>
       <c r="L8" s="17" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>-</v>
       </c>
     </row>
     <row r="9" spans="1:12" ht="17.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="14"/>
       <c r="B9" s="17" t="str">
-        <f>IFERROR(VLOOKUP(A9,$A$25:$D$139,2,FALSE),"-")</f>
+        <f t="shared" si="0"/>
         <v>-</v>
       </c>
       <c r="C9" s="17" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>-</v>
       </c>
       <c r="D9" s="14"/>
       <c r="E9" s="15">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="F9" s="15">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="G9" s="15">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="J9" s="17" t="str">
-        <f>IFERROR(VLOOKUP(A9,$A$25:$D$139,3,FALSE),"-")</f>
+        <f t="shared" si="5"/>
         <v>-</v>
       </c>
       <c r="K9" s="17" t="str">
-        <f>IFERROR(VLOOKUP(A9,$A$25:$D$139,4,FALSE),"-")</f>
+        <f t="shared" si="6"/>
         <v>-</v>
       </c>
       <c r="L9" s="17" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>-</v>
       </c>
     </row>
     <row r="10" spans="1:12" ht="17.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="14"/>
       <c r="B10" s="17" t="str">
-        <f>IFERROR(VLOOKUP(A10,$A$25:$D$139,2,FALSE),"-")</f>
+        <f t="shared" si="0"/>
         <v>-</v>
       </c>
       <c r="C10" s="17" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>-</v>
       </c>
       <c r="D10" s="14"/>
       <c r="E10" s="15">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="F10" s="15">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="G10" s="15">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="J10" s="17" t="str">
-        <f>IFERROR(VLOOKUP(A10,$A$25:$D$139,3,FALSE),"-")</f>
+        <f t="shared" si="5"/>
         <v>-</v>
       </c>
       <c r="K10" s="17" t="str">
-        <f>IFERROR(VLOOKUP(A10,$A$25:$D$139,4,FALSE),"-")</f>
+        <f t="shared" si="6"/>
         <v>-</v>
       </c>
       <c r="L10" s="17" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>-</v>
       </c>
     </row>
     <row r="11" spans="1:12" ht="17.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="14"/>
       <c r="B11" s="17" t="str">
-        <f>IFERROR(VLOOKUP(A11,$A$25:$D$139,2,FALSE),"-")</f>
+        <f t="shared" si="0"/>
         <v>-</v>
       </c>
       <c r="C11" s="17" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>-</v>
       </c>
       <c r="D11" s="14"/>
       <c r="E11" s="15">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="F11" s="15">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="G11" s="15">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="J11" s="17" t="str">
-        <f>IFERROR(VLOOKUP(A11,$A$25:$D$139,3,FALSE),"-")</f>
+        <f t="shared" si="5"/>
         <v>-</v>
       </c>
       <c r="K11" s="17" t="str">
-        <f>IFERROR(VLOOKUP(A11,$A$25:$D$139,4,FALSE),"-")</f>
+        <f t="shared" si="6"/>
         <v>-</v>
       </c>
       <c r="L11" s="17" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>-</v>
       </c>
     </row>
     <row r="12" spans="1:12" ht="17.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="14"/>
       <c r="B12" s="17" t="str">
-        <f>IFERROR(VLOOKUP(A12,$A$25:$D$139,2,FALSE),"-")</f>
+        <f t="shared" si="0"/>
         <v>-</v>
       </c>
       <c r="C12" s="17" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>-</v>
       </c>
       <c r="D12" s="14"/>
       <c r="E12" s="15">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="F12" s="15">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="G12" s="15">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="J12" s="17" t="str">
-        <f>IFERROR(VLOOKUP(A12,$A$25:$D$139,3,FALSE),"-")</f>
+        <f t="shared" si="5"/>
         <v>-</v>
       </c>
       <c r="K12" s="17" t="str">
-        <f>IFERROR(VLOOKUP(A12,$A$25:$D$139,4,FALSE),"-")</f>
+        <f t="shared" si="6"/>
         <v>-</v>
       </c>
       <c r="L12" s="17" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>-</v>
       </c>
     </row>
     <row r="13" spans="1:12" ht="17.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="14"/>
       <c r="B13" s="17" t="str">
-        <f>IFERROR(VLOOKUP(A13,$A$25:$D$139,2,FALSE),"-")</f>
+        <f t="shared" si="0"/>
         <v>-</v>
       </c>
       <c r="C13" s="17" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>-</v>
       </c>
       <c r="D13" s="14"/>
       <c r="E13" s="15">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="F13" s="15">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="G13" s="15">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="J13" s="17" t="str">
-        <f>IFERROR(VLOOKUP(A13,$A$25:$D$139,3,FALSE),"-")</f>
+        <f t="shared" si="5"/>
         <v>-</v>
       </c>
       <c r="K13" s="17" t="str">
-        <f>IFERROR(VLOOKUP(A13,$A$25:$D$139,4,FALSE),"-")</f>
+        <f t="shared" si="6"/>
         <v>-</v>
       </c>
       <c r="L13" s="17" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>-</v>
       </c>
     </row>
     <row r="14" spans="1:12" ht="17.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="14"/>
       <c r="B14" s="17" t="str">
-        <f>IFERROR(VLOOKUP(A14,$A$25:$D$139,2,FALSE),"-")</f>
+        <f t="shared" si="0"/>
         <v>-</v>
       </c>
       <c r="C14" s="17" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>-</v>
       </c>
       <c r="D14" s="14"/>
       <c r="E14" s="15">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="F14" s="15">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="G14" s="15">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="J14" s="17" t="str">
-        <f>IFERROR(VLOOKUP(A14,$A$25:$D$139,3,FALSE),"-")</f>
+        <f t="shared" si="5"/>
         <v>-</v>
       </c>
       <c r="K14" s="17" t="str">
-        <f>IFERROR(VLOOKUP(A14,$A$25:$D$139,4,FALSE),"-")</f>
+        <f t="shared" si="6"/>
         <v>-</v>
       </c>
       <c r="L14" s="17" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>-</v>
       </c>
     </row>
     <row r="15" spans="1:12" ht="17.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="14"/>
       <c r="B15" s="17" t="str">
-        <f>IFERROR(VLOOKUP(A15,$A$25:$D$139,2,FALSE),"-")</f>
+        <f t="shared" si="0"/>
         <v>-</v>
       </c>
       <c r="C15" s="17" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>-</v>
       </c>
       <c r="D15" s="14"/>
       <c r="E15" s="15">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="F15" s="15">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="G15" s="15">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="J15" s="17" t="str">
-        <f>IFERROR(VLOOKUP(A15,$A$25:$D$139,3,FALSE),"-")</f>
+        <f t="shared" si="5"/>
         <v>-</v>
       </c>
       <c r="K15" s="17" t="str">
-        <f>IFERROR(VLOOKUP(A15,$A$25:$D$139,4,FALSE),"-")</f>
+        <f t="shared" si="6"/>
         <v>-</v>
       </c>
       <c r="L15" s="17" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>-</v>
       </c>
     </row>
@@ -7519,17 +7519,17 @@
         <f>F18/20</f>
         <v>0</v>
       </c>
-      <c r="N19" s="51"/>
+      <c r="N19" s="49"/>
       <c r="P19" s="18"/>
       <c r="Q19" s="18"/>
     </row>
     <row r="20" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="N20" s="51"/>
+      <c r="N20" s="49"/>
       <c r="P20" s="18"/>
       <c r="Q20" s="18"/>
     </row>
     <row r="21" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="N21" s="51"/>
+      <c r="N21" s="49"/>
       <c r="P21" s="18"/>
       <c r="Q21" s="18"/>
     </row>
@@ -7554,7 +7554,7 @@
         <v>401</v>
       </c>
       <c r="J23" s="1"/>
-      <c r="N23" s="51"/>
+      <c r="N23" s="49"/>
     </row>
     <row r="24" spans="1:17" x14ac:dyDescent="0.25">
       <c r="C24" t="s">
@@ -7563,10 +7563,10 @@
       <c r="D24" t="s">
         <v>371</v>
       </c>
-      <c r="N24" s="51"/>
+      <c r="N24" s="49"/>
     </row>
     <row r="25" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A25" s="56" t="s">
+      <c r="A25" s="54" t="s">
         <v>367</v>
       </c>
       <c r="B25" t="s">
@@ -7581,7 +7581,7 @@
       <c r="E25" t="s">
         <v>402</v>
       </c>
-      <c r="N25" s="51"/>
+      <c r="N25" s="49"/>
     </row>
     <row r="26" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
@@ -7598,7 +7598,7 @@
       </c>
     </row>
     <row r="27" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A27" s="54" t="s">
+      <c r="A27" s="52" t="s">
         <v>124</v>
       </c>
       <c r="B27" t="s">
@@ -7612,7 +7612,7 @@
       </c>
     </row>
     <row r="28" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A28" s="55" t="s">
+      <c r="A28" s="53" t="s">
         <v>189</v>
       </c>
       <c r="B28" t="s">
@@ -7640,7 +7640,7 @@
       </c>
     </row>
     <row r="30" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A30" s="56" t="s">
+      <c r="A30" s="54" t="s">
         <v>35</v>
       </c>
       <c r="B30" t="s">
@@ -7654,7 +7654,7 @@
       </c>
     </row>
     <row r="31" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A31" s="56" t="s">
+      <c r="A31" s="54" t="s">
         <v>365</v>
       </c>
       <c r="B31" t="s">
@@ -7671,7 +7671,7 @@
       </c>
     </row>
     <row r="32" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A32" s="56" t="s">
+      <c r="A32" s="54" t="s">
         <v>224</v>
       </c>
       <c r="B32" t="s">
@@ -7688,7 +7688,7 @@
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A33" s="56" t="s">
+      <c r="A33" s="54" t="s">
         <v>225</v>
       </c>
       <c r="B33" t="s">
@@ -7719,7 +7719,7 @@
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A35" s="54" t="s">
+      <c r="A35" s="52" t="s">
         <v>363</v>
       </c>
       <c r="B35" t="s">
@@ -7733,7 +7733,7 @@
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A36" s="55" t="s">
+      <c r="A36" s="53" t="s">
         <v>362</v>
       </c>
       <c r="B36" t="s">
@@ -7775,7 +7775,7 @@
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A39" s="56" t="s">
+      <c r="A39" s="54" t="s">
         <v>33</v>
       </c>
       <c r="B39" t="s">
@@ -7789,7 +7789,7 @@
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A40" s="56" t="s">
+      <c r="A40" s="54" t="s">
         <v>361</v>
       </c>
       <c r="B40" t="s">
@@ -7803,7 +7803,7 @@
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A41" s="56" t="s">
+      <c r="A41" s="54" t="s">
         <v>360</v>
       </c>
       <c r="B41" t="s">
@@ -7820,7 +7820,7 @@
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A42" s="57" t="s">
+      <c r="A42" s="55" t="s">
         <v>10</v>
       </c>
       <c r="B42" t="s">
@@ -7834,7 +7834,7 @@
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A43" s="54" t="s">
+      <c r="A43" s="52" t="s">
         <v>430</v>
       </c>
       <c r="B43" t="s">
@@ -7848,7 +7848,7 @@
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A44" s="55" t="s">
+      <c r="A44" s="53" t="s">
         <v>223</v>
       </c>
       <c r="B44" t="s">
@@ -7862,7 +7862,7 @@
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A45" s="56" t="s">
+      <c r="A45" s="54" t="s">
         <v>359</v>
       </c>
       <c r="B45" t="s">
@@ -8044,7 +8044,7 @@
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A58" s="56" t="s">
+      <c r="A58" s="54" t="s">
         <v>346</v>
       </c>
       <c r="B58" t="s">
@@ -8058,7 +8058,7 @@
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A59" s="56" t="s">
+      <c r="A59" s="54" t="s">
         <v>345</v>
       </c>
       <c r="B59" t="s">
@@ -8075,7 +8075,7 @@
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A60" s="57" t="s">
+      <c r="A60" s="55" t="s">
         <v>344</v>
       </c>
       <c r="B60" t="s">
@@ -8089,7 +8089,7 @@
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A61" s="54" t="s">
+      <c r="A61" s="52" t="s">
         <v>343</v>
       </c>
       <c r="B61" t="s">
@@ -8103,7 +8103,7 @@
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A62" s="55" t="s">
+      <c r="A62" s="53" t="s">
         <v>342</v>
       </c>
       <c r="B62" t="s">
@@ -8313,7 +8313,7 @@
       </c>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A77" s="56" t="s">
+      <c r="A77" s="54" t="s">
         <v>403</v>
       </c>
       <c r="B77" t="s">
@@ -8330,7 +8330,7 @@
       </c>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A78" s="57" t="s">
+      <c r="A78" s="55" t="s">
         <v>12</v>
       </c>
       <c r="B78" t="s">
@@ -8344,7 +8344,7 @@
       </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A79" s="54" t="s">
+      <c r="A79" s="52" t="s">
         <v>204</v>
       </c>
       <c r="B79" t="s">
@@ -8358,7 +8358,7 @@
       </c>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A80" s="55" t="s">
+      <c r="A80" s="53" t="s">
         <v>328</v>
       </c>
       <c r="B80" t="s">
@@ -8372,7 +8372,7 @@
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A81" s="53" t="s">
+      <c r="A81" s="51" t="s">
         <v>327</v>
       </c>
       <c r="B81" t="s">
@@ -8386,7 +8386,7 @@
       </c>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A82" s="53" t="s">
+      <c r="A82" s="51" t="s">
         <v>326</v>
       </c>
       <c r="B82" t="s">
@@ -8400,7 +8400,7 @@
       </c>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A83" s="53" t="s">
+      <c r="A83" s="51" t="s">
         <v>325</v>
       </c>
       <c r="B83" t="s">
@@ -8414,7 +8414,7 @@
       </c>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A84" s="53" t="s">
+      <c r="A84" s="51" t="s">
         <v>324</v>
       </c>
       <c r="B84" t="s">
@@ -8428,7 +8428,7 @@
       </c>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A85" s="53" t="s">
+      <c r="A85" s="51" t="s">
         <v>323</v>
       </c>
       <c r="B85" t="s">
@@ -8442,7 +8442,7 @@
       </c>
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A86" s="53" t="s">
+      <c r="A86" s="51" t="s">
         <v>322</v>
       </c>
       <c r="B86" t="s">
@@ -8456,7 +8456,7 @@
       </c>
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A87" s="53" t="s">
+      <c r="A87" s="51" t="s">
         <v>321</v>
       </c>
       <c r="B87" t="s">
@@ -8470,7 +8470,7 @@
       </c>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A88" s="53" t="s">
+      <c r="A88" s="51" t="s">
         <v>320</v>
       </c>
       <c r="B88" t="s">
@@ -8484,7 +8484,7 @@
       </c>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A89" s="53" t="s">
+      <c r="A89" s="51" t="s">
         <v>319</v>
       </c>
       <c r="B89" t="s">
@@ -8498,7 +8498,7 @@
       </c>
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A90" s="53" t="s">
+      <c r="A90" s="51" t="s">
         <v>318</v>
       </c>
       <c r="B90" t="s">
@@ -8512,7 +8512,7 @@
       </c>
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A91" s="53" t="s">
+      <c r="A91" s="51" t="s">
         <v>317</v>
       </c>
       <c r="B91" t="s">
@@ -8526,7 +8526,7 @@
       </c>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A92" s="53" t="s">
+      <c r="A92" s="51" t="s">
         <v>316</v>
       </c>
       <c r="B92" t="s">
@@ -8540,7 +8540,7 @@
       </c>
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A93" s="53" t="s">
+      <c r="A93" s="51" t="s">
         <v>315</v>
       </c>
       <c r="B93" t="s">
@@ -8554,7 +8554,7 @@
       </c>
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A94" s="53" t="s">
+      <c r="A94" s="51" t="s">
         <v>314</v>
       </c>
       <c r="B94" t="s">
@@ -8568,7 +8568,7 @@
       </c>
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A95" s="53" t="s">
+      <c r="A95" s="51" t="s">
         <v>313</v>
       </c>
       <c r="B95" t="s">
@@ -8764,7 +8764,7 @@
       </c>
     </row>
     <row r="109" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A109" s="56" t="s">
+      <c r="A109" s="54" t="s">
         <v>300</v>
       </c>
       <c r="B109" t="s">
@@ -8778,7 +8778,7 @@
       </c>
     </row>
     <row r="110" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A110" s="57" t="s">
+      <c r="A110" s="55" t="s">
         <v>378</v>
       </c>
       <c r="B110" t="s">
@@ -8792,7 +8792,7 @@
       </c>
     </row>
     <row r="111" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A111" s="54" t="s">
+      <c r="A111" s="52" t="s">
         <v>379</v>
       </c>
       <c r="B111" t="s">
@@ -8806,7 +8806,7 @@
       </c>
     </row>
     <row r="112" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A112" s="55" t="s">
+      <c r="A112" s="53" t="s">
         <v>299</v>
       </c>
       <c r="B112" t="s">
@@ -8977,7 +8977,7 @@
       </c>
     </row>
     <row r="127" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A127" s="57" t="s">
+      <c r="A127" s="55" t="s">
         <v>460</v>
       </c>
       <c r="B127" t="s">
@@ -8988,7 +8988,7 @@
       </c>
     </row>
     <row r="128" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A128" s="52" t="s">
+      <c r="A128" s="50" t="s">
         <v>380</v>
       </c>
       <c r="B128" t="s">
@@ -9002,7 +9002,7 @@
       </c>
     </row>
     <row r="129" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A129" s="52" t="s">
+      <c r="A129" s="50" t="s">
         <v>202</v>
       </c>
       <c r="B129" t="s">
@@ -9016,7 +9016,7 @@
       </c>
     </row>
     <row r="130" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A130" s="52" t="s">
+      <c r="A130" s="50" t="s">
         <v>381</v>
       </c>
       <c r="B130" t="s">
@@ -9030,7 +9030,7 @@
       </c>
     </row>
     <row r="131" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A131" s="52" t="s">
+      <c r="A131" s="50" t="s">
         <v>120</v>
       </c>
       <c r="B131" t="s">
@@ -9044,7 +9044,7 @@
       </c>
     </row>
     <row r="132" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A132" s="52" t="s">
+      <c r="A132" s="50" t="s">
         <v>382</v>
       </c>
       <c r="B132" t="s">
@@ -9058,7 +9058,7 @@
       </c>
     </row>
     <row r="133" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A133" s="52" t="s">
+      <c r="A133" s="50" t="s">
         <v>195</v>
       </c>
       <c r="B133" t="s">
@@ -9072,7 +9072,7 @@
       </c>
     </row>
     <row r="134" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A134" s="52" t="s">
+      <c r="A134" s="50" t="s">
         <v>383</v>
       </c>
       <c r="B134" t="s">
@@ -9086,7 +9086,7 @@
       </c>
     </row>
     <row r="135" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A135" s="52" t="s">
+      <c r="A135" s="50" t="s">
         <v>384</v>
       </c>
       <c r="B135" t="s">
@@ -9100,7 +9100,7 @@
       </c>
     </row>
     <row r="136" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A136" s="52" t="s">
+      <c r="A136" s="50" t="s">
         <v>385</v>
       </c>
       <c r="B136" t="s">
@@ -9114,7 +9114,7 @@
       </c>
     </row>
     <row r="137" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A137" s="52" t="s">
+      <c r="A137" s="50" t="s">
         <v>386</v>
       </c>
       <c r="B137" t="s">
@@ -9128,7 +9128,7 @@
       </c>
     </row>
     <row r="138" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A138" s="52" t="s">
+      <c r="A138" s="50" t="s">
         <v>387</v>
       </c>
       <c r="B138" t="s">
@@ -9142,7 +9142,7 @@
       </c>
     </row>
     <row r="139" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A139" s="52" t="s">
+      <c r="A139" s="50" t="s">
         <v>388</v>
       </c>
       <c r="B139" t="s">
@@ -9156,7 +9156,7 @@
       </c>
     </row>
     <row r="140" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A140" s="52" t="s">
+      <c r="A140" s="50" t="s">
         <v>440</v>
       </c>
       <c r="B140" t="s">
@@ -9170,7 +9170,7 @@
       </c>
     </row>
     <row r="141" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A141" s="52" t="s">
+      <c r="A141" s="50" t="s">
         <v>441</v>
       </c>
       <c r="B141" t="s">
@@ -9184,7 +9184,7 @@
       </c>
     </row>
     <row r="142" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A142" s="52" t="s">
+      <c r="A142" s="50" t="s">
         <v>442</v>
       </c>
       <c r="B142" t="s">

--- a/RR_ISRU.xlsx
+++ b/RR_ISRU.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="31620" yWindow="0" windowWidth="17700" windowHeight="10485"/>
+    <workbookView xWindow="31620" yWindow="0" windowWidth="17700" windowHeight="10485" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Calc (Kg)" sheetId="6" r:id="rId1"/>
@@ -201,12 +201,37 @@
         </r>
       </text>
     </comment>
+    <comment ref="B105" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Jade:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Assumed living microbe.
+A chunk of DNA. Uses average of molar mass of the 4 nucleobases + Deoxyribose + custom Organophosphate PO4.(C3H5)3</t>
+        </r>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="603" uniqueCount="496">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="608" uniqueCount="500">
   <si>
     <t>Resource</t>
   </si>
@@ -1670,9 +1695,6 @@
     <t>Rutherfordium</t>
   </si>
   <si>
-    <t>R</t>
-  </si>
-  <si>
     <t>Gadolinite (R2 + (Fe,Be)3 + Si2O10)</t>
   </si>
   <si>
@@ -1728,6 +1750,21 @@
   </si>
   <si>
     <t>zCustom</t>
+  </si>
+  <si>
+    <t>c</t>
+  </si>
+  <si>
+    <t>Polymers + Metals + Chemicals</t>
+  </si>
+  <si>
+    <t>R + Si11</t>
+  </si>
+  <si>
+    <t>R (Yb)</t>
+  </si>
+  <si>
+    <t>Nucleotide custom</t>
   </si>
 </sst>
 </file>
@@ -3653,6 +3690,10 @@
       </c>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="D36">
+        <f>1/C34</f>
+        <v>1</v>
+      </c>
       <c r="G36" s="1"/>
       <c r="H36" s="1"/>
       <c r="I36" s="1"/>
@@ -3780,7 +3821,7 @@
         <v>488.46</v>
       </c>
       <c r="J4" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="K4" t="s">
         <v>0</v>
@@ -3873,7 +3914,7 @@
         <v>83.42</v>
       </c>
       <c r="J6" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="K6" t="s">
         <v>70</v>
@@ -3925,13 +3966,13 @@
         <v>12.12</v>
       </c>
       <c r="J7" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="K7" t="s">
         <v>427</v>
       </c>
       <c r="L7" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="M7">
         <v>2468.0700000000002</v>
@@ -3956,7 +3997,7 @@
         <v>67</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="C8" s="1">
         <v>0.6</v>
@@ -4364,7 +4405,7 @@
         <v>108</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="C25" s="1">
         <v>16</v>
@@ -4604,7 +4645,7 @@
         <v>25</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="C35" s="1">
         <v>160</v>
@@ -4629,7 +4670,7 @@
         <v>117</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="C36" s="1">
         <v>2</v>
@@ -4833,7 +4874,7 @@
         <v>22</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="C45" s="1">
         <v>0.01</v>
@@ -4933,7 +4974,7 @@
         <v>427</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="C49" s="1">
         <v>1.8585</v>
@@ -4958,7 +4999,7 @@
         <v>23</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="C50" s="1">
         <v>0.5</v>
@@ -5482,7 +5523,7 @@
         <v>114</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="C71" s="1">
         <v>15.8</v>
@@ -5507,7 +5548,7 @@
         <v>104</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="C72" s="1">
         <v>2</v>
@@ -5682,7 +5723,7 @@
         <v>24</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="C79" s="1">
         <v>0.8</v>
@@ -5755,7 +5796,7 @@
         <v>30</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="C82" s="1">
         <v>0.1</v>
@@ -5780,7 +5821,7 @@
         <v>122</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="C83" s="1">
         <v>0</v>
@@ -5855,7 +5896,7 @@
         <v>134</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="C86" s="1">
         <v>4</v>
@@ -6100,7 +6141,7 @@
         <v>26</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="C96" s="1">
         <v>140</v>
@@ -6125,13 +6166,14 @@
         <v>113</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>428</v>
+        <v>496</v>
       </c>
       <c r="C97" s="1">
         <v>7</v>
       </c>
       <c r="D97" s="5">
-        <v>104.15</v>
+        <f>D25+D77+D94</f>
+        <v>718.46500000000003</v>
       </c>
       <c r="E97" s="4">
         <f>0.00378*1000</f>
@@ -6139,10 +6181,11 @@
       </c>
       <c r="F97" s="12">
         <f t="shared" si="6"/>
-        <v>2.7552910052910055E-2</v>
+        <v>0.19007010582010583</v>
       </c>
       <c r="G97">
-        <v>198.8</v>
+        <f>G25+G77+G94</f>
+        <v>580.08999999999992</v>
       </c>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.25">
@@ -6150,7 +6193,7 @@
         <v>107</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>476</v>
+        <v>498</v>
       </c>
       <c r="C98" s="1">
         <v>250</v>
@@ -6213,7 +6256,7 @@
         <v>4</v>
       </c>
       <c r="F100" s="12">
-        <f t="shared" ref="F100:F104" si="7">D100/(E100 * 1000)</f>
+        <f t="shared" ref="F100:F105" si="7">D100/(E100 * 1000)</f>
         <v>2.7922499999999999E-2</v>
       </c>
       <c r="G100">
@@ -6256,7 +6299,7 @@
         <v>0.02</v>
       </c>
       <c r="D102" s="5">
-        <v>28.09</v>
+        <v>28.085000000000001</v>
       </c>
       <c r="E102" s="4">
         <f>0.002329*1000</f>
@@ -6264,7 +6307,7 @@
       </c>
       <c r="F102" s="12">
         <f t="shared" si="7"/>
-        <v>1.2060970373550882E-2</v>
+        <v>1.2058823529411768E-2</v>
       </c>
       <c r="G102">
         <v>8.15</v>
@@ -6274,16 +6317,26 @@
       <c r="A103" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="B103" s="1"/>
+      <c r="B103" s="1" t="s">
+        <v>497</v>
+      </c>
       <c r="C103" s="1">
         <v>32</v>
       </c>
-      <c r="D103" s="5"/>
+      <c r="D103" s="5">
+        <v>481.98500000000001</v>
+      </c>
       <c r="E103" s="4">
         <f>0.00378*1000</f>
         <v>3.78</v>
       </c>
-      <c r="F103" s="6"/>
+      <c r="F103" s="6">
+        <f t="shared" si="7"/>
+        <v>0.12750925925925927</v>
+      </c>
+      <c r="G103">
+        <v>95.9</v>
+      </c>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A104" s="1" t="s">
@@ -6314,23 +6367,30 @@
       <c r="A105" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B105" s="1"/>
+      <c r="B105" s="1" t="s">
+        <v>499</v>
+      </c>
       <c r="C105" s="1">
         <v>0.3</v>
       </c>
-      <c r="D105" s="5"/>
+      <c r="D105" s="5">
+        <v>483.19</v>
+      </c>
       <c r="E105" s="4">
         <f>0.0016*1000</f>
         <v>1.6</v>
       </c>
-      <c r="F105" s="6"/>
+      <c r="F105" s="6">
+        <f t="shared" si="7"/>
+        <v>0.30199375000000001</v>
+      </c>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A106" s="1" t="s">
         <v>118</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="C106" s="1">
         <v>2.5</v>
@@ -6457,7 +6517,7 @@
         <v>179</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="C111" s="1">
         <v>0</v>
@@ -6523,7 +6583,7 @@
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A114" s="1" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="B114" s="1"/>
       <c r="C114" s="1"/>
@@ -7060,83 +7120,93 @@
       </c>
     </row>
     <row r="4" spans="1:12" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="14"/>
+      <c r="A4" s="14" t="s">
+        <v>314</v>
+      </c>
       <c r="B4" s="17" t="str">
         <f t="shared" ref="B4:B15" si="0">IFERROR(VLOOKUP(A4,$A$25:$D$139,2,FALSE),"-")</f>
-        <v>-</v>
+        <v>Ytterbium</v>
       </c>
       <c r="C4" s="17" t="str">
         <f t="shared" ref="C4:C15" si="1">IF(L4="Y","Yes","-")</f>
         <v>-</v>
       </c>
-      <c r="D4" s="14"/>
+      <c r="D4" s="14">
+        <v>1</v>
+      </c>
       <c r="E4" s="15">
         <f t="shared" ref="E4:E15" si="2">D4*$D$18</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F4" s="15">
         <f t="shared" ref="F4:F15" si="3">IFERROR(E4*J4,0)</f>
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="G4" s="15">
         <f t="shared" ref="G4:G15" si="4">IFERROR(E4*K4,0)</f>
-        <v>0</v>
-      </c>
-      <c r="J4" s="17" t="str">
+        <v>173.05</v>
+      </c>
+      <c r="J4" s="17">
         <f t="shared" ref="J4:J15" si="5">IFERROR(VLOOKUP(A4,$A$25:$D$139,3,FALSE),"-")</f>
-        <v>-</v>
-      </c>
-      <c r="K4" s="17" t="str">
+        <v>6.25</v>
+      </c>
+      <c r="K4" s="17">
         <f t="shared" ref="K4:K15" si="6">IFERROR(VLOOKUP(A4,$A$25:$D$139,4,FALSE),"-")</f>
-        <v>-</v>
-      </c>
-      <c r="L4" s="17" t="str">
+        <v>173.05</v>
+      </c>
+      <c r="L4" s="17">
         <f t="shared" ref="L4:L15" si="7">IFERROR(VLOOKUP(A4,$A$25:$E$124,5,FALSE),"-")</f>
-        <v>-</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="17.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="14"/>
+      <c r="A5" s="14" t="s">
+        <v>154</v>
+      </c>
       <c r="B5" s="17" t="str">
         <f t="shared" si="0"/>
-        <v>-</v>
+        <v>Silicon</v>
       </c>
       <c r="C5" s="17" t="str">
         <f t="shared" si="1"/>
         <v>-</v>
       </c>
-      <c r="D5" s="14"/>
+      <c r="D5" s="14">
+        <v>11</v>
+      </c>
       <c r="E5" s="15">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="F5" s="15">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>89.65</v>
       </c>
       <c r="G5" s="15">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>308.935</v>
       </c>
       <c r="H5" s="56"/>
-      <c r="J5" s="17" t="str">
+      <c r="J5" s="17">
         <f t="shared" si="5"/>
-        <v>-</v>
-      </c>
-      <c r="K5" s="17" t="str">
+        <v>8.15</v>
+      </c>
+      <c r="K5" s="17">
         <f t="shared" si="6"/>
-        <v>-</v>
-      </c>
-      <c r="L5" s="17" t="str">
+        <v>28.085000000000001</v>
+      </c>
+      <c r="L5" s="17">
         <f t="shared" si="7"/>
-        <v>-</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:12" ht="17.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="14"/>
+      <c r="A6" s="14" t="s">
+        <v>495</v>
+      </c>
       <c r="B6" s="17" t="str">
         <f t="shared" si="0"/>
-        <v>-</v>
+        <v>Carbon</v>
       </c>
       <c r="C6" s="17" t="str">
         <f t="shared" si="1"/>
@@ -7155,17 +7225,17 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="J6" s="17" t="str">
+      <c r="J6" s="17">
         <f t="shared" si="5"/>
-        <v>-</v>
-      </c>
-      <c r="K6" s="17" t="str">
+        <v>11.26</v>
+      </c>
+      <c r="K6" s="17">
         <f t="shared" si="6"/>
-        <v>-</v>
-      </c>
-      <c r="L6" s="17" t="str">
+        <v>12.010999999999999</v>
+      </c>
+      <c r="L6" s="17">
         <f t="shared" si="7"/>
-        <v>-</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:12" ht="17.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -7507,17 +7577,17 @@
       </c>
       <c r="F18" s="39">
         <f>SUM(F4:F15)</f>
-        <v>0</v>
+        <v>95.9</v>
       </c>
       <c r="G18" s="15">
         <f>SUM(G4:G15)</f>
-        <v>0</v>
+        <v>481.98500000000001</v>
       </c>
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.25">
       <c r="F19" s="43">
         <f>F18/20</f>
-        <v>0</v>
+        <v>4.7949999999999999</v>
       </c>
       <c r="N19" s="49"/>
       <c r="P19" s="18"/>

--- a/RR_ISRU.xlsx
+++ b/RR_ISRU.xlsx
@@ -231,18 +231,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="608" uniqueCount="500">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="613" uniqueCount="500">
   <si>
     <t>Resource</t>
   </si>
   <si>
     <t>Real world chemical</t>
-  </si>
-  <si>
-    <t>molar mass</t>
-  </si>
-  <si>
-    <t>unit mass (from configs)</t>
   </si>
   <si>
     <t>LiquidFuel</t>
@@ -1765,6 +1759,12 @@
   </si>
   <si>
     <t>Nucleotide custom</t>
+  </si>
+  <si>
+    <t>molar mass (g/mol)</t>
+  </si>
+  <si>
+    <t>density (kg/L)</t>
   </si>
 </sst>
 </file>
@@ -2066,7 +2066,7 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="59">
+  <cellXfs count="56">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2077,12 +2077,6 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2091,16 +2085,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="167" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="1"/>
@@ -2121,12 +2106,6 @@
     <xf numFmtId="171" fontId="4" fillId="4" borderId="1" xfId="2" applyNumberFormat="1" applyAlignment="1"/>
     <xf numFmtId="170" fontId="8" fillId="4" borderId="4" xfId="6" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="167" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -2163,6 +2142,18 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="3" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="10">
@@ -2496,523 +2487,523 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="20.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="57" t="s">
-        <v>79</v>
-      </c>
-      <c r="B1" s="57"/>
-      <c r="C1" s="57"/>
-      <c r="D1" s="57"/>
-      <c r="E1" s="57"/>
-      <c r="F1" s="57"/>
-      <c r="G1" s="57"/>
+      <c r="A1" s="50" t="s">
+        <v>77</v>
+      </c>
+      <c r="B1" s="50"/>
+      <c r="C1" s="50"/>
+      <c r="D1" s="50"/>
+      <c r="E1" s="50"/>
+      <c r="F1" s="50"/>
+      <c r="G1" s="50"/>
     </row>
     <row r="2" spans="1:12" ht="16.5" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="23" t="s">
-        <v>82</v>
+      <c r="A2" s="18" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A3" s="23" t="s">
-        <v>175</v>
+      <c r="A3" s="18" t="s">
+        <v>173</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A4" s="23" t="s">
-        <v>176</v>
+      <c r="A4" s="18" t="s">
+        <v>174</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="18" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="36" t="s">
-        <v>58</v>
-      </c>
-      <c r="B5" s="36"/>
-      <c r="C5" s="36"/>
-      <c r="D5" s="36"/>
-      <c r="E5" s="36"/>
-      <c r="F5" s="36"/>
-      <c r="G5" s="36"/>
-      <c r="H5" s="37"/>
-      <c r="I5" s="37"/>
-      <c r="J5" s="37"/>
-      <c r="K5" s="37"/>
-      <c r="L5" s="37"/>
+      <c r="A5" s="29" t="s">
+        <v>56</v>
+      </c>
+      <c r="B5" s="29"/>
+      <c r="C5" s="29"/>
+      <c r="D5" s="29"/>
+      <c r="E5" s="29"/>
+      <c r="F5" s="29"/>
+      <c r="G5" s="29"/>
+      <c r="H5" s="30"/>
+      <c r="I5" s="30"/>
+      <c r="J5" s="30"/>
+      <c r="K5" s="30"/>
+      <c r="L5" s="30"/>
     </row>
     <row r="6" spans="1:12" ht="16.5" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="21" t="s">
-        <v>77</v>
-      </c>
-      <c r="B6" s="14">
+      <c r="A6" s="16" t="s">
+        <v>75</v>
+      </c>
+      <c r="B6" s="9">
         <v>0</v>
       </c>
-      <c r="C6" s="14">
+      <c r="C6" s="9">
         <v>0</v>
       </c>
-      <c r="D6" s="14">
+      <c r="D6" s="9">
         <v>0</v>
       </c>
-      <c r="E6" s="14">
+      <c r="E6" s="9">
         <v>0</v>
       </c>
-      <c r="F6" s="14">
+      <c r="F6" s="9">
         <v>0</v>
       </c>
-      <c r="G6" s="14">
+      <c r="G6" s="9">
         <v>0</v>
       </c>
       <c r="I6" t="s">
-        <v>210</v>
-      </c>
-      <c r="J6" s="14">
+        <v>208</v>
+      </c>
+      <c r="J6" s="9">
         <v>1</v>
       </c>
-      <c r="K6" s="23" t="s">
-        <v>211</v>
-      </c>
-      <c r="L6" s="15">
+      <c r="K6" s="18" t="s">
+        <v>209</v>
+      </c>
+      <c r="L6" s="10">
         <f>J7/J6</f>
         <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A7" s="7" t="s">
-        <v>83</v>
-      </c>
-      <c r="B7" s="22"/>
-      <c r="C7" s="22"/>
-      <c r="D7" s="22"/>
-      <c r="E7" s="22"/>
-      <c r="F7" s="22"/>
-      <c r="G7" s="22"/>
+      <c r="A7" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="B7" s="17"/>
+      <c r="C7" s="17"/>
+      <c r="D7" s="17"/>
+      <c r="E7" s="17"/>
+      <c r="F7" s="17"/>
+      <c r="G7" s="17"/>
       <c r="I7" t="s">
-        <v>212</v>
-      </c>
-      <c r="J7" s="14">
+        <v>210</v>
+      </c>
+      <c r="J7" s="9">
         <v>1</v>
       </c>
-      <c r="K7" s="23" t="s">
-        <v>219</v>
-      </c>
-      <c r="L7" s="15">
+      <c r="K7" s="18" t="s">
+        <v>217</v>
+      </c>
+      <c r="L7" s="10">
         <f>IF(J8&gt;0,L6-(J8*3600),0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:12" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="7" t="s">
-        <v>80</v>
-      </c>
-      <c r="B8" s="17" t="str">
+      <c r="A8" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="B8" s="12" t="str">
         <f>IFERROR(VLOOKUP(B7,Database!$A$3:$E$152,5,FALSE),"-")</f>
         <v>-</v>
       </c>
-      <c r="C8" s="17" t="str">
+      <c r="C8" s="12" t="str">
         <f>IFERROR(VLOOKUP(C7,Database!$A$3:$E$152,5,FALSE),"-")</f>
         <v>-</v>
       </c>
-      <c r="D8" s="17" t="str">
+      <c r="D8" s="12" t="str">
         <f>IFERROR(VLOOKUP(D7,Database!$A$3:$E$152,5,FALSE),"-")</f>
         <v>-</v>
       </c>
-      <c r="E8" s="17" t="str">
+      <c r="E8" s="12" t="str">
         <f>IFERROR(VLOOKUP(E7,Database!$A$3:$E$152,5,FALSE),"-")</f>
         <v>-</v>
       </c>
-      <c r="F8" s="17" t="str">
+      <c r="F8" s="12" t="str">
         <f>IFERROR(VLOOKUP(F7,Database!$A$3:$E$152,5,FALSE),"-")</f>
         <v>-</v>
       </c>
-      <c r="G8" s="17" t="str">
+      <c r="G8" s="12" t="str">
         <f>IFERROR(VLOOKUP(G7,Database!$A$3:$E$152,5,FALSE),"-")</f>
         <v>-</v>
       </c>
-      <c r="I8" s="34" t="s">
-        <v>213</v>
-      </c>
-      <c r="J8" s="35">
+      <c r="I8" s="27" t="s">
+        <v>211</v>
+      </c>
+      <c r="J8" s="28">
         <f>ROUNDDOWN(IF(L6&gt;3600,L6/3600,0),0)</f>
         <v>0</v>
       </c>
-      <c r="K8" s="23" t="s">
-        <v>207</v>
-      </c>
-      <c r="L8" s="15">
+      <c r="K8" s="18" t="s">
+        <v>205</v>
+      </c>
+      <c r="L8" s="10">
         <f>ROUNDDOWN(IF(L7&gt;0,L7/60,L6/60),0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:12" ht="17.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="42" t="s">
-        <v>412</v>
-      </c>
-      <c r="B9" s="17" t="str">
+      <c r="A9" s="35" t="s">
+        <v>410</v>
+      </c>
+      <c r="B9" s="12" t="str">
         <f>IFERROR(VLOOKUP(B7,Database!$A$3:$E$152,4,FALSE),"-")</f>
         <v>-</v>
       </c>
-      <c r="C9" s="17" t="str">
+      <c r="C9" s="12" t="str">
         <f>IFERROR(VLOOKUP(C7,Database!$A$3:$E$152,4,FALSE),"-")</f>
         <v>-</v>
       </c>
-      <c r="D9" s="17" t="str">
+      <c r="D9" s="12" t="str">
         <f>IFERROR(VLOOKUP(D7,Database!$A$3:$E$152,4,FALSE),"-")</f>
         <v>-</v>
       </c>
-      <c r="E9" s="17" t="str">
+      <c r="E9" s="12" t="str">
         <f>IFERROR(VLOOKUP(E7,Database!$A$3:$E$152,4,FALSE),"-")</f>
         <v>-</v>
       </c>
-      <c r="F9" s="17" t="str">
+      <c r="F9" s="12" t="str">
         <f>IFERROR(VLOOKUP(F7,Database!$A$3:$E$152,4,FALSE),"-")</f>
         <v>-</v>
       </c>
-      <c r="G9" s="17" t="str">
+      <c r="G9" s="12" t="str">
         <f>IFERROR(VLOOKUP(G7,Database!$A$3:$E$152,4,FALSE),"-")</f>
         <v>-</v>
       </c>
-      <c r="J9" s="35">
+      <c r="J9" s="28">
         <f>IF(L8&lt;60,L8,0)</f>
         <v>0</v>
       </c>
-      <c r="K9" s="23" t="s">
-        <v>208</v>
-      </c>
-      <c r="L9" s="15">
+      <c r="K9" s="18" t="s">
+        <v>206</v>
+      </c>
+      <c r="L9" s="10">
         <f>IF(L6&gt;0,L6-((J8*3600)+(L8*60)),0)</f>
         <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:12" ht="16.5" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="B10" s="20" t="str">
+      <c r="A10" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="B10" s="15" t="str">
         <f t="shared" ref="B10:G10" si="0">IFERROR(B6*B8,"-")</f>
         <v>-</v>
       </c>
-      <c r="C10" s="20" t="str">
+      <c r="C10" s="15" t="str">
         <f t="shared" si="0"/>
         <v>-</v>
       </c>
-      <c r="D10" s="20" t="str">
+      <c r="D10" s="15" t="str">
         <f t="shared" si="0"/>
         <v>-</v>
       </c>
-      <c r="E10" s="20" t="str">
+      <c r="E10" s="15" t="str">
         <f t="shared" si="0"/>
         <v>-</v>
       </c>
-      <c r="F10" s="20" t="str">
+      <c r="F10" s="15" t="str">
         <f t="shared" si="0"/>
         <v>-</v>
       </c>
-      <c r="G10" s="20" t="str">
+      <c r="G10" s="15" t="str">
         <f t="shared" si="0"/>
         <v>-</v>
       </c>
-      <c r="J10" s="35">
+      <c r="J10" s="28">
         <f>IF(L9&gt;0,L9,0)</f>
         <v>1</v>
       </c>
-      <c r="K10" s="23" t="s">
-        <v>209</v>
+      <c r="K10" s="18" t="s">
+        <v>207</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A11" s="42" t="s">
-        <v>413</v>
-      </c>
-      <c r="B11" s="20" t="str">
+      <c r="A11" s="35" t="s">
+        <v>411</v>
+      </c>
+      <c r="B11" s="15" t="str">
         <f t="shared" ref="B11:C11" si="1">IFERROR((B6*(B8*1000))/B9,"-")</f>
         <v>-</v>
       </c>
-      <c r="C11" s="20" t="str">
+      <c r="C11" s="15" t="str">
         <f t="shared" si="1"/>
         <v>-</v>
       </c>
-      <c r="D11" s="20" t="str">
+      <c r="D11" s="15" t="str">
         <f>IFERROR((D6*(D8*1000))/D9,"-")</f>
         <v>-</v>
       </c>
-      <c r="E11" s="20" t="str">
+      <c r="E11" s="15" t="str">
         <f t="shared" ref="E11:G11" si="2">IFERROR((E6*(E8*1000))/E9,"-")</f>
         <v>-</v>
       </c>
-      <c r="F11" s="20" t="str">
+      <c r="F11" s="15" t="str">
         <f t="shared" si="2"/>
         <v>-</v>
       </c>
-      <c r="G11" s="20" t="str">
+      <c r="G11" s="15" t="str">
         <f t="shared" si="2"/>
         <v>-</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A12" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="B12" s="28">
+      <c r="A12" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="B12" s="23">
         <f>SUM(B10:G10)</f>
         <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:12" ht="18" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="36" t="s">
-        <v>59</v>
-      </c>
-      <c r="B15" s="36"/>
-      <c r="C15" s="36"/>
-      <c r="D15" s="36"/>
-      <c r="E15" s="36"/>
-      <c r="F15" s="36"/>
-      <c r="G15" s="36"/>
-      <c r="H15" s="37"/>
-      <c r="I15" s="37"/>
-      <c r="J15" s="37"/>
-      <c r="K15" s="37"/>
-      <c r="L15" s="37"/>
+      <c r="A15" s="29" t="s">
+        <v>57</v>
+      </c>
+      <c r="B15" s="29"/>
+      <c r="C15" s="29"/>
+      <c r="D15" s="29"/>
+      <c r="E15" s="29"/>
+      <c r="F15" s="29"/>
+      <c r="G15" s="29"/>
+      <c r="H15" s="30"/>
+      <c r="I15" s="30"/>
+      <c r="J15" s="30"/>
+      <c r="K15" s="30"/>
+      <c r="L15" s="30"/>
     </row>
     <row r="16" spans="1:12" ht="16.5" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="21" t="s">
-        <v>77</v>
-      </c>
-      <c r="B16" s="14">
+      <c r="A16" s="16" t="s">
+        <v>75</v>
+      </c>
+      <c r="B16" s="9">
         <v>0</v>
       </c>
-      <c r="C16" s="14">
+      <c r="C16" s="9">
         <v>0</v>
       </c>
-      <c r="D16" s="14">
+      <c r="D16" s="9">
         <v>0</v>
       </c>
-      <c r="E16" s="14">
+      <c r="E16" s="9">
         <v>0</v>
       </c>
-      <c r="F16" s="14">
+      <c r="F16" s="9">
         <v>0</v>
       </c>
-      <c r="G16" s="14">
+      <c r="G16" s="9">
         <v>0</v>
       </c>
       <c r="I16" t="s">
-        <v>210</v>
-      </c>
-      <c r="J16" s="14">
+        <v>208</v>
+      </c>
+      <c r="J16" s="9">
         <v>1</v>
       </c>
-      <c r="K16" s="23" t="s">
-        <v>211</v>
-      </c>
-      <c r="L16" s="15">
+      <c r="K16" s="18" t="s">
+        <v>209</v>
+      </c>
+      <c r="L16" s="10">
         <f>J17/J16</f>
         <v>1</v>
       </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A17" s="7" t="s">
-        <v>83</v>
-      </c>
-      <c r="B17" s="22"/>
-      <c r="C17" s="22"/>
-      <c r="D17" s="22"/>
-      <c r="E17" s="22"/>
-      <c r="F17" s="22"/>
-      <c r="G17" s="22"/>
+      <c r="A17" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="B17" s="17"/>
+      <c r="C17" s="17"/>
+      <c r="D17" s="17"/>
+      <c r="E17" s="17"/>
+      <c r="F17" s="17"/>
+      <c r="G17" s="17"/>
       <c r="I17" t="s">
-        <v>212</v>
-      </c>
-      <c r="J17" s="14">
+        <v>210</v>
+      </c>
+      <c r="J17" s="9">
         <v>1</v>
       </c>
-      <c r="K17" s="23" t="s">
-        <v>219</v>
-      </c>
-      <c r="L17" s="15">
+      <c r="K17" s="18" t="s">
+        <v>217</v>
+      </c>
+      <c r="L17" s="10">
         <f>IF(J18&gt;0,L16-(J18*3600),0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:12" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="7" t="s">
-        <v>80</v>
-      </c>
-      <c r="B18" s="17" t="str">
+      <c r="A18" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="B18" s="12" t="str">
         <f>IFERROR(VLOOKUP(B17,Database!$A$3:$E$152,5,FALSE),"-")</f>
         <v>-</v>
       </c>
-      <c r="C18" s="17" t="str">
+      <c r="C18" s="12" t="str">
         <f>IFERROR(VLOOKUP(C17,Database!$A$3:$E$152,5,FALSE),"-")</f>
         <v>-</v>
       </c>
-      <c r="D18" s="17" t="str">
+      <c r="D18" s="12" t="str">
         <f>IFERROR(VLOOKUP(D17,Database!$A$3:$E$152,5,FALSE),"-")</f>
         <v>-</v>
       </c>
-      <c r="E18" s="17" t="str">
+      <c r="E18" s="12" t="str">
         <f>IFERROR(VLOOKUP(E17,Database!$A$3:$E$152,5,FALSE),"-")</f>
         <v>-</v>
       </c>
-      <c r="F18" s="17" t="str">
+      <c r="F18" s="12" t="str">
         <f>IFERROR(VLOOKUP(F17,Database!$A$3:$E$152,5,FALSE),"-")</f>
         <v>-</v>
       </c>
-      <c r="G18" s="17" t="str">
+      <c r="G18" s="12" t="str">
         <f>IFERROR(VLOOKUP(G17,Database!$A$3:$E$152,5,FALSE),"-")</f>
         <v>-</v>
       </c>
-      <c r="I18" s="34" t="s">
-        <v>213</v>
-      </c>
-      <c r="J18" s="35">
+      <c r="I18" s="27" t="s">
+        <v>211</v>
+      </c>
+      <c r="J18" s="28">
         <f>ROUNDDOWN(IF(L16&gt;3600,L16/3600,0),0)</f>
         <v>0</v>
       </c>
-      <c r="K18" s="23" t="s">
-        <v>207</v>
-      </c>
-      <c r="L18" s="15">
+      <c r="K18" s="18" t="s">
+        <v>205</v>
+      </c>
+      <c r="L18" s="10">
         <f>ROUNDDOWN(IF(L17&gt;0,L17/60,L16/60),0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:12" ht="17.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="42" t="s">
-        <v>412</v>
-      </c>
-      <c r="B19" s="17" t="str">
+      <c r="A19" s="35" t="s">
+        <v>410</v>
+      </c>
+      <c r="B19" s="12" t="str">
         <f>IFERROR(VLOOKUP(B17,Database!$A$3:$E$152,4,FALSE),"-")</f>
         <v>-</v>
       </c>
-      <c r="C19" s="17" t="str">
+      <c r="C19" s="12" t="str">
         <f>IFERROR(VLOOKUP(C17,Database!$A$3:$E$152,4,FALSE),"-")</f>
         <v>-</v>
       </c>
-      <c r="D19" s="17" t="str">
+      <c r="D19" s="12" t="str">
         <f>IFERROR(VLOOKUP(D17,Database!$A$3:$E$152,4,FALSE),"-")</f>
         <v>-</v>
       </c>
-      <c r="E19" s="17" t="str">
+      <c r="E19" s="12" t="str">
         <f>IFERROR(VLOOKUP(E17,Database!$A$3:$E$152,4,FALSE),"-")</f>
         <v>-</v>
       </c>
-      <c r="F19" s="17" t="str">
+      <c r="F19" s="12" t="str">
         <f>IFERROR(VLOOKUP(F17,Database!$A$3:$E$152,4,FALSE),"-")</f>
         <v>-</v>
       </c>
-      <c r="G19" s="17" t="str">
+      <c r="G19" s="12" t="str">
         <f>IFERROR(VLOOKUP(G17,Database!$A$3:$E$152,4,FALSE),"-")</f>
         <v>-</v>
       </c>
-      <c r="J19" s="35">
+      <c r="J19" s="28">
         <f>IF(L18&lt;60,L18,0)</f>
         <v>0</v>
       </c>
-      <c r="K19" s="23" t="s">
-        <v>208</v>
-      </c>
-      <c r="L19" s="15">
+      <c r="K19" s="18" t="s">
+        <v>206</v>
+      </c>
+      <c r="L19" s="10">
         <f>IF(L16&gt;0,L16-((J18*3600)+(L18*60)),0)</f>
         <v>1</v>
       </c>
     </row>
     <row r="20" spans="1:12" ht="16.5" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="B20" s="26" t="str">
+      <c r="A20" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="B20" s="21" t="str">
         <f t="shared" ref="B20:G20" si="3">IFERROR(B16*B18,"-")</f>
         <v>-</v>
       </c>
-      <c r="C20" s="20" t="str">
+      <c r="C20" s="15" t="str">
         <f t="shared" si="3"/>
         <v>-</v>
       </c>
-      <c r="D20" s="26" t="str">
+      <c r="D20" s="21" t="str">
         <f t="shared" si="3"/>
         <v>-</v>
       </c>
-      <c r="E20" s="20" t="str">
+      <c r="E20" s="15" t="str">
         <f t="shared" si="3"/>
         <v>-</v>
       </c>
-      <c r="F20" s="20" t="str">
+      <c r="F20" s="15" t="str">
         <f t="shared" si="3"/>
         <v>-</v>
       </c>
-      <c r="G20" s="20" t="str">
+      <c r="G20" s="15" t="str">
         <f t="shared" si="3"/>
         <v>-</v>
       </c>
-      <c r="J20" s="35">
+      <c r="J20" s="28">
         <f>IF(L19&gt;0,L19,0)</f>
         <v>1</v>
       </c>
-      <c r="K20" s="23" t="s">
-        <v>209</v>
+      <c r="K20" s="18" t="s">
+        <v>207</v>
       </c>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A21" s="42" t="s">
-        <v>413</v>
-      </c>
-      <c r="B21" s="20" t="str">
+      <c r="A21" s="35" t="s">
+        <v>411</v>
+      </c>
+      <c r="B21" s="15" t="str">
         <f t="shared" ref="B21:G21" si="4">IFERROR((B16*(B18*1000))/B19,"-")</f>
         <v>-</v>
       </c>
-      <c r="C21" s="20" t="str">
+      <c r="C21" s="15" t="str">
         <f t="shared" si="4"/>
         <v>-</v>
       </c>
-      <c r="D21" s="20" t="str">
+      <c r="D21" s="15" t="str">
         <f t="shared" si="4"/>
         <v>-</v>
       </c>
-      <c r="E21" s="20" t="str">
+      <c r="E21" s="15" t="str">
         <f t="shared" si="4"/>
         <v>-</v>
       </c>
-      <c r="F21" s="20" t="str">
+      <c r="F21" s="15" t="str">
         <f t="shared" si="4"/>
         <v>-</v>
       </c>
-      <c r="G21" s="20" t="str">
+      <c r="G21" s="15" t="str">
         <f t="shared" si="4"/>
         <v>-</v>
       </c>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A22" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="B22" s="28">
+      <c r="A22" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="B22" s="23">
         <f>SUM(B20:G20)</f>
         <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:12" ht="18" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="58" t="s">
-        <v>62</v>
-      </c>
-      <c r="B25" s="58"/>
-      <c r="C25" s="58"/>
-      <c r="D25" s="58"/>
-      <c r="E25" s="58"/>
-      <c r="F25" s="58"/>
-      <c r="G25" s="58"/>
+      <c r="A25" s="51" t="s">
+        <v>60</v>
+      </c>
+      <c r="B25" s="51"/>
+      <c r="C25" s="51"/>
+      <c r="D25" s="51"/>
+      <c r="E25" s="51"/>
+      <c r="F25" s="51"/>
+      <c r="G25" s="51"/>
     </row>
     <row r="26" spans="1:12" ht="16.5" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="B26" s="16" t="str">
+      <c r="A26" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="B26" s="11" t="str">
         <f>IF($B$12&gt;$B$22,"Input excesive",IF($B$12&lt;$B$22,"Output excessive","Equal"))</f>
         <v>Equal</v>
       </c>
-      <c r="C26" s="27">
+      <c r="C26" s="22">
         <f>IF($B$12&gt;$B$22,B12/B22,IF($B$12&lt;$B$22,B22/B12,1))</f>
         <v>1</v>
       </c>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A27" s="7"/>
+      <c r="A27" s="5"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -3050,659 +3041,673 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="20.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="57" t="s">
+      <c r="A1" s="50" t="s">
+        <v>76</v>
+      </c>
+      <c r="B1" s="50"/>
+      <c r="C1" s="50"/>
+      <c r="D1" s="50"/>
+      <c r="E1" s="50"/>
+      <c r="F1" s="50"/>
+      <c r="G1" s="50"/>
+      <c r="H1" s="40"/>
+      <c r="I1" s="40"/>
+    </row>
+    <row r="2" spans="1:12" ht="16.5" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="18" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A3" s="18" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A4" s="18" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" ht="18" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="29" t="s">
+        <v>56</v>
+      </c>
+      <c r="B5" s="29"/>
+      <c r="C5" s="29"/>
+      <c r="D5" s="29"/>
+      <c r="E5" s="29"/>
+      <c r="F5" s="29"/>
+      <c r="G5" s="29"/>
+      <c r="H5" s="29"/>
+      <c r="I5" s="29"/>
+      <c r="L5" s="1"/>
+    </row>
+    <row r="6" spans="1:12" ht="16.5" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="B6" s="9">
+        <v>4</v>
+      </c>
+      <c r="C6" s="9">
+        <v>0</v>
+      </c>
+      <c r="D6" s="9">
+        <v>0</v>
+      </c>
+      <c r="E6" s="9">
+        <v>0</v>
+      </c>
+      <c r="F6" s="9">
+        <v>0</v>
+      </c>
+      <c r="G6" s="9">
+        <v>0</v>
+      </c>
+      <c r="H6" s="9">
+        <v>0</v>
+      </c>
+      <c r="I6" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A7" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="B7" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="C7" s="17"/>
+      <c r="D7" s="17"/>
+      <c r="E7" s="17"/>
+      <c r="F7" s="17"/>
+      <c r="G7" s="17"/>
+      <c r="H7" s="17"/>
+      <c r="I7" s="17"/>
+    </row>
+    <row r="8" spans="1:12" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="B8" s="12">
+        <f>IFERROR(VLOOKUP(B7,Database!$A$3:$E$113,4,FALSE),"-")</f>
+        <v>589.29629999999997</v>
+      </c>
+      <c r="C8" s="12" t="str">
+        <f>IFERROR(VLOOKUP(C7,Database!$A$3:$E$113,4,FALSE),"-")</f>
+        <v>-</v>
+      </c>
+      <c r="D8" s="12" t="str">
+        <f>IFERROR(VLOOKUP(D7,Database!$A$3:$E$113,4,FALSE),"-")</f>
+        <v>-</v>
+      </c>
+      <c r="E8" s="12" t="str">
+        <f>IFERROR(VLOOKUP(E7,Database!$A$3:$E$113,4,FALSE),"-")</f>
+        <v>-</v>
+      </c>
+      <c r="F8" s="12" t="str">
+        <f>IFERROR(VLOOKUP(F7,Database!$A$3:$E$113,4,FALSE),"-")</f>
+        <v>-</v>
+      </c>
+      <c r="G8" s="12" t="str">
+        <f>IFERROR(VLOOKUP(G7,Database!$A$3:$E$113,4,FALSE),"-")</f>
+        <v>-</v>
+      </c>
+      <c r="H8" s="12" t="str">
+        <f>IFERROR(VLOOKUP(H7,Database!$A$3:$E$113,4,FALSE),"-")</f>
+        <v>-</v>
+      </c>
+      <c r="I8" s="12" t="str">
+        <f>IFERROR(VLOOKUP(I7,Database!$A$3:$E$113,4,FALSE),"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" ht="17.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="B1" s="57"/>
-      <c r="C1" s="57"/>
-      <c r="D1" s="57"/>
-      <c r="E1" s="57"/>
-      <c r="F1" s="57"/>
-      <c r="G1" s="57"/>
-      <c r="H1" s="47"/>
-      <c r="I1" s="47"/>
-    </row>
-    <row r="2" spans="1:12" ht="16.5" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="23" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A3" s="23" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A4" s="23" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" ht="18" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="36" t="s">
-        <v>58</v>
-      </c>
-      <c r="B5" s="36"/>
-      <c r="C5" s="36"/>
-      <c r="D5" s="36"/>
-      <c r="E5" s="36"/>
-      <c r="F5" s="36"/>
-      <c r="G5" s="36"/>
-      <c r="H5" s="36"/>
-      <c r="I5" s="36"/>
-      <c r="L5" s="1"/>
-    </row>
-    <row r="6" spans="1:12" ht="16.5" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="7" t="s">
+      <c r="B9" s="12">
+        <f>IFERROR(VLOOKUP(B7,Database!$A$3:$E$113,5,FALSE),"-")</f>
+        <v>7.8</v>
+      </c>
+      <c r="C9" s="12" t="str">
+        <f>IFERROR(VLOOKUP(C7,Database!$A$3:$E$113,5,FALSE),"-")</f>
+        <v>-</v>
+      </c>
+      <c r="D9" s="12" t="str">
+        <f>IFERROR(VLOOKUP(D7,Database!$A$3:$E$113,5,FALSE),"-")</f>
+        <v>-</v>
+      </c>
+      <c r="E9" s="12" t="str">
+        <f>IFERROR(VLOOKUP(E7,Database!$A$3:$E$113,5,FALSE),"-")</f>
+        <v>-</v>
+      </c>
+      <c r="F9" s="12" t="str">
+        <f>IFERROR(VLOOKUP(F7,Database!$A$3:$E$113,5,FALSE),"-")</f>
+        <v>-</v>
+      </c>
+      <c r="G9" s="12" t="str">
+        <f>IFERROR(VLOOKUP(G7,Database!$A$3:$E$113,5,FALSE),"-")</f>
+        <v>-</v>
+      </c>
+      <c r="H9" s="12" t="str">
+        <f>IFERROR(VLOOKUP(H7,Database!$A$3:$E$113,5,FALSE),"-")</f>
+        <v>-</v>
+      </c>
+      <c r="I9" s="12" t="str">
+        <f>IFERROR(VLOOKUP(I7,Database!$A$3:$E$113,5,FALSE),"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" ht="16.5" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="B6" s="14">
-        <v>0</v>
-      </c>
-      <c r="C6" s="14">
-        <v>0</v>
-      </c>
-      <c r="D6" s="14">
-        <v>0</v>
-      </c>
-      <c r="E6" s="14">
-        <v>0</v>
-      </c>
-      <c r="F6" s="14">
-        <v>0</v>
-      </c>
-      <c r="G6" s="14">
-        <v>0</v>
-      </c>
-      <c r="H6" s="14">
-        <v>0</v>
-      </c>
-      <c r="I6" s="14">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A7" s="7" t="s">
-        <v>83</v>
-      </c>
-      <c r="B7" s="22"/>
-      <c r="C7" s="22"/>
-      <c r="D7" s="22"/>
-      <c r="E7" s="22"/>
-      <c r="F7" s="22"/>
-      <c r="G7" s="22"/>
-      <c r="H7" s="22"/>
-      <c r="I7" s="22"/>
-    </row>
-    <row r="8" spans="1:12" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="7" t="s">
+      <c r="B10" s="32">
+        <f>IFERROR(B6*B8,0)</f>
+        <v>2357.1851999999999</v>
+      </c>
+      <c r="C10" s="32" t="str">
+        <f>IFERROR(C6*C8,"-")</f>
+        <v>-</v>
+      </c>
+      <c r="D10" s="10" t="str">
+        <f>IFERROR(D6*D8,"-")</f>
+        <v>-</v>
+      </c>
+      <c r="E10" s="10" t="str">
+        <f>IFERROR(E6*E8,"-")</f>
+        <v>-</v>
+      </c>
+      <c r="F10" s="10" t="str">
+        <f>IFERROR(F6*F8,"-")</f>
+        <v>-</v>
+      </c>
+      <c r="G10" s="10" t="str">
+        <f>IFERROR(G6*G8,"-")</f>
+        <v>-</v>
+      </c>
+      <c r="H10" s="10" t="str">
+        <f t="shared" ref="H10:I10" si="0">IFERROR(H6*H8,"-")</f>
+        <v>-</v>
+      </c>
+      <c r="I10" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A11" s="16" t="s">
         <v>75</v>
       </c>
-      <c r="B8" s="17" t="str">
-        <f>IFERROR(VLOOKUP(B7,Database!$A$3:$E$113,4,FALSE),"-")</f>
-        <v>-</v>
-      </c>
-      <c r="C8" s="17" t="str">
-        <f>IFERROR(VLOOKUP(C7,Database!$A$3:$E$113,4,FALSE),"-")</f>
-        <v>-</v>
-      </c>
-      <c r="D8" s="17" t="str">
-        <f>IFERROR(VLOOKUP(D7,Database!$A$3:$E$113,4,FALSE),"-")</f>
-        <v>-</v>
-      </c>
-      <c r="E8" s="17" t="str">
-        <f>IFERROR(VLOOKUP(E7,Database!$A$3:$E$113,4,FALSE),"-")</f>
-        <v>-</v>
-      </c>
-      <c r="F8" s="17" t="str">
-        <f>IFERROR(VLOOKUP(F7,Database!$A$3:$E$113,4,FALSE),"-")</f>
-        <v>-</v>
-      </c>
-      <c r="G8" s="17" t="str">
-        <f>IFERROR(VLOOKUP(G7,Database!$A$3:$E$113,4,FALSE),"-")</f>
-        <v>-</v>
-      </c>
-      <c r="H8" s="17" t="str">
-        <f>IFERROR(VLOOKUP(H7,Database!$A$3:$E$113,4,FALSE),"-")</f>
-        <v>-</v>
-      </c>
-      <c r="I8" s="17" t="str">
-        <f>IFERROR(VLOOKUP(I7,Database!$A$3:$E$113,4,FALSE),"-")</f>
-        <v>-</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" ht="17.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="7" t="s">
-        <v>80</v>
-      </c>
-      <c r="B9" s="17" t="str">
-        <f>IFERROR(VLOOKUP(B7,Database!$A$3:$E$113,5,FALSE),"-")</f>
-        <v>-</v>
-      </c>
-      <c r="C9" s="17" t="str">
-        <f>IFERROR(VLOOKUP(C7,Database!$A$3:$E$113,5,FALSE),"-")</f>
-        <v>-</v>
-      </c>
-      <c r="D9" s="17" t="str">
-        <f>IFERROR(VLOOKUP(D7,Database!$A$3:$E$113,5,FALSE),"-")</f>
-        <v>-</v>
-      </c>
-      <c r="E9" s="17" t="str">
-        <f>IFERROR(VLOOKUP(E7,Database!$A$3:$E$113,5,FALSE),"-")</f>
-        <v>-</v>
-      </c>
-      <c r="F9" s="17" t="str">
-        <f>IFERROR(VLOOKUP(F7,Database!$A$3:$E$113,5,FALSE),"-")</f>
-        <v>-</v>
-      </c>
-      <c r="G9" s="17" t="str">
-        <f>IFERROR(VLOOKUP(G7,Database!$A$3:$E$113,5,FALSE),"-")</f>
-        <v>-</v>
-      </c>
-      <c r="H9" s="17" t="str">
-        <f>IFERROR(VLOOKUP(H7,Database!$A$3:$E$113,5,FALSE),"-")</f>
-        <v>-</v>
-      </c>
-      <c r="I9" s="17" t="str">
-        <f>IFERROR(VLOOKUP(I7,Database!$A$3:$E$113,5,FALSE),"-")</f>
-        <v>-</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" ht="16.5" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="B10" s="39">
-        <f>IFERROR(B6*B8,0)</f>
-        <v>0</v>
-      </c>
-      <c r="C10" s="39" t="str">
-        <f>IFERROR(C6*C8,"-")</f>
-        <v>-</v>
-      </c>
-      <c r="D10" s="15" t="str">
-        <f>IFERROR(D6*D8,"-")</f>
-        <v>-</v>
-      </c>
-      <c r="E10" s="15" t="str">
-        <f>IFERROR(E6*E8,"-")</f>
-        <v>-</v>
-      </c>
-      <c r="F10" s="15" t="str">
-        <f>IFERROR(F6*F8,"-")</f>
-        <v>-</v>
-      </c>
-      <c r="G10" s="15" t="str">
-        <f>IFERROR(G6*G8,"-")</f>
-        <v>-</v>
-      </c>
-      <c r="H10" s="15" t="str">
-        <f t="shared" ref="H10:I10" si="0">IFERROR(H6*H8,"-")</f>
-        <v>-</v>
-      </c>
-      <c r="I10" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v>-</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A11" s="21" t="s">
-        <v>77</v>
-      </c>
-      <c r="B11" s="28" t="str">
+      <c r="B11" s="23">
         <f t="shared" ref="B11:G11" si="1">IFERROR(B10/(B9*1000),"-")</f>
-        <v>-</v>
-      </c>
-      <c r="C11" s="28" t="str">
+        <v>0.30220323076923078</v>
+      </c>
+      <c r="C11" s="23" t="str">
         <f t="shared" si="1"/>
         <v>-</v>
       </c>
-      <c r="D11" s="28" t="str">
+      <c r="D11" s="23" t="str">
         <f t="shared" si="1"/>
         <v>-</v>
       </c>
-      <c r="E11" s="28" t="str">
+      <c r="E11" s="23" t="str">
         <f t="shared" si="1"/>
         <v>-</v>
       </c>
-      <c r="F11" s="28" t="str">
+      <c r="F11" s="23" t="str">
         <f t="shared" si="1"/>
         <v>-</v>
       </c>
-      <c r="G11" s="28" t="str">
+      <c r="G11" s="23" t="str">
         <f t="shared" si="1"/>
         <v>-</v>
       </c>
-      <c r="H11" s="28" t="str">
+      <c r="H11" s="23" t="str">
         <f t="shared" ref="H11:I11" si="2">IFERROR(H10/(H9*1000),"-")</f>
         <v>-</v>
       </c>
-      <c r="I11" s="28" t="str">
+      <c r="I11" s="23" t="str">
         <f t="shared" si="2"/>
         <v>-</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A12" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="B12" s="20">
+      <c r="A12" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="B12" s="15">
         <f>SUM(B10:I10)</f>
-        <v>0</v>
+        <v>2357.1851999999999</v>
       </c>
     </row>
     <row r="14" spans="1:12" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="42" t="s">
-        <v>407</v>
-      </c>
-      <c r="B14" s="17" t="str">
+      <c r="A14" s="35" t="s">
+        <v>405</v>
+      </c>
+      <c r="B14" s="12">
         <f>IFERROR(VLOOKUP(B7,Database!$A$3:$G$113,7,FALSE),"-")</f>
-        <v>-</v>
-      </c>
-      <c r="C14" s="17" t="str">
+        <v>192.86</v>
+      </c>
+      <c r="C14" s="12" t="str">
         <f>IFERROR(VLOOKUP(C7,Database!$A$3:$G$113,7,FALSE),"-")</f>
         <v>-</v>
       </c>
-      <c r="D14" s="17" t="str">
+      <c r="D14" s="12" t="str">
         <f>IFERROR(VLOOKUP(D7,Database!$A$3:$G$113,7,FALSE),"-")</f>
         <v>-</v>
       </c>
-      <c r="E14" s="17" t="str">
+      <c r="E14" s="12" t="str">
         <f>IFERROR(VLOOKUP(E7,Database!$A$3:$G$113,7,FALSE),"-")</f>
         <v>-</v>
       </c>
-      <c r="F14" s="17" t="str">
+      <c r="F14" s="12" t="str">
         <f>IFERROR(VLOOKUP(F7,Database!$A$3:$G$113,7,FALSE),"-")</f>
         <v>-</v>
       </c>
-      <c r="G14" s="17" t="str">
+      <c r="G14" s="12" t="str">
         <f>IFERROR(VLOOKUP(G7,Database!$A$3:$G$113,7,FALSE),"-")</f>
         <v>-</v>
       </c>
-      <c r="H14" s="17" t="str">
+      <c r="H14" s="12" t="str">
         <f>IFERROR(VLOOKUP(H7,Database!$A$3:$G$113,7,FALSE),"-")</f>
         <v>-</v>
       </c>
-      <c r="I14" s="17" t="str">
+      <c r="I14" s="12" t="str">
         <f>IFERROR(VLOOKUP(I7,Database!$A$3:$G$113,7,FALSE),"-")</f>
         <v>-</v>
       </c>
     </row>
     <row r="15" spans="1:12" ht="16.5" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="15">
+      <c r="B15" s="10">
         <f>IFERROR(B6*B14,0)</f>
-        <v>0</v>
-      </c>
-      <c r="C15" s="15">
+        <v>771.44</v>
+      </c>
+      <c r="C15" s="10">
         <f t="shared" ref="C15:G15" si="3">IFERROR(C6*C14,0)</f>
         <v>0</v>
       </c>
-      <c r="D15" s="15">
+      <c r="D15" s="10">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="E15" s="15">
+      <c r="E15" s="10">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="F15" s="15">
+      <c r="F15" s="10">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="G15" s="15">
+      <c r="G15" s="10">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="H15" s="15">
+      <c r="H15" s="10">
         <f t="shared" ref="H15:I15" si="4">IFERROR(H6*H14,0)</f>
         <v>0</v>
       </c>
-      <c r="I15" s="15">
+      <c r="I15" s="10">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A16" s="7" t="s">
-        <v>411</v>
-      </c>
-      <c r="B16" s="41">
+      <c r="A16" s="5" t="s">
+        <v>409</v>
+      </c>
+      <c r="B16" s="34">
         <f>SUM(B15:I15)/20</f>
+        <v>38.572000000000003</v>
+      </c>
+      <c r="K16" s="1"/>
+    </row>
+    <row r="19" spans="1:11" ht="18" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="29" t="s">
+        <v>57</v>
+      </c>
+      <c r="B19" s="29"/>
+      <c r="C19" s="29"/>
+      <c r="D19" s="29"/>
+      <c r="E19" s="29"/>
+      <c r="F19" s="29"/>
+      <c r="G19" s="29"/>
+      <c r="H19" s="29"/>
+      <c r="I19" s="29"/>
+    </row>
+    <row r="20" spans="1:11" ht="16.5" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="B20" s="41">
+        <f>B6*2</f>
+        <v>8</v>
+      </c>
+      <c r="C20" s="9">
+        <f>B6*3</f>
+        <v>12</v>
+      </c>
+      <c r="D20" s="9">
+        <f>B6*2</f>
+        <v>8</v>
+      </c>
+      <c r="E20" s="9">
+        <f>B6*10</f>
+        <v>40</v>
+      </c>
+      <c r="F20" s="9">
         <v>0</v>
       </c>
-      <c r="K16" s="1"/>
-    </row>
-    <row r="19" spans="1:11" ht="18" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="36" t="s">
-        <v>59</v>
-      </c>
-      <c r="B19" s="36"/>
-      <c r="C19" s="36"/>
-      <c r="D19" s="36"/>
-      <c r="E19" s="36"/>
-      <c r="F19" s="36"/>
-      <c r="G19" s="36"/>
-      <c r="H19" s="36"/>
-      <c r="I19" s="36"/>
-    </row>
-    <row r="20" spans="1:11" ht="16.5" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="7" t="s">
+      <c r="G20" s="9">
+        <v>0</v>
+      </c>
+      <c r="H20" s="9">
+        <v>0</v>
+      </c>
+      <c r="I20" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A21" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="B21" s="17" t="s">
+        <v>105</v>
+      </c>
+      <c r="C21" s="17" t="s">
+        <v>186</v>
+      </c>
+      <c r="D21" s="17" t="s">
+        <v>151</v>
+      </c>
+      <c r="E21" s="17" t="s">
+        <v>62</v>
+      </c>
+      <c r="F21" s="17"/>
+      <c r="G21" s="17"/>
+      <c r="H21" s="17"/>
+      <c r="I21" s="17"/>
+    </row>
+    <row r="22" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="B22" s="12">
+        <f>IFERROR(VLOOKUP(B21,Database!$A$3:$G$113,4,FALSE),"-")</f>
+        <v>173.05</v>
+      </c>
+      <c r="C22" s="12">
+        <f>IFERROR(VLOOKUP(C21,Database!$A$3:$G$113,4,FALSE),"-")</f>
+        <v>9.01</v>
+      </c>
+      <c r="D22" s="12">
+        <f>IFERROR(VLOOKUP(D21,Database!$A$3:$G$113,4,FALSE),"-")</f>
+        <v>28.085000000000001</v>
+      </c>
+      <c r="E22" s="12">
+        <f>IFERROR(VLOOKUP(E21,Database!$A$3:$G$113,4,FALSE),"-")</f>
+        <v>16</v>
+      </c>
+      <c r="F22" s="12" t="str">
+        <f>IFERROR(VLOOKUP(F21,Database!$A$3:$G$113,4,FALSE),"-")</f>
+        <v>-</v>
+      </c>
+      <c r="G22" s="12" t="str">
+        <f>IFERROR(VLOOKUP(G21,Database!$A$3:$G$113,4,FALSE),"-")</f>
+        <v>-</v>
+      </c>
+      <c r="H22" s="12" t="str">
+        <f>IFERROR(VLOOKUP(H21,Database!$A$3:$G$113,4,FALSE),"-")</f>
+        <v>-</v>
+      </c>
+      <c r="I22" s="12" t="str">
+        <f>IFERROR(VLOOKUP(I21,Database!$A$3:$G$113,4,FALSE),"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" ht="17.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="B23" s="12">
+        <f>IFERROR(VLOOKUP(B21,Database!$A$3:$G$113,5,FALSE),"-")</f>
+        <v>5.2</v>
+      </c>
+      <c r="C23" s="12">
+        <f>IFERROR(VLOOKUP(C21,Database!$A$3:$G$113,5,FALSE),"-")</f>
+        <v>0.75080000000000002</v>
+      </c>
+      <c r="D23" s="12">
+        <f>IFERROR(VLOOKUP(D21,Database!$A$3:$G$113,5,FALSE),"-")</f>
+        <v>2.3289999999999997</v>
+      </c>
+      <c r="E23" s="12">
+        <f>IFERROR(VLOOKUP(E21,Database!$A$3:$G$113,5,FALSE),"-")</f>
+        <v>1.141</v>
+      </c>
+      <c r="F23" s="12" t="str">
+        <f>IFERROR(VLOOKUP(F21,Database!$A$3:$G$113,5,FALSE),"-")</f>
+        <v>-</v>
+      </c>
+      <c r="G23" s="12" t="str">
+        <f>IFERROR(VLOOKUP(G21,Database!$A$3:$G$113,5,FALSE),"-")</f>
+        <v>-</v>
+      </c>
+      <c r="H23" s="12" t="str">
+        <f>IFERROR(VLOOKUP(H21,Database!$A$3:$G$113,5,FALSE),"-")</f>
+        <v>-</v>
+      </c>
+      <c r="I23" s="12" t="str">
+        <f>IFERROR(VLOOKUP(I21,Database!$A$3:$G$113,5,FALSE),"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" ht="16.5" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="B20" s="48">
-        <v>0</v>
-      </c>
-      <c r="C20" s="14">
-        <v>0</v>
-      </c>
-      <c r="D20" s="14">
-        <v>0</v>
-      </c>
-      <c r="E20" s="14">
-        <v>0</v>
-      </c>
-      <c r="F20" s="14">
-        <v>0</v>
-      </c>
-      <c r="G20" s="14">
-        <v>0</v>
-      </c>
-      <c r="H20" s="14">
-        <v>0</v>
-      </c>
-      <c r="I20" s="14">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A21" s="7" t="s">
-        <v>83</v>
-      </c>
-      <c r="B21" s="22"/>
-      <c r="C21" s="22"/>
-      <c r="D21" s="22"/>
-      <c r="E21" s="22"/>
-      <c r="F21" s="22"/>
-      <c r="G21" s="22"/>
-      <c r="H21" s="22"/>
-      <c r="I21" s="22"/>
-    </row>
-    <row r="22" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="7" t="s">
+      <c r="B24" s="10">
+        <f>IFERROR(B20*B22,0)</f>
+        <v>1384.4</v>
+      </c>
+      <c r="C24" s="10">
+        <f>IFERROR(C20*C22,"-")</f>
+        <v>108.12</v>
+      </c>
+      <c r="D24" s="10">
+        <f>IFERROR(D20*D22,"-")</f>
+        <v>224.68</v>
+      </c>
+      <c r="E24" s="10">
+        <f>IFERROR(E20*E22,"-")</f>
+        <v>640</v>
+      </c>
+      <c r="F24" s="10" t="str">
+        <f>IFERROR(F20*F22,"-")</f>
+        <v>-</v>
+      </c>
+      <c r="G24" s="10" t="str">
+        <f>IFERROR(G20*G22,"-")</f>
+        <v>-</v>
+      </c>
+      <c r="H24" s="10" t="str">
+        <f t="shared" ref="H24:I24" si="5">IFERROR(H20*H22,"-")</f>
+        <v>-</v>
+      </c>
+      <c r="I24" s="10" t="str">
+        <f t="shared" si="5"/>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A25" s="16" t="s">
         <v>75</v>
       </c>
-      <c r="B22" s="17" t="str">
-        <f>IFERROR(VLOOKUP(B21,Database!$A$3:$G$113,4,FALSE),"-")</f>
-        <v>-</v>
-      </c>
-      <c r="C22" s="17" t="str">
-        <f>IFERROR(VLOOKUP(C21,Database!$A$3:$G$113,4,FALSE),"-")</f>
-        <v>-</v>
-      </c>
-      <c r="D22" s="17" t="str">
-        <f>IFERROR(VLOOKUP(D21,Database!$A$3:$G$113,4,FALSE),"-")</f>
-        <v>-</v>
-      </c>
-      <c r="E22" s="17" t="str">
-        <f>IFERROR(VLOOKUP(E21,Database!$A$3:$G$113,4,FALSE),"-")</f>
-        <v>-</v>
-      </c>
-      <c r="F22" s="17" t="str">
-        <f>IFERROR(VLOOKUP(F21,Database!$A$3:$G$113,4,FALSE),"-")</f>
-        <v>-</v>
-      </c>
-      <c r="G22" s="17" t="str">
-        <f>IFERROR(VLOOKUP(G21,Database!$A$3:$G$113,4,FALSE),"-")</f>
-        <v>-</v>
-      </c>
-      <c r="H22" s="17" t="str">
-        <f>IFERROR(VLOOKUP(H21,Database!$A$3:$G$113,4,FALSE),"-")</f>
-        <v>-</v>
-      </c>
-      <c r="I22" s="17" t="str">
-        <f>IFERROR(VLOOKUP(I21,Database!$A$3:$G$113,4,FALSE),"-")</f>
-        <v>-</v>
-      </c>
-    </row>
-    <row r="23" spans="1:11" ht="17.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="7" t="s">
-        <v>80</v>
-      </c>
-      <c r="B23" s="17" t="str">
-        <f>IFERROR(VLOOKUP(B21,Database!$A$3:$G$113,5,FALSE),"-")</f>
-        <v>-</v>
-      </c>
-      <c r="C23" s="17" t="str">
-        <f>IFERROR(VLOOKUP(C21,Database!$A$3:$G$113,5,FALSE),"-")</f>
-        <v>-</v>
-      </c>
-      <c r="D23" s="17" t="str">
-        <f>IFERROR(VLOOKUP(D21,Database!$A$3:$G$113,5,FALSE),"-")</f>
-        <v>-</v>
-      </c>
-      <c r="E23" s="17" t="str">
-        <f>IFERROR(VLOOKUP(E21,Database!$A$3:$G$113,5,FALSE),"-")</f>
-        <v>-</v>
-      </c>
-      <c r="F23" s="17" t="str">
-        <f>IFERROR(VLOOKUP(F21,Database!$A$3:$G$113,5,FALSE),"-")</f>
-        <v>-</v>
-      </c>
-      <c r="G23" s="17" t="str">
-        <f>IFERROR(VLOOKUP(G21,Database!$A$3:$G$113,5,FALSE),"-")</f>
-        <v>-</v>
-      </c>
-      <c r="H23" s="17" t="str">
-        <f>IFERROR(VLOOKUP(H21,Database!$A$3:$G$113,5,FALSE),"-")</f>
-        <v>-</v>
-      </c>
-      <c r="I23" s="17" t="str">
-        <f>IFERROR(VLOOKUP(I21,Database!$A$3:$G$113,5,FALSE),"-")</f>
-        <v>-</v>
-      </c>
-    </row>
-    <row r="24" spans="1:11" ht="16.5" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="B24" s="15">
-        <f>IFERROR(B20*B22,0)</f>
-        <v>0</v>
-      </c>
-      <c r="C24" s="15" t="str">
-        <f>IFERROR(C20*C22,"-")</f>
-        <v>-</v>
-      </c>
-      <c r="D24" s="15" t="str">
-        <f>IFERROR(D20*D22,"-")</f>
-        <v>-</v>
-      </c>
-      <c r="E24" s="15" t="str">
-        <f>IFERROR(E20*E22,"-")</f>
-        <v>-</v>
-      </c>
-      <c r="F24" s="15" t="str">
-        <f>IFERROR(F20*F22,"-")</f>
-        <v>-</v>
-      </c>
-      <c r="G24" s="15" t="str">
-        <f>IFERROR(G20*G22,"-")</f>
-        <v>-</v>
-      </c>
-      <c r="H24" s="15" t="str">
-        <f t="shared" ref="H24:I24" si="5">IFERROR(H20*H22,"-")</f>
-        <v>-</v>
-      </c>
-      <c r="I24" s="15" t="str">
-        <f t="shared" si="5"/>
-        <v>-</v>
-      </c>
-    </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A25" s="21" t="s">
-        <v>77</v>
-      </c>
-      <c r="B25" s="28" t="str">
+      <c r="B25" s="23">
         <f t="shared" ref="B25:G25" si="6">IFERROR(B24/(B23*1000),"-")</f>
-        <v>-</v>
-      </c>
-      <c r="C25" s="28" t="str">
+        <v>0.26623076923076927</v>
+      </c>
+      <c r="C25" s="23">
         <f t="shared" si="6"/>
-        <v>-</v>
-      </c>
-      <c r="D25" s="28" t="str">
+        <v>0.14400639318060734</v>
+      </c>
+      <c r="D25" s="23">
         <f t="shared" si="6"/>
-        <v>-</v>
-      </c>
-      <c r="E25" s="28" t="str">
+        <v>9.6470588235294141E-2</v>
+      </c>
+      <c r="E25" s="23">
         <f t="shared" si="6"/>
-        <v>-</v>
-      </c>
-      <c r="F25" s="28" t="str">
+        <v>0.56091148115687994</v>
+      </c>
+      <c r="F25" s="23" t="str">
         <f t="shared" si="6"/>
         <v>-</v>
       </c>
-      <c r="G25" s="28" t="str">
+      <c r="G25" s="23" t="str">
         <f t="shared" si="6"/>
         <v>-</v>
       </c>
-      <c r="H25" s="28" t="str">
+      <c r="H25" s="23" t="str">
         <f t="shared" ref="H25:I25" si="7">IFERROR(H24/(H23*1000),"-")</f>
         <v>-</v>
       </c>
-      <c r="I25" s="28" t="str">
+      <c r="I25" s="23" t="str">
         <f t="shared" si="7"/>
         <v>-</v>
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A26" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="B26" s="20">
+      <c r="A26" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="B26" s="15">
         <f>SUM(B24:I24)</f>
-        <v>0</v>
+        <v>2357.1999999999998</v>
       </c>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A27" s="7"/>
+      <c r="A27" s="5"/>
     </row>
     <row r="28" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="42" t="s">
-        <v>407</v>
-      </c>
-      <c r="B28" s="17" t="str">
+      <c r="A28" s="35" t="s">
+        <v>405</v>
+      </c>
+      <c r="B28" s="12">
         <f>IFERROR(VLOOKUP(B21,Database!$A$3:$G$113,7,FALSE),"-")</f>
-        <v>-</v>
-      </c>
-      <c r="C28" s="17" t="str">
+        <v>6.25</v>
+      </c>
+      <c r="C28" s="12">
         <f>IFERROR(VLOOKUP(C21,Database!$A$3:$G$113,7,FALSE),"-")</f>
-        <v>-</v>
-      </c>
-      <c r="D28" s="17" t="str">
+        <v>9.32</v>
+      </c>
+      <c r="D28" s="12">
         <f>IFERROR(VLOOKUP(D21,Database!$A$3:$G$113,7,FALSE),"-")</f>
-        <v>-</v>
-      </c>
-      <c r="E28" s="17" t="str">
+        <v>8.15</v>
+      </c>
+      <c r="E28" s="12">
         <f>IFERROR(VLOOKUP(E21,Database!$A$3:$G$113,7,FALSE),"-")</f>
-        <v>-</v>
-      </c>
-      <c r="F28" s="17" t="str">
+        <v>13.61</v>
+      </c>
+      <c r="F28" s="12" t="str">
         <f>IFERROR(VLOOKUP(F21,Database!$A$3:$G$113,7,FALSE),"-")</f>
         <v>-</v>
       </c>
-      <c r="G28" s="17" t="str">
+      <c r="G28" s="12" t="str">
         <f>IFERROR(VLOOKUP(G21,Database!$A$3:$G$113,7,FALSE),"-")</f>
         <v>-</v>
       </c>
-      <c r="H28" s="17"/>
-      <c r="I28" s="17"/>
+      <c r="H28" s="12"/>
+      <c r="I28" s="12"/>
     </row>
     <row r="29" spans="1:11" ht="16.5" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="B29" s="15">
+      <c r="B29" s="10">
         <f>IFERROR(B20*B28,0)</f>
-        <v>0</v>
-      </c>
-      <c r="C29" s="15">
+        <v>50</v>
+      </c>
+      <c r="C29" s="10">
         <f t="shared" ref="C29:I29" si="8">IFERROR(C20*C28,0)</f>
-        <v>0</v>
-      </c>
-      <c r="D29" s="15">
+        <v>111.84</v>
+      </c>
+      <c r="D29" s="10">
+        <f t="shared" si="8"/>
+        <v>65.2</v>
+      </c>
+      <c r="E29" s="10">
+        <f t="shared" si="8"/>
+        <v>544.4</v>
+      </c>
+      <c r="F29" s="10">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="E29" s="15">
+      <c r="G29" s="10">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="F29" s="15">
+      <c r="H29" s="10">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="G29" s="15">
+      <c r="I29" s="10">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="H29" s="15">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="I29" s="15">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A30" s="7" t="s">
-        <v>411</v>
-      </c>
-      <c r="B30" s="41">
+      <c r="A30" s="5" t="s">
+        <v>409</v>
+      </c>
+      <c r="B30" s="34">
         <f>SUM(B29:I29)/20</f>
-        <v>0</v>
+        <v>38.572000000000003</v>
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.25">
       <c r="K31" s="1"/>
     </row>
     <row r="33" spans="1:9" ht="18" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="38" t="s">
-        <v>62</v>
-      </c>
-      <c r="B33" s="38"/>
-      <c r="C33" s="38"/>
-      <c r="D33" s="38"/>
-      <c r="E33" s="38"/>
-      <c r="F33" s="38"/>
-      <c r="G33" s="38"/>
-      <c r="H33" s="38"/>
-      <c r="I33" s="38"/>
+      <c r="A33" s="31" t="s">
+        <v>60</v>
+      </c>
+      <c r="B33" s="31"/>
+      <c r="C33" s="31"/>
+      <c r="D33" s="31"/>
+      <c r="E33" s="31"/>
+      <c r="F33" s="31"/>
+      <c r="G33" s="31"/>
+      <c r="H33" s="31"/>
+      <c r="I33" s="31"/>
     </row>
     <row r="34" spans="1:9" ht="16.5" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="B34" s="16" t="str">
+      <c r="A34" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="B34" s="11" t="str">
         <f>IF($B$12&gt;$B$26,"Input excesive",IF($B$12&lt;$B$26,"Output excessive","Equal"))</f>
-        <v>Equal</v>
-      </c>
-      <c r="C34" s="27">
+        <v>Output excessive</v>
+      </c>
+      <c r="C34" s="22">
         <f>IF($B$12&gt;$B$26,B12/B26,IF($B$12&lt;$B$26,B26/B12,1))</f>
-        <v>1</v>
+        <v>1.000006278675091</v>
       </c>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.25">
       <c r="D36">
         <f>1/C34</f>
-        <v>1</v>
+        <v>0.99999372136433051</v>
       </c>
       <c r="G36" s="1"/>
       <c r="H36" s="1"/>
       <c r="I36" s="1"/>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B37" s="45"/>
+      <c r="B37" s="38"/>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B39" s="44"/>
+      <c r="B39" s="37"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -3748,19 +3753,19 @@
         <v>1</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>2</v>
+        <v>498</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>3</v>
+        <v>499</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
     </row>
     <row r="2" spans="1:17" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -3773,47 +3778,47 @@
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="C3" s="1">
         <v>0.02</v>
       </c>
-      <c r="D3" s="5">
+      <c r="D3" s="52">
         <v>576.85</v>
       </c>
-      <c r="E3" s="4">
+      <c r="E3" s="52">
         <f>0.01*1000</f>
         <v>10</v>
       </c>
-      <c r="F3" s="6">
+      <c r="F3" s="4">
         <f>D3/(E3 * 1000)</f>
         <v>5.7685E-2</v>
       </c>
-      <c r="G3" s="8">
+      <c r="G3" s="6">
         <v>283.27</v>
       </c>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C4" s="1">
         <v>0.8</v>
       </c>
-      <c r="D4" s="5">
+      <c r="D4" s="52">
         <v>170.34</v>
       </c>
-      <c r="E4" s="4">
+      <c r="E4" s="52">
         <f>0.005*1000</f>
         <v>5</v>
       </c>
-      <c r="F4" s="6">
+      <c r="F4" s="4">
         <f t="shared" ref="F4:F8" si="0">D4/(E4 * 1000)</f>
         <v>3.4068000000000001E-2</v>
       </c>
@@ -3821,40 +3826,40 @@
         <v>488.46</v>
       </c>
       <c r="J4" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="K4" t="s">
         <v>0</v>
       </c>
       <c r="L4" t="s">
+        <v>69</v>
+      </c>
+      <c r="M4" t="s">
+        <v>70</v>
+      </c>
+      <c r="N4" t="s">
         <v>71</v>
       </c>
-      <c r="M4" t="s">
-        <v>72</v>
-      </c>
-      <c r="N4" t="s">
-        <v>73</v>
-      </c>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A5" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5" s="9" t="s">
-        <v>169</v>
-      </c>
-      <c r="C5" s="9">
+      <c r="A5" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>167</v>
+      </c>
+      <c r="C5" s="7">
         <v>0.18</v>
       </c>
-      <c r="D5" s="10">
+      <c r="D5" s="53">
         <f>54.4</f>
         <v>54.4</v>
       </c>
-      <c r="E5" s="11">
+      <c r="E5" s="53">
         <f>0.005*1000</f>
         <v>5</v>
       </c>
-      <c r="F5" s="6">
+      <c r="F5" s="4">
         <f t="shared" si="0"/>
         <v>1.0879999999999999E-2</v>
       </c>
@@ -3862,18 +3867,18 @@
         <v>54.4</v>
       </c>
       <c r="J5" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K5" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="L5" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="M5">
         <v>117.49</v>
       </c>
-      <c r="N5" s="18">
+      <c r="N5" s="13">
         <v>0.7</v>
       </c>
       <c r="O5">
@@ -3883,30 +3888,30 @@
         <f>M5*O5</f>
         <v>11631.51</v>
       </c>
-      <c r="Q5" s="56">
+      <c r="Q5" s="49">
         <f>P5/$P$8</f>
         <v>0.70146498497745102</v>
       </c>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C6" s="1">
         <v>1.2</v>
       </c>
-      <c r="D6" s="5">
+      <c r="D6" s="52">
         <f>(14.007*2)+(1.008*4)</f>
         <v>32.045999999999999</v>
       </c>
-      <c r="E6" s="4">
+      <c r="E6" s="52">
         <f>0.004*1000</f>
         <v>4</v>
       </c>
-      <c r="F6" s="6">
+      <c r="F6" s="4">
         <f t="shared" si="0"/>
         <v>8.0114999999999995E-3</v>
       </c>
@@ -3914,18 +3919,18 @@
         <v>83.42</v>
       </c>
       <c r="J6" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="K6" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="L6" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="M6">
         <v>26.98</v>
       </c>
-      <c r="N6" s="19">
+      <c r="N6" s="14">
         <v>0.15</v>
       </c>
       <c r="O6">
@@ -3935,30 +3940,30 @@
         <f t="shared" ref="P6:P7" si="1">M6*O6</f>
         <v>2482.16</v>
       </c>
-      <c r="Q6" s="56">
+      <c r="Q6" s="49">
         <f>P6/$P$8</f>
         <v>0.14969237245307185</v>
       </c>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C7" s="1">
         <v>4</v>
       </c>
-      <c r="D7" s="5">
+      <c r="D7" s="52">
         <f>131.29</f>
         <v>131.29</v>
       </c>
-      <c r="E7" s="4">
+      <c r="E7" s="52">
         <f>0.0001*1000</f>
         <v>0.1</v>
       </c>
-      <c r="F7" s="6">
+      <c r="F7" s="4">
         <f t="shared" si="0"/>
         <v>1.3129</v>
       </c>
@@ -3966,18 +3971,18 @@
         <v>12.12</v>
       </c>
       <c r="J7" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="K7" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="L7" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="M7">
         <v>2468.0700000000002</v>
       </c>
-      <c r="N7" s="18">
+      <c r="N7" s="13">
         <v>0.15</v>
       </c>
       <c r="O7">
@@ -3987,60 +3992,62 @@
         <f t="shared" si="1"/>
         <v>2468.0700000000002</v>
       </c>
-      <c r="Q7" s="56">
+      <c r="Q7" s="49">
         <f>P7/$P$8</f>
         <v>0.14884264256947702</v>
       </c>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="C8" s="1">
         <v>0.6</v>
       </c>
-      <c r="D8" s="5">
+      <c r="D8" s="52">
         <v>1658.174</v>
       </c>
-      <c r="E8" s="4">
+      <c r="E8" s="52">
         <f>0.0075*1000</f>
         <v>7.5</v>
       </c>
-      <c r="F8" s="6">
+      <c r="F8" s="4">
         <f t="shared" si="0"/>
         <v>0.22108986666666666</v>
       </c>
-      <c r="N8" s="18"/>
+      <c r="N8" s="13"/>
       <c r="P8">
         <f>SUM(P5:P7)</f>
         <v>16581.740000000002</v>
       </c>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="L9" s="19"/>
+      <c r="D9" s="37"/>
+      <c r="E9" s="37"/>
+      <c r="L9" s="14"/>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="C10" s="1">
         <v>1.35</v>
       </c>
-      <c r="D10" s="5">
+      <c r="D10" s="52">
         <f>SUM(($D$51*0.5)+($D$109*0.5))</f>
         <v>46.073</v>
       </c>
-      <c r="E10" s="4">
+      <c r="E10" s="52">
         <f>0.0009*1000</f>
         <v>0.9</v>
       </c>
-      <c r="F10" s="6">
+      <c r="F10" s="4">
         <f>D10/(E10 * 1000)</f>
         <v>5.1192222222222222E-2</v>
       </c>
@@ -4048,26 +4055,26 @@
         <f>(G51/2)+(G109/2)</f>
         <v>1623.855</v>
       </c>
-      <c r="L10" s="18"/>
+      <c r="L10" s="13"/>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B11" s="1" t="s">
         <v>29</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>31</v>
       </c>
       <c r="C11" s="1">
         <v>0.5</v>
       </c>
-      <c r="D11" s="5">
+      <c r="D11" s="52">
         <v>101.96</v>
       </c>
-      <c r="E11" s="4">
+      <c r="E11" s="52">
         <f>0.00398*1000</f>
         <v>3.98</v>
       </c>
-      <c r="F11" s="6">
+      <c r="F11" s="4">
         <f t="shared" ref="F11:F15" si="2">D11/(E11 * 1000)</f>
         <v>2.5618090452261304E-2</v>
       </c>
@@ -4077,22 +4084,22 @@
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C12" s="1">
         <v>1.5</v>
       </c>
-      <c r="D12" s="5">
+      <c r="D12" s="52">
         <v>26.98</v>
       </c>
-      <c r="E12" s="4">
+      <c r="E12" s="52">
         <f>0.00277*1000</f>
         <v>2.77</v>
       </c>
-      <c r="F12" s="6">
+      <c r="F12" s="4">
         <f t="shared" si="2"/>
         <v>9.7400722021660658E-3</v>
       </c>
@@ -4102,22 +4109,22 @@
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C13" s="1">
         <v>1.4999999999999999E-4</v>
       </c>
-      <c r="D13" s="5">
+      <c r="D13" s="52">
         <v>17.03</v>
       </c>
-      <c r="E13" s="4">
+      <c r="E13" s="52">
         <f>0.000000769*1000</f>
         <v>7.6899999999999994E-4</v>
       </c>
-      <c r="F13" s="6">
+      <c r="F13" s="4">
         <f t="shared" si="2"/>
         <v>22.145643693107935</v>
       </c>
@@ -4127,22 +4134,22 @@
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C14" s="1">
         <v>1.0500000000000001E-2</v>
       </c>
-      <c r="D14" s="5">
+      <c r="D14" s="52">
         <v>39.950000000000003</v>
       </c>
-      <c r="E14" s="4">
+      <c r="E14" s="52">
         <f>0.000001784*1000</f>
         <v>1.784E-3</v>
       </c>
-      <c r="F14" s="6">
+      <c r="F14" s="4">
         <f t="shared" si="2"/>
         <v>22.393497757847534</v>
       </c>
@@ -4152,22 +4159,22 @@
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="C15" s="1">
         <v>0.5213333</v>
       </c>
-      <c r="D15" s="5">
+      <c r="D15" s="52">
         <v>93.13</v>
       </c>
-      <c r="E15" s="4">
+      <c r="E15" s="52">
         <f>0.00102*1000</f>
         <v>1.02</v>
       </c>
-      <c r="F15" s="6">
+      <c r="F15" s="4">
         <f t="shared" si="2"/>
         <v>9.1303921568627447E-2</v>
       </c>
@@ -4176,23 +4183,23 @@
       </c>
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A16" s="29" t="s">
-        <v>188</v>
-      </c>
-      <c r="B16" s="29" t="s">
-        <v>189</v>
-      </c>
-      <c r="C16" s="29">
-        <v>250</v>
-      </c>
-      <c r="D16" s="30">
+      <c r="A16" s="24" t="s">
+        <v>186</v>
+      </c>
+      <c r="B16" s="24" t="s">
+        <v>187</v>
+      </c>
+      <c r="C16" s="24">
+        <v>1.4</v>
+      </c>
+      <c r="D16" s="54">
         <v>9.01</v>
       </c>
-      <c r="E16" s="31">
+      <c r="E16" s="54">
         <f>0.0007508*1000</f>
         <v>0.75080000000000002</v>
       </c>
-      <c r="F16" s="32">
+      <c r="F16" s="25">
         <f>D16/(E16 * 1000)</f>
         <v>1.2000532765050611E-2</v>
       </c>
@@ -4201,23 +4208,23 @@
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A17" s="29" t="s">
-        <v>190</v>
-      </c>
-      <c r="B17" s="29" t="s">
-        <v>191</v>
-      </c>
-      <c r="C17" s="29">
+      <c r="A17" s="24" t="s">
+        <v>188</v>
+      </c>
+      <c r="B17" s="24" t="s">
+        <v>189</v>
+      </c>
+      <c r="C17" s="24">
         <v>0.8</v>
       </c>
-      <c r="D17" s="30">
+      <c r="D17" s="54">
         <v>66.02</v>
       </c>
-      <c r="E17" s="31">
+      <c r="E17" s="54">
         <f>0.00244518*1000</f>
         <v>2.4451800000000001</v>
       </c>
-      <c r="F17" s="32">
+      <c r="F17" s="25">
         <f t="shared" ref="F17:F18" si="3">D17/(E17 * 1000)</f>
         <v>2.7000057255498568E-2</v>
       </c>
@@ -4226,21 +4233,21 @@
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A18" s="29" t="s">
-        <v>218</v>
-      </c>
-      <c r="B18" s="29" t="s">
-        <v>214</v>
-      </c>
-      <c r="C18" s="29"/>
-      <c r="D18" s="30">
+      <c r="A18" s="24" t="s">
+        <v>216</v>
+      </c>
+      <c r="B18" s="24" t="s">
+        <v>212</v>
+      </c>
+      <c r="C18" s="24"/>
+      <c r="D18" s="54">
         <v>720.6</v>
       </c>
-      <c r="E18" s="31">
+      <c r="E18" s="54">
         <f>0.126*1000</f>
         <v>126</v>
       </c>
-      <c r="F18" s="32">
+      <c r="F18" s="25">
         <f t="shared" si="3"/>
         <v>5.7190476190476193E-3</v>
       </c>
@@ -4249,23 +4256,23 @@
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A19" s="9" t="s">
-        <v>192</v>
-      </c>
-      <c r="B19" s="9" t="s">
-        <v>193</v>
-      </c>
-      <c r="C19" s="9">
+      <c r="A19" s="7" t="s">
+        <v>190</v>
+      </c>
+      <c r="B19" s="7" t="s">
+        <v>191</v>
+      </c>
+      <c r="C19" s="7">
         <v>0.85099999999999998</v>
       </c>
-      <c r="D19" s="10">
+      <c r="D19" s="53">
         <v>10.81</v>
       </c>
-      <c r="E19" s="11">
+      <c r="E19" s="53">
         <f>0.00246*1000</f>
         <v>2.46</v>
       </c>
-      <c r="F19" s="12">
+      <c r="F19" s="8">
         <f>D19/(E19 * 1000)</f>
         <v>4.3943089430894307E-3</v>
       </c>
@@ -4274,75 +4281,75 @@
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A20" s="9" t="s">
-        <v>203</v>
-      </c>
-      <c r="B20" s="9" t="s">
-        <v>204</v>
-      </c>
-      <c r="C20" s="9">
+      <c r="A20" s="7" t="s">
+        <v>201</v>
+      </c>
+      <c r="B20" s="7" t="s">
+        <v>202</v>
+      </c>
+      <c r="C20" s="7">
         <v>77</v>
       </c>
-      <c r="D20" s="10">
+      <c r="D20" s="53">
         <v>132.91</v>
       </c>
-      <c r="E20" s="11">
+      <c r="E20" s="53">
         <f>0.00193*1000</f>
         <v>1.9300000000000002</v>
       </c>
-      <c r="F20" s="12">
+      <c r="F20" s="8">
         <f t="shared" ref="F20:F36" si="4">D20/(E20 * 1000)</f>
         <v>6.8865284974093249E-2</v>
       </c>
-      <c r="G20" s="33">
+      <c r="G20" s="26">
         <v>3.89</v>
       </c>
-      <c r="H20" s="33"/>
+      <c r="H20" s="26"/>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A21" s="9" t="s">
-        <v>234</v>
-      </c>
-      <c r="B21" s="9" t="s">
-        <v>223</v>
-      </c>
-      <c r="C21" s="9">
+      <c r="A21" s="7" t="s">
+        <v>232</v>
+      </c>
+      <c r="B21" s="7" t="s">
+        <v>221</v>
+      </c>
+      <c r="C21" s="7">
         <v>1.4999999999999999E-4</v>
       </c>
-      <c r="D21" s="10">
+      <c r="D21" s="53">
         <v>40.08</v>
       </c>
-      <c r="E21" s="11">
+      <c r="E21" s="53">
         <f>0.00155*1000</f>
         <v>1.55</v>
       </c>
-      <c r="F21" s="12">
+      <c r="F21" s="8">
         <f t="shared" si="4"/>
         <v>2.5858064516129032E-2</v>
       </c>
-      <c r="G21" s="33">
+      <c r="G21" s="26">
         <v>6.11</v>
       </c>
-      <c r="H21" s="33"/>
+      <c r="H21" s="26"/>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C22" s="1">
         <v>0</v>
       </c>
-      <c r="D22" s="5">
+      <c r="D22" s="52">
         <v>12.01</v>
       </c>
-      <c r="E22" s="4">
+      <c r="E22" s="52">
         <f>0.0021*1000</f>
         <v>2.1</v>
       </c>
-      <c r="F22" s="12">
+      <c r="F22" s="8">
         <f t="shared" si="4"/>
         <v>5.7190476190476193E-3</v>
       </c>
@@ -4352,22 +4359,22 @@
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C23" s="1">
         <v>2.8636999999999998E-6</v>
       </c>
-      <c r="D23" s="5">
+      <c r="D23" s="52">
         <v>44.01</v>
       </c>
-      <c r="E23" s="4">
+      <c r="E23" s="52">
         <f>0.000001951*1000</f>
         <v>1.951E-3</v>
       </c>
-      <c r="F23" s="12">
+      <c r="F23" s="8">
         <f t="shared" si="4"/>
         <v>22.557662737057917</v>
       </c>
@@ -4377,22 +4384,22 @@
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="B24" s="1" t="s">
         <v>166</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>168</v>
       </c>
       <c r="C24" s="1">
         <v>3.32E-6</v>
       </c>
-      <c r="D24" s="5">
+      <c r="D24" s="52">
         <v>28.01</v>
       </c>
-      <c r="E24" s="4">
+      <c r="E24" s="52">
         <f>0.00000125*1000</f>
         <v>1.25E-3</v>
       </c>
-      <c r="F24" s="12">
+      <c r="F24" s="8">
         <f t="shared" si="4"/>
         <v>22.408000000000001</v>
       </c>
@@ -4402,22 +4409,22 @@
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="C25" s="1">
         <v>16</v>
       </c>
-      <c r="D25" s="5">
+      <c r="D25" s="52">
         <v>558.47</v>
       </c>
-      <c r="E25" s="4">
+      <c r="E25" s="52">
         <f>0.0025*1000</f>
         <v>2.5</v>
       </c>
-      <c r="F25" s="6">
+      <c r="F25" s="4">
         <f t="shared" si="4"/>
         <v>0.223388</v>
       </c>
@@ -4427,22 +4434,22 @@
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="C26" s="1">
         <v>1.4999999999999999E-4</v>
       </c>
-      <c r="D26" s="5">
+      <c r="D26" s="52">
         <v>35.450000000000003</v>
       </c>
-      <c r="E26" s="4">
+      <c r="E26" s="52">
         <f>0.0032*1000</f>
         <v>3.2</v>
       </c>
-      <c r="F26" s="12">
+      <c r="F26" s="8">
         <f t="shared" si="4"/>
         <v>1.1078125000000001E-2</v>
       </c>
@@ -4452,37 +4459,37 @@
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="B27" s="1"/>
       <c r="C27" s="1">
         <v>15</v>
       </c>
-      <c r="D27" s="5"/>
-      <c r="E27" s="4">
+      <c r="D27" s="52"/>
+      <c r="E27" s="52">
         <f>0.001556*1000</f>
         <v>1.556</v>
       </c>
-      <c r="F27" s="6"/>
+      <c r="F27" s="4"/>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="C28" s="1">
         <v>0</v>
       </c>
-      <c r="D28" s="5">
+      <c r="D28" s="52">
         <v>238.03</v>
       </c>
-      <c r="E28" s="4">
+      <c r="E28" s="52">
         <f>0.01097*1000</f>
         <v>10.97</v>
       </c>
-      <c r="F28" s="12">
+      <c r="F28" s="8">
         <f t="shared" si="4"/>
         <v>2.1698268003646309E-2</v>
       </c>
@@ -4492,72 +4499,72 @@
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C29" s="1">
         <v>2.7999999999999998E-4</v>
       </c>
-      <c r="D29" s="5">
+      <c r="D29" s="52">
         <v>2.0139999999999998</v>
       </c>
-      <c r="E29" s="4">
+      <c r="E29" s="52">
         <f>0.00000018*1000</f>
         <v>1.7999999999999998E-4</v>
       </c>
-      <c r="F29" s="12">
+      <c r="F29" s="8">
         <f t="shared" si="4"/>
         <v>11.188888888888888</v>
       </c>
-      <c r="G29" s="8">
+      <c r="G29" s="6">
         <v>13.59</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="C30" s="1">
         <v>4.21</v>
       </c>
-      <c r="D30" s="5">
+      <c r="D30" s="52">
         <v>27.67</v>
       </c>
-      <c r="E30" s="4">
+      <c r="E30" s="52">
         <f>0.000421*1000</f>
         <v>0.42099999999999999</v>
       </c>
-      <c r="F30" s="12">
+      <c r="F30" s="8">
         <f t="shared" si="4"/>
         <v>6.5724465558194778E-2</v>
       </c>
-      <c r="G30" s="8">
+      <c r="G30" s="6">
         <v>98.12</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C31" s="1">
         <v>0.3</v>
       </c>
-      <c r="D31" s="5">
+      <c r="D31" s="52">
         <v>60.08</v>
       </c>
-      <c r="E31" s="4">
+      <c r="E31" s="52">
         <f>0.0016*1000</f>
         <v>1.6</v>
       </c>
-      <c r="F31" s="12">
+      <c r="F31" s="8">
         <f t="shared" si="4"/>
         <v>3.755E-2</v>
       </c>
@@ -4567,22 +4574,22 @@
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="C32" s="1">
         <v>865</v>
       </c>
-      <c r="D32" s="5">
+      <c r="D32" s="52">
         <v>238.03</v>
       </c>
-      <c r="E32" s="4">
+      <c r="E32" s="52">
         <f>0.01097*1000</f>
         <v>10.97</v>
       </c>
-      <c r="F32" s="12">
+      <c r="F32" s="8">
         <f t="shared" si="4"/>
         <v>2.1698268003646309E-2</v>
       </c>
@@ -4592,22 +4599,22 @@
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="C33" s="1">
         <v>0.12623999999999999</v>
       </c>
-      <c r="D33" s="5">
+      <c r="D33" s="52">
         <v>46.07</v>
       </c>
-      <c r="E33" s="4">
+      <c r="E33" s="52">
         <f>0.000789*1000</f>
         <v>0.78900000000000003</v>
       </c>
-      <c r="F33" s="12">
+      <c r="F33" s="8">
         <f t="shared" si="4"/>
         <v>5.8390367553865653E-2</v>
       </c>
@@ -4617,22 +4624,22 @@
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="C34" s="1">
         <v>0.12623999999999999</v>
       </c>
-      <c r="D34" s="5">
+      <c r="D34" s="52">
         <v>61.206800000000001</v>
       </c>
-      <c r="E34" s="4">
+      <c r="E34" s="52">
         <f>0.00084175*1000</f>
         <v>0.84175</v>
       </c>
-      <c r="F34" s="12">
+      <c r="F34" s="8">
         <f t="shared" si="4"/>
         <v>7.2713751113751113E-2</v>
       </c>
@@ -4642,22 +4649,22 @@
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="C35" s="1">
         <v>160</v>
       </c>
-      <c r="D35" s="5">
+      <c r="D35" s="52">
         <v>953.52809999999999</v>
       </c>
-      <c r="E35" s="4">
+      <c r="E35" s="52">
         <f>0.0025*1000</f>
         <v>2.5</v>
       </c>
-      <c r="F35" s="12">
+      <c r="F35" s="8">
         <f t="shared" si="4"/>
         <v>0.38141123999999998</v>
       </c>
@@ -4667,22 +4674,22 @@
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="C36" s="1">
         <v>2</v>
       </c>
-      <c r="D36" s="5">
+      <c r="D36" s="52">
         <v>852.68320000000006</v>
       </c>
-      <c r="E36" s="4">
+      <c r="E36" s="52">
         <f>0.001*1000</f>
         <v>1</v>
       </c>
-      <c r="F36" s="12">
+      <c r="F36" s="8">
         <f t="shared" si="4"/>
         <v>0.85268320000000009</v>
       </c>
@@ -4691,104 +4698,104 @@
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A37" s="29" t="s">
+      <c r="A37" s="24" t="s">
+        <v>195</v>
+      </c>
+      <c r="B37" s="24" t="s">
         <v>197</v>
       </c>
-      <c r="B37" s="29" t="s">
-        <v>199</v>
-      </c>
-      <c r="C37" s="29">
+      <c r="C37" s="24">
         <v>920</v>
       </c>
-      <c r="D37" s="30">
+      <c r="D37" s="54">
         <v>412.91</v>
       </c>
-      <c r="E37" s="31">
+      <c r="E37" s="54">
         <f>0.001556*1000</f>
         <v>1.556</v>
       </c>
-      <c r="F37" s="32">
+      <c r="F37" s="25">
         <f>D37/(E37 * 1000)</f>
         <v>0.26536632390745502</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A38" s="29" t="s">
+      <c r="A38" s="24" t="s">
+        <v>196</v>
+      </c>
+      <c r="B38" s="24" t="s">
         <v>198</v>
       </c>
-      <c r="B38" s="29" t="s">
-        <v>200</v>
-      </c>
-      <c r="C38" s="29">
+      <c r="C38" s="24">
         <v>1150</v>
       </c>
-      <c r="D38" s="30">
+      <c r="D38" s="54">
         <v>278.13</v>
       </c>
-      <c r="E38" s="31">
+      <c r="E38" s="54">
         <f>0.00321*1000</f>
         <v>3.21</v>
       </c>
-      <c r="F38" s="32">
+      <c r="F38" s="25">
         <f>D38/(E38 * 1000)</f>
         <v>8.6644859813084105E-2</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B39" s="1"/>
       <c r="C39" s="1">
         <v>12</v>
       </c>
-      <c r="D39" s="5"/>
-      <c r="E39" s="4">
+      <c r="D39" s="52"/>
+      <c r="E39" s="52">
         <f>0.001*1000</f>
         <v>1</v>
       </c>
-      <c r="F39" s="6"/>
+      <c r="F39" s="4"/>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="C40" s="1">
         <v>175</v>
       </c>
-      <c r="D40" s="5">
+      <c r="D40" s="52">
         <v>741.30799999999999</v>
       </c>
-      <c r="E40" s="4">
+      <c r="E40" s="52">
         <f>0.05*1000</f>
         <v>50</v>
       </c>
-      <c r="F40" s="12">
+      <c r="F40" s="8">
         <f t="shared" ref="F40:F72" si="5">D40/(E40 * 1000)</f>
         <v>1.482616E-2</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="C41" s="1">
         <v>1.0175999999999999E-2</v>
       </c>
-      <c r="D41" s="5">
+      <c r="D41" s="52">
         <v>19</v>
       </c>
-      <c r="E41" s="4">
+      <c r="E41" s="52">
         <f>0.000001696*1000</f>
         <v>1.696E-3</v>
       </c>
-      <c r="F41" s="12">
+      <c r="F41" s="8">
         <f t="shared" si="5"/>
         <v>11.202830188679245</v>
       </c>
@@ -4798,22 +4805,22 @@
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="C42" s="1">
         <v>0.238874700854701</v>
       </c>
-      <c r="D42" s="5">
+      <c r="D42" s="52">
         <v>103.14</v>
       </c>
-      <c r="E42" s="4">
+      <c r="E42" s="52">
         <f xml:space="preserve"> 0.00028102905982906*1000</f>
         <v>0.28102905982906001</v>
       </c>
-      <c r="F42" s="12">
+      <c r="F42" s="8">
         <f t="shared" si="5"/>
         <v>0.36700830890135128</v>
       </c>
@@ -4823,45 +4830,45 @@
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="C43" s="1">
         <v>150</v>
       </c>
-      <c r="D43" s="5">
+      <c r="D43" s="52">
         <f>5.03</f>
         <v>5.03</v>
       </c>
-      <c r="E43" s="4">
+      <c r="E43" s="52">
         <f>0.000216*1000</f>
         <v>0.216</v>
       </c>
-      <c r="F43" s="12">
+      <c r="F43" s="8">
         <f t="shared" si="5"/>
         <v>2.3287037037037037E-2</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="C44" s="1">
         <v>2</v>
       </c>
-      <c r="D44" s="5">
+      <c r="D44" s="52">
         <v>92.09</v>
       </c>
-      <c r="E44" s="4">
+      <c r="E44" s="52">
         <f>0.012*1000</f>
         <v>12</v>
       </c>
-      <c r="F44" s="12">
+      <c r="F44" s="8">
         <f t="shared" si="5"/>
         <v>7.6741666666666668E-3</v>
       </c>
@@ -4871,22 +4878,22 @@
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="C45" s="1">
         <v>0.01</v>
       </c>
-      <c r="D45" s="5">
+      <c r="D45" s="52">
         <v>172.14</v>
       </c>
-      <c r="E45" s="4">
+      <c r="E45" s="52">
         <f>0.0055*1000</f>
         <v>5.5</v>
       </c>
-      <c r="F45" s="12">
+      <c r="F45" s="8">
         <f t="shared" si="5"/>
         <v>3.1298181818181815E-2</v>
       </c>
@@ -4896,22 +4903,22 @@
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C46" s="1">
         <v>0.11126999999999999</v>
       </c>
-      <c r="D46" s="5">
+      <c r="D46" s="52">
         <v>3.016</v>
       </c>
-      <c r="E46" s="4">
+      <c r="E46" s="52">
         <f>0.000000125*1000</f>
         <v>1.25E-4</v>
       </c>
-      <c r="F46" s="12">
+      <c r="F46" s="8">
         <f t="shared" si="5"/>
         <v>24.128</v>
       </c>
@@ -4921,22 +4928,22 @@
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C47" s="1">
         <v>9.0999999999999993E-6</v>
       </c>
-      <c r="D47" s="5">
+      <c r="D47" s="52">
         <v>4.0019999999999998</v>
       </c>
-      <c r="E47" s="4">
+      <c r="E47" s="52">
         <f>0.0000001786*1000</f>
         <v>1.786E-4</v>
       </c>
-      <c r="F47" s="12">
+      <c r="F47" s="8">
         <f t="shared" si="5"/>
         <v>22.407614781634937</v>
       </c>
@@ -4946,22 +4953,22 @@
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="C48" s="1">
         <v>2.1465000000000001</v>
       </c>
-      <c r="D48" s="5">
+      <c r="D48" s="52">
         <v>34.01</v>
       </c>
-      <c r="E48" s="4">
+      <c r="E48" s="52">
         <f>0.001431*1000</f>
         <v>1.431</v>
       </c>
-      <c r="F48" s="12">
+      <c r="F48" s="8">
         <f t="shared" si="5"/>
         <v>2.3766596785464708E-2</v>
       </c>
@@ -4971,22 +4978,22 @@
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="C49" s="1">
         <v>1.8585</v>
       </c>
-      <c r="D49" s="5">
+      <c r="D49" s="52">
         <v>2468.0700000000002</v>
       </c>
-      <c r="E49" s="4">
+      <c r="E49" s="52">
         <f>0.00177*1000</f>
         <v>1.77</v>
       </c>
-      <c r="F49" s="12">
+      <c r="F49" s="8">
         <f t="shared" si="5"/>
         <v>1.3943898305084748</v>
       </c>
@@ -4996,22 +5003,22 @@
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="C50" s="1">
         <v>0.5</v>
       </c>
-      <c r="D50" s="5">
+      <c r="D50" s="52">
         <v>1009.6214</v>
       </c>
-      <c r="E50" s="4">
+      <c r="E50" s="52">
         <f>0.0015*1000</f>
         <v>1.5</v>
       </c>
-      <c r="F50" s="12">
+      <c r="F50" s="8">
         <f t="shared" si="5"/>
         <v>0.6730809333333333</v>
       </c>
@@ -5021,23 +5028,23 @@
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="C51" s="1">
         <v>2.008</v>
       </c>
-      <c r="D51" s="5">
+      <c r="D51" s="52">
         <f>(14.007*2)+(1.008*4)</f>
         <v>32.045999999999999</v>
       </c>
-      <c r="E51" s="4">
+      <c r="E51" s="52">
         <f>0.001004*1000</f>
         <v>1.004</v>
       </c>
-      <c r="F51" s="12">
+      <c r="F51" s="8">
         <f t="shared" si="5"/>
         <v>3.1918326693227091E-2</v>
       </c>
@@ -5047,72 +5054,72 @@
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="C52" s="1">
         <v>5.5835999999999999E-5</v>
       </c>
-      <c r="D52" s="5">
+      <c r="D52" s="52">
         <v>1.01</v>
       </c>
-      <c r="E52" s="4">
+      <c r="E52" s="52">
         <f>0.0000000899*1000</f>
         <v>8.9900000000000003E-5</v>
       </c>
-      <c r="F52" s="12">
+      <c r="F52" s="8">
         <f t="shared" si="5"/>
         <v>11.234705228031144</v>
       </c>
-      <c r="G52" s="8">
+      <c r="G52" s="6">
         <v>13.59</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="C53" s="1">
         <v>0.31773000000000001</v>
       </c>
-      <c r="D53" s="5">
+      <c r="D53" s="52">
         <v>63.01</v>
       </c>
-      <c r="E53" s="4">
+      <c r="E53" s="52">
         <f>0.001513*1000</f>
         <v>1.5130000000000001</v>
       </c>
-      <c r="F53" s="12">
+      <c r="F53" s="8">
         <f t="shared" si="5"/>
         <v>4.1645736946463972E-2</v>
       </c>
-      <c r="G53" s="8">
+      <c r="G53" s="6">
         <v>68.95</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C54" s="1">
         <v>4.1000000000000002E-2</v>
       </c>
-      <c r="D54" s="5">
+      <c r="D54" s="52">
         <v>170.34</v>
       </c>
-      <c r="E54" s="4">
+      <c r="E54" s="52">
         <f>0.00082*1000</f>
         <v>0.82</v>
       </c>
-      <c r="F54" s="12">
+      <c r="F54" s="8">
         <f t="shared" si="5"/>
         <v>0.20773170731707319</v>
       </c>
@@ -5122,122 +5129,122 @@
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C55" s="1">
         <v>0.60750000000000004</v>
       </c>
-      <c r="D55" s="5">
+      <c r="D55" s="52">
         <v>6.94</v>
       </c>
-      <c r="E55" s="4">
+      <c r="E55" s="52">
         <f>0.000534*1000</f>
         <v>0.53399999999999992</v>
       </c>
-      <c r="F55" s="12">
+      <c r="F55" s="8">
         <f t="shared" si="5"/>
         <v>1.2996254681647943E-2</v>
       </c>
-      <c r="G55" s="8">
+      <c r="G55" s="6">
         <v>5.39</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="C56" s="1">
         <v>4</v>
       </c>
-      <c r="D56" s="5">
+      <c r="D56" s="52">
         <v>6.94</v>
       </c>
-      <c r="E56" s="4">
+      <c r="E56" s="52">
         <f>0.000458*1000</f>
         <v>0.45800000000000002</v>
       </c>
-      <c r="F56" s="12">
+      <c r="F56" s="8">
         <f t="shared" si="5"/>
         <v>1.5152838427947599E-2</v>
       </c>
-      <c r="G56" s="8">
+      <c r="G56" s="6">
         <v>5.39</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="C57" s="1">
         <v>5</v>
       </c>
-      <c r="D57" s="5">
+      <c r="D57" s="52">
         <v>8.0079999999999991</v>
       </c>
-      <c r="E57" s="4">
+      <c r="E57" s="52">
         <f>0.00082*1000</f>
         <v>0.82</v>
       </c>
-      <c r="F57" s="12">
+      <c r="F57" s="8">
         <f t="shared" si="5"/>
         <v>9.7658536585365843E-3</v>
       </c>
-      <c r="G57" s="8">
+      <c r="G57" s="6">
         <v>18.98</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A58" s="29" t="s">
-        <v>217</v>
-      </c>
-      <c r="B58" s="29" t="s">
-        <v>436</v>
-      </c>
-      <c r="C58" s="29">
+      <c r="A58" s="24" t="s">
+        <v>215</v>
+      </c>
+      <c r="B58" s="24" t="s">
+        <v>434</v>
+      </c>
+      <c r="C58" s="24">
         <v>7</v>
       </c>
-      <c r="D58" s="30">
+      <c r="D58" s="54">
         <v>153.114</v>
       </c>
-      <c r="E58" s="31">
+      <c r="E58" s="54">
         <f>0.0086964*1000</f>
         <v>8.6964000000000006</v>
       </c>
-      <c r="F58" s="32">
+      <c r="F58" s="25">
         <f>D58/(E58 * 1000)</f>
         <v>1.7606595832758379E-2</v>
       </c>
-      <c r="G58" s="44">
+      <c r="G58" s="37">
         <v>6215.4</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C59" s="1">
         <v>0.14199999999999999</v>
       </c>
-      <c r="D59" s="5">
+      <c r="D59" s="52">
         <v>17.03</v>
       </c>
-      <c r="E59" s="4">
+      <c r="E59" s="52">
         <f>0.0007021*1000</f>
         <v>0.70209999999999995</v>
       </c>
-      <c r="F59" s="12">
+      <c r="F59" s="8">
         <f t="shared" si="5"/>
         <v>2.4255804016521866E-2</v>
       </c>
@@ -5247,22 +5254,22 @@
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C60" s="1">
         <v>1.4</v>
       </c>
-      <c r="D60" s="5">
+      <c r="D60" s="52">
         <v>39.950000000000003</v>
       </c>
-      <c r="E60" s="4">
+      <c r="E60" s="52">
         <f>0.0013954*1000</f>
         <v>1.3954</v>
       </c>
-      <c r="F60" s="12">
+      <c r="F60" s="8">
         <f t="shared" si="5"/>
         <v>2.8629783574602271E-2</v>
       </c>
@@ -5272,22 +5279,22 @@
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="C61" s="1">
         <v>2.0999999999999999E-3</v>
       </c>
-      <c r="D61" s="5">
+      <c r="D61" s="52">
         <v>28.01</v>
       </c>
-      <c r="E61" s="4">
+      <c r="E61" s="52">
         <f>0.00079*1000</f>
         <v>0.79</v>
       </c>
-      <c r="F61" s="12">
+      <c r="F61" s="8">
         <f t="shared" si="5"/>
         <v>3.5455696202531646E-2</v>
       </c>
@@ -5297,22 +5304,22 @@
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C62" s="1">
         <v>1.7247E-3</v>
       </c>
-      <c r="D62" s="5">
+      <c r="D62" s="52">
         <v>44.01</v>
       </c>
-      <c r="E62" s="4">
+      <c r="E62" s="52">
         <f>0.00117325*1000</f>
         <v>1.1732500000000001</v>
       </c>
-      <c r="F62" s="12">
+      <c r="F62" s="8">
         <f t="shared" si="5"/>
         <v>3.7511186874067751E-2</v>
       </c>
@@ -5322,22 +5329,22 @@
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C63" s="1">
         <v>0.25600000000000001</v>
       </c>
-      <c r="D63" s="5">
+      <c r="D63" s="52">
         <v>2.0139999999999998</v>
       </c>
-      <c r="E63" s="4">
+      <c r="E63" s="52">
         <f>0.0001624*1000</f>
         <v>0.16239999999999999</v>
       </c>
-      <c r="F63" s="12">
+      <c r="F63" s="8">
         <f t="shared" si="5"/>
         <v>1.2401477832512315E-2</v>
       </c>
@@ -5347,22 +5354,22 @@
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="C64" s="1">
         <v>9.0299999999999994</v>
       </c>
-      <c r="D64" s="5">
+      <c r="D64" s="52">
         <v>19</v>
       </c>
-      <c r="E64" s="4">
+      <c r="E64" s="52">
         <f>0.001505*1000</f>
         <v>1.5050000000000001</v>
       </c>
-      <c r="F64" s="12">
+      <c r="F64" s="8">
         <f t="shared" si="5"/>
         <v>1.2624584717607971E-2</v>
       </c>
@@ -5372,22 +5379,22 @@
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C65" s="1">
         <v>52.52</v>
       </c>
-      <c r="D65" s="5">
+      <c r="D65" s="52">
         <v>3.016</v>
       </c>
-      <c r="E65" s="4">
+      <c r="E65" s="52">
         <f>0.000059*1000</f>
         <v>5.8999999999999997E-2</v>
       </c>
-      <c r="F65" s="12">
+      <c r="F65" s="8">
         <f t="shared" si="5"/>
         <v>5.1118644067796613E-2</v>
       </c>
@@ -5397,22 +5404,22 @@
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C66" s="1">
         <v>1.3299999999999999E-2</v>
       </c>
-      <c r="D66" s="5">
+      <c r="D66" s="52">
         <v>4.0019999999999998</v>
       </c>
-      <c r="E66" s="4">
+      <c r="E66" s="52">
         <f>0.0001786*1000</f>
         <v>0.17860000000000001</v>
       </c>
-      <c r="F66" s="12">
+      <c r="F66" s="8">
         <f t="shared" si="5"/>
         <v>2.2407614781634933E-2</v>
       </c>
@@ -5422,22 +5429,22 @@
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="C67" s="1">
         <v>3.6749999999999998E-2</v>
       </c>
-      <c r="D67" s="5">
+      <c r="D67" s="52">
         <v>1.01</v>
       </c>
-      <c r="E67" s="4">
+      <c r="E67" s="52">
         <f>0.00007085*1000</f>
         <v>7.0849999999999996E-2</v>
       </c>
-      <c r="F67" s="12">
+      <c r="F67" s="8">
         <f t="shared" si="5"/>
         <v>1.4255469301340862E-2</v>
       </c>
@@ -5447,20 +5454,20 @@
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C68" s="1"/>
-      <c r="D68" s="5">
+      <c r="D68" s="52">
         <v>16.05</v>
       </c>
-      <c r="E68" s="4">
+      <c r="E68" s="52">
         <f>0.00042561*1000</f>
         <v>0.42560999999999999</v>
       </c>
-      <c r="F68" s="12">
+      <c r="F68" s="8">
         <f t="shared" si="5"/>
         <v>3.7710580108550079E-2</v>
       </c>
@@ -5470,22 +5477,22 @@
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="C69" s="1">
         <v>8.2399999999999997E-4</v>
       </c>
-      <c r="D69" s="5">
+      <c r="D69" s="52">
         <v>14.01</v>
       </c>
-      <c r="E69" s="4">
+      <c r="E69" s="52">
         <f>0.000824907*1000</f>
         <v>0.82490700000000006</v>
       </c>
-      <c r="F69" s="12">
+      <c r="F69" s="8">
         <f t="shared" si="5"/>
         <v>1.6983732711687499E-2</v>
       </c>
@@ -5495,22 +5502,22 @@
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="B70" s="9" t="s">
-        <v>224</v>
-      </c>
-      <c r="C70" s="9">
+        <v>62</v>
+      </c>
+      <c r="B70" s="7" t="s">
+        <v>222</v>
+      </c>
+      <c r="C70" s="7">
         <v>4.564E-2</v>
       </c>
-      <c r="D70" s="10">
+      <c r="D70" s="53">
         <v>16</v>
       </c>
-      <c r="E70" s="11">
+      <c r="E70" s="53">
         <f>0.001141*1000</f>
         <v>1.141</v>
       </c>
-      <c r="F70" s="12">
+      <c r="F70" s="8">
         <f t="shared" si="5"/>
         <v>1.4022787028921999E-2</v>
       </c>
@@ -5520,22 +5527,22 @@
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="C71" s="1">
         <v>15.8</v>
       </c>
-      <c r="D71" s="5">
+      <c r="D71" s="52">
         <v>570.41099999999994</v>
       </c>
-      <c r="E71" s="4">
+      <c r="E71" s="52">
         <f>0.00378*1000</f>
         <v>3.78</v>
       </c>
-      <c r="F71" s="6">
+      <c r="F71" s="4">
         <f t="shared" si="5"/>
         <v>0.15090238095238093</v>
       </c>
@@ -5545,22 +5552,22 @@
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="C72" s="1">
         <v>2</v>
       </c>
-      <c r="D72" s="5">
+      <c r="D72" s="52">
         <v>510.40309999999999</v>
       </c>
-      <c r="E72" s="4">
+      <c r="E72" s="52">
         <f>0.001*1000</f>
         <v>1</v>
       </c>
-      <c r="F72" s="6">
+      <c r="F72" s="4">
         <f t="shared" si="5"/>
         <v>0.5104031</v>
       </c>
@@ -5570,23 +5577,23 @@
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="C73" s="1">
         <v>1.25</v>
       </c>
-      <c r="D73" s="5">
+      <c r="D73" s="52">
         <f>D67</f>
         <v>1.01</v>
       </c>
-      <c r="E73" s="4">
+      <c r="E73" s="52">
         <f>0.007085*1000</f>
         <v>7.085</v>
       </c>
-      <c r="F73" s="12">
+      <c r="F73" s="8">
         <f t="shared" ref="F73:F99" si="6">D73/(E73 * 1000)</f>
         <v>1.425546930134086E-4</v>
       </c>
@@ -5596,22 +5603,22 @@
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C74" s="1">
         <v>1.76</v>
       </c>
-      <c r="D74" s="5">
+      <c r="D74" s="52">
         <v>159.69</v>
       </c>
-      <c r="E74" s="4">
+      <c r="E74" s="52">
         <f>0.0055*1000</f>
         <v>5.5</v>
       </c>
-      <c r="F74" s="12">
+      <c r="F74" s="8">
         <f t="shared" si="6"/>
         <v>2.9034545454545455E-2</v>
       </c>
@@ -5621,20 +5628,20 @@
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C75" s="1"/>
-      <c r="D75" s="5">
+      <c r="D75" s="52">
         <v>159.69</v>
       </c>
-      <c r="E75" s="4">
+      <c r="E75" s="52">
         <f>0.026*1000</f>
         <v>26</v>
       </c>
-      <c r="F75" s="12">
+      <c r="F75" s="8">
         <f t="shared" si="6"/>
         <v>6.1419230769230769E-3</v>
       </c>
@@ -5644,21 +5651,21 @@
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="C76" s="1"/>
-      <c r="D76" s="5">
+      <c r="D76" s="52">
         <f>55.845</f>
         <v>55.844999999999999</v>
       </c>
-      <c r="E76" s="4">
+      <c r="E76" s="52">
         <f>0.039*1000</f>
         <v>39</v>
       </c>
-      <c r="F76" s="12">
+      <c r="F76" s="8">
         <f t="shared" si="6"/>
         <v>1.4319230769230769E-3</v>
       </c>
@@ -5668,23 +5675,23 @@
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="C77" s="1">
         <v>14.24</v>
       </c>
-      <c r="D77" s="5">
+      <c r="D77" s="52">
         <f>55.845</f>
         <v>55.844999999999999</v>
       </c>
-      <c r="E77" s="4">
+      <c r="E77" s="52">
         <f>0.0078*1000</f>
         <v>7.8</v>
       </c>
-      <c r="F77" s="12">
+      <c r="F77" s="8">
         <f t="shared" si="6"/>
         <v>7.1596153846153841E-3</v>
       </c>
@@ -5694,23 +5701,23 @@
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C78" s="1">
         <v>1.8642000000000001E-3</v>
       </c>
-      <c r="D78" s="5">
+      <c r="D78" s="52">
         <f>12.02+4*1.008</f>
         <v>16.052</v>
       </c>
-      <c r="E78" s="4">
+      <c r="E78" s="52">
         <f>0.000000717*1000</f>
         <v>7.1699999999999997E-4</v>
       </c>
-      <c r="F78" s="12">
+      <c r="F78" s="8">
         <f t="shared" si="6"/>
         <v>22.387726638772666</v>
       </c>
@@ -5720,22 +5727,22 @@
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="C79" s="1">
         <v>0.8</v>
       </c>
-      <c r="D79" s="5">
+      <c r="D79" s="52">
         <v>910.77710000000002</v>
       </c>
-      <c r="E79" s="4">
+      <c r="E79" s="52">
         <f>0.0027*1000</f>
         <v>2.7</v>
       </c>
-      <c r="F79" s="12">
+      <c r="F79" s="8">
         <f t="shared" si="6"/>
         <v>0.33732485185185185</v>
       </c>
@@ -5745,22 +5752,22 @@
     </row>
     <row r="80" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="C80" s="1">
         <v>1.748</v>
       </c>
-      <c r="D80" s="5">
+      <c r="D80" s="52">
         <v>46.07</v>
       </c>
-      <c r="E80" s="4">
+      <c r="E80" s="52">
         <f>0.00088*1000</f>
         <v>0.88</v>
       </c>
-      <c r="F80" s="12">
+      <c r="F80" s="8">
         <f t="shared" si="6"/>
         <v>5.2352272727272726E-2</v>
       </c>
@@ -5769,21 +5776,21 @@
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A81" s="29" t="s">
-        <v>186</v>
-      </c>
-      <c r="B81" s="29" t="s">
-        <v>187</v>
-      </c>
-      <c r="C81" s="29"/>
-      <c r="D81" s="30">
+      <c r="A81" s="24" t="s">
+        <v>184</v>
+      </c>
+      <c r="B81" s="24" t="s">
+        <v>185</v>
+      </c>
+      <c r="C81" s="24"/>
+      <c r="D81" s="54">
         <v>60.08</v>
       </c>
-      <c r="E81" s="31">
+      <c r="E81" s="54">
         <f>0.00347*1000</f>
         <v>3.47</v>
       </c>
-      <c r="F81" s="32">
+      <c r="F81" s="25">
         <f>C81*D81/(E81 * 1000)</f>
         <v>0</v>
       </c>
@@ -5793,22 +5800,22 @@
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="C82" s="1">
         <v>0.1</v>
       </c>
-      <c r="D82" s="5">
+      <c r="D82" s="52">
         <v>387.0077</v>
       </c>
-      <c r="E82" s="4">
+      <c r="E82" s="52">
         <f>0.005*1000</f>
         <v>5</v>
       </c>
-      <c r="F82" s="12">
+      <c r="F82" s="8">
         <f t="shared" si="6"/>
         <v>7.7401540000000005E-2</v>
       </c>
@@ -5818,22 +5825,22 @@
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="C83" s="1">
         <v>0</v>
       </c>
-      <c r="D83" s="5">
+      <c r="D83" s="52">
         <v>565.95500000000004</v>
       </c>
-      <c r="E83" s="4">
+      <c r="E83" s="52">
         <f>0.001*1000</f>
         <v>1</v>
       </c>
-      <c r="F83" s="12">
+      <c r="F83" s="8">
         <f t="shared" si="6"/>
         <v>0.56595499999999999</v>
       </c>
@@ -5843,22 +5850,22 @@
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="C84" s="1">
         <v>5.0000000000000002E-5</v>
       </c>
-      <c r="D84" s="5">
+      <c r="D84" s="52">
         <v>14.01</v>
       </c>
-      <c r="E84" s="4">
+      <c r="E84" s="52">
         <f>0.000001251*1000</f>
         <v>1.2509999999999999E-3</v>
       </c>
-      <c r="F84" s="12">
+      <c r="F84" s="8">
         <f t="shared" si="6"/>
         <v>11.199040767386093</v>
       </c>
@@ -5868,22 +5875,22 @@
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="C85" s="1">
         <v>0.2175</v>
       </c>
-      <c r="D85" s="5">
+      <c r="D85" s="52">
         <v>92.04</v>
       </c>
-      <c r="E85" s="4">
+      <c r="E85" s="52">
         <f>0.00145*1000</f>
         <v>1.45</v>
       </c>
-      <c r="F85" s="12">
+      <c r="F85" s="8">
         <f t="shared" si="6"/>
         <v>6.3475862068965522E-2</v>
       </c>
@@ -5893,22 +5900,22 @@
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="C86" s="1">
         <v>4</v>
       </c>
-      <c r="D86" s="5">
+      <c r="D86" s="52">
         <v>1004.26</v>
       </c>
-      <c r="E86" s="4">
+      <c r="E86" s="52">
         <f>0.00105*1000</f>
         <v>1.05</v>
       </c>
-      <c r="F86" s="12">
+      <c r="F86" s="8">
         <f t="shared" si="6"/>
         <v>0.9564380952380952</v>
       </c>
@@ -5918,22 +5925,22 @@
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="C87" s="1">
         <v>24.06</v>
       </c>
-      <c r="D87" s="5">
+      <c r="D87" s="52">
         <v>104.01</v>
       </c>
-      <c r="E87" s="4">
+      <c r="E87" s="52">
         <f>0.001604*1000</f>
         <v>1.6039999999999999</v>
       </c>
-      <c r="F87" s="12">
+      <c r="F87" s="8">
         <f t="shared" si="6"/>
         <v>6.4844139650872837E-2</v>
       </c>
@@ -5942,22 +5949,22 @@
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A88" s="29" t="s">
-        <v>215</v>
-      </c>
-      <c r="B88" s="29" t="s">
-        <v>216</v>
-      </c>
-      <c r="C88" s="29"/>
-      <c r="D88" s="30">
+      <c r="A88" s="24" t="s">
+        <v>213</v>
+      </c>
+      <c r="B88" s="24" t="s">
+        <v>214</v>
+      </c>
+      <c r="C88" s="24"/>
+      <c r="D88" s="54">
         <f>(14.005*8)+(39.95*6)</f>
         <v>351.74</v>
       </c>
-      <c r="E88" s="31">
+      <c r="E88" s="54">
         <f>0.003310332*1000</f>
         <v>3.3103319999999998</v>
       </c>
-      <c r="F88" s="32">
+      <c r="F88" s="25">
         <f>C88*D88/(E88 * 1000)</f>
         <v>0</v>
       </c>
@@ -5967,22 +5974,22 @@
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="C89" s="1">
         <v>0.5</v>
       </c>
-      <c r="D89" s="5">
+      <c r="D89" s="52">
         <v>131.16999999999999</v>
       </c>
-      <c r="E89" s="4">
+      <c r="E89" s="52">
         <f>0.001*1000</f>
         <v>1</v>
       </c>
-      <c r="F89" s="12">
+      <c r="F89" s="8">
         <f t="shared" si="6"/>
         <v>0.13116999999999998</v>
       </c>
@@ -5992,22 +5999,22 @@
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="C90" s="1">
         <v>5.5835999999999999E-5</v>
       </c>
-      <c r="D90" s="5">
+      <c r="D90" s="52">
         <v>16</v>
       </c>
-      <c r="E90" s="4">
+      <c r="E90" s="52">
         <f>0.00000141*1000</f>
         <v>1.41E-3</v>
       </c>
-      <c r="F90" s="12">
+      <c r="F90" s="8">
         <f t="shared" si="6"/>
         <v>11.347517730496454</v>
       </c>
@@ -6017,22 +6024,22 @@
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="C91" s="1">
         <v>6.18</v>
       </c>
-      <c r="D91" s="5">
+      <c r="D91" s="52">
         <v>63.13</v>
       </c>
-      <c r="E91" s="4">
+      <c r="E91" s="52">
         <f>0.000618*1000</f>
         <v>0.61799999999999999</v>
       </c>
-      <c r="F91" s="12">
+      <c r="F91" s="8">
         <f t="shared" si="6"/>
         <v>0.10215210355987056</v>
       </c>
@@ -6042,20 +6049,20 @@
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C92" s="1"/>
-      <c r="D92" s="5">
+      <c r="D92" s="52">
         <v>30.97</v>
       </c>
-      <c r="E92" s="13">
+      <c r="E92" s="55">
         <f>$E$4</f>
         <v>5</v>
       </c>
-      <c r="F92" s="12">
+      <c r="F92" s="8">
         <f t="shared" si="6"/>
         <v>6.1939999999999999E-3</v>
       </c>
@@ -6065,20 +6072,20 @@
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="C93" s="1"/>
-      <c r="D93" s="5">
+      <c r="D93" s="52">
         <v>244</v>
       </c>
-      <c r="E93" s="4">
+      <c r="E93" s="52">
         <f>0.019816*1000</f>
         <v>19.815999999999999</v>
       </c>
-      <c r="F93" s="12">
+      <c r="F93" s="8">
         <f t="shared" si="6"/>
         <v>1.2313282196205087E-2</v>
       </c>
@@ -6088,22 +6095,22 @@
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="C94" s="1">
         <v>8</v>
       </c>
-      <c r="D94" s="5">
+      <c r="D94" s="52">
         <v>104.15</v>
       </c>
-      <c r="E94" s="4">
+      <c r="E94" s="52">
         <f>0.00104*1000</f>
         <v>1.0399999999999998</v>
       </c>
-      <c r="F94" s="12">
+      <c r="F94" s="8">
         <f t="shared" si="6"/>
         <v>0.10014423076923079</v>
       </c>
@@ -6113,22 +6120,22 @@
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="C95" s="1">
         <v>0.01</v>
       </c>
-      <c r="D95" s="5">
+      <c r="D95" s="52">
         <v>284.77100000000002</v>
       </c>
-      <c r="E95" s="4">
+      <c r="E95" s="52">
         <f>0.00174*1000</f>
         <v>1.74</v>
       </c>
-      <c r="F95" s="12">
+      <c r="F95" s="8">
         <f t="shared" si="6"/>
         <v>0.16366149425287357</v>
       </c>
@@ -6138,22 +6145,22 @@
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A96" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="C96" s="1">
         <v>140</v>
       </c>
-      <c r="D96" s="5">
+      <c r="D96" s="52">
         <v>589.29629999999997</v>
       </c>
-      <c r="E96" s="4">
+      <c r="E96" s="52">
         <f>0.0078*1000</f>
         <v>7.8</v>
       </c>
-      <c r="F96" s="12">
+      <c r="F96" s="8">
         <f t="shared" si="6"/>
         <v>7.5550807692307695E-2</v>
       </c>
@@ -6163,23 +6170,23 @@
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A97" s="1" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="C97" s="1">
         <v>7</v>
       </c>
-      <c r="D97" s="5">
+      <c r="D97" s="52">
         <f>D25+D77+D94</f>
         <v>718.46500000000003</v>
       </c>
-      <c r="E97" s="4">
+      <c r="E97" s="52">
         <f>0.00378*1000</f>
         <v>3.78</v>
       </c>
-      <c r="F97" s="12">
+      <c r="F97" s="8">
         <f t="shared" si="6"/>
         <v>0.19007010582010583</v>
       </c>
@@ -6190,22 +6197,22 @@
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="C98" s="1">
         <v>250</v>
       </c>
-      <c r="D98" s="5">
+      <c r="D98" s="52">
         <v>173.05</v>
       </c>
-      <c r="E98" s="4">
+      <c r="E98" s="52">
         <f>0.0052*1000</f>
         <v>5.2</v>
       </c>
-      <c r="F98" s="12">
+      <c r="F98" s="8">
         <f t="shared" si="6"/>
         <v>3.3278846153846159E-2</v>
       </c>
@@ -6215,23 +6222,23 @@
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="C99" s="1">
         <v>1.5</v>
       </c>
-      <c r="D99" s="5">
+      <c r="D99" s="52">
         <f>55.845</f>
         <v>55.844999999999999</v>
       </c>
-      <c r="E99" s="4">
+      <c r="E99" s="52">
         <f>0.0025*1000</f>
         <v>2.5</v>
       </c>
-      <c r="F99" s="12">
+      <c r="F99" s="8">
         <f t="shared" si="6"/>
         <v>2.2338E-2</v>
       </c>
@@ -6241,21 +6248,21 @@
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="C100" s="1"/>
-      <c r="D100" s="5">
+      <c r="D100" s="52">
         <f>55.845*2</f>
         <v>111.69</v>
       </c>
-      <c r="E100" s="4">
+      <c r="E100" s="52">
         <f>0.004*1000</f>
         <v>4</v>
       </c>
-      <c r="F100" s="12">
+      <c r="F100" s="8">
         <f t="shared" ref="F100:F105" si="7">D100/(E100 * 1000)</f>
         <v>2.7922499999999999E-2</v>
       </c>
@@ -6265,22 +6272,22 @@
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A101" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="C101" s="1">
         <v>0.01</v>
       </c>
-      <c r="D101" s="5">
+      <c r="D101" s="52">
         <v>76.08</v>
       </c>
-      <c r="E101" s="4">
+      <c r="E101" s="52">
         <f>0.0025*1000</f>
         <v>2.5</v>
       </c>
-      <c r="F101" s="12">
+      <c r="F101" s="8">
         <f t="shared" si="7"/>
         <v>3.0432000000000001E-2</v>
       </c>
@@ -6290,22 +6297,22 @@
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A102" s="1" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C102" s="1">
         <v>0.02</v>
       </c>
-      <c r="D102" s="5">
+      <c r="D102" s="52">
         <v>28.085000000000001</v>
       </c>
-      <c r="E102" s="4">
+      <c r="E102" s="52">
         <f>0.002329*1000</f>
         <v>2.3289999999999997</v>
       </c>
-      <c r="F102" s="12">
+      <c r="F102" s="8">
         <f t="shared" si="7"/>
         <v>1.2058823529411768E-2</v>
       </c>
@@ -6315,22 +6322,22 @@
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="C103" s="1">
         <v>32</v>
       </c>
-      <c r="D103" s="5">
+      <c r="D103" s="52">
         <v>481.98500000000001</v>
       </c>
-      <c r="E103" s="4">
+      <c r="E103" s="52">
         <f>0.00378*1000</f>
         <v>3.78</v>
       </c>
-      <c r="F103" s="6">
+      <c r="F103" s="4">
         <f t="shared" si="7"/>
         <v>0.12750925925925927</v>
       </c>
@@ -6340,22 +6347,22 @@
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A104" s="1" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C104" s="1">
         <v>0.17399999999999999</v>
       </c>
-      <c r="D104" s="5">
+      <c r="D104" s="52">
         <v>186.09</v>
       </c>
-      <c r="E104" s="4">
+      <c r="E104" s="52">
         <f>0.0031*1000</f>
         <v>3.1</v>
       </c>
-      <c r="F104" s="12">
+      <c r="F104" s="8">
         <f t="shared" si="7"/>
         <v>6.0029032258064517E-2</v>
       </c>
@@ -6365,44 +6372,44 @@
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A105" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="C105" s="1">
         <v>0.3</v>
       </c>
-      <c r="D105" s="5">
+      <c r="D105" s="52">
         <v>483.19</v>
       </c>
-      <c r="E105" s="4">
+      <c r="E105" s="52">
         <f>0.0016*1000</f>
         <v>1.6</v>
       </c>
-      <c r="F105" s="6">
+      <c r="F105" s="4">
         <f t="shared" si="7"/>
         <v>0.30199375000000001</v>
       </c>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A106" s="1" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="C106" s="1">
         <v>2.5</v>
       </c>
-      <c r="D106" s="5">
+      <c r="D106" s="52">
         <v>516.76</v>
       </c>
-      <c r="E106" s="4">
+      <c r="E106" s="52">
         <f>0.001*1000</f>
         <v>1</v>
       </c>
-      <c r="F106" s="12">
+      <c r="F106" s="8">
         <f t="shared" ref="F106:F111" si="8">D106/(E106 * 1000)</f>
         <v>0.51676</v>
       </c>
@@ -6412,22 +6419,22 @@
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A107" s="1" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C107" s="1">
         <v>46.8</v>
       </c>
-      <c r="D107" s="5">
+      <c r="D107" s="52">
         <v>232.04</v>
       </c>
-      <c r="E107" s="4">
+      <c r="E107" s="52">
         <f>0.0117*1000</f>
         <v>11.700000000000001</v>
       </c>
-      <c r="F107" s="12">
+      <c r="F107" s="8">
         <f t="shared" si="8"/>
         <v>1.9832478632478629E-2</v>
       </c>
@@ -6437,22 +6444,22 @@
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A108" s="1" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C108" s="1">
         <v>0.7</v>
       </c>
-      <c r="D108" s="5">
+      <c r="D108" s="52">
         <v>270.02999999999997</v>
       </c>
-      <c r="E108" s="4">
+      <c r="E108" s="52">
         <f>0.0075*1000</f>
         <v>7.5</v>
       </c>
-      <c r="F108" s="12">
+      <c r="F108" s="8">
         <f t="shared" si="8"/>
         <v>3.6003999999999994E-2</v>
       </c>
@@ -6462,22 +6469,22 @@
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A109" s="1" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="C109" s="1">
         <v>0.79100000000000004</v>
       </c>
-      <c r="D109" s="5">
+      <c r="D109" s="52">
         <v>60.1</v>
       </c>
-      <c r="E109" s="4">
+      <c r="E109" s="52">
         <f>0.000791*1000</f>
         <v>0.79100000000000004</v>
       </c>
-      <c r="F109" s="12">
+      <c r="F109" s="8">
         <f t="shared" si="8"/>
         <v>7.5979772439949439E-2</v>
       </c>
@@ -6487,23 +6494,23 @@
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A110" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="B110" s="1" t="s">
         <v>142</v>
-      </c>
-      <c r="B110" s="1" t="s">
-        <v>144</v>
       </c>
       <c r="C110" s="1">
         <v>8.2899999999999998E-4</v>
       </c>
-      <c r="D110" s="5">
+      <c r="D110" s="52">
         <f>SUM(($D$51*0.25)+($D$109*0.75))</f>
         <v>53.086500000000001</v>
       </c>
-      <c r="E110" s="4">
+      <c r="E110" s="52">
         <f>0.000829*1000</f>
         <v>0.82899999999999996</v>
       </c>
-      <c r="F110" s="12">
+      <c r="F110" s="8">
         <f t="shared" si="8"/>
         <v>6.4036791314837152E-2</v>
       </c>
@@ -6514,22 +6521,22 @@
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A111" s="1" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="C111" s="1">
         <v>0</v>
       </c>
-      <c r="D111" s="5">
+      <c r="D111" s="52">
         <v>565.95500000000004</v>
       </c>
-      <c r="E111" s="4">
+      <c r="E111" s="52">
         <f>0.00075*1000</f>
         <v>0.75</v>
       </c>
-      <c r="F111" s="12">
+      <c r="F111" s="8">
         <f t="shared" si="8"/>
         <v>0.75460666666666676</v>
       </c>
@@ -6539,41 +6546,41 @@
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A112" s="1" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="C112" s="1">
         <v>0</v>
       </c>
-      <c r="D112" s="5">
+      <c r="D112" s="52">
         <v>78.08</v>
       </c>
-      <c r="E112" s="4">
+      <c r="E112" s="52">
         <f>0.001005*1000</f>
         <v>1.0050000000000001</v>
       </c>
-      <c r="F112" s="6"/>
+      <c r="F112" s="4"/>
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A113" s="1" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C113" s="1">
         <v>8.0000000000000004E-4</v>
       </c>
-      <c r="D113" s="5">
+      <c r="D113" s="52">
         <v>18.02</v>
       </c>
-      <c r="E113" s="4">
+      <c r="E113" s="52">
         <f>0.001*1000</f>
         <v>1</v>
       </c>
-      <c r="F113" s="12">
+      <c r="F113" s="8">
         <f t="shared" ref="F113:F114" si="9">D113/(E113 * 1000)</f>
         <v>1.8020000000000001E-2</v>
       </c>
@@ -6583,472 +6590,476 @@
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A114" s="1" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="B114" s="1"/>
       <c r="C114" s="1"/>
-      <c r="D114" s="5">
+      <c r="D114" s="52">
         <v>117.49</v>
       </c>
-      <c r="E114" s="4"/>
-      <c r="F114" s="12" t="e">
-        <f t="shared" si="9"/>
-        <v>#DIV/0!</v>
-      </c>
+      <c r="E114" s="52"/>
+      <c r="F114" s="8" t="str">
+        <f>IFERROR(D114/(E114 * 1000),"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="115" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E115" s="37"/>
     </row>
     <row r="116" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A116" s="1" t="s">
-        <v>84</v>
-      </c>
+        <v>82</v>
+      </c>
+      <c r="E116" s="37"/>
     </row>
     <row r="117" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A117" s="24" t="s">
-        <v>85</v>
-      </c>
-      <c r="D117" s="25"/>
-      <c r="E117" s="4">
+      <c r="A117" s="19" t="s">
+        <v>83</v>
+      </c>
+      <c r="D117" s="20"/>
+      <c r="E117" s="52">
         <f t="shared" ref="E117:E126" si="10">F117*1000</f>
         <v>5</v>
       </c>
-      <c r="F117" s="6">
+      <c r="F117" s="4">
         <v>5.0000000000000001E-3</v>
       </c>
     </row>
     <row r="118" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A118" s="24" t="s">
-        <v>93</v>
-      </c>
-      <c r="E118" s="4">
+      <c r="A118" s="19" t="s">
+        <v>91</v>
+      </c>
+      <c r="E118" s="52">
         <f t="shared" si="10"/>
         <v>19.3</v>
       </c>
-      <c r="F118" s="6">
+      <c r="F118" s="4">
         <v>1.9300000000000001E-2</v>
       </c>
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A119" s="24" t="s">
-        <v>43</v>
-      </c>
-      <c r="E119" s="4">
+      <c r="A119" s="19" t="s">
+        <v>41</v>
+      </c>
+      <c r="E119" s="52">
         <f t="shared" si="10"/>
         <v>54.4</v>
       </c>
-      <c r="F119" s="6">
+      <c r="F119" s="4">
         <v>5.4399999999999997E-2</v>
       </c>
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A120" s="24" t="s">
-        <v>86</v>
-      </c>
-      <c r="E120" s="4">
+      <c r="A120" s="19" t="s">
+        <v>84</v>
+      </c>
+      <c r="E120" s="52">
         <f t="shared" si="10"/>
         <v>5</v>
       </c>
-      <c r="F120" s="6">
+      <c r="F120" s="4">
         <v>5.0000000000000001E-3</v>
       </c>
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A121" s="24" t="s">
-        <v>95</v>
-      </c>
-      <c r="E121" s="4">
+      <c r="A121" s="19" t="s">
+        <v>93</v>
+      </c>
+      <c r="E121" s="52">
         <f t="shared" si="10"/>
         <v>7</v>
       </c>
-      <c r="F121" s="6">
+      <c r="F121" s="4">
         <v>7.0000000000000001E-3</v>
       </c>
     </row>
     <row r="122" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A122" s="24" t="s">
-        <v>129</v>
-      </c>
-      <c r="E122" s="4">
+      <c r="A122" s="19" t="s">
+        <v>127</v>
+      </c>
+      <c r="E122" s="52">
         <f t="shared" si="10"/>
         <v>0.53399999999999992</v>
       </c>
-      <c r="F122" s="6">
+      <c r="F122" s="4">
         <v>5.3399999999999997E-4</v>
       </c>
     </row>
     <row r="123" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A123" s="24" t="s">
-        <v>87</v>
-      </c>
-      <c r="E123" s="4">
+      <c r="A123" s="19" t="s">
+        <v>85</v>
+      </c>
+      <c r="E123" s="52">
         <f t="shared" si="10"/>
         <v>6.0000000000000005E-2</v>
       </c>
-      <c r="F123" s="6">
+      <c r="F123" s="4">
         <v>6.0000000000000002E-5</v>
       </c>
     </row>
     <row r="124" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A124" s="24" t="s">
-        <v>91</v>
-      </c>
-      <c r="E124" s="4">
+      <c r="A124" s="19" t="s">
+        <v>89</v>
+      </c>
+      <c r="E124" s="52">
         <f t="shared" si="10"/>
         <v>2.5</v>
       </c>
-      <c r="F124" s="6">
+      <c r="F124" s="4">
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
     <row r="125" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A125" s="24" t="s">
-        <v>53</v>
-      </c>
-      <c r="E125" s="4">
+      <c r="A125" s="19" t="s">
+        <v>51</v>
+      </c>
+      <c r="E125" s="52">
         <f t="shared" si="10"/>
         <v>5.0108799999999993</v>
       </c>
-      <c r="F125" s="6">
+      <c r="F125" s="4">
         <v>5.0108799999999997E-3</v>
       </c>
     </row>
     <row r="126" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A126" s="24" t="s">
-        <v>96</v>
-      </c>
-      <c r="E126" s="4">
+      <c r="A126" s="19" t="s">
+        <v>94</v>
+      </c>
+      <c r="E126" s="52">
         <f t="shared" si="10"/>
         <v>4.3499999999999996</v>
       </c>
-      <c r="F126" s="6">
+      <c r="F126" s="4">
         <v>4.3499999999999997E-3</v>
       </c>
     </row>
     <row r="127" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A127" s="24" t="s">
-        <v>414</v>
-      </c>
-      <c r="E127" s="4">
+      <c r="A127" s="19" t="s">
+        <v>412</v>
+      </c>
+      <c r="E127" s="52">
         <f t="shared" ref="E127:E152" si="11">F127*1000</f>
         <v>6.24</v>
       </c>
-      <c r="F127" s="6">
+      <c r="F127" s="4">
         <v>6.2399999999999999E-3</v>
       </c>
     </row>
     <row r="128" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A128" s="24" t="s">
-        <v>90</v>
-      </c>
-      <c r="E128" s="4">
+      <c r="A128" s="19" t="s">
+        <v>88</v>
+      </c>
+      <c r="E128" s="52">
         <f t="shared" si="11"/>
         <v>0.216</v>
       </c>
-      <c r="F128" s="6">
+      <c r="F128" s="4">
         <v>2.1599999999999999E-4</v>
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A129" s="24" t="s">
-        <v>44</v>
-      </c>
-      <c r="E129" s="4">
+      <c r="A129" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="E129" s="52">
         <f t="shared" si="11"/>
         <v>23.125</v>
       </c>
-      <c r="F129" s="6">
+      <c r="F129" s="4">
         <v>2.3125E-2</v>
       </c>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A130" s="24" t="s">
-        <v>45</v>
-      </c>
-      <c r="E130" s="4">
+      <c r="A130" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="E130" s="52">
         <f t="shared" si="11"/>
         <v>5.25</v>
       </c>
-      <c r="F130" s="6">
+      <c r="F130" s="4">
         <v>5.2500000000000003E-3</v>
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A131" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="E131" s="4">
+      <c r="A131" s="19" t="s">
+        <v>44</v>
+      </c>
+      <c r="E131" s="52">
         <f t="shared" si="11"/>
         <v>5</v>
       </c>
-      <c r="F131" s="6">
+      <c r="F131" s="4">
         <v>5.0000000000000001E-3</v>
       </c>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A132" s="24" t="s">
-        <v>128</v>
-      </c>
-      <c r="E132" s="4">
+      <c r="A132" s="19" t="s">
+        <v>126</v>
+      </c>
+      <c r="E132" s="52">
         <f t="shared" si="11"/>
         <v>1</v>
       </c>
-      <c r="F132" s="6">
+      <c r="F132" s="4">
         <v>1E-3</v>
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A133" s="24" t="s">
-        <v>47</v>
-      </c>
-      <c r="E133" s="4">
+      <c r="A133" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="E133" s="52">
         <f t="shared" si="11"/>
         <v>12.5</v>
       </c>
-      <c r="F133" s="6">
+      <c r="F133" s="4">
         <v>1.2500000000000001E-2</v>
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A134" s="24" t="s">
-        <v>92</v>
-      </c>
-      <c r="E134" s="4">
+      <c r="A134" s="19" t="s">
+        <v>90</v>
+      </c>
+      <c r="E134" s="52">
         <f t="shared" si="11"/>
         <v>2.4</v>
       </c>
-      <c r="F134" s="6">
+      <c r="F134" s="4">
         <v>2.3999999999999998E-3</v>
       </c>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A135" s="24" t="s">
-        <v>48</v>
-      </c>
-      <c r="E135" s="4">
+      <c r="A135" s="19" t="s">
+        <v>46</v>
+      </c>
+      <c r="E135" s="52">
         <f t="shared" si="11"/>
         <v>13.5</v>
       </c>
-      <c r="F135" s="6">
+      <c r="F135" s="4">
         <v>1.35E-2</v>
       </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A136" s="24" t="s">
-        <v>49</v>
-      </c>
-      <c r="E136" s="4">
+      <c r="A136" s="19" t="s">
+        <v>47</v>
+      </c>
+      <c r="E136" s="52">
         <f t="shared" si="11"/>
         <v>8.6</v>
       </c>
-      <c r="F136" s="6">
+      <c r="F136" s="4">
         <v>8.6E-3</v>
       </c>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A137" s="24" t="s">
-        <v>151</v>
-      </c>
-      <c r="E137" s="4">
+      <c r="A137" s="19" t="s">
+        <v>149</v>
+      </c>
+      <c r="E137" s="52">
         <f t="shared" si="11"/>
         <v>19.099999999999998</v>
       </c>
-      <c r="F137" s="6">
+      <c r="F137" s="4">
         <v>1.9099999999999999E-2</v>
       </c>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A138" s="24" t="s">
-        <v>152</v>
-      </c>
-      <c r="E138" s="4">
+      <c r="A138" s="19" t="s">
+        <v>150</v>
+      </c>
+      <c r="E138" s="52">
         <f t="shared" si="11"/>
         <v>10.97</v>
       </c>
-      <c r="F138" s="6">
+      <c r="F138" s="4">
         <v>1.0970000000000001E-2</v>
       </c>
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A139" s="24" t="s">
-        <v>50</v>
+      <c r="A139" s="19" t="s">
+        <v>48</v>
       </c>
       <c r="B139" s="1"/>
       <c r="C139" s="1"/>
       <c r="D139" s="3"/>
-      <c r="E139" s="4">
+      <c r="E139" s="52">
         <f t="shared" si="11"/>
         <v>5.7050000000000001</v>
       </c>
-      <c r="F139" s="6">
+      <c r="F139" s="4">
         <v>5.705E-3</v>
       </c>
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A140" s="24" t="s">
-        <v>51</v>
+      <c r="A140" s="19" t="s">
+        <v>49</v>
       </c>
       <c r="B140" s="1"/>
       <c r="C140" s="1"/>
       <c r="D140" s="3"/>
-      <c r="E140" s="4">
+      <c r="E140" s="52">
         <f t="shared" si="11"/>
         <v>13.5</v>
       </c>
-      <c r="F140" s="6">
+      <c r="F140" s="4">
         <v>1.35E-2</v>
       </c>
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A141" s="24" t="s">
-        <v>55</v>
+      <c r="A141" s="19" t="s">
+        <v>53</v>
       </c>
       <c r="B141" s="1"/>
       <c r="C141" s="1"/>
       <c r="D141" s="3"/>
-      <c r="E141" s="4">
+      <c r="E141" s="52">
         <f t="shared" si="11"/>
         <v>0.35399999999999998</v>
       </c>
-      <c r="F141" s="6">
+      <c r="F141" s="4">
         <v>3.5399999999999999E-4</v>
       </c>
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A142" s="24" t="s">
-        <v>88</v>
+      <c r="A142" s="19" t="s">
+        <v>86</v>
       </c>
       <c r="B142" s="1"/>
       <c r="C142" s="1"/>
       <c r="D142" s="3"/>
-      <c r="E142" s="4">
+      <c r="E142" s="52">
         <f t="shared" si="11"/>
         <v>2.12805</v>
       </c>
-      <c r="F142" s="6">
+      <c r="F142" s="4">
         <v>2.1280499999999998E-3</v>
       </c>
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A143" s="24" t="s">
-        <v>98</v>
+      <c r="A143" s="19" t="s">
+        <v>96</v>
       </c>
       <c r="B143" s="1"/>
       <c r="C143" s="1"/>
       <c r="D143" s="3"/>
-      <c r="E143" s="4">
+      <c r="E143" s="52">
         <f t="shared" si="11"/>
         <v>1.08</v>
       </c>
-      <c r="F143" s="6">
+      <c r="F143" s="4">
         <v>1.08E-3</v>
       </c>
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A144" s="24" t="s">
-        <v>89</v>
+      <c r="A144" s="19" t="s">
+        <v>87</v>
       </c>
       <c r="B144" s="1"/>
       <c r="C144" s="1"/>
       <c r="D144" s="3"/>
-      <c r="E144" s="4">
+      <c r="E144" s="52">
         <f t="shared" si="11"/>
         <v>4.1000000000000005</v>
       </c>
-      <c r="F144" s="6">
+      <c r="F144" s="4">
         <v>4.1000000000000003E-3</v>
       </c>
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A145" s="24" t="s">
-        <v>38</v>
-      </c>
-      <c r="E145" s="4">
+      <c r="A145" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="E145" s="52">
         <f t="shared" si="11"/>
         <v>12.5</v>
       </c>
-      <c r="F145" s="6">
+      <c r="F145" s="4">
         <v>1.2500000000000001E-2</v>
       </c>
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A146" s="24" t="s">
-        <v>57</v>
-      </c>
-      <c r="E146" s="4">
+      <c r="A146" s="19" t="s">
+        <v>55</v>
+      </c>
+      <c r="E146" s="52">
         <f t="shared" si="11"/>
         <v>4.5999999999999996</v>
       </c>
-      <c r="F146" s="6">
+      <c r="F146" s="4">
         <v>4.5999999999999999E-3</v>
       </c>
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A147" s="24" t="s">
-        <v>99</v>
-      </c>
-      <c r="E147" s="4">
+      <c r="A147" s="19" t="s">
+        <v>97</v>
+      </c>
+      <c r="E147" s="52">
         <f t="shared" si="11"/>
         <v>1</v>
       </c>
-      <c r="F147" s="6">
+      <c r="F147" s="4">
         <v>1E-3</v>
       </c>
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A148" s="24" t="s">
-        <v>100</v>
-      </c>
-      <c r="E148" s="4">
+      <c r="A148" s="19" t="s">
+        <v>98</v>
+      </c>
+      <c r="E148" s="52">
         <f t="shared" si="11"/>
         <v>1</v>
       </c>
-      <c r="F148" s="6">
+      <c r="F148" s="4">
         <v>1E-3</v>
       </c>
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A149" s="24" t="s">
-        <v>94</v>
-      </c>
-      <c r="E149" s="4">
+      <c r="A149" s="19" t="s">
+        <v>92</v>
+      </c>
+      <c r="E149" s="52">
         <f t="shared" si="11"/>
         <v>7.5</v>
       </c>
-      <c r="F149" s="6">
+      <c r="F149" s="4">
         <v>7.4999999999999997E-3</v>
       </c>
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A150" s="24" t="s">
-        <v>97</v>
-      </c>
-      <c r="E150" s="4">
+      <c r="A150" s="19" t="s">
+        <v>95</v>
+      </c>
+      <c r="E150" s="52">
         <f t="shared" si="11"/>
         <v>4.3499999999999996</v>
       </c>
-      <c r="F150" s="6">
+      <c r="F150" s="4">
         <v>4.3499999999999997E-3</v>
       </c>
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A151" s="24" t="s">
-        <v>102</v>
-      </c>
-      <c r="E151" s="4">
+      <c r="A151" s="19" t="s">
+        <v>100</v>
+      </c>
+      <c r="E151" s="52">
         <f t="shared" si="11"/>
         <v>5</v>
       </c>
-      <c r="F151" s="6">
+      <c r="F151" s="4">
         <v>5.0000000000000001E-3</v>
       </c>
     </row>
     <row r="152" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A152" s="24" t="s">
-        <v>52</v>
-      </c>
-      <c r="E152" s="4">
+      <c r="A152" s="19" t="s">
+        <v>50</v>
+      </c>
+      <c r="E152" s="52">
         <f t="shared" si="11"/>
         <v>5</v>
       </c>
-      <c r="F152" s="6">
+      <c r="F152" s="4">
         <v>5.0000000000000001E-3</v>
       </c>
     </row>
@@ -7069,495 +7080,495 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="20.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="40" t="s">
-        <v>408</v>
-      </c>
-      <c r="B1" s="40"/>
-      <c r="C1" s="40"/>
-      <c r="D1" s="40"/>
-      <c r="E1" s="40"/>
-      <c r="F1" s="40"/>
-      <c r="G1" s="40"/>
+      <c r="A1" s="33" t="s">
+        <v>406</v>
+      </c>
+      <c r="B1" s="33"/>
+      <c r="C1" s="33"/>
+      <c r="D1" s="33"/>
+      <c r="E1" s="33"/>
+      <c r="F1" s="33"/>
+      <c r="G1" s="33"/>
     </row>
     <row r="2" spans="1:12" ht="16.5" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="D2" t="s">
+        <v>368</v>
+      </c>
+      <c r="F2" t="s">
         <v>370</v>
       </c>
-      <c r="F2" t="s">
-        <v>372</v>
-      </c>
       <c r="G2" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="J2" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="K2" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="L2" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A3" s="23" t="s">
-        <v>368</v>
-      </c>
-      <c r="B3" s="23" t="s">
+      <c r="A3" s="18" t="s">
+        <v>366</v>
+      </c>
+      <c r="B3" s="18" t="s">
+        <v>367</v>
+      </c>
+      <c r="C3" s="18" t="s">
+        <v>399</v>
+      </c>
+      <c r="F3" s="18" t="s">
+        <v>373</v>
+      </c>
+      <c r="G3" s="18" t="s">
         <v>369</v>
       </c>
-      <c r="C3" s="23" t="s">
-        <v>401</v>
-      </c>
-      <c r="F3" s="23" t="s">
-        <v>375</v>
-      </c>
-      <c r="G3" s="23" t="s">
-        <v>371</v>
-      </c>
     </row>
     <row r="4" spans="1:12" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="14" t="s">
-        <v>314</v>
-      </c>
-      <c r="B4" s="17" t="str">
+      <c r="A4" s="9" t="s">
+        <v>312</v>
+      </c>
+      <c r="B4" s="12" t="str">
         <f t="shared" ref="B4:B15" si="0">IFERROR(VLOOKUP(A4,$A$25:$D$139,2,FALSE),"-")</f>
         <v>Ytterbium</v>
       </c>
-      <c r="C4" s="17" t="str">
+      <c r="C4" s="12" t="str">
         <f t="shared" ref="C4:C15" si="1">IF(L4="Y","Yes","-")</f>
         <v>-</v>
       </c>
-      <c r="D4" s="14">
+      <c r="D4" s="9">
         <v>1</v>
       </c>
-      <c r="E4" s="15">
+      <c r="E4" s="10">
         <f t="shared" ref="E4:E15" si="2">D4*$D$18</f>
         <v>1</v>
       </c>
-      <c r="F4" s="15">
+      <c r="F4" s="10">
         <f t="shared" ref="F4:F15" si="3">IFERROR(E4*J4,0)</f>
         <v>6.25</v>
       </c>
-      <c r="G4" s="15">
+      <c r="G4" s="10">
         <f t="shared" ref="G4:G15" si="4">IFERROR(E4*K4,0)</f>
         <v>173.05</v>
       </c>
-      <c r="J4" s="17">
+      <c r="J4" s="12">
         <f t="shared" ref="J4:J15" si="5">IFERROR(VLOOKUP(A4,$A$25:$D$139,3,FALSE),"-")</f>
         <v>6.25</v>
       </c>
-      <c r="K4" s="17">
+      <c r="K4" s="12">
         <f t="shared" ref="K4:K15" si="6">IFERROR(VLOOKUP(A4,$A$25:$D$139,4,FALSE),"-")</f>
         <v>173.05</v>
       </c>
-      <c r="L4" s="17">
+      <c r="L4" s="12">
         <f t="shared" ref="L4:L15" si="7">IFERROR(VLOOKUP(A4,$A$25:$E$124,5,FALSE),"-")</f>
         <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="17.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="14" t="s">
-        <v>154</v>
-      </c>
-      <c r="B5" s="17" t="str">
+      <c r="A5" s="9" t="s">
+        <v>152</v>
+      </c>
+      <c r="B5" s="12" t="str">
         <f t="shared" si="0"/>
         <v>Silicon</v>
       </c>
-      <c r="C5" s="17" t="str">
+      <c r="C5" s="12" t="str">
         <f t="shared" si="1"/>
         <v>-</v>
       </c>
-      <c r="D5" s="14">
+      <c r="D5" s="9">
         <v>11</v>
       </c>
-      <c r="E5" s="15">
+      <c r="E5" s="10">
         <f t="shared" si="2"/>
         <v>11</v>
       </c>
-      <c r="F5" s="15">
+      <c r="F5" s="10">
         <f t="shared" si="3"/>
         <v>89.65</v>
       </c>
-      <c r="G5" s="15">
+      <c r="G5" s="10">
         <f t="shared" si="4"/>
         <v>308.935</v>
       </c>
-      <c r="H5" s="56"/>
-      <c r="J5" s="17">
+      <c r="H5" s="49"/>
+      <c r="J5" s="12">
         <f t="shared" si="5"/>
         <v>8.15</v>
       </c>
-      <c r="K5" s="17">
+      <c r="K5" s="12">
         <f t="shared" si="6"/>
         <v>28.085000000000001</v>
       </c>
-      <c r="L5" s="17">
+      <c r="L5" s="12">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:12" ht="17.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="14" t="s">
-        <v>495</v>
-      </c>
-      <c r="B6" s="17" t="str">
+      <c r="A6" s="9" t="s">
+        <v>493</v>
+      </c>
+      <c r="B6" s="12" t="str">
         <f t="shared" si="0"/>
         <v>Carbon</v>
       </c>
-      <c r="C6" s="17" t="str">
+      <c r="C6" s="12" t="str">
         <f t="shared" si="1"/>
         <v>-</v>
       </c>
-      <c r="D6" s="14"/>
-      <c r="E6" s="15">
+      <c r="D6" s="9"/>
+      <c r="E6" s="10">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="F6" s="15">
+      <c r="F6" s="10">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="G6" s="15">
+      <c r="G6" s="10">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="J6" s="17">
+      <c r="J6" s="12">
         <f t="shared" si="5"/>
         <v>11.26</v>
       </c>
-      <c r="K6" s="17">
+      <c r="K6" s="12">
         <f t="shared" si="6"/>
         <v>12.010999999999999</v>
       </c>
-      <c r="L6" s="17">
+      <c r="L6" s="12">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:12" ht="17.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="14"/>
-      <c r="B7" s="17" t="str">
+      <c r="A7" s="9"/>
+      <c r="B7" s="12" t="str">
         <f t="shared" si="0"/>
         <v>-</v>
       </c>
-      <c r="C7" s="17" t="str">
+      <c r="C7" s="12" t="str">
         <f t="shared" si="1"/>
         <v>-</v>
       </c>
-      <c r="D7" s="14"/>
-      <c r="E7" s="15">
+      <c r="D7" s="9"/>
+      <c r="E7" s="10">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="F7" s="15">
+      <c r="F7" s="10">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="G7" s="15">
+      <c r="G7" s="10">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="J7" s="17" t="str">
+      <c r="J7" s="12" t="str">
         <f t="shared" si="5"/>
         <v>-</v>
       </c>
-      <c r="K7" s="17" t="str">
+      <c r="K7" s="12" t="str">
         <f t="shared" si="6"/>
         <v>-</v>
       </c>
-      <c r="L7" s="17" t="str">
+      <c r="L7" s="12" t="str">
         <f t="shared" si="7"/>
         <v>-</v>
       </c>
     </row>
     <row r="8" spans="1:12" ht="17.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="14"/>
-      <c r="B8" s="17" t="str">
+      <c r="A8" s="9"/>
+      <c r="B8" s="12" t="str">
         <f t="shared" si="0"/>
         <v>-</v>
       </c>
-      <c r="C8" s="17" t="str">
+      <c r="C8" s="12" t="str">
         <f t="shared" si="1"/>
         <v>-</v>
       </c>
-      <c r="D8" s="14"/>
-      <c r="E8" s="15">
+      <c r="D8" s="9"/>
+      <c r="E8" s="10">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="F8" s="15">
+      <c r="F8" s="10">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="G8" s="15">
+      <c r="G8" s="10">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="J8" s="17" t="str">
+      <c r="J8" s="12" t="str">
         <f t="shared" si="5"/>
         <v>-</v>
       </c>
-      <c r="K8" s="17" t="str">
+      <c r="K8" s="12" t="str">
         <f t="shared" si="6"/>
         <v>-</v>
       </c>
-      <c r="L8" s="17" t="str">
+      <c r="L8" s="12" t="str">
         <f t="shared" si="7"/>
         <v>-</v>
       </c>
     </row>
     <row r="9" spans="1:12" ht="17.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="14"/>
-      <c r="B9" s="17" t="str">
+      <c r="A9" s="9"/>
+      <c r="B9" s="12" t="str">
         <f t="shared" si="0"/>
         <v>-</v>
       </c>
-      <c r="C9" s="17" t="str">
+      <c r="C9" s="12" t="str">
         <f t="shared" si="1"/>
         <v>-</v>
       </c>
-      <c r="D9" s="14"/>
-      <c r="E9" s="15">
+      <c r="D9" s="9"/>
+      <c r="E9" s="10">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="F9" s="15">
+      <c r="F9" s="10">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="G9" s="15">
+      <c r="G9" s="10">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="J9" s="17" t="str">
+      <c r="J9" s="12" t="str">
         <f t="shared" si="5"/>
         <v>-</v>
       </c>
-      <c r="K9" s="17" t="str">
+      <c r="K9" s="12" t="str">
         <f t="shared" si="6"/>
         <v>-</v>
       </c>
-      <c r="L9" s="17" t="str">
+      <c r="L9" s="12" t="str">
         <f t="shared" si="7"/>
         <v>-</v>
       </c>
     </row>
     <row r="10" spans="1:12" ht="17.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="14"/>
-      <c r="B10" s="17" t="str">
+      <c r="A10" s="9"/>
+      <c r="B10" s="12" t="str">
         <f t="shared" si="0"/>
         <v>-</v>
       </c>
-      <c r="C10" s="17" t="str">
+      <c r="C10" s="12" t="str">
         <f t="shared" si="1"/>
         <v>-</v>
       </c>
-      <c r="D10" s="14"/>
-      <c r="E10" s="15">
+      <c r="D10" s="9"/>
+      <c r="E10" s="10">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="F10" s="15">
+      <c r="F10" s="10">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="G10" s="15">
+      <c r="G10" s="10">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="J10" s="17" t="str">
+      <c r="J10" s="12" t="str">
         <f t="shared" si="5"/>
         <v>-</v>
       </c>
-      <c r="K10" s="17" t="str">
+      <c r="K10" s="12" t="str">
         <f t="shared" si="6"/>
         <v>-</v>
       </c>
-      <c r="L10" s="17" t="str">
+      <c r="L10" s="12" t="str">
         <f t="shared" si="7"/>
         <v>-</v>
       </c>
     </row>
     <row r="11" spans="1:12" ht="17.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="14"/>
-      <c r="B11" s="17" t="str">
+      <c r="A11" s="9"/>
+      <c r="B11" s="12" t="str">
         <f t="shared" si="0"/>
         <v>-</v>
       </c>
-      <c r="C11" s="17" t="str">
+      <c r="C11" s="12" t="str">
         <f t="shared" si="1"/>
         <v>-</v>
       </c>
-      <c r="D11" s="14"/>
-      <c r="E11" s="15">
+      <c r="D11" s="9"/>
+      <c r="E11" s="10">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="F11" s="15">
+      <c r="F11" s="10">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="G11" s="15">
+      <c r="G11" s="10">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="J11" s="17" t="str">
+      <c r="J11" s="12" t="str">
         <f t="shared" si="5"/>
         <v>-</v>
       </c>
-      <c r="K11" s="17" t="str">
+      <c r="K11" s="12" t="str">
         <f t="shared" si="6"/>
         <v>-</v>
       </c>
-      <c r="L11" s="17" t="str">
+      <c r="L11" s="12" t="str">
         <f t="shared" si="7"/>
         <v>-</v>
       </c>
     </row>
     <row r="12" spans="1:12" ht="17.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="14"/>
-      <c r="B12" s="17" t="str">
+      <c r="A12" s="9"/>
+      <c r="B12" s="12" t="str">
         <f t="shared" si="0"/>
         <v>-</v>
       </c>
-      <c r="C12" s="17" t="str">
+      <c r="C12" s="12" t="str">
         <f t="shared" si="1"/>
         <v>-</v>
       </c>
-      <c r="D12" s="14"/>
-      <c r="E12" s="15">
+      <c r="D12" s="9"/>
+      <c r="E12" s="10">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="F12" s="15">
+      <c r="F12" s="10">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="G12" s="15">
+      <c r="G12" s="10">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="J12" s="17" t="str">
+      <c r="J12" s="12" t="str">
         <f t="shared" si="5"/>
         <v>-</v>
       </c>
-      <c r="K12" s="17" t="str">
+      <c r="K12" s="12" t="str">
         <f t="shared" si="6"/>
         <v>-</v>
       </c>
-      <c r="L12" s="17" t="str">
+      <c r="L12" s="12" t="str">
         <f t="shared" si="7"/>
         <v>-</v>
       </c>
     </row>
     <row r="13" spans="1:12" ht="17.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="14"/>
-      <c r="B13" s="17" t="str">
+      <c r="A13" s="9"/>
+      <c r="B13" s="12" t="str">
         <f t="shared" si="0"/>
         <v>-</v>
       </c>
-      <c r="C13" s="17" t="str">
+      <c r="C13" s="12" t="str">
         <f t="shared" si="1"/>
         <v>-</v>
       </c>
-      <c r="D13" s="14"/>
-      <c r="E13" s="15">
+      <c r="D13" s="9"/>
+      <c r="E13" s="10">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="F13" s="15">
+      <c r="F13" s="10">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="G13" s="15">
+      <c r="G13" s="10">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="J13" s="17" t="str">
+      <c r="J13" s="12" t="str">
         <f t="shared" si="5"/>
         <v>-</v>
       </c>
-      <c r="K13" s="17" t="str">
+      <c r="K13" s="12" t="str">
         <f t="shared" si="6"/>
         <v>-</v>
       </c>
-      <c r="L13" s="17" t="str">
+      <c r="L13" s="12" t="str">
         <f t="shared" si="7"/>
         <v>-</v>
       </c>
     </row>
     <row r="14" spans="1:12" ht="17.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="14"/>
-      <c r="B14" s="17" t="str">
+      <c r="A14" s="9"/>
+      <c r="B14" s="12" t="str">
         <f t="shared" si="0"/>
         <v>-</v>
       </c>
-      <c r="C14" s="17" t="str">
+      <c r="C14" s="12" t="str">
         <f t="shared" si="1"/>
         <v>-</v>
       </c>
-      <c r="D14" s="14"/>
-      <c r="E14" s="15">
+      <c r="D14" s="9"/>
+      <c r="E14" s="10">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="F14" s="15">
+      <c r="F14" s="10">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="G14" s="15">
+      <c r="G14" s="10">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="J14" s="17" t="str">
+      <c r="J14" s="12" t="str">
         <f t="shared" si="5"/>
         <v>-</v>
       </c>
-      <c r="K14" s="17" t="str">
+      <c r="K14" s="12" t="str">
         <f t="shared" si="6"/>
         <v>-</v>
       </c>
-      <c r="L14" s="17" t="str">
+      <c r="L14" s="12" t="str">
         <f t="shared" si="7"/>
         <v>-</v>
       </c>
     </row>
     <row r="15" spans="1:12" ht="17.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="14"/>
-      <c r="B15" s="17" t="str">
+      <c r="A15" s="9"/>
+      <c r="B15" s="12" t="str">
         <f t="shared" si="0"/>
         <v>-</v>
       </c>
-      <c r="C15" s="17" t="str">
+      <c r="C15" s="12" t="str">
         <f t="shared" si="1"/>
         <v>-</v>
       </c>
-      <c r="D15" s="14"/>
-      <c r="E15" s="15">
+      <c r="D15" s="9"/>
+      <c r="E15" s="10">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="F15" s="15">
+      <c r="F15" s="10">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="G15" s="15">
+      <c r="G15" s="10">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="J15" s="17" t="str">
+      <c r="J15" s="12" t="str">
         <f t="shared" si="5"/>
         <v>-</v>
       </c>
-      <c r="K15" s="17" t="str">
+      <c r="K15" s="12" t="str">
         <f t="shared" si="6"/>
         <v>-</v>
       </c>
-      <c r="L15" s="17" t="str">
+      <c r="L15" s="12" t="str">
         <f t="shared" si="7"/>
         <v>-</v>
       </c>
@@ -7565,82 +7576,82 @@
     <row r="16" spans="1:12" ht="16.5" thickTop="1" x14ac:dyDescent="0.25"/>
     <row r="17" spans="1:17" x14ac:dyDescent="0.25">
       <c r="D17" t="s">
-        <v>376</v>
-      </c>
-      <c r="F17" s="23" t="s">
         <v>374</v>
       </c>
+      <c r="F17" s="18" t="s">
+        <v>372</v>
+      </c>
     </row>
     <row r="18" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="D18" s="14">
+      <c r="D18" s="9">
         <v>1</v>
       </c>
-      <c r="F18" s="39">
+      <c r="F18" s="32">
         <f>SUM(F4:F15)</f>
         <v>95.9</v>
       </c>
-      <c r="G18" s="15">
+      <c r="G18" s="10">
         <f>SUM(G4:G15)</f>
         <v>481.98500000000001</v>
       </c>
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="F19" s="43">
+      <c r="F19" s="36">
         <f>F18/20</f>
         <v>4.7949999999999999</v>
       </c>
-      <c r="N19" s="49"/>
-      <c r="P19" s="18"/>
-      <c r="Q19" s="18"/>
+      <c r="N19" s="42"/>
+      <c r="P19" s="13"/>
+      <c r="Q19" s="13"/>
     </row>
     <row r="20" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="N20" s="49"/>
-      <c r="P20" s="18"/>
-      <c r="Q20" s="18"/>
+      <c r="N20" s="42"/>
+      <c r="P20" s="13"/>
+      <c r="Q20" s="13"/>
     </row>
     <row r="21" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="N21" s="49"/>
-      <c r="P21" s="18"/>
-      <c r="Q21" s="18"/>
+      <c r="N21" s="42"/>
+      <c r="P21" s="13"/>
+      <c r="Q21" s="13"/>
     </row>
     <row r="22" spans="1:17" ht="20.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="40" t="s">
-        <v>404</v>
-      </c>
-      <c r="B22" s="40"/>
-      <c r="C22" s="40"/>
-      <c r="D22" s="40"/>
-      <c r="E22" s="40"/>
-      <c r="H22" s="46"/>
+      <c r="A22" s="33" t="s">
+        <v>402</v>
+      </c>
+      <c r="B22" s="33"/>
+      <c r="C22" s="33"/>
+      <c r="D22" s="33"/>
+      <c r="E22" s="33"/>
+      <c r="H22" s="39"/>
     </row>
     <row r="23" spans="1:17" ht="16.5" thickTop="1" x14ac:dyDescent="0.25">
       <c r="C23" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="D23" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="E23" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="J23" s="1"/>
-      <c r="N23" s="49"/>
+      <c r="N23" s="42"/>
     </row>
     <row r="24" spans="1:17" x14ac:dyDescent="0.25">
       <c r="C24" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="D24" t="s">
-        <v>371</v>
-      </c>
-      <c r="N24" s="49"/>
+        <v>369</v>
+      </c>
+      <c r="N24" s="42"/>
     </row>
     <row r="25" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A25" s="54" t="s">
-        <v>367</v>
+      <c r="A25" s="47" t="s">
+        <v>365</v>
       </c>
       <c r="B25" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C25">
         <v>13.59</v>
@@ -7649,16 +7660,16 @@
         <v>1.008</v>
       </c>
       <c r="E25" t="s">
-        <v>402</v>
-      </c>
-      <c r="N25" s="49"/>
+        <v>400</v>
+      </c>
+      <c r="N25" s="42"/>
     </row>
     <row r="26" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="B26" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="C26">
         <v>24.58</v>
@@ -7668,11 +7679,11 @@
       </c>
     </row>
     <row r="27" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A27" s="52" t="s">
-        <v>124</v>
+      <c r="A27" s="45" t="s">
+        <v>122</v>
       </c>
       <c r="B27" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C27">
         <v>5.39</v>
@@ -7682,11 +7693,11 @@
       </c>
     </row>
     <row r="28" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A28" s="53" t="s">
-        <v>189</v>
+      <c r="A28" s="46" t="s">
+        <v>187</v>
       </c>
       <c r="B28" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="C28">
         <v>9.32</v>
@@ -7697,10 +7708,10 @@
     </row>
     <row r="29" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="B29" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="C29">
         <v>8.2899999999999991</v>
@@ -7710,11 +7721,11 @@
       </c>
     </row>
     <row r="30" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A30" s="54" t="s">
-        <v>35</v>
+      <c r="A30" s="47" t="s">
+        <v>33</v>
       </c>
       <c r="B30" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C30">
         <v>11.26</v>
@@ -7724,11 +7735,11 @@
       </c>
     </row>
     <row r="31" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A31" s="54" t="s">
-        <v>365</v>
+      <c r="A31" s="47" t="s">
+        <v>363</v>
       </c>
       <c r="B31" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C31">
         <v>14.53</v>
@@ -7737,15 +7748,15 @@
         <v>14.007</v>
       </c>
       <c r="E31" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="32" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A32" s="54" t="s">
-        <v>224</v>
+      <c r="A32" s="47" t="s">
+        <v>222</v>
       </c>
       <c r="B32" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C32">
         <v>13.61</v>
@@ -7754,15 +7765,15 @@
         <v>15.999000000000001</v>
       </c>
       <c r="E32" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A33" s="54" t="s">
-        <v>225</v>
+      <c r="A33" s="47" t="s">
+        <v>223</v>
       </c>
       <c r="B33" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C33">
         <v>17.420000000000002</v>
@@ -7771,15 +7782,15 @@
         <v>18.998000000000001</v>
       </c>
       <c r="E33" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="B34" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="C34">
         <v>21.56</v>
@@ -7789,11 +7800,11 @@
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A35" s="52" t="s">
-        <v>363</v>
+      <c r="A35" s="45" t="s">
+        <v>361</v>
       </c>
       <c r="B35" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="C35">
         <v>5.13</v>
@@ -7803,11 +7814,11 @@
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A36" s="53" t="s">
-        <v>362</v>
+      <c r="A36" s="46" t="s">
+        <v>360</v>
       </c>
       <c r="B36" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="C36">
         <v>7.64</v>
@@ -7818,10 +7829,10 @@
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B37" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C37">
         <v>5.98</v>
@@ -7832,10 +7843,10 @@
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="B38" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C38">
         <v>8.15</v>
@@ -7845,11 +7856,11 @@
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A39" s="54" t="s">
-        <v>33</v>
+      <c r="A39" s="47" t="s">
+        <v>31</v>
       </c>
       <c r="B39" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C39">
         <v>10.48</v>
@@ -7859,11 +7870,11 @@
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A40" s="54" t="s">
-        <v>361</v>
+      <c r="A40" s="47" t="s">
+        <v>359</v>
       </c>
       <c r="B40" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="C40">
         <v>10.36</v>
@@ -7873,11 +7884,11 @@
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A41" s="54" t="s">
-        <v>360</v>
+      <c r="A41" s="47" t="s">
+        <v>358</v>
       </c>
       <c r="B41" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="C41">
         <v>12.96</v>
@@ -7886,15 +7897,15 @@
         <v>18.9984</v>
       </c>
       <c r="E41" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A42" s="55" t="s">
-        <v>10</v>
+      <c r="A42" s="48" t="s">
+        <v>8</v>
       </c>
       <c r="B42" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="C42">
         <v>15.75</v>
@@ -7904,11 +7915,11 @@
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A43" s="52" t="s">
-        <v>430</v>
+      <c r="A43" s="45" t="s">
+        <v>428</v>
       </c>
       <c r="B43" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="C43">
         <v>4.34</v>
@@ -7918,11 +7929,11 @@
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A44" s="53" t="s">
-        <v>223</v>
+      <c r="A44" s="46" t="s">
+        <v>221</v>
       </c>
       <c r="B44" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="C44">
         <v>6.11</v>
@@ -7932,11 +7943,11 @@
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A45" s="54" t="s">
-        <v>359</v>
+      <c r="A45" s="47" t="s">
+        <v>357</v>
       </c>
       <c r="B45" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="C45">
         <v>6.56</v>
@@ -7947,10 +7958,10 @@
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="B46" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="C46">
         <v>6.82</v>
@@ -7961,10 +7972,10 @@
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="B47" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="C47">
         <v>6.74</v>
@@ -7975,10 +7986,10 @@
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="B48" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C48">
         <v>6.76</v>
@@ -7989,10 +8000,10 @@
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B49" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="C49">
         <v>7.43</v>
@@ -8003,10 +8014,10 @@
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="B50" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="C50">
         <v>7.9</v>
@@ -8017,10 +8028,10 @@
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="B51" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="C51">
         <v>7.88</v>
@@ -8031,10 +8042,10 @@
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="B52" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="C52">
         <v>7.63</v>
@@ -8045,10 +8056,10 @@
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="B53" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="C53">
         <v>7.72</v>
@@ -8059,10 +8070,10 @@
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="B54" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="C54">
         <v>9.39</v>
@@ -8073,10 +8084,10 @@
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="B55" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="C55">
         <v>5.99</v>
@@ -8087,10 +8098,10 @@
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="B56" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="C56">
         <v>7.89</v>
@@ -8101,10 +8112,10 @@
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="B57" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="C57">
         <v>9.7799999999999994</v>
@@ -8114,11 +8125,11 @@
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A58" s="54" t="s">
-        <v>346</v>
+      <c r="A58" s="47" t="s">
+        <v>344</v>
       </c>
       <c r="B58" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="C58">
         <v>9.75</v>
@@ -8128,11 +8139,11 @@
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A59" s="54" t="s">
-        <v>345</v>
+      <c r="A59" s="47" t="s">
+        <v>343</v>
       </c>
       <c r="B59" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="C59">
         <v>11.81</v>
@@ -8141,15 +8152,15 @@
         <v>79.900000000000006</v>
       </c>
       <c r="E59" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A60" s="55" t="s">
-        <v>344</v>
+      <c r="A60" s="48" t="s">
+        <v>342</v>
       </c>
       <c r="B60" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="C60">
         <v>13.99</v>
@@ -8159,11 +8170,11 @@
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A61" s="52" t="s">
-        <v>343</v>
+      <c r="A61" s="45" t="s">
+        <v>341</v>
       </c>
       <c r="B61" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="C61">
         <v>4.17</v>
@@ -8173,11 +8184,11 @@
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A62" s="53" t="s">
-        <v>342</v>
+      <c r="A62" s="46" t="s">
+        <v>340</v>
       </c>
       <c r="B62" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="C62">
         <v>5.69</v>
@@ -8188,10 +8199,10 @@
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="B63" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="C63">
         <v>6.21</v>
@@ -8202,10 +8213,10 @@
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="B64" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="C64">
         <v>6.63</v>
@@ -8216,10 +8227,10 @@
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="B65" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="C65">
         <v>6.75</v>
@@ -8230,10 +8241,10 @@
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="B66" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="C66">
         <v>7.09</v>
@@ -8244,10 +8255,10 @@
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="B67" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="C67">
         <v>7.28</v>
@@ -8258,10 +8269,10 @@
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="B68" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C68">
         <v>7.36</v>
@@ -8272,10 +8283,10 @@
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="B69" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="C69">
         <v>7.45</v>
@@ -8286,10 +8297,10 @@
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="B70" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C70">
         <v>8.33</v>
@@ -8300,10 +8311,10 @@
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="B71" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="C71">
         <v>7.57</v>
@@ -8314,10 +8325,10 @@
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="B72" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="C72">
         <v>8.99</v>
@@ -8328,10 +8339,10 @@
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="B73" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="C73">
         <v>5.78</v>
@@ -8342,10 +8353,10 @@
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="B74" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="C74">
         <v>7.34</v>
@@ -8356,10 +8367,10 @@
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="B75" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="C75">
         <v>8.6</v>
@@ -8370,10 +8381,10 @@
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="B76" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="C76">
         <v>9</v>
@@ -8383,11 +8394,11 @@
       </c>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A77" s="54" t="s">
-        <v>403</v>
+      <c r="A77" s="47" t="s">
+        <v>401</v>
       </c>
       <c r="B77" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="C77">
         <v>10.45</v>
@@ -8396,15 +8407,15 @@
         <v>126.9045</v>
       </c>
       <c r="E77" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A78" s="55" t="s">
-        <v>12</v>
+      <c r="A78" s="48" t="s">
+        <v>10</v>
       </c>
       <c r="B78" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="C78">
         <v>12.12</v>
@@ -8414,11 +8425,11 @@
       </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A79" s="52" t="s">
-        <v>204</v>
+      <c r="A79" s="45" t="s">
+        <v>202</v>
       </c>
       <c r="B79" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="C79">
         <v>3.89</v>
@@ -8428,11 +8439,11 @@
       </c>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A80" s="53" t="s">
-        <v>328</v>
+      <c r="A80" s="46" t="s">
+        <v>326</v>
       </c>
       <c r="B80" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="C80">
         <v>5.21</v>
@@ -8442,11 +8453,11 @@
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A81" s="51" t="s">
-        <v>327</v>
+      <c r="A81" s="44" t="s">
+        <v>325</v>
       </c>
       <c r="B81" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="C81">
         <v>5.57</v>
@@ -8456,11 +8467,11 @@
       </c>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A82" s="51" t="s">
-        <v>326</v>
+      <c r="A82" s="44" t="s">
+        <v>324</v>
       </c>
       <c r="B82" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="C82">
         <v>5.53</v>
@@ -8470,11 +8481,11 @@
       </c>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A83" s="51" t="s">
-        <v>325</v>
+      <c r="A83" s="44" t="s">
+        <v>323</v>
       </c>
       <c r="B83" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="C83">
         <v>5.47</v>
@@ -8484,11 +8495,11 @@
       </c>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A84" s="51" t="s">
-        <v>324</v>
+      <c r="A84" s="44" t="s">
+        <v>322</v>
       </c>
       <c r="B84" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="C84">
         <v>5.52</v>
@@ -8498,11 +8509,11 @@
       </c>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A85" s="51" t="s">
-        <v>323</v>
+      <c r="A85" s="44" t="s">
+        <v>321</v>
       </c>
       <c r="B85" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="C85">
         <v>5.58</v>
@@ -8512,11 +8523,11 @@
       </c>
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A86" s="51" t="s">
-        <v>322</v>
+      <c r="A86" s="44" t="s">
+        <v>320</v>
       </c>
       <c r="B86" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="C86">
         <v>5.64</v>
@@ -8526,11 +8537,11 @@
       </c>
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A87" s="51" t="s">
-        <v>321</v>
+      <c r="A87" s="44" t="s">
+        <v>319</v>
       </c>
       <c r="B87" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="C87">
         <v>5.67</v>
@@ -8540,11 +8551,11 @@
       </c>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A88" s="51" t="s">
-        <v>320</v>
+      <c r="A88" s="44" t="s">
+        <v>318</v>
       </c>
       <c r="B88" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C88">
         <v>6.15</v>
@@ -8554,11 +8565,11 @@
       </c>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A89" s="51" t="s">
-        <v>319</v>
+      <c r="A89" s="44" t="s">
+        <v>317</v>
       </c>
       <c r="B89" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="C89">
         <v>5.86</v>
@@ -8568,11 +8579,11 @@
       </c>
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A90" s="51" t="s">
-        <v>318</v>
+      <c r="A90" s="44" t="s">
+        <v>316</v>
       </c>
       <c r="B90" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="C90">
         <v>5.93</v>
@@ -8582,11 +8593,11 @@
       </c>
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A91" s="51" t="s">
-        <v>317</v>
+      <c r="A91" s="44" t="s">
+        <v>315</v>
       </c>
       <c r="B91" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="C91">
         <v>6.02</v>
@@ -8596,11 +8607,11 @@
       </c>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A92" s="51" t="s">
-        <v>316</v>
+      <c r="A92" s="44" t="s">
+        <v>314</v>
       </c>
       <c r="B92" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="C92">
         <v>6.1</v>
@@ -8610,11 +8621,11 @@
       </c>
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A93" s="51" t="s">
-        <v>315</v>
+      <c r="A93" s="44" t="s">
+        <v>313</v>
       </c>
       <c r="B93" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="C93">
         <v>6.18</v>
@@ -8624,11 +8635,11 @@
       </c>
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A94" s="51" t="s">
-        <v>314</v>
+      <c r="A94" s="44" t="s">
+        <v>312</v>
       </c>
       <c r="B94" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="C94">
         <v>6.25</v>
@@ -8638,11 +8649,11 @@
       </c>
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A95" s="51" t="s">
-        <v>313</v>
+      <c r="A95" s="44" t="s">
+        <v>311</v>
       </c>
       <c r="B95" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="C95">
         <v>5.42</v>
@@ -8653,10 +8664,10 @@
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="B96" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="C96">
         <v>6.82</v>
@@ -8667,10 +8678,10 @@
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="B97" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="C97">
         <v>7.54</v>
@@ -8681,10 +8692,10 @@
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="B98" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="C98">
         <v>7.86</v>
@@ -8695,10 +8706,10 @@
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="B99" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="C99">
         <v>7.83</v>
@@ -8709,10 +8720,10 @@
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="B100" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="C100">
         <v>8.43</v>
@@ -8723,10 +8734,10 @@
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="B101" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="C101">
         <v>8.9600000000000009</v>
@@ -8737,10 +8748,10 @@
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="B102" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="C102">
         <v>8.9499999999999993</v>
@@ -8751,10 +8762,10 @@
     </row>
     <row r="103" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="B103" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="C103">
         <v>9.2200000000000006</v>
@@ -8765,10 +8776,10 @@
     </row>
     <row r="104" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="B104" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="C104">
         <v>10.43</v>
@@ -8779,10 +8790,10 @@
     </row>
     <row r="105" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="B105" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="C105">
         <v>6.1</v>
@@ -8793,10 +8804,10 @@
     </row>
     <row r="106" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B106" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="C106">
         <v>7.41</v>
@@ -8807,10 +8818,10 @@
     </row>
     <row r="107" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="B107" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="C107">
         <v>7.28</v>
@@ -8821,10 +8832,10 @@
     </row>
     <row r="108" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="B108" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="C108">
         <v>8.41</v>
@@ -8834,11 +8845,11 @@
       </c>
     </row>
     <row r="109" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A109" s="54" t="s">
-        <v>300</v>
+      <c r="A109" s="47" t="s">
+        <v>298</v>
       </c>
       <c r="B109" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="C109">
         <v>9.31</v>
@@ -8848,11 +8859,11 @@
       </c>
     </row>
     <row r="110" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A110" s="55" t="s">
-        <v>378</v>
+      <c r="A110" s="48" t="s">
+        <v>376</v>
       </c>
       <c r="B110" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="C110">
         <v>10.74</v>
@@ -8862,11 +8873,11 @@
       </c>
     </row>
     <row r="111" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A111" s="52" t="s">
-        <v>379</v>
+      <c r="A111" s="45" t="s">
+        <v>377</v>
       </c>
       <c r="B111" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="C111">
         <v>4.07</v>
@@ -8876,11 +8887,11 @@
       </c>
     </row>
     <row r="112" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A112" s="53" t="s">
-        <v>299</v>
+      <c r="A112" s="46" t="s">
+        <v>297</v>
       </c>
       <c r="B112" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="C112">
         <v>5.27</v>
@@ -8891,10 +8902,10 @@
     </row>
     <row r="113" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="B113" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="C113">
         <v>6</v>
@@ -8905,10 +8916,10 @@
     </row>
     <row r="114" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="B114" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="D114">
         <v>268.12599999999998</v>
@@ -8916,10 +8927,10 @@
     </row>
     <row r="115" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="B115" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="D115">
         <v>269.12799999999999</v>
@@ -8927,10 +8938,10 @@
     </row>
     <row r="116" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="B116" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="D116">
         <v>270.13299999999998</v>
@@ -8938,10 +8949,10 @@
     </row>
     <row r="117" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="B117" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="D117">
         <v>269.1336</v>
@@ -8949,10 +8960,10 @@
     </row>
     <row r="118" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="B118" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="D118">
         <v>277.154</v>
@@ -8960,10 +8971,10 @@
     </row>
     <row r="119" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="B119" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="D119">
         <v>282.166</v>
@@ -8971,10 +8982,10 @@
     </row>
     <row r="120" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B120" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="D120">
         <v>282.16899999999998</v>
@@ -8982,10 +8993,10 @@
     </row>
     <row r="121" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="B121" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="D121">
         <v>286.17899999999997</v>
@@ -8993,10 +9004,10 @@
     </row>
     <row r="122" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="B122" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="D122">
         <v>286.18200000000002</v>
@@ -9004,10 +9015,10 @@
     </row>
     <row r="123" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="B123" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="D123">
         <v>290.19200000000001</v>
@@ -9015,10 +9026,10 @@
     </row>
     <row r="124" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="B124" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="D124">
         <v>290.19600000000003</v>
@@ -9026,10 +9037,10 @@
     </row>
     <row r="125" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="B125" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="D125">
         <v>293.20499999999998</v>
@@ -9037,32 +9048,32 @@
     </row>
     <row r="126" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="B126" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="D126">
         <v>294.21100000000001</v>
       </c>
     </row>
     <row r="127" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A127" s="55" t="s">
-        <v>460</v>
+      <c r="A127" s="48" t="s">
+        <v>458</v>
       </c>
       <c r="B127" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="D127">
         <v>295.21600000000001</v>
       </c>
     </row>
     <row r="128" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A128" s="50" t="s">
-        <v>380</v>
+      <c r="A128" s="43" t="s">
+        <v>378</v>
       </c>
       <c r="B128" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="C128">
         <v>5.17</v>
@@ -9072,11 +9083,11 @@
       </c>
     </row>
     <row r="129" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A129" s="50" t="s">
-        <v>202</v>
+      <c r="A129" s="43" t="s">
+        <v>200</v>
       </c>
       <c r="B129" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C129">
         <v>6.3</v>
@@ -9086,11 +9097,11 @@
       </c>
     </row>
     <row r="130" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A130" s="50" t="s">
-        <v>381</v>
+      <c r="A130" s="43" t="s">
+        <v>379</v>
       </c>
       <c r="B130" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="C130">
         <v>5.89</v>
@@ -9100,11 +9111,11 @@
       </c>
     </row>
     <row r="131" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A131" s="50" t="s">
-        <v>120</v>
+      <c r="A131" s="43" t="s">
+        <v>118</v>
       </c>
       <c r="B131" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="C131">
         <v>6.19</v>
@@ -9114,11 +9125,11 @@
       </c>
     </row>
     <row r="132" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A132" s="50" t="s">
-        <v>382</v>
+      <c r="A132" s="43" t="s">
+        <v>380</v>
       </c>
       <c r="B132" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="C132">
         <v>6.26</v>
@@ -9128,11 +9139,11 @@
       </c>
     </row>
     <row r="133" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A133" s="50" t="s">
-        <v>195</v>
+      <c r="A133" s="43" t="s">
+        <v>193</v>
       </c>
       <c r="B133" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="C133">
         <v>6.02</v>
@@ -9142,11 +9153,11 @@
       </c>
     </row>
     <row r="134" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A134" s="50" t="s">
-        <v>383</v>
+      <c r="A134" s="43" t="s">
+        <v>381</v>
       </c>
       <c r="B134" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="C134">
         <v>5.97</v>
@@ -9156,11 +9167,11 @@
       </c>
     </row>
     <row r="135" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A135" s="50" t="s">
-        <v>384</v>
+      <c r="A135" s="43" t="s">
+        <v>382</v>
       </c>
       <c r="B135" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="C135">
         <v>5.99</v>
@@ -9170,11 +9181,11 @@
       </c>
     </row>
     <row r="136" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A136" s="50" t="s">
-        <v>385</v>
+      <c r="A136" s="43" t="s">
+        <v>383</v>
       </c>
       <c r="B136" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="C136">
         <v>6.19</v>
@@ -9184,11 +9195,11 @@
       </c>
     </row>
     <row r="137" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A137" s="50" t="s">
-        <v>386</v>
+      <c r="A137" s="43" t="s">
+        <v>384</v>
       </c>
       <c r="B137" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="C137">
         <v>6.28</v>
@@ -9198,11 +9209,11 @@
       </c>
     </row>
     <row r="138" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A138" s="50" t="s">
-        <v>387</v>
+      <c r="A138" s="43" t="s">
+        <v>385</v>
       </c>
       <c r="B138" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="C138">
         <v>6.42</v>
@@ -9212,11 +9223,11 @@
       </c>
     </row>
     <row r="139" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A139" s="50" t="s">
-        <v>388</v>
+      <c r="A139" s="43" t="s">
+        <v>386</v>
       </c>
       <c r="B139" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="C139">
         <v>6.5</v>
@@ -9226,11 +9237,11 @@
       </c>
     </row>
     <row r="140" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A140" s="50" t="s">
-        <v>440</v>
+      <c r="A140" s="43" t="s">
+        <v>438</v>
       </c>
       <c r="B140" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="C140">
         <v>6.58</v>
@@ -9240,11 +9251,11 @@
       </c>
     </row>
     <row r="141" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A141" s="50" t="s">
-        <v>441</v>
+      <c r="A141" s="43" t="s">
+        <v>439</v>
       </c>
       <c r="B141" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="C141">
         <v>6.65</v>
@@ -9254,11 +9265,11 @@
       </c>
     </row>
     <row r="142" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A142" s="50" t="s">
-        <v>442</v>
+      <c r="A142" s="43" t="s">
+        <v>440</v>
       </c>
       <c r="B142" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="C142">
         <v>4.9000000000000004</v>
